--- a/data/SOL.MI.xlsx
+++ b/data/SOL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="1269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="1270">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14939069747925</t>
+    <t xml:space="preserve">7.14939212799072</t>
   </si>
   <si>
     <t xml:space="preserve">SOL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14067220687866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18862581253052</t>
+    <t xml:space="preserve">7.14067268371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18862533569336</t>
   </si>
   <si>
     <t xml:space="preserve">7.16246938705444</t>
@@ -56,19 +56,19 @@
     <t xml:space="preserve">7.0622034072876</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90962600708008</t>
+    <t xml:space="preserve">6.90962505340576</t>
   </si>
   <si>
     <t xml:space="preserve">6.90526628494263</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94885969161987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71781253814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62626552581787</t>
+    <t xml:space="preserve">6.94885873794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71781206130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62626504898071</t>
   </si>
   <si>
     <t xml:space="preserve">6.71345281600952</t>
@@ -80,97 +80,97 @@
     <t xml:space="preserve">6.36470222473145</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43009328842163</t>
+    <t xml:space="preserve">6.43009233474731</t>
   </si>
   <si>
     <t xml:space="preserve">6.41265535354614</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44752979278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20776414871216</t>
+    <t xml:space="preserve">6.44753074645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.207763671875</t>
   </si>
   <si>
     <t xml:space="preserve">6.1728892326355</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46060943603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54779577255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38213968276978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51292133331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50420331954956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6524224281311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80064105987549</t>
+    <t xml:space="preserve">6.46060752868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54779672622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38214015960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51292085647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50420236587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65242147445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80064058303833</t>
   </si>
   <si>
     <t xml:space="preserve">6.72217130661011</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79192161560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00989198684692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84423494338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07964181900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88346862792969</t>
+    <t xml:space="preserve">6.79192209243774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00989103317261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84423446655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07964134216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88346910476685</t>
   </si>
   <si>
     <t xml:space="preserve">6.9662971496582</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08835983276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73525047302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83115577697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67857789993286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57395219802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63062477111816</t>
+    <t xml:space="preserve">7.08835935592651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73524951934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83115673065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6785774230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57395267486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63062429428101</t>
   </si>
   <si>
     <t xml:space="preserve">6.68729639053345</t>
   </si>
   <si>
-    <t xml:space="preserve">6.783203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77884387969971</t>
+    <t xml:space="preserve">6.78320360183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77884340286255</t>
   </si>
   <si>
     <t xml:space="preserve">6.81371831893921</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80935907363892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7962818145752</t>
+    <t xml:space="preserve">6.80936002731323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79628133773804</t>
   </si>
   <si>
     <t xml:space="preserve">6.69601583480835</t>
@@ -179,22 +179,22 @@
     <t xml:space="preserve">6.81807851791382</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87475061416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91398429870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67421913146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55215549468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46496772766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43881273269653</t>
+    <t xml:space="preserve">6.8747501373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91398477554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67421817779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55215454101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46496725082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43881130218506</t>
   </si>
   <si>
     <t xml:space="preserve">6.73089027404785</t>
@@ -212,16 +212,16 @@
     <t xml:space="preserve">6.85731220245361</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74832725524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51728105545044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37342119216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56523418426514</t>
+    <t xml:space="preserve">6.74832773208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51728057861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37342071533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56523323059082</t>
   </si>
   <si>
     <t xml:space="preserve">6.66985893249512</t>
@@ -230,160 +230,160 @@
     <t xml:space="preserve">6.7701244354248</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86167240142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97501707077026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9416298866272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95048427581787</t>
+    <t xml:space="preserve">6.86167192459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97501564025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94162940979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95048379898071</t>
   </si>
   <si>
     <t xml:space="preserve">6.88407802581787</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90178680419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34006547927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22496128082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41975164413452</t>
+    <t xml:space="preserve">6.9017858505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34006500244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22496175765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.419753074646</t>
   </si>
   <si>
     <t xml:space="preserve">7.43745994567871</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36662817001343</t>
+    <t xml:space="preserve">7.36662769317627</t>
   </si>
   <si>
     <t xml:space="preserve">7.26037788391113</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46845006942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40204381942749</t>
+    <t xml:space="preserve">7.46845054626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40204238891602</t>
   </si>
   <si>
     <t xml:space="preserve">7.44631433486938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3843355178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04345226287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97261953353882</t>
+    <t xml:space="preserve">7.38433504104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04345178604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97261905670166</t>
   </si>
   <si>
     <t xml:space="preserve">7.1098575592041</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8707971572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20725393295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37105417251587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57027101516724</t>
+    <t xml:space="preserve">6.87079668045044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20725440979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37105464935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57027244567871</t>
   </si>
   <si>
     <t xml:space="preserve">7.69422912597656</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70308351516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71193885803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65881204605103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04396724700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61454248428345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29579401016235</t>
+    <t xml:space="preserve">7.70308446884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71193838119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65881252288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04396820068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61454200744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29579448699951</t>
   </si>
   <si>
     <t xml:space="preserve">6.99475431442261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10100507736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55256462097168</t>
+    <t xml:space="preserve">7.10100412368774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55256319046021</t>
   </si>
   <si>
     <t xml:space="preserve">7.31350326538086</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50829362869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42417860031128</t>
+    <t xml:space="preserve">7.50829219818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42418003082275</t>
   </si>
   <si>
     <t xml:space="preserve">7.37548160552979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52600240707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54371070861816</t>
+    <t xml:space="preserve">7.52600288391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54370927810669</t>
   </si>
   <si>
     <t xml:space="preserve">7.41532564163208</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21610689163208</t>
+    <t xml:space="preserve">7.21610736846924</t>
   </si>
   <si>
     <t xml:space="preserve">6.99032735824585</t>
   </si>
   <si>
-    <t xml:space="preserve">6.799964427948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75569343566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00803565979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26923370361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34449243545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46402311325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51714658737183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39319038391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45516872406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17183685302734</t>
+    <t xml:space="preserve">6.79996347427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7556939125061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0080361366272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26923179626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34449195861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46402359008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51714754104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39318990707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45516920089722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17183780670166</t>
   </si>
   <si>
     <t xml:space="preserve">7.33563804626465</t>
@@ -392,46 +392,46 @@
     <t xml:space="preserve">7.33121109008789</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39761781692505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30464839935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27808666229248</t>
+    <t xml:space="preserve">7.39761543273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30464887619019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27808618545532</t>
   </si>
   <si>
     <t xml:space="preserve">7.25152397155762</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16298294067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03017091751099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87965059280396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91064071655273</t>
+    <t xml:space="preserve">7.16298198699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03017044067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87965106964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91063976287842</t>
   </si>
   <si>
     <t xml:space="preserve">6.95491123199463</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88850498199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95933818817139</t>
+    <t xml:space="preserve">6.88850545883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95933866500854</t>
   </si>
   <si>
     <t xml:space="preserve">6.85751533508301</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77340173721313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74683904647827</t>
+    <t xml:space="preserve">6.77340126037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74683856964111</t>
   </si>
   <si>
     <t xml:space="preserve">6.82652616500854</t>
@@ -440,25 +440,25 @@
     <t xml:space="preserve">6.68486070632935</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81767225265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90621376037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01689004898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8973593711853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83538055419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86194324493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92392158508301</t>
+    <t xml:space="preserve">6.81767177581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90621328353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01688957214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89735889434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8353796005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86194276809692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92392110824585</t>
   </si>
   <si>
     <t xml:space="preserve">6.97704601287842</t>
@@ -467,10 +467,10 @@
     <t xml:space="preserve">7.00360822677612</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91506719589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91949415206909</t>
+    <t xml:space="preserve">6.91506767272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91949462890625</t>
   </si>
   <si>
     <t xml:space="preserve">6.93720245361328</t>
@@ -479,7 +479,7 @@
     <t xml:space="preserve">7.07001447677612</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98590087890625</t>
+    <t xml:space="preserve">6.98590040206909</t>
   </si>
   <si>
     <t xml:space="preserve">6.75126647949219</t>
@@ -491,13 +491,13 @@
     <t xml:space="preserve">6.64944410324097</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38382053375244</t>
+    <t xml:space="preserve">6.38382005691528</t>
   </si>
   <si>
     <t xml:space="preserve">6.37053871154785</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36168527603149</t>
+    <t xml:space="preserve">6.36168432235718</t>
   </si>
   <si>
     <t xml:space="preserve">6.37939310073853</t>
@@ -506,91 +506,91 @@
     <t xml:space="preserve">6.40595531463623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48121547698975</t>
+    <t xml:space="preserve">6.4812159538269</t>
   </si>
   <si>
     <t xml:space="preserve">6.47678804397583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54319429397583</t>
+    <t xml:space="preserve">6.54319381713867</t>
   </si>
   <si>
     <t xml:space="preserve">6.46350717544556</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24215459823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25986289978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22444581985474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64501714706421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64059066772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03902530670166</t>
+    <t xml:space="preserve">6.24215412139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25986242294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22444629669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64501762390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64059019088745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0390248298645</t>
   </si>
   <si>
     <t xml:space="preserve">6.79111003875732</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70256900787354</t>
+    <t xml:space="preserve">6.70256853103638</t>
   </si>
   <si>
     <t xml:space="preserve">6.70699548721313</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65829801559448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58303880691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05673313140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11428499221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34891939163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18511867523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12756681442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19397211074829</t>
+    <t xml:space="preserve">6.65829753875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58303785324097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05673265457153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11428594589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34891891479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18511772155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12756633758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19397258758545</t>
   </si>
   <si>
     <t xml:space="preserve">7.24267053604126</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41089820861816</t>
+    <t xml:space="preserve">7.41089868545532</t>
   </si>
   <si>
     <t xml:space="preserve">7.48173189163208</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14527463912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27365970611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1762638092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04787969589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23381662368774</t>
+    <t xml:space="preserve">7.14527416229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27365922927856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17626333236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04787921905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23381614685059</t>
   </si>
   <si>
     <t xml:space="preserve">7.29136657714844</t>
@@ -602,64 +602,64 @@
     <t xml:space="preserve">7.83589649200439</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82704067230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13693428039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27860164642334</t>
+    <t xml:space="preserve">7.8270411491394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13693618774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27860069274902</t>
   </si>
   <si>
     <t xml:space="preserve">8.32287216186523</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03120231628418</t>
+    <t xml:space="preserve">9.0312032699585</t>
   </si>
   <si>
     <t xml:space="preserve">8.53094482421875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49995517730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26089382171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92495250701904</t>
+    <t xml:space="preserve">8.49995422363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26089286804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92495346069336</t>
   </si>
   <si>
     <t xml:space="preserve">8.5884952545166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97807693481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7655782699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87182807922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56245040893555</t>
+    <t xml:space="preserve">8.97807884216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76557922363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87182903289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56244850158691</t>
   </si>
   <si>
     <t xml:space="preserve">9.25255393981934</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02234649658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85411834716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82755756378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71245384216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98692989349365</t>
+    <t xml:space="preserve">9.02234840393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8541202545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82755947113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7124547958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98693084716797</t>
   </si>
   <si>
     <t xml:space="preserve">8.8983907699585</t>
@@ -671,55 +671,55 @@
     <t xml:space="preserve">8.72130870819092</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78328609466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67703914642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75672435760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1020336151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82312965393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94266033172607</t>
+    <t xml:space="preserve">8.78328704833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67703628540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7567253112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10203456878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82312870025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94266128540039</t>
   </si>
   <si>
     <t xml:space="preserve">9.20828342437744</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43287467956543</t>
+    <t xml:space="preserve">9.43287658691406</t>
   </si>
   <si>
     <t xml:space="preserve">9.4598274230957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52271270751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3250732421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3879566192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35202217102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42389297485352</t>
+    <t xml:space="preserve">9.52271366119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32507228851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38795757293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35202407836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4238920211792</t>
   </si>
   <si>
     <t xml:space="preserve">9.29812145233154</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55864906311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67543601989746</t>
+    <t xml:space="preserve">9.55864810943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67543506622314</t>
   </si>
   <si>
     <t xml:space="preserve">9.86409282684326</t>
@@ -728,31 +728,31 @@
     <t xml:space="preserve">10.5199031829834</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0617341995239</t>
+    <t xml:space="preserve">10.0617351531982</t>
   </si>
   <si>
     <t xml:space="preserve">9.88206100463867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74730491638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56763172149658</t>
+    <t xml:space="preserve">9.74730587005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5676326751709</t>
   </si>
   <si>
     <t xml:space="preserve">9.44185924530029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54068088531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34303855895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36100673675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50474548339844</t>
+    <t xml:space="preserve">9.54067993164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34303951263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36100769042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50474643707275</t>
   </si>
   <si>
     <t xml:space="preserve">9.48677921295166</t>
@@ -764,34 +764,34 @@
     <t xml:space="preserve">9.77425765991211</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46881294250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54966449737549</t>
+    <t xml:space="preserve">9.46881103515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54966354370117</t>
   </si>
   <si>
     <t xml:space="preserve">9.47779560089111</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70238780975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30710411071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28015327453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21726703643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16336631774902</t>
+    <t xml:space="preserve">9.7023868560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30710506439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28015422821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2172679901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16336536407471</t>
   </si>
   <si>
     <t xml:space="preserve">9.20828437805176</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25320339202881</t>
+    <t xml:space="preserve">9.25320243835449</t>
   </si>
   <si>
     <t xml:space="preserve">9.45084381103516</t>
@@ -803,16 +803,16 @@
     <t xml:space="preserve">9.33405685424805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59458351135254</t>
+    <t xml:space="preserve">9.59458160400391</t>
   </si>
   <si>
     <t xml:space="preserve">9.66645336151123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71137237548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40592479705811</t>
+    <t xml:space="preserve">9.71137142181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40592575073242</t>
   </si>
   <si>
     <t xml:space="preserve">9.26218700408936</t>
@@ -824,7 +824,7 @@
     <t xml:space="preserve">9.28913688659668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36999225616455</t>
+    <t xml:space="preserve">9.36999130249023</t>
   </si>
   <si>
     <t xml:space="preserve">9.65746879577637</t>
@@ -833,61 +833,61 @@
     <t xml:space="preserve">9.79222393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76527214050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7203540802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81019115447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37897491455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90901184082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81917572021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73832225799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78324127197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69340419769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11844539642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08251285552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31608772277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19031715393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10048007965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22625160217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41491031646729</t>
+    <t xml:space="preserve">9.76527404785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72035598754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81019020080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37897396087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90901279449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81917381286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73832321166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78324222564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69340229034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11844635009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08251190185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31608867645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19031524658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1004810333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22625255584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41490936279297</t>
   </si>
   <si>
     <t xml:space="preserve">9.39694118499756</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07352924346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57661437988281</t>
+    <t xml:space="preserve">9.07353019714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57661533355713</t>
   </si>
   <si>
     <t xml:space="preserve">9.68441963195801</t>
@@ -899,40 +899,40 @@
     <t xml:space="preserve">9.05556106567383</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14539813995361</t>
+    <t xml:space="preserve">9.14540004730225</t>
   </si>
   <si>
     <t xml:space="preserve">8.89385509490967</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10946369171143</t>
+    <t xml:space="preserve">9.10946464538574</t>
   </si>
   <si>
     <t xml:space="preserve">9.23523426055908</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95392990112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5109205245972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.74449634552</t>
+    <t xml:space="preserve">9.95393085479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5109195709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7444953918457</t>
   </si>
   <si>
     <t xml:space="preserve">10.546854019165</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6905927658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9062023162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7804298400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7085609436035</t>
+    <t xml:space="preserve">10.6905918121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9062013626099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7804307937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7085590362549</t>
   </si>
   <si>
     <t xml:space="preserve">10.6546583175659</t>
@@ -941,76 +941,76 @@
     <t xml:space="preserve">10.5288877487183</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4390506744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.331244468689</t>
+    <t xml:space="preserve">10.4390497207642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3312454223633</t>
   </si>
   <si>
     <t xml:space="preserve">10.1695394515991</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1875066757202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1336040496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7562894821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63051700592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0078325271606</t>
+    <t xml:space="preserve">10.1875076293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.133602142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75629043579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63051891326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.007833480835</t>
   </si>
   <si>
     <t xml:space="preserve">9.84612560272217</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0976705551147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.205472946167</t>
+    <t xml:space="preserve">10.0976686477661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2054738998413</t>
   </si>
   <si>
     <t xml:space="preserve">10.2773427963257</t>
   </si>
   <si>
-    <t xml:space="preserve">10.223443031311</t>
+    <t xml:space="preserve">10.2234420776367</t>
   </si>
   <si>
     <t xml:space="preserve">10.2414083480835</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7624616622925</t>
+    <t xml:space="preserve">10.7624626159668</t>
   </si>
   <si>
     <t xml:space="preserve">10.2593765258789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91799449920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9000301361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67380714416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74667835235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87420558929443</t>
+    <t xml:space="preserve">9.91799640655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90002918243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67380523681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74667930603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87420654296875</t>
   </si>
   <si>
     <t xml:space="preserve">10.1656942367554</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85598754882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63737010955811</t>
+    <t xml:space="preserve">9.85598850250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63737106323242</t>
   </si>
   <si>
     <t xml:space="preserve">9.47340679168701</t>
@@ -1022,58 +1022,58 @@
     <t xml:space="preserve">9.96529579162598</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0746059417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2385683059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3843116760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.420747756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8033275604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6940202713013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6211471557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7851095199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5482740402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4025297164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2203493118286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1474771499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3296575546265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5847120285034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3478746414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72846126556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56449699401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4187536239624</t>
+    <t xml:space="preserve">10.0746049880981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2385663986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3843126296997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4207487106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8033285140991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.694019317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6211462020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7851104736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5482749938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4025316238403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2203483581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1474761962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3296585083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5847101211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3478755950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72845935821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56449794769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41875267028809</t>
   </si>
   <si>
     <t xml:space="preserve">9.40053462982178</t>
@@ -1091,7 +1091,7 @@
     <t xml:space="preserve">9.92885971069336</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0199499130249</t>
+    <t xml:space="preserve">10.0199508666992</t>
   </si>
   <si>
     <t xml:space="preserve">10.2021312713623</t>
@@ -1100,22 +1100,22 @@
     <t xml:space="preserve">10.0928220748901</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8013334274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69202518463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83776950836182</t>
+    <t xml:space="preserve">9.80133438110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69202327728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8377685546875</t>
   </si>
   <si>
     <t xml:space="preserve">9.94707775115967</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89242267608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6555871963501</t>
+    <t xml:space="preserve">9.89242458343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65558815002441</t>
   </si>
   <si>
     <t xml:space="preserve">9.78311538696289</t>
@@ -1124,31 +1124,31 @@
     <t xml:space="preserve">9.91064262390137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45519065856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20013618469238</t>
+    <t xml:space="preserve">9.45518970489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2001371383667</t>
   </si>
   <si>
     <t xml:space="preserve">9.50984382629395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43697071075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81955051422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49162483215332</t>
+    <t xml:space="preserve">9.43697166442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81955146789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49162578582764</t>
   </si>
   <si>
     <t xml:space="preserve">9.61915302276611</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98351383209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6009349822998</t>
+    <t xml:space="preserve">9.9835147857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60093402862549</t>
   </si>
   <si>
     <t xml:space="preserve">9.10904598236084</t>
@@ -1157,10 +1157,10 @@
     <t xml:space="preserve">9.09993648529053</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38231658935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36409759521484</t>
+    <t xml:space="preserve">9.38231754302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36409854888916</t>
   </si>
   <si>
     <t xml:space="preserve">9.27300930023193</t>
@@ -1169,46 +1169,46 @@
     <t xml:space="preserve">9.71024131774902</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5827169418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29122734069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14548206329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3660955429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32766246795654</t>
+    <t xml:space="preserve">9.58271598815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29122638702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14548015594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3660945892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32766342163086</t>
   </si>
   <si>
     <t xml:space="preserve">10.0017318725586</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4754028320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8397645950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5664920806885</t>
+    <t xml:space="preserve">10.4754018783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8397636413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5664939880371</t>
   </si>
   <si>
     <t xml:space="preserve">10.3114404678345</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2932224273682</t>
+    <t xml:space="preserve">10.2932233810425</t>
   </si>
   <si>
     <t xml:space="preserve">10.0381689071655</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0563850402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1292600631714</t>
+    <t xml:space="preserve">10.0563859939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1292591094971</t>
   </si>
   <si>
     <t xml:space="preserve">10.2750024795532</t>
@@ -1232,28 +1232,28 @@
     <t xml:space="preserve">10.8762006759644</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8944187164307</t>
+    <t xml:space="preserve">10.8944177627563</t>
   </si>
   <si>
     <t xml:space="preserve">10.7304544448853</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6575841903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2644624710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1349859237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0979928970337</t>
+    <t xml:space="preserve">10.6575832366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2644653320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1349849700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.097993850708</t>
   </si>
   <si>
     <t xml:space="preserve">11.2459669113159</t>
   </si>
   <si>
-    <t xml:space="preserve">11.319953918457</t>
+    <t xml:space="preserve">11.3199529647827</t>
   </si>
   <si>
     <t xml:space="preserve">11.0240068435669</t>
@@ -1265,19 +1265,19 @@
     <t xml:space="preserve">10.8390407562256</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7280597686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8575372695923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7095623016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6725692749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6540746688843</t>
+    <t xml:space="preserve">10.7280607223511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.857536315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7095632553101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6725702285767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.65407371521</t>
   </si>
   <si>
     <t xml:space="preserve">10.7835502624512</t>
@@ -1286,7 +1286,7 @@
     <t xml:space="preserve">10.7650537490845</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8020458221436</t>
+    <t xml:space="preserve">10.8020467758179</t>
   </si>
   <si>
     <t xml:space="preserve">10.5615901947021</t>
@@ -1295,10 +1295,10 @@
     <t xml:space="preserve">10.6170806884766</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3951215744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1176700592041</t>
+    <t xml:space="preserve">10.3951206207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1176710128784</t>
   </si>
   <si>
     <t xml:space="preserve">10.284140586853</t>
@@ -1307,16 +1307,16 @@
     <t xml:space="preserve">10.265643119812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3026371002197</t>
+    <t xml:space="preserve">10.302638053894</t>
   </si>
   <si>
     <t xml:space="preserve">10.5060997009277</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3396310806274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1361665725708</t>
+    <t xml:space="preserve">10.3396301269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1361675262451</t>
   </si>
   <si>
     <t xml:space="preserve">10.0806770324707</t>
@@ -1325,19 +1325,19 @@
     <t xml:space="preserve">9.98819446563721</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0991735458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93270397186279</t>
+    <t xml:space="preserve">10.0991744995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93270301818848</t>
   </si>
   <si>
     <t xml:space="preserve">9.89571094512939</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96969699859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1731595993042</t>
+    <t xml:space="preserve">9.96969795227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1731615066528</t>
   </si>
   <si>
     <t xml:space="preserve">10.0621814727783</t>
@@ -1346,7 +1346,7 @@
     <t xml:space="preserve">10.1546640396118</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71074295043945</t>
+    <t xml:space="preserve">9.71074390411377</t>
   </si>
   <si>
     <t xml:space="preserve">10.0251874923706</t>
@@ -1361,28 +1361,28 @@
     <t xml:space="preserve">9.72924137115479</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65525436401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67374992370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47028732299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54427337646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56277084350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45179176330566</t>
+    <t xml:space="preserve">9.65525341033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67375087738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47028827667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54427433013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56277179718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45179080963135</t>
   </si>
   <si>
     <t xml:space="preserve">9.35930824279785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52577781677246</t>
+    <t xml:space="preserve">9.52577686309814</t>
   </si>
   <si>
     <t xml:space="preserve">9.59976482391357</t>
@@ -1391,34 +1391,34 @@
     <t xml:space="preserve">9.61826038360596</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69224834442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80322647094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2286520004272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78472995758057</t>
+    <t xml:space="preserve">9.69224739074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8032283782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2286510467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78473091125488</t>
   </si>
   <si>
     <t xml:space="preserve">9.85871696472168</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0066909790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8772144317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74773788452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58126735687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3211336135864</t>
+    <t xml:space="preserve">10.0066890716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87721538543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74773693084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58126831054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3211355209351</t>
   </si>
   <si>
     <t xml:space="preserve">10.4321136474609</t>
@@ -1427,139 +1427,139 @@
     <t xml:space="preserve">10.3766241073608</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2471466064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2101526260376</t>
+    <t xml:space="preserve">10.2471485137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2101535797119</t>
   </si>
   <si>
     <t xml:space="preserve">9.8402214050293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63675689697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43329524993896</t>
+    <t xml:space="preserve">9.63675785064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43329429626465</t>
   </si>
   <si>
     <t xml:space="preserve">9.41479778289795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39630126953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24832725524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06336212158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10960388183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32231426239014</t>
+    <t xml:space="preserve">9.39630222320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24832820892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06336116790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10960292816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32231521606445</t>
   </si>
   <si>
     <t xml:space="preserve">9.28532123565674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26682472229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19283771514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22983074188232</t>
+    <t xml:space="preserve">9.26682376861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19283676147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22982978820801</t>
   </si>
   <si>
     <t xml:space="preserve">9.48878383636475</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0263671875</t>
+    <t xml:space="preserve">9.02636909484863</t>
   </si>
   <si>
     <t xml:space="preserve">8.9708776473999</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13734722137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96162891387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82290458679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61944007873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55470275878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36048889160156</t>
+    <t xml:space="preserve">9.13734817504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96162986755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82290554046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61944198608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55470371246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36048984527588</t>
   </si>
   <si>
     <t xml:space="preserve">8.33274364471436</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01830005645752</t>
+    <t xml:space="preserve">8.01830101013184</t>
   </si>
   <si>
     <t xml:space="preserve">7.81483745574951</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95356178283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49114561080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86107921600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50964260101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53738641738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58362865447998</t>
+    <t xml:space="preserve">7.95356225967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49114608764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86107969284058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50964164733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53738689422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58362913131714</t>
   </si>
   <si>
     <t xml:space="preserve">8.76741409301758</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98937511444092</t>
+    <t xml:space="preserve">8.9893741607666</t>
   </si>
   <si>
     <t xml:space="preserve">9.16509246826172</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12809944152832</t>
+    <t xml:space="preserve">9.128098487854</t>
   </si>
   <si>
     <t xml:space="preserve">9.09110546112061</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0818567276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34081172943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04486465454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21133327484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38705158233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17434024810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29456996917725</t>
+    <t xml:space="preserve">9.08185768127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34081077575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0448637008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21133518218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38705062866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17434215545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29456901550293</t>
   </si>
   <si>
     <t xml:space="preserve">9.11885070800781</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">8.78591060638428</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89689159393311</t>
+    <t xml:space="preserve">8.89689064025879</t>
   </si>
   <si>
     <t xml:space="preserve">8.7489185333252</t>
@@ -1577,16 +1577,16 @@
     <t xml:space="preserve">8.80440807342529</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87839508056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93388557434082</t>
+    <t xml:space="preserve">8.87839603424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9338846206665</t>
   </si>
   <si>
     <t xml:space="preserve">8.63793849945068</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71192359924316</t>
+    <t xml:space="preserve">8.71192455291748</t>
   </si>
   <si>
     <t xml:space="preserve">8.58244800567627</t>
@@ -1595,13 +1595,13 @@
     <t xml:space="preserve">8.69342803955078</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46114063262939</t>
+    <t xml:space="preserve">9.46113967895508</t>
   </si>
   <si>
     <t xml:space="preserve">9.64942073822021</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69649219512939</t>
+    <t xml:space="preserve">9.69649124145508</t>
   </si>
   <si>
     <t xml:space="preserve">9.74356174468994</t>
@@ -1610,13 +1610,13 @@
     <t xml:space="preserve">9.97891330718994</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93184280395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7906322479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0730543136597</t>
+    <t xml:space="preserve">9.93184375762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79063129425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0730533599854</t>
   </si>
   <si>
     <t xml:space="preserve">10.3084049224854</t>
@@ -1628,13 +1628,13 @@
     <t xml:space="preserve">10.1671953201294</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1201238632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0259828567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2142648696899</t>
+    <t xml:space="preserve">10.1201248168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0259838104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2142658233643</t>
   </si>
   <si>
     <t xml:space="preserve">10.3554754257202</t>
@@ -1652,28 +1652,28 @@
     <t xml:space="preserve">10.4966869354248</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5437574386597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2027416229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1556720733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9673910140991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0615310668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7791090011597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8261795043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.014461517334</t>
+    <t xml:space="preserve">10.5437564849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2027425765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1556711196899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9673900604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0615301132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7791080474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8261785507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0144605636597</t>
   </si>
   <si>
     <t xml:space="preserve">11.1086015701294</t>
@@ -1682,22 +1682,22 @@
     <t xml:space="preserve">10.9203205108643</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8732500076294</t>
+    <t xml:space="preserve">10.8732490539551</t>
   </si>
   <si>
     <t xml:space="preserve">10.7320384979248</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6378984451294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5322351455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6263751983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7675857543945</t>
+    <t xml:space="preserve">10.6378974914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5322341918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6263742446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7675867080688</t>
   </si>
   <si>
     <t xml:space="preserve">11.8146562576294</t>
@@ -1709,25 +1709,25 @@
     <t xml:space="preserve">11.6734447479248</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7205152511597</t>
+    <t xml:space="preserve">11.7205142974854</t>
   </si>
   <si>
     <t xml:space="preserve">12.0029382705688</t>
   </si>
   <si>
-    <t xml:space="preserve">12.285361289978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5677824020386</t>
+    <t xml:space="preserve">12.2853603363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5677814483643</t>
   </si>
   <si>
     <t xml:space="preserve">12.5207118988037</t>
   </si>
   <si>
-    <t xml:space="preserve">12.897274017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7560634613037</t>
+    <t xml:space="preserve">12.8972730636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7560625076294</t>
   </si>
   <si>
     <t xml:space="preserve">12.661922454834</t>
@@ -1736,37 +1736,37 @@
     <t xml:space="preserve">12.6148519515991</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8031339645386</t>
+    <t xml:space="preserve">12.8031320571899</t>
   </si>
   <si>
     <t xml:space="preserve">12.8502035140991</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9914150238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1796970367432</t>
+    <t xml:space="preserve">12.9914140701294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1796960830688</t>
   </si>
   <si>
     <t xml:space="preserve">13.4621181488037</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8386812210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7445421218872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6504011154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5091886520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7916107177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8857517242432</t>
+    <t xml:space="preserve">13.838680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7445411682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6504001617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5091896057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7916116714478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8857526779175</t>
   </si>
   <si>
     <t xml:space="preserve">13.9798927307129</t>
@@ -1775,19 +1775,19 @@
     <t xml:space="preserve">14.0269622802734</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0740327835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.168173789978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1211042404175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2623138427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2152452468872</t>
+    <t xml:space="preserve">14.074031829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1681728363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1211032867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2623128890991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2152442932129</t>
   </si>
   <si>
     <t xml:space="preserve">14.4505958557129</t>
@@ -1796,31 +1796,31 @@
     <t xml:space="preserve">14.6859474182129</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3093852996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4035243988037</t>
+    <t xml:space="preserve">14.3093843460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.403525352478</t>
   </si>
   <si>
     <t xml:space="preserve">14.3564548492432</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5447368621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5918064117432</t>
+    <t xml:space="preserve">14.5447359085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5918073654175</t>
   </si>
   <si>
     <t xml:space="preserve">14.638876914978</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7800874710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8271579742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8742275238037</t>
+    <t xml:space="preserve">14.7800884246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8271589279175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8742294311523</t>
   </si>
   <si>
     <t xml:space="preserve">14.7330169677734</t>
@@ -1829,91 +1829,91 @@
     <t xml:space="preserve">15.3449306488037</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7685670852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0039157867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0415725708008</t>
+    <t xml:space="preserve">15.7685661315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0039176940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0415744781494</t>
   </si>
   <si>
     <t xml:space="preserve">16.0792293548584</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1921977996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1168842315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2298545837402</t>
+    <t xml:space="preserve">16.1921997070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.116886138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2298564910889</t>
   </si>
   <si>
     <t xml:space="preserve">16.3804798126221</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3993091583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4181346893311</t>
+    <t xml:space="preserve">16.3993072509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4181365966797</t>
   </si>
   <si>
     <t xml:space="preserve">16.5311050415039</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2675094604492</t>
+    <t xml:space="preserve">16.2675113677979</t>
   </si>
   <si>
     <t xml:space="preserve">15.9286050796509</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8909482955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.815634727478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9662599563599</t>
+    <t xml:space="preserve">15.8909473419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8156337738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9662590026855</t>
   </si>
   <si>
     <t xml:space="preserve">15.7214956283569</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5332126617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5143842697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7026662826538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2696199417114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4767293930054</t>
+    <t xml:space="preserve">15.5332145690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5143852233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7026681900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2696189880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4767284393311</t>
   </si>
   <si>
     <t xml:space="preserve">15.6838369369507</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6650104522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4202442169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1566514968872</t>
+    <t xml:space="preserve">15.6650094985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4202451705933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1566505432129</t>
   </si>
   <si>
     <t xml:space="preserve">15.2319631576538</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7779769897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9833707809448</t>
+    <t xml:space="preserve">15.7779788970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9833726882935</t>
   </si>
   <si>
     <t xml:space="preserve">15.964301109314</t>
@@ -1931,7 +1931,7 @@
     <t xml:space="preserve">15.8117141723633</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6019086837769</t>
+    <t xml:space="preserve">15.6019096374512</t>
   </si>
   <si>
     <t xml:space="preserve">15.5446872711182</t>
@@ -1946,13 +1946,10 @@
     <t xml:space="preserve">15.8307867050171</t>
   </si>
   <si>
-    <t xml:space="preserve">16.116886138916</t>
-  </si>
-  <si>
     <t xml:space="preserve">16.2503986358643</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2313251495361</t>
+    <t xml:space="preserve">16.2313270568848</t>
   </si>
   <si>
     <t xml:space="preserve">16.0024471282959</t>
@@ -1964,31 +1961,31 @@
     <t xml:space="preserve">16.212251663208</t>
   </si>
   <si>
-    <t xml:space="preserve">16.460205078125</t>
+    <t xml:space="preserve">16.4602069854736</t>
   </si>
   <si>
     <t xml:space="preserve">16.4411315917969</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5364971160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5555725097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1659145355225</t>
+    <t xml:space="preserve">16.5364952087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.555570602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1659126281738</t>
   </si>
   <si>
     <t xml:space="preserve">16.9561080932617</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2231349945068</t>
+    <t xml:space="preserve">17.2231330871582</t>
   </si>
   <si>
     <t xml:space="preserve">17.3185005187988</t>
   </si>
   <si>
-    <t xml:space="preserve">17.08962059021</t>
+    <t xml:space="preserve">17.0896224975586</t>
   </si>
   <si>
     <t xml:space="preserve">16.8416690826416</t>
@@ -2000,19 +1997,19 @@
     <t xml:space="preserve">16.9751815795898</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1277675628662</t>
+    <t xml:space="preserve">17.1277656555176</t>
   </si>
   <si>
     <t xml:space="preserve">17.5092334747314</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5473785400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7571849822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6427459716797</t>
+    <t xml:space="preserve">17.5473804473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7571830749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6427440643311</t>
   </si>
   <si>
     <t xml:space="preserve">17.7381134033203</t>
@@ -2021,10 +2018,10 @@
     <t xml:space="preserve">17.4901580810547</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4710865020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3375720977783</t>
+    <t xml:space="preserve">17.4710845947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.337574005127</t>
   </si>
   <si>
     <t xml:space="preserve">17.2994251251221</t>
@@ -2042,7 +2039,7 @@
     <t xml:space="preserve">17.0133266448975</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4520111083984</t>
+    <t xml:space="preserve">17.4520130157471</t>
   </si>
   <si>
     <t xml:space="preserve">17.8334789276123</t>
@@ -2066,13 +2063,13 @@
     <t xml:space="preserve">18.5010395050049</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6536254882812</t>
+    <t xml:space="preserve">18.6536273956299</t>
   </si>
   <si>
     <t xml:space="preserve">18.5964069366455</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5582580566406</t>
+    <t xml:space="preserve">18.5582599639893</t>
   </si>
   <si>
     <t xml:space="preserve">18.7108478546143</t>
@@ -2084,7 +2081,7 @@
     <t xml:space="preserve">18.5201148986816</t>
   </si>
   <si>
-    <t xml:space="preserve">19.55006980896</t>
+    <t xml:space="preserve">19.5500679016113</t>
   </si>
   <si>
     <t xml:space="preserve">19.5023880004883</t>
@@ -2093,10 +2090,10 @@
     <t xml:space="preserve">19.8838520050049</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9792194366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.454704284668</t>
+    <t xml:space="preserve">19.9792175292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4547023773193</t>
   </si>
   <si>
     <t xml:space="preserve">19.3593349456787</t>
@@ -2105,16 +2102,16 @@
     <t xml:space="preserve">19.1686058044434</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7871398925781</t>
+    <t xml:space="preserve">18.7871417999268</t>
   </si>
   <si>
     <t xml:space="preserve">18.6917743682861</t>
   </si>
   <si>
-    <t xml:space="preserve">19.216287612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.120922088623</t>
+    <t xml:space="preserve">19.2162857055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1209201812744</t>
   </si>
   <si>
     <t xml:space="preserve">18.76806640625</t>
@@ -2126,19 +2123,19 @@
     <t xml:space="preserve">18.1195755004883</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6236686706543</t>
+    <t xml:space="preserve">17.6236705780029</t>
   </si>
   <si>
     <t xml:space="preserve">17.890697479248</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1005020141602</t>
+    <t xml:space="preserve">18.1005001068115</t>
   </si>
   <si>
     <t xml:space="preserve">18.2530860900879</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9669876098633</t>
+    <t xml:space="preserve">17.9669895172119</t>
   </si>
   <si>
     <t xml:space="preserve">18.1767959594727</t>
@@ -2150,16 +2147,16 @@
     <t xml:space="preserve">19.0732383728027</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9778728485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8825054168701</t>
+    <t xml:space="preserve">18.9778709411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8825035095215</t>
   </si>
   <si>
     <t xml:space="preserve">18.9397258758545</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9015769958496</t>
+    <t xml:space="preserve">18.9015789031982</t>
   </si>
   <si>
     <t xml:space="preserve">20.0268993377686</t>
@@ -2171,16 +2168,16 @@
     <t xml:space="preserve">20.2653160095215</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7421455383301</t>
+    <t xml:space="preserve">20.7421474456787</t>
   </si>
   <si>
     <t xml:space="preserve">20.9328804016113</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2189769744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4573917388916</t>
+    <t xml:space="preserve">21.2189788818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4573936462402</t>
   </si>
   <si>
     <t xml:space="preserve">20.6944637298584</t>
@@ -2192,7 +2189,7 @@
     <t xml:space="preserve">20.4560489654541</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9805603027344</t>
+    <t xml:space="preserve">20.980562210083</t>
   </si>
   <si>
     <t xml:space="preserve">19.8361682891846</t>
@@ -2201,7 +2198,7 @@
     <t xml:space="preserve">20.4083652496338</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1222667694092</t>
+    <t xml:space="preserve">20.1222686767578</t>
   </si>
   <si>
     <t xml:space="preserve">19.3116550445557</t>
@@ -2222,25 +2219,25 @@
     <t xml:space="preserve">19.9315338134766</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7408027648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8443584442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0160179138184</t>
+    <t xml:space="preserve">19.7408008575439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8443603515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.016019821167</t>
   </si>
   <si>
     <t xml:space="preserve">18.0432834625244</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0051364898682</t>
+    <t xml:space="preserve">18.0051345825195</t>
   </si>
   <si>
     <t xml:space="preserve">18.1386489868164</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0623550415039</t>
+    <t xml:space="preserve">18.0623569488525</t>
   </si>
   <si>
     <t xml:space="preserve">18.081428527832</t>
@@ -2273,13 +2270,13 @@
     <t xml:space="preserve">17.0705490112305</t>
   </si>
   <si>
-    <t xml:space="preserve">16.650936126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8607406616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3076190948486</t>
+    <t xml:space="preserve">16.6509342193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8607425689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3076171875</t>
   </si>
   <si>
     <t xml:space="preserve">16.5937175750732</t>
@@ -2297,192 +2294,195 @@
     <t xml:space="preserve">14.4956607818604</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3730306625366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9915657043457</t>
+    <t xml:space="preserve">15.3730316162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9915647506714</t>
   </si>
   <si>
     <t xml:space="preserve">15.0869312286377</t>
   </si>
   <si>
-    <t xml:space="preserve">15.678201675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1441497802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9452266693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0787391662598</t>
+    <t xml:space="preserve">15.6782007217407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1441507339478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9452247619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0787410736084</t>
   </si>
   <si>
     <t xml:space="preserve">16.0405921936035</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5746421813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6890830993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5174217224121</t>
+    <t xml:space="preserve">16.5746440887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6890850067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5174236297607</t>
   </si>
   <si>
     <t xml:space="preserve">16.4983501434326</t>
   </si>
   <si>
+    <t xml:space="preserve">15.7354211807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8880052566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5065412521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9724912643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3348827362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2204427719116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9152717590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.781759262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8961992263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6400547027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0978126525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2395153045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1060047149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0063877105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1999359130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3547744750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0450973510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1418704986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2773532867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4709033966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7805767059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1483173370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.767671585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.419282913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2321853637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7289600372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9418659210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4967041015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5934791564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4579963684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8967037200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4515476226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9870338439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8321962356567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9483232498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3676805496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4450988769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1741333007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1160688400269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.135422706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3289709091187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.619291305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8902597427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7547750473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8128395080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.161226272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6580018997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.870903968811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4128360748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4321899414062</t>
+  </si>
+  <si>
     <t xml:space="preserve">15.7354202270508</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8880052566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5065412521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9724912643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3348827362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2204427719116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9152727127075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.781759262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8961982727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6400547027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0978126525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2395153045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1060047149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0063896179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1999359130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3547744750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0450973510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1418704986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2773532867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4709014892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7805786132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1483173370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.767671585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4192848205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2321834564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7289619445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9418640136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4967041015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5934772491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4579944610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8967056274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4515476226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9870338439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8321952819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9483222961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3676795959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4450988769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1741333007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1160678863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1354236602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3289709091187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.619291305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8902606964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7547760009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.812840461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.161226272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6580018997192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.870903968811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4128360748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4321918487549</t>
-  </si>
-  <si>
     <t xml:space="preserve">15.7160663604736</t>
   </si>
   <si>
@@ -2504,10 +2504,10 @@
     <t xml:space="preserve">17.5354137420654</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3805751800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3418655395508</t>
+    <t xml:space="preserve">17.3805732727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3418674468994</t>
   </si>
   <si>
     <t xml:space="preserve">17.2063827514648</t>
@@ -2531,16 +2531,16 @@
     <t xml:space="preserve">17.6128330230713</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8192863464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1096076965332</t>
+    <t xml:space="preserve">16.8192882537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1096096038818</t>
   </si>
   <si>
     <t xml:space="preserve">16.7225131988525</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1289653778076</t>
+    <t xml:space="preserve">17.128963470459</t>
   </si>
   <si>
     <t xml:space="preserve">16.8773517608643</t>
@@ -2561,13 +2561,13 @@
     <t xml:space="preserve">15.5031642913818</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2128429412842</t>
+    <t xml:space="preserve">15.2128419876099</t>
   </si>
   <si>
     <t xml:space="preserve">15.3096160888672</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5805835723877</t>
+    <t xml:space="preserve">15.5805826187134</t>
   </si>
   <si>
     <t xml:space="preserve">15.1547775268555</t>
@@ -2588,7 +2588,7 @@
     <t xml:space="preserve">15.5612277984619</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1805801391602</t>
+    <t xml:space="preserve">16.1805782318115</t>
   </si>
   <si>
     <t xml:space="preserve">16.8579978942871</t>
@@ -2597,10 +2597,10 @@
     <t xml:space="preserve">17.3031558990479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9031543731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8063793182373</t>
+    <t xml:space="preserve">17.9031524658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8063812255859</t>
   </si>
   <si>
     <t xml:space="preserve">17.1676731109619</t>
@@ -2615,7 +2615,7 @@
     <t xml:space="preserve">18.735408782959</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6579914093018</t>
+    <t xml:space="preserve">18.6579895019531</t>
   </si>
   <si>
     <t xml:space="preserve">18.4837970733643</t>
@@ -2630,7 +2630,7 @@
     <t xml:space="preserve">18.2515392303467</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8837966918945</t>
+    <t xml:space="preserve">17.8837985992432</t>
   </si>
   <si>
     <t xml:space="preserve">18.0386352539062</t>
@@ -2648,7 +2648,7 @@
     <t xml:space="preserve">18.1547660827637</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0192832946777</t>
+    <t xml:space="preserve">18.0192813873291</t>
   </si>
   <si>
     <t xml:space="preserve">17.9805736541748</t>
@@ -2660,7 +2660,7 @@
     <t xml:space="preserve">17.8450908660889</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6902503967285</t>
+    <t xml:space="preserve">17.6902523040771</t>
   </si>
   <si>
     <t xml:space="preserve">17.6321868896484</t>
@@ -2678,19 +2678,19 @@
     <t xml:space="preserve">17.2644462585449</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7096042633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4773502349854</t>
+    <t xml:space="preserve">17.7096061706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4773483276367</t>
   </si>
   <si>
     <t xml:space="preserve">17.8257369995117</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5805702209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.928955078125</t>
+    <t xml:space="preserve">18.5805721282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9289569854736</t>
   </si>
   <si>
     <t xml:space="preserve">18.8128299713135</t>
@@ -2705,10 +2705,10 @@
     <t xml:space="preserve">19.7902450561523</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0321788787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7418575286865</t>
+    <t xml:space="preserve">20.0321769714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7418556213379</t>
   </si>
   <si>
     <t xml:space="preserve">19.5966968536377</t>
@@ -2717,13 +2717,13 @@
     <t xml:space="preserve">19.9837894439697</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8386306762695</t>
+    <t xml:space="preserve">19.8386287689209</t>
   </si>
   <si>
     <t xml:space="preserve">20.0805644989014</t>
   </si>
   <si>
-    <t xml:space="preserve">20.370885848999</t>
+    <t xml:space="preserve">20.3708839416504</t>
   </si>
   <si>
     <t xml:space="preserve">19.8870162963867</t>
@@ -2738,7 +2738,7 @@
     <t xml:space="preserve">20.177339553833</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4192733764648</t>
+    <t xml:space="preserve">20.4192752838135</t>
   </si>
   <si>
     <t xml:space="preserve">20.467658996582</t>
@@ -2762,10 +2762,10 @@
     <t xml:space="preserve">21.6289443969727</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0644264221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2579746246338</t>
+    <t xml:space="preserve">22.0644283294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2579727172852</t>
   </si>
   <si>
     <t xml:space="preserve">22.6450710296631</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">22.7902297973633</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7418441772461</t>
+    <t xml:space="preserve">22.7418422698975</t>
   </si>
   <si>
     <t xml:space="preserve">21.9676532745361</t>
@@ -2798,31 +2798,31 @@
     <t xml:space="preserve">22.3063621520996</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8224906921387</t>
+    <t xml:space="preserve">21.8224925994873</t>
   </si>
   <si>
     <t xml:space="preserve">22.3547496795654</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1128158569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5482978820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9837799072266</t>
+    <t xml:space="preserve">22.112813949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5482959747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9837779998779</t>
   </si>
   <si>
     <t xml:space="preserve">23.9031295776367</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1934509277344</t>
+    <t xml:space="preserve">24.193452835083</t>
   </si>
   <si>
     <t xml:space="preserve">24.0966758728027</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0160293579102</t>
+    <t xml:space="preserve">25.0160312652588</t>
   </si>
   <si>
     <t xml:space="preserve">24.9676399230957</t>
@@ -2837,22 +2837,22 @@
     <t xml:space="preserve">25.9353790283203</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3547382354736</t>
+    <t xml:space="preserve">25.354736328125</t>
   </si>
   <si>
     <t xml:space="preserve">25.161190032959</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8708667755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2579650878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4515113830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2095756530762</t>
+    <t xml:space="preserve">24.8708686828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.257963180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.451509475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2095737457275</t>
   </si>
   <si>
     <t xml:space="preserve">25.5482845306396</t>
@@ -2870,7 +2870,7 @@
     <t xml:space="preserve">26.9515056610107</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6934452056885</t>
+    <t xml:space="preserve">25.6934432983398</t>
   </si>
   <si>
     <t xml:space="preserve">25.5966720581055</t>
@@ -2882,7 +2882,7 @@
     <t xml:space="preserve">25.8869934082031</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3708610534668</t>
+    <t xml:space="preserve">26.3708629608154</t>
   </si>
   <si>
     <t xml:space="preserve">26.2043304443359</t>
@@ -3819,6 +3819,9 @@
   </si>
   <si>
     <t xml:space="preserve">49.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.4000015258789</t>
   </si>
 </sst>
 </file>
@@ -40055,7 +40058,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1381" t="s">
-        <v>644</v>
+        <v>610</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -40081,7 +40084,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1382" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -40107,7 +40110,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1383" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -40133,7 +40136,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1384" t="s">
-        <v>644</v>
+        <v>610</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -40185,7 +40188,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1386" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -40211,7 +40214,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1387" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -40237,7 +40240,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G1388" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -40289,7 +40292,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1390" t="s">
-        <v>644</v>
+        <v>610</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -40315,7 +40318,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1391" t="s">
-        <v>644</v>
+        <v>610</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -40341,7 +40344,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1392" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -40367,7 +40370,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1393" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -40393,7 +40396,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1394" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -40419,7 +40422,7 @@
         <v>17</v>
       </c>
       <c r="G1395" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -40445,7 +40448,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1396" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -40471,7 +40474,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1397" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -40497,7 +40500,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1398" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -40523,7 +40526,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1399" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -40549,7 +40552,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1400" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -40575,7 +40578,7 @@
         <v>18</v>
       </c>
       <c r="G1401" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -40601,7 +40604,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1402" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -40627,7 +40630,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1403" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -40653,7 +40656,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1404" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -40679,7 +40682,7 @@
         <v>18</v>
       </c>
       <c r="G1405" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -40705,7 +40708,7 @@
         <v>18</v>
       </c>
       <c r="G1406" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -40731,7 +40734,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1407" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -40757,7 +40760,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G1408" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -40783,7 +40786,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1409" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -40809,7 +40812,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1410" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -40835,7 +40838,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1411" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -40861,7 +40864,7 @@
         <v>18</v>
       </c>
       <c r="G1412" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -40887,7 +40890,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G1413" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -40913,7 +40916,7 @@
         <v>18</v>
       </c>
       <c r="G1414" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -40939,7 +40942,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G1415" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -40965,7 +40968,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1416" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -40991,7 +40994,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1417" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -41017,7 +41020,7 @@
         <v>18.5</v>
       </c>
       <c r="G1418" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -41043,7 +41046,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1419" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -41069,7 +41072,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1420" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -41095,7 +41098,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1421" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -41121,7 +41124,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1422" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -41147,7 +41150,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1423" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -41173,7 +41176,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1424" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -41199,7 +41202,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1425" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -41225,7 +41228,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1426" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -41251,7 +41254,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1427" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -41277,7 +41280,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G1428" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -41303,7 +41306,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G1429" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -41329,7 +41332,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1430" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -41355,7 +41358,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1431" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -41381,7 +41384,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1432" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -41407,7 +41410,7 @@
         <v>18.5</v>
       </c>
       <c r="G1433" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -41433,7 +41436,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1434" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -41459,7 +41462,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1435" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -41485,7 +41488,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1436" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -41511,7 +41514,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G1437" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -41537,7 +41540,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1438" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -41563,7 +41566,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1439" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -41589,7 +41592,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1440" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -41615,7 +41618,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1441" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -41641,7 +41644,7 @@
         <v>19.5</v>
       </c>
       <c r="G1442" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -41667,7 +41670,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1443" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -41693,7 +41696,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G1444" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -41719,7 +41722,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1445" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -41745,7 +41748,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1446" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -41771,7 +41774,7 @@
         <v>20.5</v>
       </c>
       <c r="G1447" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -41797,7 +41800,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1448" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -41823,7 +41826,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1449" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -41849,7 +41852,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1450" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -41875,7 +41878,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1451" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -41901,7 +41904,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1452" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -41927,7 +41930,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1453" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -41953,7 +41956,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1454" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -41979,7 +41982,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1455" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -42005,7 +42008,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1456" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -42031,7 +42034,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1457" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -42057,7 +42060,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1458" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -42083,7 +42086,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1459" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -42109,7 +42112,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G1460" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -42135,7 +42138,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1461" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -42161,7 +42164,7 @@
         <v>19</v>
       </c>
       <c r="G1462" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -42187,7 +42190,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1463" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -42213,7 +42216,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G1464" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -42239,7 +42242,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1465" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -42265,7 +42268,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G1466" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -42291,7 +42294,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G1467" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -42317,7 +42320,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1468" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -42343,7 +42346,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1469" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -42369,7 +42372,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1470" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -42395,7 +42398,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1471" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -42421,7 +42424,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1472" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -42447,7 +42450,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G1473" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -42473,7 +42476,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1474" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -42499,7 +42502,7 @@
         <v>20</v>
       </c>
       <c r="G1475" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -42525,7 +42528,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1476" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -42551,7 +42554,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1477" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -42577,7 +42580,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1478" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -42603,7 +42606,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G1479" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -42629,7 +42632,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1480" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -42655,7 +42658,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1481" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -42681,7 +42684,7 @@
         <v>20</v>
       </c>
       <c r="G1482" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -42707,7 +42710,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1483" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -42733,7 +42736,7 @@
         <v>20</v>
       </c>
       <c r="G1484" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -42759,7 +42762,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1485" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -42785,7 +42788,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1486" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -42811,7 +42814,7 @@
         <v>20</v>
       </c>
       <c r="G1487" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -42837,7 +42840,7 @@
         <v>20</v>
       </c>
       <c r="G1488" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -42863,7 +42866,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G1489" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -42889,7 +42892,7 @@
         <v>20</v>
       </c>
       <c r="G1490" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -42915,7 +42918,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1491" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -42941,7 +42944,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1492" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -42967,7 +42970,7 @@
         <v>21</v>
       </c>
       <c r="G1493" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -42993,7 +42996,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1494" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -43019,7 +43022,7 @@
         <v>21.25</v>
       </c>
       <c r="G1495" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -43045,7 +43048,7 @@
         <v>21.75</v>
       </c>
       <c r="G1496" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -43071,7 +43074,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G1497" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -43097,7 +43100,7 @@
         <v>22.25</v>
       </c>
       <c r="G1498" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -43123,7 +43126,7 @@
         <v>22.5</v>
       </c>
       <c r="G1499" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -43149,7 +43152,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1500" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -43175,7 +43178,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1501" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -43201,7 +43204,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G1502" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -43227,7 +43230,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1503" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -43253,7 +43256,7 @@
         <v>22</v>
       </c>
       <c r="G1504" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -43279,7 +43282,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1505" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -43305,7 +43308,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1506" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -43331,7 +43334,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1507" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -43357,7 +43360,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1508" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -43383,7 +43386,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1509" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -43409,7 +43412,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1510" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -43435,7 +43438,7 @@
         <v>20.25</v>
       </c>
       <c r="G1511" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -43461,7 +43464,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1512" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -43487,7 +43490,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1513" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -43513,7 +43516,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1514" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -43539,7 +43542,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1515" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -43565,7 +43568,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G1516" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -43591,7 +43594,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1517" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -43617,7 +43620,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1518" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -43643,7 +43646,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1519" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -43669,7 +43672,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1520" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -43695,7 +43698,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1521" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -43721,7 +43724,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1522" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -43747,7 +43750,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1523" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -43773,7 +43776,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1524" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -43799,7 +43802,7 @@
         <v>21</v>
       </c>
       <c r="G1525" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -43825,7 +43828,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1526" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -43851,7 +43854,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1527" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -43877,7 +43880,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1528" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -43903,7 +43906,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1529" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -43929,7 +43932,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1530" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -43955,7 +43958,7 @@
         <v>20.5</v>
       </c>
       <c r="G1531" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -43981,7 +43984,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G1532" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -44007,7 +44010,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1533" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -44033,7 +44036,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1534" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -44059,7 +44062,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1535" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -44085,7 +44088,7 @@
         <v>20</v>
       </c>
       <c r="G1536" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -44111,7 +44114,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1537" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -44137,7 +44140,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1538" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -44163,7 +44166,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G1539" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -44189,7 +44192,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1540" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -44215,7 +44218,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1541" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -44241,7 +44244,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G1542" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -44267,7 +44270,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1543" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -44293,7 +44296,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1544" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -44319,7 +44322,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1545" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -44345,7 +44348,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G1546" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -44371,7 +44374,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G1547" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -44397,7 +44400,7 @@
         <v>19</v>
       </c>
       <c r="G1548" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -44423,7 +44426,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G1549" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -44449,7 +44452,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G1550" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -44475,7 +44478,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1551" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -44501,7 +44504,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G1552" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -44527,7 +44530,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G1553" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -44553,7 +44556,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1554" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -44579,7 +44582,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1555" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -44605,7 +44608,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1556" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -44631,7 +44634,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1557" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -44657,7 +44660,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G1558" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -44683,7 +44686,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1559" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -44709,7 +44712,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1560" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -44735,7 +44738,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G1561" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -44761,7 +44764,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1562" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -44787,7 +44790,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1563" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -44813,7 +44816,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G1564" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -44839,7 +44842,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1565" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -44865,7 +44868,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1566" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -44891,7 +44894,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1567" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -44917,7 +44920,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1568" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -44943,7 +44946,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1569" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -44969,7 +44972,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G1570" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -44995,7 +44998,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G1571" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -45021,7 +45024,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1572" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -45047,7 +45050,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1573" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -45073,7 +45076,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G1574" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -45099,7 +45102,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G1575" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -45125,7 +45128,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1576" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -45151,7 +45154,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1577" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -45177,7 +45180,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1578" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -45203,7 +45206,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1579" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -45229,7 +45232,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G1580" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -45255,7 +45258,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1581" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -45281,7 +45284,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1582" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -45307,7 +45310,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1583" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -45333,7 +45336,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1584" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -45359,7 +45362,7 @@
         <v>17</v>
       </c>
       <c r="G1585" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -45385,7 +45388,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G1586" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -45411,7 +45414,7 @@
         <v>17.5</v>
       </c>
       <c r="G1587" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -45437,7 +45440,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1588" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -45463,7 +45466,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1589" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -45489,7 +45492,7 @@
         <v>16.5</v>
       </c>
       <c r="G1590" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -45515,7 +45518,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1591" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -45593,7 +45596,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G1594" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -45619,7 +45622,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G1595" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -45671,7 +45674,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1597" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -45723,7 +45726,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G1599" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -45749,7 +45752,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G1600" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -45775,7 +45778,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1601" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -45801,7 +45804,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1602" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -45827,7 +45830,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G1603" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -45853,7 +45856,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1604" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -45879,7 +45882,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1605" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -45905,7 +45908,7 @@
         <v>15.5</v>
       </c>
       <c r="G1606" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -45931,7 +45934,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G1607" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -45957,7 +45960,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1608" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -46009,7 +46012,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G1610" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -46061,7 +46064,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1612" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -46139,7 +46142,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G1615" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -46191,7 +46194,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1617" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -46217,7 +46220,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G1618" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -46243,7 +46246,7 @@
         <v>16.5</v>
       </c>
       <c r="G1619" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -46269,7 +46272,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1620" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -46295,7 +46298,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1621" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -46321,7 +46324,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1622" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -46347,7 +46350,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G1623" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -46373,7 +46376,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1624" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -46399,7 +46402,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1625" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -46425,7 +46428,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1626" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -46451,7 +46454,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1627" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -46477,7 +46480,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1628" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -46503,7 +46506,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G1629" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -46529,7 +46532,7 @@
         <v>18</v>
       </c>
       <c r="G1630" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -46555,7 +46558,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1631" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -46581,7 +46584,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1632" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -46607,7 +46610,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1633" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -46633,7 +46636,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1634" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -46659,7 +46662,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1635" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -46685,7 +46688,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1636" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -46711,7 +46714,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1637" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -46737,7 +46740,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1638" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -46763,7 +46766,7 @@
         <v>17</v>
       </c>
       <c r="G1639" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -46789,7 +46792,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1640" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -46815,7 +46818,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1641" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -46841,7 +46844,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1642" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -46867,7 +46870,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1643" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -46893,7 +46896,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1644" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -46919,7 +46922,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1645" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -46945,7 +46948,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1646" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -46971,7 +46974,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G1647" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -46997,7 +47000,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1648" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -47023,7 +47026,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G1649" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -47049,7 +47052,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1650" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -47075,7 +47078,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G1651" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -47101,7 +47104,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G1652" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -47127,7 +47130,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1653" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -47153,7 +47156,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1654" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -47179,7 +47182,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1655" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -47205,7 +47208,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G1656" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -47231,7 +47234,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1657" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -47257,7 +47260,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1658" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -47283,7 +47286,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1659" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -47309,7 +47312,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G1660" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -47335,7 +47338,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1661" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -47361,7 +47364,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G1662" t="s">
-        <v>773</v>
+        <v>822</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -47439,7 +47442,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1665" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -47465,7 +47468,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1666" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -47491,7 +47494,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G1667" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -47517,7 +47520,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1668" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -47543,7 +47546,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1669" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -47959,7 +47962,7 @@
         <v>18</v>
       </c>
       <c r="G1685" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -48011,7 +48014,7 @@
         <v>18</v>
       </c>
       <c r="G1687" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -48063,7 +48066,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1689" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -48193,7 +48196,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1694" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -48219,7 +48222,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1695" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -48271,7 +48274,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1697" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -48375,7 +48378,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1701" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -48453,7 +48456,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1704" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -48479,7 +48482,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1705" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -48531,7 +48534,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1707" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -48583,7 +48586,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G1709" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -48635,7 +48638,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1711" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -48973,7 +48976,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1724" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -49025,7 +49028,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1726" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -49077,7 +49080,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1728" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -49259,7 +49262,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1735" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -49389,7 +49392,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1740" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -49441,7 +49444,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1742" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -49467,7 +49470,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1743" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -49961,7 +49964,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1762" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -50039,7 +50042,7 @@
         <v>18</v>
       </c>
       <c r="G1765" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -50091,7 +50094,7 @@
         <v>18</v>
       </c>
       <c r="G1767" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -50325,7 +50328,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1776" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -50403,7 +50406,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1779" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -50533,7 +50536,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1784" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -50611,7 +50614,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1787" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -68793,7 +68796,7 @@
     </row>
     <row r="2487">
       <c r="A2487" s="1" t="n">
-        <v>45940.6495601852</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2487" t="n">
         <v>50026</v>
@@ -68814,6 +68817,32 @@
         <v>1268</v>
       </c>
       <c r="H2487" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>45943.6493518519</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>15834</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>49.75</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>49.1500015258789</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>49.4000015258789</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>1269</v>
+      </c>
+      <c r="H2488" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SOL.MI.xlsx
+++ b/data/SOL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="1272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="1273">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,40 +38,40 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14939165115356</t>
+    <t xml:space="preserve">7.14939117431641</t>
   </si>
   <si>
     <t xml:space="preserve">SOL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14067316055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18862581253052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16246891021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06220436096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90962553024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90526533126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94885969161987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71781253814697</t>
+    <t xml:space="preserve">7.1406717300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18862533569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16246938705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0622034072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90962505340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90526580810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94885873794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71781206130981</t>
   </si>
   <si>
     <t xml:space="preserve">6.62626552581787</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71345281600952</t>
+    <t xml:space="preserve">6.71345233917236</t>
   </si>
   <si>
     <t xml:space="preserve">6.2993106842041</t>
@@ -80,25 +80,25 @@
     <t xml:space="preserve">6.36470222473145</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43009328842163</t>
+    <t xml:space="preserve">6.43009281158447</t>
   </si>
   <si>
     <t xml:space="preserve">6.41265487670898</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44752979278564</t>
+    <t xml:space="preserve">6.4475302696228</t>
   </si>
   <si>
     <t xml:space="preserve">6.20776414871216</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1728892326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46060848236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54779720306396</t>
+    <t xml:space="preserve">6.17288875579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.460608959198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54779624938965</t>
   </si>
   <si>
     <t xml:space="preserve">6.38214015960693</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">6.51292133331299</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50420236587524</t>
+    <t xml:space="preserve">6.50420188903809</t>
   </si>
   <si>
     <t xml:space="preserve">6.65242147445679</t>
@@ -116,13 +116,13 @@
     <t xml:space="preserve">6.80064058303833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72217178344727</t>
+    <t xml:space="preserve">6.72217130661011</t>
   </si>
   <si>
     <t xml:space="preserve">6.79192209243774</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00989103317261</t>
+    <t xml:space="preserve">7.00989007949829</t>
   </si>
   <si>
     <t xml:space="preserve">6.84423446655273</t>
@@ -131,25 +131,25 @@
     <t xml:space="preserve">7.07964134216309</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88346815109253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96629619598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08835935592651</t>
+    <t xml:space="preserve">6.88346910476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9662971496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08835983276367</t>
   </si>
   <si>
     <t xml:space="preserve">6.73524951934814</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8311562538147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67857694625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57395267486572</t>
+    <t xml:space="preserve">6.83115673065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6785774230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57395219802856</t>
   </si>
   <si>
     <t xml:space="preserve">6.63062429428101</t>
@@ -158,16 +158,16 @@
     <t xml:space="preserve">6.68729639053345</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78320360183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77884340286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81371784210205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80935955047607</t>
+    <t xml:space="preserve">6.783203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77884387969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81371879577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80936002731323</t>
   </si>
   <si>
     <t xml:space="preserve">6.79628133773804</t>
@@ -176,10 +176,10 @@
     <t xml:space="preserve">6.69601535797119</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81807804107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87475109100342</t>
+    <t xml:space="preserve">6.8180775642395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87475061416626</t>
   </si>
   <si>
     <t xml:space="preserve">6.91398477554321</t>
@@ -188,25 +188,25 @@
     <t xml:space="preserve">6.67421865463257</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5521559715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46496820449829</t>
+    <t xml:space="preserve">6.55215549468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46496772766113</t>
   </si>
   <si>
     <t xml:space="preserve">6.43881225585938</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73089075088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87910890579224</t>
+    <t xml:space="preserve">6.73089027404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87910985946655</t>
   </si>
   <si>
     <t xml:space="preserve">6.85295343399048</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84859275817871</t>
+    <t xml:space="preserve">6.84859418869019</t>
   </si>
   <si>
     <t xml:space="preserve">6.85731220245361</t>
@@ -215,22 +215,22 @@
     <t xml:space="preserve">6.74832773208618</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51727962493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37342071533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56523323059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66985988616943</t>
+    <t xml:space="preserve">6.51728057861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37342119216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56523418426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66985893249512</t>
   </si>
   <si>
     <t xml:space="preserve">6.77012491226196</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86167144775391</t>
+    <t xml:space="preserve">6.86167192459106</t>
   </si>
   <si>
     <t xml:space="preserve">6.97501611709595</t>
@@ -239,43 +239,43 @@
     <t xml:space="preserve">6.94162940979004</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95048379898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88407754898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90178632736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34006595611572</t>
+    <t xml:space="preserve">6.95048427581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88407850265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90178680419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34006404876709</t>
   </si>
   <si>
     <t xml:space="preserve">7.22496128082275</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41975212097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43746042251587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36662817001343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26037836074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46845054626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40204429626465</t>
+    <t xml:space="preserve">7.41975259780884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43746089935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36662769317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26037788391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46844959259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40204286575317</t>
   </si>
   <si>
     <t xml:space="preserve">7.44631481170654</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38433599472046</t>
+    <t xml:space="preserve">7.38433742523193</t>
   </si>
   <si>
     <t xml:space="preserve">7.04345178604126</t>
@@ -287,19 +287,19 @@
     <t xml:space="preserve">7.1098575592041</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8707971572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20725250244141</t>
+    <t xml:space="preserve">6.87079668045044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20725297927856</t>
   </si>
   <si>
     <t xml:space="preserve">7.37105417251587</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57027149200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69422960281372</t>
+    <t xml:space="preserve">7.57027292251587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69422912597656</t>
   </si>
   <si>
     <t xml:space="preserve">7.70308351516724</t>
@@ -308,52 +308,52 @@
     <t xml:space="preserve">7.71193742752075</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65881204605103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04396820068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61454296112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29579448699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99475431442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10100507736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55256366729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3135027885437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50829267501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42417860031128</t>
+    <t xml:space="preserve">7.6588134765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04396629333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61454343795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2957935333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99475479125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1010046005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55256414413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31350231170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50829172134399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42417907714844</t>
   </si>
   <si>
     <t xml:space="preserve">7.37548160552979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5260009765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54370880126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41532516479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21610689163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99032688140869</t>
+    <t xml:space="preserve">7.52600193023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54371070861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41532468795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21610736846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99032783508301</t>
   </si>
   <si>
     <t xml:space="preserve">6.79996395111084</t>
@@ -362,49 +362,49 @@
     <t xml:space="preserve">6.75569343566895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00803565979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26923322677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34449148178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46402311325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51714658737183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39319086074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4551682472229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1718373298645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33563804626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33121109008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39761638641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30464935302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27808666229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25152444839478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16298246383667</t>
+    <t xml:space="preserve">7.0080361366272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26923227310181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34449195861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46402406692505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51714849472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39318990707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45516872406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17183637619019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33563709259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33121061325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39761590957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30464792251587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27808570861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25152349472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16298294067383</t>
   </si>
   <si>
     <t xml:space="preserve">7.03017139434814</t>
@@ -416,28 +416,28 @@
     <t xml:space="preserve">6.91064071655273</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95490980148315</t>
+    <t xml:space="preserve">6.95491123199463</t>
   </si>
   <si>
     <t xml:space="preserve">6.88850545883179</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95933818817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85751581192017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77340221405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74683952331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82652616500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6848611831665</t>
+    <t xml:space="preserve">6.95933771133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85751533508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77340126037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74683856964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82652568817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68486070632935</t>
   </si>
   <si>
     <t xml:space="preserve">6.81767177581787</t>
@@ -452,34 +452,34 @@
     <t xml:space="preserve">6.8973593711853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83538055419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86194324493408</t>
+    <t xml:space="preserve">6.83538007736206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86194229125977</t>
   </si>
   <si>
     <t xml:space="preserve">6.92392158508301</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97704553604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00360822677612</t>
+    <t xml:space="preserve">6.97704648971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00360870361328</t>
   </si>
   <si>
     <t xml:space="preserve">6.91506767272949</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91949367523193</t>
+    <t xml:space="preserve">6.91949462890625</t>
   </si>
   <si>
     <t xml:space="preserve">6.93720245361328</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07001399993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98589992523193</t>
+    <t xml:space="preserve">7.07001447677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98590087890625</t>
   </si>
   <si>
     <t xml:space="preserve">6.75126647949219</t>
@@ -488,28 +488,28 @@
     <t xml:space="preserve">6.77782869338989</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64944458007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38381958007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37053966522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36168432235718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37939310073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40595579147339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4812159538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47678852081299</t>
+    <t xml:space="preserve">6.64944362640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38382005691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37053871154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36168479919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37939214706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40595531463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48121547698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47678804397583</t>
   </si>
   <si>
     <t xml:space="preserve">6.54319429397583</t>
@@ -527,31 +527,31 @@
     <t xml:space="preserve">6.22444629669189</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64501667022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64058971405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03902435302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79110956192017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70256853103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70699548721313</t>
+    <t xml:space="preserve">6.64501619338989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64058923721313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0390248298645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79111003875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70256900787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70699501037598</t>
   </si>
   <si>
     <t xml:space="preserve">6.65829801559448</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58303737640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05673313140869</t>
+    <t xml:space="preserve">6.58303689956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05673265457153</t>
   </si>
   <si>
     <t xml:space="preserve">7.11428499221802</t>
@@ -560,58 +560,58 @@
     <t xml:space="preserve">7.34891939163208</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18511819839478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12756586074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19397258758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24267053604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41089916229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48173046112061</t>
+    <t xml:space="preserve">7.18511867523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12756681442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19397211074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24266958236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41089868545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48173093795776</t>
   </si>
   <si>
     <t xml:space="preserve">7.14527368545532</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27365875244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17626333236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04787826538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23381567001343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2913670539856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42860651016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83589649200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82704257965088</t>
+    <t xml:space="preserve">7.27365922927856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1762638092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04787874221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23381519317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29136753082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42860555648804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83589601516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82704210281372</t>
   </si>
   <si>
     <t xml:space="preserve">8.13693523406982</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27860164642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32287216186523</t>
+    <t xml:space="preserve">8.27860260009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3228702545166</t>
   </si>
   <si>
     <t xml:space="preserve">9.03120231628418</t>
@@ -620,199 +620,199 @@
     <t xml:space="preserve">8.53094387054443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49995517730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26089191436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92495250701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58849716186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97807884216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76557731628418</t>
+    <t xml:space="preserve">8.49995422363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26089382171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92495346069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58849620819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97807598114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76557636260986</t>
   </si>
   <si>
     <t xml:space="preserve">8.87182807922363</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56244850158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25255584716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02234840393066</t>
+    <t xml:space="preserve">9.56244945526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25255393981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02234649658203</t>
   </si>
   <si>
     <t xml:space="preserve">8.85411930084229</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82755851745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71245288848877</t>
+    <t xml:space="preserve">8.82755661010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7124547958374</t>
   </si>
   <si>
     <t xml:space="preserve">8.98692989349365</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89839172363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80984878540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7213077545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78328704833984</t>
+    <t xml:space="preserve">8.8983907699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80984783172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72130966186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78328609466553</t>
   </si>
   <si>
     <t xml:space="preserve">8.67703723907471</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7567253112793</t>
+    <t xml:space="preserve">8.75672340393066</t>
   </si>
   <si>
     <t xml:space="preserve">9.10203552246094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82313060760498</t>
+    <t xml:space="preserve">8.82312965393066</t>
   </si>
   <si>
     <t xml:space="preserve">8.94266128540039</t>
   </si>
   <si>
+    <t xml:space="preserve">9.20828247070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43287563323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4598274230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52271461486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32507228851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38795757293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35202217102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42389297485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29812145233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55864810943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67543697357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86409378051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5199031829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0617341995239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88206100463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74730682373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56763172149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44186115264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54068183898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34303760528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36100769042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50474548339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48677921295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61255073547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77425670623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46881198883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5496654510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47779560089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70238780975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30710601806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28015422821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21726894378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16336631774902</t>
+  </si>
+  <si>
     <t xml:space="preserve">9.20828437805176</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43287563323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45982837677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52271366119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32507133483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38795852661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35202312469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4238920211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29812240600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55864906311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67543697357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86409282684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5199041366577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0617341995239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88206195831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74730587005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5676326751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44186019897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54068088531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34304141998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36100769042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50474643707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48678112030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61255073547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77425670623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46881198883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5496654510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47779560089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7023868560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30710506439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28015422821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21726894378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16336631774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20828342437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25320339202881</t>
+    <t xml:space="preserve">9.25320434570312</t>
   </si>
   <si>
     <t xml:space="preserve">9.45084476470947</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58559989929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33405685424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59458351135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66645240783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71137142181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40592765808105</t>
+    <t xml:space="preserve">9.58559703826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33405590057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59458255767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66645336151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71137237548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40592479705811</t>
   </si>
   <si>
     <t xml:space="preserve">9.26218700408936</t>
@@ -821,43 +821,43 @@
     <t xml:space="preserve">9.27116966247559</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28913688659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36999130249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65746879577637</t>
+    <t xml:space="preserve">9.28913879394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36999034881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65746784210205</t>
   </si>
   <si>
     <t xml:space="preserve">9.79222393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76527214050293</t>
+    <t xml:space="preserve">9.76527309417725</t>
   </si>
   <si>
     <t xml:space="preserve">9.7203540802002</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81019115447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37897396087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.909010887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81917476654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73832130432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78324031829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69340515136719</t>
+    <t xml:space="preserve">9.8101921081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37897300720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90901184082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81917572021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73832225799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78324127197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69340419769287</t>
   </si>
   <si>
     <t xml:space="preserve">9.11844635009766</t>
@@ -872,49 +872,49 @@
     <t xml:space="preserve">9.19031620025635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1004810333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22625255584717</t>
+    <t xml:space="preserve">9.10047912597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22625350952148</t>
   </si>
   <si>
     <t xml:space="preserve">9.41490936279297</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39694213867188</t>
+    <t xml:space="preserve">9.39694118499756</t>
   </si>
   <si>
     <t xml:space="preserve">9.07352924346924</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57661533355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68442058563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09149551391602</t>
+    <t xml:space="preserve">9.57661437988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68442153930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09149646759033</t>
   </si>
   <si>
     <t xml:space="preserve">9.05556201934814</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1453971862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89385414123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10946559906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2352352142334</t>
+    <t xml:space="preserve">9.14539909362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89385318756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10946273803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23523616790771</t>
   </si>
   <si>
     <t xml:space="preserve">9.95392990112305</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5109186172485</t>
+    <t xml:space="preserve">10.5109205245972</t>
   </si>
   <si>
     <t xml:space="preserve">10.74449634552</t>
@@ -926,103 +926,103 @@
     <t xml:space="preserve">10.6905937194824</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9062023162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7804307937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7085618972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6546583175659</t>
+    <t xml:space="preserve">10.9062032699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7804298400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7085599899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6546573638916</t>
   </si>
   <si>
     <t xml:space="preserve">10.5288867950439</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4390487670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3312463760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1695404052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1875057220459</t>
+    <t xml:space="preserve">10.4390506744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3312454223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1695384979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1875076293945</t>
   </si>
   <si>
     <t xml:space="preserve">10.1336040496826</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7562894821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63051986694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0078325271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84612464904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0976696014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.205472946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2773427963257</t>
+    <t xml:space="preserve">9.75629043579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63051795959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.007833480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84612560272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0976686477661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2054738998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.27734375</t>
   </si>
   <si>
     <t xml:space="preserve">10.2234411239624</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2414083480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7624616622925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2593755722046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91799640655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90002822875977</t>
+    <t xml:space="preserve">10.2414102554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7624626159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2593765258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91799545288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90002918243408</t>
   </si>
   <si>
     <t xml:space="preserve">9.67380619049072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74667930603027</t>
+    <t xml:space="preserve">9.74667835235596</t>
   </si>
   <si>
     <t xml:space="preserve">9.87420558929443</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1656951904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85598754882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63737106323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47340774536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76489734649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96529674530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0746049880981</t>
+    <t xml:space="preserve">10.165696144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85598659515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63737010955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47340679168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7648983001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96529579162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0746040344238</t>
   </si>
   <si>
     <t xml:space="preserve">10.2385663986206</t>
@@ -1034,22 +1034,22 @@
     <t xml:space="preserve">10.420747756958</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8033266067505</t>
+    <t xml:space="preserve">10.8033275604248</t>
   </si>
   <si>
     <t xml:space="preserve">10.694019317627</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6211471557617</t>
+    <t xml:space="preserve">10.6211462020874</t>
   </si>
   <si>
     <t xml:space="preserve">10.7851095199585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5482740402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4025297164917</t>
+    <t xml:space="preserve">10.5482759475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4025287628174</t>
   </si>
   <si>
     <t xml:space="preserve">10.2203493118286</t>
@@ -1058,16 +1058,16 @@
     <t xml:space="preserve">10.1474771499634</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3296575546265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5847101211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3478755950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72846221923828</t>
+    <t xml:space="preserve">10.3296585083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5847110748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3478746414185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72846126556396</t>
   </si>
   <si>
     <t xml:space="preserve">9.56449794769287</t>
@@ -1079,43 +1079,43 @@
     <t xml:space="preserve">9.40053558349609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54628086090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1110410690308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2567844390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92886066436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0199499130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2021312713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0928211212158</t>
+    <t xml:space="preserve">9.54627990722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1110420227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2567853927612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92885971069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0199489593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.202130317688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0928220748901</t>
   </si>
   <si>
     <t xml:space="preserve">9.80133247375488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69202613830566</t>
+    <t xml:space="preserve">9.69202423095703</t>
   </si>
   <si>
     <t xml:space="preserve">9.83777046203613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94707775115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89242362976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65558815002441</t>
+    <t xml:space="preserve">9.94707870483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89242458343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65558910369873</t>
   </si>
   <si>
     <t xml:space="preserve">9.78311538696289</t>
@@ -1124,130 +1124,130 @@
     <t xml:space="preserve">9.91064167022705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45519065856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2001371383667</t>
+    <t xml:space="preserve">9.4551887512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20013618469238</t>
   </si>
   <si>
     <t xml:space="preserve">9.50984287261963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43697071075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81955051422119</t>
+    <t xml:space="preserve">9.43697166442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81955146789551</t>
   </si>
   <si>
     <t xml:space="preserve">9.49162673950195</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61915302276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98351383209229</t>
+    <t xml:space="preserve">9.6191520690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9835147857666</t>
   </si>
   <si>
     <t xml:space="preserve">9.6009349822998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10904502868652</t>
+    <t xml:space="preserve">9.10904598236084</t>
   </si>
   <si>
     <t xml:space="preserve">9.09993553161621</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38231754302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36409854888916</t>
+    <t xml:space="preserve">9.3823184967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36409950256348</t>
   </si>
   <si>
     <t xml:space="preserve">9.27300930023193</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71024227142334</t>
+    <t xml:space="preserve">9.71024322509766</t>
   </si>
   <si>
     <t xml:space="preserve">9.58271598815918</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29122543334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14548110961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3660945892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32766151428223</t>
+    <t xml:space="preserve">9.29122734069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14548206329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3660936355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32766342163086</t>
   </si>
   <si>
     <t xml:space="preserve">10.0017318725586</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4754018783569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8397636413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5664930343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3114404678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2932224273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0381679534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0563859939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1292591094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2750024795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.183913230896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6758031845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7122373580933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9308547973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0219440460205</t>
+    <t xml:space="preserve">10.4754028320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8397626876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5664920806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3114395141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2932205200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0381689071655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0563869476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1292581558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2750034332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1839122772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6758012771606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7122392654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9308557510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0219459533691</t>
   </si>
   <si>
     <t xml:space="preserve">10.87619972229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.894419670105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7304544448853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.65758228302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2644643783569</t>
+    <t xml:space="preserve">10.8944177627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7304553985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6575841903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2644634246826</t>
   </si>
   <si>
     <t xml:space="preserve">11.1349868774414</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0979928970337</t>
+    <t xml:space="preserve">11.097993850708</t>
   </si>
   <si>
     <t xml:space="preserve">11.2459669113159</t>
@@ -1256,52 +1256,52 @@
     <t xml:space="preserve">11.3199529647827</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0240077972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8205432891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8390417098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7280607223511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8575372695923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7095632553101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6725702285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.65407371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7835502624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7650537490845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8020467758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5615901947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6170797348022</t>
+    <t xml:space="preserve">11.0240068435669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8205442428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8390398025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7280597686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.857536315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7095642089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6725692749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6540746688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7835493087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7650547027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8020477294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5615892410278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6170787811279</t>
   </si>
   <si>
     <t xml:space="preserve">10.3951196670532</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1176710128784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2841415405273</t>
+    <t xml:space="preserve">10.1176700592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2841396331787</t>
   </si>
   <si>
     <t xml:space="preserve">10.2656450271606</t>
@@ -1310,40 +1310,40 @@
     <t xml:space="preserve">10.3026371002197</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5061006546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3396310806274</t>
+    <t xml:space="preserve">10.5060987472534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3396301269531</t>
   </si>
   <si>
     <t xml:space="preserve">10.1361675262451</t>
   </si>
   <si>
-    <t xml:space="preserve">10.080677986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98819446563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0991735458374</t>
+    <t xml:space="preserve">10.0806770324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98819541931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0991744995117</t>
   </si>
   <si>
     <t xml:space="preserve">9.93270397186279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89571094512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96969604492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1731605529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0621814727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1546630859375</t>
+    <t xml:space="preserve">9.89570999145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96969795227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1731595993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.062180519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1546640396118</t>
   </si>
   <si>
     <t xml:space="preserve">9.71074390411377</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">10.0251874923706</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91420745849609</t>
+    <t xml:space="preserve">9.91420841217041</t>
   </si>
   <si>
     <t xml:space="preserve">9.76623439788818</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72924137115479</t>
+    <t xml:space="preserve">9.72924041748047</t>
   </si>
   <si>
     <t xml:space="preserve">9.65525341033936</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">9.67374992370605</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47028636932373</t>
+    <t xml:space="preserve">9.47028827667236</t>
   </si>
   <si>
     <t xml:space="preserve">9.54427433013916</t>
@@ -1376,79 +1376,79 @@
     <t xml:space="preserve">9.56277084350586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45179176330566</t>
+    <t xml:space="preserve">9.45179080963135</t>
   </si>
   <si>
     <t xml:space="preserve">9.35930824279785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52577781677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59976577758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61826133728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69224834442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80322742462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2286510467529</t>
+    <t xml:space="preserve">9.52577877044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59976387023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61826038360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69224739074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8032283782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2286500930786</t>
   </si>
   <si>
     <t xml:space="preserve">9.78473091125488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85871601104736</t>
+    <t xml:space="preserve">9.858717918396</t>
   </si>
   <si>
     <t xml:space="preserve">10.0066900253296</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87721538543701</t>
+    <t xml:space="preserve">9.8772144317627</t>
   </si>
   <si>
     <t xml:space="preserve">9.74773788452148</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58126735687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3211336135864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4321126937866</t>
+    <t xml:space="preserve">9.58126831054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3211345672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4321136474609</t>
   </si>
   <si>
     <t xml:space="preserve">10.3766241073608</t>
   </si>
   <si>
-    <t xml:space="preserve">10.247145652771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2101535797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84022235870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63675785064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43329334259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41479778289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39630031585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24832725524902</t>
+    <t xml:space="preserve">10.2471466064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2101545333862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84022045135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63675880432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43329524993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41479873657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39630126953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24832820892334</t>
   </si>
   <si>
     <t xml:space="preserve">9.06336116790771</t>
@@ -1460,7 +1460,7 @@
     <t xml:space="preserve">9.32231426239014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28532028198242</t>
+    <t xml:space="preserve">9.28532123565674</t>
   </si>
   <si>
     <t xml:space="preserve">9.26682472229004</t>
@@ -1469,7 +1469,7 @@
     <t xml:space="preserve">9.19283771514893</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22982978820801</t>
+    <t xml:space="preserve">9.22983074188232</t>
   </si>
   <si>
     <t xml:space="preserve">9.48878479003906</t>
@@ -1481,7 +1481,7 @@
     <t xml:space="preserve">8.9708776473999</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13734912872314</t>
+    <t xml:space="preserve">9.13734817504883</t>
   </si>
   <si>
     <t xml:space="preserve">8.96162891387939</t>
@@ -1490,16 +1490,16 @@
     <t xml:space="preserve">8.82290554046631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61944007873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55470371246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36048889160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33274269104004</t>
+    <t xml:space="preserve">8.61944198608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55470275878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36048793792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33274364471436</t>
   </si>
   <si>
     <t xml:space="preserve">8.01830101013184</t>
@@ -1508,43 +1508,43 @@
     <t xml:space="preserve">7.8148365020752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95356321334839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49114608764648</t>
+    <t xml:space="preserve">7.95356273651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49114561080933</t>
   </si>
   <si>
     <t xml:space="preserve">7.86107873916626</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50964260101318</t>
+    <t xml:space="preserve">7.50964212417603</t>
   </si>
   <si>
     <t xml:space="preserve">7.53738641738892</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58362865447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76741313934326</t>
+    <t xml:space="preserve">7.58362817764282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76741409301758</t>
   </si>
   <si>
     <t xml:space="preserve">8.98937511444092</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16509342193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12810039520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09110546112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0818567276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34081172943115</t>
+    <t xml:space="preserve">9.16509246826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12809944152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09110641479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08185863494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34081077575684</t>
   </si>
   <si>
     <t xml:space="preserve">9.04486465454102</t>
@@ -1559,49 +1559,49 @@
     <t xml:space="preserve">9.17434120178223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29456996917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11885166168213</t>
+    <t xml:space="preserve">9.29456901550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11885070800781</t>
   </si>
   <si>
     <t xml:space="preserve">8.78591156005859</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89689159393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7489185333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80440902709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87839508056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93388557434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63793849945068</t>
+    <t xml:space="preserve">8.89689254760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74891662597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80440711975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87839603424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9338846206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63793659210205</t>
   </si>
   <si>
     <t xml:space="preserve">8.71192455291748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58244800567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69342803955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46113967895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64942073822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69649028778076</t>
+    <t xml:space="preserve">8.58244609832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69342613220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46113872528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6494197845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69649124145508</t>
   </si>
   <si>
     <t xml:space="preserve">9.74356079101562</t>
@@ -1610,7 +1610,7 @@
     <t xml:space="preserve">9.97891330718994</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93184280395508</t>
+    <t xml:space="preserve">9.93184185028076</t>
   </si>
   <si>
     <t xml:space="preserve">9.79063129425049</t>
@@ -1622,13 +1622,13 @@
     <t xml:space="preserve">10.3084058761597</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4496154785156</t>
+    <t xml:space="preserve">10.4496173858643</t>
   </si>
   <si>
     <t xml:space="preserve">10.1671953201294</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1201229095459</t>
+    <t xml:space="preserve">10.1201238632202</t>
   </si>
   <si>
     <t xml:space="preserve">10.0259828567505</t>
@@ -1643,28 +1643,28 @@
     <t xml:space="preserve">10.2613344192505</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88477230072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5908269882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4966869354248</t>
+    <t xml:space="preserve">9.8847713470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5908279418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4966859817505</t>
   </si>
   <si>
     <t xml:space="preserve">10.5437564849854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2027416229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1556711196899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9673900604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0615310668945</t>
+    <t xml:space="preserve">11.2027406692505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1556720733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9673891067505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0615301132202</t>
   </si>
   <si>
     <t xml:space="preserve">10.7791080474854</t>
@@ -1676,22 +1676,22 @@
     <t xml:space="preserve">11.0144605636597</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1086015701294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9203205108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8732490539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7320375442505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6378984451294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5322351455688</t>
+    <t xml:space="preserve">11.1086006164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9203195571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8732500076294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7320394515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6378974914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5322341918945</t>
   </si>
   <si>
     <t xml:space="preserve">11.6263751983643</t>
@@ -1706,34 +1706,34 @@
     <t xml:space="preserve">11.5793046951294</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6734457015991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.720516204834</t>
+    <t xml:space="preserve">11.6734447479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7205152511597</t>
   </si>
   <si>
     <t xml:space="preserve">12.0029382705688</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2853603363037</t>
+    <t xml:space="preserve">12.2853593826294</t>
   </si>
   <si>
     <t xml:space="preserve">12.5677824020386</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5207109451294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.897274017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.756064414978</t>
+    <t xml:space="preserve">12.5207118988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8972730636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7560625076294</t>
   </si>
   <si>
     <t xml:space="preserve">12.661922454834</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6148519515991</t>
+    <t xml:space="preserve">12.6148509979248</t>
   </si>
   <si>
     <t xml:space="preserve">12.8031339645386</t>
@@ -1745,13 +1745,13 @@
     <t xml:space="preserve">12.9914150238037</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1796970367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.462119102478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.838680267334</t>
+    <t xml:space="preserve">13.1796960830688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4621181488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8386812210083</t>
   </si>
   <si>
     <t xml:space="preserve">13.7445402145386</t>
@@ -1760,16 +1760,16 @@
     <t xml:space="preserve">13.6504001617432</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5091905593872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7916107177734</t>
+    <t xml:space="preserve">13.5091886520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7916097640991</t>
   </si>
   <si>
     <t xml:space="preserve">13.8857507705688</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9798917770386</t>
+    <t xml:space="preserve">13.9798927307129</t>
   </si>
   <si>
     <t xml:space="preserve">14.0269613265991</t>
@@ -1784,10 +1784,10 @@
     <t xml:space="preserve">14.1211032867432</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2623128890991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2152452468872</t>
+    <t xml:space="preserve">14.2623138427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2152442932129</t>
   </si>
   <si>
     <t xml:space="preserve">14.4505958557129</t>
@@ -1802,25 +1802,25 @@
     <t xml:space="preserve">14.403525352478</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3564538955688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5447368621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5918054580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6388759613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7800874710083</t>
+    <t xml:space="preserve">14.3564548492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5447359085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5918064117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.638876914978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7800884246826</t>
   </si>
   <si>
     <t xml:space="preserve">14.8271589279175</t>
   </si>
   <si>
-    <t xml:space="preserve">14.874228477478</t>
+    <t xml:space="preserve">14.8742294311523</t>
   </si>
   <si>
     <t xml:space="preserve">14.7330169677734</t>
@@ -1829,16 +1829,16 @@
     <t xml:space="preserve">15.3449306488037</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7685651779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0039176940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0415744781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0792293548584</t>
+    <t xml:space="preserve">15.7685642242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0039157867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.041576385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.079231262207</t>
   </si>
   <si>
     <t xml:space="preserve">16.1921997070312</t>
@@ -1856,55 +1856,55 @@
     <t xml:space="preserve">16.3993072509766</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4181346893311</t>
+    <t xml:space="preserve">16.4181365966797</t>
   </si>
   <si>
     <t xml:space="preserve">16.5311050415039</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2675113677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9286041259766</t>
+    <t xml:space="preserve">16.2675132751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9286060333252</t>
   </si>
   <si>
     <t xml:space="preserve">15.8909473419189</t>
   </si>
   <si>
-    <t xml:space="preserve">15.815634727478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9662590026855</t>
+    <t xml:space="preserve">15.8156366348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9662599563599</t>
   </si>
   <si>
     <t xml:space="preserve">15.7214956283569</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5332145690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5143842697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7026681900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2696189880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4767284393311</t>
+    <t xml:space="preserve">15.5332126617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.51438331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7026691436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2696180343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4767293930054</t>
   </si>
   <si>
     <t xml:space="preserve">15.683837890625</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6650094985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4202442169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1566514968872</t>
+    <t xml:space="preserve">15.6650104522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4202432632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1566505432129</t>
   </si>
   <si>
     <t xml:space="preserve">15.2319631576538</t>
@@ -1913,13 +1913,13 @@
     <t xml:space="preserve">15.777979850769</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9833717346191</t>
+    <t xml:space="preserve">15.9833736419678</t>
   </si>
   <si>
     <t xml:space="preserve">15.964301109314</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6209812164307</t>
+    <t xml:space="preserve">15.6209802627563</t>
   </si>
   <si>
     <t xml:space="preserve">15.4874687194824</t>
@@ -1928,10 +1928,10 @@
     <t xml:space="preserve">15.7926397323608</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8117141723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6019105911255</t>
+    <t xml:space="preserve">15.8117122650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6019086837769</t>
   </si>
   <si>
     <t xml:space="preserve">15.5446872711182</t>
@@ -1943,7 +1943,10 @@
     <t xml:space="preserve">15.6972723007202</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8307876586914</t>
+    <t xml:space="preserve">15.8307857513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1168842315674</t>
   </si>
   <si>
     <t xml:space="preserve">16.2504005432129</t>
@@ -1952,19 +1955,19 @@
     <t xml:space="preserve">16.2313251495361</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0024471282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2694721221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2122535705566</t>
+    <t xml:space="preserve">16.0024452209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2694702148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.212251663208</t>
   </si>
   <si>
     <t xml:space="preserve">16.460205078125</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4411334991455</t>
+    <t xml:space="preserve">16.4411296844482</t>
   </si>
   <si>
     <t xml:space="preserve">16.5364971160889</t>
@@ -1979,7 +1982,7 @@
     <t xml:space="preserve">16.9561080932617</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2231349945068</t>
+    <t xml:space="preserve">17.2231330871582</t>
   </si>
   <si>
     <t xml:space="preserve">17.3185005187988</t>
@@ -1988,25 +1991,25 @@
     <t xml:space="preserve">17.0896224975586</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8416690826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7463035583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9751815795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1277656555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5092334747314</t>
+    <t xml:space="preserve">16.841667175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.746301651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9751796722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1277675628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5092315673828</t>
   </si>
   <si>
     <t xml:space="preserve">17.5473785400391</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7571849822998</t>
+    <t xml:space="preserve">17.7571830749512</t>
   </si>
   <si>
     <t xml:space="preserve">17.6427440643311</t>
@@ -2015,25 +2018,25 @@
     <t xml:space="preserve">17.7381114959717</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4901580810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4710845947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.337574005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2994251251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3566455841064</t>
+    <t xml:space="preserve">17.4901599884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4710865020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3375720977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2994270324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3566474914551</t>
   </si>
   <si>
     <t xml:space="preserve">17.2422065734863</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1468391418457</t>
+    <t xml:space="preserve">17.1468410491943</t>
   </si>
   <si>
     <t xml:space="preserve">17.0133266448975</t>
@@ -2042,37 +2045,37 @@
     <t xml:space="preserve">17.4520111083984</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8334770202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6999645233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8716239929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8525505065918</t>
+    <t xml:space="preserve">17.8334789276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6999626159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8716220855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8525485992432</t>
   </si>
   <si>
     <t xml:space="preserve">18.0242080688477</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4247455596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5010395050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6536273956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5964050292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5582580566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7108478546143</t>
+    <t xml:space="preserve">18.424747467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5010414123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6536254882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5964069366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5582599639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7108459472656</t>
   </si>
   <si>
     <t xml:space="preserve">18.8062114715576</t>
@@ -2084,10 +2087,10 @@
     <t xml:space="preserve">19.5500679016113</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5023880004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8838500976562</t>
+    <t xml:space="preserve">19.5023860931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8838481903076</t>
   </si>
   <si>
     <t xml:space="preserve">19.9792175292969</t>
@@ -2099,13 +2102,13 @@
     <t xml:space="preserve">19.3593349456787</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1686058044434</t>
+    <t xml:space="preserve">19.1686038970947</t>
   </si>
   <si>
     <t xml:space="preserve">18.7871398925781</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6917743682861</t>
+    <t xml:space="preserve">18.6917724609375</t>
   </si>
   <si>
     <t xml:space="preserve">19.2162857055664</t>
@@ -2117,37 +2120,37 @@
     <t xml:space="preserve">18.76806640625</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9097709655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1195735931396</t>
+    <t xml:space="preserve">17.9097690582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1195755004883</t>
   </si>
   <si>
     <t xml:space="preserve">17.6236705780029</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8906955718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1005020141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2530860900879</t>
+    <t xml:space="preserve">17.890697479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1005001068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2530879974365</t>
   </si>
   <si>
     <t xml:space="preserve">17.9669895172119</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1767959594727</t>
+    <t xml:space="preserve">18.176794052124</t>
   </si>
   <si>
     <t xml:space="preserve">18.9969444274902</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0732364654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9778709411621</t>
+    <t xml:space="preserve">19.0732383728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9778690338135</t>
   </si>
   <si>
     <t xml:space="preserve">18.8825035095215</t>
@@ -2156,22 +2159,22 @@
     <t xml:space="preserve">18.9397258758545</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9015769958496</t>
+    <t xml:space="preserve">18.9015789031982</t>
   </si>
   <si>
     <t xml:space="preserve">20.0268974304199</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2176303863525</t>
+    <t xml:space="preserve">20.2176322937012</t>
   </si>
   <si>
     <t xml:space="preserve">20.2653160095215</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7421474456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9328804016113</t>
+    <t xml:space="preserve">20.7421455383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9328765869141</t>
   </si>
   <si>
     <t xml:space="preserve">21.2189769744873</t>
@@ -2180,16 +2183,16 @@
     <t xml:space="preserve">21.4573917388916</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6944618225098</t>
+    <t xml:space="preserve">20.6944637298584</t>
   </si>
   <si>
     <t xml:space="preserve">20.3129978179932</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4560489654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9805603027344</t>
+    <t xml:space="preserve">20.4560470581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.980562210083</t>
   </si>
   <si>
     <t xml:space="preserve">19.8361663818359</t>
@@ -2198,25 +2201,25 @@
     <t xml:space="preserve">20.4083633422852</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1222667694092</t>
+    <t xml:space="preserve">20.1222648620605</t>
   </si>
   <si>
     <t xml:space="preserve">19.311653137207</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2639713287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.597749710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6454372406006</t>
+    <t xml:space="preserve">19.2639694213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5977516174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.645435333252</t>
   </si>
   <si>
     <t xml:space="preserve">20.1699485778809</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9315319061279</t>
+    <t xml:space="preserve">19.9315338134766</t>
   </si>
   <si>
     <t xml:space="preserve">19.7408008575439</t>
@@ -2225,13 +2228,13 @@
     <t xml:space="preserve">18.8443584442139</t>
   </si>
   <si>
-    <t xml:space="preserve">19.016019821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.043285369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0051345825195</t>
+    <t xml:space="preserve">19.0160179138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0432796478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0051364898682</t>
   </si>
   <si>
     <t xml:space="preserve">18.1386489868164</t>
@@ -2243,64 +2246,64 @@
     <t xml:space="preserve">18.0814266204834</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6045970916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2612800598145</t>
+    <t xml:space="preserve">17.6045989990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2612819671631</t>
   </si>
   <si>
     <t xml:space="preserve">17.0514736175537</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2885437011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0324020385742</t>
+    <t xml:space="preserve">16.2885456085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0324039459229</t>
   </si>
   <si>
     <t xml:space="preserve">16.7272300720215</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4792766571045</t>
+    <t xml:space="preserve">16.4792785644531</t>
   </si>
   <si>
     <t xml:space="preserve">16.8225936889648</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0705490112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6509342193604</t>
+    <t xml:space="preserve">17.0705471038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.650936126709</t>
   </si>
   <si>
     <t xml:space="preserve">16.8607425689697</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3076171875</t>
+    <t xml:space="preserve">16.3076190948486</t>
   </si>
   <si>
     <t xml:space="preserve">16.5937175750732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6318626403809</t>
+    <t xml:space="preserve">16.6318645477295</t>
   </si>
   <si>
     <t xml:space="preserve">15.277663230896</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8771257400513</t>
+    <t xml:space="preserve">14.877124786377</t>
   </si>
   <si>
     <t xml:space="preserve">14.4956607818604</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3730306625366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9915637969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0869302749634</t>
+    <t xml:space="preserve">15.3730297088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9915647506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0869312286377</t>
   </si>
   <si>
     <t xml:space="preserve">15.6782007217407</t>
@@ -2309,28 +2312,28 @@
     <t xml:space="preserve">15.1441507339478</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9452257156372</t>
+    <t xml:space="preserve">15.9452247619629</t>
   </si>
   <si>
     <t xml:space="preserve">16.0787410736084</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0405902862549</t>
+    <t xml:space="preserve">16.0405921936035</t>
   </si>
   <si>
     <t xml:space="preserve">16.5746421813965</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6890850067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5174217224121</t>
+    <t xml:space="preserve">16.6890830993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5174236297607</t>
   </si>
   <si>
     <t xml:space="preserve">16.4983501434326</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7354211807251</t>
+    <t xml:space="preserve">15.7354202270508</t>
   </si>
   <si>
     <t xml:space="preserve">15.8880062103271</t>
@@ -2339,13 +2342,13 @@
     <t xml:space="preserve">15.5065422058105</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9724922180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3348836898804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2204427719116</t>
+    <t xml:space="preserve">14.9724912643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3348827362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2204437255859</t>
   </si>
   <si>
     <t xml:space="preserve">14.9152717590332</t>
@@ -2354,10 +2357,10 @@
     <t xml:space="preserve">14.781759262085</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8961992263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6400547027588</t>
+    <t xml:space="preserve">14.8961982727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6400537490845</t>
   </si>
   <si>
     <t xml:space="preserve">16.0978126525879</t>
@@ -2375,16 +2378,16 @@
     <t xml:space="preserve">16.1999359130859</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3547744750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0450973510742</t>
+    <t xml:space="preserve">16.354772567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0450954437256</t>
   </si>
   <si>
     <t xml:space="preserve">16.1418704986572</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2773532867432</t>
+    <t xml:space="preserve">16.2773551940918</t>
   </si>
   <si>
     <t xml:space="preserve">16.4709033966064</t>
@@ -2399,40 +2402,40 @@
     <t xml:space="preserve">17.767671585083</t>
   </si>
   <si>
-    <t xml:space="preserve">17.419282913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2321853637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7289600372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9418659210205</t>
+    <t xml:space="preserve">17.4192848205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2321834564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7289619445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9418640136719</t>
   </si>
   <si>
     <t xml:space="preserve">17.4967041015625</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5934791564941</t>
+    <t xml:space="preserve">17.5934772491455</t>
   </si>
   <si>
     <t xml:space="preserve">17.4579963684082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8967037200928</t>
+    <t xml:space="preserve">16.8967056274414</t>
   </si>
   <si>
     <t xml:space="preserve">16.4515476226807</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9870338439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8321962356567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9483232498169</t>
+    <t xml:space="preserve">15.9870328903198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8321943283081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9483213424683</t>
   </si>
   <si>
     <t xml:space="preserve">15.3676805496216</t>
@@ -2441,10 +2444,10 @@
     <t xml:space="preserve">15.4450988769531</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1741333007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1160688400269</t>
+    <t xml:space="preserve">15.1741323471069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1160678863525</t>
   </si>
   <si>
     <t xml:space="preserve">15.135422706604</t>
@@ -2456,10 +2459,10 @@
     <t xml:space="preserve">15.619291305542</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8902597427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7547750473022</t>
+    <t xml:space="preserve">15.8902587890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7547760009766</t>
   </si>
   <si>
     <t xml:space="preserve">15.8128395080566</t>
@@ -2471,28 +2474,25 @@
     <t xml:space="preserve">15.6580018997192</t>
   </si>
   <si>
-    <t xml:space="preserve">15.870903968811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4128360748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4321899414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7354202270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7160663604736</t>
+    <t xml:space="preserve">15.8709030151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4128379821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4321918487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7160654067993</t>
   </si>
   <si>
     <t xml:space="preserve">16.0644512176514</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5289669036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6838054656982</t>
+    <t xml:space="preserve">16.5289649963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6838035583496</t>
   </si>
   <si>
     <t xml:space="preserve">16.5096111297607</t>
@@ -2501,40 +2501,40 @@
     <t xml:space="preserve">16.9160594940186</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5354137420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3805732727051</t>
+    <t xml:space="preserve">17.5354156494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3805751800537</t>
   </si>
   <si>
     <t xml:space="preserve">17.3418674468994</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2063827514648</t>
+    <t xml:space="preserve">17.2063808441162</t>
   </si>
   <si>
     <t xml:space="preserve">17.3225116729736</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2838020324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0515441894531</t>
+    <t xml:space="preserve">17.2838039398193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0515460968018</t>
   </si>
   <si>
     <t xml:space="preserve">16.8386421203613</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2450904846191</t>
+    <t xml:space="preserve">17.2450923919678</t>
   </si>
   <si>
     <t xml:space="preserve">17.6128330230713</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8192882537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1096096038818</t>
+    <t xml:space="preserve">16.8192863464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1096076965332</t>
   </si>
   <si>
     <t xml:space="preserve">16.7225131988525</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">16.4902572631836</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1225147247314</t>
+    <t xml:space="preserve">16.1225166320801</t>
   </si>
   <si>
     <t xml:space="preserve">16.0257415771484</t>
@@ -2561,7 +2561,7 @@
     <t xml:space="preserve">15.5031642913818</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2128419876099</t>
+    <t xml:space="preserve">15.2128429412842</t>
   </si>
   <si>
     <t xml:space="preserve">15.3096160888672</t>
@@ -2570,10 +2570,10 @@
     <t xml:space="preserve">15.5805826187134</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1547775268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1934871673584</t>
+    <t xml:space="preserve">15.1547765731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1934881210327</t>
   </si>
   <si>
     <t xml:space="preserve">16.0838069915771</t>
@@ -2582,13 +2582,13 @@
     <t xml:space="preserve">15.7741289138794</t>
   </si>
   <si>
-    <t xml:space="preserve">15.677357673645</t>
+    <t xml:space="preserve">15.6773567199707</t>
   </si>
   <si>
     <t xml:space="preserve">15.5612277984619</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1805782318115</t>
+    <t xml:space="preserve">16.1805820465088</t>
   </si>
   <si>
     <t xml:space="preserve">16.8579978942871</t>
@@ -2597,31 +2597,31 @@
     <t xml:space="preserve">17.3031558990479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9031524658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8063812255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1676731109619</t>
+    <t xml:space="preserve">17.9031543731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8063793182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1676712036133</t>
   </si>
   <si>
     <t xml:space="preserve">17.5160598754883</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3612194061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.735408782959</t>
+    <t xml:space="preserve">17.3612213134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7354106903076</t>
   </si>
   <si>
     <t xml:space="preserve">18.6579895019531</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4837970733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1741218566895</t>
+    <t xml:space="preserve">18.4837989807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1741199493408</t>
   </si>
   <si>
     <t xml:space="preserve">17.7870235443115</t>
@@ -2648,10 +2648,10 @@
     <t xml:space="preserve">18.1547660827637</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0192813873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9805736541748</t>
+    <t xml:space="preserve">18.0192832946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9805717468262</t>
   </si>
   <si>
     <t xml:space="preserve">17.961217880249</t>
@@ -2669,7 +2669,7 @@
     <t xml:space="preserve">17.6515426635742</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4386405944824</t>
+    <t xml:space="preserve">17.4386425018311</t>
   </si>
   <si>
     <t xml:space="preserve">17.3999290466309</t>
@@ -2681,10 +2681,10 @@
     <t xml:space="preserve">17.7096061706543</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4773483276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8257369995117</t>
+    <t xml:space="preserve">17.4773502349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8257350921631</t>
   </si>
   <si>
     <t xml:space="preserve">18.5805721282959</t>
@@ -2693,7 +2693,7 @@
     <t xml:space="preserve">18.9289569854736</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8128299713135</t>
+    <t xml:space="preserve">18.8128280639648</t>
   </si>
   <si>
     <t xml:space="preserve">19.5483093261719</t>
@@ -2702,88 +2702,88 @@
     <t xml:space="preserve">19.9354057312012</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7902450561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0321769714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7418556213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5966968536377</t>
+    <t xml:space="preserve">19.7902431488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0321788787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7418575286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5966949462891</t>
   </si>
   <si>
     <t xml:space="preserve">19.9837894439697</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8386287689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0805644989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3708839416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8870162963867</t>
+    <t xml:space="preserve">19.8386306762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0805625915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.370885848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8870143890381</t>
   </si>
   <si>
     <t xml:space="preserve">19.6450805664062</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1289520263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.177339553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4192752838135</t>
+    <t xml:space="preserve">20.1289501190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1773376464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4192733764648</t>
   </si>
   <si>
     <t xml:space="preserve">20.467658996582</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2418518066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1934623718262</t>
+    <t xml:space="preserve">21.241849899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1934642791748</t>
   </si>
   <si>
     <t xml:space="preserve">21.435396194458</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5805587768555</t>
+    <t xml:space="preserve">21.5805568695068</t>
   </si>
   <si>
     <t xml:space="preserve">21.6773319244385</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6289443969727</t>
+    <t xml:space="preserve">21.6289463043213</t>
   </si>
   <si>
     <t xml:space="preserve">22.0644283294678</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2579727172852</t>
+    <t xml:space="preserve">22.2579765319824</t>
   </si>
   <si>
     <t xml:space="preserve">22.6450710296631</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0321655273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4676475524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3224868774414</t>
+    <t xml:space="preserve">23.0321636199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4676456451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.32248878479</t>
   </si>
   <si>
     <t xml:space="preserve">22.7902297973633</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7418422698975</t>
+    <t xml:space="preserve">22.7418441772461</t>
   </si>
   <si>
     <t xml:space="preserve">21.9676532745361</t>
@@ -2795,7 +2795,7 @@
     <t xml:space="preserve">22.1612014770508</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3063621520996</t>
+    <t xml:space="preserve">22.306360244751</t>
   </si>
   <si>
     <t xml:space="preserve">21.8224925994873</t>
@@ -2813,31 +2813,31 @@
     <t xml:space="preserve">22.9837779998779</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9031295776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.193452835083</t>
+    <t xml:space="preserve">23.9031314849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1934509277344</t>
   </si>
   <si>
     <t xml:space="preserve">24.0966758728027</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0160312652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9676399230957</t>
+    <t xml:space="preserve">25.0160293579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9676418304443</t>
   </si>
   <si>
     <t xml:space="preserve">25.4031238555908</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8386058807373</t>
+    <t xml:space="preserve">25.8386077880859</t>
   </si>
   <si>
     <t xml:space="preserve">25.9353790283203</t>
   </si>
   <si>
-    <t xml:space="preserve">25.354736328125</t>
+    <t xml:space="preserve">25.3547382354736</t>
   </si>
   <si>
     <t xml:space="preserve">25.161190032959</t>
@@ -2852,22 +2852,22 @@
     <t xml:space="preserve">25.451509475708</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2095737457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5482845306396</t>
+    <t xml:space="preserve">25.2095756530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.548282623291</t>
   </si>
   <si>
     <t xml:space="preserve">25.6450595855713</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1773128509521</t>
+    <t xml:space="preserve">26.1773109436035</t>
   </si>
   <si>
     <t xml:space="preserve">26.5160217285156</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9515056610107</t>
+    <t xml:space="preserve">26.9515037536621</t>
   </si>
   <si>
     <t xml:space="preserve">25.6934432983398</t>
@@ -2876,13 +2876,13 @@
     <t xml:space="preserve">25.5966720581055</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3063507080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8869934082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3708629608154</t>
+    <t xml:space="preserve">25.3063488006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8869915008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3708610534668</t>
   </si>
   <si>
     <t xml:space="preserve">26.2043304443359</t>
@@ -2891,7 +2891,7 @@
     <t xml:space="preserve">25.616569519043</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1267700195312</t>
+    <t xml:space="preserve">25.1267681121826</t>
   </si>
   <si>
     <t xml:space="preserve">25.9594306945801</t>
@@ -2903,16 +2903,16 @@
     <t xml:space="preserve">25.2737083435059</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0288066864014</t>
+    <t xml:space="preserve">25.02880859375</t>
   </si>
   <si>
     <t xml:space="preserve">25.2247295379639</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7349281311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4410495758057</t>
+    <t xml:space="preserve">24.7349300384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.441047668457</t>
   </si>
   <si>
     <t xml:space="preserve">24.8818683624268</t>
@@ -2927,10 +2927,10 @@
     <t xml:space="preserve">24.4900283813477</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7839088439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8328876495361</t>
+    <t xml:space="preserve">24.7839069366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8328895568848</t>
   </si>
   <si>
     <t xml:space="preserve">24.979829788208</t>
@@ -2939,19 +2939,19 @@
     <t xml:space="preserve">25.4696292877197</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9104499816895</t>
+    <t xml:space="preserve">25.9104518890381</t>
   </si>
   <si>
     <t xml:space="preserve">25.8614692687988</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7635097503662</t>
+    <t xml:space="preserve">25.7635078430176</t>
   </si>
   <si>
     <t xml:space="preserve">25.7145290374756</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2533092498779</t>
+    <t xml:space="preserve">26.2533111572266</t>
   </si>
   <si>
     <t xml:space="preserve">26.6941299438477</t>
@@ -2963,7 +2963,7 @@
     <t xml:space="preserve">26.7920913696289</t>
   </si>
   <si>
-    <t xml:space="preserve">26.596170425415</t>
+    <t xml:space="preserve">26.5961685180664</t>
   </si>
   <si>
     <t xml:space="preserve">26.4492301940918</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">25.3716678619385</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1471691131592</t>
+    <t xml:space="preserve">24.1471672058105</t>
   </si>
   <si>
     <t xml:space="preserve">26.3512687683105</t>
@@ -3008,13 +3008,13 @@
     <t xml:space="preserve">26.9880104064941</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9390316009521</t>
+    <t xml:space="preserve">26.9390296936035</t>
   </si>
   <si>
     <t xml:space="preserve">26.0573902130127</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1063709259033</t>
+    <t xml:space="preserve">26.1063690185547</t>
   </si>
   <si>
     <t xml:space="preserve">26.6451511383057</t>
@@ -3029,40 +3029,40 @@
     <t xml:space="preserve">27.134952545166</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1553497314453</t>
+    <t xml:space="preserve">26.1553516387939</t>
   </si>
   <si>
     <t xml:space="preserve">27.3798522949219</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3308696746826</t>
+    <t xml:space="preserve">27.3308715820312</t>
   </si>
   <si>
     <t xml:space="preserve">27.7227115631104</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6737308502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0165920257568</t>
+    <t xml:space="preserve">27.6737327575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0165939331055</t>
   </si>
   <si>
     <t xml:space="preserve">27.5757713317871</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4778099060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5267925262451</t>
+    <t xml:space="preserve">27.4778118133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5267906188965</t>
   </si>
   <si>
     <t xml:space="preserve">25.8124904632568</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3022918701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2818927764893</t>
+    <t xml:space="preserve">26.3022899627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2818908691406</t>
   </si>
   <si>
     <t xml:space="preserve">27.4288330078125</t>
@@ -3071,13 +3071,13 @@
     <t xml:space="preserve">27.23291015625</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6247539520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8410701751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4982089996338</t>
+    <t xml:space="preserve">27.6247520446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8410720825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4982109069824</t>
   </si>
   <si>
     <t xml:space="preserve">25.567590713501</t>
@@ -3104,7 +3104,7 @@
     <t xml:space="preserve">28.5553722381592</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0451736450195</t>
+    <t xml:space="preserve">29.0451717376709</t>
   </si>
   <si>
     <t xml:space="preserve">29.1431331634521</t>
@@ -3122,10 +3122,10 @@
     <t xml:space="preserve">29.6819133758545</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7798748016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1921119689941</t>
+    <t xml:space="preserve">29.7798728942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1921138763428</t>
   </si>
   <si>
     <t xml:space="preserve">29.5349731445312</t>
@@ -3137,10 +3137,10 @@
     <t xml:space="preserve">30.2206954956055</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5145740509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8574352264404</t>
+    <t xml:space="preserve">30.514575958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8574371337891</t>
   </si>
   <si>
     <t xml:space="preserve">32.1798973083496</t>
@@ -3155,10 +3155,10 @@
     <t xml:space="preserve">32.5227584838867</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0901184082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.824821472168</t>
+    <t xml:space="preserve">34.0901222229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8248176574707</t>
   </si>
   <si>
     <t xml:space="preserve">34.2860374450684</t>
@@ -3167,22 +3167,22 @@
     <t xml:space="preserve">34.6288986206055</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1390991210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7758407592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.747257232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8941955566406</t>
+    <t xml:space="preserve">34.1390953063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7758369445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7472610473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8941993713379</t>
   </si>
   <si>
     <t xml:space="preserve">34.335018157959</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9431838989258</t>
+    <t xml:space="preserve">33.9431800842285</t>
   </si>
   <si>
     <t xml:space="preserve">35.0207405090332</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">35.4125823974609</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9635810852051</t>
+    <t xml:space="preserve">32.9635772705078</t>
   </si>
   <si>
     <t xml:space="preserve">32.9145965576172</t>
@@ -3209,7 +3209,7 @@
     <t xml:space="preserve">33.0125579833984</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4451942443848</t>
+    <t xml:space="preserve">31.4451961517334</t>
   </si>
   <si>
     <t xml:space="preserve">31.5641193389893</t>
@@ -3828,6 +3828,9 @@
   </si>
   <si>
     <t xml:space="preserve">51.5999984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51</t>
   </si>
 </sst>
 </file>
@@ -40064,7 +40067,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1381" t="s">
-        <v>610</v>
+        <v>644</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -40090,7 +40093,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1382" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -40116,7 +40119,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1383" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -40142,7 +40145,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1384" t="s">
-        <v>610</v>
+        <v>644</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -40194,7 +40197,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1386" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -40220,7 +40223,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1387" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -40246,7 +40249,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G1388" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -40298,7 +40301,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1390" t="s">
-        <v>610</v>
+        <v>644</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -40324,7 +40327,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1391" t="s">
-        <v>610</v>
+        <v>644</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -40350,7 +40353,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1392" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -40376,7 +40379,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1393" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -40402,7 +40405,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1394" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -40428,7 +40431,7 @@
         <v>17</v>
       </c>
       <c r="G1395" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -40454,7 +40457,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1396" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -40480,7 +40483,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1397" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -40506,7 +40509,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1398" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -40532,7 +40535,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1399" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -40558,7 +40561,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1400" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -40584,7 +40587,7 @@
         <v>18</v>
       </c>
       <c r="G1401" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -40610,7 +40613,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1402" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -40636,7 +40639,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1403" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -40662,7 +40665,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1404" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -40688,7 +40691,7 @@
         <v>18</v>
       </c>
       <c r="G1405" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -40714,7 +40717,7 @@
         <v>18</v>
       </c>
       <c r="G1406" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -40740,7 +40743,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1407" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -40766,7 +40769,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G1408" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -40792,7 +40795,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1409" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -40818,7 +40821,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1410" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -40844,7 +40847,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1411" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -40870,7 +40873,7 @@
         <v>18</v>
       </c>
       <c r="G1412" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -40896,7 +40899,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G1413" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -40922,7 +40925,7 @@
         <v>18</v>
       </c>
       <c r="G1414" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -40948,7 +40951,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G1415" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -40974,7 +40977,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1416" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -41000,7 +41003,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1417" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -41026,7 +41029,7 @@
         <v>18.5</v>
       </c>
       <c r="G1418" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -41052,7 +41055,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1419" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -41078,7 +41081,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1420" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -41104,7 +41107,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1421" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -41130,7 +41133,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1422" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -41156,7 +41159,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1423" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -41182,7 +41185,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1424" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -41208,7 +41211,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1425" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -41234,7 +41237,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1426" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -41260,7 +41263,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1427" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -41286,7 +41289,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G1428" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -41312,7 +41315,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G1429" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -41338,7 +41341,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1430" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -41364,7 +41367,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1431" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -41390,7 +41393,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1432" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -41416,7 +41419,7 @@
         <v>18.5</v>
       </c>
       <c r="G1433" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -41442,7 +41445,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1434" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -41468,7 +41471,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1435" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -41494,7 +41497,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1436" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -41520,7 +41523,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G1437" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -41546,7 +41549,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1438" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -41572,7 +41575,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1439" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -41598,7 +41601,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1440" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -41624,7 +41627,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1441" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -41650,7 +41653,7 @@
         <v>19.5</v>
       </c>
       <c r="G1442" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -41676,7 +41679,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1443" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -41702,7 +41705,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G1444" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -41728,7 +41731,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1445" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -41754,7 +41757,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1446" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -41780,7 +41783,7 @@
         <v>20.5</v>
       </c>
       <c r="G1447" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -41806,7 +41809,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1448" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -41832,7 +41835,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1449" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -41858,7 +41861,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1450" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -41884,7 +41887,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1451" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -41910,7 +41913,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1452" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -41936,7 +41939,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1453" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -41962,7 +41965,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1454" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -41988,7 +41991,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1455" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -42014,7 +42017,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1456" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -42040,7 +42043,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1457" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -42066,7 +42069,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1458" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -42092,7 +42095,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1459" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -42118,7 +42121,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G1460" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -42144,7 +42147,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1461" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -42170,7 +42173,7 @@
         <v>19</v>
       </c>
       <c r="G1462" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -42196,7 +42199,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1463" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -42222,7 +42225,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G1464" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -42248,7 +42251,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1465" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -42274,7 +42277,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G1466" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -42300,7 +42303,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G1467" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -42326,7 +42329,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1468" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -42352,7 +42355,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1469" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -42378,7 +42381,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1470" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -42404,7 +42407,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1471" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -42430,7 +42433,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1472" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -42456,7 +42459,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G1473" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -42482,7 +42485,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1474" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -42508,7 +42511,7 @@
         <v>20</v>
       </c>
       <c r="G1475" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -42534,7 +42537,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1476" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -42560,7 +42563,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1477" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -42586,7 +42589,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1478" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -42612,7 +42615,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G1479" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -42638,7 +42641,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1480" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -42664,7 +42667,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1481" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -42690,7 +42693,7 @@
         <v>20</v>
       </c>
       <c r="G1482" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -42716,7 +42719,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1483" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -42742,7 +42745,7 @@
         <v>20</v>
       </c>
       <c r="G1484" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -42768,7 +42771,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1485" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -42794,7 +42797,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1486" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -42820,7 +42823,7 @@
         <v>20</v>
       </c>
       <c r="G1487" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -42846,7 +42849,7 @@
         <v>20</v>
       </c>
       <c r="G1488" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -42872,7 +42875,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G1489" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -42898,7 +42901,7 @@
         <v>20</v>
       </c>
       <c r="G1490" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -42924,7 +42927,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1491" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -42950,7 +42953,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1492" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -42976,7 +42979,7 @@
         <v>21</v>
       </c>
       <c r="G1493" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -43002,7 +43005,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1494" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -43028,7 +43031,7 @@
         <v>21.25</v>
       </c>
       <c r="G1495" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -43054,7 +43057,7 @@
         <v>21.75</v>
       </c>
       <c r="G1496" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -43080,7 +43083,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G1497" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -43106,7 +43109,7 @@
         <v>22.25</v>
       </c>
       <c r="G1498" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -43132,7 +43135,7 @@
         <v>22.5</v>
       </c>
       <c r="G1499" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -43158,7 +43161,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1500" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -43184,7 +43187,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1501" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -43210,7 +43213,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G1502" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -43236,7 +43239,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1503" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -43262,7 +43265,7 @@
         <v>22</v>
       </c>
       <c r="G1504" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -43288,7 +43291,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1505" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -43314,7 +43317,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1506" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -43340,7 +43343,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1507" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -43366,7 +43369,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1508" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -43392,7 +43395,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1509" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -43418,7 +43421,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1510" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -43444,7 +43447,7 @@
         <v>20.25</v>
       </c>
       <c r="G1511" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -43470,7 +43473,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1512" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -43496,7 +43499,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1513" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -43522,7 +43525,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1514" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -43548,7 +43551,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1515" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -43574,7 +43577,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G1516" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -43600,7 +43603,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1517" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -43626,7 +43629,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1518" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -43652,7 +43655,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1519" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -43678,7 +43681,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1520" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -43704,7 +43707,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1521" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -43730,7 +43733,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1522" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -43756,7 +43759,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1523" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -43782,7 +43785,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1524" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -43808,7 +43811,7 @@
         <v>21</v>
       </c>
       <c r="G1525" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -43834,7 +43837,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1526" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -43860,7 +43863,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1527" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -43886,7 +43889,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1528" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -43912,7 +43915,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1529" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -43938,7 +43941,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1530" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -43964,7 +43967,7 @@
         <v>20.5</v>
       </c>
       <c r="G1531" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -43990,7 +43993,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G1532" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -44016,7 +44019,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1533" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -44042,7 +44045,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1534" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -44068,7 +44071,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1535" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -44094,7 +44097,7 @@
         <v>20</v>
       </c>
       <c r="G1536" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -44120,7 +44123,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1537" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -44146,7 +44149,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1538" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -44172,7 +44175,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G1539" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -44198,7 +44201,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1540" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -44224,7 +44227,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1541" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -44250,7 +44253,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G1542" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -44276,7 +44279,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1543" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -44302,7 +44305,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1544" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -44328,7 +44331,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1545" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -44354,7 +44357,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G1546" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -44380,7 +44383,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G1547" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -44406,7 +44409,7 @@
         <v>19</v>
       </c>
       <c r="G1548" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -44432,7 +44435,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G1549" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -44458,7 +44461,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G1550" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -44484,7 +44487,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1551" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -44510,7 +44513,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G1552" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -44536,7 +44539,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G1553" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -44562,7 +44565,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1554" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -44588,7 +44591,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1555" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -44614,7 +44617,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1556" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -44640,7 +44643,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1557" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -44666,7 +44669,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G1558" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -44692,7 +44695,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1559" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -44718,7 +44721,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1560" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -44744,7 +44747,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G1561" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -44770,7 +44773,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1562" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -44796,7 +44799,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1563" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -44822,7 +44825,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G1564" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -44848,7 +44851,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1565" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -44874,7 +44877,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1566" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -44900,7 +44903,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1567" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -44926,7 +44929,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1568" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -44952,7 +44955,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1569" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -44978,7 +44981,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G1570" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -45004,7 +45007,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G1571" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -45030,7 +45033,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1572" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -45056,7 +45059,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1573" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -45082,7 +45085,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G1574" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -45108,7 +45111,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G1575" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -45134,7 +45137,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1576" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -45160,7 +45163,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1577" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -45186,7 +45189,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1578" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -45212,7 +45215,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1579" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -45238,7 +45241,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G1580" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -45264,7 +45267,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1581" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -45290,7 +45293,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1582" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -45316,7 +45319,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1583" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -45342,7 +45345,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1584" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -45368,7 +45371,7 @@
         <v>17</v>
       </c>
       <c r="G1585" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -45394,7 +45397,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G1586" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -45420,7 +45423,7 @@
         <v>17.5</v>
       </c>
       <c r="G1587" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -45446,7 +45449,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1588" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -45472,7 +45475,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1589" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -45498,7 +45501,7 @@
         <v>16.5</v>
       </c>
       <c r="G1590" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -45524,7 +45527,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1591" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -45602,7 +45605,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G1594" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -45628,7 +45631,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G1595" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -45680,7 +45683,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1597" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -45732,7 +45735,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G1599" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -45758,7 +45761,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G1600" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -45784,7 +45787,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1601" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -45810,7 +45813,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1602" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -45836,7 +45839,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G1603" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -45862,7 +45865,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1604" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -45888,7 +45891,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1605" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -45914,7 +45917,7 @@
         <v>15.5</v>
       </c>
       <c r="G1606" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -45940,7 +45943,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G1607" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -45966,7 +45969,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1608" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -46018,7 +46021,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G1610" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -46070,7 +46073,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1612" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -46148,7 +46151,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G1615" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -46200,7 +46203,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1617" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -46226,7 +46229,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G1618" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -46252,7 +46255,7 @@
         <v>16.5</v>
       </c>
       <c r="G1619" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -46278,7 +46281,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1620" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -46304,7 +46307,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1621" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -46330,7 +46333,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1622" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -46356,7 +46359,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G1623" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -46382,7 +46385,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1624" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -46408,7 +46411,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1625" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -46434,7 +46437,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1626" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -46460,7 +46463,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1627" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -46486,7 +46489,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1628" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -46512,7 +46515,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G1629" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -46538,7 +46541,7 @@
         <v>18</v>
       </c>
       <c r="G1630" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -46564,7 +46567,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1631" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -46590,7 +46593,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1632" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -46616,7 +46619,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1633" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -46642,7 +46645,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1634" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -46668,7 +46671,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1635" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -46694,7 +46697,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1636" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -46720,7 +46723,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1637" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -46746,7 +46749,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1638" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -46772,7 +46775,7 @@
         <v>17</v>
       </c>
       <c r="G1639" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -46798,7 +46801,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1640" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -46824,7 +46827,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1641" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -46850,7 +46853,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1642" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -46876,7 +46879,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1643" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -46902,7 +46905,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1644" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -46928,7 +46931,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1645" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -46954,7 +46957,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1646" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -46980,7 +46983,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G1647" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -47006,7 +47009,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1648" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -47032,7 +47035,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G1649" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -47058,7 +47061,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1650" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -47084,7 +47087,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G1651" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -47110,7 +47113,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G1652" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -47136,7 +47139,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1653" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -47162,7 +47165,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1654" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -47188,7 +47191,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1655" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -47214,7 +47217,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G1656" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -47240,7 +47243,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1657" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -47266,7 +47269,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1658" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -47292,7 +47295,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1659" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -47318,7 +47321,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G1660" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -47344,7 +47347,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1661" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -47370,7 +47373,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G1662" t="s">
-        <v>822</v>
+        <v>773</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -47448,7 +47451,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1665" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -47474,7 +47477,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1666" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -47500,7 +47503,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G1667" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -47526,7 +47529,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1668" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -47552,7 +47555,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1669" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -47968,7 +47971,7 @@
         <v>18</v>
       </c>
       <c r="G1685" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -48020,7 +48023,7 @@
         <v>18</v>
       </c>
       <c r="G1687" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -48072,7 +48075,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1689" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -48202,7 +48205,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1694" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -48228,7 +48231,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1695" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -48280,7 +48283,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1697" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -48384,7 +48387,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1701" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -48462,7 +48465,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1704" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -48488,7 +48491,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1705" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -48540,7 +48543,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1707" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -48592,7 +48595,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G1709" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -48644,7 +48647,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1711" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -48982,7 +48985,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1724" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -49034,7 +49037,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1726" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -49086,7 +49089,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1728" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -49268,7 +49271,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1735" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -49398,7 +49401,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1740" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -49450,7 +49453,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1742" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -49476,7 +49479,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1743" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -49970,7 +49973,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1762" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -50048,7 +50051,7 @@
         <v>18</v>
       </c>
       <c r="G1765" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -50100,7 +50103,7 @@
         <v>18</v>
       </c>
       <c r="G1767" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -50334,7 +50337,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1776" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -50412,7 +50415,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1779" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -50542,7 +50545,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1784" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -50620,7 +50623,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1787" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -68906,7 +68909,7 @@
     </row>
     <row r="2491">
       <c r="A2491" s="1" t="n">
-        <v>45946.6496412037</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2491" t="n">
         <v>55273</v>
@@ -68927,6 +68930,32 @@
         <v>1271</v>
       </c>
       <c r="H2491" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="1" t="n">
+        <v>45947.649525463</v>
+      </c>
+      <c r="B2492" t="n">
+        <v>44929</v>
+      </c>
+      <c r="C2492" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>50.2999992370605</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>51.0999984741211</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>51</v>
+      </c>
+      <c r="G2492" t="s">
+        <v>1272</v>
+      </c>
+      <c r="H2492" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SOL.MI.xlsx
+++ b/data/SOL.MI.xlsx
@@ -44,31 +44,31 @@
     <t xml:space="preserve">SOL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1406717300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18862533569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16246938705444</t>
+    <t xml:space="preserve">7.14067268371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18862581253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1624698638916</t>
   </si>
   <si>
     <t xml:space="preserve">7.0622034072876</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90962505340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90526580810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94885873794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71781206130981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62626552581787</t>
+    <t xml:space="preserve">6.90962553024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90526676177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94885969161987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71781158447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62626504898071</t>
   </si>
   <si>
     <t xml:space="preserve">6.71345233917236</t>
@@ -83,46 +83,46 @@
     <t xml:space="preserve">6.43009281158447</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41265487670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4475302696228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20776414871216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17288875579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.460608959198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54779624938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38214015960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51292133331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50420188903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65242147445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80064058303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72217130661011</t>
+    <t xml:space="preserve">6.4126558303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44753074645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20776319503784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17288780212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46060800552368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54779720306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38213968276978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51292085647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5042028427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6524224281311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80064153671265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72217178344727</t>
   </si>
   <si>
     <t xml:space="preserve">6.79192209243774</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00989007949829</t>
+    <t xml:space="preserve">7.00989198684692</t>
   </si>
   <si>
     <t xml:space="preserve">6.84423446655273</t>
@@ -131,13 +131,13 @@
     <t xml:space="preserve">7.07964134216309</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88346910476685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9662971496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08835983276367</t>
+    <t xml:space="preserve">6.883469581604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96629762649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08836030960083</t>
   </si>
   <si>
     <t xml:space="preserve">6.73524951934814</t>
@@ -146,28 +146,28 @@
     <t xml:space="preserve">6.83115673065186</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6785774230957</t>
+    <t xml:space="preserve">6.67857789993286</t>
   </si>
   <si>
     <t xml:space="preserve">6.57395219802856</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63062429428101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68729639053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.783203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77884387969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81371879577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80936002731323</t>
+    <t xml:space="preserve">6.63062572479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68729734420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78320264816284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77884483337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81371927261353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80935955047607</t>
   </si>
   <si>
     <t xml:space="preserve">6.79628133773804</t>
@@ -179,28 +179,28 @@
     <t xml:space="preserve">6.8180775642395</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87475061416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91398477554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67421865463257</t>
+    <t xml:space="preserve">6.8747501373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91398429870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67421913146973</t>
   </si>
   <si>
     <t xml:space="preserve">6.55215549468994</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46496772766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43881225585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73089027404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87910985946655</t>
+    <t xml:space="preserve">6.46496820449829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43881130218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73089075088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87910938262939</t>
   </si>
   <si>
     <t xml:space="preserve">6.85295343399048</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">6.84859418869019</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85731220245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74832773208618</t>
+    <t xml:space="preserve">6.85731267929077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74832725524902</t>
   </si>
   <si>
     <t xml:space="preserve">6.51728057861328</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">6.37342119216919</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56523418426514</t>
+    <t xml:space="preserve">6.56523370742798</t>
   </si>
   <si>
     <t xml:space="preserve">6.66985893249512</t>
@@ -239,16 +239,16 @@
     <t xml:space="preserve">6.94162940979004</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95048427581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88407850265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90178680419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34006404876709</t>
+    <t xml:space="preserve">6.95048379898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88407802581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9017858505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34006452560425</t>
   </si>
   <si>
     <t xml:space="preserve">7.22496128082275</t>
@@ -266,19 +266,19 @@
     <t xml:space="preserve">7.26037788391113</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46844959259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40204286575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44631481170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38433742523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04345178604126</t>
+    <t xml:space="preserve">7.46845054626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40204334259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44631385803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38433504104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04345226287842</t>
   </si>
   <si>
     <t xml:space="preserve">6.97261905670166</t>
@@ -287,19 +287,19 @@
     <t xml:space="preserve">7.1098575592041</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87079668045044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20725297927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37105417251587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57027292251587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69422912597656</t>
+    <t xml:space="preserve">6.87079620361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20725393295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37105512619019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57027244567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69422960281372</t>
   </si>
   <si>
     <t xml:space="preserve">7.70308351516724</t>
@@ -308,49 +308,49 @@
     <t xml:space="preserve">7.71193742752075</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6588134765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04396629333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61454343795776</t>
+    <t xml:space="preserve">7.65881204605103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04396724700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61454153060913</t>
   </si>
   <si>
     <t xml:space="preserve">7.2957935333252</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99475479125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1010046005249</t>
+    <t xml:space="preserve">6.99475383758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10100412368774</t>
   </si>
   <si>
     <t xml:space="preserve">7.55256414413452</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31350231170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50829172134399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42417907714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37548160552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52600193023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54371070861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41532468795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21610736846924</t>
+    <t xml:space="preserve">7.31350326538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50829219818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4241795539856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37548065185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52600240707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54370927810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41532564163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2161078453064</t>
   </si>
   <si>
     <t xml:space="preserve">6.99032783508301</t>
@@ -359,10 +359,10 @@
     <t xml:space="preserve">6.79996395111084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75569343566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0080361366272</t>
+    <t xml:space="preserve">6.7556939125061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00803518295288</t>
   </si>
   <si>
     <t xml:space="preserve">7.26923227310181</t>
@@ -371,67 +371,67 @@
     <t xml:space="preserve">7.34449195861816</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46402406692505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51714849472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39318990707397</t>
+    <t xml:space="preserve">7.46402359008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5171480178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39318943023682</t>
   </si>
   <si>
     <t xml:space="preserve">7.45516872406006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17183637619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33563709259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33121061325073</t>
+    <t xml:space="preserve">7.17183685302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33563804626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33121109008789</t>
   </si>
   <si>
     <t xml:space="preserve">7.39761590957642</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30464792251587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27808570861816</t>
+    <t xml:space="preserve">7.30464935302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27808618545532</t>
   </si>
   <si>
     <t xml:space="preserve">7.25152349472046</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16298294067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03017139434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87965059280396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91064071655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95491123199463</t>
+    <t xml:space="preserve">7.16298246383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03017044067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87965106964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91064023971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95491075515747</t>
   </si>
   <si>
     <t xml:space="preserve">6.88850545883179</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95933771133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85751533508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77340126037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74683856964111</t>
+    <t xml:space="preserve">6.95933866500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85751581192017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77340078353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74683904647827</t>
   </si>
   <si>
     <t xml:space="preserve">6.82652568817139</t>
@@ -440,28 +440,28 @@
     <t xml:space="preserve">6.68486070632935</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81767177581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90621328353882</t>
+    <t xml:space="preserve">6.81767129898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90621376037598</t>
   </si>
   <si>
     <t xml:space="preserve">7.01689004898071</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8973593711853</t>
+    <t xml:space="preserve">6.89735889434814</t>
   </si>
   <si>
     <t xml:space="preserve">6.83538007736206</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86194229125977</t>
+    <t xml:space="preserve">6.86194324493408</t>
   </si>
   <si>
     <t xml:space="preserve">6.92392158508301</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97704648971558</t>
+    <t xml:space="preserve">6.97704601287842</t>
   </si>
   <si>
     <t xml:space="preserve">7.00360870361328</t>
@@ -473,34 +473,34 @@
     <t xml:space="preserve">6.91949462890625</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93720245361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07001447677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98590087890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75126647949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77782869338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64944362640381</t>
+    <t xml:space="preserve">6.93720197677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07001495361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98589992523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75126600265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77782917022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64944410324097</t>
   </si>
   <si>
     <t xml:space="preserve">6.38382005691528</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37053871154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36168479919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37939214706421</t>
+    <t xml:space="preserve">6.37053966522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36168432235718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37939310073853</t>
   </si>
   <si>
     <t xml:space="preserve">6.40595531463623</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">6.48121547698975</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47678804397583</t>
+    <t xml:space="preserve">6.4767894744873</t>
   </si>
   <si>
     <t xml:space="preserve">6.54319429397583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46350765228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24215459823608</t>
+    <t xml:space="preserve">6.46350717544556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24215412139893</t>
   </si>
   <si>
     <t xml:space="preserve">6.25986242294312</t>
@@ -527,10 +527,10 @@
     <t xml:space="preserve">6.22444629669189</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64501619338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64058923721313</t>
+    <t xml:space="preserve">6.64501667022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64058971405029</t>
   </si>
   <si>
     <t xml:space="preserve">7.0390248298645</t>
@@ -539,46 +539,46 @@
     <t xml:space="preserve">6.79111003875732</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70256900787354</t>
+    <t xml:space="preserve">6.70256853103638</t>
   </si>
   <si>
     <t xml:space="preserve">6.70699501037598</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65829801559448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58303689956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05673265457153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11428499221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34891939163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18511867523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12756681442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19397211074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24266958236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41089868545532</t>
+    <t xml:space="preserve">6.65829849243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58303737640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05673313140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11428546905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34891891479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18511772155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12756586074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19397258758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2426700592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41089820861816</t>
   </si>
   <si>
     <t xml:space="preserve">7.48173093795776</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14527368545532</t>
+    <t xml:space="preserve">7.14527416229248</t>
   </si>
   <si>
     <t xml:space="preserve">7.27365922927856</t>
@@ -587,88 +587,88 @@
     <t xml:space="preserve">7.1762638092041</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04787874221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23381519317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29136753082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42860555648804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83589601516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82704210281372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13693523406982</t>
+    <t xml:space="preserve">7.04787969589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23381567001343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29136657714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42860651016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83589696884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82704162597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13693618774414</t>
   </si>
   <si>
     <t xml:space="preserve">8.27860260009766</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3228702545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03120231628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53094387054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49995422363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26089382171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92495346069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58849620819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97807598114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76557636260986</t>
+    <t xml:space="preserve">8.32287216186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0312032699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53094291687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49995517730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26089286804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92495441436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5884952545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97807693481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7655782699585</t>
   </si>
   <si>
     <t xml:space="preserve">8.87182807922363</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56244945526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25255393981934</t>
+    <t xml:space="preserve">9.56244850158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25255489349365</t>
   </si>
   <si>
     <t xml:space="preserve">9.02234649658203</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85411930084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82755661010742</t>
+    <t xml:space="preserve">8.8541202545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82755756378174</t>
   </si>
   <si>
     <t xml:space="preserve">8.7124547958374</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98692989349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8983907699585</t>
+    <t xml:space="preserve">8.98693084716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89838981628418</t>
   </si>
   <si>
     <t xml:space="preserve">8.80984783172607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72130966186523</t>
+    <t xml:space="preserve">8.72130870819092</t>
   </si>
   <si>
     <t xml:space="preserve">8.78328609466553</t>
@@ -677,37 +677,37 @@
     <t xml:space="preserve">8.67703723907471</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75672340393066</t>
+    <t xml:space="preserve">8.75672435760498</t>
   </si>
   <si>
     <t xml:space="preserve">9.10203552246094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82312965393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94266128540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20828247070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43287563323975</t>
+    <t xml:space="preserve">8.82313060760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94266033172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20828342437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43287658691406</t>
   </si>
   <si>
     <t xml:space="preserve">9.4598274230957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52271461486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32507228851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38795757293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35202217102051</t>
+    <t xml:space="preserve">9.52271366119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32507133483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38795852661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35202312469482</t>
   </si>
   <si>
     <t xml:space="preserve">9.42389297485352</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">9.55864810943604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67543697357178</t>
+    <t xml:space="preserve">9.67543601989746</t>
   </si>
   <si>
     <t xml:space="preserve">9.86409378051758</t>
@@ -728,25 +728,25 @@
     <t xml:space="preserve">10.5199031829834</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0617341995239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88206100463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74730682373047</t>
+    <t xml:space="preserve">10.0617351531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88206195831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74730587005615</t>
   </si>
   <si>
     <t xml:space="preserve">9.56763172149658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44186115264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54068183898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34303760528564</t>
+    <t xml:space="preserve">9.44185924530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54068088531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34303951263428</t>
   </si>
   <si>
     <t xml:space="preserve">9.36100769042969</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">9.50474548339844</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48677921295166</t>
+    <t xml:space="preserve">9.48677825927734</t>
   </si>
   <si>
     <t xml:space="preserve">9.61255073547363</t>
@@ -764,25 +764,25 @@
     <t xml:space="preserve">9.77425670623779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46881198883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5496654510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47779560089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70238780975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30710601806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28015422821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21726894378662</t>
+    <t xml:space="preserve">9.46881103515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54966354370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4777946472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7023868560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30710506439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28015518188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2172679901123</t>
   </si>
   <si>
     <t xml:space="preserve">9.16336631774902</t>
@@ -791,37 +791,37 @@
     <t xml:space="preserve">9.20828437805176</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25320434570312</t>
+    <t xml:space="preserve">9.25320339202881</t>
   </si>
   <si>
     <t xml:space="preserve">9.45084476470947</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58559703826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33405590057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59458255767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66645336151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71137237548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40592479705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26218700408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27116966247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28913879394531</t>
+    <t xml:space="preserve">9.58559989929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33405685424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59458351135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66645431518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71137142181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40592670440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26218605041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27116870880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.289137840271</t>
   </si>
   <si>
     <t xml:space="preserve">9.36999034881592</t>
@@ -830,10 +830,10 @@
     <t xml:space="preserve">9.65746784210205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79222393035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76527309417725</t>
+    <t xml:space="preserve">9.79222297668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76527214050293</t>
   </si>
   <si>
     <t xml:space="preserve">9.7203540802002</t>
@@ -845,16 +845,16 @@
     <t xml:space="preserve">9.37897300720215</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90901184082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81917572021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73832225799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78324127197266</t>
+    <t xml:space="preserve">9.909010887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81917476654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73832321166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78324031829834</t>
   </si>
   <si>
     <t xml:space="preserve">9.69340419769287</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">9.11844635009766</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08251190185547</t>
+    <t xml:space="preserve">9.08251285552979</t>
   </si>
   <si>
     <t xml:space="preserve">9.31608867645264</t>
@@ -872,106 +872,106 @@
     <t xml:space="preserve">9.19031620025635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10047912597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22625350952148</t>
+    <t xml:space="preserve">9.1004810333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22625160217285</t>
   </si>
   <si>
     <t xml:space="preserve">9.41490936279297</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39694118499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07352924346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57661437988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68442153930664</t>
+    <t xml:space="preserve">9.39694213867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07352828979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57661533355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68442058563232</t>
   </si>
   <si>
     <t xml:space="preserve">9.09149646759033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05556201934814</t>
+    <t xml:space="preserve">9.05556297302246</t>
   </si>
   <si>
     <t xml:space="preserve">9.14539909362793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89385318756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10946273803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23523616790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95392990112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5109205245972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.74449634552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.546854019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6905937194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9062032699585</t>
+    <t xml:space="preserve">8.89385509490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10946464538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2352352142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95393180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5109214782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7444953918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5468521118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6905918121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9062023162842</t>
   </si>
   <si>
     <t xml:space="preserve">10.7804298400879</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7085599899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6546573638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5288867950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4390506744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3312454223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1695384979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1875076293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1336040496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75629043579102</t>
+    <t xml:space="preserve">10.7085609436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6546583175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5288877487183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4390487670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.331244468689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1695404052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1875057220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.133602142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7562894821167</t>
   </si>
   <si>
     <t xml:space="preserve">9.63051795959473</t>
   </si>
   <si>
-    <t xml:space="preserve">10.007833480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84612560272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0976686477661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2054738998413</t>
+    <t xml:space="preserve">10.0078325271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84612655639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0976705551147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.205472946167</t>
   </si>
   <si>
     <t xml:space="preserve">10.27734375</t>
@@ -980,7 +980,7 @@
     <t xml:space="preserve">10.2234411239624</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2414102554321</t>
+    <t xml:space="preserve">10.2414083480835</t>
   </si>
   <si>
     <t xml:space="preserve">10.7624626159668</t>
@@ -992,7 +992,7 @@
     <t xml:space="preserve">9.91799545288086</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90002918243408</t>
+    <t xml:space="preserve">9.90002822875977</t>
   </si>
   <si>
     <t xml:space="preserve">9.67380619049072</t>
@@ -1001,13 +1001,13 @@
     <t xml:space="preserve">9.74667835235596</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87420558929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.165696144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85598659515381</t>
+    <t xml:space="preserve">9.87420654296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1656942367554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85598754882812</t>
   </si>
   <si>
     <t xml:space="preserve">9.63737010955811</t>
@@ -1022,10 +1022,10 @@
     <t xml:space="preserve">9.96529579162598</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0746040344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2385663986206</t>
+    <t xml:space="preserve">10.0746068954468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2385673522949</t>
   </si>
   <si>
     <t xml:space="preserve">10.3843126296997</t>
@@ -1034,40 +1034,40 @@
     <t xml:space="preserve">10.420747756958</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8033275604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.694019317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6211462020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7851095199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5482759475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4025287628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2203493118286</t>
+    <t xml:space="preserve">10.8033266067505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6940202713013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6211471557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7851104736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5482749938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.402530670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2203502655029</t>
   </si>
   <si>
     <t xml:space="preserve">10.1474771499634</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3296585083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5847110748291</t>
+    <t xml:space="preserve">10.3296575546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5847101211548</t>
   </si>
   <si>
     <t xml:space="preserve">10.3478746414185</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72846126556396</t>
+    <t xml:space="preserve">9.72846031188965</t>
   </si>
   <si>
     <t xml:space="preserve">9.56449794769287</t>
@@ -1076,13 +1076,13 @@
     <t xml:space="preserve">9.4187536239624</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40053558349609</t>
+    <t xml:space="preserve">9.40053462982178</t>
   </si>
   <si>
     <t xml:space="preserve">9.54627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1110420227051</t>
+    <t xml:space="preserve">10.1110410690308</t>
   </si>
   <si>
     <t xml:space="preserve">10.2567853927612</t>
@@ -1091,31 +1091,31 @@
     <t xml:space="preserve">9.92885971069336</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0199489593506</t>
+    <t xml:space="preserve">10.0199508666992</t>
   </si>
   <si>
     <t xml:space="preserve">10.202130317688</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0928220748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80133247375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69202423095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83777046203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94707870483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89242458343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65558910369873</t>
+    <t xml:space="preserve">10.0928239822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8013334274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69202613830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83776950836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94707679748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89242362976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65558815002441</t>
   </si>
   <si>
     <t xml:space="preserve">9.78311538696289</t>
@@ -1133,37 +1133,37 @@
     <t xml:space="preserve">9.50984287261963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43697166442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81955146789551</t>
+    <t xml:space="preserve">9.43697071075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81955051422119</t>
   </si>
   <si>
     <t xml:space="preserve">9.49162673950195</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6191520690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9835147857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6009349822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10904598236084</t>
+    <t xml:space="preserve">9.61915302276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98351383209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60093307495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10904693603516</t>
   </si>
   <si>
     <t xml:space="preserve">9.09993553161621</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3823184967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36409950256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27300930023193</t>
+    <t xml:space="preserve">9.38231754302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36409759521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27300834655762</t>
   </si>
   <si>
     <t xml:space="preserve">9.71024322509766</t>
@@ -1175,7 +1175,7 @@
     <t xml:space="preserve">9.29122734069824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14548206329346</t>
+    <t xml:space="preserve">9.14548110961914</t>
   </si>
   <si>
     <t xml:space="preserve">10.3660936355591</t>
@@ -1190,61 +1190,61 @@
     <t xml:space="preserve">10.4754028320312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8397626876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5664920806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3114395141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2932205200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0381689071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0563869476318</t>
+    <t xml:space="preserve">10.8397636413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5664930343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3114404678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2932233810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0381679534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0563840866089</t>
   </si>
   <si>
     <t xml:space="preserve">10.1292581558228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2750034332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1839122772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6758012771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7122392654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9308557510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0219459533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.87619972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8944177627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7304553985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6575841903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2644634246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1349868774414</t>
+    <t xml:space="preserve">10.2750024795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1839141845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.675802230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7122383117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9308547973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0219449996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8762006759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.894419670105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7304544448853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6575832366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2644643783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1349859237671</t>
   </si>
   <si>
     <t xml:space="preserve">11.097993850708</t>
@@ -1259,130 +1259,130 @@
     <t xml:space="preserve">11.0240068435669</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8205442428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8390398025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7280597686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.857536315918</t>
+    <t xml:space="preserve">10.8205432891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8390407562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7280607223511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8575353622437</t>
   </si>
   <si>
     <t xml:space="preserve">10.7095642089844</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6725692749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6540746688843</t>
+    <t xml:space="preserve">10.672571182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6540727615356</t>
   </si>
   <si>
     <t xml:space="preserve">10.7835493087769</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7650547027588</t>
+    <t xml:space="preserve">10.7650537490845</t>
   </si>
   <si>
     <t xml:space="preserve">10.8020477294922</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5615892410278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6170787811279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3951196670532</t>
+    <t xml:space="preserve">10.5615911483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6170797348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3951215744019</t>
   </si>
   <si>
     <t xml:space="preserve">10.1176700592041</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2841396331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2656450271606</t>
+    <t xml:space="preserve">10.284140586853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2656440734863</t>
   </si>
   <si>
     <t xml:space="preserve">10.3026371002197</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5060987472534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3396301269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1361675262451</t>
+    <t xml:space="preserve">10.5060997009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3396291732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1361665725708</t>
   </si>
   <si>
     <t xml:space="preserve">10.0806770324707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98819541931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0991744995117</t>
+    <t xml:space="preserve">9.98819351196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0991735458374</t>
   </si>
   <si>
     <t xml:space="preserve">9.93270397186279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89570999145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96969795227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1731595993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.062180519104</t>
+    <t xml:space="preserve">9.89571094512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96969699859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1731605529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0621814727783</t>
   </si>
   <si>
     <t xml:space="preserve">10.1546640396118</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71074390411377</t>
+    <t xml:space="preserve">9.71074485778809</t>
   </si>
   <si>
     <t xml:space="preserve">10.0251874923706</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91420841217041</t>
+    <t xml:space="preserve">9.91420650482178</t>
   </si>
   <si>
     <t xml:space="preserve">9.76623439788818</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72924041748047</t>
+    <t xml:space="preserve">9.7292423248291</t>
   </si>
   <si>
     <t xml:space="preserve">9.65525341033936</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67374992370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47028827667236</t>
+    <t xml:space="preserve">9.67375087738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47028732299805</t>
   </si>
   <si>
     <t xml:space="preserve">9.54427433013916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56277084350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45179080963135</t>
+    <t xml:space="preserve">9.56277179718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45179176330566</t>
   </si>
   <si>
     <t xml:space="preserve">9.35930824279785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52577877044678</t>
+    <t xml:space="preserve">9.52577686309814</t>
   </si>
   <si>
     <t xml:space="preserve">9.59976387023926</t>
@@ -1397,7 +1397,7 @@
     <t xml:space="preserve">9.8032283782959</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2286500930786</t>
+    <t xml:space="preserve">10.2286510467529</t>
   </si>
   <si>
     <t xml:space="preserve">9.78473091125488</t>
@@ -1406,70 +1406,70 @@
     <t xml:space="preserve">9.858717918396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0066900253296</t>
+    <t xml:space="preserve">10.0066909790039</t>
   </si>
   <si>
     <t xml:space="preserve">9.8772144317627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74773788452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58126831054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3211345672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4321136474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3766241073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2471466064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2101545333862</t>
+    <t xml:space="preserve">9.74773693084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58126735687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3211336135864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4321126937866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3766250610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2471475601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2101535797119</t>
   </si>
   <si>
     <t xml:space="preserve">9.84022045135498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63675880432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43329524993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41479873657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39630126953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24832820892334</t>
+    <t xml:space="preserve">9.63675689697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43329334259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41479778289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39630031585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24832725524902</t>
   </si>
   <si>
     <t xml:space="preserve">9.06336116790771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10960292816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32231426239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28532123565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26682472229004</t>
+    <t xml:space="preserve">9.1096019744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32231330871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28532028198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26682567596436</t>
   </si>
   <si>
     <t xml:space="preserve">9.19283771514893</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22983074188232</t>
+    <t xml:space="preserve">9.22982978820801</t>
   </si>
   <si>
     <t xml:space="preserve">9.48878479003906</t>
@@ -1481,7 +1481,7 @@
     <t xml:space="preserve">8.9708776473999</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13734817504883</t>
+    <t xml:space="preserve">9.13734912872314</t>
   </si>
   <si>
     <t xml:space="preserve">8.96162891387939</t>
@@ -1490,40 +1490,40 @@
     <t xml:space="preserve">8.82290554046631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61944198608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55470275878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36048793792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33274364471436</t>
+    <t xml:space="preserve">8.61944007873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55470371246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36048889160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33274555206299</t>
   </si>
   <si>
     <t xml:space="preserve">8.01830101013184</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8148365020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95356273651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49114561080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86107873916626</t>
+    <t xml:space="preserve">7.81483745574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95356130599976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49114608764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86107921600342</t>
   </si>
   <si>
     <t xml:space="preserve">7.50964212417603</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53738641738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58362817764282</t>
+    <t xml:space="preserve">7.53738689422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58362913131714</t>
   </si>
   <si>
     <t xml:space="preserve">8.76741409301758</t>
@@ -1532,22 +1532,22 @@
     <t xml:space="preserve">8.98937511444092</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16509246826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12809944152832</t>
+    <t xml:space="preserve">9.16509437561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.128098487854</t>
   </si>
   <si>
     <t xml:space="preserve">9.09110641479492</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08185863494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34081077575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04486465454102</t>
+    <t xml:space="preserve">9.0818567276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34081268310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04486560821533</t>
   </si>
   <si>
     <t xml:space="preserve">9.21133422851562</t>
@@ -1568,37 +1568,37 @@
     <t xml:space="preserve">8.78591156005859</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89689254760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74891662597656</t>
+    <t xml:space="preserve">8.89689064025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7489185333252</t>
   </si>
   <si>
     <t xml:space="preserve">8.80440711975098</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87839603424072</t>
+    <t xml:space="preserve">8.87839508056641</t>
   </si>
   <si>
     <t xml:space="preserve">8.9338846206665</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63793659210205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71192455291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58244609832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69342613220215</t>
+    <t xml:space="preserve">8.63793754577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7119255065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58244705200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69342803955078</t>
   </si>
   <si>
     <t xml:space="preserve">9.46113872528076</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6494197845459</t>
+    <t xml:space="preserve">9.64942073822021</t>
   </si>
   <si>
     <t xml:space="preserve">9.69649124145508</t>
@@ -1616,55 +1616,55 @@
     <t xml:space="preserve">9.79063129425049</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0730533599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3084058761597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4496173858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1671953201294</t>
+    <t xml:space="preserve">10.0730543136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3084049224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4496164321899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1671943664551</t>
   </si>
   <si>
     <t xml:space="preserve">10.1201238632202</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0259828567505</t>
+    <t xml:space="preserve">10.0259838104248</t>
   </si>
   <si>
     <t xml:space="preserve">10.2142648696899</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3554754257202</t>
+    <t xml:space="preserve">10.3554744720459</t>
   </si>
   <si>
     <t xml:space="preserve">10.2613344192505</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8847713470459</t>
+    <t xml:space="preserve">9.88477230072021</t>
   </si>
   <si>
     <t xml:space="preserve">10.5908279418945</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4966859817505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5437564849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2027406692505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1556720733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9673891067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0615301132202</t>
+    <t xml:space="preserve">10.4966869354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5437574386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2027416229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1556711196899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9673900604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0615310668945</t>
   </si>
   <si>
     <t xml:space="preserve">10.7791080474854</t>
@@ -1676,22 +1676,22 @@
     <t xml:space="preserve">11.0144605636597</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1086006164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9203195571899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8732500076294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7320394515991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6378974914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5322341918945</t>
+    <t xml:space="preserve">11.1086025238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9203205108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8732490539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7320384979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6378984451294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5322351455688</t>
   </si>
   <si>
     <t xml:space="preserve">11.6263751983643</t>
@@ -1718,16 +1718,16 @@
     <t xml:space="preserve">12.2853593826294</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5677824020386</t>
+    <t xml:space="preserve">12.5677814483643</t>
   </si>
   <si>
     <t xml:space="preserve">12.5207118988037</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8972730636597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7560625076294</t>
+    <t xml:space="preserve">12.8972749710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7560634613037</t>
   </si>
   <si>
     <t xml:space="preserve">12.661922454834</t>
@@ -1736,10 +1736,10 @@
     <t xml:space="preserve">12.6148509979248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8031339645386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8502035140991</t>
+    <t xml:space="preserve">12.8031330108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8502044677734</t>
   </si>
   <si>
     <t xml:space="preserve">12.9914150238037</t>
@@ -1757,22 +1757,22 @@
     <t xml:space="preserve">13.7445402145386</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6504001617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5091886520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7916097640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8857507705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9798927307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0269613265991</t>
+    <t xml:space="preserve">13.6503992080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5091876983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7916116714478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8857517242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9798917770386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0269622802734</t>
   </si>
   <si>
     <t xml:space="preserve">14.074031829834</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">14.6859474182129</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3093843460083</t>
+    <t xml:space="preserve">14.3093852996826</t>
   </si>
   <si>
     <t xml:space="preserve">14.403525352478</t>
@@ -1808,13 +1808,13 @@
     <t xml:space="preserve">14.5447359085083</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5918064117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.638876914978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7800884246826</t>
+    <t xml:space="preserve">14.5918054580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6388778686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7800874710083</t>
   </si>
   <si>
     <t xml:space="preserve">14.8271589279175</t>
@@ -1823,151 +1823,151 @@
     <t xml:space="preserve">14.8742294311523</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7330169677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3449306488037</t>
+    <t xml:space="preserve">14.7330179214478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.344931602478</t>
   </si>
   <si>
     <t xml:space="preserve">15.7685642242432</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0039157867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.041576385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.079231262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1921997070312</t>
+    <t xml:space="preserve">16.0039176940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0415744781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0792293548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1921977996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1168880462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2298526763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3804798126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3993053436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4181385040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5311031341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2675113677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9286041259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8909473419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.815634727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9662609100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7214937210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5332145690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5143871307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7026681900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2696189880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4767293930054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.683837890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6650104522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4202432632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1566514968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2319641113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7779788970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9833736419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9643001556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6209802627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4874687194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7926387786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.811713218689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6019096374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5446872711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2585887908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6972742080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8307876586914</t>
   </si>
   <si>
     <t xml:space="preserve">16.116886138916</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2298545837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3804798126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3993072509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4181365966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5311050415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2675132751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9286060333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8909473419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8156366348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9662599563599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7214956283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5332126617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.51438331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7026691436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2696180343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4767293930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.683837890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6650104522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4202432632446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1566505432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2319631576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.777979850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9833736419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.964301109314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6209802627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4874687194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7926397323608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8117122650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6019086837769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5446872711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2585897445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6972723007202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8307857513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1168842315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2504005432129</t>
+    <t xml:space="preserve">16.2503986358643</t>
   </si>
   <si>
     <t xml:space="preserve">16.2313251495361</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0024452209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2694702148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.212251663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.460205078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4411296844482</t>
+    <t xml:space="preserve">16.0024490356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2694683074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2122535705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4602031707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4411315917969</t>
   </si>
   <si>
     <t xml:space="preserve">16.5364971160889</t>
@@ -1988,37 +1988,37 @@
     <t xml:space="preserve">17.3185005187988</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0896224975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.841667175293</t>
+    <t xml:space="preserve">17.08962059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8416690826416</t>
   </si>
   <si>
     <t xml:space="preserve">16.746301651001</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9751796722412</t>
+    <t xml:space="preserve">16.9751815795898</t>
   </si>
   <si>
     <t xml:space="preserve">17.1277675628662</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5092315673828</t>
+    <t xml:space="preserve">17.5092353820801</t>
   </si>
   <si>
     <t xml:space="preserve">17.5473785400391</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7571830749512</t>
+    <t xml:space="preserve">17.7571849822998</t>
   </si>
   <si>
     <t xml:space="preserve">17.6427440643311</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7381114959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4901599884033</t>
+    <t xml:space="preserve">17.738109588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4901580810547</t>
   </si>
   <si>
     <t xml:space="preserve">17.4710865020752</t>
@@ -2027,7 +2027,7 @@
     <t xml:space="preserve">17.3375720977783</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2994270324707</t>
+    <t xml:space="preserve">17.2994251251221</t>
   </si>
   <si>
     <t xml:space="preserve">17.3566474914551</t>
@@ -2045,7 +2045,7 @@
     <t xml:space="preserve">17.4520111083984</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8334789276123</t>
+    <t xml:space="preserve">17.8334770202637</t>
   </si>
   <si>
     <t xml:space="preserve">17.6999626159668</t>
@@ -2072,7 +2072,7 @@
     <t xml:space="preserve">18.5964069366455</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5582599639893</t>
+    <t xml:space="preserve">18.5582580566406</t>
   </si>
   <si>
     <t xml:space="preserve">18.7108459472656</t>
@@ -2081,16 +2081,16 @@
     <t xml:space="preserve">18.8062114715576</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5201148986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5500679016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5023860931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8838481903076</t>
+    <t xml:space="preserve">18.520112991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.55006980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.502384185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8838500976562</t>
   </si>
   <si>
     <t xml:space="preserve">19.9792175292969</t>
@@ -2117,43 +2117,43 @@
     <t xml:space="preserve">19.1209182739258</t>
   </si>
   <si>
-    <t xml:space="preserve">18.76806640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9097690582275</t>
+    <t xml:space="preserve">18.7680644989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9097709655762</t>
   </si>
   <si>
     <t xml:space="preserve">18.1195755004883</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6236705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.890697479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1005001068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2530879974365</t>
+    <t xml:space="preserve">17.6236724853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8906955718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1005020141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2530860900879</t>
   </si>
   <si>
     <t xml:space="preserve">17.9669895172119</t>
   </si>
   <si>
-    <t xml:space="preserve">18.176794052124</t>
+    <t xml:space="preserve">18.1767921447754</t>
   </si>
   <si>
     <t xml:space="preserve">18.9969444274902</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0732383728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9778690338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8825035095215</t>
+    <t xml:space="preserve">19.0732364654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9778728485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8825054168701</t>
   </si>
   <si>
     <t xml:space="preserve">18.9397258758545</t>
@@ -2162,7 +2162,7 @@
     <t xml:space="preserve">18.9015789031982</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0268974304199</t>
+    <t xml:space="preserve">20.0268993377686</t>
   </si>
   <si>
     <t xml:space="preserve">20.2176322937012</t>
@@ -2174,13 +2174,13 @@
     <t xml:space="preserve">20.7421455383301</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9328765869141</t>
+    <t xml:space="preserve">20.9328784942627</t>
   </si>
   <si>
     <t xml:space="preserve">21.2189769744873</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4573917388916</t>
+    <t xml:space="preserve">21.4573936462402</t>
   </si>
   <si>
     <t xml:space="preserve">20.6944637298584</t>
@@ -2189,16 +2189,16 @@
     <t xml:space="preserve">20.3129978179932</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4560470581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.980562210083</t>
+    <t xml:space="preserve">20.4560489654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9805603027344</t>
   </si>
   <si>
     <t xml:space="preserve">19.8361663818359</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4083633422852</t>
+    <t xml:space="preserve">20.4083652496338</t>
   </si>
   <si>
     <t xml:space="preserve">20.1222648620605</t>
@@ -2207,7 +2207,7 @@
     <t xml:space="preserve">19.311653137207</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2639694213867</t>
+    <t xml:space="preserve">19.2639713287354</t>
   </si>
   <si>
     <t xml:space="preserve">19.5977516174316</t>
@@ -2222,19 +2222,19 @@
     <t xml:space="preserve">19.9315338134766</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7408008575439</t>
+    <t xml:space="preserve">19.7408027648926</t>
   </si>
   <si>
     <t xml:space="preserve">18.8443584442139</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0160179138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0432796478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0051364898682</t>
+    <t xml:space="preserve">19.016019821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0432834625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0051345825195</t>
   </si>
   <si>
     <t xml:space="preserve">18.1386489868164</t>
@@ -2249,37 +2249,37 @@
     <t xml:space="preserve">17.6045989990234</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2612819671631</t>
+    <t xml:space="preserve">17.2612781524658</t>
   </si>
   <si>
     <t xml:space="preserve">17.0514736175537</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2885456085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0324039459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7272300720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4792785644531</t>
+    <t xml:space="preserve">16.2885437011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0324020385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7272281646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4792766571045</t>
   </si>
   <si>
     <t xml:space="preserve">16.8225936889648</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0705471038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.650936126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8607425689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3076190948486</t>
+    <t xml:space="preserve">17.0705490112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6509342193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8607406616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3076171875</t>
   </si>
   <si>
     <t xml:space="preserve">16.5937175750732</t>
@@ -2291,10 +2291,10 @@
     <t xml:space="preserve">15.277663230896</t>
   </si>
   <si>
-    <t xml:space="preserve">14.877124786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4956607818604</t>
+    <t xml:space="preserve">14.8771257400513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.495659828186</t>
   </si>
   <si>
     <t xml:space="preserve">15.3730297088623</t>
@@ -2303,16 +2303,16 @@
     <t xml:space="preserve">14.9915647506714</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0869312286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6782007217407</t>
+    <t xml:space="preserve">15.0869302749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6782035827637</t>
   </si>
   <si>
     <t xml:space="preserve">15.1441507339478</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9452247619629</t>
+    <t xml:space="preserve">15.9452257156372</t>
   </si>
   <si>
     <t xml:space="preserve">16.0787410736084</t>
@@ -2321,7 +2321,7 @@
     <t xml:space="preserve">16.0405921936035</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5746421813965</t>
+    <t xml:space="preserve">16.5746402740479</t>
   </si>
   <si>
     <t xml:space="preserve">16.6890830993652</t>
@@ -2330,7 +2330,7 @@
     <t xml:space="preserve">16.5174236297607</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4983501434326</t>
+    <t xml:space="preserve">16.498348236084</t>
   </si>
   <si>
     <t xml:space="preserve">15.7354202270508</t>
@@ -2342,13 +2342,13 @@
     <t xml:space="preserve">15.5065422058105</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9724912643433</t>
+    <t xml:space="preserve">14.9724922180176</t>
   </si>
   <si>
     <t xml:space="preserve">15.3348827362061</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2204437255859</t>
+    <t xml:space="preserve">15.2204427719116</t>
   </si>
   <si>
     <t xml:space="preserve">14.9152717590332</t>
@@ -2357,10 +2357,10 @@
     <t xml:space="preserve">14.781759262085</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8961982727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6400537490845</t>
+    <t xml:space="preserve">14.8961992263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6400547027588</t>
   </si>
   <si>
     <t xml:space="preserve">16.0978126525879</t>
@@ -2378,16 +2378,16 @@
     <t xml:space="preserve">16.1999359130859</t>
   </si>
   <si>
-    <t xml:space="preserve">16.354772567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0450954437256</t>
+    <t xml:space="preserve">16.3547744750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0450973510742</t>
   </si>
   <si>
     <t xml:space="preserve">16.1418704986572</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2773551940918</t>
+    <t xml:space="preserve">16.2773532867432</t>
   </si>
   <si>
     <t xml:space="preserve">16.4709033966064</t>
@@ -2402,40 +2402,40 @@
     <t xml:space="preserve">17.767671585083</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4192848205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2321834564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7289619445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9418640136719</t>
+    <t xml:space="preserve">17.419282913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2321853637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7289600372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9418659210205</t>
   </si>
   <si>
     <t xml:space="preserve">17.4967041015625</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5934772491455</t>
+    <t xml:space="preserve">17.5934791564941</t>
   </si>
   <si>
     <t xml:space="preserve">17.4579963684082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8967056274414</t>
+    <t xml:space="preserve">16.8967037200928</t>
   </si>
   <si>
     <t xml:space="preserve">16.4515476226807</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9870328903198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8321943283081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9483213424683</t>
+    <t xml:space="preserve">15.9870338439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8321962356567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9483232498169</t>
   </si>
   <si>
     <t xml:space="preserve">15.3676805496216</t>
@@ -2444,10 +2444,10 @@
     <t xml:space="preserve">15.4450988769531</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1741323471069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1160678863525</t>
+    <t xml:space="preserve">15.1741333007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1160688400269</t>
   </si>
   <si>
     <t xml:space="preserve">15.135422706604</t>
@@ -2459,10 +2459,10 @@
     <t xml:space="preserve">15.619291305542</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8902587890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7547760009766</t>
+    <t xml:space="preserve">15.8902597427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7547750473022</t>
   </si>
   <si>
     <t xml:space="preserve">15.8128395080566</t>
@@ -2474,25 +2474,25 @@
     <t xml:space="preserve">15.6580018997192</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8709030151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4128379821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4321918487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7160654067993</t>
+    <t xml:space="preserve">15.870903968811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4128360748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4321899414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7160663604736</t>
   </si>
   <si>
     <t xml:space="preserve">16.0644512176514</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5289649963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6838035583496</t>
+    <t xml:space="preserve">16.5289669036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6838054656982</t>
   </si>
   <si>
     <t xml:space="preserve">16.5096111297607</t>
@@ -2501,40 +2501,40 @@
     <t xml:space="preserve">16.9160594940186</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5354156494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3805751800537</t>
+    <t xml:space="preserve">17.5354137420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3805732727051</t>
   </si>
   <si>
     <t xml:space="preserve">17.3418674468994</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2063808441162</t>
+    <t xml:space="preserve">17.2063827514648</t>
   </si>
   <si>
     <t xml:space="preserve">17.3225116729736</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2838039398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0515460968018</t>
+    <t xml:space="preserve">17.2838020324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0515441894531</t>
   </si>
   <si>
     <t xml:space="preserve">16.8386421203613</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2450923919678</t>
+    <t xml:space="preserve">17.2450904846191</t>
   </si>
   <si>
     <t xml:space="preserve">17.6128330230713</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8192863464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1096076965332</t>
+    <t xml:space="preserve">16.8192882537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1096096038818</t>
   </si>
   <si>
     <t xml:space="preserve">16.7225131988525</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">16.4902572631836</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1225166320801</t>
+    <t xml:space="preserve">16.1225147247314</t>
   </si>
   <si>
     <t xml:space="preserve">16.0257415771484</t>
@@ -2561,7 +2561,7 @@
     <t xml:space="preserve">15.5031642913818</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2128429412842</t>
+    <t xml:space="preserve">15.2128419876099</t>
   </si>
   <si>
     <t xml:space="preserve">15.3096160888672</t>
@@ -2570,10 +2570,10 @@
     <t xml:space="preserve">15.5805826187134</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1547765731812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1934881210327</t>
+    <t xml:space="preserve">15.1547775268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1934871673584</t>
   </si>
   <si>
     <t xml:space="preserve">16.0838069915771</t>
@@ -2582,13 +2582,13 @@
     <t xml:space="preserve">15.7741289138794</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6773567199707</t>
+    <t xml:space="preserve">15.677357673645</t>
   </si>
   <si>
     <t xml:space="preserve">15.5612277984619</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1805820465088</t>
+    <t xml:space="preserve">16.1805782318115</t>
   </si>
   <si>
     <t xml:space="preserve">16.8579978942871</t>
@@ -2597,31 +2597,31 @@
     <t xml:space="preserve">17.3031558990479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9031543731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8063793182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1676712036133</t>
+    <t xml:space="preserve">17.9031524658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8063812255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1676731109619</t>
   </si>
   <si>
     <t xml:space="preserve">17.5160598754883</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3612213134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7354106903076</t>
+    <t xml:space="preserve">17.3612194061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.735408782959</t>
   </si>
   <si>
     <t xml:space="preserve">18.6579895019531</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4837989807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1741199493408</t>
+    <t xml:space="preserve">18.4837970733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1741218566895</t>
   </si>
   <si>
     <t xml:space="preserve">17.7870235443115</t>
@@ -2648,10 +2648,10 @@
     <t xml:space="preserve">18.1547660827637</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0192832946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9805717468262</t>
+    <t xml:space="preserve">18.0192813873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9805736541748</t>
   </si>
   <si>
     <t xml:space="preserve">17.961217880249</t>
@@ -2669,7 +2669,7 @@
     <t xml:space="preserve">17.6515426635742</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4386425018311</t>
+    <t xml:space="preserve">17.4386405944824</t>
   </si>
   <si>
     <t xml:space="preserve">17.3999290466309</t>
@@ -2681,10 +2681,10 @@
     <t xml:space="preserve">17.7096061706543</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4773502349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8257350921631</t>
+    <t xml:space="preserve">17.4773483276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8257369995117</t>
   </si>
   <si>
     <t xml:space="preserve">18.5805721282959</t>
@@ -2693,7 +2693,7 @@
     <t xml:space="preserve">18.9289569854736</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8128280639648</t>
+    <t xml:space="preserve">18.8128299713135</t>
   </si>
   <si>
     <t xml:space="preserve">19.5483093261719</t>
@@ -2702,88 +2702,88 @@
     <t xml:space="preserve">19.9354057312012</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7902431488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0321788787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7418575286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5966949462891</t>
+    <t xml:space="preserve">19.7902450561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0321769714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7418556213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5966968536377</t>
   </si>
   <si>
     <t xml:space="preserve">19.9837894439697</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8386306762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0805625915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.370885848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8870143890381</t>
+    <t xml:space="preserve">19.8386287689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0805644989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3708839416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8870162963867</t>
   </si>
   <si>
     <t xml:space="preserve">19.6450805664062</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1289501190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1773376464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4192733764648</t>
+    <t xml:space="preserve">20.1289520263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.177339553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4192752838135</t>
   </si>
   <si>
     <t xml:space="preserve">20.467658996582</t>
   </si>
   <si>
-    <t xml:space="preserve">21.241849899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1934642791748</t>
+    <t xml:space="preserve">21.2418518066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1934623718262</t>
   </si>
   <si>
     <t xml:space="preserve">21.435396194458</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5805568695068</t>
+    <t xml:space="preserve">21.5805587768555</t>
   </si>
   <si>
     <t xml:space="preserve">21.6773319244385</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6289463043213</t>
+    <t xml:space="preserve">21.6289443969727</t>
   </si>
   <si>
     <t xml:space="preserve">22.0644283294678</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2579765319824</t>
+    <t xml:space="preserve">22.2579727172852</t>
   </si>
   <si>
     <t xml:space="preserve">22.6450710296631</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0321636199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4676456451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.32248878479</t>
+    <t xml:space="preserve">23.0321655273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4676475524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3224868774414</t>
   </si>
   <si>
     <t xml:space="preserve">22.7902297973633</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7418441772461</t>
+    <t xml:space="preserve">22.7418422698975</t>
   </si>
   <si>
     <t xml:space="preserve">21.9676532745361</t>
@@ -2795,7 +2795,7 @@
     <t xml:space="preserve">22.1612014770508</t>
   </si>
   <si>
-    <t xml:space="preserve">22.306360244751</t>
+    <t xml:space="preserve">22.3063621520996</t>
   </si>
   <si>
     <t xml:space="preserve">21.8224925994873</t>
@@ -2813,31 +2813,31 @@
     <t xml:space="preserve">22.9837779998779</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9031314849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1934509277344</t>
+    <t xml:space="preserve">23.9031295776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.193452835083</t>
   </si>
   <si>
     <t xml:space="preserve">24.0966758728027</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0160293579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9676418304443</t>
+    <t xml:space="preserve">25.0160312652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9676399230957</t>
   </si>
   <si>
     <t xml:space="preserve">25.4031238555908</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8386077880859</t>
+    <t xml:space="preserve">25.8386058807373</t>
   </si>
   <si>
     <t xml:space="preserve">25.9353790283203</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3547382354736</t>
+    <t xml:space="preserve">25.354736328125</t>
   </si>
   <si>
     <t xml:space="preserve">25.161190032959</t>
@@ -2852,22 +2852,22 @@
     <t xml:space="preserve">25.451509475708</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2095756530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.548282623291</t>
+    <t xml:space="preserve">25.2095737457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5482845306396</t>
   </si>
   <si>
     <t xml:space="preserve">25.6450595855713</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1773109436035</t>
+    <t xml:space="preserve">26.1773128509521</t>
   </si>
   <si>
     <t xml:space="preserve">26.5160217285156</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9515037536621</t>
+    <t xml:space="preserve">26.9515056610107</t>
   </si>
   <si>
     <t xml:space="preserve">25.6934432983398</t>
@@ -2876,13 +2876,13 @@
     <t xml:space="preserve">25.5966720581055</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3063488006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8869915008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3708610534668</t>
+    <t xml:space="preserve">25.3063507080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8869934082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3708629608154</t>
   </si>
   <si>
     <t xml:space="preserve">26.2043304443359</t>
@@ -2891,7 +2891,7 @@
     <t xml:space="preserve">25.616569519043</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1267681121826</t>
+    <t xml:space="preserve">25.1267700195312</t>
   </si>
   <si>
     <t xml:space="preserve">25.9594306945801</t>
@@ -2903,16 +2903,16 @@
     <t xml:space="preserve">25.2737083435059</t>
   </si>
   <si>
-    <t xml:space="preserve">25.02880859375</t>
+    <t xml:space="preserve">25.0288066864014</t>
   </si>
   <si>
     <t xml:space="preserve">25.2247295379639</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7349300384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.441047668457</t>
+    <t xml:space="preserve">24.7349281311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4410495758057</t>
   </si>
   <si>
     <t xml:space="preserve">24.8818683624268</t>
@@ -2927,10 +2927,10 @@
     <t xml:space="preserve">24.4900283813477</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7839069366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8328895568848</t>
+    <t xml:space="preserve">24.7839088439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8328876495361</t>
   </si>
   <si>
     <t xml:space="preserve">24.979829788208</t>
@@ -2939,19 +2939,19 @@
     <t xml:space="preserve">25.4696292877197</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9104518890381</t>
+    <t xml:space="preserve">25.9104499816895</t>
   </si>
   <si>
     <t xml:space="preserve">25.8614692687988</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7635078430176</t>
+    <t xml:space="preserve">25.7635097503662</t>
   </si>
   <si>
     <t xml:space="preserve">25.7145290374756</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2533111572266</t>
+    <t xml:space="preserve">26.2533092498779</t>
   </si>
   <si>
     <t xml:space="preserve">26.6941299438477</t>
@@ -2963,7 +2963,7 @@
     <t xml:space="preserve">26.7920913696289</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5961685180664</t>
+    <t xml:space="preserve">26.596170425415</t>
   </si>
   <si>
     <t xml:space="preserve">26.4492301940918</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">25.3716678619385</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1471672058105</t>
+    <t xml:space="preserve">24.1471691131592</t>
   </si>
   <si>
     <t xml:space="preserve">26.3512687683105</t>
@@ -3008,13 +3008,13 @@
     <t xml:space="preserve">26.9880104064941</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9390296936035</t>
+    <t xml:space="preserve">26.9390316009521</t>
   </si>
   <si>
     <t xml:space="preserve">26.0573902130127</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1063690185547</t>
+    <t xml:space="preserve">26.1063709259033</t>
   </si>
   <si>
     <t xml:space="preserve">26.6451511383057</t>
@@ -3029,40 +3029,40 @@
     <t xml:space="preserve">27.134952545166</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1553516387939</t>
+    <t xml:space="preserve">26.1553497314453</t>
   </si>
   <si>
     <t xml:space="preserve">27.3798522949219</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3308715820312</t>
+    <t xml:space="preserve">27.3308696746826</t>
   </si>
   <si>
     <t xml:space="preserve">27.7227115631104</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6737327575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0165939331055</t>
+    <t xml:space="preserve">27.6737308502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0165920257568</t>
   </si>
   <si>
     <t xml:space="preserve">27.5757713317871</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4778118133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5267906188965</t>
+    <t xml:space="preserve">27.4778099060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5267925262451</t>
   </si>
   <si>
     <t xml:space="preserve">25.8124904632568</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3022899627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2818908691406</t>
+    <t xml:space="preserve">26.3022918701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2818927764893</t>
   </si>
   <si>
     <t xml:space="preserve">27.4288330078125</t>
@@ -3071,13 +3071,13 @@
     <t xml:space="preserve">27.23291015625</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6247520446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8410720825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4982109069824</t>
+    <t xml:space="preserve">27.6247539520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8410701751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4982089996338</t>
   </si>
   <si>
     <t xml:space="preserve">25.567590713501</t>
@@ -3104,7 +3104,7 @@
     <t xml:space="preserve">28.5553722381592</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0451717376709</t>
+    <t xml:space="preserve">29.0451736450195</t>
   </si>
   <si>
     <t xml:space="preserve">29.1431331634521</t>
@@ -3122,10 +3122,10 @@
     <t xml:space="preserve">29.6819133758545</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7798728942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1921138763428</t>
+    <t xml:space="preserve">29.7798748016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1921119689941</t>
   </si>
   <si>
     <t xml:space="preserve">29.5349731445312</t>
@@ -3137,10 +3137,10 @@
     <t xml:space="preserve">30.2206954956055</t>
   </si>
   <si>
-    <t xml:space="preserve">30.514575958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8574371337891</t>
+    <t xml:space="preserve">30.5145740509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8574352264404</t>
   </si>
   <si>
     <t xml:space="preserve">32.1798973083496</t>
@@ -3155,10 +3155,10 @@
     <t xml:space="preserve">32.5227584838867</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0901222229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8248176574707</t>
+    <t xml:space="preserve">34.0901184082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.824821472168</t>
   </si>
   <si>
     <t xml:space="preserve">34.2860374450684</t>
@@ -3167,22 +3167,22 @@
     <t xml:space="preserve">34.6288986206055</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1390953063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7758369445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7472610473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8941993713379</t>
+    <t xml:space="preserve">34.1390991210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7758407592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.747257232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8941955566406</t>
   </si>
   <si>
     <t xml:space="preserve">34.335018157959</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9431800842285</t>
+    <t xml:space="preserve">33.9431838989258</t>
   </si>
   <si>
     <t xml:space="preserve">35.0207405090332</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">35.4125823974609</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9635772705078</t>
+    <t xml:space="preserve">32.9635810852051</t>
   </si>
   <si>
     <t xml:space="preserve">32.9145965576172</t>
@@ -3209,7 +3209,7 @@
     <t xml:space="preserve">33.0125579833984</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4451961517334</t>
+    <t xml:space="preserve">31.4451942443848</t>
   </si>
   <si>
     <t xml:space="preserve">31.5641193389893</t>
@@ -68935,7 +68935,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.649525463</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>44929</v>
@@ -68956,6 +68956,32 @@
         <v>1272</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.6496064815</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>26226</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>51.9000015258789</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>50.7999992370605</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>51.9000015258789</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>51.2999992370605</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>1243</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SOL.MI.xlsx
+++ b/data/SOL.MI.xlsx
@@ -38,91 +38,91 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14939117431641</t>
+    <t xml:space="preserve">7.14939165115356</t>
   </si>
   <si>
     <t xml:space="preserve">SOL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1406717300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1886248588562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16246891021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06220388412476</t>
+    <t xml:space="preserve">7.14067220687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18862581253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1624698638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0622034072876</t>
   </si>
   <si>
     <t xml:space="preserve">6.90962553024292</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90526580810547</t>
+    <t xml:space="preserve">6.90526533126831</t>
   </si>
   <si>
     <t xml:space="preserve">6.94885921478271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71781158447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62626552581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71345233917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29931116104126</t>
+    <t xml:space="preserve">6.71781253814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62626457214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71345281600952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2993106842041</t>
   </si>
   <si>
     <t xml:space="preserve">6.36470222473145</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43009281158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41265487670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44753074645996</t>
+    <t xml:space="preserve">6.43009233474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4126558303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4475302696228</t>
   </si>
   <si>
     <t xml:space="preserve">6.207763671875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17288875579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46060800552368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54779672622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38214015960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51292037963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50420236587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65242147445679</t>
+    <t xml:space="preserve">6.1728892326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46060752868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54779624938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38213920593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51292085647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50420188903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65242195129395</t>
   </si>
   <si>
     <t xml:space="preserve">6.80064058303833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72217130661011</t>
+    <t xml:space="preserve">6.72217178344727</t>
   </si>
   <si>
     <t xml:space="preserve">6.79192161560059</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00989055633545</t>
+    <t xml:space="preserve">7.00989103317261</t>
   </si>
   <si>
     <t xml:space="preserve">6.84423446655273</t>
@@ -131,52 +131,52 @@
     <t xml:space="preserve">7.07964181900024</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88346910476685</t>
+    <t xml:space="preserve">6.883469581604</t>
   </si>
   <si>
     <t xml:space="preserve">6.9662971496582</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08835983276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7352499961853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83115577697754</t>
+    <t xml:space="preserve">7.08836078643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73524951934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8311562538147</t>
   </si>
   <si>
     <t xml:space="preserve">6.67857789993286</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57395219802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63062429428101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68729686737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78320264816284</t>
+    <t xml:space="preserve">6.57395267486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63062381744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68729782104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.783203125</t>
   </si>
   <si>
     <t xml:space="preserve">6.77884387969971</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81371927261353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80935955047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79628086090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69601535797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81807899475098</t>
+    <t xml:space="preserve">6.81371879577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80935907363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79628133773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69601488113403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81807804107666</t>
   </si>
   <si>
     <t xml:space="preserve">6.8747501373291</t>
@@ -191,13 +191,13 @@
     <t xml:space="preserve">6.55215549468994</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46496820449829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43881177902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73088979721069</t>
+    <t xml:space="preserve">6.46496772766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43881225585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73089027404785</t>
   </si>
   <si>
     <t xml:space="preserve">6.87910890579224</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">6.85295343399048</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84859371185303</t>
+    <t xml:space="preserve">6.84859418869019</t>
   </si>
   <si>
     <t xml:space="preserve">6.85731267929077</t>
@@ -215,19 +215,19 @@
     <t xml:space="preserve">6.74832725524902</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51728057861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37342071533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56523370742798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66985893249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7701244354248</t>
+    <t xml:space="preserve">6.51727962493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37342119216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56523323059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66985940933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77012491226196</t>
   </si>
   <si>
     <t xml:space="preserve">6.86167144775391</t>
@@ -245,112 +245,112 @@
     <t xml:space="preserve">6.88407850265503</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9017858505249</t>
+    <t xml:space="preserve">6.90178632736206</t>
   </si>
   <si>
     <t xml:space="preserve">7.34006500244141</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22496223449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41975116729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43745994567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36662673950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26037788391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46845006942749</t>
+    <t xml:space="preserve">7.22496175765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41975212097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43746089935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36662769317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26037836074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46845054626465</t>
   </si>
   <si>
     <t xml:space="preserve">7.40204429626465</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44631433486938</t>
+    <t xml:space="preserve">7.44631481170654</t>
   </si>
   <si>
     <t xml:space="preserve">7.38433599472046</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04345178604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97261953353882</t>
+    <t xml:space="preserve">7.04345226287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97261905670166</t>
   </si>
   <si>
     <t xml:space="preserve">7.10985803604126</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87079763412476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20725393295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37105417251587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57027292251587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69422960281372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70308351516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71193885803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65881204605103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04396724700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61454439163208</t>
+    <t xml:space="preserve">6.8707971572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20725297927856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37105464935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57027196884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69423007965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70308446884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71193742752075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6588134765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04396820068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61454296112061</t>
   </si>
   <si>
     <t xml:space="preserve">7.29579496383667</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99475479125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10100507736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55256462097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3135027885437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50829315185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42418003082275</t>
+    <t xml:space="preserve">6.99475431442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1010046005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55256366729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31350326538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50829267501831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4241795539856</t>
   </si>
   <si>
     <t xml:space="preserve">7.37548208236694</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5260009765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54371070861816</t>
+    <t xml:space="preserve">7.52600145339966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54371023178101</t>
   </si>
   <si>
     <t xml:space="preserve">7.41532421112061</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21610689163208</t>
+    <t xml:space="preserve">7.21610736846924</t>
   </si>
   <si>
     <t xml:space="preserve">6.99032783508301</t>
@@ -365,61 +365,61 @@
     <t xml:space="preserve">7.00803565979004</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26923179626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34449195861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46402263641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51714754104614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39319038391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45516872406006</t>
+    <t xml:space="preserve">7.26923274993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34449148178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46402311325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51714706420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39318990707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45516920089722</t>
   </si>
   <si>
     <t xml:space="preserve">7.17183685302734</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33563804626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33121013641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39761590957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30464935302734</t>
+    <t xml:space="preserve">7.33563756942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33121109008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39761638641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30464887619019</t>
   </si>
   <si>
     <t xml:space="preserve">7.27808666229248</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2515230178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16298341751099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03017139434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87965106964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91064023971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95491075515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88850498199463</t>
+    <t xml:space="preserve">7.25152349472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16298294067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03017091751099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8796501159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91064071655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95491170883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88850545883179</t>
   </si>
   <si>
     <t xml:space="preserve">6.95933818817139</t>
@@ -428,10 +428,10 @@
     <t xml:space="preserve">6.85751533508301</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77340078353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74683856964111</t>
+    <t xml:space="preserve">6.77340173721313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74683952331543</t>
   </si>
   <si>
     <t xml:space="preserve">6.82652616500854</t>
@@ -443,49 +443,49 @@
     <t xml:space="preserve">6.81767177581787</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90621328353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01688957214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89735889434814</t>
+    <t xml:space="preserve">6.90621376037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01689004898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89735794067383</t>
   </si>
   <si>
     <t xml:space="preserve">6.83538007736206</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86194276809692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92392206192017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97704648971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00360870361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91506767272949</t>
+    <t xml:space="preserve">6.86194229125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92392158508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97704601287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00360822677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91506719589233</t>
   </si>
   <si>
     <t xml:space="preserve">6.91949510574341</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93720197677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07001447677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98589992523193</t>
+    <t xml:space="preserve">6.93720293045044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07001495361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98590040206909</t>
   </si>
   <si>
     <t xml:space="preserve">6.75126647949219</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77782821655273</t>
+    <t xml:space="preserve">6.77782869338989</t>
   </si>
   <si>
     <t xml:space="preserve">6.64944410324097</t>
@@ -494,25 +494,25 @@
     <t xml:space="preserve">6.38382005691528</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37053918838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36168527603149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37939357757568</t>
+    <t xml:space="preserve">6.37053871154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36168479919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37939310073853</t>
   </si>
   <si>
     <t xml:space="preserve">6.40595531463623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4812159538269</t>
+    <t xml:space="preserve">6.48121500015259</t>
   </si>
   <si>
     <t xml:space="preserve">6.47678804397583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54319334030151</t>
+    <t xml:space="preserve">6.54319381713867</t>
   </si>
   <si>
     <t xml:space="preserve">6.46350765228271</t>
@@ -524,19 +524,19 @@
     <t xml:space="preserve">6.25986337661743</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22444629669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64501667022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64059019088745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03902387619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79110956192017</t>
+    <t xml:space="preserve">6.22444581985474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64501619338989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64058923721313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0390248298645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79111099243164</t>
   </si>
   <si>
     <t xml:space="preserve">6.70256805419922</t>
@@ -545,19 +545,19 @@
     <t xml:space="preserve">6.70699501037598</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65829753875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58303737640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05673313140869</t>
+    <t xml:space="preserve">6.65829801559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58303785324097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05673265457153</t>
   </si>
   <si>
     <t xml:space="preserve">7.11428499221802</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34891891479492</t>
+    <t xml:space="preserve">7.34891843795776</t>
   </si>
   <si>
     <t xml:space="preserve">7.18511772155762</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">7.12756633758545</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19397163391113</t>
+    <t xml:space="preserve">7.19397258758545</t>
   </si>
   <si>
     <t xml:space="preserve">7.24267053604126</t>
@@ -575,19 +575,19 @@
     <t xml:space="preserve">7.41089820861816</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48173141479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14527416229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27365827560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17626333236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04787874221802</t>
+    <t xml:space="preserve">7.48173046112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14527463912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27365970611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1762638092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04787969589233</t>
   </si>
   <si>
     <t xml:space="preserve">7.23381614685059</t>
@@ -596,10 +596,10 @@
     <t xml:space="preserve">7.29136753082275</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42860555648804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83589696884155</t>
+    <t xml:space="preserve">7.4286060333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83589601516724</t>
   </si>
   <si>
     <t xml:space="preserve">7.82704210281372</t>
@@ -611,16 +611,16 @@
     <t xml:space="preserve">8.27860260009766</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32287216186523</t>
+    <t xml:space="preserve">8.32287311553955</t>
   </si>
   <si>
     <t xml:space="preserve">9.03120136260986</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53094482421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49995422363281</t>
+    <t xml:space="preserve">8.53094387054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49995517730713</t>
   </si>
   <si>
     <t xml:space="preserve">8.26089382171631</t>
@@ -632,10 +632,10 @@
     <t xml:space="preserve">8.58849620819092</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97807693481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76557922363281</t>
+    <t xml:space="preserve">8.97807788848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7655782699585</t>
   </si>
   <si>
     <t xml:space="preserve">8.87182807922363</t>
@@ -644,46 +644,46 @@
     <t xml:space="preserve">9.56244850158691</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25255489349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02234649658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85412120819092</t>
+    <t xml:space="preserve">9.25255393981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02234554290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85411930084229</t>
   </si>
   <si>
     <t xml:space="preserve">8.82755661010742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71245193481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98693084716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8983907699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80984687805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72130680084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78328800201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67703723907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7567253112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10203456878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82312965393066</t>
+    <t xml:space="preserve">8.71245384216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98693180084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89838981628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80984878540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72130966186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78328609466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67703628540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75672435760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10203552246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82313060760498</t>
   </si>
   <si>
     <t xml:space="preserve">8.94266128540039</t>
@@ -692,52 +692,52 @@
     <t xml:space="preserve">9.20828342437744</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43287658691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4598274230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52271461486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32507228851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38795757293701</t>
+    <t xml:space="preserve">9.43287563323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45982837677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52271366119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3250732421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38795852661133</t>
   </si>
   <si>
     <t xml:space="preserve">9.35202407836914</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4238920211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29812240600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55864906311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67543697357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86409378051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5199031829834</t>
+    <t xml:space="preserve">9.42389297485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29812145233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55864810943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67543792724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86409282684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5199022293091</t>
   </si>
   <si>
     <t xml:space="preserve">10.0617351531982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88206195831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74730587005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5676326751709</t>
+    <t xml:space="preserve">9.88206005096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74730777740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56763076782227</t>
   </si>
   <si>
     <t xml:space="preserve">9.44186019897461</t>
@@ -746,13 +746,13 @@
     <t xml:space="preserve">9.54068088531494</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34303855895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.361008644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50474643707275</t>
+    <t xml:space="preserve">9.34303951263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36100769042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50474739074707</t>
   </si>
   <si>
     <t xml:space="preserve">9.48677921295166</t>
@@ -782,16 +782,16 @@
     <t xml:space="preserve">9.28015422821045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21726894378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16336536407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20828437805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25320339202881</t>
+    <t xml:space="preserve">9.2172679901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16336631774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20828247070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25320434570312</t>
   </si>
   <si>
     <t xml:space="preserve">9.45084285736084</t>
@@ -809,7 +809,7 @@
     <t xml:space="preserve">9.66645240783691</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71137142181396</t>
+    <t xml:space="preserve">9.71137237548828</t>
   </si>
   <si>
     <t xml:space="preserve">9.40592479705811</t>
@@ -821,43 +821,43 @@
     <t xml:space="preserve">9.2711706161499</t>
   </si>
   <si>
-    <t xml:space="preserve">9.289137840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36999130249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65746974945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79222393035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76527404785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72035503387451</t>
+    <t xml:space="preserve">9.28913879394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36999034881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.657470703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79222297668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76527309417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7203540802002</t>
   </si>
   <si>
     <t xml:space="preserve">9.81019115447998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37897396087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90901184082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81917572021484</t>
+    <t xml:space="preserve">9.37897300720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.909010887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81917762756348</t>
   </si>
   <si>
     <t xml:space="preserve">9.73832225799561</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78324127197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69340324401855</t>
+    <t xml:space="preserve">9.78324222564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69340419769287</t>
   </si>
   <si>
     <t xml:space="preserve">9.11844730377197</t>
@@ -866,19 +866,19 @@
     <t xml:space="preserve">9.08251190185547</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31608772277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19031715393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10047912597656</t>
+    <t xml:space="preserve">9.31608867645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19031620025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10048007965088</t>
   </si>
   <si>
     <t xml:space="preserve">9.22625160217285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41490840911865</t>
+    <t xml:space="preserve">9.41490745544434</t>
   </si>
   <si>
     <t xml:space="preserve">9.39694118499756</t>
@@ -887,40 +887,40 @@
     <t xml:space="preserve">9.07352924346924</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57661724090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68442058563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09149646759033</t>
+    <t xml:space="preserve">9.57661533355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68441963195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09149742126465</t>
   </si>
   <si>
     <t xml:space="preserve">9.05556106567383</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14540004730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89385604858398</t>
+    <t xml:space="preserve">9.14539909362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89385509490967</t>
   </si>
   <si>
     <t xml:space="preserve">9.10946464538574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23523426055908</t>
+    <t xml:space="preserve">9.2352352142334</t>
   </si>
   <si>
     <t xml:space="preserve">9.95393085479736</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5109186172485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7444953918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5468549728394</t>
+    <t xml:space="preserve">10.5109195709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.74449634552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.546854019165</t>
   </si>
   <si>
     <t xml:space="preserve">10.6905927658081</t>
@@ -929,16 +929,16 @@
     <t xml:space="preserve">10.9062023162842</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7804307937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7085599899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6546583175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5288877487183</t>
+    <t xml:space="preserve">10.7804298400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7085618972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6546592712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5288858413696</t>
   </si>
   <si>
     <t xml:space="preserve">10.4390497207642</t>
@@ -950,10 +950,10 @@
     <t xml:space="preserve">10.1695404052734</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1875076293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1336050033569</t>
+    <t xml:space="preserve">10.1875057220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1336040496826</t>
   </si>
   <si>
     <t xml:space="preserve">9.7562894821167</t>
@@ -962,25 +962,25 @@
     <t xml:space="preserve">9.63051700592041</t>
   </si>
   <si>
-    <t xml:space="preserve">10.007833480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84612655639648</t>
+    <t xml:space="preserve">10.0078344345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8461275100708</t>
   </si>
   <si>
     <t xml:space="preserve">10.0976696014404</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2054748535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.27734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2234420776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2414073944092</t>
+    <t xml:space="preserve">10.2054738998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2773447036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2234411239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2414102554321</t>
   </si>
   <si>
     <t xml:space="preserve">10.7624626159668</t>
@@ -995,82 +995,82 @@
     <t xml:space="preserve">9.90002918243408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67380619049072</t>
+    <t xml:space="preserve">9.67380714416504</t>
   </si>
   <si>
     <t xml:space="preserve">9.74667835235596</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87420558929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1656951904297</t>
+    <t xml:space="preserve">9.87420654296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1656942367554</t>
   </si>
   <si>
     <t xml:space="preserve">9.85598754882812</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63737010955811</t>
+    <t xml:space="preserve">9.63737106323242</t>
   </si>
   <si>
     <t xml:space="preserve">9.47340679168701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76489734649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96529483795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0746049880981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2385663986206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3843116760254</t>
+    <t xml:space="preserve">9.76489639282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96529579162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0746059417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2385673522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.384313583374</t>
   </si>
   <si>
     <t xml:space="preserve">10.4207487106323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8033294677734</t>
+    <t xml:space="preserve">10.8033285140991</t>
   </si>
   <si>
     <t xml:space="preserve">10.6940202713013</t>
   </si>
   <si>
-    <t xml:space="preserve">10.621148109436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7851104736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5482740402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4025316238403</t>
+    <t xml:space="preserve">10.6211471557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7851114273071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5482749938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4025297164917</t>
   </si>
   <si>
     <t xml:space="preserve">10.2203502655029</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1474771499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3296585083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5847101211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3478775024414</t>
+    <t xml:space="preserve">10.1474781036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3296575546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5847110748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3478765487671</t>
   </si>
   <si>
     <t xml:space="preserve">9.72846031188965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56449699401855</t>
+    <t xml:space="preserve">9.56449794769287</t>
   </si>
   <si>
     <t xml:space="preserve">9.41875457763672</t>
@@ -1085,13 +1085,13 @@
     <t xml:space="preserve">10.1110410690308</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2567853927612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92885971069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0199499130249</t>
+    <t xml:space="preserve">10.2567863464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92885875701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0199489593506</t>
   </si>
   <si>
     <t xml:space="preserve">10.2021312713623</t>
@@ -1100,52 +1100,52 @@
     <t xml:space="preserve">10.0928220748901</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80133438110352</t>
+    <t xml:space="preserve">9.80133247375488</t>
   </si>
   <si>
     <t xml:space="preserve">9.69202423095703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8377685546875</t>
+    <t xml:space="preserve">9.83776950836182</t>
   </si>
   <si>
     <t xml:space="preserve">9.94707775115967</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89242458343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65558815002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78311443328857</t>
+    <t xml:space="preserve">9.89242362976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65558910369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78311347961426</t>
   </si>
   <si>
     <t xml:space="preserve">9.91064167022705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45518970489502</t>
+    <t xml:space="preserve">9.45519065856934</t>
   </si>
   <si>
     <t xml:space="preserve">9.20013618469238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50984382629395</t>
+    <t xml:space="preserve">9.50984287261963</t>
   </si>
   <si>
     <t xml:space="preserve">9.43697071075439</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81955242156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49162578582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61915302276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98351383209229</t>
+    <t xml:space="preserve">9.81955051422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49162673950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6191520690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9835147857666</t>
   </si>
   <si>
     <t xml:space="preserve">9.60093402862549</t>
@@ -1154,43 +1154,43 @@
     <t xml:space="preserve">9.10904502868652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09993743896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38231658935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36409854888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27300930023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71024322509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58271598815918</t>
+    <t xml:space="preserve">9.09993553161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3823184967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36409950256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27300834655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71024227142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58271503448486</t>
   </si>
   <si>
     <t xml:space="preserve">9.29122638702393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14548110961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3660936355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32766342163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0017328262329</t>
+    <t xml:space="preserve">9.14548301696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3660945892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32766246795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0017309188843</t>
   </si>
   <si>
     <t xml:space="preserve">10.4754018783569</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8397645950317</t>
+    <t xml:space="preserve">10.8397636413574</t>
   </si>
   <si>
     <t xml:space="preserve">10.5664939880371</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">10.3114404678345</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2932224273682</t>
+    <t xml:space="preserve">10.2932233810425</t>
   </si>
   <si>
     <t xml:space="preserve">10.0381689071655</t>
@@ -1214,22 +1214,22 @@
     <t xml:space="preserve">10.2750034332275</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1839113235474</t>
+    <t xml:space="preserve">10.1839141845703</t>
   </si>
   <si>
     <t xml:space="preserve">10.6758012771606</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7122392654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9308547973633</t>
+    <t xml:space="preserve">10.7122373580933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.930853843689</t>
   </si>
   <si>
     <t xml:space="preserve">11.0219459533691</t>
   </si>
   <si>
-    <t xml:space="preserve">10.87619972229</t>
+    <t xml:space="preserve">10.8762006759644</t>
   </si>
   <si>
     <t xml:space="preserve">10.894419670105</t>
@@ -1238,19 +1238,19 @@
     <t xml:space="preserve">10.7304544448853</t>
   </si>
   <si>
-    <t xml:space="preserve">10.65758228302</t>
+    <t xml:space="preserve">10.6575832366943</t>
   </si>
   <si>
     <t xml:space="preserve">11.2644634246826</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1349868774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0979928970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2459669113159</t>
+    <t xml:space="preserve">11.1349859237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.097993850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2459659576416</t>
   </si>
   <si>
     <t xml:space="preserve">11.319953918457</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">11.0240068435669</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8205423355103</t>
+    <t xml:space="preserve">10.8205432891846</t>
   </si>
   <si>
     <t xml:space="preserve">10.8390407562256</t>
@@ -1268,7 +1268,7 @@
     <t xml:space="preserve">10.7280607223511</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8575382232666</t>
+    <t xml:space="preserve">10.8575372695923</t>
   </si>
   <si>
     <t xml:space="preserve">10.7095632553101</t>
@@ -1277,16 +1277,16 @@
     <t xml:space="preserve">10.6725702285767</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6540756225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7835512161255</t>
+    <t xml:space="preserve">10.6540746688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7835502624512</t>
   </si>
   <si>
     <t xml:space="preserve">10.7650547027588</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8020467758179</t>
+    <t xml:space="preserve">10.8020477294922</t>
   </si>
   <si>
     <t xml:space="preserve">10.5615911483765</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">10.6170797348022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3951196670532</t>
+    <t xml:space="preserve">10.3951206207275</t>
   </si>
   <si>
     <t xml:space="preserve">10.1176700592041</t>
@@ -1307,28 +1307,28 @@
     <t xml:space="preserve">10.2656440734863</t>
   </si>
   <si>
-    <t xml:space="preserve">10.302638053894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5061016082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3396291732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1361665725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0806770324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98819351196289</t>
+    <t xml:space="preserve">10.3026371002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5060997009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3396310806274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1361656188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.080677986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98819446563721</t>
   </si>
   <si>
     <t xml:space="preserve">10.0991735458374</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93270301818848</t>
+    <t xml:space="preserve">9.93270397186279</t>
   </si>
   <si>
     <t xml:space="preserve">9.89571094512939</t>
@@ -1337,7 +1337,7 @@
     <t xml:space="preserve">9.96969795227051</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1731605529785</t>
+    <t xml:space="preserve">10.1731595993042</t>
   </si>
   <si>
     <t xml:space="preserve">10.0621795654297</t>
@@ -1352,37 +1352,37 @@
     <t xml:space="preserve">10.0251874923706</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91420745849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7662353515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72924041748047</t>
+    <t xml:space="preserve">9.91420650482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76623439788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72924137115479</t>
   </si>
   <si>
     <t xml:space="preserve">9.65525341033936</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67375183105469</t>
+    <t xml:space="preserve">9.67375087738037</t>
   </si>
   <si>
     <t xml:space="preserve">9.47028732299805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54427433013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56277179718018</t>
+    <t xml:space="preserve">9.54427528381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56277084350586</t>
   </si>
   <si>
     <t xml:space="preserve">9.45179176330566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35930728912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52577686309814</t>
+    <t xml:space="preserve">9.35930824279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52577781677246</t>
   </si>
   <si>
     <t xml:space="preserve">9.59976387023926</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">9.61826038360596</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69224643707275</t>
+    <t xml:space="preserve">9.69224548339844</t>
   </si>
   <si>
     <t xml:space="preserve">9.80322742462158</t>
@@ -1403,28 +1403,28 @@
     <t xml:space="preserve">9.78473091125488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.858717918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0066900253296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87721347808838</t>
+    <t xml:space="preserve">9.85871887207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0066909790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8772144317627</t>
   </si>
   <si>
     <t xml:space="preserve">9.74773788452148</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58126735687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3211345672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4321136474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3766250610352</t>
+    <t xml:space="preserve">9.58126640319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3211336135864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4321146011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3766241073608</t>
   </si>
   <si>
     <t xml:space="preserve">10.2471475601196</t>
@@ -1436,31 +1436,31 @@
     <t xml:space="preserve">9.8402214050293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63675785064697</t>
+    <t xml:space="preserve">9.63675880432129</t>
   </si>
   <si>
     <t xml:space="preserve">9.43329429626465</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41479778289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39630031585693</t>
+    <t xml:space="preserve">9.41479873657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39630126953125</t>
   </si>
   <si>
     <t xml:space="preserve">9.24832820892334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06336116790771</t>
+    <t xml:space="preserve">9.06336212158203</t>
   </si>
   <si>
     <t xml:space="preserve">9.1096019744873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32231330871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28532028198242</t>
+    <t xml:space="preserve">9.32231426239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28532123565674</t>
   </si>
   <si>
     <t xml:space="preserve">9.26682567596436</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">9.13734817504883</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96162986755371</t>
+    <t xml:space="preserve">8.96162891387939</t>
   </si>
   <si>
     <t xml:space="preserve">8.82290458679199</t>
@@ -1493,40 +1493,40 @@
     <t xml:space="preserve">8.61944198608398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55470275878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36048889160156</t>
+    <t xml:space="preserve">8.55470371246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36048793792725</t>
   </si>
   <si>
     <t xml:space="preserve">8.33274459838867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01830005645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8148365020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95356225967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49114561080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8610782623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50964212417603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53738641738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58362913131714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76741504669189</t>
+    <t xml:space="preserve">8.0182991027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81483793258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95356321334839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49114608764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86107873916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50964260101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53738689422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58362817764282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76741409301758</t>
   </si>
   <si>
     <t xml:space="preserve">8.9893741607666</t>
@@ -1535,10 +1535,10 @@
     <t xml:space="preserve">9.16509342193604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12809944152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09110736846924</t>
+    <t xml:space="preserve">9.12810039520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09110641479492</t>
   </si>
   <si>
     <t xml:space="preserve">9.08185768127441</t>
@@ -1547,10 +1547,10 @@
     <t xml:space="preserve">9.34081172943115</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04486465454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21133518218994</t>
+    <t xml:space="preserve">9.04486560821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21133327484131</t>
   </si>
   <si>
     <t xml:space="preserve">9.38705158233643</t>
@@ -1565,19 +1565,19 @@
     <t xml:space="preserve">9.11885070800781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78591060638428</t>
+    <t xml:space="preserve">8.78591156005859</t>
   </si>
   <si>
     <t xml:space="preserve">8.89689159393311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7489185333252</t>
+    <t xml:space="preserve">8.74891757965088</t>
   </si>
   <si>
     <t xml:space="preserve">8.80440807342529</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87839412689209</t>
+    <t xml:space="preserve">8.87839508056641</t>
   </si>
   <si>
     <t xml:space="preserve">8.9338846206665</t>
@@ -1601,70 +1601,70 @@
     <t xml:space="preserve">9.6494197845459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69649028778076</t>
+    <t xml:space="preserve">9.69649124145508</t>
   </si>
   <si>
     <t xml:space="preserve">9.74356174468994</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97891235351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93184280395508</t>
+    <t xml:space="preserve">9.97891330718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93184375762939</t>
   </si>
   <si>
     <t xml:space="preserve">9.79063034057617</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0730533599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3084058761597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4496173858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1671934127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1201238632202</t>
+    <t xml:space="preserve">10.0730543136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3084049224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4496164321899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1671943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1201248168945</t>
   </si>
   <si>
     <t xml:space="preserve">10.0259838104248</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2142658233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3554754257202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2613353729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8847713470459</t>
+    <t xml:space="preserve">10.2142648696899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3554744720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2613344192505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88477230072021</t>
   </si>
   <si>
     <t xml:space="preserve">10.5908269882202</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4966869354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.543758392334</t>
+    <t xml:space="preserve">10.4966850280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5437574386597</t>
   </si>
   <si>
     <t xml:space="preserve">11.2027416229248</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1556711196899</t>
+    <t xml:space="preserve">11.1556720733643</t>
   </si>
   <si>
     <t xml:space="preserve">10.9673900604248</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0615301132202</t>
+    <t xml:space="preserve">11.0615310668945</t>
   </si>
   <si>
     <t xml:space="preserve">10.7791090011597</t>
@@ -1676,16 +1676,16 @@
     <t xml:space="preserve">11.0144605636597</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1086015701294</t>
+    <t xml:space="preserve">11.1086025238037</t>
   </si>
   <si>
     <t xml:space="preserve">10.9203205108643</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8732490539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7320384979248</t>
+    <t xml:space="preserve">10.8732500076294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7320375442505</t>
   </si>
   <si>
     <t xml:space="preserve">10.6378984451294</t>
@@ -1700,25 +1700,25 @@
     <t xml:space="preserve">11.7675848007202</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8146562576294</t>
+    <t xml:space="preserve">11.8146572113037</t>
   </si>
   <si>
     <t xml:space="preserve">11.5793046951294</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6734447479248</t>
+    <t xml:space="preserve">11.6734437942505</t>
   </si>
   <si>
     <t xml:space="preserve">11.7205152511597</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0029373168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2853593826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5677824020386</t>
+    <t xml:space="preserve">12.0029382705688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2853603363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5677814483643</t>
   </si>
   <si>
     <t xml:space="preserve">12.5207118988037</t>
@@ -1730,25 +1730,25 @@
     <t xml:space="preserve">12.7560634613037</t>
   </si>
   <si>
-    <t xml:space="preserve">12.661922454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6148519515991</t>
+    <t xml:space="preserve">12.6619215011597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6148509979248</t>
   </si>
   <si>
     <t xml:space="preserve">12.8031330108643</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8502044677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9914140701294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1796951293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4621181488037</t>
+    <t xml:space="preserve">12.8502035140991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9914150238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1796960830688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.462119102478</t>
   </si>
   <si>
     <t xml:space="preserve">13.838680267334</t>
@@ -1763,22 +1763,22 @@
     <t xml:space="preserve">13.5091886520386</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7916107177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8857517242432</t>
+    <t xml:space="preserve">13.7916097640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8857507705688</t>
   </si>
   <si>
     <t xml:space="preserve">13.9798927307129</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0269622802734</t>
+    <t xml:space="preserve">14.0269613265991</t>
   </si>
   <si>
     <t xml:space="preserve">14.0740327835083</t>
   </si>
   <si>
-    <t xml:space="preserve">14.168173789978</t>
+    <t xml:space="preserve">14.1681747436523</t>
   </si>
   <si>
     <t xml:space="preserve">14.1211032867432</t>
@@ -1799,10 +1799,10 @@
     <t xml:space="preserve">14.3093852996826</t>
   </si>
   <si>
-    <t xml:space="preserve">14.403525352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3564538955688</t>
+    <t xml:space="preserve">14.4035263061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3564548492432</t>
   </si>
   <si>
     <t xml:space="preserve">14.5447359085083</t>
@@ -1811,31 +1811,31 @@
     <t xml:space="preserve">14.5918064117432</t>
   </si>
   <si>
-    <t xml:space="preserve">14.638876914978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7800874710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8271589279175</t>
+    <t xml:space="preserve">14.6388778686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.780086517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8271579742432</t>
   </si>
   <si>
     <t xml:space="preserve">14.874228477478</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7330169677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3449306488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7685623168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0039157867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0415744781494</t>
+    <t xml:space="preserve">14.7330160140991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.344931602478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7685632705688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0039176940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0415725708008</t>
   </si>
   <si>
     <t xml:space="preserve">16.0792274475098</t>
@@ -1844,7 +1844,7 @@
     <t xml:space="preserve">16.1921997070312</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1168880462646</t>
+    <t xml:space="preserve">16.116886138916</t>
   </si>
   <si>
     <t xml:space="preserve">16.2298526763916</t>
@@ -1853,7 +1853,7 @@
     <t xml:space="preserve">16.3804779052734</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3993072509766</t>
+    <t xml:space="preserve">16.3993053436279</t>
   </si>
   <si>
     <t xml:space="preserve">16.4181365966797</t>
@@ -1865,31 +1865,31 @@
     <t xml:space="preserve">16.2675113677979</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9286050796509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8909492492676</t>
+    <t xml:space="preserve">15.9286031723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8909482955933</t>
   </si>
   <si>
     <t xml:space="preserve">15.815634727478</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9662609100342</t>
+    <t xml:space="preserve">15.9662599563599</t>
   </si>
   <si>
     <t xml:space="preserve">15.7214956283569</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5332145690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.514386177063</t>
+    <t xml:space="preserve">15.5332136154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5143852233887</t>
   </si>
   <si>
     <t xml:space="preserve">15.7026672363281</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2696180343628</t>
+    <t xml:space="preserve">15.2696189880371</t>
   </si>
   <si>
     <t xml:space="preserve">15.4767303466797</t>
@@ -1898,10 +1898,10 @@
     <t xml:space="preserve">15.6838388442993</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6650104522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4202423095703</t>
+    <t xml:space="preserve">15.6650085449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4202432632446</t>
   </si>
   <si>
     <t xml:space="preserve">15.1566514968872</t>
@@ -1916,19 +1916,19 @@
     <t xml:space="preserve">15.9833707809448</t>
   </si>
   <si>
-    <t xml:space="preserve">15.964301109314</t>
+    <t xml:space="preserve">15.9643001556396</t>
   </si>
   <si>
     <t xml:space="preserve">15.6209812164307</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4874696731567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7926397323608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8117141723633</t>
+    <t xml:space="preserve">15.4874687194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7926406860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8117160797119</t>
   </si>
   <si>
     <t xml:space="preserve">15.6019086837769</t>
@@ -1937,16 +1937,16 @@
     <t xml:space="preserve">15.5446872711182</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2585906982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6972723007202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8307867050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.116886138916</t>
+    <t xml:space="preserve">15.2585897445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6972742080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8307876586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1168842315674</t>
   </si>
   <si>
     <t xml:space="preserve">16.2503986358643</t>
@@ -1955,13 +1955,13 @@
     <t xml:space="preserve">16.2313251495361</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0024471282959</t>
+    <t xml:space="preserve">16.0024452209473</t>
   </si>
   <si>
     <t xml:space="preserve">16.2694721221924</t>
   </si>
   <si>
-    <t xml:space="preserve">16.212251663208</t>
+    <t xml:space="preserve">16.2122535705566</t>
   </si>
   <si>
     <t xml:space="preserve">16.460205078125</t>
@@ -1973,10 +1973,10 @@
     <t xml:space="preserve">16.5364971160889</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5555725097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1659145355225</t>
+    <t xml:space="preserve">16.555570602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1659126281738</t>
   </si>
   <si>
     <t xml:space="preserve">16.9561080932617</t>
@@ -1988,31 +1988,31 @@
     <t xml:space="preserve">17.3185005187988</t>
   </si>
   <si>
-    <t xml:space="preserve">17.08962059021</t>
+    <t xml:space="preserve">17.0896224975586</t>
   </si>
   <si>
     <t xml:space="preserve">16.8416690826416</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7463035583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9751815795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1277675628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5092334747314</t>
+    <t xml:space="preserve">16.746301651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9751796722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1277656555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5092315673828</t>
   </si>
   <si>
     <t xml:space="preserve">17.5473785400391</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7571849822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6427459716797</t>
+    <t xml:space="preserve">17.7571830749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6427440643311</t>
   </si>
   <si>
     <t xml:space="preserve">17.7381134033203</t>
@@ -2021,10 +2021,10 @@
     <t xml:space="preserve">17.4901580810547</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4710865020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3375720977783</t>
+    <t xml:space="preserve">17.4710845947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.337574005127</t>
   </si>
   <si>
     <t xml:space="preserve">17.2994251251221</t>
@@ -2051,13 +2051,13 @@
     <t xml:space="preserve">17.6999645233154</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8716220855713</t>
+    <t xml:space="preserve">17.8716259002686</t>
   </si>
   <si>
     <t xml:space="preserve">17.8525505065918</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0242099761963</t>
+    <t xml:space="preserve">18.0242080688477</t>
   </si>
   <si>
     <t xml:space="preserve">18.424747467041</t>
@@ -2081,28 +2081,28 @@
     <t xml:space="preserve">18.8062114715576</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5201148986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.55006980896</t>
+    <t xml:space="preserve">18.520112991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5500659942627</t>
   </si>
   <si>
     <t xml:space="preserve">19.5023880004883</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8838520050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9792194366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.454704284668</t>
+    <t xml:space="preserve">19.8838500976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9792175292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4547023773193</t>
   </si>
   <si>
     <t xml:space="preserve">19.3593349456787</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1686058044434</t>
+    <t xml:space="preserve">19.1686038970947</t>
   </si>
   <si>
     <t xml:space="preserve">18.7871398925781</t>
@@ -2111,13 +2111,13 @@
     <t xml:space="preserve">18.6917743682861</t>
   </si>
   <si>
-    <t xml:space="preserve">19.216287612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.120922088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.76806640625</t>
+    <t xml:space="preserve">19.2162857055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1209182739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7680644989014</t>
   </si>
   <si>
     <t xml:space="preserve">17.9097709655762</t>
@@ -2135,19 +2135,19 @@
     <t xml:space="preserve">18.1005020141602</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2530860900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9669876098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1767959594727</t>
+    <t xml:space="preserve">18.2530879974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9669895172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.176794052124</t>
   </si>
   <si>
     <t xml:space="preserve">18.9969444274902</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0732383728027</t>
+    <t xml:space="preserve">19.0732364654541</t>
   </si>
   <si>
     <t xml:space="preserve">18.9778728485107</t>
@@ -2168,7 +2168,7 @@
     <t xml:space="preserve">20.2176322937012</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2653160095215</t>
+    <t xml:space="preserve">20.2653141021729</t>
   </si>
   <si>
     <t xml:space="preserve">20.7421455383301</t>
@@ -2183,22 +2183,22 @@
     <t xml:space="preserve">21.4573917388916</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6944637298584</t>
+    <t xml:space="preserve">20.6944618225098</t>
   </si>
   <si>
     <t xml:space="preserve">20.3129978179932</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4560489654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9805603027344</t>
+    <t xml:space="preserve">20.4560508728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.980562210083</t>
   </si>
   <si>
     <t xml:space="preserve">19.8361682891846</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4083652496338</t>
+    <t xml:space="preserve">20.4083633422852</t>
   </si>
   <si>
     <t xml:space="preserve">20.1222667694092</t>
@@ -2207,49 +2207,49 @@
     <t xml:space="preserve">19.3116550445557</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2639713287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5977516174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6454372406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1699485778809</t>
+    <t xml:space="preserve">19.2639694213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.597749710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6454334259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1699466705322</t>
   </si>
   <si>
     <t xml:space="preserve">19.9315338134766</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7408027648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8443584442139</t>
+    <t xml:space="preserve">19.7408008575439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8443603515625</t>
   </si>
   <si>
     <t xml:space="preserve">19.0160179138184</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0432834625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0051364898682</t>
+    <t xml:space="preserve">18.0432815551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0051345825195</t>
   </si>
   <si>
     <t xml:space="preserve">18.1386489868164</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0623550415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.081428527832</t>
+    <t xml:space="preserve">18.0623569488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0814266204834</t>
   </si>
   <si>
     <t xml:space="preserve">17.6045970916748</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2612819671631</t>
+    <t xml:space="preserve">17.2612800598145</t>
   </si>
   <si>
     <t xml:space="preserve">17.0514736175537</t>
@@ -2258,25 +2258,25 @@
     <t xml:space="preserve">16.2885456085205</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0324020385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7272300720215</t>
+    <t xml:space="preserve">17.0324001312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7272319793701</t>
   </si>
   <si>
     <t xml:space="preserve">16.4792766571045</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8225936889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0705490112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.650936126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8607406616211</t>
+    <t xml:space="preserve">16.8225955963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0705471038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6509342193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8607444763184</t>
   </si>
   <si>
     <t xml:space="preserve">16.3076190948486</t>
@@ -2288,34 +2288,34 @@
     <t xml:space="preserve">16.6318626403809</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2776641845703</t>
+    <t xml:space="preserve">15.277663230896</t>
   </si>
   <si>
     <t xml:space="preserve">14.8771257400513</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4956607818604</t>
+    <t xml:space="preserve">14.495659828186</t>
   </si>
   <si>
     <t xml:space="preserve">15.3730306625366</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9915657043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0869312286377</t>
+    <t xml:space="preserve">14.9915647506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0869302749634</t>
   </si>
   <si>
     <t xml:space="preserve">15.678201675415</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1441497802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9452266693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0787391662598</t>
+    <t xml:space="preserve">15.1441507339478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9452257156372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0787410736084</t>
   </si>
   <si>
     <t xml:space="preserve">16.0405921936035</t>
@@ -2330,7 +2330,7 @@
     <t xml:space="preserve">16.5174217224121</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4983501434326</t>
+    <t xml:space="preserve">16.498348236084</t>
   </si>
   <si>
     <t xml:space="preserve">15.7354202270508</t>
@@ -2339,7 +2339,7 @@
     <t xml:space="preserve">15.8880052566528</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5065412521362</t>
+    <t xml:space="preserve">15.5065402984619</t>
   </si>
   <si>
     <t xml:space="preserve">14.9724912643433</t>
@@ -2348,7 +2348,7 @@
     <t xml:space="preserve">15.3348827362061</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2204427719116</t>
+    <t xml:space="preserve">15.2204437255859</t>
   </si>
   <si>
     <t xml:space="preserve">14.9152727127075</t>
@@ -2357,7 +2357,7 @@
     <t xml:space="preserve">14.781759262085</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8961982727051</t>
+    <t xml:space="preserve">14.8961992263794</t>
   </si>
   <si>
     <t xml:space="preserve">15.6400547027588</t>
@@ -2366,7 +2366,7 @@
     <t xml:space="preserve">16.0978126525879</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2395153045654</t>
+    <t xml:space="preserve">15.2395162582397</t>
   </si>
   <si>
     <t xml:space="preserve">15.1060047149658</t>
@@ -69013,7 +69013,7 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.6493171296</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>49212</v>
@@ -69034,6 +69034,32 @@
         <v>1248</v>
       </c>
       <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.6495949074</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>33374</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>52.5999984741211</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>52</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>52.2000007629395</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>1260</v>
+      </c>
+      <c r="H2496" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SOL.MI.xlsx
+++ b/data/SOL.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14939165115356</t>
+    <t xml:space="preserve">7.14939117431641</t>
   </si>
   <si>
     <t xml:space="preserve">SOL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14067220687866</t>
+    <t xml:space="preserve">7.14067268371582</t>
   </si>
   <si>
     <t xml:space="preserve">7.18862581253052</t>
@@ -53,25 +53,25 @@
     <t xml:space="preserve">7.1624698638916</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0622034072876</t>
+    <t xml:space="preserve">7.06220483779907</t>
   </si>
   <si>
     <t xml:space="preserve">6.90962553024292</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90526533126831</t>
+    <t xml:space="preserve">6.90526580810547</t>
   </si>
   <si>
     <t xml:space="preserve">6.94885921478271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71781253814697</t>
+    <t xml:space="preserve">6.71781158447266</t>
   </si>
   <si>
     <t xml:space="preserve">6.62626457214355</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71345281600952</t>
+    <t xml:space="preserve">6.71345329284668</t>
   </si>
   <si>
     <t xml:space="preserve">6.2993106842041</t>
@@ -80,25 +80,25 @@
     <t xml:space="preserve">6.36470222473145</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43009233474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4126558303833</t>
+    <t xml:space="preserve">6.43009328842163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41265487670898</t>
   </si>
   <si>
     <t xml:space="preserve">6.4475302696228</t>
   </si>
   <si>
-    <t xml:space="preserve">6.207763671875</t>
+    <t xml:space="preserve">6.20776462554932</t>
   </si>
   <si>
     <t xml:space="preserve">6.1728892326355</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46060752868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54779624938965</t>
+    <t xml:space="preserve">6.46060848236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54779672622681</t>
   </si>
   <si>
     <t xml:space="preserve">6.38213920593262</t>
@@ -119,49 +119,49 @@
     <t xml:space="preserve">6.72217178344727</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79192161560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00989103317261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84423446655273</t>
+    <t xml:space="preserve">6.79192209243774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00989055633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84423398971558</t>
   </si>
   <si>
     <t xml:space="preserve">7.07964181900024</t>
   </si>
   <si>
-    <t xml:space="preserve">6.883469581604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9662971496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08836078643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73524951934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8311562538147</t>
+    <t xml:space="preserve">6.88346862792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96629667282104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08836030960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73524904251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83115673065186</t>
   </si>
   <si>
     <t xml:space="preserve">6.67857789993286</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57395267486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63062381744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68729782104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.783203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77884387969971</t>
+    <t xml:space="preserve">6.57395219802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63062524795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68729686737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78320264816284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77884340286255</t>
   </si>
   <si>
     <t xml:space="preserve">6.81371879577637</t>
@@ -170,58 +170,58 @@
     <t xml:space="preserve">6.80935907363892</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79628133773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69601488113403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81807804107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8747501373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91398429870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67421865463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55215549468994</t>
+    <t xml:space="preserve">6.79628086090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69601535797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8180775642395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87475061416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91398477554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67421817779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55215501785278</t>
   </si>
   <si>
     <t xml:space="preserve">6.46496772766113</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43881225585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73089027404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87910890579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85295343399048</t>
+    <t xml:space="preserve">6.43881177902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73088979721069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87910938262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85295391082764</t>
   </si>
   <si>
     <t xml:space="preserve">6.84859418869019</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85731267929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74832725524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51727962493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37342119216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56523323059082</t>
+    <t xml:space="preserve">6.85731220245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74832773208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51728010177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37342071533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56523418426514</t>
   </si>
   <si>
     <t xml:space="preserve">6.66985940933228</t>
@@ -230,22 +230,22 @@
     <t xml:space="preserve">6.77012491226196</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86167144775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97501611709595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9416298866272</t>
+    <t xml:space="preserve">6.86167240142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97501564025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94162940979004</t>
   </si>
   <si>
     <t xml:space="preserve">6.95048379898071</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88407850265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90178632736206</t>
+    <t xml:space="preserve">6.88407802581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9017858505249</t>
   </si>
   <si>
     <t xml:space="preserve">7.34006500244141</t>
@@ -254,229 +254,229 @@
     <t xml:space="preserve">7.22496175765991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41975212097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43746089935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36662769317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26037836074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46845054626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40204429626465</t>
+    <t xml:space="preserve">7.41975355148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43745946884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36662721633911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26037788391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46845006942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40204381942749</t>
   </si>
   <si>
     <t xml:space="preserve">7.44631481170654</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38433599472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04345226287842</t>
+    <t xml:space="preserve">7.38433647155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04345178604126</t>
   </si>
   <si>
     <t xml:space="preserve">6.97261905670166</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10985803604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8707971572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20725297927856</t>
+    <t xml:space="preserve">7.1098575592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87079620361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20725440979004</t>
   </si>
   <si>
     <t xml:space="preserve">7.37105464935303</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57027196884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69423007965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70308446884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71193742752075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6588134765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04396820068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61454296112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29579496383667</t>
+    <t xml:space="preserve">7.57027292251587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69422960281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70308351516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71193790435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65881299972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04396724700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61454200744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29579401016235</t>
   </si>
   <si>
     <t xml:space="preserve">6.99475431442261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1010046005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55256366729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31350326538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50829267501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4241795539856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37548208236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52600145339966</t>
+    <t xml:space="preserve">7.10100412368774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55256509780884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31350231170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50829219818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42418003082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37548112869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52600240707397</t>
   </si>
   <si>
     <t xml:space="preserve">7.54371023178101</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41532421112061</t>
+    <t xml:space="preserve">7.41532516479492</t>
   </si>
   <si>
     <t xml:space="preserve">7.21610736846924</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99032783508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79996347427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75569343566895</t>
+    <t xml:space="preserve">6.99032735824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79996395111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7556939125061</t>
   </si>
   <si>
     <t xml:space="preserve">7.00803565979004</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26923274993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34449148178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46402311325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51714706420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39318990707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45516920089722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17183685302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33563756942749</t>
+    <t xml:space="preserve">7.26923179626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34449291229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46402263641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5171480178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39319038391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45517015457153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17183780670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33563804626465</t>
   </si>
   <si>
     <t xml:space="preserve">7.33121109008789</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39761638641357</t>
+    <t xml:space="preserve">7.39761447906494</t>
   </si>
   <si>
     <t xml:space="preserve">7.30464887619019</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27808666229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25152349472046</t>
+    <t xml:space="preserve">7.27808523178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25152397155762</t>
   </si>
   <si>
     <t xml:space="preserve">7.16298294067383</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03017091751099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8796501159668</t>
+    <t xml:space="preserve">7.03017139434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87965059280396</t>
   </si>
   <si>
     <t xml:space="preserve">6.91064071655273</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95491170883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88850545883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95933818817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85751533508301</t>
+    <t xml:space="preserve">6.95491123199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88850498199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95933866500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85751628875732</t>
   </si>
   <si>
     <t xml:space="preserve">6.77340173721313</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74683952331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82652616500854</t>
+    <t xml:space="preserve">6.74683904647827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8265266418457</t>
   </si>
   <si>
     <t xml:space="preserve">6.68486070632935</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81767177581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90621376037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01689004898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89735794067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83538007736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86194229125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92392158508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97704601287842</t>
+    <t xml:space="preserve">6.81767225265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90621328353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01689052581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8973593711853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8353796005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86194276809692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92392110824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97704648971558</t>
   </si>
   <si>
     <t xml:space="preserve">7.00360822677612</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91506719589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91949510574341</t>
+    <t xml:space="preserve">6.91506671905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91949462890625</t>
   </si>
   <si>
     <t xml:space="preserve">6.93720293045044</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07001495361328</t>
+    <t xml:space="preserve">7.07001447677612</t>
   </si>
   <si>
     <t xml:space="preserve">6.98590040206909</t>
@@ -485,16 +485,16 @@
     <t xml:space="preserve">6.75126647949219</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77782869338989</t>
+    <t xml:space="preserve">6.77782821655273</t>
   </si>
   <si>
     <t xml:space="preserve">6.64944410324097</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38382005691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37053871154785</t>
+    <t xml:space="preserve">6.38382053375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37053918838501</t>
   </si>
   <si>
     <t xml:space="preserve">6.36168479919434</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">6.48121500015259</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47678804397583</t>
+    <t xml:space="preserve">6.47678852081299</t>
   </si>
   <si>
     <t xml:space="preserve">6.54319381713867</t>
@@ -518,88 +518,88 @@
     <t xml:space="preserve">6.46350765228271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24215459823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25986337661743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22444581985474</t>
+    <t xml:space="preserve">6.24215412139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25986289978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22444677352905</t>
   </si>
   <si>
     <t xml:space="preserve">6.64501619338989</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64058923721313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0390248298645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79111099243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70256805419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70699501037598</t>
+    <t xml:space="preserve">6.64058971405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03902435302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79111003875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70256900787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70699548721313</t>
   </si>
   <si>
     <t xml:space="preserve">6.65829801559448</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58303785324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05673265457153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11428499221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34891843795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18511772155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12756633758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19397258758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24267053604126</t>
+    <t xml:space="preserve">6.58303833007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05673313140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11428451538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34891891479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18511724472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12756681442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19397211074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2426700592041</t>
   </si>
   <si>
     <t xml:space="preserve">7.41089820861816</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48173046112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14527463912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27365970611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1762638092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04787969589233</t>
+    <t xml:space="preserve">7.48173093795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14527416229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27365922927856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17626333236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04787921905518</t>
   </si>
   <si>
     <t xml:space="preserve">7.23381614685059</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29136753082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4286060333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83589601516724</t>
+    <t xml:space="preserve">7.2913670539856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42860651016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83589553833008</t>
   </si>
   <si>
     <t xml:space="preserve">7.82704210281372</t>
@@ -614,22 +614,22 @@
     <t xml:space="preserve">8.32287311553955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03120136260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53094387054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49995517730713</t>
+    <t xml:space="preserve">9.03120231628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53094577789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49995422363281</t>
   </si>
   <si>
     <t xml:space="preserve">8.26089382171631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92495155334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58849620819092</t>
+    <t xml:space="preserve">8.92495250701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5884952545166</t>
   </si>
   <si>
     <t xml:space="preserve">8.97807788848877</t>
@@ -641,13 +641,13 @@
     <t xml:space="preserve">8.87182807922363</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56244850158691</t>
+    <t xml:space="preserve">9.5624475479126</t>
   </si>
   <si>
     <t xml:space="preserve">9.25255393981934</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02234554290771</t>
+    <t xml:space="preserve">9.02234649658203</t>
   </si>
   <si>
     <t xml:space="preserve">8.85411930084229</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">8.71245384216309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98693180084229</t>
+    <t xml:space="preserve">8.98692989349365</t>
   </si>
   <si>
     <t xml:space="preserve">8.89838981628418</t>
@@ -668,19 +668,19 @@
     <t xml:space="preserve">8.80984878540039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72130966186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78328609466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67703628540039</t>
+    <t xml:space="preserve">8.72130870819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78328704833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67703723907471</t>
   </si>
   <si>
     <t xml:space="preserve">8.75672435760498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10203552246094</t>
+    <t xml:space="preserve">9.10203456878662</t>
   </si>
   <si>
     <t xml:space="preserve">8.82313060760498</t>
@@ -689,13 +689,13 @@
     <t xml:space="preserve">8.94266128540039</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20828342437744</t>
+    <t xml:space="preserve">9.20828533172607</t>
   </si>
   <si>
     <t xml:space="preserve">9.43287563323975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45982837677002</t>
+    <t xml:space="preserve">9.45982646942139</t>
   </si>
   <si>
     <t xml:space="preserve">9.52271366119385</t>
@@ -704,10 +704,10 @@
     <t xml:space="preserve">9.3250732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38795852661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35202407836914</t>
+    <t xml:space="preserve">9.38795757293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35202312469482</t>
   </si>
   <si>
     <t xml:space="preserve">9.42389297485352</t>
@@ -716,49 +716,49 @@
     <t xml:space="preserve">9.29812145233154</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55864810943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67543792724609</t>
+    <t xml:space="preserve">9.55864906311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67543697357178</t>
   </si>
   <si>
     <t xml:space="preserve">9.86409282684326</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5199022293091</t>
+    <t xml:space="preserve">10.519905090332</t>
   </si>
   <si>
     <t xml:space="preserve">10.0617351531982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88206005096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74730777740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56763076782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44186019897461</t>
+    <t xml:space="preserve">9.88206195831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74730682373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56763172149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44186115264893</t>
   </si>
   <si>
     <t xml:space="preserve">9.54068088531494</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34303951263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36100769042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50474739074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48677921295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61254978179932</t>
+    <t xml:space="preserve">9.34304046630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36100673675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50474643707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48677825927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61255073547363</t>
   </si>
   <si>
     <t xml:space="preserve">9.77425670623779</t>
@@ -767,40 +767,40 @@
     <t xml:space="preserve">9.46881198883057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54966449737549</t>
+    <t xml:space="preserve">9.5496654510498</t>
   </si>
   <si>
     <t xml:space="preserve">9.47779560089111</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7023868560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30710411071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28015422821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2172679901123</t>
+    <t xml:space="preserve">9.70238590240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30710601806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28015518188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21726894378662</t>
   </si>
   <si>
     <t xml:space="preserve">9.16336631774902</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20828247070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25320434570312</t>
+    <t xml:space="preserve">9.20828437805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25320243835449</t>
   </si>
   <si>
     <t xml:space="preserve">9.45084285736084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58559989929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33405685424805</t>
+    <t xml:space="preserve">9.58559894561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33405590057373</t>
   </si>
   <si>
     <t xml:space="preserve">9.59458255767822</t>
@@ -809,76 +809,76 @@
     <t xml:space="preserve">9.66645240783691</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71137237548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40592479705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26218700408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2711706161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28913879394531</t>
+    <t xml:space="preserve">9.7113733291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40592670440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26218605041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27116870880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28913688659668</t>
   </si>
   <si>
     <t xml:space="preserve">9.36999034881592</t>
   </si>
   <si>
-    <t xml:space="preserve">9.657470703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79222297668457</t>
+    <t xml:space="preserve">9.65746974945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79222393035889</t>
   </si>
   <si>
     <t xml:space="preserve">9.76527309417725</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7203540802002</t>
+    <t xml:space="preserve">9.72035503387451</t>
   </si>
   <si>
     <t xml:space="preserve">9.81019115447998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37897300720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.909010887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81917762756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73832225799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78324222564697</t>
+    <t xml:space="preserve">9.37897396087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90901184082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81917572021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73832130432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78324127197266</t>
   </si>
   <si>
     <t xml:space="preserve">9.69340419769287</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11844730377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08251190185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31608867645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19031620025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10048007965088</t>
+    <t xml:space="preserve">9.11844635009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08251285552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31608963012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19031524658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10047912597656</t>
   </si>
   <si>
     <t xml:space="preserve">9.22625160217285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41490745544434</t>
+    <t xml:space="preserve">9.41490840911865</t>
   </si>
   <si>
     <t xml:space="preserve">9.39694118499756</t>
@@ -890,7 +890,7 @@
     <t xml:space="preserve">9.57661533355713</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68441963195801</t>
+    <t xml:space="preserve">9.68441867828369</t>
   </si>
   <si>
     <t xml:space="preserve">9.09149742126465</t>
@@ -899,7 +899,7 @@
     <t xml:space="preserve">9.05556106567383</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14539909362793</t>
+    <t xml:space="preserve">9.14540004730225</t>
   </si>
   <si>
     <t xml:space="preserve">8.89385509490967</t>
@@ -911,25 +911,25 @@
     <t xml:space="preserve">9.2352352142334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95393085479736</t>
+    <t xml:space="preserve">9.95393180847168</t>
   </si>
   <si>
     <t xml:space="preserve">10.5109195709229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.74449634552</t>
+    <t xml:space="preserve">10.7444953918457</t>
   </si>
   <si>
     <t xml:space="preserve">10.546854019165</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6905927658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9062023162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7804298400879</t>
+    <t xml:space="preserve">10.6905937194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9062013626099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7804307937622</t>
   </si>
   <si>
     <t xml:space="preserve">10.7085618972778</t>
@@ -938,40 +938,40 @@
     <t xml:space="preserve">10.6546592712402</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5288858413696</t>
+    <t xml:space="preserve">10.5288867950439</t>
   </si>
   <si>
     <t xml:space="preserve">10.4390497207642</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3312454223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1695404052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1875057220459</t>
+    <t xml:space="preserve">10.331244468689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1695384979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1875066757202</t>
   </si>
   <si>
     <t xml:space="preserve">10.1336040496826</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7562894821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63051700592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0078344345093</t>
+    <t xml:space="preserve">9.75628852844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63051891326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.007833480835</t>
   </si>
   <si>
     <t xml:space="preserve">9.8461275100708</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0976696014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2054738998413</t>
+    <t xml:space="preserve">10.0976686477661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2054748535156</t>
   </si>
   <si>
     <t xml:space="preserve">10.2773447036743</t>
@@ -980,28 +980,28 @@
     <t xml:space="preserve">10.2234411239624</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2414102554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7624626159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2593765258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91799545288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90002918243408</t>
+    <t xml:space="preserve">10.2414093017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7624616622925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2593774795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91799640655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90002822875977</t>
   </si>
   <si>
     <t xml:space="preserve">9.67380714416504</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74667835235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87420654296875</t>
+    <t xml:space="preserve">9.74667930603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87420558929443</t>
   </si>
   <si>
     <t xml:space="preserve">10.1656942367554</t>
@@ -1010,25 +1010,25 @@
     <t xml:space="preserve">9.85598754882812</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63737106323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47340679168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76489639282227</t>
+    <t xml:space="preserve">9.63737010955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47340774536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76489734649658</t>
   </si>
   <si>
     <t xml:space="preserve">9.96529579162598</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0746059417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2385673522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.384313583374</t>
+    <t xml:space="preserve">10.0746049880981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2385663986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3843126296997</t>
   </si>
   <si>
     <t xml:space="preserve">10.4207487106323</t>
@@ -1040,16 +1040,16 @@
     <t xml:space="preserve">10.6940202713013</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6211471557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7851114273071</t>
+    <t xml:space="preserve">10.6211462020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7851104736328</t>
   </si>
   <si>
     <t xml:space="preserve">10.5482749938965</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4025297164917</t>
+    <t xml:space="preserve">10.402530670166</t>
   </si>
   <si>
     <t xml:space="preserve">10.2203502655029</t>
@@ -1058,7 +1058,7 @@
     <t xml:space="preserve">10.1474781036377</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3296575546265</t>
+    <t xml:space="preserve">10.3296585083008</t>
   </si>
   <si>
     <t xml:space="preserve">10.5847110748291</t>
@@ -1073,16 +1073,16 @@
     <t xml:space="preserve">9.56449794769287</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41875457763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40053558349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54627895355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1110410690308</t>
+    <t xml:space="preserve">9.4187536239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40053367614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54627990722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1110420227051</t>
   </si>
   <si>
     <t xml:space="preserve">10.2567863464355</t>
@@ -1091,22 +1091,22 @@
     <t xml:space="preserve">9.92885875701904</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0199489593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2021312713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0928220748901</t>
+    <t xml:space="preserve">10.0199508666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.202130317688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0928230285645</t>
   </si>
   <si>
     <t xml:space="preserve">9.80133247375488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69202423095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83776950836182</t>
+    <t xml:space="preserve">9.69202518463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8377685546875</t>
   </si>
   <si>
     <t xml:space="preserve">9.94707775115967</t>
@@ -1118,7 +1118,7 @@
     <t xml:space="preserve">9.65558910369873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78311347961426</t>
+    <t xml:space="preserve">9.78311443328857</t>
   </si>
   <si>
     <t xml:space="preserve">9.91064167022705</t>
@@ -1130,55 +1130,55 @@
     <t xml:space="preserve">9.20013618469238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50984287261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43697071075439</t>
+    <t xml:space="preserve">9.50984382629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43697261810303</t>
   </si>
   <si>
     <t xml:space="preserve">9.81955051422119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49162673950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6191520690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9835147857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60093402862549</t>
+    <t xml:space="preserve">9.49162578582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61915111541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98351573944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60093307495117</t>
   </si>
   <si>
     <t xml:space="preserve">9.10904502868652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09993553161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3823184967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36409950256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27300834655762</t>
+    <t xml:space="preserve">9.09993648529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38231658935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36409854888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27300930023193</t>
   </si>
   <si>
     <t xml:space="preserve">9.71024227142334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58271503448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29122638702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14548301696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3660945892334</t>
+    <t xml:space="preserve">9.58271598815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29122734069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14548206329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3660936355591</t>
   </si>
   <si>
     <t xml:space="preserve">9.32766246795654</t>
@@ -1196,16 +1196,16 @@
     <t xml:space="preserve">10.5664939880371</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3114404678345</t>
+    <t xml:space="preserve">10.3114395141602</t>
   </si>
   <si>
     <t xml:space="preserve">10.2932233810425</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0381689071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0563859939575</t>
+    <t xml:space="preserve">10.0381679534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0563869476318</t>
   </si>
   <si>
     <t xml:space="preserve">10.1292581558228</t>
@@ -1214,13 +1214,13 @@
     <t xml:space="preserve">10.2750034332275</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1839141845703</t>
+    <t xml:space="preserve">10.1839151382446</t>
   </si>
   <si>
     <t xml:space="preserve">10.6758012771606</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7122373580933</t>
+    <t xml:space="preserve">10.7122364044189</t>
   </si>
   <si>
     <t xml:space="preserve">10.930853843689</t>
@@ -1247,10 +1247,10 @@
     <t xml:space="preserve">11.1349859237671</t>
   </si>
   <si>
-    <t xml:space="preserve">11.097993850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2459659576416</t>
+    <t xml:space="preserve">11.0979928970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2459669113159</t>
   </si>
   <si>
     <t xml:space="preserve">11.319953918457</t>
@@ -1292,16 +1292,16 @@
     <t xml:space="preserve">10.5615911483765</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6170797348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3951206207275</t>
+    <t xml:space="preserve">10.6170806884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3951215744019</t>
   </si>
   <si>
     <t xml:space="preserve">10.1176700592041</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2841396331787</t>
+    <t xml:space="preserve">10.2841386795044</t>
   </si>
   <si>
     <t xml:space="preserve">10.2656440734863</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">10.3026371002197</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5060997009277</t>
+    <t xml:space="preserve">10.5061006546021</t>
   </si>
   <si>
     <t xml:space="preserve">10.3396310806274</t>
@@ -1322,7 +1322,7 @@
     <t xml:space="preserve">10.080677986145</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98819446563721</t>
+    <t xml:space="preserve">9.98819351196289</t>
   </si>
   <si>
     <t xml:space="preserve">10.0991735458374</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">9.71074390411377</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0251874923706</t>
+    <t xml:space="preserve">10.0251865386963</t>
   </si>
   <si>
     <t xml:space="preserve">9.91420650482178</t>
@@ -1361,7 +1361,7 @@
     <t xml:space="preserve">9.72924137115479</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65525341033936</t>
+    <t xml:space="preserve">9.65525436401367</t>
   </si>
   <si>
     <t xml:space="preserve">9.67375087738037</t>
@@ -1373,25 +1373,25 @@
     <t xml:space="preserve">9.54427528381348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56277084350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45179176330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35930824279785</t>
+    <t xml:space="preserve">9.56277179718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45179080963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35930728912354</t>
   </si>
   <si>
     <t xml:space="preserve">9.52577781677246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59976387023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61826038360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69224548339844</t>
+    <t xml:space="preserve">9.59976482391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61826133728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69224643707275</t>
   </si>
   <si>
     <t xml:space="preserve">9.80322742462158</t>
@@ -1403,7 +1403,7 @@
     <t xml:space="preserve">9.78473091125488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85871887207031</t>
+    <t xml:space="preserve">9.858717918396</t>
   </si>
   <si>
     <t xml:space="preserve">10.0066909790039</t>
@@ -1415,10 +1415,10 @@
     <t xml:space="preserve">9.74773788452148</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58126640319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3211336135864</t>
+    <t xml:space="preserve">9.58126735687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3211345672607</t>
   </si>
   <si>
     <t xml:space="preserve">10.4321146011353</t>
@@ -1427,10 +1427,10 @@
     <t xml:space="preserve">10.3766241073608</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2471475601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2101535797119</t>
+    <t xml:space="preserve">10.2471466064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2101526260376</t>
   </si>
   <si>
     <t xml:space="preserve">9.8402214050293</t>
@@ -1442,25 +1442,25 @@
     <t xml:space="preserve">9.43329429626465</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41479873657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39630126953125</t>
+    <t xml:space="preserve">9.41479778289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39630031585693</t>
   </si>
   <si>
     <t xml:space="preserve">9.24832820892334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06336212158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1096019744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32231426239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28532123565674</t>
+    <t xml:space="preserve">9.06336116790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10960292816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32231330871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28532028198242</t>
   </si>
   <si>
     <t xml:space="preserve">9.26682567596436</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">9.22983074188232</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48878574371338</t>
+    <t xml:space="preserve">9.48878479003906</t>
   </si>
   <si>
     <t xml:space="preserve">9.02636909484863</t>
@@ -1490,7 +1490,7 @@
     <t xml:space="preserve">8.82290458679199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61944198608398</t>
+    <t xml:space="preserve">8.61944103240967</t>
   </si>
   <si>
     <t xml:space="preserve">8.55470371246338</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">8.0182991027832</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81483793258667</t>
+    <t xml:space="preserve">7.81483697891235</t>
   </si>
   <si>
     <t xml:space="preserve">7.95356321334839</t>
@@ -1520,13 +1520,13 @@
     <t xml:space="preserve">7.50964260101318</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53738689422607</t>
+    <t xml:space="preserve">7.53738641738892</t>
   </si>
   <si>
     <t xml:space="preserve">7.58362817764282</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76741409301758</t>
+    <t xml:space="preserve">8.76741504669189</t>
   </si>
   <si>
     <t xml:space="preserve">8.9893741607666</t>
@@ -1553,7 +1553,7 @@
     <t xml:space="preserve">9.21133327484131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38705158233643</t>
+    <t xml:space="preserve">9.38705253601074</t>
   </si>
   <si>
     <t xml:space="preserve">9.17434120178223</t>
@@ -1562,7 +1562,7 @@
     <t xml:space="preserve">9.29456901550293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11885070800781</t>
+    <t xml:space="preserve">9.11885166168213</t>
   </si>
   <si>
     <t xml:space="preserve">8.78591156005859</t>
@@ -1574,7 +1574,7 @@
     <t xml:space="preserve">8.74891757965088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80440807342529</t>
+    <t xml:space="preserve">8.80440902709961</t>
   </si>
   <si>
     <t xml:space="preserve">8.87839508056641</t>
@@ -1586,13 +1586,13 @@
     <t xml:space="preserve">8.63793849945068</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71192359924316</t>
+    <t xml:space="preserve">8.71192455291748</t>
   </si>
   <si>
     <t xml:space="preserve">8.58244800567627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69342708587646</t>
+    <t xml:space="preserve">8.69342803955078</t>
   </si>
   <si>
     <t xml:space="preserve">9.46113872528076</t>
@@ -1610,10 +1610,10 @@
     <t xml:space="preserve">9.97891330718994</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93184375762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79063034057617</t>
+    <t xml:space="preserve">9.93184280395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79063129425049</t>
   </si>
   <si>
     <t xml:space="preserve">10.0730543136597</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">10.4496164321899</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1671943664551</t>
+    <t xml:space="preserve">10.1671934127808</t>
   </si>
   <si>
     <t xml:space="preserve">10.1201248168945</t>
@@ -1649,10 +1649,10 @@
     <t xml:space="preserve">10.5908269882202</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4966850280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5437574386597</t>
+    <t xml:space="preserve">10.4966859817505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.543758392334</t>
   </si>
   <si>
     <t xml:space="preserve">11.2027416229248</t>
@@ -1661,7 +1661,7 @@
     <t xml:space="preserve">11.1556720733643</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9673900604248</t>
+    <t xml:space="preserve">10.9673910140991</t>
   </si>
   <si>
     <t xml:space="preserve">11.0615310668945</t>
@@ -1676,16 +1676,16 @@
     <t xml:space="preserve">11.0144605636597</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1086025238037</t>
+    <t xml:space="preserve">11.1086015701294</t>
   </si>
   <si>
     <t xml:space="preserve">10.9203205108643</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8732500076294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7320375442505</t>
+    <t xml:space="preserve">10.8732490539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7320384979248</t>
   </si>
   <si>
     <t xml:space="preserve">10.6378984451294</t>
@@ -1706,7 +1706,7 @@
     <t xml:space="preserve">11.5793046951294</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6734437942505</t>
+    <t xml:space="preserve">11.6734447479248</t>
   </si>
   <si>
     <t xml:space="preserve">11.7205152511597</t>
@@ -1715,7 +1715,7 @@
     <t xml:space="preserve">12.0029382705688</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2853603363037</t>
+    <t xml:space="preserve">12.2853593826294</t>
   </si>
   <si>
     <t xml:space="preserve">12.5677814483643</t>
@@ -1730,25 +1730,25 @@
     <t xml:space="preserve">12.7560634613037</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6619215011597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6148509979248</t>
+    <t xml:space="preserve">12.661922454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6148519515991</t>
   </si>
   <si>
     <t xml:space="preserve">12.8031330108643</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8502035140991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9914150238037</t>
+    <t xml:space="preserve">12.8502044677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9914140701294</t>
   </si>
   <si>
     <t xml:space="preserve">13.1796960830688</t>
   </si>
   <si>
-    <t xml:space="preserve">13.462119102478</t>
+    <t xml:space="preserve">13.4621181488037</t>
   </si>
   <si>
     <t xml:space="preserve">13.838680267334</t>
@@ -1763,7 +1763,7 @@
     <t xml:space="preserve">13.5091886520386</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7916097640991</t>
+    <t xml:space="preserve">13.7916107177734</t>
   </si>
   <si>
     <t xml:space="preserve">13.8857507705688</t>
@@ -1772,13 +1772,13 @@
     <t xml:space="preserve">13.9798927307129</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0269613265991</t>
+    <t xml:space="preserve">14.0269622802734</t>
   </si>
   <si>
     <t xml:space="preserve">14.0740327835083</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1681747436523</t>
+    <t xml:space="preserve">14.168173789978</t>
   </si>
   <si>
     <t xml:space="preserve">14.1211032867432</t>
@@ -1793,13 +1793,13 @@
     <t xml:space="preserve">14.4505958557129</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6859483718872</t>
+    <t xml:space="preserve">14.6859474182129</t>
   </si>
   <si>
     <t xml:space="preserve">14.3093852996826</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4035263061523</t>
+    <t xml:space="preserve">14.403525352478</t>
   </si>
   <si>
     <t xml:space="preserve">14.3564548492432</t>
@@ -1808,34 +1808,34 @@
     <t xml:space="preserve">14.5447359085083</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5918064117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6388778686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.780086517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8271579742432</t>
+    <t xml:space="preserve">14.5918054580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.638876914978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7800874710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8271589279175</t>
   </si>
   <si>
     <t xml:space="preserve">14.874228477478</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7330160140991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.344931602478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7685632705688</t>
+    <t xml:space="preserve">14.7330169677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3449306488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7685623168945</t>
   </si>
   <si>
     <t xml:space="preserve">16.0039176940918</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0415725708008</t>
+    <t xml:space="preserve">16.0415744781494</t>
   </si>
   <si>
     <t xml:space="preserve">16.0792274475098</t>
@@ -1844,118 +1844,118 @@
     <t xml:space="preserve">16.1921997070312</t>
   </si>
   <si>
+    <t xml:space="preserve">16.1168880462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2298526763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3804779052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3993053436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4181365966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5311050415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2675113677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9286031723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8909482955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.815634727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9662618637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7214956283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5332136154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5143852233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7026672363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2696180343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4767303466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6838388442993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6650104522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4202423095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1566514968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2319641113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7779788970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9833707809448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9643001556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6209802627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4874687194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7926406860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8117141723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6019086837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5446872711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2585897445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6972732543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8307876586914</t>
+  </si>
+  <si>
     <t xml:space="preserve">16.116886138916</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2298526763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3804779052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3993053436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4181365966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5311050415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2675113677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9286031723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8909482955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.815634727478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9662599563599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7214956283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5332136154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5143852233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7026672363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2696189880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4767303466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6838388442993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6650085449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4202432632446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1566514968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2319641113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7779788970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9833707809448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9643001556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6209812164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4874687194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7926406860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8117160797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6019086837769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5446872711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2585897445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6972742080688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8307876586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1168842315674</t>
-  </si>
-  <si>
     <t xml:space="preserve">16.2503986358643</t>
   </si>
   <si>
     <t xml:space="preserve">16.2313251495361</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0024452209473</t>
+    <t xml:space="preserve">16.0024471282959</t>
   </si>
   <si>
     <t xml:space="preserve">16.2694721221924</t>
@@ -1967,10 +1967,10 @@
     <t xml:space="preserve">16.460205078125</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4411315917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5364971160889</t>
+    <t xml:space="preserve">16.4411334991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5364990234375</t>
   </si>
   <si>
     <t xml:space="preserve">16.555570602417</t>
@@ -1979,7 +1979,7 @@
     <t xml:space="preserve">17.1659126281738</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9561080932617</t>
+    <t xml:space="preserve">16.9561100006104</t>
   </si>
   <si>
     <t xml:space="preserve">17.2231349945068</t>
@@ -1991,7 +1991,7 @@
     <t xml:space="preserve">17.0896224975586</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8416690826416</t>
+    <t xml:space="preserve">16.841667175293</t>
   </si>
   <si>
     <t xml:space="preserve">16.746301651001</t>
@@ -2000,10 +2000,10 @@
     <t xml:space="preserve">16.9751796722412</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1277656555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5092315673828</t>
+    <t xml:space="preserve">17.1277675628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5092334747314</t>
   </si>
   <si>
     <t xml:space="preserve">17.5473785400391</t>
@@ -2012,7 +2012,7 @@
     <t xml:space="preserve">17.7571830749512</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6427440643311</t>
+    <t xml:space="preserve">17.6427459716797</t>
   </si>
   <si>
     <t xml:space="preserve">17.7381134033203</t>
@@ -2021,22 +2021,22 @@
     <t xml:space="preserve">17.4901580810547</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4710845947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.337574005127</t>
+    <t xml:space="preserve">17.4710865020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3375720977783</t>
   </si>
   <si>
     <t xml:space="preserve">17.2994251251221</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3566474914551</t>
+    <t xml:space="preserve">17.3566455841064</t>
   </si>
   <si>
     <t xml:space="preserve">17.2422065734863</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1468391418457</t>
+    <t xml:space="preserve">17.1468410491943</t>
   </si>
   <si>
     <t xml:space="preserve">17.0133266448975</t>
@@ -2051,13 +2051,13 @@
     <t xml:space="preserve">17.6999645233154</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8716259002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8525505065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0242080688477</t>
+    <t xml:space="preserve">17.8716239929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8525485992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0242099761963</t>
   </si>
   <si>
     <t xml:space="preserve">18.424747467041</t>
@@ -2081,10 +2081,10 @@
     <t xml:space="preserve">18.8062114715576</t>
   </si>
   <si>
-    <t xml:space="preserve">18.520112991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5500659942627</t>
+    <t xml:space="preserve">18.5201148986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5500679016113</t>
   </si>
   <si>
     <t xml:space="preserve">19.5023880004883</t>
@@ -2099,7 +2099,7 @@
     <t xml:space="preserve">19.4547023773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3593349456787</t>
+    <t xml:space="preserve">19.3593330383301</t>
   </si>
   <si>
     <t xml:space="preserve">19.1686038970947</t>
@@ -2111,13 +2111,13 @@
     <t xml:space="preserve">18.6917743682861</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2162857055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1209182739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7680644989014</t>
+    <t xml:space="preserve">19.216287612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1209201812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.76806640625</t>
   </si>
   <si>
     <t xml:space="preserve">17.9097709655762</t>
@@ -2150,10 +2150,10 @@
     <t xml:space="preserve">19.0732364654541</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9778728485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8825054168701</t>
+    <t xml:space="preserve">18.9778709411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8825035095215</t>
   </si>
   <si>
     <t xml:space="preserve">18.9397258758545</t>
@@ -2189,16 +2189,16 @@
     <t xml:space="preserve">20.3129978179932</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4560508728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.980562210083</t>
+    <t xml:space="preserve">20.4560489654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9805603027344</t>
   </si>
   <si>
     <t xml:space="preserve">19.8361682891846</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4083633422852</t>
+    <t xml:space="preserve">20.4083652496338</t>
   </si>
   <si>
     <t xml:space="preserve">20.1222667694092</t>
@@ -2210,10 +2210,10 @@
     <t xml:space="preserve">19.2639694213867</t>
   </si>
   <si>
-    <t xml:space="preserve">19.597749710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6454334259033</t>
+    <t xml:space="preserve">19.5977516174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.645435333252</t>
   </si>
   <si>
     <t xml:space="preserve">20.1699466705322</t>
@@ -2225,7 +2225,7 @@
     <t xml:space="preserve">19.7408008575439</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8443603515625</t>
+    <t xml:space="preserve">18.8443584442139</t>
   </si>
   <si>
     <t xml:space="preserve">19.0160179138184</t>
@@ -2234,7 +2234,7 @@
     <t xml:space="preserve">18.0432815551758</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0051345825195</t>
+    <t xml:space="preserve">18.0051364898682</t>
   </si>
   <si>
     <t xml:space="preserve">18.1386489868164</t>
@@ -2252,7 +2252,7 @@
     <t xml:space="preserve">17.2612800598145</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0514736175537</t>
+    <t xml:space="preserve">17.0514755249023</t>
   </si>
   <si>
     <t xml:space="preserve">16.2885456085205</t>
@@ -2267,7 +2267,7 @@
     <t xml:space="preserve">16.4792766571045</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8225955963135</t>
+    <t xml:space="preserve">16.8225936889648</t>
   </si>
   <si>
     <t xml:space="preserve">17.0705471038818</t>
@@ -2276,16 +2276,16 @@
     <t xml:space="preserve">16.6509342193604</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8607444763184</t>
+    <t xml:space="preserve">16.8607425689697</t>
   </si>
   <si>
     <t xml:space="preserve">16.3076190948486</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5937175750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6318626403809</t>
+    <t xml:space="preserve">16.5937156677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6318645477295</t>
   </si>
   <si>
     <t xml:space="preserve">15.277663230896</t>
@@ -2294,10 +2294,10 @@
     <t xml:space="preserve">14.8771257400513</t>
   </si>
   <si>
-    <t xml:space="preserve">14.495659828186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3730306625366</t>
+    <t xml:space="preserve">14.4956607818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3730297088623</t>
   </si>
   <si>
     <t xml:space="preserve">14.9915647506714</t>
@@ -2315,7 +2315,7 @@
     <t xml:space="preserve">15.9452257156372</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0787410736084</t>
+    <t xml:space="preserve">16.0787391662598</t>
   </si>
   <si>
     <t xml:space="preserve">16.0405921936035</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">16.5746421813965</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6890830993652</t>
+    <t xml:space="preserve">16.6890811920166</t>
   </si>
   <si>
     <t xml:space="preserve">16.5174217224121</t>
@@ -2336,16 +2336,16 @@
     <t xml:space="preserve">15.7354202270508</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8880052566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5065402984619</t>
+    <t xml:space="preserve">15.8880071640015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5065412521362</t>
   </si>
   <si>
     <t xml:space="preserve">14.9724912643433</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3348827362061</t>
+    <t xml:space="preserve">15.3348836898804</t>
   </si>
   <si>
     <t xml:space="preserve">15.2204437255859</t>
@@ -69039,7 +69039,7 @@
     </row>
     <row r="2496">
       <c r="A2496" s="1" t="n">
-        <v>45953.6495949074</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2496" t="n">
         <v>33374</v>
@@ -69060,6 +69060,32 @@
         <v>1260</v>
       </c>
       <c r="H2496" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>45954.6495023148</v>
+      </c>
+      <c r="B2497" t="n">
+        <v>26678</v>
+      </c>
+      <c r="C2497" t="n">
+        <v>52.5999984741211</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>51.2999992370605</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>52.5999984741211</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>52.2000007629395</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>1260</v>
+      </c>
+      <c r="H2497" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SOL.MI.xlsx
+++ b/data/SOL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="1275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1276" uniqueCount="1276">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,55 +38,55 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14939165115356</t>
+    <t xml:space="preserve">7.14939212799072</t>
   </si>
   <si>
     <t xml:space="preserve">SOL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14067268371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18862581253052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1624698638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06220436096191</t>
+    <t xml:space="preserve">7.14067220687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18862533569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16246938705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06220483779907</t>
   </si>
   <si>
     <t xml:space="preserve">6.90962553024292</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90526628494263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94885873794556</t>
+    <t xml:space="preserve">6.90526580810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94885969161987</t>
   </si>
   <si>
     <t xml:space="preserve">6.71781206130981</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62626552581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71345233917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29931116104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36470222473145</t>
+    <t xml:space="preserve">6.62626457214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71345281600952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2993106842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3647027015686</t>
   </si>
   <si>
     <t xml:space="preserve">6.43009281158447</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41265535354614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44753074645996</t>
+    <t xml:space="preserve">6.41265487670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44752979278564</t>
   </si>
   <si>
     <t xml:space="preserve">6.207763671875</t>
@@ -95,10 +95,10 @@
     <t xml:space="preserve">6.1728892326355</t>
   </si>
   <si>
-    <t xml:space="preserve">6.460608959198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54779577255249</t>
+    <t xml:space="preserve">6.46060800552368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54779672622681</t>
   </si>
   <si>
     <t xml:space="preserve">6.38213968276978</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">6.80064058303833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72217130661011</t>
+    <t xml:space="preserve">6.72217178344727</t>
   </si>
   <si>
     <t xml:space="preserve">6.79192161560059</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">6.84423494338989</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07964134216309</t>
+    <t xml:space="preserve">7.07964086532593</t>
   </si>
   <si>
     <t xml:space="preserve">6.88346862792969</t>
@@ -137,28 +137,28 @@
     <t xml:space="preserve">6.96629667282104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08835935592651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73524856567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8311562538147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67857789993286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57395267486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63062477111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68729686737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78320360183716</t>
+    <t xml:space="preserve">7.08836078643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73524951934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83115673065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6785774230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57395219802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63062429428101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68729591369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.783203125</t>
   </si>
   <si>
     <t xml:space="preserve">6.77884387969971</t>
@@ -167,34 +167,34 @@
     <t xml:space="preserve">6.81371879577637</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80935907363892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79628086090088</t>
+    <t xml:space="preserve">6.80935859680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79628133773804</t>
   </si>
   <si>
     <t xml:space="preserve">6.69601535797119</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81807899475098</t>
+    <t xml:space="preserve">6.81807804107666</t>
   </si>
   <si>
     <t xml:space="preserve">6.87475061416626</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91398429870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67421865463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55215454101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46496868133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43881177902222</t>
+    <t xml:space="preserve">6.9139838218689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67421817779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5521559715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46496772766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43881225585938</t>
   </si>
   <si>
     <t xml:space="preserve">6.73088979721069</t>
@@ -203,16 +203,16 @@
     <t xml:space="preserve">6.87910890579224</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85295343399048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84859323501587</t>
+    <t xml:space="preserve">6.85295295715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84859371185303</t>
   </si>
   <si>
     <t xml:space="preserve">6.85731267929077</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74832773208618</t>
+    <t xml:space="preserve">6.74832820892334</t>
   </si>
   <si>
     <t xml:space="preserve">6.51728010177612</t>
@@ -221,16 +221,16 @@
     <t xml:space="preserve">6.37342071533203</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56523323059082</t>
+    <t xml:space="preserve">6.56523370742798</t>
   </si>
   <si>
     <t xml:space="preserve">6.66985940933228</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7701244354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86167144775391</t>
+    <t xml:space="preserve">6.77012538909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86167192459106</t>
   </si>
   <si>
     <t xml:space="preserve">6.97501611709595</t>
@@ -245,13 +245,13 @@
     <t xml:space="preserve">6.88407850265503</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9017858505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34006500244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22496175765991</t>
+    <t xml:space="preserve">6.90178632736206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34006547927856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22496128082275</t>
   </si>
   <si>
     <t xml:space="preserve">7.41975164413452</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">7.26037788391113</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46845054626465</t>
+    <t xml:space="preserve">7.46845006942749</t>
   </si>
   <si>
     <t xml:space="preserve">7.40204381942749</t>
@@ -275,106 +275,106 @@
     <t xml:space="preserve">7.44631433486938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38433504104614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0434513092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9726185798645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10985851287842</t>
+    <t xml:space="preserve">7.38433456420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04345273971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97261905670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1098575592041</t>
   </si>
   <si>
     <t xml:space="preserve">6.87079620361328</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20725345611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37105369567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57027244567871</t>
+    <t xml:space="preserve">7.20725393295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37105417251587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57027149200439</t>
   </si>
   <si>
     <t xml:space="preserve">7.6942286491394</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70308351516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71193933486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65881299972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04396629333496</t>
+    <t xml:space="preserve">7.70308446884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71193885803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6588134765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04396724700928</t>
   </si>
   <si>
     <t xml:space="preserve">7.61454343795776</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29579496383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99475526809692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10100412368774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55256414413452</t>
+    <t xml:space="preserve">7.29579448699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99475479125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1010046005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55256462097168</t>
   </si>
   <si>
     <t xml:space="preserve">7.3135027885437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50829219818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42418003082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37548112869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52600240707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54371023178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41532468795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21610689163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99032735824585</t>
+    <t xml:space="preserve">7.50829267501831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42417907714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37548208236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52600288391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54370927810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41532516479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21610736846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99032783508301</t>
   </si>
   <si>
     <t xml:space="preserve">6.79996347427368</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75569343566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00803565979004</t>
+    <t xml:space="preserve">6.7556939125061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0080361366272</t>
   </si>
   <si>
     <t xml:space="preserve">7.26923227310181</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34449148178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46402215957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51714849472046</t>
+    <t xml:space="preserve">7.34449291229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46402311325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51714706420898</t>
   </si>
   <si>
     <t xml:space="preserve">7.39318990707397</t>
@@ -383,7 +383,7 @@
     <t xml:space="preserve">7.45516920089722</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1718373298645</t>
+    <t xml:space="preserve">7.17183685302734</t>
   </si>
   <si>
     <t xml:space="preserve">7.33563756942749</t>
@@ -392,10 +392,10 @@
     <t xml:space="preserve">7.33121109008789</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39761686325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30464887619019</t>
+    <t xml:space="preserve">7.39761734008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30464935302734</t>
   </si>
   <si>
     <t xml:space="preserve">7.27808618545532</t>
@@ -404,7 +404,7 @@
     <t xml:space="preserve">7.25152397155762</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16298294067383</t>
+    <t xml:space="preserve">7.16298341751099</t>
   </si>
   <si>
     <t xml:space="preserve">7.03017091751099</t>
@@ -413,43 +413,43 @@
     <t xml:space="preserve">6.87965106964111</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91064023971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95491027832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88850593566895</t>
+    <t xml:space="preserve">6.91064071655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95491123199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88850450515747</t>
   </si>
   <si>
     <t xml:space="preserve">6.95933818817139</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85751533508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77340126037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74683952331543</t>
+    <t xml:space="preserve">6.85751581192017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77340173721313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74683904647827</t>
   </si>
   <si>
     <t xml:space="preserve">6.82652616500854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68485975265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81767177581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90621328353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01688957214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89735889434814</t>
+    <t xml:space="preserve">6.68486022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81767225265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90621280670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01689004898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8973593711853</t>
   </si>
   <si>
     <t xml:space="preserve">6.83538007736206</t>
@@ -458,7 +458,7 @@
     <t xml:space="preserve">6.86194276809692</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92392206192017</t>
+    <t xml:space="preserve">6.92392110824585</t>
   </si>
   <si>
     <t xml:space="preserve">6.97704648971558</t>
@@ -467,13 +467,13 @@
     <t xml:space="preserve">7.00360822677612</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91506719589233</t>
+    <t xml:space="preserve">6.91506767272949</t>
   </si>
   <si>
     <t xml:space="preserve">6.91949462890625</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93720245361328</t>
+    <t xml:space="preserve">6.93720293045044</t>
   </si>
   <si>
     <t xml:space="preserve">7.07001447677612</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">6.75126647949219</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77782821655273</t>
+    <t xml:space="preserve">6.77782773971558</t>
   </si>
   <si>
     <t xml:space="preserve">6.64944362640381</t>
@@ -494,25 +494,25 @@
     <t xml:space="preserve">6.38382005691528</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37053871154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36168575286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37939405441284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40595531463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48121547698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47678852081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54319429397583</t>
+    <t xml:space="preserve">6.37053966522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36168527603149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37939262390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40595626831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4812159538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47678804397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54319381713867</t>
   </si>
   <si>
     <t xml:space="preserve">6.46350765228271</t>
@@ -521,46 +521,46 @@
     <t xml:space="preserve">6.24215412139893</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25986289978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22444629669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64501714706421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64058971405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03902435302734</t>
+    <t xml:space="preserve">6.25986242294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22444581985474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64501667022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64059019088745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0390248298645</t>
   </si>
   <si>
     <t xml:space="preserve">6.79110956192017</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70256853103638</t>
+    <t xml:space="preserve">6.70256900787354</t>
   </si>
   <si>
     <t xml:space="preserve">6.70699548721313</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65829753875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58303785324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05673265457153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11428451538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34891939163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18511772155762</t>
+    <t xml:space="preserve">6.6582989692688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58303737640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05673360824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11428546905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34891891479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18511819839478</t>
   </si>
   <si>
     <t xml:space="preserve">7.12756633758545</t>
@@ -569,76 +569,76 @@
     <t xml:space="preserve">7.19397211074829</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2426700592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41089725494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48173141479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14527416229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27365922927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17626285552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04787969589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23381567001343</t>
+    <t xml:space="preserve">7.24266958236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41089868545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48173046112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14527463912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27365875244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17626333236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04787874221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23381519317627</t>
   </si>
   <si>
     <t xml:space="preserve">7.29136610031128</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42860555648804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83589553833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82704210281372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13693714141846</t>
+    <t xml:space="preserve">7.42860651016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83589458465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82704162597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13693618774414</t>
   </si>
   <si>
     <t xml:space="preserve">8.27860355377197</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32287216186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0312032699585</t>
+    <t xml:space="preserve">8.32287120819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03120231628418</t>
   </si>
   <si>
     <t xml:space="preserve">8.53094482421875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49995517730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26089477539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92495059967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58849430084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97807788848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7655782699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87182807922363</t>
+    <t xml:space="preserve">8.49995613098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26089286804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92495346069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58849620819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97807884216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76557731628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87182903289795</t>
   </si>
   <si>
     <t xml:space="preserve">9.56244850158691</t>
@@ -647,64 +647,64 @@
     <t xml:space="preserve">9.25255393981934</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02234840393066</t>
+    <t xml:space="preserve">9.02234649658203</t>
   </si>
   <si>
     <t xml:space="preserve">8.85411930084229</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82755851745605</t>
+    <t xml:space="preserve">8.82755756378174</t>
   </si>
   <si>
     <t xml:space="preserve">8.71245384216309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98693180084229</t>
+    <t xml:space="preserve">8.98693084716797</t>
   </si>
   <si>
     <t xml:space="preserve">8.8983907699585</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80984878540039</t>
+    <t xml:space="preserve">8.80984783172607</t>
   </si>
   <si>
     <t xml:space="preserve">8.72130870819092</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78328704833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67703723907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75672340393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10203552246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82312870025635</t>
+    <t xml:space="preserve">8.78328609466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67703628540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75672435760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10203456878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82312965393066</t>
   </si>
   <si>
     <t xml:space="preserve">8.94266033172607</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20828533172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43287754058838</t>
+    <t xml:space="preserve">9.20828437805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43287658691406</t>
   </si>
   <si>
     <t xml:space="preserve">9.4598274230957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52271366119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32507228851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3879566192627</t>
+    <t xml:space="preserve">9.52271461486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3250732421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38795757293701</t>
   </si>
   <si>
     <t xml:space="preserve">9.35202312469482</t>
@@ -713,19 +713,19 @@
     <t xml:space="preserve">9.4238920211792</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29812145233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55864810943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67543792724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86409187316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5199022293091</t>
+    <t xml:space="preserve">9.29812240600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55864906311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67543697357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86409282684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5199041366577</t>
   </si>
   <si>
     <t xml:space="preserve">10.0617351531982</t>
@@ -740,16 +740,16 @@
     <t xml:space="preserve">9.56763076782227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44185924530029</t>
+    <t xml:space="preserve">9.44186019897461</t>
   </si>
   <si>
     <t xml:space="preserve">9.54068088531494</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34304046630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36100769042969</t>
+    <t xml:space="preserve">9.34303951263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36100673675537</t>
   </si>
   <si>
     <t xml:space="preserve">9.50474643707275</t>
@@ -764,19 +764,19 @@
     <t xml:space="preserve">9.77425670623779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46881103515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5496654510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47779560089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70238780975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30710411071777</t>
+    <t xml:space="preserve">9.46881198883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54966449737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4777946472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7023868560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30710315704346</t>
   </si>
   <si>
     <t xml:space="preserve">9.28015422821045</t>
@@ -794,19 +794,19 @@
     <t xml:space="preserve">9.45084381103516</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58559989929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33405780792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59458160400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66645336151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71137046813965</t>
+    <t xml:space="preserve">9.58559894561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33405590057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59458351135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66645240783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71137142181396</t>
   </si>
   <si>
     <t xml:space="preserve">9.40592575073242</t>
@@ -821,43 +821,43 @@
     <t xml:space="preserve">9.28913688659668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36999034881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65746784210205</t>
+    <t xml:space="preserve">9.36999130249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65746879577637</t>
   </si>
   <si>
     <t xml:space="preserve">9.79222393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76527404785156</t>
+    <t xml:space="preserve">9.76527309417725</t>
   </si>
   <si>
     <t xml:space="preserve">9.7203540802002</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81019020080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37897300720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90901184082031</t>
+    <t xml:space="preserve">9.8101921081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37897396087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.909010887146</t>
   </si>
   <si>
     <t xml:space="preserve">9.81917572021484</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73832130432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78324127197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69340324401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11844730377197</t>
+    <t xml:space="preserve">9.73832225799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78324031829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69340419769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11844635009766</t>
   </si>
   <si>
     <t xml:space="preserve">9.08251190185547</t>
@@ -866,13 +866,13 @@
     <t xml:space="preserve">9.31608867645264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19031715393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10048007965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22625255584717</t>
+    <t xml:space="preserve">9.19031620025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10047912597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22625160217285</t>
   </si>
   <si>
     <t xml:space="preserve">9.41490936279297</t>
@@ -881,31 +881,31 @@
     <t xml:space="preserve">9.39694213867188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07353115081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57661628723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68441963195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09149742126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05556106567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14539813995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89385509490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10946273803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23523426055908</t>
+    <t xml:space="preserve">9.07353019714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57661533355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68442058563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09149646759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05556201934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14539909362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89385414123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10946369171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2352352142334</t>
   </si>
   <si>
     <t xml:space="preserve">9.95393085479736</t>
@@ -917,25 +917,25 @@
     <t xml:space="preserve">10.7444953918457</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5468549728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6905927658081</t>
+    <t xml:space="preserve">10.546854019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6905937194824</t>
   </si>
   <si>
     <t xml:space="preserve">10.9062023162842</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7804307937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7085599899292</t>
+    <t xml:space="preserve">10.7804317474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7085609436035</t>
   </si>
   <si>
     <t xml:space="preserve">10.6546583175659</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5288877487183</t>
+    <t xml:space="preserve">10.5288858413696</t>
   </si>
   <si>
     <t xml:space="preserve">10.4390497207642</t>
@@ -944,28 +944,28 @@
     <t xml:space="preserve">10.3312463760376</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1695394515991</t>
+    <t xml:space="preserve">10.1695384979248</t>
   </si>
   <si>
     <t xml:space="preserve">10.1875076293945</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1336040496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7562894821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63051795959473</t>
+    <t xml:space="preserve">10.1336030960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75628852844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63051700592041</t>
   </si>
   <si>
     <t xml:space="preserve">10.007833480835</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84612655639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0976705551147</t>
+    <t xml:space="preserve">9.84612560272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0976696014404</t>
   </si>
   <si>
     <t xml:space="preserve">10.2054738998413</t>
@@ -974,34 +974,34 @@
     <t xml:space="preserve">10.2773427963257</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2234411239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2414073944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7624626159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2593765258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91799640655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90002918243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67380619049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74667739868164</t>
+    <t xml:space="preserve">10.2234420776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2414083480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7624616622925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2593755722046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91799736022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90002822875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67380714416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74667930603027</t>
   </si>
   <si>
     <t xml:space="preserve">9.87420558929443</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1656932830811</t>
+    <t xml:space="preserve">10.1656951904297</t>
   </si>
   <si>
     <t xml:space="preserve">9.85598754882812</t>
@@ -1010,25 +1010,25 @@
     <t xml:space="preserve">9.63737010955811</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47340679168701</t>
+    <t xml:space="preserve">9.47340774536133</t>
   </si>
   <si>
     <t xml:space="preserve">9.76489734649658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96529674530029</t>
+    <t xml:space="preserve">9.96529579162598</t>
   </si>
   <si>
     <t xml:space="preserve">10.0746049880981</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2385673522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3843116760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4207496643066</t>
+    <t xml:space="preserve">10.2385654449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3843107223511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.420747756958</t>
   </si>
   <si>
     <t xml:space="preserve">10.8033285140991</t>
@@ -1043,31 +1043,31 @@
     <t xml:space="preserve">10.7851104736328</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5482740402222</t>
+    <t xml:space="preserve">10.5482749938965</t>
   </si>
   <si>
     <t xml:space="preserve">10.4025316238403</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2203502655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1474761962891</t>
+    <t xml:space="preserve">10.2203493118286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1474771499634</t>
   </si>
   <si>
     <t xml:space="preserve">10.3296585083008</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5847091674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3478765487671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72846031188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56449890136719</t>
+    <t xml:space="preserve">10.5847110748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3478746414185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7284631729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56449794769287</t>
   </si>
   <si>
     <t xml:space="preserve">9.4187536239624</t>
@@ -1088,19 +1088,19 @@
     <t xml:space="preserve">9.92885971069336</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0199508666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2021312713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0928230285645</t>
+    <t xml:space="preserve">10.0199499130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.202130317688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0928220748901</t>
   </si>
   <si>
     <t xml:space="preserve">9.8013334274292</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69202518463135</t>
+    <t xml:space="preserve">9.69202613830566</t>
   </si>
   <si>
     <t xml:space="preserve">9.83776950836182</t>
@@ -1109,10 +1109,10 @@
     <t xml:space="preserve">9.94707775115967</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89242458343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65558815002441</t>
+    <t xml:space="preserve">9.89242267608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65559005737305</t>
   </si>
   <si>
     <t xml:space="preserve">9.78311443328857</t>
@@ -1121,31 +1121,31 @@
     <t xml:space="preserve">9.91064167022705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45519065856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2001371383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50984287261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43697166442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81955242156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49162673950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6191520690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98351383209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6009349822998</t>
+    <t xml:space="preserve">9.45518970489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20013618469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50984382629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43697071075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81955146789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49162578582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61915397644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98351287841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60093402862549</t>
   </si>
   <si>
     <t xml:space="preserve">9.10904502868652</t>
@@ -1154,67 +1154,67 @@
     <t xml:space="preserve">9.09993648529053</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38231658935547</t>
+    <t xml:space="preserve">9.38231754302979</t>
   </si>
   <si>
     <t xml:space="preserve">9.36409854888916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27300834655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71024227142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58271598815918</t>
+    <t xml:space="preserve">9.27301025390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71024322509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5827169418335</t>
   </si>
   <si>
     <t xml:space="preserve">9.29122734069824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14548206329346</t>
+    <t xml:space="preserve">9.14548110961914</t>
   </si>
   <si>
     <t xml:space="preserve">10.3660945892334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32766246795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0017328262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4754018783569</t>
+    <t xml:space="preserve">9.32766342163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0017309188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4754028320312</t>
   </si>
   <si>
     <t xml:space="preserve">10.8397636413574</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5664930343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3114404678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2932233810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0381689071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0563850402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1292581558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2750034332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1839122772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6758012771606</t>
+    <t xml:space="preserve">10.5664949417114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3114385604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2932214736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0381679534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0563859939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1292591094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2750024795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.183913230896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.675802230835</t>
   </si>
   <si>
     <t xml:space="preserve">10.7122383117676</t>
@@ -1223,7 +1223,7 @@
     <t xml:space="preserve">10.9308557510376</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0219469070435</t>
+    <t xml:space="preserve">11.0219459533691</t>
   </si>
   <si>
     <t xml:space="preserve">10.87619972229</t>
@@ -1232,22 +1232,22 @@
     <t xml:space="preserve">10.8944187164307</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7304553985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6575832366943</t>
+    <t xml:space="preserve">10.7304563522339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6575841903687</t>
   </si>
   <si>
     <t xml:space="preserve">11.2644634246826</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1349859237671</t>
+    <t xml:space="preserve">11.1349878311157</t>
   </si>
   <si>
     <t xml:space="preserve">11.097993850708</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2459659576416</t>
+    <t xml:space="preserve">11.2459669113159</t>
   </si>
   <si>
     <t xml:space="preserve">11.3199529647827</t>
@@ -1259,25 +1259,25 @@
     <t xml:space="preserve">10.8205432891846</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8390398025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7280607223511</t>
+    <t xml:space="preserve">10.839038848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7280616760254</t>
   </si>
   <si>
     <t xml:space="preserve">10.8575372695923</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7095632553101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6725702285767</t>
+    <t xml:space="preserve">10.7095642089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6725692749023</t>
   </si>
   <si>
     <t xml:space="preserve">10.6540746688843</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7835512161255</t>
+    <t xml:space="preserve">10.7835502624512</t>
   </si>
   <si>
     <t xml:space="preserve">10.7650547027588</t>
@@ -1286,16 +1286,16 @@
     <t xml:space="preserve">10.8020467758179</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5615911483765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6170806884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3951206207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1176710128784</t>
+    <t xml:space="preserve">10.5615901947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6170797348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3951187133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1176700592041</t>
   </si>
   <si>
     <t xml:space="preserve">10.284140586853</t>
@@ -1304,37 +1304,37 @@
     <t xml:space="preserve">10.2656440734863</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3026371002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5061006546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3396301269531</t>
+    <t xml:space="preserve">10.3026390075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5060997009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3396310806274</t>
   </si>
   <si>
     <t xml:space="preserve">10.1361665725708</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0806770324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98819446563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0991735458374</t>
+    <t xml:space="preserve">10.080677986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98819351196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0991744995117</t>
   </si>
   <si>
     <t xml:space="preserve">9.93270301818848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89570999145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96969795227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1731615066528</t>
+    <t xml:space="preserve">9.89571094512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96969699859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1731605529785</t>
   </si>
   <si>
     <t xml:space="preserve">10.062180519104</t>
@@ -1343,31 +1343,31 @@
     <t xml:space="preserve">10.1546640396118</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71074485778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0251874923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91420841217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76623439788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72924041748047</t>
+    <t xml:space="preserve">9.71074390411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0251884460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91420745849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7662353515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72924137115479</t>
   </si>
   <si>
     <t xml:space="preserve">9.65525341033936</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67375087738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47028732299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54427433013916</t>
+    <t xml:space="preserve">9.67375183105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47028827667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54427337646484</t>
   </si>
   <si>
     <t xml:space="preserve">9.56277084350586</t>
@@ -1376,10 +1376,10 @@
     <t xml:space="preserve">9.45179080963135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35930728912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52577686309814</t>
+    <t xml:space="preserve">9.35930919647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52577781677246</t>
   </si>
   <si>
     <t xml:space="preserve">9.59976482391357</t>
@@ -1406,31 +1406,31 @@
     <t xml:space="preserve">10.0066900253296</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8772144317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74773788452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58126831054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3211336135864</t>
+    <t xml:space="preserve">9.87721633911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7477388381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58126640319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3211345672607</t>
   </si>
   <si>
     <t xml:space="preserve">10.4321136474609</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3766250610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2471485137939</t>
+    <t xml:space="preserve">10.3766241073608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2471475601196</t>
   </si>
   <si>
     <t xml:space="preserve">10.2101535797119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84022235870361</t>
+    <t xml:space="preserve">9.8402214050293</t>
   </si>
   <si>
     <t xml:space="preserve">9.63675880432129</t>
@@ -1439,7 +1439,7 @@
     <t xml:space="preserve">9.43329524993896</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41479778289795</t>
+    <t xml:space="preserve">9.41479873657227</t>
   </si>
   <si>
     <t xml:space="preserve">9.39630126953125</t>
@@ -1448,34 +1448,34 @@
     <t xml:space="preserve">9.24832820892334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06336212158203</t>
+    <t xml:space="preserve">9.06336116790771</t>
   </si>
   <si>
     <t xml:space="preserve">9.10960388183594</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32231330871582</t>
+    <t xml:space="preserve">9.32231521606445</t>
   </si>
   <si>
     <t xml:space="preserve">9.28532123565674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26682567596436</t>
+    <t xml:space="preserve">9.26682472229004</t>
   </si>
   <si>
     <t xml:space="preserve">9.19283771514893</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22983169555664</t>
+    <t xml:space="preserve">9.22983074188232</t>
   </si>
   <si>
     <t xml:space="preserve">9.48878479003906</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02636909484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97087860107422</t>
+    <t xml:space="preserve">9.02636814117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9708776473999</t>
   </si>
   <si>
     <t xml:space="preserve">9.13734817504883</t>
@@ -1487,13 +1487,13 @@
     <t xml:space="preserve">8.82290458679199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61944198608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55470275878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36048889160156</t>
+    <t xml:space="preserve">8.61944103240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55470371246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36048793792725</t>
   </si>
   <si>
     <t xml:space="preserve">8.33274364471436</t>
@@ -1502,31 +1502,31 @@
     <t xml:space="preserve">8.01830005645752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8148365020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95356225967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49114608764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86107778549194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50964260101318</t>
+    <t xml:space="preserve">7.81483745574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95356273651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49114513397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86107873916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50964212417603</t>
   </si>
   <si>
     <t xml:space="preserve">7.53738641738892</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58362913131714</t>
+    <t xml:space="preserve">7.5836296081543</t>
   </si>
   <si>
     <t xml:space="preserve">8.76741504669189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98937511444092</t>
+    <t xml:space="preserve">8.9893741607666</t>
   </si>
   <si>
     <t xml:space="preserve">9.16509246826172</t>
@@ -1535,10 +1535,10 @@
     <t xml:space="preserve">9.12809944152832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09110546112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08185768127441</t>
+    <t xml:space="preserve">9.09110641479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08185863494873</t>
   </si>
   <si>
     <t xml:space="preserve">9.34081172943115</t>
@@ -1547,49 +1547,49 @@
     <t xml:space="preserve">9.04486465454102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21133422851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38705158233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17434215545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29456901550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1188497543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78591060638428</t>
+    <t xml:space="preserve">9.21133518218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38705253601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17434120178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29456996917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11885070800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78591156005859</t>
   </si>
   <si>
     <t xml:space="preserve">8.89689159393311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74891757965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80440807342529</t>
+    <t xml:space="preserve">8.7489185333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80440902709961</t>
   </si>
   <si>
     <t xml:space="preserve">8.87839508056641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9338846206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63793849945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71192359924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58244800567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69342803955078</t>
+    <t xml:space="preserve">8.93388557434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63793754577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71192455291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58244705200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69342708587646</t>
   </si>
   <si>
     <t xml:space="preserve">9.46113872528076</t>
@@ -1604,19 +1604,19 @@
     <t xml:space="preserve">9.74356174468994</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97891330718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93184375762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79063034057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0730533599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3084049224854</t>
+    <t xml:space="preserve">9.97891235351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93184185028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79063129425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0730543136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3084058761597</t>
   </si>
   <si>
     <t xml:space="preserve">10.4496164321899</t>
@@ -1625,10 +1625,10 @@
     <t xml:space="preserve">10.1671943664551</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1201248168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0259838104248</t>
+    <t xml:space="preserve">10.1201238632202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0259828567505</t>
   </si>
   <si>
     <t xml:space="preserve">10.2142658233643</t>
@@ -1643,28 +1643,28 @@
     <t xml:space="preserve">9.88477230072021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5908269882202</t>
+    <t xml:space="preserve">10.5908279418945</t>
   </si>
   <si>
     <t xml:space="preserve">10.4966859817505</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5437574386597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2027416229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1556711196899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9673900604248</t>
+    <t xml:space="preserve">10.543758392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2027406692505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1556720733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9673891067505</t>
   </si>
   <si>
     <t xml:space="preserve">11.0615310668945</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7791080474854</t>
+    <t xml:space="preserve">10.7791090011597</t>
   </si>
   <si>
     <t xml:space="preserve">10.8261785507202</t>
@@ -1676,40 +1676,40 @@
     <t xml:space="preserve">11.1086015701294</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9203205108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8732490539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7320375442505</t>
+    <t xml:space="preserve">10.9203195571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8732481002808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7320384979248</t>
   </si>
   <si>
     <t xml:space="preserve">10.6378984451294</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5322332382202</t>
+    <t xml:space="preserve">11.5322351455688</t>
   </si>
   <si>
     <t xml:space="preserve">11.6263751983643</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7675848007202</t>
+    <t xml:space="preserve">11.7675857543945</t>
   </si>
   <si>
     <t xml:space="preserve">11.8146562576294</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5793046951294</t>
+    <t xml:space="preserve">11.5793056488037</t>
   </si>
   <si>
     <t xml:space="preserve">11.6734447479248</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7205152511597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0029382705688</t>
+    <t xml:space="preserve">11.720516204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0029392242432</t>
   </si>
   <si>
     <t xml:space="preserve">12.2853593826294</t>
@@ -1718,7 +1718,7 @@
     <t xml:space="preserve">12.5677824020386</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5207118988037</t>
+    <t xml:space="preserve">12.5207109451294</t>
   </si>
   <si>
     <t xml:space="preserve">12.8972730636597</t>
@@ -1733,73 +1733,73 @@
     <t xml:space="preserve">12.6148519515991</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8031330108643</t>
+    <t xml:space="preserve">12.8031339645386</t>
   </si>
   <si>
     <t xml:space="preserve">12.8502035140991</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9914140701294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1796951293945</t>
+    <t xml:space="preserve">12.9914150238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1796970367432</t>
   </si>
   <si>
     <t xml:space="preserve">13.462119102478</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8386812210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7445411682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6504001617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5091896057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7916116714478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8857517242432</t>
+    <t xml:space="preserve">13.8386793136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7445402145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6504011154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5091905593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7916097640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8857507705688</t>
   </si>
   <si>
     <t xml:space="preserve">13.9798927307129</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0269613265991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.074031829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.168173789978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1211032867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2623119354248</t>
+    <t xml:space="preserve">14.0269622802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0740327835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1681728363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1211023330688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2623128890991</t>
   </si>
   <si>
     <t xml:space="preserve">14.2152442932129</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4505958557129</t>
+    <t xml:space="preserve">14.4505968093872</t>
   </si>
   <si>
     <t xml:space="preserve">14.6859483718872</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3093843460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.403525352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3564538955688</t>
+    <t xml:space="preserve">14.309383392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4035243988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3564548492432</t>
   </si>
   <si>
     <t xml:space="preserve">14.5447359085083</t>
@@ -1817,7 +1817,7 @@
     <t xml:space="preserve">14.8271589279175</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8742294311523</t>
+    <t xml:space="preserve">14.874228477478</t>
   </si>
   <si>
     <t xml:space="preserve">14.7330169677734</t>
@@ -1826,7 +1826,7 @@
     <t xml:space="preserve">15.3449306488037</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7685623168945</t>
+    <t xml:space="preserve">15.7685661315918</t>
   </si>
   <si>
     <t xml:space="preserve">16.0039157867432</t>
@@ -1835,7 +1835,7 @@
     <t xml:space="preserve">16.0415744781494</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0792274475098</t>
+    <t xml:space="preserve">16.0792293548584</t>
   </si>
   <si>
     <t xml:space="preserve">16.1921997070312</t>
@@ -1844,76 +1844,76 @@
     <t xml:space="preserve">16.1168880462646</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2298526763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3804798126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3993053436279</t>
+    <t xml:space="preserve">16.2298545837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3804817199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3993091583252</t>
   </si>
   <si>
     <t xml:space="preserve">16.4181365966797</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5311050415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2675113677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9286050796509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8909492492676</t>
+    <t xml:space="preserve">16.5311031341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2675132751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9286041259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8909473419189</t>
   </si>
   <si>
     <t xml:space="preserve">15.8156337738037</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9662609100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7214956283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5332145690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.514386177063</t>
+    <t xml:space="preserve">15.9662618637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7214965820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5332126617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.51438331604</t>
   </si>
   <si>
     <t xml:space="preserve">15.7026681900024</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2696180343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4767303466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6838388442993</t>
+    <t xml:space="preserve">15.2696199417114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4767284393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.683837890625</t>
   </si>
   <si>
     <t xml:space="preserve">15.6650094985962</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4202432632446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1566514968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2319641113281</t>
+    <t xml:space="preserve">15.4202442169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1566505432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2319631576538</t>
   </si>
   <si>
     <t xml:space="preserve">15.7779788970947</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9833726882935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.964301109314</t>
+    <t xml:space="preserve">15.9833717346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9642992019653</t>
   </si>
   <si>
     <t xml:space="preserve">15.6209812164307</t>
@@ -1928,16 +1928,16 @@
     <t xml:space="preserve">15.8117141723633</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6019096374512</t>
+    <t xml:space="preserve">15.6019077301025</t>
   </si>
   <si>
     <t xml:space="preserve">15.5446872711182</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2585906982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6972723007202</t>
+    <t xml:space="preserve">15.2585897445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6972732543945</t>
   </si>
   <si>
     <t xml:space="preserve">15.8307867050171</t>
@@ -1949,22 +1949,22 @@
     <t xml:space="preserve">16.2503986358643</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2313270568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0024471282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2694721221924</t>
+    <t xml:space="preserve">16.2313251495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0024452209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2694683074951</t>
   </si>
   <si>
     <t xml:space="preserve">16.212251663208</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4602069854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4411315917969</t>
+    <t xml:space="preserve">16.460205078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4411296844482</t>
   </si>
   <si>
     <t xml:space="preserve">16.5364952087402</t>
@@ -1973,10 +1973,10 @@
     <t xml:space="preserve">16.555570602417</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1659126281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9561080932617</t>
+    <t xml:space="preserve">17.1659145355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9561100006104</t>
   </si>
   <si>
     <t xml:space="preserve">17.2231330871582</t>
@@ -1985,16 +1985,16 @@
     <t xml:space="preserve">17.3185005187988</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0896224975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8416690826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7463035583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9751815795898</t>
+    <t xml:space="preserve">17.08962059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.841667175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.746301651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9751796722412</t>
   </si>
   <si>
     <t xml:space="preserve">17.1277656555176</t>
@@ -2003,28 +2003,28 @@
     <t xml:space="preserve">17.5092334747314</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5473804473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7571830749512</t>
+    <t xml:space="preserve">17.5473785400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7571849822998</t>
   </si>
   <si>
     <t xml:space="preserve">17.6427440643311</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7381134033203</t>
+    <t xml:space="preserve">17.7381114959717</t>
   </si>
   <si>
     <t xml:space="preserve">17.4901580810547</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4710845947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.337574005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2994251251221</t>
+    <t xml:space="preserve">17.4710865020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3375720977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2994270324707</t>
   </si>
   <si>
     <t xml:space="preserve">17.3566474914551</t>
@@ -2033,22 +2033,22 @@
     <t xml:space="preserve">17.2422065734863</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1468391418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0133266448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4520130157471</t>
+    <t xml:space="preserve">17.1468372344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0133285522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4520111083984</t>
   </si>
   <si>
     <t xml:space="preserve">17.8334789276123</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6999645233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8716220855713</t>
+    <t xml:space="preserve">17.6999626159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8716259002686</t>
   </si>
   <si>
     <t xml:space="preserve">17.8525505065918</t>
@@ -2057,13 +2057,13 @@
     <t xml:space="preserve">18.0242099761963</t>
   </si>
   <si>
-    <t xml:space="preserve">18.424747467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5010395050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6536273956299</t>
+    <t xml:space="preserve">18.4247493743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5010414123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6536235809326</t>
   </si>
   <si>
     <t xml:space="preserve">18.5964069366455</t>
@@ -2078,7 +2078,7 @@
     <t xml:space="preserve">18.8062114715576</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5201148986816</t>
+    <t xml:space="preserve">18.520112991333</t>
   </si>
   <si>
     <t xml:space="preserve">19.5500679016113</t>
@@ -2087,10 +2087,10 @@
     <t xml:space="preserve">19.5023880004883</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8838520050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9792175292969</t>
+    <t xml:space="preserve">19.8838500976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9792156219482</t>
   </si>
   <si>
     <t xml:space="preserve">19.4547023773193</t>
@@ -2099,19 +2099,19 @@
     <t xml:space="preserve">19.3593349456787</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1686058044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7871417999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6917743682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2162857055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1209201812744</t>
+    <t xml:space="preserve">19.1686038970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7871398925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6917724609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.216287612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1209182739258</t>
   </si>
   <si>
     <t xml:space="preserve">18.76806640625</t>
@@ -2129,7 +2129,7 @@
     <t xml:space="preserve">17.890697479248</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1005001068115</t>
+    <t xml:space="preserve">18.1005020141602</t>
   </si>
   <si>
     <t xml:space="preserve">18.2530860900879</t>
@@ -2138,10 +2138,10 @@
     <t xml:space="preserve">17.9669895172119</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1767959594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9969444274902</t>
+    <t xml:space="preserve">18.176794052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9969463348389</t>
   </si>
   <si>
     <t xml:space="preserve">19.0732383728027</t>
@@ -2165,19 +2165,19 @@
     <t xml:space="preserve">20.2176322937012</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2653160095215</t>
+    <t xml:space="preserve">20.2653141021729</t>
   </si>
   <si>
     <t xml:space="preserve">20.7421474456787</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9328804016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2189788818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4573936462402</t>
+    <t xml:space="preserve">20.9328784942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2189750671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4573917388916</t>
   </si>
   <si>
     <t xml:space="preserve">20.6944637298584</t>
@@ -2192,16 +2192,16 @@
     <t xml:space="preserve">20.980562210083</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8361682891846</t>
+    <t xml:space="preserve">19.8361663818359</t>
   </si>
   <si>
     <t xml:space="preserve">20.4083652496338</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1222686767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3116550445557</t>
+    <t xml:space="preserve">20.1222648620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3116512298584</t>
   </si>
   <si>
     <t xml:space="preserve">19.2639713287354</t>
@@ -2210,70 +2210,70 @@
     <t xml:space="preserve">19.5977516174316</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6454372406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1699485778809</t>
+    <t xml:space="preserve">19.6454334259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1699504852295</t>
   </si>
   <si>
     <t xml:space="preserve">19.9315338134766</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7408008575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8443603515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.016019821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0432834625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0051345825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1386489868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0623569488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.081428527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6045970916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2612819671631</t>
+    <t xml:space="preserve">19.7408027648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8443584442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0160179138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0432815551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0051364898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.138650894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0623550415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0814266204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6045989990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2612800598145</t>
   </si>
   <si>
     <t xml:space="preserve">17.0514736175537</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2885456085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0324020385742</t>
+    <t xml:space="preserve">16.2885437011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0324039459229</t>
   </si>
   <si>
     <t xml:space="preserve">16.7272300720215</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4792766571045</t>
+    <t xml:space="preserve">16.4792785644531</t>
   </si>
   <si>
     <t xml:space="preserve">16.8225936889648</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0705490112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6509342193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8607425689697</t>
+    <t xml:space="preserve">17.0705471038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.650936126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8607406616211</t>
   </si>
   <si>
     <t xml:space="preserve">16.3076171875</t>
@@ -2282,22 +2282,22 @@
     <t xml:space="preserve">16.5937175750732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6318626403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2776641845703</t>
+    <t xml:space="preserve">16.6318645477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.277663230896</t>
   </si>
   <si>
     <t xml:space="preserve">14.8771257400513</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4956607818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3730316162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9915647506714</t>
+    <t xml:space="preserve">14.495659828186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3730306625366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9915637969971</t>
   </si>
   <si>
     <t xml:space="preserve">15.0869312286377</t>
@@ -2306,7 +2306,7 @@
     <t xml:space="preserve">15.6782007217407</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1441507339478</t>
+    <t xml:space="preserve">15.1441497802734</t>
   </si>
   <si>
     <t xml:space="preserve">15.9452247619629</t>
@@ -2315,13 +2315,13 @@
     <t xml:space="preserve">16.0787410736084</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0405921936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5746440887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6890850067139</t>
+    <t xml:space="preserve">16.0405941009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5746402740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6890830993652</t>
   </si>
   <si>
     <t xml:space="preserve">16.5174236297607</t>
@@ -2330,172 +2330,172 @@
     <t xml:space="preserve">16.4983501434326</t>
   </si>
   <si>
+    <t xml:space="preserve">15.7354202270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8880062103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5065431594849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9724903106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3348836898804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2204437255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9152727127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.781759262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8961992263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6400566101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0978126525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2395162582397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1060037612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0063896179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1999359130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.354772567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0450973510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1418704986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2773551940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4709014892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7805767059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1483173370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.767671585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4192848205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2321834564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7289619445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9418640136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4967041015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5934772491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4579963684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8967056274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4515476226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9870328903198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8321943283081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9483213424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3676795959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4450988769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1741333007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1160688400269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1354236602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3289709091187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6192922592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8902587890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7547760009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8128395080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.161226272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6580018997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8709049224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4128379821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4321918487549</t>
+  </si>
+  <si>
     <t xml:space="preserve">15.7354211807251</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8880052566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5065412521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9724912643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3348827362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2204427719116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9152717590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.781759262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8961992263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6400547027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0978126525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2395153045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1060047149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0063877105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1999359130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3547744750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0450973510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1418704986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2773532867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4709033966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7805767059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1483173370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.767671585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.419282913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2321853637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7289600372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9418659210205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4967041015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5934791564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4579963684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8967037200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4515476226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9870338439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8321962356567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9483232498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3676805496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4450988769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1741333007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1160688400269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.135422706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3289709091187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.619291305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8902597427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7547750473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8128395080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.161226272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6580018997192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.870903968811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4128360748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4321899414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7354202270508</t>
-  </si>
-  <si>
     <t xml:space="preserve">15.7160663604736</t>
   </si>
   <si>
     <t xml:space="preserve">16.0644512176514</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5289669036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6838054656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5096111297607</t>
+    <t xml:space="preserve">16.5289649963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6838035583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5096092224121</t>
   </si>
   <si>
     <t xml:space="preserve">16.9160594940186</t>
@@ -2507,7 +2507,7 @@
     <t xml:space="preserve">17.3805732727051</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3418674468994</t>
+    <t xml:space="preserve">17.3418655395508</t>
   </si>
   <si>
     <t xml:space="preserve">17.2063827514648</t>
@@ -2516,31 +2516,31 @@
     <t xml:space="preserve">17.3225116729736</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2838020324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0515441894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8386421203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2450904846191</t>
+    <t xml:space="preserve">17.2838039398193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0515460968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.83864402771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2450923919678</t>
   </si>
   <si>
     <t xml:space="preserve">17.6128330230713</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8192882537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1096096038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7225131988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.128963470459</t>
+    <t xml:space="preserve">16.8192863464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1096076965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7225151062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1289653778076</t>
   </si>
   <si>
     <t xml:space="preserve">16.8773517608643</t>
@@ -2582,13 +2582,13 @@
     <t xml:space="preserve">15.7741289138794</t>
   </si>
   <si>
-    <t xml:space="preserve">15.677357673645</t>
+    <t xml:space="preserve">15.6773557662964</t>
   </si>
   <si>
     <t xml:space="preserve">15.5612277984619</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1805782318115</t>
+    <t xml:space="preserve">16.1805801391602</t>
   </si>
   <si>
     <t xml:space="preserve">16.8579978942871</t>
@@ -2597,22 +2597,22 @@
     <t xml:space="preserve">17.3031558990479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9031524658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8063812255859</t>
+    <t xml:space="preserve">17.9031543731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8063793182373</t>
   </si>
   <si>
     <t xml:space="preserve">17.1676731109619</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5160598754883</t>
+    <t xml:space="preserve">17.5160579681396</t>
   </si>
   <si>
     <t xml:space="preserve">17.3612194061279</t>
   </si>
   <si>
-    <t xml:space="preserve">18.735408782959</t>
+    <t xml:space="preserve">18.7354106903076</t>
   </si>
   <si>
     <t xml:space="preserve">18.6579895019531</t>
@@ -2642,25 +2642,25 @@
     <t xml:space="preserve">18.2128295898438</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2902488708496</t>
+    <t xml:space="preserve">18.2902507781982</t>
   </si>
   <si>
     <t xml:space="preserve">18.1547660827637</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0192813873291</t>
+    <t xml:space="preserve">18.0192832946777</t>
   </si>
   <si>
     <t xml:space="preserve">17.9805736541748</t>
   </si>
   <si>
-    <t xml:space="preserve">17.961217880249</t>
+    <t xml:space="preserve">17.9612159729004</t>
   </si>
   <si>
     <t xml:space="preserve">17.8450908660889</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6902523040771</t>
+    <t xml:space="preserve">17.6902542114258</t>
   </si>
   <si>
     <t xml:space="preserve">17.6321868896484</t>
@@ -2672,10 +2672,10 @@
     <t xml:space="preserve">17.4386405944824</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3999290466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2644462585449</t>
+    <t xml:space="preserve">17.3999271392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2644481658936</t>
   </si>
   <si>
     <t xml:space="preserve">17.7096061706543</t>
@@ -2684,46 +2684,46 @@
     <t xml:space="preserve">17.4773483276367</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8257369995117</t>
+    <t xml:space="preserve">17.8257331848145</t>
   </si>
   <si>
     <t xml:space="preserve">18.5805721282959</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9289569854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8128299713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5483093261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9354057312012</t>
+    <t xml:space="preserve">18.928955078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8128261566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5483112335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9354038238525</t>
   </si>
   <si>
     <t xml:space="preserve">19.7902450561523</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0321769714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7418556213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5966968536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9837894439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8386287689209</t>
+    <t xml:space="preserve">20.0321788787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7418575286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5966949462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9837913513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8386306762695</t>
   </si>
   <si>
     <t xml:space="preserve">20.0805644989014</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3708839416504</t>
+    <t xml:space="preserve">20.370885848999</t>
   </si>
   <si>
     <t xml:space="preserve">19.8870162963867</t>
@@ -2732,46 +2732,46 @@
     <t xml:space="preserve">19.6450805664062</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1289520263672</t>
+    <t xml:space="preserve">20.1289501190186</t>
   </si>
   <si>
     <t xml:space="preserve">20.177339553833</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4192752838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.467658996582</t>
+    <t xml:space="preserve">20.4192733764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4676609039307</t>
   </si>
   <si>
     <t xml:space="preserve">21.2418518066406</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1934623718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.435396194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5805587768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6773319244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6289443969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0644283294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2579727172852</t>
+    <t xml:space="preserve">21.1934642791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4353981018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5805568695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6773338317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6289463043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0644264221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2579765319824</t>
   </si>
   <si>
     <t xml:space="preserve">22.6450710296631</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0321655273438</t>
+    <t xml:space="preserve">23.0321636199951</t>
   </si>
   <si>
     <t xml:space="preserve">23.4676475524902</t>
@@ -2783,10 +2783,10 @@
     <t xml:space="preserve">22.7902297973633</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7418422698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9676532745361</t>
+    <t xml:space="preserve">22.7418441772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9676551818848</t>
   </si>
   <si>
     <t xml:space="preserve">22.6934585571289</t>
@@ -2801,7 +2801,7 @@
     <t xml:space="preserve">21.8224925994873</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3547496795654</t>
+    <t xml:space="preserve">22.3547477722168</t>
   </si>
   <si>
     <t xml:space="preserve">22.112813949585</t>
@@ -2813,31 +2813,31 @@
     <t xml:space="preserve">22.9837779998779</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9031295776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.193452835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0966758728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0160312652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9676399230957</t>
+    <t xml:space="preserve">23.9031314849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1934509277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0966777801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0160293579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9676418304443</t>
   </si>
   <si>
     <t xml:space="preserve">25.4031238555908</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8386058807373</t>
+    <t xml:space="preserve">25.8386077880859</t>
   </si>
   <si>
     <t xml:space="preserve">25.9353790283203</t>
   </si>
   <si>
-    <t xml:space="preserve">25.354736328125</t>
+    <t xml:space="preserve">25.3547382354736</t>
   </si>
   <si>
     <t xml:space="preserve">25.161190032959</t>
@@ -2852,7 +2852,7 @@
     <t xml:space="preserve">25.451509475708</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2095737457275</t>
+    <t xml:space="preserve">25.2095756530762</t>
   </si>
   <si>
     <t xml:space="preserve">25.5482845306396</t>
@@ -2867,22 +2867,22 @@
     <t xml:space="preserve">26.5160217285156</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9515056610107</t>
+    <t xml:space="preserve">26.9515037536621</t>
   </si>
   <si>
     <t xml:space="preserve">25.6934432983398</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5966720581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3063507080078</t>
+    <t xml:space="preserve">25.5966739654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3063488006592</t>
   </si>
   <si>
     <t xml:space="preserve">25.8869934082031</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3708629608154</t>
+    <t xml:space="preserve">26.3708610534668</t>
   </si>
   <si>
     <t xml:space="preserve">26.2043304443359</t>
@@ -2891,7 +2891,7 @@
     <t xml:space="preserve">25.616569519043</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1267700195312</t>
+    <t xml:space="preserve">25.1267681121826</t>
   </si>
   <si>
     <t xml:space="preserve">25.9594306945801</t>
@@ -2903,16 +2903,16 @@
     <t xml:space="preserve">25.2737083435059</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0288066864014</t>
+    <t xml:space="preserve">25.02880859375</t>
   </si>
   <si>
     <t xml:space="preserve">25.2247295379639</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7349281311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4410495758057</t>
+    <t xml:space="preserve">24.7349300384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.441047668457</t>
   </si>
   <si>
     <t xml:space="preserve">24.8818683624268</t>
@@ -2927,10 +2927,10 @@
     <t xml:space="preserve">24.4900283813477</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7839088439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8328876495361</t>
+    <t xml:space="preserve">24.7839069366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8328895568848</t>
   </si>
   <si>
     <t xml:space="preserve">24.979829788208</t>
@@ -2939,19 +2939,19 @@
     <t xml:space="preserve">25.4696292877197</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9104499816895</t>
+    <t xml:space="preserve">25.9104518890381</t>
   </si>
   <si>
     <t xml:space="preserve">25.8614692687988</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7635097503662</t>
+    <t xml:space="preserve">25.7635078430176</t>
   </si>
   <si>
     <t xml:space="preserve">25.7145290374756</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2533092498779</t>
+    <t xml:space="preserve">26.2533111572266</t>
   </si>
   <si>
     <t xml:space="preserve">26.6941299438477</t>
@@ -2963,7 +2963,7 @@
     <t xml:space="preserve">26.7920913696289</t>
   </si>
   <si>
-    <t xml:space="preserve">26.596170425415</t>
+    <t xml:space="preserve">26.5961685180664</t>
   </si>
   <si>
     <t xml:space="preserve">26.4492301940918</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">25.3716678619385</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1471691131592</t>
+    <t xml:space="preserve">24.1471672058105</t>
   </si>
   <si>
     <t xml:space="preserve">26.3512687683105</t>
@@ -3008,13 +3008,13 @@
     <t xml:space="preserve">26.9880104064941</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9390316009521</t>
+    <t xml:space="preserve">26.9390296936035</t>
   </si>
   <si>
     <t xml:space="preserve">26.0573902130127</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1063709259033</t>
+    <t xml:space="preserve">26.1063690185547</t>
   </si>
   <si>
     <t xml:space="preserve">26.6451511383057</t>
@@ -3029,40 +3029,40 @@
     <t xml:space="preserve">27.134952545166</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1553497314453</t>
+    <t xml:space="preserve">26.1553516387939</t>
   </si>
   <si>
     <t xml:space="preserve">27.3798522949219</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3308696746826</t>
+    <t xml:space="preserve">27.3308715820312</t>
   </si>
   <si>
     <t xml:space="preserve">27.7227115631104</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6737308502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0165920257568</t>
+    <t xml:space="preserve">27.6737327575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0165939331055</t>
   </si>
   <si>
     <t xml:space="preserve">27.5757713317871</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4778099060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5267925262451</t>
+    <t xml:space="preserve">27.4778118133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5267906188965</t>
   </si>
   <si>
     <t xml:space="preserve">25.8124904632568</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3022918701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2818927764893</t>
+    <t xml:space="preserve">26.3022899627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2818908691406</t>
   </si>
   <si>
     <t xml:space="preserve">27.4288330078125</t>
@@ -3071,13 +3071,13 @@
     <t xml:space="preserve">27.23291015625</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6247539520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8410701751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4982089996338</t>
+    <t xml:space="preserve">27.6247520446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8410720825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4982109069824</t>
   </si>
   <si>
     <t xml:space="preserve">25.567590713501</t>
@@ -3104,7 +3104,7 @@
     <t xml:space="preserve">28.5553722381592</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0451736450195</t>
+    <t xml:space="preserve">29.0451717376709</t>
   </si>
   <si>
     <t xml:space="preserve">29.1431331634521</t>
@@ -3122,10 +3122,10 @@
     <t xml:space="preserve">29.6819133758545</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7798748016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1921119689941</t>
+    <t xml:space="preserve">29.7798728942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1921138763428</t>
   </si>
   <si>
     <t xml:space="preserve">29.5349731445312</t>
@@ -3137,10 +3137,10 @@
     <t xml:space="preserve">30.2206954956055</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5145740509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8574352264404</t>
+    <t xml:space="preserve">30.514575958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8574371337891</t>
   </si>
   <si>
     <t xml:space="preserve">32.1798973083496</t>
@@ -3155,10 +3155,10 @@
     <t xml:space="preserve">32.5227584838867</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0901184082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.824821472168</t>
+    <t xml:space="preserve">34.0901222229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8248176574707</t>
   </si>
   <si>
     <t xml:space="preserve">34.2860374450684</t>
@@ -3167,22 +3167,22 @@
     <t xml:space="preserve">34.6288986206055</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1390991210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7758407592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.747257232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8941955566406</t>
+    <t xml:space="preserve">34.1390953063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7758369445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7472610473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8941993713379</t>
   </si>
   <si>
     <t xml:space="preserve">34.335018157959</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9431838989258</t>
+    <t xml:space="preserve">33.9431800842285</t>
   </si>
   <si>
     <t xml:space="preserve">35.0207405090332</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">35.4125823974609</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9635810852051</t>
+    <t xml:space="preserve">32.9635772705078</t>
   </si>
   <si>
     <t xml:space="preserve">32.9145965576172</t>
@@ -3209,7 +3209,7 @@
     <t xml:space="preserve">33.0125579833984</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4451942443848</t>
+    <t xml:space="preserve">31.4451961517334</t>
   </si>
   <si>
     <t xml:space="preserve">31.5641193389893</t>
@@ -3837,6 +3837,9 @@
   </si>
   <si>
     <t xml:space="preserve">50.0999984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.0999984741211</t>
   </si>
 </sst>
 </file>
@@ -69227,7 +69230,7 @@
     </row>
     <row r="2503">
       <c r="A2503" s="1" t="n">
-        <v>45964.6912384259</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2503" t="n">
         <v>35496</v>
@@ -69248,6 +69251,32 @@
         <v>1274</v>
       </c>
       <c r="H2503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>45965.6910416667</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>63442</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>49.9000015258789</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>48</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>49.9000015258789</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>49.0999984741211</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>1275</v>
+      </c>
+      <c r="H2504" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SOL.MI.xlsx
+++ b/data/SOL.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14939069747925</t>
+    <t xml:space="preserve">7.14939117431641</t>
   </si>
   <si>
     <t xml:space="preserve">SOL.MI</t>
@@ -47,16 +47,16 @@
     <t xml:space="preserve">7.14067268371582</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18862533569336</t>
+    <t xml:space="preserve">7.18862581253052</t>
   </si>
   <si>
     <t xml:space="preserve">7.1624698638916</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06220436096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90962600708008</t>
+    <t xml:space="preserve">7.06220388412476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90962553024292</t>
   </si>
   <si>
     <t xml:space="preserve">6.90526580810547</t>
@@ -65,10 +65,10 @@
     <t xml:space="preserve">6.94885969161987</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71781253814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6262640953064</t>
+    <t xml:space="preserve">6.71781206130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62626552581787</t>
   </si>
   <si>
     <t xml:space="preserve">6.71345233917236</t>
@@ -77,160 +77,160 @@
     <t xml:space="preserve">6.29931116104126</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36470174789429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43009376525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41265487670898</t>
+    <t xml:space="preserve">6.3647027015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43009281158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41265535354614</t>
   </si>
   <si>
     <t xml:space="preserve">6.44753074645996</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20776462554932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17288875579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46060800552368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54779624938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38213920593262</t>
+    <t xml:space="preserve">6.207763671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1728892326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46060848236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54779672622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38213968276978</t>
   </si>
   <si>
     <t xml:space="preserve">6.51292085647583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50420141220093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65242195129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80064105987549</t>
+    <t xml:space="preserve">6.50420331954956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65242099761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80064058303833</t>
   </si>
   <si>
     <t xml:space="preserve">6.72217130661011</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79192209243774</t>
+    <t xml:space="preserve">6.79192161560059</t>
   </si>
   <si>
     <t xml:space="preserve">7.00989151000977</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84423398971558</t>
+    <t xml:space="preserve">6.84423446655273</t>
   </si>
   <si>
     <t xml:space="preserve">7.07964134216309</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88346910476685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96629619598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08836030960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73524904251099</t>
+    <t xml:space="preserve">6.88346815109253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9662971496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08835935592651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73524951934814</t>
   </si>
   <si>
     <t xml:space="preserve">6.83115577697754</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6785774230957</t>
+    <t xml:space="preserve">6.67857789993286</t>
   </si>
   <si>
     <t xml:space="preserve">6.57395219802856</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63062572479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68729686737061</t>
+    <t xml:space="preserve">6.63062381744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68729734420776</t>
   </si>
   <si>
     <t xml:space="preserve">6.78320264816284</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77884340286255</t>
+    <t xml:space="preserve">6.77884292602539</t>
   </si>
   <si>
     <t xml:space="preserve">6.81371831893921</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80935907363892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79628133773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69601488113403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81807851791382</t>
+    <t xml:space="preserve">6.80935955047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79628086090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69601583480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81807804107666</t>
   </si>
   <si>
     <t xml:space="preserve">6.8747501373291</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91398477554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67421817779541</t>
+    <t xml:space="preserve">6.91398429870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67421913146973</t>
   </si>
   <si>
     <t xml:space="preserve">6.55215549468994</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46496772766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43881225585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73089027404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87910938262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85295343399048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84859418869019</t>
+    <t xml:space="preserve">6.46496820449829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43881177902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73088979721069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87910985946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85295295715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84859323501587</t>
   </si>
   <si>
     <t xml:space="preserve">6.85731220245361</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7483286857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51728057861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37342023849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56523418426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66985940933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77012491226196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86167240142822</t>
+    <t xml:space="preserve">6.74832773208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51728105545044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37342119216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56523370742798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66985893249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7701244354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86167144775391</t>
   </si>
   <si>
     <t xml:space="preserve">6.97501611709595</t>
@@ -239,40 +239,40 @@
     <t xml:space="preserve">6.9416298866272</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95048332214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88407754898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90178632736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34006500244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22496175765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.419753074646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43746042251587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36662769317627</t>
+    <t xml:space="preserve">6.95048427581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88407802581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9017858505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34006547927856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22496128082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41975116729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43745946884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36662673950195</t>
   </si>
   <si>
     <t xml:space="preserve">7.26037788391113</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46845006942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40204286575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44631481170654</t>
+    <t xml:space="preserve">7.46845054626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40204334259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44631433486938</t>
   </si>
   <si>
     <t xml:space="preserve">7.38433599472046</t>
@@ -281,40 +281,40 @@
     <t xml:space="preserve">7.04345178604126</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97261905670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1098575592041</t>
+    <t xml:space="preserve">6.97261953353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10985803604126</t>
   </si>
   <si>
     <t xml:space="preserve">6.8707971572876</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20725440979004</t>
+    <t xml:space="preserve">7.20725345611572</t>
   </si>
   <si>
     <t xml:space="preserve">7.37105417251587</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57027196884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6942286491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70308303833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71193838119507</t>
+    <t xml:space="preserve">7.57027149200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69423055648804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70308399200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71193885803223</t>
   </si>
   <si>
     <t xml:space="preserve">7.65881252288818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04396724700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61454248428345</t>
+    <t xml:space="preserve">8.04396915435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61454200744629</t>
   </si>
   <si>
     <t xml:space="preserve">7.2957935333252</t>
@@ -323,22 +323,22 @@
     <t xml:space="preserve">6.99475431442261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10100412368774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55256414413452</t>
+    <t xml:space="preserve">7.1010046005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55256462097168</t>
   </si>
   <si>
     <t xml:space="preserve">7.3135027885437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50829267501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42417907714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37548065185547</t>
+    <t xml:space="preserve">7.50829219818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42417860031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37548208236694</t>
   </si>
   <si>
     <t xml:space="preserve">7.52600145339966</t>
@@ -347,43 +347,43 @@
     <t xml:space="preserve">7.54371070861816</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41532468795776</t>
+    <t xml:space="preserve">7.41532564163208</t>
   </si>
   <si>
     <t xml:space="preserve">7.21610736846924</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99032783508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79996395111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7556939125061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00803565979004</t>
+    <t xml:space="preserve">6.99032688140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.799964427948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75569343566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00803518295288</t>
   </si>
   <si>
     <t xml:space="preserve">7.26923227310181</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34449291229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46402263641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51714849472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39318990707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45516967773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17183780670166</t>
+    <t xml:space="preserve">7.34449243545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46402311325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51714754104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39319038391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4551682472229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17183685302734</t>
   </si>
   <si>
     <t xml:space="preserve">7.33563804626465</t>
@@ -392,7 +392,7 @@
     <t xml:space="preserve">7.33121109008789</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39761543273926</t>
+    <t xml:space="preserve">7.39761638641357</t>
   </si>
   <si>
     <t xml:space="preserve">7.30464887619019</t>
@@ -404,28 +404,28 @@
     <t xml:space="preserve">7.25152397155762</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16298246383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03017139434814</t>
+    <t xml:space="preserve">7.16298294067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03017044067383</t>
   </si>
   <si>
     <t xml:space="preserve">6.87965106964111</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91064071655273</t>
+    <t xml:space="preserve">6.91064023971558</t>
   </si>
   <si>
     <t xml:space="preserve">6.95491075515747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88850498199463</t>
+    <t xml:space="preserve">6.88850545883179</t>
   </si>
   <si>
     <t xml:space="preserve">6.95933818817139</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85751581192017</t>
+    <t xml:space="preserve">6.85751533508301</t>
   </si>
   <si>
     <t xml:space="preserve">6.77340173721313</t>
@@ -434,22 +434,22 @@
     <t xml:space="preserve">6.74683904647827</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82652568817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68486070632935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81767129898071</t>
+    <t xml:space="preserve">6.8265266418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68485975265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81767177581787</t>
   </si>
   <si>
     <t xml:space="preserve">6.90621328353882</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01689052581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8973593711853</t>
+    <t xml:space="preserve">7.01688957214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89735889434814</t>
   </si>
   <si>
     <t xml:space="preserve">6.83538007736206</t>
@@ -464,10 +464,10 @@
     <t xml:space="preserve">6.97704648971558</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00360822677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91506671905518</t>
+    <t xml:space="preserve">7.00360870361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91506719589233</t>
   </si>
   <si>
     <t xml:space="preserve">6.91949415206909</t>
@@ -479,10 +479,10 @@
     <t xml:space="preserve">7.07001399993896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98590040206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75126647949219</t>
+    <t xml:space="preserve">6.98590087890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75126600265503</t>
   </si>
   <si>
     <t xml:space="preserve">6.77782821655273</t>
@@ -491,61 +491,61 @@
     <t xml:space="preserve">6.64944362640381</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38381958007812</t>
+    <t xml:space="preserve">6.3838210105896</t>
   </si>
   <si>
     <t xml:space="preserve">6.37053918838501</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36168479919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37939310073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40595531463623</t>
+    <t xml:space="preserve">6.36168527603149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37939357757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40595579147339</t>
   </si>
   <si>
     <t xml:space="preserve">6.48121500015259</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47678899765015</t>
+    <t xml:space="preserve">6.47678852081299</t>
   </si>
   <si>
     <t xml:space="preserve">6.54319381713867</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46350717544556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24215412139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25986194610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22444629669189</t>
+    <t xml:space="preserve">6.46350812911987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24215507507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25986289978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22444581985474</t>
   </si>
   <si>
     <t xml:space="preserve">6.64501714706421</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64058971405029</t>
+    <t xml:space="preserve">6.64059019088745</t>
   </si>
   <si>
     <t xml:space="preserve">7.03902435302734</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79111051559448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70256948471069</t>
+    <t xml:space="preserve">6.79111003875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70256853103638</t>
   </si>
   <si>
     <t xml:space="preserve">6.70699501037598</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65829801559448</t>
+    <t xml:space="preserve">6.65829753875732</t>
   </si>
   <si>
     <t xml:space="preserve">6.58303785324097</t>
@@ -554,70 +554,70 @@
     <t xml:space="preserve">7.05673313140869</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11428499221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34891891479492</t>
+    <t xml:space="preserve">7.11428451538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34891939163208</t>
   </si>
   <si>
     <t xml:space="preserve">7.18511772155762</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12756681442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19397258758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24267053604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41089820861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48173141479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14527416229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27365922927856</t>
+    <t xml:space="preserve">7.12756729125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19397211074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2426700592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41089868545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48173093795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14527368545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27365875244141</t>
   </si>
   <si>
     <t xml:space="preserve">7.17626333236694</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04787921905518</t>
+    <t xml:space="preserve">7.04787969589233</t>
   </si>
   <si>
     <t xml:space="preserve">7.23381614685059</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29136657714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42860746383667</t>
+    <t xml:space="preserve">7.2913670539856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4286060333252</t>
   </si>
   <si>
     <t xml:space="preserve">7.83589601516724</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82704210281372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13693428039551</t>
+    <t xml:space="preserve">7.82704019546509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13693523406982</t>
   </si>
   <si>
     <t xml:space="preserve">8.27860260009766</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32287311553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0312032699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53094577789307</t>
+    <t xml:space="preserve">8.3228702545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03120136260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53094482421875</t>
   </si>
   <si>
     <t xml:space="preserve">8.49995517730713</t>
@@ -626,10 +626,10 @@
     <t xml:space="preserve">8.26089286804199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92495346069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58849430084229</t>
+    <t xml:space="preserve">8.92495155334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58849620819092</t>
   </si>
   <si>
     <t xml:space="preserve">8.97807693481445</t>
@@ -638,49 +638,49 @@
     <t xml:space="preserve">8.76557731628418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87182903289795</t>
+    <t xml:space="preserve">8.87182807922363</t>
   </si>
   <si>
     <t xml:space="preserve">9.56244945526123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25255489349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02234554290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8541202545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82755661010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71245384216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98693084716797</t>
+    <t xml:space="preserve">9.25255584716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02234745025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85411834716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82755851745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71245288848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98692989349365</t>
   </si>
   <si>
     <t xml:space="preserve">8.8983907699585</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80984878540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72130966186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78328514099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67703723907471</t>
+    <t xml:space="preserve">8.80984973907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72130870819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78328609466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67703628540039</t>
   </si>
   <si>
     <t xml:space="preserve">8.7567253112793</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10203552246094</t>
+    <t xml:space="preserve">9.10203456878662</t>
   </si>
   <si>
     <t xml:space="preserve">8.82313060760498</t>
@@ -689,22 +689,22 @@
     <t xml:space="preserve">8.94266128540039</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20828533172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43287658691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4598274230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52271366119385</t>
+    <t xml:space="preserve">9.20828247070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43287563323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45982837677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52271461486816</t>
   </si>
   <si>
     <t xml:space="preserve">9.32507228851318</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38795757293701</t>
+    <t xml:space="preserve">9.38795852661133</t>
   </si>
   <si>
     <t xml:space="preserve">9.35202312469482</t>
@@ -722,70 +722,70 @@
     <t xml:space="preserve">9.67543601989746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86409378051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5199031829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0617341995239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88206100463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74730587005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56763076782227</t>
+    <t xml:space="preserve">9.86409282684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5199022293091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0617332458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88206005096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74730682373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5676326751709</t>
   </si>
   <si>
     <t xml:space="preserve">9.44186019897461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54068088531494</t>
+    <t xml:space="preserve">9.54067993164062</t>
   </si>
   <si>
     <t xml:space="preserve">9.34303951263428</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36100578308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50474643707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48677825927734</t>
+    <t xml:space="preserve">9.36100673675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50474548339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48677921295166</t>
   </si>
   <si>
     <t xml:space="preserve">9.61254978179932</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77425670623779</t>
+    <t xml:space="preserve">9.77425765991211</t>
   </si>
   <si>
     <t xml:space="preserve">9.46881103515625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54966449737549</t>
+    <t xml:space="preserve">9.54966640472412</t>
   </si>
   <si>
     <t xml:space="preserve">9.47779560089111</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70238780975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30710601806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28015422821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21726894378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16336631774902</t>
+    <t xml:space="preserve">9.7023868560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30710506439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28015327453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21726703643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16336441040039</t>
   </si>
   <si>
     <t xml:space="preserve">9.20828437805176</t>
@@ -794,76 +794,76 @@
     <t xml:space="preserve">9.25320339202881</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45084285736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58559894561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33405590057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59458351135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6664514541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71137237548828</t>
+    <t xml:space="preserve">9.45084476470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58559989929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33405780792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59458160400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66645240783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71137142181396</t>
   </si>
   <si>
     <t xml:space="preserve">9.40592575073242</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26218509674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27116966247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28913879394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36999034881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65746974945068</t>
+    <t xml:space="preserve">9.26218795776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27116870880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.289137840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36999130249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65746879577637</t>
   </si>
   <si>
     <t xml:space="preserve">9.79222393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76527309417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72035503387451</t>
+    <t xml:space="preserve">9.76527404785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7203540802002</t>
   </si>
   <si>
     <t xml:space="preserve">9.81019115447998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37897491455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.909010887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81917572021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73832321166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78324127197266</t>
+    <t xml:space="preserve">9.37897396087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90901184082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81917476654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73832225799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78324222564697</t>
   </si>
   <si>
     <t xml:space="preserve">9.69340419769287</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11844635009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08251190185547</t>
+    <t xml:space="preserve">9.11844730377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08251285552979</t>
   </si>
   <si>
     <t xml:space="preserve">9.31608963012695</t>
@@ -881,25 +881,25 @@
     <t xml:space="preserve">9.41490840911865</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39694118499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07353019714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57661437988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68441867828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09149742126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05556201934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14539813995361</t>
+    <t xml:space="preserve">9.39694213867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07352924346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57661628723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68441963195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09149646759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05556106567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14540004730225</t>
   </si>
   <si>
     <t xml:space="preserve">8.89385414123535</t>
@@ -908,16 +908,16 @@
     <t xml:space="preserve">9.10946369171143</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23523616790771</t>
+    <t xml:space="preserve">9.2352352142334</t>
   </si>
   <si>
     <t xml:space="preserve">9.95393085479736</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5109195709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.74449634552</t>
+    <t xml:space="preserve">10.5109186172485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7444953918457</t>
   </si>
   <si>
     <t xml:space="preserve">10.546854019165</t>
@@ -929,73 +929,73 @@
     <t xml:space="preserve">10.9062023162842</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7804298400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7085618972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6546592712402</t>
+    <t xml:space="preserve">10.7804307937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7085599899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6546573638916</t>
   </si>
   <si>
     <t xml:space="preserve">10.5288867950439</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4390497207642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3312463760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1695404052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1875076293945</t>
+    <t xml:space="preserve">10.4390506744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3312454223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1695384979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1875066757202</t>
   </si>
   <si>
     <t xml:space="preserve">10.1336040496826</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75628852844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63051795959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0078344345093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8461275100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0976686477661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2054748535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2773427963257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2234420776367</t>
+    <t xml:space="preserve">9.7562894821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63051891326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.007833480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84612464904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0976705551147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2054738998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2773418426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2234401702881</t>
   </si>
   <si>
     <t xml:space="preserve">10.2414083480835</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7624616622925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2593774795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91799545288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90002918243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67380619049072</t>
+    <t xml:space="preserve">10.7624626159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2593765258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91799640655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90002822875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67380523681641</t>
   </si>
   <si>
     <t xml:space="preserve">9.74667835235596</t>
@@ -1007,10 +1007,10 @@
     <t xml:space="preserve">10.1656942367554</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85598754882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63737106323242</t>
+    <t xml:space="preserve">9.85598659515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63736915588379</t>
   </si>
   <si>
     <t xml:space="preserve">9.47340774536133</t>
@@ -1019,13 +1019,13 @@
     <t xml:space="preserve">9.76489734649658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96529674530029</t>
+    <t xml:space="preserve">9.96529483795166</t>
   </si>
   <si>
     <t xml:space="preserve">10.0746059417725</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2385663986206</t>
+    <t xml:space="preserve">10.2385673522949</t>
   </si>
   <si>
     <t xml:space="preserve">10.3843116760254</t>
@@ -1034,61 +1034,61 @@
     <t xml:space="preserve">10.420747756958</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8033285140991</t>
+    <t xml:space="preserve">10.8033275604248</t>
   </si>
   <si>
     <t xml:space="preserve">10.694019317627</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6211462020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7851114273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5482749938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4025316238403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2203502655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1474781036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3296585083008</t>
+    <t xml:space="preserve">10.6211471557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7851104736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5482730865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4025297164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2203493118286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1474761962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3296575546265</t>
   </si>
   <si>
     <t xml:space="preserve">10.5847110748291</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3478765487671</t>
+    <t xml:space="preserve">10.3478755950928</t>
   </si>
   <si>
     <t xml:space="preserve">9.72846126556396</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56449794769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41875457763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40053462982178</t>
+    <t xml:space="preserve">9.56449699401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41875267028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40053367614746</t>
   </si>
   <si>
     <t xml:space="preserve">9.54627895355225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1110420227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2567863464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92885971069336</t>
+    <t xml:space="preserve">10.1110410690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2567844390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92886066436768</t>
   </si>
   <si>
     <t xml:space="preserve">10.0199499130249</t>
@@ -1097,10 +1097,10 @@
     <t xml:space="preserve">10.202130317688</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0928230285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80133247375488</t>
+    <t xml:space="preserve">10.0928220748901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8013334274292</t>
   </si>
   <si>
     <t xml:space="preserve">9.69202518463135</t>
@@ -1109,112 +1109,112 @@
     <t xml:space="preserve">9.83776950836182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94707775115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89242267608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65558910369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78311347961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91064167022705</t>
+    <t xml:space="preserve">9.94707679748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89242458343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65558815002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78311443328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91064262390137</t>
   </si>
   <si>
     <t xml:space="preserve">9.45518970489502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2001371383667</t>
+    <t xml:space="preserve">9.20013618469238</t>
   </si>
   <si>
     <t xml:space="preserve">9.50984382629395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43697261810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81954956054688</t>
+    <t xml:space="preserve">9.43697071075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81955051422119</t>
   </si>
   <si>
     <t xml:space="preserve">9.49162483215332</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6191520690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9835147857666</t>
+    <t xml:space="preserve">9.61915302276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98351383209229</t>
   </si>
   <si>
     <t xml:space="preserve">9.60093402862549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10904598236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09993553161621</t>
+    <t xml:space="preserve">9.10904502868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09993648529053</t>
   </si>
   <si>
     <t xml:space="preserve">9.38231754302979</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36409950256348</t>
+    <t xml:space="preserve">9.36409854888916</t>
   </si>
   <si>
     <t xml:space="preserve">9.27300834655762</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71024131774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58271503448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29122734069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14548301696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3660945892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32766246795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0017318725586</t>
+    <t xml:space="preserve">9.71024227142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58271598815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29122638702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14548110961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3660936355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32766342163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0017309188843</t>
   </si>
   <si>
     <t xml:space="preserve">10.4754028320312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8397636413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5664939880371</t>
+    <t xml:space="preserve">10.8397645950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5664920806885</t>
   </si>
   <si>
     <t xml:space="preserve">10.3114404678345</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2932224273682</t>
+    <t xml:space="preserve">10.2932233810425</t>
   </si>
   <si>
     <t xml:space="preserve">10.0381689071655</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0563859939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1292591094971</t>
+    <t xml:space="preserve">10.0563869476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1292581558228</t>
   </si>
   <si>
     <t xml:space="preserve">10.2750034332275</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1839151382446</t>
+    <t xml:space="preserve">10.1839122772217</t>
   </si>
   <si>
     <t xml:space="preserve">10.6758012771606</t>
@@ -1223,7 +1223,7 @@
     <t xml:space="preserve">10.7122364044189</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9308547973633</t>
+    <t xml:space="preserve">10.9308557510376</t>
   </si>
   <si>
     <t xml:space="preserve">11.0219459533691</t>
@@ -1232,7 +1232,7 @@
     <t xml:space="preserve">10.8762006759644</t>
   </si>
   <si>
-    <t xml:space="preserve">10.894419670105</t>
+    <t xml:space="preserve">10.8944187164307</t>
   </si>
   <si>
     <t xml:space="preserve">10.7304544448853</t>
@@ -1241,16 +1241,16 @@
     <t xml:space="preserve">10.6575832366943</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2644624710083</t>
+    <t xml:space="preserve">11.2644634246826</t>
   </si>
   <si>
     <t xml:space="preserve">11.1349868774414</t>
   </si>
   <si>
-    <t xml:space="preserve">11.097993850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2459659576416</t>
+    <t xml:space="preserve">11.0979928970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2459678649902</t>
   </si>
   <si>
     <t xml:space="preserve">11.319953918457</t>
@@ -1268,16 +1268,16 @@
     <t xml:space="preserve">10.7280607223511</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8575372695923</t>
+    <t xml:space="preserve">10.8575382232666</t>
   </si>
   <si>
     <t xml:space="preserve">10.7095632553101</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6725692749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6540746688843</t>
+    <t xml:space="preserve">10.6725702285767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6540756225586</t>
   </si>
   <si>
     <t xml:space="preserve">10.7835512161255</t>
@@ -1286,10 +1286,10 @@
     <t xml:space="preserve">10.7650547027588</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8020477294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5615911483765</t>
+    <t xml:space="preserve">10.8020458221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5615901947021</t>
   </si>
   <si>
     <t xml:space="preserve">10.6170797348022</t>
@@ -1301,34 +1301,34 @@
     <t xml:space="preserve">10.1176710128784</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2841396331787</t>
+    <t xml:space="preserve">10.2841415405273</t>
   </si>
   <si>
     <t xml:space="preserve">10.2656440734863</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3026371002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5061006546021</t>
+    <t xml:space="preserve">10.302638053894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5060997009277</t>
   </si>
   <si>
     <t xml:space="preserve">10.3396301269531</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1361665725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.080677986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98819351196289</t>
+    <t xml:space="preserve">10.1361675262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0806770324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98819446563721</t>
   </si>
   <si>
     <t xml:space="preserve">10.0991735458374</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93270397186279</t>
+    <t xml:space="preserve">9.93270301818848</t>
   </si>
   <si>
     <t xml:space="preserve">9.89571094512939</t>
@@ -1343,19 +1343,19 @@
     <t xml:space="preserve">10.062180519104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1546649932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71074485778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0251865386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91420650482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76623439788818</t>
+    <t xml:space="preserve">10.1546630859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71074390411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0251874923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91420841217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7662353515625</t>
   </si>
   <si>
     <t xml:space="preserve">9.72924137115479</t>
@@ -1370,16 +1370,16 @@
     <t xml:space="preserve">9.47028732299805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54427528381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56277179718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45179176330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35930824279785</t>
+    <t xml:space="preserve">9.54427337646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56277084350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45179080963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35930919647217</t>
   </si>
   <si>
     <t xml:space="preserve">9.52577781677246</t>
@@ -1388,25 +1388,25 @@
     <t xml:space="preserve">9.59976387023926</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61826038360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69224548339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80322742462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2286510467529</t>
+    <t xml:space="preserve">9.61826133728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69224834442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80322647094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2286520004272</t>
   </si>
   <si>
     <t xml:space="preserve">9.78473091125488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85871887207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0066900253296</t>
+    <t xml:space="preserve">9.85871601104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0066919326782</t>
   </si>
   <si>
     <t xml:space="preserve">9.8772144317627</t>
@@ -1415,25 +1415,25 @@
     <t xml:space="preserve">9.74773788452148</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58126735687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3211326599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4321146011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3766231536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2471475601196</t>
+    <t xml:space="preserve">9.58126831054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3211336135864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4321136474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3766250610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2471466064453</t>
   </si>
   <si>
     <t xml:space="preserve">10.2101535797119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8402214050293</t>
+    <t xml:space="preserve">9.84022235870361</t>
   </si>
   <si>
     <t xml:space="preserve">9.63675880432129</t>
@@ -1442,76 +1442,76 @@
     <t xml:space="preserve">9.43329429626465</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41479873657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39630126953125</t>
+    <t xml:space="preserve">9.41479778289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39630031585693</t>
   </si>
   <si>
     <t xml:space="preserve">9.24832820892334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06336212158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10960292816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32231426239014</t>
+    <t xml:space="preserve">9.06336116790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10960388183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32231330871582</t>
   </si>
   <si>
     <t xml:space="preserve">9.28532123565674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26682567596436</t>
+    <t xml:space="preserve">9.26682472229004</t>
   </si>
   <si>
     <t xml:space="preserve">9.19283771514893</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22983169555664</t>
+    <t xml:space="preserve">9.22983074188232</t>
   </si>
   <si>
     <t xml:space="preserve">9.48878479003906</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02636909484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97087860107422</t>
+    <t xml:space="preserve">9.02636814117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9708776473999</t>
   </si>
   <si>
     <t xml:space="preserve">9.13734817504883</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96162891387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82290458679199</t>
+    <t xml:space="preserve">8.96162986755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82290554046631</t>
   </si>
   <si>
     <t xml:space="preserve">8.61944103240967</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55470371246338</t>
+    <t xml:space="preserve">8.55470275878906</t>
   </si>
   <si>
     <t xml:space="preserve">8.36048889160156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33274459838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01830005645752</t>
+    <t xml:space="preserve">8.33274364471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0182991027832</t>
   </si>
   <si>
     <t xml:space="preserve">7.81483745574951</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95356321334839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49114561080933</t>
+    <t xml:space="preserve">7.95356225967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49114608764648</t>
   </si>
   <si>
     <t xml:space="preserve">7.86107873916626</t>
@@ -1520,55 +1520,55 @@
     <t xml:space="preserve">7.50964260101318</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53738641738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58362865447998</t>
+    <t xml:space="preserve">7.53738689422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58362913131714</t>
   </si>
   <si>
     <t xml:space="preserve">8.76741409301758</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9893741607666</t>
+    <t xml:space="preserve">8.98937511444092</t>
   </si>
   <si>
     <t xml:space="preserve">9.16509342193604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12810039520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09110736846924</t>
+    <t xml:space="preserve">9.12809944152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09110546112061</t>
   </si>
   <si>
     <t xml:space="preserve">9.08185768127441</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34081172943115</t>
+    <t xml:space="preserve">9.34081077575684</t>
   </si>
   <si>
     <t xml:space="preserve">9.04486560821533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21133327484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38705253601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17434120178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29456806182861</t>
+    <t xml:space="preserve">9.21133422851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38705158233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17434215545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29456996917725</t>
   </si>
   <si>
     <t xml:space="preserve">9.11885070800781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78591156005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89689064025879</t>
+    <t xml:space="preserve">8.78591060638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89689159393311</t>
   </si>
   <si>
     <t xml:space="preserve">8.7489185333252</t>
@@ -1589,13 +1589,13 @@
     <t xml:space="preserve">8.71192455291748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58244705200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69342803955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46113872528076</t>
+    <t xml:space="preserve">8.58244800567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69342708587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46113967895508</t>
   </si>
   <si>
     <t xml:space="preserve">9.6494197845459</t>
@@ -1604,19 +1604,19 @@
     <t xml:space="preserve">9.69649124145508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74356174468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97891330718994</t>
+    <t xml:space="preserve">9.74356079101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97891235351562</t>
   </si>
   <si>
     <t xml:space="preserve">9.93184375762939</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79063034057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0730543136597</t>
+    <t xml:space="preserve">9.79063129425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0730533599854</t>
   </si>
   <si>
     <t xml:space="preserve">10.3084049224854</t>
@@ -1628,106 +1628,106 @@
     <t xml:space="preserve">10.1671943664551</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1201248168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0259838104248</t>
+    <t xml:space="preserve">10.1201238632202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0259828567505</t>
   </si>
   <si>
     <t xml:space="preserve">10.2142648696899</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3554744720459</t>
+    <t xml:space="preserve">10.3554754257202</t>
   </si>
   <si>
     <t xml:space="preserve">10.2613344192505</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88477230072021</t>
+    <t xml:space="preserve">9.8847713470459</t>
   </si>
   <si>
     <t xml:space="preserve">10.5908269882202</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4966850280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5437574386597</t>
+    <t xml:space="preserve">10.4966869354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5437564849854</t>
   </si>
   <si>
     <t xml:space="preserve">11.2027416229248</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1556720733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9673900604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0615310668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7791090011597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8261785507202</t>
+    <t xml:space="preserve">11.1556711196899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9673891067505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0615291595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7791080474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8261775970459</t>
   </si>
   <si>
     <t xml:space="preserve">11.0144605636597</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1086025238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9203205108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8732500076294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7320375442505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6378984451294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5322332382202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6263751983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7675848007202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8146572113037</t>
+    <t xml:space="preserve">11.1086015701294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9203195571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8732490539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7320384979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6378974914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5322341918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6263742446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7675867080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8146562576294</t>
   </si>
   <si>
     <t xml:space="preserve">11.5793046951294</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6734437942505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7205152511597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0029382705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2853603363037</t>
+    <t xml:space="preserve">11.6734447479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7205142974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0029373168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2853593826294</t>
   </si>
   <si>
     <t xml:space="preserve">12.5677814483643</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5207118988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.897274017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7560634613037</t>
+    <t xml:space="preserve">12.5207109451294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8972730636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7560625076294</t>
   </si>
   <si>
     <t xml:space="preserve">12.6619215011597</t>
@@ -1736,52 +1736,52 @@
     <t xml:space="preserve">12.6148509979248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8031330108643</t>
+    <t xml:space="preserve">12.8031320571899</t>
   </si>
   <si>
     <t xml:space="preserve">12.8502035140991</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9914150238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1796960830688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.462119102478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.838680267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7445402145386</t>
+    <t xml:space="preserve">12.9914140701294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1796951293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4621171951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8386793136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7445411682129</t>
   </si>
   <si>
     <t xml:space="preserve">13.6503992080688</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5091886520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7916097640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8857507705688</t>
+    <t xml:space="preserve">13.5091896057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7916107177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8857517242432</t>
   </si>
   <si>
     <t xml:space="preserve">13.9798927307129</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0269613265991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0740327835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1681747436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1211032867432</t>
+    <t xml:space="preserve">14.0269622802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.074031829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1681728363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1211023330688</t>
   </si>
   <si>
     <t xml:space="preserve">14.2623128890991</t>
@@ -1793,16 +1793,16 @@
     <t xml:space="preserve">14.4505958557129</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6859483718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3093852996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4035263061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3564548492432</t>
+    <t xml:space="preserve">14.6859474182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3093843460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.403525352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3564538955688</t>
   </si>
   <si>
     <t xml:space="preserve">14.5447359085083</t>
@@ -1811,25 +1811,25 @@
     <t xml:space="preserve">14.5918064117432</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6388778686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.780086517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8271579742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.874228477478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7330160140991</t>
+    <t xml:space="preserve">14.638876914978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7800884246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8271589279175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8742294311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7330169677734</t>
   </si>
   <si>
     <t xml:space="preserve">15.344931602478</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7685632705688</t>
+    <t xml:space="preserve">15.7685661315918</t>
   </si>
   <si>
     <t xml:space="preserve">16.0039176940918</t>
@@ -1838,7 +1838,7 @@
     <t xml:space="preserve">16.0415725708008</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0792274475098</t>
+    <t xml:space="preserve">16.079231262207</t>
   </si>
   <si>
     <t xml:space="preserve">16.1921997070312</t>
@@ -1847,16 +1847,16 @@
     <t xml:space="preserve">16.116886138916</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2298526763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3804779052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3993053436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4181365966797</t>
+    <t xml:space="preserve">16.2298545837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3804798126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3993091583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4181346893311</t>
   </si>
   <si>
     <t xml:space="preserve">16.5311050415039</t>
@@ -1865,112 +1865,109 @@
     <t xml:space="preserve">16.2675113677979</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9286031723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8909482955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.815634727478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9662599563599</t>
+    <t xml:space="preserve">15.9286050796509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8909492492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8156337738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9662590026855</t>
   </si>
   <si>
     <t xml:space="preserve">15.7214956283569</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5332136154175</t>
+    <t xml:space="preserve">15.5332145690918</t>
   </si>
   <si>
     <t xml:space="preserve">15.5143852233887</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7026672363281</t>
+    <t xml:space="preserve">15.7026662826538</t>
   </si>
   <si>
     <t xml:space="preserve">15.2696189880371</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4767303466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6838388442993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6650085449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4202432632446</t>
+    <t xml:space="preserve">15.4767284393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6838369369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6650104522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4202442169189</t>
   </si>
   <si>
     <t xml:space="preserve">15.1566514968872</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2319641113281</t>
+    <t xml:space="preserve">15.2319631576538</t>
   </si>
   <si>
     <t xml:space="preserve">15.7779788970947</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9833707809448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9643001556396</t>
+    <t xml:space="preserve">15.9833726882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.964301109314</t>
   </si>
   <si>
     <t xml:space="preserve">15.6209812164307</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4874687194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7926406860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8117160797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6019086837769</t>
+    <t xml:space="preserve">15.4874696731567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7926397323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8117141723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6019096374512</t>
   </si>
   <si>
     <t xml:space="preserve">15.5446872711182</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2585897445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6972742080688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8307876586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1168842315674</t>
+    <t xml:space="preserve">15.2585906982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6972723007202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8307867050171</t>
   </si>
   <si>
     <t xml:space="preserve">16.2503986358643</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2313251495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0024452209473</t>
+    <t xml:space="preserve">16.2313270568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0024471282959</t>
   </si>
   <si>
     <t xml:space="preserve">16.2694721221924</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2122535705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.460205078125</t>
+    <t xml:space="preserve">16.212251663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4602069854736</t>
   </si>
   <si>
     <t xml:space="preserve">16.4411315917969</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5364971160889</t>
+    <t xml:space="preserve">16.5364952087402</t>
   </si>
   <si>
     <t xml:space="preserve">16.555570602417</t>
@@ -1982,7 +1979,7 @@
     <t xml:space="preserve">16.9561080932617</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2231349945068</t>
+    <t xml:space="preserve">17.2231330871582</t>
   </si>
   <si>
     <t xml:space="preserve">17.3185005187988</t>
@@ -1994,19 +1991,19 @@
     <t xml:space="preserve">16.8416690826416</t>
   </si>
   <si>
-    <t xml:space="preserve">16.746301651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9751796722412</t>
+    <t xml:space="preserve">16.7463035583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9751815795898</t>
   </si>
   <si>
     <t xml:space="preserve">17.1277656555176</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5092315673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5473785400391</t>
+    <t xml:space="preserve">17.5092334747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5473804473877</t>
   </si>
   <si>
     <t xml:space="preserve">17.7571830749512</t>
@@ -2042,7 +2039,7 @@
     <t xml:space="preserve">17.0133266448975</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4520111083984</t>
+    <t xml:space="preserve">17.4520130157471</t>
   </si>
   <si>
     <t xml:space="preserve">17.8334789276123</t>
@@ -2051,13 +2048,13 @@
     <t xml:space="preserve">17.6999645233154</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8716259002686</t>
+    <t xml:space="preserve">17.8716220855713</t>
   </si>
   <si>
     <t xml:space="preserve">17.8525505065918</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0242080688477</t>
+    <t xml:space="preserve">18.0242099761963</t>
   </si>
   <si>
     <t xml:space="preserve">18.424747467041</t>
@@ -2066,13 +2063,13 @@
     <t xml:space="preserve">18.5010395050049</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6536254882812</t>
+    <t xml:space="preserve">18.6536273956299</t>
   </si>
   <si>
     <t xml:space="preserve">18.5964069366455</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5582580566406</t>
+    <t xml:space="preserve">18.5582599639893</t>
   </si>
   <si>
     <t xml:space="preserve">18.7108478546143</t>
@@ -2081,16 +2078,16 @@
     <t xml:space="preserve">18.8062114715576</t>
   </si>
   <si>
-    <t xml:space="preserve">18.520112991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5500659942627</t>
+    <t xml:space="preserve">18.5201148986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5500679016113</t>
   </si>
   <si>
     <t xml:space="preserve">19.5023880004883</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8838500976562</t>
+    <t xml:space="preserve">19.8838520050049</t>
   </si>
   <si>
     <t xml:space="preserve">19.9792175292969</t>
@@ -2102,10 +2099,10 @@
     <t xml:space="preserve">19.3593349456787</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1686038970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7871398925781</t>
+    <t xml:space="preserve">19.1686058044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7871417999268</t>
   </si>
   <si>
     <t xml:space="preserve">18.6917743682861</t>
@@ -2114,10 +2111,10 @@
     <t xml:space="preserve">19.2162857055664</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1209182739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7680644989014</t>
+    <t xml:space="preserve">19.1209201812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.76806640625</t>
   </si>
   <si>
     <t xml:space="preserve">17.9097709655762</t>
@@ -2126,40 +2123,40 @@
     <t xml:space="preserve">18.1195755004883</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6236686706543</t>
+    <t xml:space="preserve">17.6236705780029</t>
   </si>
   <si>
     <t xml:space="preserve">17.890697479248</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1005020141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2530879974365</t>
+    <t xml:space="preserve">18.1005001068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2530860900879</t>
   </si>
   <si>
     <t xml:space="preserve">17.9669895172119</t>
   </si>
   <si>
-    <t xml:space="preserve">18.176794052124</t>
+    <t xml:space="preserve">18.1767959594727</t>
   </si>
   <si>
     <t xml:space="preserve">18.9969444274902</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0732364654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9778728485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8825054168701</t>
+    <t xml:space="preserve">19.0732383728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9778709411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8825035095215</t>
   </si>
   <si>
     <t xml:space="preserve">18.9397258758545</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9015769958496</t>
+    <t xml:space="preserve">18.9015789031982</t>
   </si>
   <si>
     <t xml:space="preserve">20.0268993377686</t>
@@ -2168,28 +2165,28 @@
     <t xml:space="preserve">20.2176322937012</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2653141021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7421455383301</t>
+    <t xml:space="preserve">20.2653160095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7421474456787</t>
   </si>
   <si>
     <t xml:space="preserve">20.9328804016113</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2189769744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4573917388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6944618225098</t>
+    <t xml:space="preserve">21.2189788818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4573936462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6944637298584</t>
   </si>
   <si>
     <t xml:space="preserve">20.3129978179932</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4560508728027</t>
+    <t xml:space="preserve">20.4560489654541</t>
   </si>
   <si>
     <t xml:space="preserve">20.980562210083</t>
@@ -2198,25 +2195,25 @@
     <t xml:space="preserve">19.8361682891846</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4083633422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1222667694092</t>
+    <t xml:space="preserve">20.4083652496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1222686767578</t>
   </si>
   <si>
     <t xml:space="preserve">19.3116550445557</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2639694213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.597749710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6454334259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1699466705322</t>
+    <t xml:space="preserve">19.2639713287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5977516174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6454372406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1699485778809</t>
   </si>
   <si>
     <t xml:space="preserve">19.9315338134766</t>
@@ -2228,10 +2225,10 @@
     <t xml:space="preserve">18.8443603515625</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0160179138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0432815551758</t>
+    <t xml:space="preserve">19.016019821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0432834625244</t>
   </si>
   <si>
     <t xml:space="preserve">18.0051345825195</t>
@@ -2243,13 +2240,13 @@
     <t xml:space="preserve">18.0623569488525</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0814266204834</t>
+    <t xml:space="preserve">18.081428527832</t>
   </si>
   <si>
     <t xml:space="preserve">17.6045970916748</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2612800598145</t>
+    <t xml:space="preserve">17.2612819671631</t>
   </si>
   <si>
     <t xml:space="preserve">17.0514736175537</t>
@@ -2258,28 +2255,28 @@
     <t xml:space="preserve">16.2885456085205</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0324001312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7272319793701</t>
+    <t xml:space="preserve">17.0324020385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7272300720215</t>
   </si>
   <si>
     <t xml:space="preserve">16.4792766571045</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8225955963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0705471038818</t>
+    <t xml:space="preserve">16.8225936889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0705490112305</t>
   </si>
   <si>
     <t xml:space="preserve">16.6509342193604</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8607444763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3076190948486</t>
+    <t xml:space="preserve">16.8607425689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3076171875</t>
   </si>
   <si>
     <t xml:space="preserve">16.5937175750732</t>
@@ -2288,31 +2285,31 @@
     <t xml:space="preserve">16.6318626403809</t>
   </si>
   <si>
-    <t xml:space="preserve">15.277663230896</t>
+    <t xml:space="preserve">15.2776641845703</t>
   </si>
   <si>
     <t xml:space="preserve">14.8771257400513</t>
   </si>
   <si>
-    <t xml:space="preserve">14.495659828186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3730306625366</t>
+    <t xml:space="preserve">14.4956607818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3730316162109</t>
   </si>
   <si>
     <t xml:space="preserve">14.9915647506714</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0869302749634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.678201675415</t>
+    <t xml:space="preserve">15.0869312286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6782007217407</t>
   </si>
   <si>
     <t xml:space="preserve">15.1441507339478</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9452257156372</t>
+    <t xml:space="preserve">15.9452247619629</t>
   </si>
   <si>
     <t xml:space="preserve">16.0787410736084</t>
@@ -2321,168 +2318,171 @@
     <t xml:space="preserve">16.0405921936035</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5746421813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6890830993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5174217224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.498348236084</t>
+    <t xml:space="preserve">16.5746440887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6890850067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5174236297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4983501434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7354211807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8880052566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5065412521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9724912643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3348827362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2204427719116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9152717590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.781759262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8961992263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6400547027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0978126525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2395153045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1060047149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0063877105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1999359130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3547744750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0450973510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1418704986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2773532867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4709033966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7805767059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1483173370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.767671585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.419282913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2321853637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7289600372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9418659210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4967041015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5934791564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4579963684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8967037200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4515476226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9870338439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8321962356567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9483232498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3676805496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4450988769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1741333007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1160688400269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.135422706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3289709091187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.619291305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8902597427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7547750473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8128395080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.161226272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6580018997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.870903968811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4128360748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4321899414062</t>
   </si>
   <si>
     <t xml:space="preserve">15.7354202270508</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8880052566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5065402984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9724912643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3348827362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2204437255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9152727127075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.781759262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8961992263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6400547027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0978126525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2395162582397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1060047149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0063896179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1999359130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3547744750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0450973510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1418704986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2773532867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4709014892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7805786132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1483173370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.767671585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4192848205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2321834564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7289619445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9418640136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4967041015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5934772491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4579944610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8967056274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4515476226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9870338439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8321952819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9483222961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3676795959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4450988769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1741333007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1160678863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1354236602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3289709091187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.619291305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8902606964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7547760009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.812840461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.161226272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6580018997192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.870903968811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4128360748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4321918487549</t>
-  </si>
-  <si>
     <t xml:space="preserve">15.7160663604736</t>
   </si>
   <si>
@@ -2504,10 +2504,10 @@
     <t xml:space="preserve">17.5354137420654</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3805751800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3418655395508</t>
+    <t xml:space="preserve">17.3805732727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3418674468994</t>
   </si>
   <si>
     <t xml:space="preserve">17.2063827514648</t>
@@ -2531,16 +2531,16 @@
     <t xml:space="preserve">17.6128330230713</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8192863464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1096076965332</t>
+    <t xml:space="preserve">16.8192882537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1096096038818</t>
   </si>
   <si>
     <t xml:space="preserve">16.7225131988525</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1289653778076</t>
+    <t xml:space="preserve">17.128963470459</t>
   </si>
   <si>
     <t xml:space="preserve">16.8773517608643</t>
@@ -2561,13 +2561,13 @@
     <t xml:space="preserve">15.5031642913818</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2128429412842</t>
+    <t xml:space="preserve">15.2128419876099</t>
   </si>
   <si>
     <t xml:space="preserve">15.3096160888672</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5805835723877</t>
+    <t xml:space="preserve">15.5805826187134</t>
   </si>
   <si>
     <t xml:space="preserve">15.1547775268555</t>
@@ -2588,7 +2588,7 @@
     <t xml:space="preserve">15.5612277984619</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1805801391602</t>
+    <t xml:space="preserve">16.1805782318115</t>
   </si>
   <si>
     <t xml:space="preserve">16.8579978942871</t>
@@ -2597,10 +2597,10 @@
     <t xml:space="preserve">17.3031558990479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9031543731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8063793182373</t>
+    <t xml:space="preserve">17.9031524658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8063812255859</t>
   </si>
   <si>
     <t xml:space="preserve">17.1676731109619</t>
@@ -2615,7 +2615,7 @@
     <t xml:space="preserve">18.735408782959</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6579914093018</t>
+    <t xml:space="preserve">18.6579895019531</t>
   </si>
   <si>
     <t xml:space="preserve">18.4837970733643</t>
@@ -2630,7 +2630,7 @@
     <t xml:space="preserve">18.2515392303467</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8837966918945</t>
+    <t xml:space="preserve">17.8837985992432</t>
   </si>
   <si>
     <t xml:space="preserve">18.0386352539062</t>
@@ -2648,7 +2648,7 @@
     <t xml:space="preserve">18.1547660827637</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0192832946777</t>
+    <t xml:space="preserve">18.0192813873291</t>
   </si>
   <si>
     <t xml:space="preserve">17.9805736541748</t>
@@ -2660,7 +2660,7 @@
     <t xml:space="preserve">17.8450908660889</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6902503967285</t>
+    <t xml:space="preserve">17.6902523040771</t>
   </si>
   <si>
     <t xml:space="preserve">17.6321868896484</t>
@@ -2678,19 +2678,19 @@
     <t xml:space="preserve">17.2644462585449</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7096042633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4773502349854</t>
+    <t xml:space="preserve">17.7096061706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4773483276367</t>
   </si>
   <si>
     <t xml:space="preserve">17.8257369995117</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5805702209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.928955078125</t>
+    <t xml:space="preserve">18.5805721282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9289569854736</t>
   </si>
   <si>
     <t xml:space="preserve">18.8128299713135</t>
@@ -2705,10 +2705,10 @@
     <t xml:space="preserve">19.7902450561523</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0321788787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7418575286865</t>
+    <t xml:space="preserve">20.0321769714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7418556213379</t>
   </si>
   <si>
     <t xml:space="preserve">19.5966968536377</t>
@@ -2717,13 +2717,13 @@
     <t xml:space="preserve">19.9837894439697</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8386306762695</t>
+    <t xml:space="preserve">19.8386287689209</t>
   </si>
   <si>
     <t xml:space="preserve">20.0805644989014</t>
   </si>
   <si>
-    <t xml:space="preserve">20.370885848999</t>
+    <t xml:space="preserve">20.3708839416504</t>
   </si>
   <si>
     <t xml:space="preserve">19.8870162963867</t>
@@ -2738,7 +2738,7 @@
     <t xml:space="preserve">20.177339553833</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4192733764648</t>
+    <t xml:space="preserve">20.4192752838135</t>
   </si>
   <si>
     <t xml:space="preserve">20.467658996582</t>
@@ -2762,10 +2762,10 @@
     <t xml:space="preserve">21.6289443969727</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0644264221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2579746246338</t>
+    <t xml:space="preserve">22.0644283294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2579727172852</t>
   </si>
   <si>
     <t xml:space="preserve">22.6450710296631</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">22.7902297973633</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7418441772461</t>
+    <t xml:space="preserve">22.7418422698975</t>
   </si>
   <si>
     <t xml:space="preserve">21.9676532745361</t>
@@ -2798,31 +2798,31 @@
     <t xml:space="preserve">22.3063621520996</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8224906921387</t>
+    <t xml:space="preserve">21.8224925994873</t>
   </si>
   <si>
     <t xml:space="preserve">22.3547496795654</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1128158569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5482978820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9837799072266</t>
+    <t xml:space="preserve">22.112813949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5482959747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9837779998779</t>
   </si>
   <si>
     <t xml:space="preserve">23.9031295776367</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1934509277344</t>
+    <t xml:space="preserve">24.193452835083</t>
   </si>
   <si>
     <t xml:space="preserve">24.0966758728027</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0160293579102</t>
+    <t xml:space="preserve">25.0160312652588</t>
   </si>
   <si>
     <t xml:space="preserve">24.9676399230957</t>
@@ -2837,22 +2837,22 @@
     <t xml:space="preserve">25.9353790283203</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3547382354736</t>
+    <t xml:space="preserve">25.354736328125</t>
   </si>
   <si>
     <t xml:space="preserve">25.161190032959</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8708667755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2579650878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4515113830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2095756530762</t>
+    <t xml:space="preserve">24.8708686828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.257963180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.451509475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2095737457275</t>
   </si>
   <si>
     <t xml:space="preserve">25.5482845306396</t>
@@ -2870,7 +2870,7 @@
     <t xml:space="preserve">26.9515056610107</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6934452056885</t>
+    <t xml:space="preserve">25.6934432983398</t>
   </si>
   <si>
     <t xml:space="preserve">25.5966720581055</t>
@@ -2882,7 +2882,7 @@
     <t xml:space="preserve">25.8869934082031</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3708610534668</t>
+    <t xml:space="preserve">26.3708629608154</t>
   </si>
   <si>
     <t xml:space="preserve">26.2043304443359</t>
@@ -40079,7 +40079,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1381" t="s">
-        <v>644</v>
+        <v>610</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -40105,7 +40105,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1382" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -40131,7 +40131,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1383" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -40157,7 +40157,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1384" t="s">
-        <v>644</v>
+        <v>610</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -40209,7 +40209,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1386" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -40235,7 +40235,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1387" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -40261,7 +40261,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G1388" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -40313,7 +40313,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1390" t="s">
-        <v>644</v>
+        <v>610</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -40339,7 +40339,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1391" t="s">
-        <v>644</v>
+        <v>610</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -40365,7 +40365,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1392" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -40391,7 +40391,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1393" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -40417,7 +40417,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1394" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -40443,7 +40443,7 @@
         <v>17</v>
       </c>
       <c r="G1395" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -40469,7 +40469,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1396" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -40495,7 +40495,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1397" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -40521,7 +40521,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1398" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -40547,7 +40547,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1399" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -40573,7 +40573,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1400" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -40599,7 +40599,7 @@
         <v>18</v>
       </c>
       <c r="G1401" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -40625,7 +40625,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1402" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -40651,7 +40651,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1403" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -40677,7 +40677,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1404" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -40703,7 +40703,7 @@
         <v>18</v>
       </c>
       <c r="G1405" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -40729,7 +40729,7 @@
         <v>18</v>
       </c>
       <c r="G1406" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -40755,7 +40755,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1407" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -40781,7 +40781,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G1408" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -40807,7 +40807,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1409" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -40833,7 +40833,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1410" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -40859,7 +40859,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1411" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -40885,7 +40885,7 @@
         <v>18</v>
       </c>
       <c r="G1412" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -40911,7 +40911,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G1413" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -40937,7 +40937,7 @@
         <v>18</v>
       </c>
       <c r="G1414" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -40963,7 +40963,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G1415" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -40989,7 +40989,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1416" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -41015,7 +41015,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1417" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -41041,7 +41041,7 @@
         <v>18.5</v>
       </c>
       <c r="G1418" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -41067,7 +41067,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1419" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -41093,7 +41093,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1420" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -41119,7 +41119,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1421" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -41145,7 +41145,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1422" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -41171,7 +41171,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1423" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -41197,7 +41197,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1424" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -41223,7 +41223,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1425" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -41249,7 +41249,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1426" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -41275,7 +41275,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1427" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -41301,7 +41301,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G1428" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -41327,7 +41327,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G1429" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -41353,7 +41353,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1430" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -41379,7 +41379,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1431" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -41405,7 +41405,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1432" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -41431,7 +41431,7 @@
         <v>18.5</v>
       </c>
       <c r="G1433" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -41457,7 +41457,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1434" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -41483,7 +41483,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1435" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -41509,7 +41509,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1436" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -41535,7 +41535,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G1437" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -41561,7 +41561,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1438" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -41587,7 +41587,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1439" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -41613,7 +41613,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1440" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -41639,7 +41639,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1441" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -41665,7 +41665,7 @@
         <v>19.5</v>
       </c>
       <c r="G1442" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -41691,7 +41691,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1443" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -41717,7 +41717,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G1444" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -41743,7 +41743,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1445" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -41769,7 +41769,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1446" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -41795,7 +41795,7 @@
         <v>20.5</v>
       </c>
       <c r="G1447" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -41821,7 +41821,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1448" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -41847,7 +41847,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1449" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -41873,7 +41873,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1450" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -41899,7 +41899,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1451" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -41925,7 +41925,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1452" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -41951,7 +41951,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1453" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -41977,7 +41977,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1454" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -42003,7 +42003,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1455" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -42029,7 +42029,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1456" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -42055,7 +42055,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1457" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -42081,7 +42081,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1458" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -42107,7 +42107,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1459" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -42133,7 +42133,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G1460" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -42159,7 +42159,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1461" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -42185,7 +42185,7 @@
         <v>19</v>
       </c>
       <c r="G1462" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -42211,7 +42211,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1463" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -42237,7 +42237,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G1464" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -42263,7 +42263,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1465" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -42289,7 +42289,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G1466" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -42315,7 +42315,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G1467" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -42341,7 +42341,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1468" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -42367,7 +42367,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1469" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -42393,7 +42393,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1470" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -42419,7 +42419,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1471" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -42445,7 +42445,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1472" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -42471,7 +42471,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G1473" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -42497,7 +42497,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1474" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -42523,7 +42523,7 @@
         <v>20</v>
       </c>
       <c r="G1475" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -42549,7 +42549,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1476" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -42575,7 +42575,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1477" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -42601,7 +42601,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1478" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -42627,7 +42627,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G1479" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -42653,7 +42653,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1480" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -42679,7 +42679,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1481" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -42705,7 +42705,7 @@
         <v>20</v>
       </c>
       <c r="G1482" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -42731,7 +42731,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1483" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -42757,7 +42757,7 @@
         <v>20</v>
       </c>
       <c r="G1484" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -42783,7 +42783,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1485" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -42809,7 +42809,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1486" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -42835,7 +42835,7 @@
         <v>20</v>
       </c>
       <c r="G1487" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -42861,7 +42861,7 @@
         <v>20</v>
       </c>
       <c r="G1488" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -42887,7 +42887,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G1489" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -42913,7 +42913,7 @@
         <v>20</v>
       </c>
       <c r="G1490" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -42939,7 +42939,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1491" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -42965,7 +42965,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1492" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -42991,7 +42991,7 @@
         <v>21</v>
       </c>
       <c r="G1493" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -43017,7 +43017,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1494" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -43043,7 +43043,7 @@
         <v>21.25</v>
       </c>
       <c r="G1495" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -43069,7 +43069,7 @@
         <v>21.75</v>
       </c>
       <c r="G1496" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -43095,7 +43095,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G1497" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -43121,7 +43121,7 @@
         <v>22.25</v>
       </c>
       <c r="G1498" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -43147,7 +43147,7 @@
         <v>22.5</v>
       </c>
       <c r="G1499" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -43173,7 +43173,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1500" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -43199,7 +43199,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1501" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -43225,7 +43225,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G1502" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -43251,7 +43251,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1503" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -43277,7 +43277,7 @@
         <v>22</v>
       </c>
       <c r="G1504" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -43303,7 +43303,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1505" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -43329,7 +43329,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1506" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -43355,7 +43355,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1507" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -43381,7 +43381,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1508" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -43407,7 +43407,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1509" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -43433,7 +43433,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1510" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -43459,7 +43459,7 @@
         <v>20.25</v>
       </c>
       <c r="G1511" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -43485,7 +43485,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1512" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -43511,7 +43511,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1513" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -43537,7 +43537,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1514" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -43563,7 +43563,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1515" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -43589,7 +43589,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G1516" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -43615,7 +43615,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1517" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -43641,7 +43641,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1518" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -43667,7 +43667,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1519" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -43693,7 +43693,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1520" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -43719,7 +43719,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1521" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -43745,7 +43745,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1522" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -43771,7 +43771,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1523" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -43797,7 +43797,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1524" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -43823,7 +43823,7 @@
         <v>21</v>
       </c>
       <c r="G1525" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -43849,7 +43849,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1526" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -43875,7 +43875,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1527" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -43901,7 +43901,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1528" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -43927,7 +43927,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1529" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -43953,7 +43953,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1530" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -43979,7 +43979,7 @@
         <v>20.5</v>
       </c>
       <c r="G1531" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -44005,7 +44005,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G1532" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -44031,7 +44031,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1533" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -44057,7 +44057,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1534" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -44083,7 +44083,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1535" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -44109,7 +44109,7 @@
         <v>20</v>
       </c>
       <c r="G1536" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -44135,7 +44135,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1537" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -44161,7 +44161,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1538" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -44187,7 +44187,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G1539" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -44213,7 +44213,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1540" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -44239,7 +44239,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1541" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -44265,7 +44265,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G1542" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -44291,7 +44291,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1543" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -44317,7 +44317,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1544" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -44343,7 +44343,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1545" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -44369,7 +44369,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G1546" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -44395,7 +44395,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G1547" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -44421,7 +44421,7 @@
         <v>19</v>
       </c>
       <c r="G1548" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -44447,7 +44447,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G1549" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -44473,7 +44473,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G1550" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -44499,7 +44499,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1551" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -44525,7 +44525,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G1552" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -44551,7 +44551,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G1553" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -44577,7 +44577,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1554" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -44603,7 +44603,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1555" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -44629,7 +44629,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1556" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -44655,7 +44655,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1557" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -44681,7 +44681,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G1558" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -44707,7 +44707,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1559" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -44733,7 +44733,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1560" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -44759,7 +44759,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G1561" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -44785,7 +44785,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1562" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -44811,7 +44811,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1563" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -44837,7 +44837,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G1564" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -44863,7 +44863,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1565" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -44889,7 +44889,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1566" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -44915,7 +44915,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1567" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -44941,7 +44941,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1568" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -44967,7 +44967,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1569" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -44993,7 +44993,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G1570" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -45019,7 +45019,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G1571" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -45045,7 +45045,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1572" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -45071,7 +45071,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1573" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -45097,7 +45097,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G1574" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -45123,7 +45123,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G1575" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -45149,7 +45149,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1576" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -45175,7 +45175,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1577" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -45201,7 +45201,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1578" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -45227,7 +45227,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1579" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -45253,7 +45253,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G1580" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -45279,7 +45279,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1581" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -45305,7 +45305,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1582" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -45331,7 +45331,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1583" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -45357,7 +45357,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1584" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -45383,7 +45383,7 @@
         <v>17</v>
       </c>
       <c r="G1585" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -45409,7 +45409,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G1586" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -45435,7 +45435,7 @@
         <v>17.5</v>
       </c>
       <c r="G1587" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -45461,7 +45461,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1588" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -45487,7 +45487,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1589" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -45513,7 +45513,7 @@
         <v>16.5</v>
       </c>
       <c r="G1590" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -45539,7 +45539,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1591" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -45617,7 +45617,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G1594" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -45643,7 +45643,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G1595" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -45695,7 +45695,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1597" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -45747,7 +45747,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G1599" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -45773,7 +45773,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G1600" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -45799,7 +45799,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1601" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -45825,7 +45825,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1602" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -45851,7 +45851,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G1603" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -45877,7 +45877,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1604" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -45903,7 +45903,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1605" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -45929,7 +45929,7 @@
         <v>15.5</v>
       </c>
       <c r="G1606" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -45955,7 +45955,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G1607" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -45981,7 +45981,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1608" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -46033,7 +46033,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G1610" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -46085,7 +46085,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1612" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -46163,7 +46163,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G1615" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -46215,7 +46215,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1617" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -46241,7 +46241,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G1618" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -46267,7 +46267,7 @@
         <v>16.5</v>
       </c>
       <c r="G1619" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -46293,7 +46293,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1620" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -46319,7 +46319,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1621" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -46345,7 +46345,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1622" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -46371,7 +46371,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G1623" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -46397,7 +46397,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1624" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -46423,7 +46423,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1625" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -46449,7 +46449,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1626" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -46475,7 +46475,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1627" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -46501,7 +46501,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1628" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -46527,7 +46527,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G1629" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -46553,7 +46553,7 @@
         <v>18</v>
       </c>
       <c r="G1630" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -46579,7 +46579,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1631" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -46605,7 +46605,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1632" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -46631,7 +46631,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1633" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -46657,7 +46657,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1634" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -46683,7 +46683,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1635" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -46709,7 +46709,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1636" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -46735,7 +46735,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1637" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -46761,7 +46761,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1638" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -46787,7 +46787,7 @@
         <v>17</v>
       </c>
       <c r="G1639" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -46813,7 +46813,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1640" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -46839,7 +46839,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1641" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -46865,7 +46865,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1642" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -46891,7 +46891,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1643" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -46917,7 +46917,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1644" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -46943,7 +46943,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1645" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -46969,7 +46969,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1646" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -46995,7 +46995,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G1647" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -47021,7 +47021,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1648" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -47047,7 +47047,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G1649" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -47073,7 +47073,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1650" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -47099,7 +47099,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G1651" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -47125,7 +47125,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G1652" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -47151,7 +47151,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1653" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -47177,7 +47177,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1654" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -47203,7 +47203,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1655" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -47229,7 +47229,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G1656" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -47255,7 +47255,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1657" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -47281,7 +47281,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1658" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -47307,7 +47307,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1659" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -47333,7 +47333,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G1660" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -47359,7 +47359,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1661" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -47385,7 +47385,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G1662" t="s">
-        <v>773</v>
+        <v>822</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -47463,7 +47463,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1665" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -47489,7 +47489,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1666" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -47515,7 +47515,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G1667" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -47541,7 +47541,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1668" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -47567,7 +47567,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1669" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -47983,7 +47983,7 @@
         <v>18</v>
       </c>
       <c r="G1685" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -48035,7 +48035,7 @@
         <v>18</v>
       </c>
       <c r="G1687" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -48087,7 +48087,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1689" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -48217,7 +48217,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1694" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -48243,7 +48243,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1695" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -48295,7 +48295,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1697" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -48399,7 +48399,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1701" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -48477,7 +48477,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1704" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -48503,7 +48503,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1705" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -48555,7 +48555,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1707" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -48607,7 +48607,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G1709" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -48659,7 +48659,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1711" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -48997,7 +48997,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1724" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -49049,7 +49049,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1726" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -49101,7 +49101,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1728" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -49283,7 +49283,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1735" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -49413,7 +49413,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1740" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -49465,7 +49465,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1742" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -49491,7 +49491,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1743" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -49985,7 +49985,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1762" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -50063,7 +50063,7 @@
         <v>18</v>
       </c>
       <c r="G1765" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -50115,7 +50115,7 @@
         <v>18</v>
       </c>
       <c r="G1767" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -50349,7 +50349,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1776" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -50427,7 +50427,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1779" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -50557,7 +50557,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1784" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -50635,7 +50635,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1787" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -69363,7 +69363,7 @@
     </row>
     <row r="2508">
       <c r="A2508" s="1" t="n">
-        <v>45971.6912615741</v>
+        <v>45971.3333333333</v>
       </c>
       <c r="B2508" t="n">
         <v>41282</v>
@@ -69384,6 +69384,32 @@
         <v>1276</v>
       </c>
       <c r="H2508" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2509">
+      <c r="A2509" s="1" t="n">
+        <v>45972.6913078704</v>
+      </c>
+      <c r="B2509" t="n">
+        <v>34278</v>
+      </c>
+      <c r="C2509" t="n">
+        <v>50.2000007629395</v>
+      </c>
+      <c r="D2509" t="n">
+        <v>49.1500015258789</v>
+      </c>
+      <c r="E2509" t="n">
+        <v>49.4500007629395</v>
+      </c>
+      <c r="F2509" t="n">
+        <v>49.7000007629395</v>
+      </c>
+      <c r="G2509" t="s">
+        <v>1265</v>
+      </c>
+      <c r="H2509" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SOL.MI.xlsx
+++ b/data/SOL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1279" uniqueCount="1279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="1280">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14939117431641</t>
+    <t xml:space="preserve">7.14939069747925</t>
   </si>
   <si>
     <t xml:space="preserve">SOL.MI</t>
@@ -47,88 +47,88 @@
     <t xml:space="preserve">7.14067268371582</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18862628936768</t>
+    <t xml:space="preserve">7.18862676620483</t>
   </si>
   <si>
     <t xml:space="preserve">7.16246938705444</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0622034072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90962553024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90526628494263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94885969161987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71781253814697</t>
+    <t xml:space="preserve">7.06220483779907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90962505340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90526580810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94885921478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71781158447266</t>
   </si>
   <si>
     <t xml:space="preserve">6.62626504898071</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71345281600952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29931163787842</t>
+    <t xml:space="preserve">6.71345233917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2993106842041</t>
   </si>
   <si>
     <t xml:space="preserve">6.36470174789429</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43009328842163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41265439987183</t>
+    <t xml:space="preserve">6.43009233474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41265487670898</t>
   </si>
   <si>
     <t xml:space="preserve">6.44753074645996</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20776414871216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17288875579834</t>
+    <t xml:space="preserve">6.20776462554932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17288970947266</t>
   </si>
   <si>
     <t xml:space="preserve">6.46060848236084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54779624938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38213920593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51292085647583</t>
+    <t xml:space="preserve">6.54779672622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38213968276978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51292037963867</t>
   </si>
   <si>
     <t xml:space="preserve">6.5042028427124</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65242195129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80064058303833</t>
+    <t xml:space="preserve">6.65242147445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80064153671265</t>
   </si>
   <si>
     <t xml:space="preserve">6.72217130661011</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79192161560059</t>
+    <t xml:space="preserve">6.79192209243774</t>
   </si>
   <si>
     <t xml:space="preserve">7.00989151000977</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84423494338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0796422958374</t>
+    <t xml:space="preserve">6.84423446655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07964181900024</t>
   </si>
   <si>
     <t xml:space="preserve">6.88346910476685</t>
@@ -137,73 +137,73 @@
     <t xml:space="preserve">6.96629667282104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08836030960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7352499961853</t>
+    <t xml:space="preserve">7.08836078643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73524904251099</t>
   </si>
   <si>
     <t xml:space="preserve">6.8311562538147</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6785774230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57395172119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63062429428101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68729639053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78320360183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77884435653687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81371831893921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80935955047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79628086090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69601488113403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8180775642395</t>
+    <t xml:space="preserve">6.67857694625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57395219802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63062477111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68729686737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.783203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77884340286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81371879577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80935859680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79628133773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69601535797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81807804107666</t>
   </si>
   <si>
     <t xml:space="preserve">6.87474966049194</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91398477554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67421817779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55215644836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46496725082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43881225585938</t>
+    <t xml:space="preserve">6.9139838218689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67421865463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55215549468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46496772766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43881177902222</t>
   </si>
   <si>
     <t xml:space="preserve">6.73089027404785</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87911033630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85295343399048</t>
+    <t xml:space="preserve">6.87910938262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85295391082764</t>
   </si>
   <si>
     <t xml:space="preserve">6.84859371185303</t>
@@ -215,73 +215,73 @@
     <t xml:space="preserve">6.74832725524902</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51728057861328</t>
+    <t xml:space="preserve">6.51728010177612</t>
   </si>
   <si>
     <t xml:space="preserve">6.37342071533203</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56523323059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66985893249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77012491226196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86167192459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97501611709595</t>
+    <t xml:space="preserve">6.56523370742798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66985845565796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7701244354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86167240142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97501564025879</t>
   </si>
   <si>
     <t xml:space="preserve">6.9416298866272</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95048427581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88407850265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9017858505249</t>
+    <t xml:space="preserve">6.95048379898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88407754898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90178632736206</t>
   </si>
   <si>
     <t xml:space="preserve">7.34006452560425</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22496128082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41975212097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43746042251587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36662721633911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26037788391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46844911575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40204381942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44631481170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3843355178833</t>
+    <t xml:space="preserve">7.22496175765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41975259780884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43745994567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36662769317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26037740707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46845006942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40204334259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44631433486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38433504104614</t>
   </si>
   <si>
     <t xml:space="preserve">7.04345178604126</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97261905670166</t>
+    <t xml:space="preserve">6.9726185798645</t>
   </si>
   <si>
     <t xml:space="preserve">7.1098575592041</t>
@@ -293,43 +293,43 @@
     <t xml:space="preserve">7.20725345611572</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37105464935303</t>
+    <t xml:space="preserve">7.37105417251587</t>
   </si>
   <si>
     <t xml:space="preserve">7.57027196884155</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69423055648804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70308494567871</t>
+    <t xml:space="preserve">7.69422960281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70308351516724</t>
   </si>
   <si>
     <t xml:space="preserve">7.71193838119507</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6588134765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04396820068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61454248428345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29579448699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99475479125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1010046005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55256366729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31350374221802</t>
+    <t xml:space="preserve">7.65881252288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04396724700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61454153060913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2957935333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99475431442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10100364685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55256414413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31350326538086</t>
   </si>
   <si>
     <t xml:space="preserve">7.50829267501831</t>
@@ -338,55 +338,55 @@
     <t xml:space="preserve">7.4241795539856</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37548065185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5260009765625</t>
+    <t xml:space="preserve">7.37548112869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52600240707397</t>
   </si>
   <si>
     <t xml:space="preserve">7.54371023178101</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41532611846924</t>
+    <t xml:space="preserve">7.4153265953064</t>
   </si>
   <si>
     <t xml:space="preserve">7.2161078453064</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99032783508301</t>
+    <t xml:space="preserve">6.99032735824585</t>
   </si>
   <si>
     <t xml:space="preserve">6.79996347427368</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7556939125061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00803518295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26923227310181</t>
+    <t xml:space="preserve">6.75569343566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00803565979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26923179626465</t>
   </si>
   <si>
     <t xml:space="preserve">7.34449243545532</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46402359008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51714706420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39319086074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45516872406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17183637619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33563756942749</t>
+    <t xml:space="preserve">7.46402311325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5171480178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39318943023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45516920089722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17183780670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33563804626465</t>
   </si>
   <si>
     <t xml:space="preserve">7.33121109008789</t>
@@ -395,7 +395,7 @@
     <t xml:space="preserve">7.39761543273926</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30464792251587</t>
+    <t xml:space="preserve">7.30464887619019</t>
   </si>
   <si>
     <t xml:space="preserve">7.27808618545532</t>
@@ -410,34 +410,34 @@
     <t xml:space="preserve">7.03017044067383</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87965106964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91064023971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95491075515747</t>
+    <t xml:space="preserve">6.87965059280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91064071655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95491123199463</t>
   </si>
   <si>
     <t xml:space="preserve">6.88850545883179</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95933818817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85751628875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77340126037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74683952331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82652568817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68486022949219</t>
+    <t xml:space="preserve">6.95933866500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85751581192017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77340078353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74683904647827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82652616500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68486070632935</t>
   </si>
   <si>
     <t xml:space="preserve">6.81767177581787</t>
@@ -458,10 +458,10 @@
     <t xml:space="preserve">6.86194276809692</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92392110824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97704648971558</t>
+    <t xml:space="preserve">6.92392158508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97704601287842</t>
   </si>
   <si>
     <t xml:space="preserve">7.00360870361328</t>
@@ -473,28 +473,28 @@
     <t xml:space="preserve">6.91949415206909</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93720245361328</t>
+    <t xml:space="preserve">6.93720293045044</t>
   </si>
   <si>
     <t xml:space="preserve">7.07001447677612</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98590135574341</t>
+    <t xml:space="preserve">6.98589992523193</t>
   </si>
   <si>
     <t xml:space="preserve">6.75126647949219</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77782821655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64944362640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38381958007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37053966522217</t>
+    <t xml:space="preserve">6.77782869338989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64944410324097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38382005691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37053871154785</t>
   </si>
   <si>
     <t xml:space="preserve">6.36168479919434</t>
@@ -503,10 +503,10 @@
     <t xml:space="preserve">6.37939310073853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40595579147339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48121500015259</t>
+    <t xml:space="preserve">6.40595531463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4812159538269</t>
   </si>
   <si>
     <t xml:space="preserve">6.47678804397583</t>
@@ -515,28 +515,28 @@
     <t xml:space="preserve">6.54319429397583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46350717544556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24215412139893</t>
+    <t xml:space="preserve">6.46350765228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24215507507324</t>
   </si>
   <si>
     <t xml:space="preserve">6.25986289978027</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22444677352905</t>
+    <t xml:space="preserve">6.22444581985474</t>
   </si>
   <si>
     <t xml:space="preserve">6.64501667022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64058971405029</t>
+    <t xml:space="preserve">6.64059019088745</t>
   </si>
   <si>
     <t xml:space="preserve">7.0390248298645</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79110956192017</t>
+    <t xml:space="preserve">6.79111003875732</t>
   </si>
   <si>
     <t xml:space="preserve">6.70256853103638</t>
@@ -545,82 +545,82 @@
     <t xml:space="preserve">6.70699548721313</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65829849243164</t>
+    <t xml:space="preserve">6.65829801559448</t>
   </si>
   <si>
     <t xml:space="preserve">6.58303785324097</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05673313140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11428451538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34891986846924</t>
+    <t xml:space="preserve">7.05673265457153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11428546905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34891939163208</t>
   </si>
   <si>
     <t xml:space="preserve">7.18511772155762</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12756586074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19397258758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24266910552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41089773178101</t>
+    <t xml:space="preserve">7.12756681442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19397211074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24267053604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41089916229248</t>
   </si>
   <si>
     <t xml:space="preserve">7.48173093795776</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14527368545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27365922927856</t>
+    <t xml:space="preserve">7.14527416229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27365875244141</t>
   </si>
   <si>
     <t xml:space="preserve">7.17626333236694</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04787921905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23381471633911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29136800765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42860651016235</t>
+    <t xml:space="preserve">7.04787969589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23381567001343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29136657714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42860746383667</t>
   </si>
   <si>
     <t xml:space="preserve">7.83589649200439</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82704019546509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13693523406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27860260009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32287120819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03120231628418</t>
+    <t xml:space="preserve">7.82704257965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13693618774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27860164642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32287216186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0312032699585</t>
   </si>
   <si>
     <t xml:space="preserve">8.53094482421875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49995422363281</t>
+    <t xml:space="preserve">8.49995517730713</t>
   </si>
   <si>
     <t xml:space="preserve">8.26089382171631</t>
@@ -629,34 +629,34 @@
     <t xml:space="preserve">8.92495346069336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5884952545166</t>
+    <t xml:space="preserve">8.58849334716797</t>
   </si>
   <si>
     <t xml:space="preserve">8.97807693481445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76557922363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87182807922363</t>
+    <t xml:space="preserve">8.76557731628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87182903289795</t>
   </si>
   <si>
     <t xml:space="preserve">9.5624475479126</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25255393981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02234840393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85411834716797</t>
+    <t xml:space="preserve">9.25255489349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02234745025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85411930084229</t>
   </si>
   <si>
     <t xml:space="preserve">8.82755851745605</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71245384216309</t>
+    <t xml:space="preserve">8.7124547958374</t>
   </si>
   <si>
     <t xml:space="preserve">8.98692989349365</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">8.89838981628418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80985069274902</t>
+    <t xml:space="preserve">8.80984973907471</t>
   </si>
   <si>
     <t xml:space="preserve">8.7213077545166</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">8.67703723907471</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75672435760498</t>
+    <t xml:space="preserve">8.7567253112793</t>
   </si>
   <si>
     <t xml:space="preserve">9.10203456878662</t>
@@ -689,124 +689,124 @@
     <t xml:space="preserve">8.94266033172607</t>
   </si>
   <si>
+    <t xml:space="preserve">9.20828437805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43287754058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4598274230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52271461486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32507228851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38795757293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35202407836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42389297485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29812145233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55864810943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67543601989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86409473419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5199041366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0617341995239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88206195831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74730587005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56763172149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44186019897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54067993164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34303951263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36100673675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50474548339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48677921295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61254978179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77425765991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46881008148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5496654510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47779369354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7023868560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30710506439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28015422821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2172679901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16336631774902</t>
+  </si>
+  <si>
     <t xml:space="preserve">9.20828533172607</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43287658691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4598274230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52271270751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32507228851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38795757293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35202503204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42389392852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29812145233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55864810943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67543697357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86409378051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5199031829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0617351531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8820629119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74730587005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56763172149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44186019897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54068088531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34304046630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36100769042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50474452972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48677825927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61255073547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77425765991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46881198883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54966449737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4777946472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70238590240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30710506439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28015327453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2172679901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16336631774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20828437805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25320339202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45084285736084</t>
+    <t xml:space="preserve">9.25320243835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45084381103516</t>
   </si>
   <si>
     <t xml:space="preserve">9.58559894561768</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33405685424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59458255767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66645336151123</t>
+    <t xml:space="preserve">9.33405590057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59458351135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66645431518555</t>
   </si>
   <si>
     <t xml:space="preserve">9.71137046813965</t>
@@ -818,16 +818,16 @@
     <t xml:space="preserve">9.26218605041504</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2711706161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28913688659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36999225616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65746974945068</t>
+    <t xml:space="preserve">9.27116870880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.289137840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36999034881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65746879577637</t>
   </si>
   <si>
     <t xml:space="preserve">9.79222393035889</t>
@@ -839,28 +839,28 @@
     <t xml:space="preserve">9.72035503387451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8101921081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37897300720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.909010887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81917572021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73832321166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78324127197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69340324401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11844635009766</t>
+    <t xml:space="preserve">9.81019115447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37897491455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90901184082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81917381286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73832225799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78324031829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69340419769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11844730377197</t>
   </si>
   <si>
     <t xml:space="preserve">9.08251190185547</t>
@@ -869,7 +869,7 @@
     <t xml:space="preserve">9.31608867645264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19031524658203</t>
+    <t xml:space="preserve">9.19031620025635</t>
   </si>
   <si>
     <t xml:space="preserve">9.10048007965088</t>
@@ -881,64 +881,64 @@
     <t xml:space="preserve">9.41490936279297</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39694213867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07352828979492</t>
+    <t xml:space="preserve">9.39694118499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07353019714355</t>
   </si>
   <si>
     <t xml:space="preserve">9.57661533355713</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68441963195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09149551391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05556201934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14539909362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89385604858398</t>
+    <t xml:space="preserve">9.68441772460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09149742126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05556106567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14540004730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89385414123535</t>
   </si>
   <si>
     <t xml:space="preserve">9.10946369171143</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2352352142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95393085479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5109186172485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.74449634552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.546854019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6905927658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9062023162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7804317474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7085618972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6546592712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5288867950439</t>
+    <t xml:space="preserve">9.23523426055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95392990112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5109195709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7444953918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5468530654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6905918121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9062013626099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7804298400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7085609436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6546583175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5288887023926</t>
   </si>
   <si>
     <t xml:space="preserve">10.4390487670898</t>
@@ -947,19 +947,19 @@
     <t xml:space="preserve">10.3312454223633</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1695384979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1875085830688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1336040496826</t>
+    <t xml:space="preserve">10.1695404052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1875057220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1336030960083</t>
   </si>
   <si>
     <t xml:space="preserve">9.7562894821167</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63051700592041</t>
+    <t xml:space="preserve">9.63051891326904</t>
   </si>
   <si>
     <t xml:space="preserve">10.0078325271606</t>
@@ -968,28 +968,28 @@
     <t xml:space="preserve">9.84612655639648</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0976705551147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.205472946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2773427963257</t>
+    <t xml:space="preserve">10.0976696014404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2054738998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.27734375</t>
   </si>
   <si>
     <t xml:space="preserve">10.2234411239624</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2414083480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7624626159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2593774795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91799449920654</t>
+    <t xml:space="preserve">10.2414093017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7624635696411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2593765258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91799545288086</t>
   </si>
   <si>
     <t xml:space="preserve">9.90002822875977</t>
@@ -998,13 +998,13 @@
     <t xml:space="preserve">9.67380714416504</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74668025970459</t>
+    <t xml:space="preserve">9.74667930603027</t>
   </si>
   <si>
     <t xml:space="preserve">9.87420558929443</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1656951904297</t>
+    <t xml:space="preserve">10.1656932830811</t>
   </si>
   <si>
     <t xml:space="preserve">9.85598850250244</t>
@@ -1016,7 +1016,7 @@
     <t xml:space="preserve">9.47340679168701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76489734649658</t>
+    <t xml:space="preserve">9.7648983001709</t>
   </si>
   <si>
     <t xml:space="preserve">9.96529579162598</t>
@@ -1025,25 +1025,25 @@
     <t xml:space="preserve">10.0746059417725</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2385683059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3843107223511</t>
+    <t xml:space="preserve">10.2385673522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3843116760254</t>
   </si>
   <si>
     <t xml:space="preserve">10.4207487106323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8033294677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.694019317627</t>
+    <t xml:space="preserve">10.8033275604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6940183639526</t>
   </si>
   <si>
     <t xml:space="preserve">10.6211471557617</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7851095199585</t>
+    <t xml:space="preserve">10.7851104736328</t>
   </si>
   <si>
     <t xml:space="preserve">10.5482759475708</t>
@@ -1052,22 +1052,22 @@
     <t xml:space="preserve">10.402530670166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2203493118286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1474771499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3296594619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5847120285034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3478746414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72846221923828</t>
+    <t xml:space="preserve">10.2203502655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1474761962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3296566009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5847110748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3478755950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72846126556396</t>
   </si>
   <si>
     <t xml:space="preserve">9.56449794769287</t>
@@ -1076,10 +1076,10 @@
     <t xml:space="preserve">9.4187536239624</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40053558349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54627895355225</t>
+    <t xml:space="preserve">9.40053462982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54628086090088</t>
   </si>
   <si>
     <t xml:space="preserve">10.1110401153564</t>
@@ -1091,34 +1091,34 @@
     <t xml:space="preserve">9.92885971069336</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0199518203735</t>
+    <t xml:space="preserve">10.0199508666992</t>
   </si>
   <si>
     <t xml:space="preserve">10.2021322250366</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0928230285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80133438110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69202423095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8377685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94707775115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89242267608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65558815002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78311443328857</t>
+    <t xml:space="preserve">10.0928220748901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8013334274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69202613830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83777046203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94707679748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89242172241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65558910369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78311538696289</t>
   </si>
   <si>
     <t xml:space="preserve">9.91064167022705</t>
@@ -1130,55 +1130,55 @@
     <t xml:space="preserve">9.2001371383667</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50984382629395</t>
+    <t xml:space="preserve">9.50984287261963</t>
   </si>
   <si>
     <t xml:space="preserve">9.43697166442871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81955146789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49162578582764</t>
+    <t xml:space="preserve">9.81955051422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49162673950195</t>
   </si>
   <si>
     <t xml:space="preserve">9.6191520690918</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98351383209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60093402862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10904598236084</t>
+    <t xml:space="preserve">9.9835147857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60093307495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10904502868652</t>
   </si>
   <si>
     <t xml:space="preserve">9.09993648529053</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38231658935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36409950256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27301025390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71024227142334</t>
+    <t xml:space="preserve">9.38231754302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36409759521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27300834655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71024322509766</t>
   </si>
   <si>
     <t xml:space="preserve">9.58271598815918</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29122734069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14548110961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3660936355591</t>
+    <t xml:space="preserve">9.29122638702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14548206329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3660945892334</t>
   </si>
   <si>
     <t xml:space="preserve">9.32766342163086</t>
@@ -1187,16 +1187,16 @@
     <t xml:space="preserve">10.0017309188843</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4754028320312</t>
+    <t xml:space="preserve">10.4754018783569</t>
   </si>
   <si>
     <t xml:space="preserve">10.8397626876831</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5664930343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3114385604858</t>
+    <t xml:space="preserve">10.5664939880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3114395141602</t>
   </si>
   <si>
     <t xml:space="preserve">10.2932224273682</t>
@@ -1205,43 +1205,43 @@
     <t xml:space="preserve">10.0381679534912</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0563850402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1292600631714</t>
+    <t xml:space="preserve">10.0563859939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1292591094971</t>
   </si>
   <si>
     <t xml:space="preserve">10.2750034332275</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1839141845703</t>
+    <t xml:space="preserve">10.183913230896</t>
   </si>
   <si>
     <t xml:space="preserve">10.6758012771606</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7122383117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9308557510376</t>
+    <t xml:space="preserve">10.7122392654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.930853843689</t>
   </si>
   <si>
     <t xml:space="preserve">11.0219459533691</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8762006759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.894419670105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7304553985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6575832366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2644634246826</t>
+    <t xml:space="preserve">10.87619972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8944187164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7304563522339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6575841903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2644643783569</t>
   </si>
   <si>
     <t xml:space="preserve">11.1349868774414</t>
@@ -1250,19 +1250,19 @@
     <t xml:space="preserve">11.097993850708</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2459659576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.319953918457</t>
+    <t xml:space="preserve">11.2459669113159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3199529647827</t>
   </si>
   <si>
     <t xml:space="preserve">11.0240068435669</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8205432891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8390407562256</t>
+    <t xml:space="preserve">10.8205442428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8390417098999</t>
   </si>
   <si>
     <t xml:space="preserve">10.7280607223511</t>
@@ -1271,13 +1271,13 @@
     <t xml:space="preserve">10.8575372695923</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7095642089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6725702285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.65407371521</t>
+    <t xml:space="preserve">10.7095632553101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.672571182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6540746688843</t>
   </si>
   <si>
     <t xml:space="preserve">10.7835493087769</t>
@@ -1286,16 +1286,16 @@
     <t xml:space="preserve">10.7650537490845</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8020477294922</t>
+    <t xml:space="preserve">10.8020486831665</t>
   </si>
   <si>
     <t xml:space="preserve">10.5615911483765</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6170797348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3951206207275</t>
+    <t xml:space="preserve">10.6170787811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3951196670532</t>
   </si>
   <si>
     <t xml:space="preserve">10.1176700592041</t>
@@ -1304,34 +1304,34 @@
     <t xml:space="preserve">10.284140586853</t>
   </si>
   <si>
-    <t xml:space="preserve">10.265643119812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.302638053894</t>
+    <t xml:space="preserve">10.2656440734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3026371002197</t>
   </si>
   <si>
     <t xml:space="preserve">10.5060997009277</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3396310806274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1361665725708</t>
+    <t xml:space="preserve">10.3396301269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1361675262451</t>
   </si>
   <si>
     <t xml:space="preserve">10.0806770324707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98819351196289</t>
+    <t xml:space="preserve">9.98819446563721</t>
   </si>
   <si>
     <t xml:space="preserve">10.0991735458374</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93270492553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89571189880371</t>
+    <t xml:space="preserve">9.93270397186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89571094512939</t>
   </si>
   <si>
     <t xml:space="preserve">9.96969795227051</t>
@@ -1340,13 +1340,13 @@
     <t xml:space="preserve">10.1731615066528</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0621814727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1546630859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71074390411377</t>
+    <t xml:space="preserve">10.062180519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1546640396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71074485778809</t>
   </si>
   <si>
     <t xml:space="preserve">10.0251874923706</t>
@@ -1358,31 +1358,31 @@
     <t xml:space="preserve">9.76623439788818</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72924041748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65525341033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67375087738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47028923034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54427433013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56277084350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45179080963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35930824279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52577686309814</t>
+    <t xml:space="preserve">9.7292423248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65525436401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67374992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47028827667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54427528381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56277179718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45179176330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35930728912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52577877044678</t>
   </si>
   <si>
     <t xml:space="preserve">9.59976387023926</t>
@@ -1391,10 +1391,10 @@
     <t xml:space="preserve">9.61826133728027</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69224739074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80322742462158</t>
+    <t xml:space="preserve">9.69224834442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8032283782959</t>
   </si>
   <si>
     <t xml:space="preserve">10.2286510467529</t>
@@ -1406,61 +1406,61 @@
     <t xml:space="preserve">9.858717918396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0066909790039</t>
+    <t xml:space="preserve">10.0066900253296</t>
   </si>
   <si>
     <t xml:space="preserve">9.8772144317627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74773788452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58126831054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3211345672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4321146011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3766241073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2471466064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2101535797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84022045135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63675785064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43329524993896</t>
+    <t xml:space="preserve">9.74773693084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58126735687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3211336135864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4321136474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3766231536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2471494674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2101545333862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84021949768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63675880432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43329334259033</t>
   </si>
   <si>
     <t xml:space="preserve">9.41479778289795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39630031585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24832630157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06336212158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1096019744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32231426239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28532028198242</t>
+    <t xml:space="preserve">9.39630126953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24832725524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06336116790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10960292816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32231330871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28532123565674</t>
   </si>
   <si>
     <t xml:space="preserve">9.26682472229004</t>
@@ -1469,55 +1469,55 @@
     <t xml:space="preserve">9.19283771514893</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22983169555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48878479003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0263671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9708776473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13734722137451</t>
+    <t xml:space="preserve">9.22983074188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48878383636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02636814117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97087860107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13734912872314</t>
   </si>
   <si>
     <t xml:space="preserve">8.96162891387939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82290363311768</t>
+    <t xml:space="preserve">8.82290458679199</t>
   </si>
   <si>
     <t xml:space="preserve">8.61944198608398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55470180511475</t>
+    <t xml:space="preserve">8.55470275878906</t>
   </si>
   <si>
     <t xml:space="preserve">8.36048889160156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33274269104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0182991027832</t>
+    <t xml:space="preserve">8.33274459838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01830005645752</t>
   </si>
   <si>
     <t xml:space="preserve">7.81483697891235</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95356273651123</t>
+    <t xml:space="preserve">7.95356178283691</t>
   </si>
   <si>
     <t xml:space="preserve">7.49114561080933</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86107778549194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50964260101318</t>
+    <t xml:space="preserve">7.86107921600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50964164733887</t>
   </si>
   <si>
     <t xml:space="preserve">7.53738689422607</t>
@@ -1529,22 +1529,22 @@
     <t xml:space="preserve">8.76741409301758</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9893741607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16509342193604</t>
+    <t xml:space="preserve">8.98937511444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16509246826172</t>
   </si>
   <si>
     <t xml:space="preserve">9.12809944152832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09110641479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08185863494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34081172943115</t>
+    <t xml:space="preserve">9.09110736846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08185768127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34081077575684</t>
   </si>
   <si>
     <t xml:space="preserve">9.04486465454102</t>
@@ -1565,37 +1565,37 @@
     <t xml:space="preserve">9.11885070800781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78591060638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89689159393311</t>
+    <t xml:space="preserve">8.78591156005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89689064025879</t>
   </si>
   <si>
     <t xml:space="preserve">8.74891757965088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80440998077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87839412689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93388652801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63793754577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71192359924316</t>
+    <t xml:space="preserve">8.80440616607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87839603424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9338846206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63793659210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7119255065918</t>
   </si>
   <si>
     <t xml:space="preserve">8.58244800567627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69342803955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46113967895508</t>
+    <t xml:space="preserve">8.69342708587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46113872528076</t>
   </si>
   <si>
     <t xml:space="preserve">9.6494197845459</t>
@@ -1610,16 +1610,16 @@
     <t xml:space="preserve">9.97891235351562</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93184280395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7906322479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0730543136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3084049224854</t>
+    <t xml:space="preserve">9.93184185028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79063129425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0730533599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3084058761597</t>
   </si>
   <si>
     <t xml:space="preserve">10.4496164321899</t>
@@ -1628,16 +1628,16 @@
     <t xml:space="preserve">10.1671943664551</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1201229095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0259819030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2142639160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3554763793945</t>
+    <t xml:space="preserve">10.1201238632202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0259828567505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2142648696899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3554754257202</t>
   </si>
   <si>
     <t xml:space="preserve">10.2613344192505</t>
@@ -1646,13 +1646,13 @@
     <t xml:space="preserve">9.88477230072021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5908269882202</t>
+    <t xml:space="preserve">10.5908279418945</t>
   </si>
   <si>
     <t xml:space="preserve">10.4966859817505</t>
   </si>
   <si>
-    <t xml:space="preserve">10.543758392334</t>
+    <t xml:space="preserve">10.5437574386597</t>
   </si>
   <si>
     <t xml:space="preserve">11.2027406692505</t>
@@ -1661,10 +1661,10 @@
     <t xml:space="preserve">11.1556711196899</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9673900604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0615310668945</t>
+    <t xml:space="preserve">10.9673891067505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0615301132202</t>
   </si>
   <si>
     <t xml:space="preserve">10.7791090011597</t>
@@ -1673,7 +1673,7 @@
     <t xml:space="preserve">10.8261795043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0144605636597</t>
+    <t xml:space="preserve">11.0144596099854</t>
   </si>
   <si>
     <t xml:space="preserve">11.1086015701294</t>
@@ -1688,13 +1688,13 @@
     <t xml:space="preserve">10.7320375442505</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6378984451294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5322351455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6263751983643</t>
+    <t xml:space="preserve">10.6378974914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5322341918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6263742446899</t>
   </si>
   <si>
     <t xml:space="preserve">11.7675857543945</t>
@@ -1712,10 +1712,10 @@
     <t xml:space="preserve">11.720516204834</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0029373168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.285361289978</t>
+    <t xml:space="preserve">12.0029382705688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2853603363037</t>
   </si>
   <si>
     <t xml:space="preserve">12.5677824020386</t>
@@ -1727,7 +1727,7 @@
     <t xml:space="preserve">12.897274017334</t>
   </si>
   <si>
-    <t xml:space="preserve">12.756064414978</t>
+    <t xml:space="preserve">12.7560634613037</t>
   </si>
   <si>
     <t xml:space="preserve">12.6619215011597</t>
@@ -1748,37 +1748,37 @@
     <t xml:space="preserve">13.1796960830688</t>
   </si>
   <si>
-    <t xml:space="preserve">13.462119102478</t>
+    <t xml:space="preserve">13.4621181488037</t>
   </si>
   <si>
     <t xml:space="preserve">13.838680267334</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7445402145386</t>
+    <t xml:space="preserve">13.7445392608643</t>
   </si>
   <si>
     <t xml:space="preserve">13.6504001617432</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5091896057129</t>
+    <t xml:space="preserve">13.5091905593872</t>
   </si>
   <si>
     <t xml:space="preserve">13.7916107177734</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8857517242432</t>
+    <t xml:space="preserve">13.8857507705688</t>
   </si>
   <si>
     <t xml:space="preserve">13.9798917770386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0269632339478</t>
+    <t xml:space="preserve">14.0269613265991</t>
   </si>
   <si>
     <t xml:space="preserve">14.0740327835083</t>
   </si>
   <si>
-    <t xml:space="preserve">14.168173789978</t>
+    <t xml:space="preserve">14.1681728363037</t>
   </si>
   <si>
     <t xml:space="preserve">14.1211032867432</t>
@@ -1793,13 +1793,13 @@
     <t xml:space="preserve">14.4505949020386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6859474182129</t>
+    <t xml:space="preserve">14.6859483718872</t>
   </si>
   <si>
     <t xml:space="preserve">14.3093843460083</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4035243988037</t>
+    <t xml:space="preserve">14.403525352478</t>
   </si>
   <si>
     <t xml:space="preserve">14.3564548492432</t>
@@ -1811,10 +1811,10 @@
     <t xml:space="preserve">14.5918064117432</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6388778686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7800874710083</t>
+    <t xml:space="preserve">14.638876914978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7800884246826</t>
   </si>
   <si>
     <t xml:space="preserve">14.8271589279175</t>
@@ -1823,10 +1823,10 @@
     <t xml:space="preserve">14.874228477478</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7330179214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.344931602478</t>
+    <t xml:space="preserve">14.7330169677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3449306488037</t>
   </si>
   <si>
     <t xml:space="preserve">15.7685661315918</t>
@@ -1835,16 +1835,16 @@
     <t xml:space="preserve">16.0039157867432</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0415725708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0792274475098</t>
+    <t xml:space="preserve">16.0415744781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0792293548584</t>
   </si>
   <si>
     <t xml:space="preserve">16.1921997070312</t>
   </si>
   <si>
-    <t xml:space="preserve">16.116886138916</t>
+    <t xml:space="preserve">16.1168880462646</t>
   </si>
   <si>
     <t xml:space="preserve">16.2298526763916</t>
@@ -1856,91 +1856,91 @@
     <t xml:space="preserve">16.3993072509766</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4181365966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5311031341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2675113677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9286031723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8909482955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8156328201294</t>
+    <t xml:space="preserve">16.4181385040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5311050415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2675132751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9286041259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8909473419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.815634727478</t>
   </si>
   <si>
     <t xml:space="preserve">15.9662618637085</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7214975357056</t>
+    <t xml:space="preserve">15.7214956283569</t>
   </si>
   <si>
     <t xml:space="preserve">15.5332117080688</t>
   </si>
   <si>
-    <t xml:space="preserve">15.51438331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7026662826538</t>
+    <t xml:space="preserve">15.5143842697144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7026672363281</t>
   </si>
   <si>
     <t xml:space="preserve">15.2696199417114</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4767303466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6838369369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6650094985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4202442169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1566505432129</t>
+    <t xml:space="preserve">15.476731300354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.683837890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6650085449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4202451705933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1566495895386</t>
   </si>
   <si>
     <t xml:space="preserve">15.2319631576538</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7779788970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9833726882935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.964298248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6209812164307</t>
+    <t xml:space="preserve">15.7779779434204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9833717346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9642992019653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.620982170105</t>
   </si>
   <si>
     <t xml:space="preserve">15.4874696731567</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7926406860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8117141723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6019067764282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5446882247925</t>
+    <t xml:space="preserve">15.7926397323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.811713218689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6019077301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5446872711182</t>
   </si>
   <si>
     <t xml:space="preserve">15.2585897445679</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6972742080688</t>
+    <t xml:space="preserve">15.6972732543945</t>
   </si>
   <si>
     <t xml:space="preserve">15.8307876586914</t>
@@ -1955,7 +1955,7 @@
     <t xml:space="preserve">16.2313270568848</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0024471282959</t>
+    <t xml:space="preserve">16.0024452209473</t>
   </si>
   <si>
     <t xml:space="preserve">16.2694702148438</t>
@@ -1967,16 +1967,16 @@
     <t xml:space="preserve">16.460205078125</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4411296844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5364971160889</t>
+    <t xml:space="preserve">16.4411277770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5364952087402</t>
   </si>
   <si>
     <t xml:space="preserve">16.555570602417</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1659126281738</t>
+    <t xml:space="preserve">17.1659145355225</t>
   </si>
   <si>
     <t xml:space="preserve">16.9561100006104</t>
@@ -2000,16 +2000,16 @@
     <t xml:space="preserve">16.9751796722412</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1277675628662</t>
+    <t xml:space="preserve">17.1277656555176</t>
   </si>
   <si>
     <t xml:space="preserve">17.5092315673828</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5473785400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7571849822998</t>
+    <t xml:space="preserve">17.5473766326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7571868896484</t>
   </si>
   <si>
     <t xml:space="preserve">17.6427440643311</t>
@@ -2033,7 +2033,7 @@
     <t xml:space="preserve">17.3566474914551</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2422065734863</t>
+    <t xml:space="preserve">17.2422046661377</t>
   </si>
   <si>
     <t xml:space="preserve">17.1468391418457</t>
@@ -2048,7 +2048,7 @@
     <t xml:space="preserve">17.8334789276123</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6999626159668</t>
+    <t xml:space="preserve">17.6999645233154</t>
   </si>
   <si>
     <t xml:space="preserve">17.8716239929199</t>
@@ -2063,7 +2063,7 @@
     <t xml:space="preserve">18.424747467041</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5010395050049</t>
+    <t xml:space="preserve">18.5010414123535</t>
   </si>
   <si>
     <t xml:space="preserve">18.6536254882812</t>
@@ -2072,7 +2072,7 @@
     <t xml:space="preserve">18.5964069366455</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5582618713379</t>
+    <t xml:space="preserve">18.5582599639893</t>
   </si>
   <si>
     <t xml:space="preserve">18.7108459472656</t>
@@ -2105,22 +2105,22 @@
     <t xml:space="preserve">19.1686038970947</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7871398925781</t>
+    <t xml:space="preserve">18.7871379852295</t>
   </si>
   <si>
     <t xml:space="preserve">18.6917743682861</t>
   </si>
   <si>
-    <t xml:space="preserve">19.216287612915</t>
+    <t xml:space="preserve">19.2162857055664</t>
   </si>
   <si>
     <t xml:space="preserve">19.1209182739258</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7680644989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9097709655762</t>
+    <t xml:space="preserve">18.76806640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9097690582275</t>
   </si>
   <si>
     <t xml:space="preserve">18.1195735931396</t>
@@ -2147,19 +2147,19 @@
     <t xml:space="preserve">18.9969444274902</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0732364654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9778728485107</t>
+    <t xml:space="preserve">19.0732383728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9778709411621</t>
   </si>
   <si>
     <t xml:space="preserve">18.8825054168701</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9397239685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9015769958496</t>
+    <t xml:space="preserve">18.9397258758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9015789031982</t>
   </si>
   <si>
     <t xml:space="preserve">20.0268993377686</t>
@@ -2168,7 +2168,7 @@
     <t xml:space="preserve">20.2176303863525</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2653121948242</t>
+    <t xml:space="preserve">20.2653141021729</t>
   </si>
   <si>
     <t xml:space="preserve">20.7421455383301</t>
@@ -2183,10 +2183,10 @@
     <t xml:space="preserve">21.4573917388916</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6944618225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3129959106445</t>
+    <t xml:space="preserve">20.6944637298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3129978179932</t>
   </si>
   <si>
     <t xml:space="preserve">20.4560489654541</t>
@@ -2201,7 +2201,7 @@
     <t xml:space="preserve">20.4083652496338</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1222667694092</t>
+    <t xml:space="preserve">20.1222648620605</t>
   </si>
   <si>
     <t xml:space="preserve">19.3116512298584</t>
@@ -2219,7 +2219,7 @@
     <t xml:space="preserve">20.1699485778809</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9315338134766</t>
+    <t xml:space="preserve">19.9315319061279</t>
   </si>
   <si>
     <t xml:space="preserve">19.7408008575439</t>
@@ -2234,7 +2234,7 @@
     <t xml:space="preserve">18.0432815551758</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0051364898682</t>
+    <t xml:space="preserve">18.0051383972168</t>
   </si>
   <si>
     <t xml:space="preserve">18.138650894165</t>
@@ -2249,7 +2249,7 @@
     <t xml:space="preserve">17.6045989990234</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2612781524658</t>
+    <t xml:space="preserve">17.2612800598145</t>
   </si>
   <si>
     <t xml:space="preserve">17.0514736175537</t>
@@ -2258,7 +2258,7 @@
     <t xml:space="preserve">16.2885437011719</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0324020385742</t>
+    <t xml:space="preserve">17.0324039459229</t>
   </si>
   <si>
     <t xml:space="preserve">16.7272300720215</t>
@@ -2279,13 +2279,13 @@
     <t xml:space="preserve">16.8607406616211</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3076190948486</t>
+    <t xml:space="preserve">16.3076171875</t>
   </si>
   <si>
     <t xml:space="preserve">16.5937175750732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6318645477295</t>
+    <t xml:space="preserve">16.6318664550781</t>
   </si>
   <si>
     <t xml:space="preserve">15.277663230896</t>
@@ -2294,7 +2294,7 @@
     <t xml:space="preserve">14.8771257400513</t>
   </si>
   <si>
-    <t xml:space="preserve">14.495659828186</t>
+    <t xml:space="preserve">14.4956607818604</t>
   </si>
   <si>
     <t xml:space="preserve">15.3730306625366</t>
@@ -2303,25 +2303,25 @@
     <t xml:space="preserve">14.9915647506714</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0869312286377</t>
+    <t xml:space="preserve">15.086932182312</t>
   </si>
   <si>
     <t xml:space="preserve">15.6782026290894</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1441507339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9452257156372</t>
+    <t xml:space="preserve">15.1441497802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9452266693115</t>
   </si>
   <si>
     <t xml:space="preserve">16.0787410736084</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0405941009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5746402740479</t>
+    <t xml:space="preserve">16.0405921936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5746421813965</t>
   </si>
   <si>
     <t xml:space="preserve">16.6890811920166</t>
@@ -2336,16 +2336,16 @@
     <t xml:space="preserve">15.7354192733765</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8880052566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5065422058105</t>
+    <t xml:space="preserve">15.8880062103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5065431594849</t>
   </si>
   <si>
     <t xml:space="preserve">14.9724912643433</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3348827362061</t>
+    <t xml:space="preserve">15.3348836898804</t>
   </si>
   <si>
     <t xml:space="preserve">15.2204437255859</t>
@@ -2357,7 +2357,7 @@
     <t xml:space="preserve">14.781759262085</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8961992263794</t>
+    <t xml:space="preserve">14.8961982727051</t>
   </si>
   <si>
     <t xml:space="preserve">15.6400547027588</t>
@@ -2366,10 +2366,10 @@
     <t xml:space="preserve">16.0978126525879</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2395162582397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1060047149658</t>
+    <t xml:space="preserve">15.2395153045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1060037612915</t>
   </si>
   <si>
     <t xml:space="preserve">16.0063896179199</t>
@@ -2384,16 +2384,16 @@
     <t xml:space="preserve">16.0450973510742</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1418724060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2773532867432</t>
+    <t xml:space="preserve">16.1418704986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2773551940918</t>
   </si>
   <si>
     <t xml:space="preserve">16.4709014892578</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7805786132812</t>
+    <t xml:space="preserve">16.7805767059326</t>
   </si>
   <si>
     <t xml:space="preserve">17.1483173370361</t>
@@ -2414,13 +2414,13 @@
     <t xml:space="preserve">17.9418640136719</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4967021942139</t>
+    <t xml:space="preserve">17.4967041015625</t>
   </si>
   <si>
     <t xml:space="preserve">17.5934772491455</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4579944610596</t>
+    <t xml:space="preserve">17.4579963684082</t>
   </si>
   <si>
     <t xml:space="preserve">16.8967056274414</t>
@@ -2429,13 +2429,13 @@
     <t xml:space="preserve">16.4515476226807</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9870338439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8321933746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9483222961426</t>
+    <t xml:space="preserve">15.9870328903198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8321943283081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9483213424683</t>
   </si>
   <si>
     <t xml:space="preserve">15.3676795959473</t>
@@ -2447,7 +2447,7 @@
     <t xml:space="preserve">15.1741333007812</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1160678863525</t>
+    <t xml:space="preserve">15.1160688400269</t>
   </si>
   <si>
     <t xml:space="preserve">15.1354236602783</t>
@@ -2456,7 +2456,7 @@
     <t xml:space="preserve">15.3289709091187</t>
   </si>
   <si>
-    <t xml:space="preserve">15.619291305542</t>
+    <t xml:space="preserve">15.6192922592163</t>
   </si>
   <si>
     <t xml:space="preserve">15.8902587890625</t>
@@ -2465,19 +2465,19 @@
     <t xml:space="preserve">15.7547760009766</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8128385543823</t>
+    <t xml:space="preserve">15.8128395080566</t>
   </si>
   <si>
     <t xml:space="preserve">16.161226272583</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6580009460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.870903968811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4128360748291</t>
+    <t xml:space="preserve">15.6580018997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8709049224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4128379821777</t>
   </si>
   <si>
     <t xml:space="preserve">16.4321918487549</t>
@@ -2507,7 +2507,7 @@
     <t xml:space="preserve">17.5354137420654</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3805751800537</t>
+    <t xml:space="preserve">17.3805732727051</t>
   </si>
   <si>
     <t xml:space="preserve">17.3418655395508</t>
@@ -2522,13 +2522,13 @@
     <t xml:space="preserve">17.2838039398193</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0515441894531</t>
+    <t xml:space="preserve">17.0515460968018</t>
   </si>
   <si>
     <t xml:space="preserve">16.83864402771</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2450904846191</t>
+    <t xml:space="preserve">17.2450923919678</t>
   </si>
   <si>
     <t xml:space="preserve">17.6128330230713</t>
@@ -2564,7 +2564,7 @@
     <t xml:space="preserve">15.5031642913818</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2128429412842</t>
+    <t xml:space="preserve">15.2128419876099</t>
   </si>
   <si>
     <t xml:space="preserve">15.3096160888672</t>
@@ -2582,10 +2582,10 @@
     <t xml:space="preserve">16.0838069915771</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7741298675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6773567199707</t>
+    <t xml:space="preserve">15.7741289138794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6773557662964</t>
   </si>
   <si>
     <t xml:space="preserve">15.5612277984619</t>
@@ -2594,7 +2594,7 @@
     <t xml:space="preserve">16.1805801391602</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8579959869385</t>
+    <t xml:space="preserve">16.8579978942871</t>
   </si>
   <si>
     <t xml:space="preserve">17.3031558990479</t>
@@ -2612,10 +2612,10 @@
     <t xml:space="preserve">17.5160579681396</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3612213134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.735408782959</t>
+    <t xml:space="preserve">17.3612194061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7354106903076</t>
   </si>
   <si>
     <t xml:space="preserve">18.6579895019531</t>
@@ -2639,13 +2639,13 @@
     <t xml:space="preserve">18.0386352539062</t>
   </si>
   <si>
-    <t xml:space="preserve">18.096700668335</t>
+    <t xml:space="preserve">18.0967025756836</t>
   </si>
   <si>
     <t xml:space="preserve">18.2128295898438</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2902488708496</t>
+    <t xml:space="preserve">18.2902507781982</t>
   </si>
   <si>
     <t xml:space="preserve">18.1547660827637</t>
@@ -2657,25 +2657,25 @@
     <t xml:space="preserve">17.9805736541748</t>
   </si>
   <si>
-    <t xml:space="preserve">17.961217880249</t>
+    <t xml:space="preserve">17.9612159729004</t>
   </si>
   <si>
     <t xml:space="preserve">17.8450908660889</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6902523040771</t>
+    <t xml:space="preserve">17.6902542114258</t>
   </si>
   <si>
     <t xml:space="preserve">17.6321868896484</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6515407562256</t>
+    <t xml:space="preserve">17.6515426635742</t>
   </si>
   <si>
     <t xml:space="preserve">17.4386405944824</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3999290466309</t>
+    <t xml:space="preserve">17.3999271392822</t>
   </si>
   <si>
     <t xml:space="preserve">17.2644481658936</t>
@@ -2687,16 +2687,16 @@
     <t xml:space="preserve">17.4773483276367</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8257350921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5805702209473</t>
+    <t xml:space="preserve">17.8257331848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5805721282959</t>
   </si>
   <si>
     <t xml:space="preserve">18.928955078125</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8128280639648</t>
+    <t xml:space="preserve">18.8128261566162</t>
   </si>
   <si>
     <t xml:space="preserve">19.5483112335205</t>
@@ -2711,7 +2711,7 @@
     <t xml:space="preserve">20.0321788787842</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7418556213379</t>
+    <t xml:space="preserve">19.7418575286865</t>
   </si>
   <si>
     <t xml:space="preserve">19.5966949462891</t>
@@ -2729,13 +2729,13 @@
     <t xml:space="preserve">20.370885848999</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8870182037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6450824737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1289520263672</t>
+    <t xml:space="preserve">19.8870162963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6450805664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1289501190186</t>
   </si>
   <si>
     <t xml:space="preserve">20.177339553833</t>
@@ -2747,19 +2747,19 @@
     <t xml:space="preserve">20.4676609039307</t>
   </si>
   <si>
-    <t xml:space="preserve">21.241849899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1934623718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.435396194458</t>
+    <t xml:space="preserve">21.2418518066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1934642791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4353981018066</t>
   </si>
   <si>
     <t xml:space="preserve">21.5805568695068</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6773319244385</t>
+    <t xml:space="preserve">21.6773338317871</t>
   </si>
   <si>
     <t xml:space="preserve">21.6289463043213</t>
@@ -2771,10 +2771,10 @@
     <t xml:space="preserve">22.2579765319824</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6450691223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0321655273438</t>
+    <t xml:space="preserve">22.6450710296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0321636199951</t>
   </si>
   <si>
     <t xml:space="preserve">23.4676475524902</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">23.3224868774414</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7902317047119</t>
+    <t xml:space="preserve">22.7902297973633</t>
   </si>
   <si>
     <t xml:space="preserve">22.7418441772461</t>
@@ -2801,22 +2801,22 @@
     <t xml:space="preserve">22.3063621520996</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8224906921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3547496795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1128158569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5482978820801</t>
+    <t xml:space="preserve">21.8224925994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3547477722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.112813949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5482959747314</t>
   </si>
   <si>
     <t xml:space="preserve">22.9837779998779</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9031295776367</t>
+    <t xml:space="preserve">23.9031314849854</t>
   </si>
   <si>
     <t xml:space="preserve">24.1934509277344</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">25.0160293579102</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9676399230957</t>
+    <t xml:space="preserve">24.9676418304443</t>
   </si>
   <si>
     <t xml:space="preserve">25.4031238555908</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">25.8386077880859</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9353809356689</t>
+    <t xml:space="preserve">25.9353790283203</t>
   </si>
   <si>
     <t xml:space="preserve">25.3547382354736</t>
@@ -2846,10 +2846,10 @@
     <t xml:space="preserve">25.161190032959</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8708667755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2579650878906</t>
+    <t xml:space="preserve">24.8708686828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.257963180542</t>
   </si>
   <si>
     <t xml:space="preserve">25.451509475708</t>
@@ -2864,22 +2864,22 @@
     <t xml:space="preserve">25.6450595855713</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1773147583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5160236358643</t>
+    <t xml:space="preserve">26.1773128509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5160217285156</t>
   </si>
   <si>
     <t xml:space="preserve">26.9515037536621</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6934452056885</t>
+    <t xml:space="preserve">25.6934432983398</t>
   </si>
   <si>
     <t xml:space="preserve">25.5966739654541</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3063507080078</t>
+    <t xml:space="preserve">25.3063488006592</t>
   </si>
   <si>
     <t xml:space="preserve">25.8869934082031</t>
@@ -3849,6 +3849,9 @@
   </si>
   <si>
     <t xml:space="preserve">48.9500007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.9500007629395</t>
   </si>
 </sst>
 </file>
@@ -69447,7 +69450,7 @@
     </row>
     <row r="2511">
       <c r="A2511" s="1" t="n">
-        <v>45974.6910185185</v>
+        <v>45974.3333333333</v>
       </c>
       <c r="B2511" t="n">
         <v>41027</v>
@@ -69468,6 +69471,32 @@
         <v>1230</v>
       </c>
       <c r="H2511" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2512">
+      <c r="A2512" s="1" t="n">
+        <v>45975.691099537</v>
+      </c>
+      <c r="B2512" t="n">
+        <v>44543</v>
+      </c>
+      <c r="C2512" t="n">
+        <v>48.2000007629395</v>
+      </c>
+      <c r="D2512" t="n">
+        <v>46.9000015258789</v>
+      </c>
+      <c r="E2512" t="n">
+        <v>48.2000007629395</v>
+      </c>
+      <c r="F2512" t="n">
+        <v>46.9500007629395</v>
+      </c>
+      <c r="G2512" t="s">
+        <v>1279</v>
+      </c>
+      <c r="H2512" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SOL.MI.xlsx
+++ b/data/SOL.MI.xlsx
@@ -38,40 +38,40 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14939022064209</t>
+    <t xml:space="preserve">7.14939117431641</t>
   </si>
   <si>
     <t xml:space="preserve">SOL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14067220687866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18862581253052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1624698638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06220388412476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90962505340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90526580810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94885969161987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71781206130981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62626504898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71345281600952</t>
+    <t xml:space="preserve">7.1406717300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18862628936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16246938705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0622034072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90962600708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90526533126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94885921478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71781253814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62626552581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71345233917236</t>
   </si>
   <si>
     <t xml:space="preserve">6.29931116104126</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">6.36470222473145</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43009233474731</t>
+    <t xml:space="preserve">6.43009281158447</t>
   </si>
   <si>
     <t xml:space="preserve">6.41265487670898</t>
@@ -98,76 +98,76 @@
     <t xml:space="preserve">6.46060848236084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54779624938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38213920593262</t>
+    <t xml:space="preserve">6.54779720306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38213968276978</t>
   </si>
   <si>
     <t xml:space="preserve">6.51292133331299</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50420236587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65242099761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80064105987549</t>
+    <t xml:space="preserve">6.5042028427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65242147445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80064010620117</t>
   </si>
   <si>
     <t xml:space="preserve">6.72217178344727</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79192113876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00989151000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84423446655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07964181900024</t>
+    <t xml:space="preserve">6.79192161560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00989198684692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84423494338989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07964134216309</t>
   </si>
   <si>
     <t xml:space="preserve">6.88346862792969</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96629762649536</t>
+    <t xml:space="preserve">6.9662971496582</t>
   </si>
   <si>
     <t xml:space="preserve">7.08836030960083</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7352499961853</t>
+    <t xml:space="preserve">6.73524951934814</t>
   </si>
   <si>
     <t xml:space="preserve">6.83115673065186</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67857694625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57395219802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63062381744385</t>
+    <t xml:space="preserve">6.67857837677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57395267486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63062429428101</t>
   </si>
   <si>
     <t xml:space="preserve">6.68729639053345</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78320360183716</t>
+    <t xml:space="preserve">6.783203125</t>
   </si>
   <si>
     <t xml:space="preserve">6.77884340286255</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81371879577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80935955047607</t>
+    <t xml:space="preserve">6.81371831893921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80935859680176</t>
   </si>
   <si>
     <t xml:space="preserve">6.79628086090088</t>
@@ -179,46 +179,46 @@
     <t xml:space="preserve">6.81807851791382</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87475061416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91398429870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67421865463257</t>
+    <t xml:space="preserve">6.8747501373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9139838218689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67421960830688</t>
   </si>
   <si>
     <t xml:space="preserve">6.5521559715271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46496820449829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43881177902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73088979721069</t>
+    <t xml:space="preserve">6.46496772766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43881130218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73089027404785</t>
   </si>
   <si>
     <t xml:space="preserve">6.87910890579224</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85295343399048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84859371185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85731315612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74832773208618</t>
+    <t xml:space="preserve">6.85295295715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84859418869019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85731172561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74832725524902</t>
   </si>
   <si>
     <t xml:space="preserve">6.51728057861328</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37342023849487</t>
+    <t xml:space="preserve">6.37341976165771</t>
   </si>
   <si>
     <t xml:space="preserve">6.56523370742798</t>
@@ -230,37 +230,37 @@
     <t xml:space="preserve">6.7701244354248</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86167144775391</t>
+    <t xml:space="preserve">6.86167240142822</t>
   </si>
   <si>
     <t xml:space="preserve">6.97501611709595</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94163036346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95048427581787</t>
+    <t xml:space="preserve">6.9416298866272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95048379898071</t>
   </si>
   <si>
     <t xml:space="preserve">6.88407754898071</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90178537368774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34006500244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2249608039856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41975259780884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43746042251587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36662721633911</t>
+    <t xml:space="preserve">6.9017858505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34006547927856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22496128082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41975116729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43745899200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36662769317627</t>
   </si>
   <si>
     <t xml:space="preserve">7.26037788391113</t>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">7.40204381942749</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44631433486938</t>
+    <t xml:space="preserve">7.44631481170654</t>
   </si>
   <si>
     <t xml:space="preserve">7.38433599472046</t>
@@ -281,58 +281,58 @@
     <t xml:space="preserve">7.04345226287842</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97261953353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10985803604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87079668045044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20725345611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37105464935303</t>
+    <t xml:space="preserve">6.97261905670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1098575592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8707971572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20725393295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37105512619019</t>
   </si>
   <si>
     <t xml:space="preserve">7.57027149200439</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69423007965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70308446884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71193885803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65881395339966</t>
+    <t xml:space="preserve">7.69422817230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70308494567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71193790435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65881252288818</t>
   </si>
   <si>
     <t xml:space="preserve">8.04396724700928</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61454296112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29579401016235</t>
+    <t xml:space="preserve">7.61454248428345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29579305648804</t>
   </si>
   <si>
     <t xml:space="preserve">6.99475431442261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10100507736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55256462097168</t>
+    <t xml:space="preserve">7.1010046005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55256414413452</t>
   </si>
   <si>
     <t xml:space="preserve">7.3135027885437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50829315185547</t>
+    <t xml:space="preserve">7.50829267501831</t>
   </si>
   <si>
     <t xml:space="preserve">7.42418003082275</t>
@@ -341,61 +341,61 @@
     <t xml:space="preserve">7.37548160552979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52600145339966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54371070861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41532564163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21610736846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99032688140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79996347427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75569295883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0080361366272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26923179626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34449243545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46402215957642</t>
+    <t xml:space="preserve">7.52600193023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54370927810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41532516479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21610689163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99032735824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79996395111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75569343566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00803518295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26923227310181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34449291229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46402406692505</t>
   </si>
   <si>
     <t xml:space="preserve">7.51714706420898</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39319038391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45516872406006</t>
+    <t xml:space="preserve">7.39318990707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4551682472229</t>
   </si>
   <si>
     <t xml:space="preserve">7.17183637619019</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33563756942749</t>
+    <t xml:space="preserve">7.33563852310181</t>
   </si>
   <si>
     <t xml:space="preserve">7.33121109008789</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39761543273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30464792251587</t>
+    <t xml:space="preserve">7.39761686325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30464839935303</t>
   </si>
   <si>
     <t xml:space="preserve">7.27808666229248</t>
@@ -404,7 +404,7 @@
     <t xml:space="preserve">7.25152349472046</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16298198699951</t>
+    <t xml:space="preserve">7.16298246383667</t>
   </si>
   <si>
     <t xml:space="preserve">7.03017091751099</t>
@@ -413,7 +413,7 @@
     <t xml:space="preserve">6.87965059280396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91064023971558</t>
+    <t xml:space="preserve">6.91063976287842</t>
   </si>
   <si>
     <t xml:space="preserve">6.95491075515747</t>
@@ -422,40 +422,40 @@
     <t xml:space="preserve">6.88850498199463</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95933866500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85751581192017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77340173721313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74683952331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82652616500854</t>
+    <t xml:space="preserve">6.95933771133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85751485824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77340126037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74683904647827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8265266418457</t>
   </si>
   <si>
     <t xml:space="preserve">6.68486022949219</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81767177581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90621376037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01688957214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8973593711853</t>
+    <t xml:space="preserve">6.81767225265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90621423721313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01689004898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89735889434814</t>
   </si>
   <si>
     <t xml:space="preserve">6.83538007736206</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86194324493408</t>
+    <t xml:space="preserve">6.86194276809692</t>
   </si>
   <si>
     <t xml:space="preserve">6.92392206192017</t>
@@ -464,16 +464,16 @@
     <t xml:space="preserve">6.97704648971558</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00360870361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91506767272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91949415206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93720245361328</t>
+    <t xml:space="preserve">7.00360822677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91506719589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91949367523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93720293045044</t>
   </si>
   <si>
     <t xml:space="preserve">7.07001495361328</t>
@@ -482,25 +482,25 @@
     <t xml:space="preserve">6.98589992523193</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75126552581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77782869338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64944362640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38382005691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37053966522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36168479919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37939310073853</t>
+    <t xml:space="preserve">6.75126600265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77782821655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64944458007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38381958007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37053918838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36168527603149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37939262390137</t>
   </si>
   <si>
     <t xml:space="preserve">6.40595531463623</t>
@@ -509,67 +509,67 @@
     <t xml:space="preserve">6.48121547698975</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47678852081299</t>
+    <t xml:space="preserve">6.47678804397583</t>
   </si>
   <si>
     <t xml:space="preserve">6.54319429397583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46350717544556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24215412139893</t>
+    <t xml:space="preserve">6.46350765228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24215364456177</t>
   </si>
   <si>
     <t xml:space="preserve">6.25986289978027</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22444629669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64501667022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64058923721313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03902530670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79110956192017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70256853103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70699501037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65829753875732</t>
+    <t xml:space="preserve">6.22444581985474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64501714706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64058971405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03902435302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79110908508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70256900787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70699548721313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65829801559448</t>
   </si>
   <si>
     <t xml:space="preserve">6.58303833007812</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05673360824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11428499221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34891891479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18511819839478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12756633758545</t>
+    <t xml:space="preserve">7.05673313140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11428546905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34891939163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18511772155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12756586074829</t>
   </si>
   <si>
     <t xml:space="preserve">7.19397211074829</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2426700592041</t>
+    <t xml:space="preserve">7.24266958236694</t>
   </si>
   <si>
     <t xml:space="preserve">7.41089820861816</t>
@@ -581,79 +581,79 @@
     <t xml:space="preserve">7.14527416229248</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27365970611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17626333236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04787921905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23381471633911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29136800765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42860698699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83589601516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82704210281372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13693428039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27860164642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32287120819092</t>
+    <t xml:space="preserve">7.27365875244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1762638092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04787874221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23381423950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2913670539856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42860746383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83589649200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82704162597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13693618774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27860069274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32287216186523</t>
   </si>
   <si>
     <t xml:space="preserve">9.03120040893555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53094482421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49995517730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26089286804199</t>
+    <t xml:space="preserve">8.53094577789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49995613098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26089477539062</t>
   </si>
   <si>
     <t xml:space="preserve">8.92495250701904</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58849430084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97807693481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7655782699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87182807922363</t>
+    <t xml:space="preserve">8.5884952545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97807598114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76557636260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87182903289795</t>
   </si>
   <si>
     <t xml:space="preserve">9.56244945526123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25255489349365</t>
+    <t xml:space="preserve">9.25255393981934</t>
   </si>
   <si>
     <t xml:space="preserve">9.02234840393066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85411930084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82755851745605</t>
+    <t xml:space="preserve">8.85411834716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82755756378174</t>
   </si>
   <si>
     <t xml:space="preserve">8.71245384216309</t>
@@ -665,28 +665,28 @@
     <t xml:space="preserve">8.8983907699585</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80984878540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72130870819092</t>
+    <t xml:space="preserve">8.80985069274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7213077545166</t>
   </si>
   <si>
     <t xml:space="preserve">8.78328514099121</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67703819274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75672435760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1020336151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82312965393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94266223907471</t>
+    <t xml:space="preserve">8.67703723907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7567253112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10203456878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82313060760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94266033172607</t>
   </si>
   <si>
     <t xml:space="preserve">9.20828533172607</t>
@@ -698,7 +698,7 @@
     <t xml:space="preserve">9.45982646942139</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52271366119385</t>
+    <t xml:space="preserve">9.52271270751953</t>
   </si>
   <si>
     <t xml:space="preserve">9.32507228851318</t>
@@ -707,13 +707,13 @@
     <t xml:space="preserve">9.38795757293701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35202217102051</t>
+    <t xml:space="preserve">9.35202407836914</t>
   </si>
   <si>
     <t xml:space="preserve">9.4238920211792</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29812049865723</t>
+    <t xml:space="preserve">9.29812240600586</t>
   </si>
   <si>
     <t xml:space="preserve">9.55864906311035</t>
@@ -722,37 +722,37 @@
     <t xml:space="preserve">9.67543697357178</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86409378051758</t>
+    <t xml:space="preserve">9.86409282684326</t>
   </si>
   <si>
     <t xml:space="preserve">10.5199041366577</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0617351531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88206100463867</t>
+    <t xml:space="preserve">10.0617361068726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88206195831299</t>
   </si>
   <si>
     <t xml:space="preserve">9.74730587005615</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56763076782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44185924530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54068088531494</t>
+    <t xml:space="preserve">9.56763172149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44186019897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54068279266357</t>
   </si>
   <si>
     <t xml:space="preserve">9.34304046630859</t>
   </si>
   <si>
-    <t xml:space="preserve">9.361008644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50474643707275</t>
+    <t xml:space="preserve">9.36100673675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50474452972412</t>
   </si>
   <si>
     <t xml:space="preserve">9.48677921295166</t>
@@ -764,28 +764,28 @@
     <t xml:space="preserve">9.77425575256348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46881198883057</t>
+    <t xml:space="preserve">9.46881103515625</t>
   </si>
   <si>
     <t xml:space="preserve">9.54966449737549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47779560089111</t>
+    <t xml:space="preserve">9.47779369354248</t>
   </si>
   <si>
     <t xml:space="preserve">9.7023868560791</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30710506439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28015327453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21726894378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16336536407471</t>
+    <t xml:space="preserve">9.30710411071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28015422821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2172679901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16336631774902</t>
   </si>
   <si>
     <t xml:space="preserve">9.25320243835449</t>
@@ -794,22 +794,22 @@
     <t xml:space="preserve">9.45084381103516</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58559799194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33405590057373</t>
+    <t xml:space="preserve">9.58559989929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33405685424805</t>
   </si>
   <si>
     <t xml:space="preserve">9.59458446502686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66645431518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71137142181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40592670440674</t>
+    <t xml:space="preserve">9.66645336151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71137237548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40592575073242</t>
   </si>
   <si>
     <t xml:space="preserve">9.26218700408936</t>
@@ -818,49 +818,49 @@
     <t xml:space="preserve">9.2711706161499</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28913879394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36999130249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65746974945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79222393035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76527404785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7203540802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8101921081543</t>
+    <t xml:space="preserve">9.289137840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36999225616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65746879577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7922248840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76527309417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72035312652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81019115447998</t>
   </si>
   <si>
     <t xml:space="preserve">9.37897396087646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90901279449463</t>
+    <t xml:space="preserve">9.909010887146</t>
   </si>
   <si>
     <t xml:space="preserve">9.81917572021484</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73832321166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78324127197266</t>
+    <t xml:space="preserve">9.73832225799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78324031829834</t>
   </si>
   <si>
     <t xml:space="preserve">9.69340324401855</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11844730377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0825138092041</t>
+    <t xml:space="preserve">9.11844635009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08251190185547</t>
   </si>
   <si>
     <t xml:space="preserve">9.31608867645264</t>
@@ -869,22 +869,22 @@
     <t xml:space="preserve">9.19031620025635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1004810333252</t>
+    <t xml:space="preserve">9.10048007965088</t>
   </si>
   <si>
     <t xml:space="preserve">9.22625255584717</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41490936279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39694309234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07352924346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57661628723145</t>
+    <t xml:space="preserve">9.41491031646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39694213867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07352828979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57661533355713</t>
   </si>
   <si>
     <t xml:space="preserve">9.68441963195801</t>
@@ -896,10 +896,10 @@
     <t xml:space="preserve">9.05556106567383</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14539813995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89385414123535</t>
+    <t xml:space="preserve">9.14539909362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89385509490967</t>
   </si>
   <si>
     <t xml:space="preserve">9.10946464538574</t>
@@ -908,16 +908,16 @@
     <t xml:space="preserve">9.2352352142334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95392990112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5109186172485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7444944381714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5468549728394</t>
+    <t xml:space="preserve">9.95393180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5109205245972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7444953918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5468530654907</t>
   </si>
   <si>
     <t xml:space="preserve">10.6905918121338</t>
@@ -926,25 +926,25 @@
     <t xml:space="preserve">10.9062023162842</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7804298400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7085609436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6546592712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5288867950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4390497207642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3312463760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1695394515991</t>
+    <t xml:space="preserve">10.7804307937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7085599899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6546583175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5288877487183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4390506744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.331244468689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1695384979248</t>
   </si>
   <si>
     <t xml:space="preserve">10.1875076293945</t>
@@ -953,22 +953,22 @@
     <t xml:space="preserve">10.1336040496826</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75628852844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63051891326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0078325271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84612464904785</t>
+    <t xml:space="preserve">9.7562894821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63051795959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0078344345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84612655639648</t>
   </si>
   <si>
     <t xml:space="preserve">10.0976696014404</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2054738998413</t>
+    <t xml:space="preserve">10.205472946167</t>
   </si>
   <si>
     <t xml:space="preserve">10.2773427963257</t>
@@ -980,7 +980,7 @@
     <t xml:space="preserve">10.2414073944092</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7624607086182</t>
+    <t xml:space="preserve">10.7624616622925</t>
   </si>
   <si>
     <t xml:space="preserve">10.2593774795532</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">9.91799545288086</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90002727508545</t>
+    <t xml:space="preserve">9.90002918243408</t>
   </si>
   <si>
     <t xml:space="preserve">9.67380809783936</t>
@@ -1001,22 +1001,22 @@
     <t xml:space="preserve">9.87420558929443</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1656951904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85598564147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63737010955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47340774536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7648983001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96529483795166</t>
+    <t xml:space="preserve">10.1656942367554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85598659515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63737106323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47340679168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76489734649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96529579162598</t>
   </si>
   <si>
     <t xml:space="preserve">10.0746049880981</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">10.3843116760254</t>
   </si>
   <si>
-    <t xml:space="preserve">10.420747756958</t>
+    <t xml:space="preserve">10.4207487106323</t>
   </si>
   <si>
     <t xml:space="preserve">10.8033285140991</t>
@@ -1037,25 +1037,25 @@
     <t xml:space="preserve">10.694019317627</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6211462020874</t>
+    <t xml:space="preserve">10.6211471557617</t>
   </si>
   <si>
     <t xml:space="preserve">10.7851095199585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5482759475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.402530670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2203502655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1474771499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3296594619751</t>
+    <t xml:space="preserve">10.5482749938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4025297164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2203483581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1474781036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3296585083008</t>
   </si>
   <si>
     <t xml:space="preserve">10.5847110748291</t>
@@ -1064,13 +1064,13 @@
     <t xml:space="preserve">10.3478755950928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72846221923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56449890136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4187536239624</t>
+    <t xml:space="preserve">9.7284631729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56449794769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41875267028809</t>
   </si>
   <si>
     <t xml:space="preserve">9.40053558349609</t>
@@ -1079,28 +1079,28 @@
     <t xml:space="preserve">9.54627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1110401153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2567853927612</t>
+    <t xml:space="preserve">10.1110420227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2567844390869</t>
   </si>
   <si>
     <t xml:space="preserve">9.92885971069336</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0199499130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2021312713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0928220748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80133438110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69202518463135</t>
+    <t xml:space="preserve">10.0199508666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2021331787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0928230285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8013334274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69202423095703</t>
   </si>
   <si>
     <t xml:space="preserve">9.8377685546875</t>
@@ -1112,31 +1112,31 @@
     <t xml:space="preserve">9.89242267608643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65558910369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78311538696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91064071655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45519065856934</t>
+    <t xml:space="preserve">9.65558815002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78311347961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91064167022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45518970489502</t>
   </si>
   <si>
     <t xml:space="preserve">9.2001371383667</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50984477996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43697166442871</t>
+    <t xml:space="preserve">9.50984287261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43697071075439</t>
   </si>
   <si>
     <t xml:space="preserve">9.81955146789551</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49162673950195</t>
+    <t xml:space="preserve">9.49162578582764</t>
   </si>
   <si>
     <t xml:space="preserve">9.61915397644043</t>
@@ -1145,28 +1145,28 @@
     <t xml:space="preserve">9.98351383209229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6009349822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10904502868652</t>
+    <t xml:space="preserve">9.60093307495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10904598236084</t>
   </si>
   <si>
     <t xml:space="preserve">9.09993648529053</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38231754302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36409950256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27300834655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71024322509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58271598815918</t>
+    <t xml:space="preserve">9.38231563568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36409854888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27301025390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71024227142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5827169418335</t>
   </si>
   <si>
     <t xml:space="preserve">9.29122638702393</t>
@@ -1184,16 +1184,16 @@
     <t xml:space="preserve">10.0017318725586</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4754028320312</t>
+    <t xml:space="preserve">10.4754037857056</t>
   </si>
   <si>
     <t xml:space="preserve">10.8397636413574</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5664930343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3114395141602</t>
+    <t xml:space="preserve">10.5664939880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3114385604858</t>
   </si>
   <si>
     <t xml:space="preserve">10.2932224273682</t>
@@ -1205,46 +1205,46 @@
     <t xml:space="preserve">10.0563859939575</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1292581558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2750043869019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.183913230896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6758012771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7122383117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.930853843689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0219459533691</t>
+    <t xml:space="preserve">10.1292591094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2750034332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1839141845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.675802230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7122373580933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9308557510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0219449996948</t>
   </si>
   <si>
     <t xml:space="preserve">10.8762006759644</t>
   </si>
   <si>
-    <t xml:space="preserve">10.894416809082</t>
+    <t xml:space="preserve">10.8944187164307</t>
   </si>
   <si>
     <t xml:space="preserve">10.7304553985596</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6575832366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2644634246826</t>
+    <t xml:space="preserve">10.6575841903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2644643783569</t>
   </si>
   <si>
     <t xml:space="preserve">11.1349868774414</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0979928970337</t>
+    <t xml:space="preserve">11.097993850708</t>
   </si>
   <si>
     <t xml:space="preserve">11.2459669113159</t>
@@ -1253,13 +1253,13 @@
     <t xml:space="preserve">11.319953918457</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0240068435669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8205423355103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8390407562256</t>
+    <t xml:space="preserve">11.0240058898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8205442428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8390398025513</t>
   </si>
   <si>
     <t xml:space="preserve">10.7280607223511</t>
@@ -1268,13 +1268,13 @@
     <t xml:space="preserve">10.857536315918</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7095642089844</t>
+    <t xml:space="preserve">10.7095632553101</t>
   </si>
   <si>
     <t xml:space="preserve">10.6725702285767</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6540746688843</t>
+    <t xml:space="preserve">10.65407371521</t>
   </si>
   <si>
     <t xml:space="preserve">10.7835502624512</t>
@@ -1283,7 +1283,7 @@
     <t xml:space="preserve">10.7650547027588</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8020467758179</t>
+    <t xml:space="preserve">10.8020477294922</t>
   </si>
   <si>
     <t xml:space="preserve">10.5615911483765</t>
@@ -1295,37 +1295,37 @@
     <t xml:space="preserve">10.3951206207275</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1176700592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2841396331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.265643119812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3026371002197</t>
+    <t xml:space="preserve">10.1176710128784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2841415405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2656450271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.302638053894</t>
   </si>
   <si>
     <t xml:space="preserve">10.5060997009277</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3396310806274</t>
+    <t xml:space="preserve">10.3396301269531</t>
   </si>
   <si>
     <t xml:space="preserve">10.1361665725708</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0806770324707</t>
+    <t xml:space="preserve">10.080677986145</t>
   </si>
   <si>
     <t xml:space="preserve">9.98819351196289</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0991735458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93270397186279</t>
+    <t xml:space="preserve">10.0991744995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93270301818848</t>
   </si>
   <si>
     <t xml:space="preserve">9.89571189880371</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">10.0621795654297</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1546630859375</t>
+    <t xml:space="preserve">10.1546640396118</t>
   </si>
   <si>
     <t xml:space="preserve">9.71074390411377</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">10.0251874923706</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91420841217041</t>
+    <t xml:space="preserve">9.91420745849609</t>
   </si>
   <si>
     <t xml:space="preserve">9.7662353515625</t>
@@ -1358,31 +1358,31 @@
     <t xml:space="preserve">9.72924137115479</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65525436401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.673752784729</t>
+    <t xml:space="preserve">9.65525341033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67375087738037</t>
   </si>
   <si>
     <t xml:space="preserve">9.47028732299805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54427528381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56277179718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45179080963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35930824279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52577781677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59976482391357</t>
+    <t xml:space="preserve">9.54427433013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56277084350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45178985595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35930919647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52577686309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59976387023926</t>
   </si>
   <si>
     <t xml:space="preserve">9.61826133728027</t>
@@ -1391,10 +1391,10 @@
     <t xml:space="preserve">9.69224739074707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8032283782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2286510467529</t>
+    <t xml:space="preserve">9.80322742462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2286520004272</t>
   </si>
   <si>
     <t xml:space="preserve">9.78473091125488</t>
@@ -1403,7 +1403,7 @@
     <t xml:space="preserve">9.858717918396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0066890716553</t>
+    <t xml:space="preserve">10.0066900253296</t>
   </si>
   <si>
     <t xml:space="preserve">9.87721538543701</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">9.74773788452148</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58126831054688</t>
+    <t xml:space="preserve">9.58126735687256</t>
   </si>
   <si>
     <t xml:space="preserve">10.3211336135864</t>
@@ -1424,112 +1424,112 @@
     <t xml:space="preserve">10.3766241073608</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2471466064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2101535797119</t>
+    <t xml:space="preserve">10.2471475601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2101526260376</t>
   </si>
   <si>
     <t xml:space="preserve">9.8402214050293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63675880432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43329334259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41479778289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39630031585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24832725524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06336212158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10960388183594</t>
+    <t xml:space="preserve">9.63675689697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43329524993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41479873657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39630126953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24832820892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06336116790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10960292816162</t>
   </si>
   <si>
     <t xml:space="preserve">9.32231426239014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28532123565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26682472229004</t>
+    <t xml:space="preserve">9.28532028198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26682567596436</t>
   </si>
   <si>
     <t xml:space="preserve">9.19283676147461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22983074188232</t>
+    <t xml:space="preserve">9.22983169555664</t>
   </si>
   <si>
     <t xml:space="preserve">9.48878383636475</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02636814117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9708776473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13734912872314</t>
+    <t xml:space="preserve">9.0263671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97087860107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13734722137451</t>
   </si>
   <si>
     <t xml:space="preserve">8.96162891387939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82290554046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61944103240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55470371246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36048793792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33274364471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01830005645752</t>
+    <t xml:space="preserve">8.82290458679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61944007873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55470275878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36048889160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33274269104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0182991027832</t>
   </si>
   <si>
     <t xml:space="preserve">7.81483697891235</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95356273651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49114561080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86108016967773</t>
+    <t xml:space="preserve">7.95356178283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49114513397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86107873916626</t>
   </si>
   <si>
     <t xml:space="preserve">7.50964260101318</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53738689422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58362865447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76741504669189</t>
+    <t xml:space="preserve">7.53738641738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5836296081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76741409301758</t>
   </si>
   <si>
     <t xml:space="preserve">8.9893741607666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16509246826172</t>
+    <t xml:space="preserve">9.16509342193604</t>
   </si>
   <si>
     <t xml:space="preserve">9.12809944152832</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">9.09110736846924</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08185768127441</t>
+    <t xml:space="preserve">9.08185863494873</t>
   </si>
   <si>
     <t xml:space="preserve">9.34081172943115</t>
@@ -1547,7 +1547,7 @@
     <t xml:space="preserve">9.0448637008667</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21133422851562</t>
+    <t xml:space="preserve">9.21133518218994</t>
   </si>
   <si>
     <t xml:space="preserve">9.38705253601074</t>
@@ -1556,49 +1556,49 @@
     <t xml:space="preserve">9.17434024810791</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29456996917725</t>
+    <t xml:space="preserve">9.29456901550293</t>
   </si>
   <si>
     <t xml:space="preserve">9.11885070800781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78591251373291</t>
+    <t xml:space="preserve">8.78591060638428</t>
   </si>
   <si>
     <t xml:space="preserve">8.89689159393311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74891948699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80440998077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87839603424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9338846206665</t>
+    <t xml:space="preserve">8.74891757965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80440902709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87839508056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93388652801514</t>
   </si>
   <si>
     <t xml:space="preserve">8.63793754577637</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7119255065918</t>
+    <t xml:space="preserve">8.71192455291748</t>
   </si>
   <si>
     <t xml:space="preserve">8.58244800567627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6934289932251</t>
+    <t xml:space="preserve">8.69342803955078</t>
   </si>
   <si>
     <t xml:space="preserve">9.46113967895508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64942073822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69649124145508</t>
+    <t xml:space="preserve">9.6494197845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69649028778076</t>
   </si>
   <si>
     <t xml:space="preserve">9.74356174468994</t>
@@ -1607,10 +1607,10 @@
     <t xml:space="preserve">9.97891330718994</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93184280395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7906322479248</t>
+    <t xml:space="preserve">9.93184185028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79063129425049</t>
   </si>
   <si>
     <t xml:space="preserve">10.0730543136597</t>
@@ -1619,13 +1619,13 @@
     <t xml:space="preserve">10.3084049224854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4496154785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1671934127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1201248168945</t>
+    <t xml:space="preserve">10.4496173858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1671943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1201238632202</t>
   </si>
   <si>
     <t xml:space="preserve">10.0259828567505</t>
@@ -1634,10 +1634,10 @@
     <t xml:space="preserve">10.2142648696899</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3554754257202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2613344192505</t>
+    <t xml:space="preserve">10.3554763793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2613353729248</t>
   </si>
   <si>
     <t xml:space="preserve">9.88477230072021</t>
@@ -1652,25 +1652,25 @@
     <t xml:space="preserve">10.5437574386597</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2027416229248</t>
+    <t xml:space="preserve">11.2027406692505</t>
   </si>
   <si>
     <t xml:space="preserve">11.1556720733643</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9673910140991</t>
+    <t xml:space="preserve">10.9673891067505</t>
   </si>
   <si>
     <t xml:space="preserve">11.0615310668945</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7791080474854</t>
+    <t xml:space="preserve">10.7791090011597</t>
   </si>
   <si>
     <t xml:space="preserve">10.8261795043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0144596099854</t>
+    <t xml:space="preserve">11.014461517334</t>
   </si>
   <si>
     <t xml:space="preserve">11.1086015701294</t>
@@ -1682,16 +1682,16 @@
     <t xml:space="preserve">10.8732490539551</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7320375442505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6378984451294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5322332382202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6263742446899</t>
+    <t xml:space="preserve">10.7320384979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6378974914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5322341918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6263761520386</t>
   </si>
   <si>
     <t xml:space="preserve">11.7675857543945</t>
@@ -1700,13 +1700,13 @@
     <t xml:space="preserve">11.8146562576294</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5793046951294</t>
+    <t xml:space="preserve">11.5793037414551</t>
   </si>
   <si>
     <t xml:space="preserve">11.6734447479248</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7205152511597</t>
+    <t xml:space="preserve">11.720516204834</t>
   </si>
   <si>
     <t xml:space="preserve">12.0029382705688</t>
@@ -1715,7 +1715,7 @@
     <t xml:space="preserve">12.2853603363037</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5677814483643</t>
+    <t xml:space="preserve">12.5677824020386</t>
   </si>
   <si>
     <t xml:space="preserve">12.5207109451294</t>
@@ -1724,31 +1724,31 @@
     <t xml:space="preserve">12.897274017334</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7560634613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6619215011597</t>
+    <t xml:space="preserve">12.7560625076294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6619234085083</t>
   </si>
   <si>
     <t xml:space="preserve">12.6148519515991</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8031330108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8502035140991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9914140701294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1796979904175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.462119102478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.838680267334</t>
+    <t xml:space="preserve">12.8031339645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8502025604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9914150238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1796960830688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4621181488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8386812210083</t>
   </si>
   <si>
     <t xml:space="preserve">13.7445411682129</t>
@@ -1757,10 +1757,10 @@
     <t xml:space="preserve">13.6504001617432</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5091896057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7916107177734</t>
+    <t xml:space="preserve">13.5091886520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7916097640991</t>
   </si>
   <si>
     <t xml:space="preserve">13.8857517242432</t>
@@ -1769,10 +1769,10 @@
     <t xml:space="preserve">13.9798927307129</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0269632339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0740327835083</t>
+    <t xml:space="preserve">14.0269622802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.074031829834</t>
   </si>
   <si>
     <t xml:space="preserve">14.168173789978</t>
@@ -1796,22 +1796,22 @@
     <t xml:space="preserve">14.3093843460083</t>
   </si>
   <si>
-    <t xml:space="preserve">14.403525352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3564558029175</t>
+    <t xml:space="preserve">14.4035243988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3564548492432</t>
   </si>
   <si>
     <t xml:space="preserve">14.5447368621826</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5918054580688</t>
+    <t xml:space="preserve">14.5918064117432</t>
   </si>
   <si>
     <t xml:space="preserve">14.638876914978</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7800884246826</t>
+    <t xml:space="preserve">14.780086517334</t>
   </si>
   <si>
     <t xml:space="preserve">14.8271589279175</t>
@@ -1823,55 +1823,55 @@
     <t xml:space="preserve">14.7330169677734</t>
   </si>
   <si>
-    <t xml:space="preserve">15.344931602478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7685661315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0039196014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0415744781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0792293548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1921997070312</t>
+    <t xml:space="preserve">15.3449306488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7685670852661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0039157867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0415725708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0792274475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1921977996826</t>
   </si>
   <si>
     <t xml:space="preserve">16.1168880462646</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2298545837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3804817199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3993072509766</t>
+    <t xml:space="preserve">16.2298526763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3804798126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3993091583252</t>
   </si>
   <si>
     <t xml:space="preserve">16.4181365966797</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5311050415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2675132751465</t>
+    <t xml:space="preserve">16.5311031341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2675113677979</t>
   </si>
   <si>
     <t xml:space="preserve">15.9286031723022</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8909463882446</t>
+    <t xml:space="preserve">15.8909482955933</t>
   </si>
   <si>
     <t xml:space="preserve">15.815634727478</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9662618637085</t>
+    <t xml:space="preserve">15.9662599563599</t>
   </si>
   <si>
     <t xml:space="preserve">15.7214956283569</t>
@@ -1880,58 +1880,58 @@
     <t xml:space="preserve">15.5332126617432</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5143842697144</t>
+    <t xml:space="preserve">15.51438331604</t>
   </si>
   <si>
     <t xml:space="preserve">15.7026672363281</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2696199417114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4767293930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6838388442993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6650104522705</t>
+    <t xml:space="preserve">15.2696189880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4767284393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.683837890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6650085449219</t>
   </si>
   <si>
     <t xml:space="preserve">15.4202442169189</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1566505432129</t>
+    <t xml:space="preserve">15.1566514968872</t>
   </si>
   <si>
     <t xml:space="preserve">15.2319631576538</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7779808044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9833726882935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9643001556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6209802627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4874687194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7926406860352</t>
+    <t xml:space="preserve">15.7779779434204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9833717346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9642992019653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6209812164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4874696731567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7926397323608</t>
   </si>
   <si>
     <t xml:space="preserve">15.8117141723633</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6019067764282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5446882247925</t>
+    <t xml:space="preserve">15.6019077301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5446872711182</t>
   </si>
   <si>
     <t xml:space="preserve">15.2585897445679</t>
@@ -1940,10 +1940,10 @@
     <t xml:space="preserve">15.6972732543945</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8307876586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1168842315674</t>
+    <t xml:space="preserve">15.8307867050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.116886138916</t>
   </si>
   <si>
     <t xml:space="preserve">16.2503986358643</t>
@@ -1952,28 +1952,28 @@
     <t xml:space="preserve">16.2313251495361</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0024471282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2694702148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2122535705566</t>
+    <t xml:space="preserve">16.0024452209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2694683074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.212251663208</t>
   </si>
   <si>
     <t xml:space="preserve">16.460205078125</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4411315917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5364990234375</t>
+    <t xml:space="preserve">16.4411296844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5364952087402</t>
   </si>
   <si>
     <t xml:space="preserve">16.555570602417</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1659126281738</t>
+    <t xml:space="preserve">17.1659145355225</t>
   </si>
   <si>
     <t xml:space="preserve">16.9561100006104</t>
@@ -1985,7 +1985,7 @@
     <t xml:space="preserve">17.3185005187988</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0896224975586</t>
+    <t xml:space="preserve">17.08962059021</t>
   </si>
   <si>
     <t xml:space="preserve">16.841667175293</t>
@@ -1997,7 +1997,7 @@
     <t xml:space="preserve">16.9751796722412</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1277675628662</t>
+    <t xml:space="preserve">17.1277656555176</t>
   </si>
   <si>
     <t xml:space="preserve">17.5092334747314</t>
@@ -2006,10 +2006,10 @@
     <t xml:space="preserve">17.5473785400391</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7571830749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6427459716797</t>
+    <t xml:space="preserve">17.7571849822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6427440643311</t>
   </si>
   <si>
     <t xml:space="preserve">17.7381114959717</t>
@@ -2024,46 +2024,46 @@
     <t xml:space="preserve">17.3375720977783</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2994251251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3566455841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2422046661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1468410491943</t>
+    <t xml:space="preserve">17.2994270324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3566474914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2422065734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1468372344971</t>
   </si>
   <si>
     <t xml:space="preserve">17.0133285522461</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4520130157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8334770202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6999645233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8716239929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8525485992432</t>
+    <t xml:space="preserve">17.4520111083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8334789276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6999626159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8716259002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8525505065918</t>
   </si>
   <si>
     <t xml:space="preserve">18.0242099761963</t>
   </si>
   <si>
-    <t xml:space="preserve">18.424747467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5010395050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6536254882812</t>
+    <t xml:space="preserve">18.4247493743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5010414123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6536235809326</t>
   </si>
   <si>
     <t xml:space="preserve">18.5964069366455</t>
@@ -2093,7 +2093,7 @@
     <t xml:space="preserve">19.9792156219482</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4547004699707</t>
+    <t xml:space="preserve">19.4547023773193</t>
   </si>
   <si>
     <t xml:space="preserve">19.3593349456787</t>
@@ -2105,13 +2105,13 @@
     <t xml:space="preserve">18.7871398925781</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6917743682861</t>
+    <t xml:space="preserve">18.6917724609375</t>
   </si>
   <si>
     <t xml:space="preserve">19.216287612915</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1209201812744</t>
+    <t xml:space="preserve">19.1209182739258</t>
   </si>
   <si>
     <t xml:space="preserve">18.76806640625</t>
@@ -2132,7 +2132,7 @@
     <t xml:space="preserve">18.1005020141602</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2530879974365</t>
+    <t xml:space="preserve">18.2530860900879</t>
   </si>
   <si>
     <t xml:space="preserve">17.9669895172119</t>
@@ -2141,10 +2141,10 @@
     <t xml:space="preserve">18.176794052124</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9969444274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0732364654541</t>
+    <t xml:space="preserve">18.9969463348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0732383728027</t>
   </si>
   <si>
     <t xml:space="preserve">18.9778709411621</t>
@@ -2153,10 +2153,10 @@
     <t xml:space="preserve">18.8825035095215</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9397239685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9015769958496</t>
+    <t xml:space="preserve">18.9397258758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9015789031982</t>
   </si>
   <si>
     <t xml:space="preserve">20.0268993377686</t>
@@ -2165,7 +2165,7 @@
     <t xml:space="preserve">20.2176322937012</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2653121948242</t>
+    <t xml:space="preserve">20.2653141021729</t>
   </si>
   <si>
     <t xml:space="preserve">20.7421474456787</t>
@@ -2174,13 +2174,13 @@
     <t xml:space="preserve">20.9328784942627</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2189769744873</t>
+    <t xml:space="preserve">21.2189750671387</t>
   </si>
   <si>
     <t xml:space="preserve">21.4573917388916</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6944618225098</t>
+    <t xml:space="preserve">20.6944637298584</t>
   </si>
   <si>
     <t xml:space="preserve">20.3129978179932</t>
@@ -2192,16 +2192,16 @@
     <t xml:space="preserve">20.980562210083</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8361682891846</t>
+    <t xml:space="preserve">19.8361663818359</t>
   </si>
   <si>
     <t xml:space="preserve">20.4083652496338</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1222667694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.311653137207</t>
+    <t xml:space="preserve">20.1222648620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3116512298584</t>
   </si>
   <si>
     <t xml:space="preserve">19.2639713287354</t>
@@ -2213,16 +2213,16 @@
     <t xml:space="preserve">19.6454334259033</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1699485778809</t>
+    <t xml:space="preserve">20.1699504852295</t>
   </si>
   <si>
     <t xml:space="preserve">19.9315338134766</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7408008575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8443603515625</t>
+    <t xml:space="preserve">19.7408027648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8443584442139</t>
   </si>
   <si>
     <t xml:space="preserve">19.0160179138184</t>
@@ -2237,7 +2237,7 @@
     <t xml:space="preserve">18.138650894165</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0623569488525</t>
+    <t xml:space="preserve">18.0623550415039</t>
   </si>
   <si>
     <t xml:space="preserve">18.0814266204834</t>
@@ -2246,16 +2246,16 @@
     <t xml:space="preserve">17.6045989990234</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2612781524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0514755249023</t>
+    <t xml:space="preserve">17.2612800598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0514736175537</t>
   </si>
   <si>
     <t xml:space="preserve">16.2885437011719</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0324020385742</t>
+    <t xml:space="preserve">17.0324039459229</t>
   </si>
   <si>
     <t xml:space="preserve">16.7272300720215</t>
@@ -2270,13 +2270,13 @@
     <t xml:space="preserve">17.0705471038818</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6509342193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8607425689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3076190948486</t>
+    <t xml:space="preserve">16.650936126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8607406616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3076171875</t>
   </si>
   <si>
     <t xml:space="preserve">16.5937175750732</t>
@@ -2294,34 +2294,34 @@
     <t xml:space="preserve">14.495659828186</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3730297088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9915647506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0869302749634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.678201675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1441507339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9452257156372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0787391662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0405921936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5746421813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6890811920166</t>
+    <t xml:space="preserve">15.3730306625366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9915637969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0869312286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6782007217407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1441497802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9452247619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0787410736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0405941009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5746402740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6890830993652</t>
   </si>
   <si>
     <t xml:space="preserve">16.5174236297607</t>
@@ -2333,13 +2333,13 @@
     <t xml:space="preserve">15.7354202270508</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8880071640015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5065422058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9724912643433</t>
+    <t xml:space="preserve">15.8880062103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5065431594849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9724903106689</t>
   </si>
   <si>
     <t xml:space="preserve">15.3348836898804</t>
@@ -2351,22 +2351,22 @@
     <t xml:space="preserve">14.9152727127075</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7817583084106</t>
+    <t xml:space="preserve">14.781759262085</t>
   </si>
   <si>
     <t xml:space="preserve">14.8961992263794</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6400547027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0978107452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2395172119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1060047149658</t>
+    <t xml:space="preserve">15.6400566101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0978126525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2395162582397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1060037612915</t>
   </si>
   <si>
     <t xml:space="preserve">16.0063896179199</t>
@@ -2381,16 +2381,16 @@
     <t xml:space="preserve">16.0450973510742</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1418724060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2773532867432</t>
+    <t xml:space="preserve">16.1418704986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2773551940918</t>
   </si>
   <si>
     <t xml:space="preserve">16.4709014892578</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7805786132812</t>
+    <t xml:space="preserve">16.7805767059326</t>
   </si>
   <si>
     <t xml:space="preserve">17.1483173370361</t>
@@ -2411,13 +2411,13 @@
     <t xml:space="preserve">17.9418640136719</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4967021942139</t>
+    <t xml:space="preserve">17.4967041015625</t>
   </si>
   <si>
     <t xml:space="preserve">17.5934772491455</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4579944610596</t>
+    <t xml:space="preserve">17.4579963684082</t>
   </si>
   <si>
     <t xml:space="preserve">16.8967056274414</t>
@@ -2426,13 +2426,13 @@
     <t xml:space="preserve">16.4515476226807</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9870338439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8321933746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9483222961426</t>
+    <t xml:space="preserve">15.9870328903198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8321943283081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9483213424683</t>
   </si>
   <si>
     <t xml:space="preserve">15.3676795959473</t>
@@ -2444,7 +2444,7 @@
     <t xml:space="preserve">15.1741333007812</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1160678863525</t>
+    <t xml:space="preserve">15.1160688400269</t>
   </si>
   <si>
     <t xml:space="preserve">15.1354236602783</t>
@@ -2453,7 +2453,7 @@
     <t xml:space="preserve">15.3289709091187</t>
   </si>
   <si>
-    <t xml:space="preserve">15.619291305542</t>
+    <t xml:space="preserve">15.6192922592163</t>
   </si>
   <si>
     <t xml:space="preserve">15.8902587890625</t>
@@ -2462,19 +2462,19 @@
     <t xml:space="preserve">15.7547760009766</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8128385543823</t>
+    <t xml:space="preserve">15.8128395080566</t>
   </si>
   <si>
     <t xml:space="preserve">16.161226272583</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6580009460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.870903968811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4128360748291</t>
+    <t xml:space="preserve">15.6580018997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8709049224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4128379821777</t>
   </si>
   <si>
     <t xml:space="preserve">16.4321918487549</t>
@@ -2504,7 +2504,7 @@
     <t xml:space="preserve">17.5354137420654</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3805751800537</t>
+    <t xml:space="preserve">17.3805732727051</t>
   </si>
   <si>
     <t xml:space="preserve">17.3418655395508</t>
@@ -2519,13 +2519,13 @@
     <t xml:space="preserve">17.2838039398193</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0515441894531</t>
+    <t xml:space="preserve">17.0515460968018</t>
   </si>
   <si>
     <t xml:space="preserve">16.83864402771</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2450904846191</t>
+    <t xml:space="preserve">17.2450923919678</t>
   </si>
   <si>
     <t xml:space="preserve">17.6128330230713</t>
@@ -2561,7 +2561,7 @@
     <t xml:space="preserve">15.5031642913818</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2128429412842</t>
+    <t xml:space="preserve">15.2128419876099</t>
   </si>
   <si>
     <t xml:space="preserve">15.3096160888672</t>
@@ -2579,10 +2579,10 @@
     <t xml:space="preserve">16.0838069915771</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7741298675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6773567199707</t>
+    <t xml:space="preserve">15.7741289138794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6773557662964</t>
   </si>
   <si>
     <t xml:space="preserve">15.5612277984619</t>
@@ -2591,7 +2591,7 @@
     <t xml:space="preserve">16.1805801391602</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8579959869385</t>
+    <t xml:space="preserve">16.8579978942871</t>
   </si>
   <si>
     <t xml:space="preserve">17.3031558990479</t>
@@ -2609,10 +2609,10 @@
     <t xml:space="preserve">17.5160579681396</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3612213134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.735408782959</t>
+    <t xml:space="preserve">17.3612194061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7354106903076</t>
   </si>
   <si>
     <t xml:space="preserve">18.6579895019531</t>
@@ -2636,13 +2636,13 @@
     <t xml:space="preserve">18.0386352539062</t>
   </si>
   <si>
-    <t xml:space="preserve">18.096700668335</t>
+    <t xml:space="preserve">18.0967025756836</t>
   </si>
   <si>
     <t xml:space="preserve">18.2128295898438</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2902488708496</t>
+    <t xml:space="preserve">18.2902507781982</t>
   </si>
   <si>
     <t xml:space="preserve">18.1547660827637</t>
@@ -2654,25 +2654,25 @@
     <t xml:space="preserve">17.9805736541748</t>
   </si>
   <si>
-    <t xml:space="preserve">17.961217880249</t>
+    <t xml:space="preserve">17.9612159729004</t>
   </si>
   <si>
     <t xml:space="preserve">17.8450908660889</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6902523040771</t>
+    <t xml:space="preserve">17.6902542114258</t>
   </si>
   <si>
     <t xml:space="preserve">17.6321868896484</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6515407562256</t>
+    <t xml:space="preserve">17.6515426635742</t>
   </si>
   <si>
     <t xml:space="preserve">17.4386405944824</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3999290466309</t>
+    <t xml:space="preserve">17.3999271392822</t>
   </si>
   <si>
     <t xml:space="preserve">17.2644481658936</t>
@@ -2684,16 +2684,16 @@
     <t xml:space="preserve">17.4773483276367</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8257350921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5805702209473</t>
+    <t xml:space="preserve">17.8257331848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5805721282959</t>
   </si>
   <si>
     <t xml:space="preserve">18.928955078125</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8128280639648</t>
+    <t xml:space="preserve">18.8128261566162</t>
   </si>
   <si>
     <t xml:space="preserve">19.5483112335205</t>
@@ -2708,7 +2708,7 @@
     <t xml:space="preserve">20.0321788787842</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7418556213379</t>
+    <t xml:space="preserve">19.7418575286865</t>
   </si>
   <si>
     <t xml:space="preserve">19.5966949462891</t>
@@ -2726,13 +2726,13 @@
     <t xml:space="preserve">20.370885848999</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8870182037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6450824737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1289520263672</t>
+    <t xml:space="preserve">19.8870162963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6450805664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1289501190186</t>
   </si>
   <si>
     <t xml:space="preserve">20.177339553833</t>
@@ -2744,19 +2744,19 @@
     <t xml:space="preserve">20.4676609039307</t>
   </si>
   <si>
-    <t xml:space="preserve">21.241849899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1934623718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.435396194458</t>
+    <t xml:space="preserve">21.2418518066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1934642791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4353981018066</t>
   </si>
   <si>
     <t xml:space="preserve">21.5805568695068</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6773319244385</t>
+    <t xml:space="preserve">21.6773338317871</t>
   </si>
   <si>
     <t xml:space="preserve">21.6289463043213</t>
@@ -2768,10 +2768,10 @@
     <t xml:space="preserve">22.2579765319824</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6450691223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0321655273438</t>
+    <t xml:space="preserve">22.6450710296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0321636199951</t>
   </si>
   <si>
     <t xml:space="preserve">23.4676475524902</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">23.3224868774414</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7902317047119</t>
+    <t xml:space="preserve">22.7902297973633</t>
   </si>
   <si>
     <t xml:space="preserve">22.7418441772461</t>
@@ -2798,22 +2798,22 @@
     <t xml:space="preserve">22.3063621520996</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8224906921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3547496795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1128158569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5482978820801</t>
+    <t xml:space="preserve">21.8224925994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3547477722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.112813949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5482959747314</t>
   </si>
   <si>
     <t xml:space="preserve">22.9837779998779</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9031295776367</t>
+    <t xml:space="preserve">23.9031314849854</t>
   </si>
   <si>
     <t xml:space="preserve">24.1934509277344</t>
@@ -2825,7 +2825,7 @@
     <t xml:space="preserve">25.0160293579102</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9676399230957</t>
+    <t xml:space="preserve">24.9676418304443</t>
   </si>
   <si>
     <t xml:space="preserve">25.4031238555908</t>
@@ -2834,7 +2834,7 @@
     <t xml:space="preserve">25.8386077880859</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9353809356689</t>
+    <t xml:space="preserve">25.9353790283203</t>
   </si>
   <si>
     <t xml:space="preserve">25.3547382354736</t>
@@ -2843,10 +2843,10 @@
     <t xml:space="preserve">25.161190032959</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8708667755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2579650878906</t>
+    <t xml:space="preserve">24.8708686828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.257963180542</t>
   </si>
   <si>
     <t xml:space="preserve">25.451509475708</t>
@@ -2861,22 +2861,22 @@
     <t xml:space="preserve">25.6450595855713</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1773147583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5160236358643</t>
+    <t xml:space="preserve">26.1773128509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5160217285156</t>
   </si>
   <si>
     <t xml:space="preserve">26.9515037536621</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6934452056885</t>
+    <t xml:space="preserve">25.6934432983398</t>
   </si>
   <si>
     <t xml:space="preserve">25.5966739654541</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3063507080078</t>
+    <t xml:space="preserve">25.3063488006592</t>
   </si>
   <si>
     <t xml:space="preserve">25.8869934082031</t>
@@ -69499,7 +69499,7 @@
     </row>
     <row r="2513">
       <c r="A2513" s="1" t="n">
-        <v>45978.6912847222</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B2513" t="n">
         <v>39330</v>
@@ -69520,6 +69520,32 @@
         <v>1227</v>
       </c>
       <c r="H2513" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2514">
+      <c r="A2514" s="1" t="n">
+        <v>45979.6912962963</v>
+      </c>
+      <c r="B2514" t="n">
+        <v>78916</v>
+      </c>
+      <c r="C2514" t="n">
+        <v>48.7000007629395</v>
+      </c>
+      <c r="D2514" t="n">
+        <v>46.5999984741211</v>
+      </c>
+      <c r="E2514" t="n">
+        <v>48.7000007629395</v>
+      </c>
+      <c r="F2514" t="n">
+        <v>47.2000007629395</v>
+      </c>
+      <c r="G2514" t="s">
+        <v>1221</v>
+      </c>
+      <c r="H2514" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SOL.MI.xlsx
+++ b/data/SOL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="1278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1279" uniqueCount="1279">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,52 +38,52 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14939117431641</t>
+    <t xml:space="preserve">7.14939069747925</t>
   </si>
   <si>
     <t xml:space="preserve">SOL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14067268371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18862581253052</t>
+    <t xml:space="preserve">7.14067220687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18862533569336</t>
   </si>
   <si>
     <t xml:space="preserve">7.1624698638916</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06220388412476</t>
+    <t xml:space="preserve">7.06220436096191</t>
   </si>
   <si>
     <t xml:space="preserve">6.90962553024292</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90526580810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94885921478271</t>
+    <t xml:space="preserve">6.90526628494263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94885969161987</t>
   </si>
   <si>
     <t xml:space="preserve">6.71781301498413</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62626552581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71345233917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29931163787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3647027015686</t>
+    <t xml:space="preserve">6.62626457214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71345281600952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29931116104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36470222473145</t>
   </si>
   <si>
     <t xml:space="preserve">6.43009328842163</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41265535354614</t>
+    <t xml:space="preserve">6.4126558303833</t>
   </si>
   <si>
     <t xml:space="preserve">6.44753074645996</t>
@@ -92,28 +92,28 @@
     <t xml:space="preserve">6.20776414871216</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17288875579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.460608959198</t>
+    <t xml:space="preserve">6.1728892326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46060800552368</t>
   </si>
   <si>
     <t xml:space="preserve">6.54779624938965</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38213968276978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51292085647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5042028427124</t>
+    <t xml:space="preserve">6.38213920593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51292133331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50420236587524</t>
   </si>
   <si>
     <t xml:space="preserve">6.65242195129395</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80064058303833</t>
+    <t xml:space="preserve">6.80064010620117</t>
   </si>
   <si>
     <t xml:space="preserve">6.72217178344727</t>
@@ -125,97 +125,97 @@
     <t xml:space="preserve">7.00989103317261</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84423446655273</t>
+    <t xml:space="preserve">6.84423398971558</t>
   </si>
   <si>
     <t xml:space="preserve">7.07964134216309</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88346862792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9662971496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08835935592651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73524951934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83115673065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67857789993286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57395219802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63062429428101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68729591369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.783203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77884435653687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81371879577637</t>
+    <t xml:space="preserve">6.88346910476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96629667282104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08836030960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73524904251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83115577697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6785774230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57395172119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63062477111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68729686737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78320407867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77884387969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81371927261353</t>
   </si>
   <si>
     <t xml:space="preserve">6.80935955047607</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79628086090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69601488113403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81807804107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8747501373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91398429870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67421817779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55215549468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46496772766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43881225585938</t>
+    <t xml:space="preserve">6.7962818145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69601392745972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81807851791382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87474966049194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9139838218689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67421865463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5521559715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46496725082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43881177902222</t>
   </si>
   <si>
     <t xml:space="preserve">6.73089027404785</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87910890579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85295343399048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84859418869019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85731267929077</t>
+    <t xml:space="preserve">6.87910938262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85295391082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84859371185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85731220245361</t>
   </si>
   <si>
     <t xml:space="preserve">6.74832820892334</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51728010177612</t>
+    <t xml:space="preserve">6.51728057861328</t>
   </si>
   <si>
     <t xml:space="preserve">6.37342119216919</t>
@@ -224,31 +224,31 @@
     <t xml:space="preserve">6.56523370742798</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66986036300659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7701244354248</t>
+    <t xml:space="preserve">6.66985940933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77012491226196</t>
   </si>
   <si>
     <t xml:space="preserve">6.86167144775391</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97501611709595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94162940979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95048379898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88407850265503</t>
+    <t xml:space="preserve">6.97501659393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9416298866272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95048332214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88407802581787</t>
   </si>
   <si>
     <t xml:space="preserve">6.90178632736206</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34006500244141</t>
+    <t xml:space="preserve">7.34006547927856</t>
   </si>
   <si>
     <t xml:space="preserve">7.22496128082275</t>
@@ -257,58 +257,58 @@
     <t xml:space="preserve">7.41975164413452</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43745994567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36662721633911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26037788391113</t>
+    <t xml:space="preserve">7.43746042251587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36662817001343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26037836074829</t>
   </si>
   <si>
     <t xml:space="preserve">7.46845054626465</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40204429626465</t>
+    <t xml:space="preserve">7.40204286575317</t>
   </si>
   <si>
     <t xml:space="preserve">7.4463152885437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38433504104614</t>
+    <t xml:space="preserve">7.3843355178833</t>
   </si>
   <si>
     <t xml:space="preserve">7.04345226287842</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9726185798645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10985803604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87079668045044</t>
+    <t xml:space="preserve">6.97261905670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1098575592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8707971572876</t>
   </si>
   <si>
     <t xml:space="preserve">7.20725393295288</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37105417251587</t>
+    <t xml:space="preserve">7.37105369567871</t>
   </si>
   <si>
     <t xml:space="preserve">7.57027149200439</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69422960281372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70308446884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71193838119507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6588134765625</t>
+    <t xml:space="preserve">7.6942286491394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70308351516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71193885803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65881252288818</t>
   </si>
   <si>
     <t xml:space="preserve">8.04396724700928</t>
@@ -317,10 +317,10 @@
     <t xml:space="preserve">7.61454343795776</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29579448699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99475431442261</t>
+    <t xml:space="preserve">7.29579401016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99475479125977</t>
   </si>
   <si>
     <t xml:space="preserve">7.10100412368774</t>
@@ -329,37 +329,37 @@
     <t xml:space="preserve">7.55256366729736</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31350231170654</t>
+    <t xml:space="preserve">7.31350326538086</t>
   </si>
   <si>
     <t xml:space="preserve">7.50829315185547</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42418050765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37548208236694</t>
+    <t xml:space="preserve">7.4241795539856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37548160552979</t>
   </si>
   <si>
     <t xml:space="preserve">7.52600193023682</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54370975494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41532421112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21610689163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99032735824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79996347427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7556939125061</t>
+    <t xml:space="preserve">7.54371023178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41532564163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21610641479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99032831192017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79996395111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75569343566895</t>
   </si>
   <si>
     <t xml:space="preserve">7.00803565979004</t>
@@ -368,88 +368,88 @@
     <t xml:space="preserve">7.26923274993896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34449291229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46402311325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51714754104614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39318943023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45516872406006</t>
+    <t xml:space="preserve">7.34449148178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46402263641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5171480178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39319038391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45516967773438</t>
   </si>
   <si>
     <t xml:space="preserve">7.1718373298645</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33563852310181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33121156692505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39761734008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30464887619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27808666229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25152397155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16298246383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03017091751099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87965106964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91064071655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95491170883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88850498199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95933818817139</t>
+    <t xml:space="preserve">7.33563804626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33121109008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39761686325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30464935302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27808618545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25152349472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16298294067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03017139434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8796501159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91063976287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95491075515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88850593566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9593391418457</t>
   </si>
   <si>
     <t xml:space="preserve">6.85751533508301</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77340221405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74683904647827</t>
+    <t xml:space="preserve">6.77340126037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74683856964111</t>
   </si>
   <si>
     <t xml:space="preserve">6.82652616500854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68485975265503</t>
+    <t xml:space="preserve">6.68486022949219</t>
   </si>
   <si>
     <t xml:space="preserve">6.81767177581787</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90621280670166</t>
+    <t xml:space="preserve">6.90621328353882</t>
   </si>
   <si>
     <t xml:space="preserve">7.01688957214355</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8973593711853</t>
+    <t xml:space="preserve">6.89735889434814</t>
   </si>
   <si>
     <t xml:space="preserve">6.83538007736206</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">6.92392158508301</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97704601287842</t>
+    <t xml:space="preserve">6.97704648971558</t>
   </si>
   <si>
     <t xml:space="preserve">7.00360774993896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91506719589233</t>
+    <t xml:space="preserve">6.91506671905518</t>
   </si>
   <si>
     <t xml:space="preserve">6.91949462890625</t>
@@ -476,13 +476,13 @@
     <t xml:space="preserve">6.93720293045044</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07001543045044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98589992523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75126647949219</t>
+    <t xml:space="preserve">7.07001447677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98589944839478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75126695632935</t>
   </si>
   <si>
     <t xml:space="preserve">6.77782869338989</t>
@@ -494,67 +494,67 @@
     <t xml:space="preserve">6.38382005691528</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37053966522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36168479919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37939357757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40595531463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4812159538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47678804397583</t>
+    <t xml:space="preserve">6.37053918838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36168527603149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37939405441284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40595579147339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48121547698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47678899765015</t>
   </si>
   <si>
     <t xml:space="preserve">6.54319429397583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46350717544556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24215459823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25986194610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22444629669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64501619338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64059019088745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0390248298645</t>
+    <t xml:space="preserve">6.46350765228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24215507507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25986242294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22444677352905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64501667022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64058971405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03902435302734</t>
   </si>
   <si>
     <t xml:space="preserve">6.79110956192017</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70256805419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70699548721313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65829753875732</t>
+    <t xml:space="preserve">6.70256853103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70699501037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65829849243164</t>
   </si>
   <si>
     <t xml:space="preserve">6.58303785324097</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05673313140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11428499221802</t>
+    <t xml:space="preserve">7.05673265457153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11428546905518</t>
   </si>
   <si>
     <t xml:space="preserve">7.34891891479492</t>
@@ -563,22 +563,22 @@
     <t xml:space="preserve">7.18511772155762</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12756729125977</t>
+    <t xml:space="preserve">7.12756633758545</t>
   </si>
   <si>
     <t xml:space="preserve">7.19397163391113</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24267053604126</t>
+    <t xml:space="preserve">7.2426700592041</t>
   </si>
   <si>
     <t xml:space="preserve">7.41089820861816</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48173141479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14527463912964</t>
+    <t xml:space="preserve">7.48172998428345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14527416229248</t>
   </si>
   <si>
     <t xml:space="preserve">7.27365922927856</t>
@@ -587,97 +587,97 @@
     <t xml:space="preserve">7.17626333236694</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04787969589233</t>
+    <t xml:space="preserve">7.04787874221802</t>
   </si>
   <si>
     <t xml:space="preserve">7.23381519317627</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29136610031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4286060333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83589601516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82704305648804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13693428039551</t>
+    <t xml:space="preserve">7.2913670539856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42860651016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83589696884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82704210281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13693523406982</t>
   </si>
   <si>
     <t xml:space="preserve">8.27860260009766</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32287120819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03120136260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53094482421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49995517730713</t>
+    <t xml:space="preserve">8.32287216186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03120040893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53094291687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49995613098145</t>
   </si>
   <si>
     <t xml:space="preserve">8.26089382171631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92495250701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58849716186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97807788848877</t>
+    <t xml:space="preserve">8.92495155334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58849430084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97807693481445</t>
   </si>
   <si>
     <t xml:space="preserve">8.76557731628418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87182807922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56244850158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25255489349365</t>
+    <t xml:space="preserve">8.87182903289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56244945526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25255393981934</t>
   </si>
   <si>
     <t xml:space="preserve">9.02234840393066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8541202545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82755565643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71245384216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98693084716797</t>
+    <t xml:space="preserve">8.85411930084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82755661010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7124547958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98693180084229</t>
   </si>
   <si>
     <t xml:space="preserve">8.89838981628418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80984878540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72130966186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78328800201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67703819274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75672340393066</t>
+    <t xml:space="preserve">8.80984973907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7213077545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78328514099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67703723907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75672435760498</t>
   </si>
   <si>
     <t xml:space="preserve">9.10203552246094</t>
@@ -686,13 +686,13 @@
     <t xml:space="preserve">8.82312965393066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94266033172607</t>
+    <t xml:space="preserve">8.94266128540039</t>
   </si>
   <si>
     <t xml:space="preserve">9.20828342437744</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43287563323975</t>
+    <t xml:space="preserve">9.43287754058838</t>
   </si>
   <si>
     <t xml:space="preserve">9.4598274230957</t>
@@ -704,19 +704,19 @@
     <t xml:space="preserve">9.32507228851318</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38795757293701</t>
+    <t xml:space="preserve">9.38795948028564</t>
   </si>
   <si>
     <t xml:space="preserve">9.35202312469482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4238920211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29812145233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55864810943604</t>
+    <t xml:space="preserve">9.42389297485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29812240600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55864906311035</t>
   </si>
   <si>
     <t xml:space="preserve">9.67543601989746</t>
@@ -725,10 +725,10 @@
     <t xml:space="preserve">9.86409378051758</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5199031829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0617351531982</t>
+    <t xml:space="preserve">10.5199041366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0617361068726</t>
   </si>
   <si>
     <t xml:space="preserve">9.88206100463867</t>
@@ -737,25 +737,25 @@
     <t xml:space="preserve">9.74730587005615</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5676326751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44186019897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54067993164062</t>
+    <t xml:space="preserve">9.56763172149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44185924530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54068183898926</t>
   </si>
   <si>
     <t xml:space="preserve">9.34303951263428</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36100769042969</t>
+    <t xml:space="preserve">9.36100578308105</t>
   </si>
   <si>
     <t xml:space="preserve">9.50474548339844</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48678016662598</t>
+    <t xml:space="preserve">9.48677921295166</t>
   </si>
   <si>
     <t xml:space="preserve">9.61255073547363</t>
@@ -770,16 +770,16 @@
     <t xml:space="preserve">9.54966449737549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4777946472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70238780975342</t>
+    <t xml:space="preserve">9.47779560089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7023868560791</t>
   </si>
   <si>
     <t xml:space="preserve">9.30710411071777</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28015327453613</t>
+    <t xml:space="preserve">9.28015422821045</t>
   </si>
   <si>
     <t xml:space="preserve">9.2172679901123</t>
@@ -788,37 +788,37 @@
     <t xml:space="preserve">9.16336631774902</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25320243835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45084476470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58559989929199</t>
+    <t xml:space="preserve">9.25320148468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45084381103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58559894561768</t>
   </si>
   <si>
     <t xml:space="preserve">9.33405685424805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59458255767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66645336151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71137237548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40592670440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26218700408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27116870880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28913688659668</t>
+    <t xml:space="preserve">9.59458446502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66645050048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71137046813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40592479705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26218605041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27116966247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28913593292236</t>
   </si>
   <si>
     <t xml:space="preserve">9.36999130249023</t>
@@ -827,55 +827,55 @@
     <t xml:space="preserve">9.65746879577637</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79222393035889</t>
+    <t xml:space="preserve">9.7922248840332</t>
   </si>
   <si>
     <t xml:space="preserve">9.76527309417725</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72035598754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81019020080566</t>
+    <t xml:space="preserve">9.72035503387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81019115447998</t>
   </si>
   <si>
     <t xml:space="preserve">9.37897396087646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90901279449463</t>
+    <t xml:space="preserve">9.90901184082031</t>
   </si>
   <si>
     <t xml:space="preserve">9.81917572021484</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73832130432129</t>
+    <t xml:space="preserve">9.73832225799561</t>
   </si>
   <si>
     <t xml:space="preserve">9.78324127197266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69340229034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11844825744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08251285552979</t>
+    <t xml:space="preserve">9.69340419769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11844635009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08251190185547</t>
   </si>
   <si>
     <t xml:space="preserve">9.31608963012695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19031620025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10048007965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22625255584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41491031646729</t>
+    <t xml:space="preserve">9.19031715393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10047912597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22625160217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41490936279297</t>
   </si>
   <si>
     <t xml:space="preserve">9.39694118499756</t>
@@ -890,58 +890,58 @@
     <t xml:space="preserve">9.68441963195801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09149551391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05556011199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14539813995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89385414123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10946559906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23523712158203</t>
+    <t xml:space="preserve">9.09149646759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05556106567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14539909362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89385509490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10946369171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23523616790771</t>
   </si>
   <si>
     <t xml:space="preserve">9.95393085479736</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5109195709229</t>
+    <t xml:space="preserve">10.5109205245972</t>
   </si>
   <si>
     <t xml:space="preserve">10.7444953918457</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5468549728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6905927658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9062032699585</t>
+    <t xml:space="preserve">10.546854019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6905937194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9062023162842</t>
   </si>
   <si>
     <t xml:space="preserve">10.7804307937622</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7085590362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6546583175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5288867950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4390497207642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3312454223633</t>
+    <t xml:space="preserve">10.7085609436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6546592712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5288877487183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4390506744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3312463760376</t>
   </si>
   <si>
     <t xml:space="preserve">10.1695394515991</t>
@@ -950,10 +950,10 @@
     <t xml:space="preserve">10.1875076293945</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1336040496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7562894821167</t>
+    <t xml:space="preserve">10.1336030960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75628852844238</t>
   </si>
   <si>
     <t xml:space="preserve">9.63051795959473</t>
@@ -962,16 +962,16 @@
     <t xml:space="preserve">10.007833480835</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84612560272217</t>
+    <t xml:space="preserve">9.8461275100708</t>
   </si>
   <si>
     <t xml:space="preserve">10.0976696014404</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2054748535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.27734375</t>
+    <t xml:space="preserve">10.2054738998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2773418426514</t>
   </si>
   <si>
     <t xml:space="preserve">10.2234401702881</t>
@@ -980,7 +980,7 @@
     <t xml:space="preserve">10.2414093017578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7624626159668</t>
+    <t xml:space="preserve">10.7624616622925</t>
   </si>
   <si>
     <t xml:space="preserve">10.2593755722046</t>
@@ -992,49 +992,49 @@
     <t xml:space="preserve">9.90002918243408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67380619049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74667835235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87420463562012</t>
+    <t xml:space="preserve">9.67380714416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74667930603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87420558929443</t>
   </si>
   <si>
     <t xml:space="preserve">10.1656951904297</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85598850250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63736915588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47340679168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7648983001709</t>
+    <t xml:space="preserve">9.85598754882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63737010955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47340774536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76489734649658</t>
   </si>
   <si>
     <t xml:space="preserve">9.96529579162598</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0746059417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2385692596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3843116760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.420747756958</t>
+    <t xml:space="preserve">10.0746049880981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2385673522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3843126296997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4207468032837</t>
   </si>
   <si>
     <t xml:space="preserve">10.8033285140991</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6940202713013</t>
+    <t xml:space="preserve">10.694019317627</t>
   </si>
   <si>
     <t xml:space="preserve">10.6211471557617</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">10.5482749938965</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4025287628174</t>
+    <t xml:space="preserve">10.4025297164917</t>
   </si>
   <si>
     <t xml:space="preserve">10.2203502655029</t>
@@ -1058,16 +1058,16 @@
     <t xml:space="preserve">10.3296585083008</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5847101211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3478765487671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72846126556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56449794769287</t>
+    <t xml:space="preserve">10.5847120285034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3478755950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72846221923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56449890136719</t>
   </si>
   <si>
     <t xml:space="preserve">9.41875171661377</t>
@@ -1082,52 +1082,52 @@
     <t xml:space="preserve">10.1110410690308</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2567853927612</t>
+    <t xml:space="preserve">10.2567844390869</t>
   </si>
   <si>
     <t xml:space="preserve">9.92886066436768</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0199508666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2021312713623</t>
+    <t xml:space="preserve">10.0199499130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2021322250366</t>
   </si>
   <si>
     <t xml:space="preserve">10.0928230285645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8013334274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69202423095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83776950836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94707679748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89242362976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65558815002441</t>
+    <t xml:space="preserve">9.80133152008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69202518463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8377685546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94707775115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89242267608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65558910369873</t>
   </si>
   <si>
     <t xml:space="preserve">9.78311443328857</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91064167022705</t>
+    <t xml:space="preserve">9.91064262390137</t>
   </si>
   <si>
     <t xml:space="preserve">9.45518970489502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2001371383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50984382629395</t>
+    <t xml:space="preserve">9.20013618469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50984287261963</t>
   </si>
   <si>
     <t xml:space="preserve">9.43697071075439</t>
@@ -1145,31 +1145,31 @@
     <t xml:space="preserve">9.9835147857666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60093402862549</t>
+    <t xml:space="preserve">9.6009349822998</t>
   </si>
   <si>
     <t xml:space="preserve">9.10904502868652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09993648529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38231658935547</t>
+    <t xml:space="preserve">9.09993743896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38231563568115</t>
   </si>
   <si>
     <t xml:space="preserve">9.36409950256348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27300834655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71024322509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5827169418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29122638702393</t>
+    <t xml:space="preserve">9.27300930023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71024227142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58271598815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29122734069824</t>
   </si>
   <si>
     <t xml:space="preserve">9.14548206329346</t>
@@ -1178,67 +1178,67 @@
     <t xml:space="preserve">10.3660926818848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32766246795654</t>
+    <t xml:space="preserve">9.32766342163086</t>
   </si>
   <si>
     <t xml:space="preserve">10.0017318725586</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4754018783569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8397636413574</t>
+    <t xml:space="preserve">10.4754028320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8397645950317</t>
   </si>
   <si>
     <t xml:space="preserve">10.5664930343628</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3114404678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2932233810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0381698608398</t>
+    <t xml:space="preserve">10.3114395141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2932224273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0381689071655</t>
   </si>
   <si>
     <t xml:space="preserve">10.0563859939575</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1292581558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2750034332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.183913230896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6758012771606</t>
+    <t xml:space="preserve">10.1292591094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2750024795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1839141845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.675802230835</t>
   </si>
   <si>
     <t xml:space="preserve">10.7122373580933</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9308547973633</t>
+    <t xml:space="preserve">10.9308557510376</t>
   </si>
   <si>
     <t xml:space="preserve">11.0219459533691</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8762006759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8944177627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7304553985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6575832366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2644624710083</t>
+    <t xml:space="preserve">10.87619972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8944187164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7304544448853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6575841903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2644643783569</t>
   </si>
   <si>
     <t xml:space="preserve">11.1349868774414</t>
@@ -1247,28 +1247,28 @@
     <t xml:space="preserve">11.097993850708</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2459678649902</t>
+    <t xml:space="preserve">11.2459669113159</t>
   </si>
   <si>
     <t xml:space="preserve">11.319953918457</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0240049362183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8205432891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8390398025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7280607223511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8575372695923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7095632553101</t>
+    <t xml:space="preserve">11.0240068435669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8205423355103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8390417098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7280597686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.857536315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7095642089844</t>
   </si>
   <si>
     <t xml:space="preserve">10.6725702285767</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">10.7835512161255</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7650537490845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8020467758179</t>
+    <t xml:space="preserve">10.7650547027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8020477294922</t>
   </si>
   <si>
     <t xml:space="preserve">10.5615901947021</t>
@@ -1292,37 +1292,37 @@
     <t xml:space="preserve">10.6170797348022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3951215744019</t>
+    <t xml:space="preserve">10.3951206207275</t>
   </si>
   <si>
     <t xml:space="preserve">10.1176700592041</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2841396331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2656440734863</t>
+    <t xml:space="preserve">10.284140586853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2656450271606</t>
   </si>
   <si>
     <t xml:space="preserve">10.3026371002197</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5061006546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3396301269531</t>
+    <t xml:space="preserve">10.5060987472534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3396310806274</t>
   </si>
   <si>
     <t xml:space="preserve">10.1361675262451</t>
   </si>
   <si>
-    <t xml:space="preserve">10.080677986145</t>
+    <t xml:space="preserve">10.0806770324707</t>
   </si>
   <si>
     <t xml:space="preserve">9.98819446563721</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0991735458374</t>
+    <t xml:space="preserve">10.0991744995117</t>
   </si>
   <si>
     <t xml:space="preserve">9.93270301818848</t>
@@ -1337,25 +1337,25 @@
     <t xml:space="preserve">10.1731605529785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0621795654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1546630859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71074295043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0251865386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91420841217041</t>
+    <t xml:space="preserve">10.062180519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1546640396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71074390411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0251874923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91420745849609</t>
   </si>
   <si>
     <t xml:space="preserve">9.7662353515625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7292423248291</t>
+    <t xml:space="preserve">9.72924137115479</t>
   </si>
   <si>
     <t xml:space="preserve">9.65525341033936</t>
@@ -1364,52 +1364,52 @@
     <t xml:space="preserve">9.67375183105469</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47028732299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54427433013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56276988983154</t>
+    <t xml:space="preserve">9.47028827667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54427337646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56277084350586</t>
   </si>
   <si>
     <t xml:space="preserve">9.45179271697998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35930824279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52577686309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59976482391357</t>
+    <t xml:space="preserve">9.35930919647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52577590942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59976387023926</t>
   </si>
   <si>
     <t xml:space="preserve">9.61826038360596</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69224834442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80322742462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2286520004272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78472995758057</t>
+    <t xml:space="preserve">9.69224643707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80322933197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2286510467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78473091125488</t>
   </si>
   <si>
     <t xml:space="preserve">9.858717918396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0066919326782</t>
+    <t xml:space="preserve">10.0066900253296</t>
   </si>
   <si>
     <t xml:space="preserve">9.8772144317627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74773693084717</t>
+    <t xml:space="preserve">9.74773788452148</t>
   </si>
   <si>
     <t xml:space="preserve">9.58126735687256</t>
@@ -1418,22 +1418,22 @@
     <t xml:space="preserve">10.3211336135864</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4321136474609</t>
+    <t xml:space="preserve">10.4321126937866</t>
   </si>
   <si>
     <t xml:space="preserve">10.3766241073608</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2471466064453</t>
+    <t xml:space="preserve">10.2471475601196</t>
   </si>
   <si>
     <t xml:space="preserve">10.2101535797119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84022045135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63675785064697</t>
+    <t xml:space="preserve">9.8402214050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63675689697266</t>
   </si>
   <si>
     <t xml:space="preserve">9.43329429626465</t>
@@ -1442,13 +1442,13 @@
     <t xml:space="preserve">9.41479873657227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39629936218262</t>
+    <t xml:space="preserve">9.39630031585693</t>
   </si>
   <si>
     <t xml:space="preserve">9.24832725524902</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06336116790771</t>
+    <t xml:space="preserve">9.06336212158203</t>
   </si>
   <si>
     <t xml:space="preserve">9.10960388183594</t>
@@ -1460,16 +1460,16 @@
     <t xml:space="preserve">9.28532123565674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26682472229004</t>
+    <t xml:space="preserve">9.26682376861572</t>
   </si>
   <si>
     <t xml:space="preserve">9.19283866882324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22983169555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48878383636475</t>
+    <t xml:space="preserve">9.22983074188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48878479003906</t>
   </si>
   <si>
     <t xml:space="preserve">9.0263671875</t>
@@ -1478,10 +1478,10 @@
     <t xml:space="preserve">8.97087860107422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13734912872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96162986755371</t>
+    <t xml:space="preserve">9.13734817504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96162891387939</t>
   </si>
   <si>
     <t xml:space="preserve">8.82290458679199</t>
@@ -1499,13 +1499,13 @@
     <t xml:space="preserve">8.33274364471436</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01830005645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8148365020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95356273651123</t>
+    <t xml:space="preserve">8.01830101013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81483697891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95356178283691</t>
   </si>
   <si>
     <t xml:space="preserve">7.49114608764648</t>
@@ -1514,28 +1514,28 @@
     <t xml:space="preserve">7.8610782623291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50964260101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53738641738892</t>
+    <t xml:space="preserve">7.50964212417603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53738594055176</t>
   </si>
   <si>
     <t xml:space="preserve">7.58362865447998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76741409301758</t>
+    <t xml:space="preserve">8.76741504669189</t>
   </si>
   <si>
     <t xml:space="preserve">8.98937511444092</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1650915145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.128098487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09110641479492</t>
+    <t xml:space="preserve">9.16509246826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12809944152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09110546112061</t>
   </si>
   <si>
     <t xml:space="preserve">9.0818567276001</t>
@@ -1544,25 +1544,25 @@
     <t xml:space="preserve">9.34081077575684</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04486465454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21133422851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38705253601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17434024810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29456996917725</t>
+    <t xml:space="preserve">9.0448637008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21133327484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38705062866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17434120178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29456901550293</t>
   </si>
   <si>
     <t xml:space="preserve">9.11885070800781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78591060638428</t>
+    <t xml:space="preserve">8.78591156005859</t>
   </si>
   <si>
     <t xml:space="preserve">8.89689064025879</t>
@@ -1571,16 +1571,16 @@
     <t xml:space="preserve">8.7489185333252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80440807342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87839508056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93388366699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63793849945068</t>
+    <t xml:space="preserve">8.80440902709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87839603424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9338846206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63793754577637</t>
   </si>
   <si>
     <t xml:space="preserve">8.71192455291748</t>
@@ -1592,22 +1592,22 @@
     <t xml:space="preserve">8.69342803955078</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46113967895508</t>
+    <t xml:space="preserve">9.46113872528076</t>
   </si>
   <si>
     <t xml:space="preserve">9.6494197845459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69649028778076</t>
+    <t xml:space="preserve">9.69648933410645</t>
   </si>
   <si>
     <t xml:space="preserve">9.74356174468994</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97891235351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93184280395508</t>
+    <t xml:space="preserve">9.97891426086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93184185028076</t>
   </si>
   <si>
     <t xml:space="preserve">9.79063129425049</t>
@@ -1616,70 +1616,70 @@
     <t xml:space="preserve">10.0730533599854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.308406829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4496164321899</t>
+    <t xml:space="preserve">10.3084049224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4496173858643</t>
   </si>
   <si>
     <t xml:space="preserve">10.1671943664551</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1201229095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0259838104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2142658233643</t>
+    <t xml:space="preserve">10.1201238632202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0259828567505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2142648696899</t>
   </si>
   <si>
     <t xml:space="preserve">10.3554754257202</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2613353729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8847713470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5908260345459</t>
+    <t xml:space="preserve">10.2613344192505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88477230072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5908279418945</t>
   </si>
   <si>
     <t xml:space="preserve">10.4966869354248</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5437574386597</t>
+    <t xml:space="preserve">10.543758392334</t>
   </si>
   <si>
     <t xml:space="preserve">11.2027416229248</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1556711196899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9673900604248</t>
+    <t xml:space="preserve">11.1556720733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9673891067505</t>
   </si>
   <si>
     <t xml:space="preserve">11.0615301132202</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7791090011597</t>
+    <t xml:space="preserve">10.779109954834</t>
   </si>
   <si>
     <t xml:space="preserve">10.8261785507202</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0144605636597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1086015701294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9203205108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8732490539551</t>
+    <t xml:space="preserve">11.0144596099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1085996627808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9203195571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8732481002808</t>
   </si>
   <si>
     <t xml:space="preserve">10.7320384979248</t>
@@ -1691,7 +1691,7 @@
     <t xml:space="preserve">11.5322341918945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6263742446899</t>
+    <t xml:space="preserve">11.6263751983643</t>
   </si>
   <si>
     <t xml:space="preserve">11.7675857543945</t>
@@ -1703,25 +1703,25 @@
     <t xml:space="preserve">11.5793046951294</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6734457015991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7205152511597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0029373168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2853603363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5677824020386</t>
+    <t xml:space="preserve">11.6734437942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.720516204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0029382705688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2853593826294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5677814483643</t>
   </si>
   <si>
     <t xml:space="preserve">12.5207109451294</t>
   </si>
   <si>
-    <t xml:space="preserve">12.897274017334</t>
+    <t xml:space="preserve">12.8972749710083</t>
   </si>
   <si>
     <t xml:space="preserve">12.7560634613037</t>
@@ -1733,10 +1733,10 @@
     <t xml:space="preserve">12.6148519515991</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8031330108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8502035140991</t>
+    <t xml:space="preserve">12.8031339645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8502025604248</t>
   </si>
   <si>
     <t xml:space="preserve">12.9914140701294</t>
@@ -1745,34 +1745,34 @@
     <t xml:space="preserve">13.1796960830688</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4621181488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.838680267334</t>
+    <t xml:space="preserve">13.462119102478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8386812210083</t>
   </si>
   <si>
     <t xml:space="preserve">13.7445402145386</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6503992080688</t>
+    <t xml:space="preserve">13.6504001617432</t>
   </si>
   <si>
     <t xml:space="preserve">13.5091896057129</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7916107177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8857517242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9798927307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0269622802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0740327835083</t>
+    <t xml:space="preserve">13.7916097640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8857507705688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9798917770386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0269613265991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0740337371826</t>
   </si>
   <si>
     <t xml:space="preserve">14.1681728363037</t>
@@ -1784,31 +1784,31 @@
     <t xml:space="preserve">14.2623138427734</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2152452468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4505958557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6859483718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3093852996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.403525352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3564538955688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5447368621826</t>
+    <t xml:space="preserve">14.2152442932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4505968093872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6859474182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3093843460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4035243988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3564548492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5447359085083</t>
   </si>
   <si>
     <t xml:space="preserve">14.5918064117432</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6388759613037</t>
+    <t xml:space="preserve">14.638876914978</t>
   </si>
   <si>
     <t xml:space="preserve">14.7800884246826</t>
@@ -1817,34 +1817,34 @@
     <t xml:space="preserve">14.8271589279175</t>
   </si>
   <si>
-    <t xml:space="preserve">14.874228477478</t>
+    <t xml:space="preserve">14.8742294311523</t>
   </si>
   <si>
     <t xml:space="preserve">14.7330169677734</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3449306488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7685642242432</t>
+    <t xml:space="preserve">15.3449296951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7685651779175</t>
   </si>
   <si>
     <t xml:space="preserve">16.0039157867432</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0415744781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0792293548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1921997070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.116886138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2298545837402</t>
+    <t xml:space="preserve">16.041576385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.079231262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1921977996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1168842315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2298564910889</t>
   </si>
   <si>
     <t xml:space="preserve">16.3804779052734</t>
@@ -1853,16 +1853,16 @@
     <t xml:space="preserve">16.3993091583252</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4181346893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5311050415039</t>
+    <t xml:space="preserve">16.4181365966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5311031341553</t>
   </si>
   <si>
     <t xml:space="preserve">16.2675113677979</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9286050796509</t>
+    <t xml:space="preserve">15.9286041259766</t>
   </si>
   <si>
     <t xml:space="preserve">15.8909473419189</t>
@@ -1871,52 +1871,52 @@
     <t xml:space="preserve">15.815634727478</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9662590026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7214956283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5332145690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5143842697144</t>
+    <t xml:space="preserve">15.9662618637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7214965820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5332136154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5143871307373</t>
   </si>
   <si>
     <t xml:space="preserve">15.7026672363281</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2696189880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4767284393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6838369369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6650104522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4202442169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1566514968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2319631576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7779788970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9833707809448</t>
+    <t xml:space="preserve">15.2696208953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4767303466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6838388442993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6650085449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4202432632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1566505432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2319641113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.777979850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9833717346191</t>
   </si>
   <si>
     <t xml:space="preserve">15.964301109314</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6209812164307</t>
+    <t xml:space="preserve">15.6209802627563</t>
   </si>
   <si>
     <t xml:space="preserve">15.4874696731567</t>
@@ -1928,31 +1928,31 @@
     <t xml:space="preserve">15.8117141723633</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6019086837769</t>
+    <t xml:space="preserve">15.6019096374512</t>
   </si>
   <si>
     <t xml:space="preserve">15.5446872711182</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2585906982422</t>
+    <t xml:space="preserve">15.2585897445679</t>
   </si>
   <si>
     <t xml:space="preserve">15.6972723007202</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8307867050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2503986358643</t>
+    <t xml:space="preserve">15.8307876586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2504005432129</t>
   </si>
   <si>
     <t xml:space="preserve">16.2313251495361</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0024471282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2694721221924</t>
+    <t xml:space="preserve">16.0024452209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2694683074951</t>
   </si>
   <si>
     <t xml:space="preserve">16.212251663208</t>
@@ -1961,13 +1961,13 @@
     <t xml:space="preserve">16.460205078125</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4411315917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5364971160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5555725097656</t>
+    <t xml:space="preserve">16.4411296844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5364952087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.555570602417</t>
   </si>
   <si>
     <t xml:space="preserve">17.1659145355225</t>
@@ -1976,28 +1976,28 @@
     <t xml:space="preserve">16.9561080932617</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2231349945068</t>
+    <t xml:space="preserve">17.2231330871582</t>
   </si>
   <si>
     <t xml:space="preserve">17.3185005187988</t>
   </si>
   <si>
-    <t xml:space="preserve">17.08962059021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8416690826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7463035583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9751815795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1277675628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5092334747314</t>
+    <t xml:space="preserve">17.0896224975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.841667175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.746301651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9751796722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1277656555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5092315673828</t>
   </si>
   <si>
     <t xml:space="preserve">17.5473785400391</t>
@@ -2006,13 +2006,13 @@
     <t xml:space="preserve">17.7571849822998</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6427459716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7381134033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4901580810547</t>
+    <t xml:space="preserve">17.6427440643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7381114959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4901599884033</t>
   </si>
   <si>
     <t xml:space="preserve">17.4710865020752</t>
@@ -2027,10 +2027,10 @@
     <t xml:space="preserve">17.3566474914551</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2422065734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1468391418457</t>
+    <t xml:space="preserve">17.2422046661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1468410491943</t>
   </si>
   <si>
     <t xml:space="preserve">17.0133266448975</t>
@@ -2042,13 +2042,13 @@
     <t xml:space="preserve">17.8334789276123</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6999645233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8716220855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8525505065918</t>
+    <t xml:space="preserve">17.6999626159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8716239929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8525485992432</t>
   </si>
   <si>
     <t xml:space="preserve">18.0242099761963</t>
@@ -2057,61 +2057,61 @@
     <t xml:space="preserve">18.424747467041</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5010395050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6536254882812</t>
+    <t xml:space="preserve">18.5010414123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6536235809326</t>
   </si>
   <si>
     <t xml:space="preserve">18.5964069366455</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5582580566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7108478546143</t>
+    <t xml:space="preserve">18.5582599639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7108459472656</t>
   </si>
   <si>
     <t xml:space="preserve">18.8062114715576</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5201148986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.55006980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5023880004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8838520050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9792194366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.454704284668</t>
+    <t xml:space="preserve">18.520112991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5500679016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5023860931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8838500976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9792156219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4547023773193</t>
   </si>
   <si>
     <t xml:space="preserve">19.3593349456787</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1686058044434</t>
+    <t xml:space="preserve">19.1686038970947</t>
   </si>
   <si>
     <t xml:space="preserve">18.7871398925781</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6917743682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.216287612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.120922088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.76806640625</t>
+    <t xml:space="preserve">18.6917724609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2162857055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1209182739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7680644989014</t>
   </si>
   <si>
     <t xml:space="preserve">17.9097709655762</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">18.1195755004883</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6236686706543</t>
+    <t xml:space="preserve">17.6236724853516</t>
   </si>
   <si>
     <t xml:space="preserve">17.890697479248</t>
@@ -2132,10 +2132,10 @@
     <t xml:space="preserve">18.2530860900879</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9669876098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1767959594727</t>
+    <t xml:space="preserve">17.9669895172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.176794052124</t>
   </si>
   <si>
     <t xml:space="preserve">18.9969444274902</t>
@@ -2144,19 +2144,19 @@
     <t xml:space="preserve">19.0732383728027</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9778728485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8825054168701</t>
+    <t xml:space="preserve">18.9778709411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8825035095215</t>
   </si>
   <si>
     <t xml:space="preserve">18.9397258758545</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9015769958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0268993377686</t>
+    <t xml:space="preserve">18.9015808105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0268974304199</t>
   </si>
   <si>
     <t xml:space="preserve">20.2176322937012</t>
@@ -2168,7 +2168,7 @@
     <t xml:space="preserve">20.7421455383301</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9328804016113</t>
+    <t xml:space="preserve">20.9328765869141</t>
   </si>
   <si>
     <t xml:space="preserve">21.2189769744873</t>
@@ -2183,22 +2183,22 @@
     <t xml:space="preserve">20.3129978179932</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4560489654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9805603027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8361682891846</t>
+    <t xml:space="preserve">20.4560470581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.980562210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8361663818359</t>
   </si>
   <si>
     <t xml:space="preserve">20.4083652496338</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1222667694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3116550445557</t>
+    <t xml:space="preserve">20.1222648620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.311653137207</t>
   </si>
   <si>
     <t xml:space="preserve">19.2639713287354</t>
@@ -2207,7 +2207,7 @@
     <t xml:space="preserve">19.5977516174316</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6454372406006</t>
+    <t xml:space="preserve">19.6454334259033</t>
   </si>
   <si>
     <t xml:space="preserve">20.1699485778809</t>
@@ -2216,16 +2216,16 @@
     <t xml:space="preserve">19.9315338134766</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7408027648926</t>
+    <t xml:space="preserve">19.7408008575439</t>
   </si>
   <si>
     <t xml:space="preserve">18.8443584442139</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0160179138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0432834625244</t>
+    <t xml:space="preserve">19.016019821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0432815551758</t>
   </si>
   <si>
     <t xml:space="preserve">18.0051364898682</t>
@@ -2234,16 +2234,16 @@
     <t xml:space="preserve">18.1386489868164</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0623550415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.081428527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6045970916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2612819671631</t>
+    <t xml:space="preserve">18.0623588562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0814266204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6045989990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2612800598145</t>
   </si>
   <si>
     <t xml:space="preserve">17.0514736175537</t>
@@ -2252,37 +2252,37 @@
     <t xml:space="preserve">16.2885456085205</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0324020385742</t>
+    <t xml:space="preserve">17.0324039459229</t>
   </si>
   <si>
     <t xml:space="preserve">16.7272300720215</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4792766571045</t>
+    <t xml:space="preserve">16.4792785644531</t>
   </si>
   <si>
     <t xml:space="preserve">16.8225936889648</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0705490112305</t>
+    <t xml:space="preserve">17.0705471038818</t>
   </si>
   <si>
     <t xml:space="preserve">16.650936126709</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8607406616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3076190948486</t>
+    <t xml:space="preserve">16.8607425689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3076171875</t>
   </si>
   <si>
     <t xml:space="preserve">16.5937175750732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6318626403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2776641845703</t>
+    <t xml:space="preserve">16.6318664550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.277663230896</t>
   </si>
   <si>
     <t xml:space="preserve">14.8771257400513</t>
@@ -2294,22 +2294,22 @@
     <t xml:space="preserve">15.3730306625366</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9915657043457</t>
+    <t xml:space="preserve">14.9915647506714</t>
   </si>
   <si>
     <t xml:space="preserve">15.0869312286377</t>
   </si>
   <si>
-    <t xml:space="preserve">15.678201675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1441497802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9452266693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0787391662598</t>
+    <t xml:space="preserve">15.6782026290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1441507339478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9452247619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0787410736084</t>
   </si>
   <si>
     <t xml:space="preserve">16.0405921936035</t>
@@ -2321,7 +2321,7 @@
     <t xml:space="preserve">16.6890830993652</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5174217224121</t>
+    <t xml:space="preserve">16.5174255371094</t>
   </si>
   <si>
     <t xml:space="preserve">16.4983501434326</t>
@@ -2330,10 +2330,10 @@
     <t xml:space="preserve">15.7354202270508</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8880052566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5065412521362</t>
+    <t xml:space="preserve">15.8880062103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5065422058105</t>
   </si>
   <si>
     <t xml:space="preserve">14.9724912643433</t>
@@ -2342,7 +2342,7 @@
     <t xml:space="preserve">15.3348827362061</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2204427719116</t>
+    <t xml:space="preserve">15.2204437255859</t>
   </si>
   <si>
     <t xml:space="preserve">14.9152727127075</t>
@@ -2354,40 +2354,40 @@
     <t xml:space="preserve">14.8961982727051</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6400547027588</t>
+    <t xml:space="preserve">15.6400556564331</t>
   </si>
   <si>
     <t xml:space="preserve">16.0978126525879</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2395153045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1060047149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0063896179199</t>
+    <t xml:space="preserve">15.2395162582397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1060028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0063877105713</t>
   </si>
   <si>
     <t xml:space="preserve">16.1999359130859</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3547744750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0450973510742</t>
+    <t xml:space="preserve">16.354772567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0450954437256</t>
   </si>
   <si>
     <t xml:space="preserve">16.1418704986572</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2773532867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4709014892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7805786132812</t>
+    <t xml:space="preserve">16.2773551940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4709033966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7805767059326</t>
   </si>
   <si>
     <t xml:space="preserve">17.1483173370361</t>
@@ -2414,7 +2414,7 @@
     <t xml:space="preserve">17.5934772491455</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4579944610596</t>
+    <t xml:space="preserve">17.4579963684082</t>
   </si>
   <si>
     <t xml:space="preserve">16.8967056274414</t>
@@ -2423,28 +2423,28 @@
     <t xml:space="preserve">16.4515476226807</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9870338439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8321952819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9483222961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3676795959473</t>
+    <t xml:space="preserve">15.9870328903198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8321943283081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9483213424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3676805496216</t>
   </si>
   <si>
     <t xml:space="preserve">15.4450988769531</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1741333007812</t>
+    <t xml:space="preserve">15.1741323471069</t>
   </si>
   <si>
     <t xml:space="preserve">15.1160678863525</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1354236602783</t>
+    <t xml:space="preserve">15.135422706604</t>
   </si>
   <si>
     <t xml:space="preserve">15.3289709091187</t>
@@ -2453,13 +2453,13 @@
     <t xml:space="preserve">15.619291305542</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8902606964111</t>
+    <t xml:space="preserve">15.8902587890625</t>
   </si>
   <si>
     <t xml:space="preserve">15.7547760009766</t>
   </si>
   <si>
-    <t xml:space="preserve">15.812840461731</t>
+    <t xml:space="preserve">15.8128395080566</t>
   </si>
   <si>
     <t xml:space="preserve">16.161226272583</t>
@@ -2468,25 +2468,25 @@
     <t xml:space="preserve">15.6580018997192</t>
   </si>
   <si>
-    <t xml:space="preserve">15.870903968811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4128360748291</t>
+    <t xml:space="preserve">15.8709030151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4128379821777</t>
   </si>
   <si>
     <t xml:space="preserve">16.4321918487549</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7160663604736</t>
+    <t xml:space="preserve">15.7160654067993</t>
   </si>
   <si>
     <t xml:space="preserve">16.0644512176514</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5289669036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6838054656982</t>
+    <t xml:space="preserve">16.5289649963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6838035583496</t>
   </si>
   <si>
     <t xml:space="preserve">16.5096111297607</t>
@@ -2495,31 +2495,31 @@
     <t xml:space="preserve">16.9160594940186</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5354137420654</t>
+    <t xml:space="preserve">17.5354156494141</t>
   </si>
   <si>
     <t xml:space="preserve">17.3805751800537</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3418655395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2063827514648</t>
+    <t xml:space="preserve">17.3418674468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2063808441162</t>
   </si>
   <si>
     <t xml:space="preserve">17.3225116729736</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2838020324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0515441894531</t>
+    <t xml:space="preserve">17.2838039398193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0515460968018</t>
   </si>
   <si>
     <t xml:space="preserve">16.8386421203613</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2450904846191</t>
+    <t xml:space="preserve">17.2450923919678</t>
   </si>
   <si>
     <t xml:space="preserve">17.6128330230713</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">16.7225131988525</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1289653778076</t>
+    <t xml:space="preserve">17.128963470459</t>
   </si>
   <si>
     <t xml:space="preserve">16.8773517608643</t>
@@ -2546,7 +2546,7 @@
     <t xml:space="preserve">16.4902572631836</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1225147247314</t>
+    <t xml:space="preserve">16.1225166320801</t>
   </si>
   <si>
     <t xml:space="preserve">16.0257415771484</t>
@@ -2561,13 +2561,13 @@
     <t xml:space="preserve">15.3096160888672</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5805835723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1547775268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1934871673584</t>
+    <t xml:space="preserve">15.5805826187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1547765731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1934881210327</t>
   </si>
   <si>
     <t xml:space="preserve">16.0838069915771</t>
@@ -2576,13 +2576,13 @@
     <t xml:space="preserve">15.7741289138794</t>
   </si>
   <si>
-    <t xml:space="preserve">15.677357673645</t>
+    <t xml:space="preserve">15.6773567199707</t>
   </si>
   <si>
     <t xml:space="preserve">15.5612277984619</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1805801391602</t>
+    <t xml:space="preserve">16.1805820465088</t>
   </si>
   <si>
     <t xml:space="preserve">16.8579978942871</t>
@@ -2597,25 +2597,25 @@
     <t xml:space="preserve">17.8063793182373</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1676731109619</t>
+    <t xml:space="preserve">17.1676712036133</t>
   </si>
   <si>
     <t xml:space="preserve">17.5160598754883</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3612194061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.735408782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6579914093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4837970733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1741218566895</t>
+    <t xml:space="preserve">17.3612213134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7354106903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6579895019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4837989807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1741199493408</t>
   </si>
   <si>
     <t xml:space="preserve">17.7870235443115</t>
@@ -2624,7 +2624,7 @@
     <t xml:space="preserve">18.2515392303467</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8837966918945</t>
+    <t xml:space="preserve">17.8837985992432</t>
   </si>
   <si>
     <t xml:space="preserve">18.0386352539062</t>
@@ -2645,7 +2645,7 @@
     <t xml:space="preserve">18.0192832946777</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9805736541748</t>
+    <t xml:space="preserve">17.9805717468262</t>
   </si>
   <si>
     <t xml:space="preserve">17.961217880249</t>
@@ -2654,7 +2654,7 @@
     <t xml:space="preserve">17.8450908660889</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6902503967285</t>
+    <t xml:space="preserve">17.6902523040771</t>
   </si>
   <si>
     <t xml:space="preserve">17.6321868896484</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">17.6515426635742</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4386405944824</t>
+    <t xml:space="preserve">17.4386425018311</t>
   </si>
   <si>
     <t xml:space="preserve">17.3999290466309</t>
@@ -2672,22 +2672,22 @@
     <t xml:space="preserve">17.2644462585449</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7096042633057</t>
+    <t xml:space="preserve">17.7096061706543</t>
   </si>
   <si>
     <t xml:space="preserve">17.4773502349854</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8257369995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5805702209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.928955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8128299713135</t>
+    <t xml:space="preserve">17.8257350921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5805721282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9289569854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8128280639648</t>
   </si>
   <si>
     <t xml:space="preserve">19.5483093261719</t>
@@ -2696,7 +2696,7 @@
     <t xml:space="preserve">19.9354057312012</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7902450561523</t>
+    <t xml:space="preserve">19.7902431488037</t>
   </si>
   <si>
     <t xml:space="preserve">20.0321788787842</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">19.7418575286865</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5966968536377</t>
+    <t xml:space="preserve">19.5966949462891</t>
   </si>
   <si>
     <t xml:space="preserve">19.9837894439697</t>
@@ -2714,22 +2714,22 @@
     <t xml:space="preserve">19.8386306762695</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0805644989014</t>
+    <t xml:space="preserve">20.0805625915527</t>
   </si>
   <si>
     <t xml:space="preserve">20.370885848999</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8870162963867</t>
+    <t xml:space="preserve">19.8870143890381</t>
   </si>
   <si>
     <t xml:space="preserve">19.6450805664062</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1289520263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.177339553833</t>
+    <t xml:space="preserve">20.1289501190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1773376464844</t>
   </si>
   <si>
     <t xml:space="preserve">20.4192733764648</t>
@@ -2738,40 +2738,40 @@
     <t xml:space="preserve">20.467658996582</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2418518066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1934623718262</t>
+    <t xml:space="preserve">21.241849899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1934642791748</t>
   </si>
   <si>
     <t xml:space="preserve">21.435396194458</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5805587768555</t>
+    <t xml:space="preserve">21.5805568695068</t>
   </si>
   <si>
     <t xml:space="preserve">21.6773319244385</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6289443969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0644264221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2579746246338</t>
+    <t xml:space="preserve">21.6289463043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0644283294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2579765319824</t>
   </si>
   <si>
     <t xml:space="preserve">22.6450710296631</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0321655273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4676475524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3224868774414</t>
+    <t xml:space="preserve">23.0321636199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4676456451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.32248878479</t>
   </si>
   <si>
     <t xml:space="preserve">22.7902297973633</t>
@@ -2789,25 +2789,25 @@
     <t xml:space="preserve">22.1612014770508</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3063621520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8224906921387</t>
+    <t xml:space="preserve">22.306360244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8224925994873</t>
   </si>
   <si>
     <t xml:space="preserve">22.3547496795654</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1128158569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5482978820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9837799072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9031295776367</t>
+    <t xml:space="preserve">22.112813949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5482959747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9837779998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9031314849854</t>
   </si>
   <si>
     <t xml:space="preserve">24.1934509277344</t>
@@ -2819,13 +2819,13 @@
     <t xml:space="preserve">25.0160293579102</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9676399230957</t>
+    <t xml:space="preserve">24.9676418304443</t>
   </si>
   <si>
     <t xml:space="preserve">25.4031238555908</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8386058807373</t>
+    <t xml:space="preserve">25.8386077880859</t>
   </si>
   <si>
     <t xml:space="preserve">25.9353790283203</t>
@@ -2837,43 +2837,43 @@
     <t xml:space="preserve">25.161190032959</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8708667755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2579650878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4515113830566</t>
+    <t xml:space="preserve">24.8708686828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.257963180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.451509475708</t>
   </si>
   <si>
     <t xml:space="preserve">25.2095756530762</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5482845306396</t>
+    <t xml:space="preserve">25.548282623291</t>
   </si>
   <si>
     <t xml:space="preserve">25.6450595855713</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1773128509521</t>
+    <t xml:space="preserve">26.1773109436035</t>
   </si>
   <si>
     <t xml:space="preserve">26.5160217285156</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9515056610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6934452056885</t>
+    <t xml:space="preserve">26.9515037536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6934432983398</t>
   </si>
   <si>
     <t xml:space="preserve">25.5966720581055</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3063507080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8869934082031</t>
+    <t xml:space="preserve">25.3063488006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8869915008545</t>
   </si>
   <si>
     <t xml:space="preserve">26.3708610534668</t>
@@ -2885,7 +2885,7 @@
     <t xml:space="preserve">25.616569519043</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1267700195312</t>
+    <t xml:space="preserve">25.1267681121826</t>
   </si>
   <si>
     <t xml:space="preserve">25.9594306945801</t>
@@ -2897,16 +2897,16 @@
     <t xml:space="preserve">25.2737083435059</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0288066864014</t>
+    <t xml:space="preserve">25.02880859375</t>
   </si>
   <si>
     <t xml:space="preserve">25.2247295379639</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7349281311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4410495758057</t>
+    <t xml:space="preserve">24.7349300384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.441047668457</t>
   </si>
   <si>
     <t xml:space="preserve">24.8818683624268</t>
@@ -2921,10 +2921,10 @@
     <t xml:space="preserve">24.4900283813477</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7839088439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8328876495361</t>
+    <t xml:space="preserve">24.7839069366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8328895568848</t>
   </si>
   <si>
     <t xml:space="preserve">24.979829788208</t>
@@ -2933,19 +2933,19 @@
     <t xml:space="preserve">25.4696292877197</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9104499816895</t>
+    <t xml:space="preserve">25.9104518890381</t>
   </si>
   <si>
     <t xml:space="preserve">25.8614692687988</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7635097503662</t>
+    <t xml:space="preserve">25.7635078430176</t>
   </si>
   <si>
     <t xml:space="preserve">25.7145290374756</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2533092498779</t>
+    <t xml:space="preserve">26.2533111572266</t>
   </si>
   <si>
     <t xml:space="preserve">26.6941299438477</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">26.7920913696289</t>
   </si>
   <si>
-    <t xml:space="preserve">26.596170425415</t>
+    <t xml:space="preserve">26.5961685180664</t>
   </si>
   <si>
     <t xml:space="preserve">26.4492301940918</t>
@@ -2987,7 +2987,7 @@
     <t xml:space="preserve">25.3716678619385</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1471691131592</t>
+    <t xml:space="preserve">24.1471672058105</t>
   </si>
   <si>
     <t xml:space="preserve">26.3512687683105</t>
@@ -3002,13 +3002,13 @@
     <t xml:space="preserve">26.9880104064941</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9390316009521</t>
+    <t xml:space="preserve">26.9390296936035</t>
   </si>
   <si>
     <t xml:space="preserve">26.0573902130127</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1063709259033</t>
+    <t xml:space="preserve">26.1063690185547</t>
   </si>
   <si>
     <t xml:space="preserve">26.6451511383057</t>
@@ -3023,40 +3023,40 @@
     <t xml:space="preserve">27.134952545166</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1553497314453</t>
+    <t xml:space="preserve">26.1553516387939</t>
   </si>
   <si>
     <t xml:space="preserve">27.3798522949219</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3308696746826</t>
+    <t xml:space="preserve">27.3308715820312</t>
   </si>
   <si>
     <t xml:space="preserve">27.7227115631104</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6737308502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0165920257568</t>
+    <t xml:space="preserve">27.6737327575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0165939331055</t>
   </si>
   <si>
     <t xml:space="preserve">27.5757713317871</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4778099060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5267925262451</t>
+    <t xml:space="preserve">27.4778118133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5267906188965</t>
   </si>
   <si>
     <t xml:space="preserve">25.8124904632568</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3022918701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2818927764893</t>
+    <t xml:space="preserve">26.3022899627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2818908691406</t>
   </si>
   <si>
     <t xml:space="preserve">27.4288330078125</t>
@@ -3065,13 +3065,13 @@
     <t xml:space="preserve">27.23291015625</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6247539520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8410701751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4982089996338</t>
+    <t xml:space="preserve">27.6247520446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8410720825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4982109069824</t>
   </si>
   <si>
     <t xml:space="preserve">25.567590713501</t>
@@ -3098,7 +3098,7 @@
     <t xml:space="preserve">28.5553722381592</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0451736450195</t>
+    <t xml:space="preserve">29.0451717376709</t>
   </si>
   <si>
     <t xml:space="preserve">29.1431331634521</t>
@@ -3116,10 +3116,10 @@
     <t xml:space="preserve">29.6819133758545</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7798748016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1921119689941</t>
+    <t xml:space="preserve">29.7798728942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1921138763428</t>
   </si>
   <si>
     <t xml:space="preserve">29.5349731445312</t>
@@ -3131,10 +3131,10 @@
     <t xml:space="preserve">30.2206954956055</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5145740509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8574352264404</t>
+    <t xml:space="preserve">30.514575958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8574371337891</t>
   </si>
   <si>
     <t xml:space="preserve">32.1798973083496</t>
@@ -3149,10 +3149,10 @@
     <t xml:space="preserve">32.5227584838867</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0901184082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.824821472168</t>
+    <t xml:space="preserve">34.0901222229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8248176574707</t>
   </si>
   <si>
     <t xml:space="preserve">34.2860374450684</t>
@@ -3161,22 +3161,22 @@
     <t xml:space="preserve">34.6288986206055</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1390991210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7758407592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.747257232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8941955566406</t>
+    <t xml:space="preserve">34.1390953063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7758369445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7472610473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8941993713379</t>
   </si>
   <si>
     <t xml:space="preserve">34.335018157959</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9431838989258</t>
+    <t xml:space="preserve">33.9431800842285</t>
   </si>
   <si>
     <t xml:space="preserve">35.0207405090332</t>
@@ -3185,7 +3185,7 @@
     <t xml:space="preserve">35.4125823974609</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9635810852051</t>
+    <t xml:space="preserve">32.9635772705078</t>
   </si>
   <si>
     <t xml:space="preserve">32.9145965576172</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">33.0125579833984</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4451942443848</t>
+    <t xml:space="preserve">31.4451961517334</t>
   </si>
   <si>
     <t xml:space="preserve">31.5641193389893</t>
@@ -3846,6 +3846,9 @@
   </si>
   <si>
     <t xml:space="preserve">48.2000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.5</t>
   </si>
 </sst>
 </file>
@@ -69600,7 +69603,7 @@
     </row>
     <row r="2517">
       <c r="A2517" s="1" t="n">
-        <v>45982.69125</v>
+        <v>45982.3333333333</v>
       </c>
       <c r="B2517" t="n">
         <v>32114</v>
@@ -69621,6 +69624,32 @@
         <v>1234</v>
       </c>
       <c r="H2517" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2518">
+      <c r="A2518" s="1" t="n">
+        <v>45985.6911111111</v>
+      </c>
+      <c r="B2518" t="n">
+        <v>219751</v>
+      </c>
+      <c r="C2518" t="n">
+        <v>49.75</v>
+      </c>
+      <c r="D2518" t="n">
+        <v>48.2999992370605</v>
+      </c>
+      <c r="E2518" t="n">
+        <v>48.2999992370605</v>
+      </c>
+      <c r="F2518" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="G2518" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H2518" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SOL.MI.xlsx
+++ b/data/SOL.MI.xlsx
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14939117431641</t>
+    <t xml:space="preserve">7.14939165115356</t>
   </si>
   <si>
     <t xml:space="preserve">SOL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14067268371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18862581253052</t>
+    <t xml:space="preserve">7.14067220687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1886248588562</t>
   </si>
   <si>
     <t xml:space="preserve">7.16246938705444</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06220388412476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90962505340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90526628494263</t>
+    <t xml:space="preserve">7.06220436096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90962553024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90526533126831</t>
   </si>
   <si>
     <t xml:space="preserve">6.94886016845703</t>
@@ -74,40 +74,40 @@
     <t xml:space="preserve">6.71345281600952</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29931211471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3647027015686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43009376525879</t>
+    <t xml:space="preserve">6.2993106842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36470222473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43009233474731</t>
   </si>
   <si>
     <t xml:space="preserve">6.4126558303833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4475302696228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20776462554932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17288970947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46060752868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54779672622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38213968276978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51292085647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5042028427124</t>
+    <t xml:space="preserve">6.44753074645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20776414871216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17288875579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46060800552368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54779624938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38213920593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51292133331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50420236587524</t>
   </si>
   <si>
     <t xml:space="preserve">6.65242195129395</t>
@@ -119,115 +119,115 @@
     <t xml:space="preserve">6.72217130661011</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79192209243774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00989103317261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84423398971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07964134216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.883469581604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96629667282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08835935592651</t>
+    <t xml:space="preserve">6.7919225692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00989151000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84423446655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07964086532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88346815109253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96629762649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08836078643799</t>
   </si>
   <si>
     <t xml:space="preserve">6.7352499961853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83115577697754</t>
+    <t xml:space="preserve">6.83115673065186</t>
   </si>
   <si>
     <t xml:space="preserve">6.6785774230957</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57395172119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63062429428101</t>
+    <t xml:space="preserve">6.57395267486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63062477111816</t>
   </si>
   <si>
     <t xml:space="preserve">6.68729639053345</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78320360183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77884435653687</t>
+    <t xml:space="preserve">6.78320264816284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77884387969971</t>
   </si>
   <si>
     <t xml:space="preserve">6.81371879577637</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80935859680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79628133773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69601488113403</t>
+    <t xml:space="preserve">6.80935955047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79628086090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69601535797119</t>
   </si>
   <si>
     <t xml:space="preserve">6.81807804107666</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87474966049194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9139838218689</t>
+    <t xml:space="preserve">6.87475061416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91398429870605</t>
   </si>
   <si>
     <t xml:space="preserve">6.67421865463257</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5521559715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46496725082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43881225585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73089075088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87910985946655</t>
+    <t xml:space="preserve">6.55215549468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46496772766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43881177902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73089027404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87910938262939</t>
   </si>
   <si>
     <t xml:space="preserve">6.85295295715332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84859371185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85731220245361</t>
+    <t xml:space="preserve">6.84859418869019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85731315612793</t>
   </si>
   <si>
     <t xml:space="preserve">6.74832773208618</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51727962493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37342119216919</t>
+    <t xml:space="preserve">6.51728010177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37342071533203</t>
   </si>
   <si>
     <t xml:space="preserve">6.56523418426514</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66985988616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77012491226196</t>
+    <t xml:space="preserve">6.66985893249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7701244354248</t>
   </si>
   <si>
     <t xml:space="preserve">6.86167192459106</t>
@@ -239,43 +239,43 @@
     <t xml:space="preserve">6.94163036346436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95048332214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88407802581787</t>
+    <t xml:space="preserve">6.95048379898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88407754898071</t>
   </si>
   <si>
     <t xml:space="preserve">6.9017858505249</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34006547927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2249608039856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41975212097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43745946884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36662769317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26037788391113</t>
+    <t xml:space="preserve">7.34006500244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22496175765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41975164413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43746042251587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36662721633911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26037836074829</t>
   </si>
   <si>
     <t xml:space="preserve">7.46845006942749</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40204381942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44631433486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38433599472046</t>
+    <t xml:space="preserve">7.40204477310181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44631338119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3843355178833</t>
   </si>
   <si>
     <t xml:space="preserve">7.04345226287842</t>
@@ -284,112 +284,112 @@
     <t xml:space="preserve">6.9726185798645</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10985803604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87079668045044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20725393295288</t>
+    <t xml:space="preserve">7.10985708236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87079620361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20725297927856</t>
   </si>
   <si>
     <t xml:space="preserve">7.37105369567871</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57027196884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69423007965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70308446884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71193790435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65881299972534</t>
+    <t xml:space="preserve">7.57027244567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69422912597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70308399200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71193838119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6588134765625</t>
   </si>
   <si>
     <t xml:space="preserve">8.04396724700928</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61454200744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29579448699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99475431442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10100364685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55256414413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3135027885437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50829267501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4241795539856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37548160552979</t>
+    <t xml:space="preserve">7.61454391479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29579401016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99475479125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1010046005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55256509780884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31350374221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50829315185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42417907714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37548208236694</t>
   </si>
   <si>
     <t xml:space="preserve">7.52600193023682</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54370975494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41532516479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21610689163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99032783508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79996395111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75569343566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00803518295288</t>
+    <t xml:space="preserve">7.54370927810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41532421112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21610736846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99032735824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79996347427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7556939125061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00803565979004</t>
   </si>
   <si>
     <t xml:space="preserve">7.26923227310181</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34449195861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46402263641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51714706420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39319038391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45516872406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17183685302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33563804626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33121156692505</t>
+    <t xml:space="preserve">7.34449243545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46402311325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51714754104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39318990707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45516967773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1718373298645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33563899993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33121013641357</t>
   </si>
   <si>
     <t xml:space="preserve">7.39761590957642</t>
@@ -398,58 +398,58 @@
     <t xml:space="preserve">7.30464935302734</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27808666229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25152444839478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16298246383667</t>
+    <t xml:space="preserve">7.27808618545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25152397155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16298294067383</t>
   </si>
   <si>
     <t xml:space="preserve">7.03017091751099</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8796501159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91064071655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95491123199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88850450515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95933818817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85751485824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77340173721313</t>
+    <t xml:space="preserve">6.87965106964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91064023971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95491170883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88850545883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95933771133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85751533508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77340126037598</t>
   </si>
   <si>
     <t xml:space="preserve">6.74683904647827</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82652616500854</t>
+    <t xml:space="preserve">6.82652568817139</t>
   </si>
   <si>
     <t xml:space="preserve">6.68486022949219</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81767177581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90621328353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01689052581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8973593711853</t>
+    <t xml:space="preserve">6.81767129898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90621280670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01689004898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89735889434814</t>
   </si>
   <si>
     <t xml:space="preserve">6.83538007736206</t>
@@ -467,37 +467,37 @@
     <t xml:space="preserve">7.00360774993896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91506719589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91949510574341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93720293045044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07001495361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98590040206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75126647949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77782821655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64944410324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38382005691528</t>
+    <t xml:space="preserve">6.91506767272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91949415206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93720245361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07001447677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98589992523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75126552581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77782869338989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64944362640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38382053375244</t>
   </si>
   <si>
     <t xml:space="preserve">6.37053918838501</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36168527603149</t>
+    <t xml:space="preserve">6.36168479919434</t>
   </si>
   <si>
     <t xml:space="preserve">6.37939310073853</t>
@@ -506,13 +506,13 @@
     <t xml:space="preserve">6.40595579147339</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48121547698975</t>
+    <t xml:space="preserve">6.48121500015259</t>
   </si>
   <si>
     <t xml:space="preserve">6.47678852081299</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54319477081299</t>
+    <t xml:space="preserve">6.54319524765015</t>
   </si>
   <si>
     <t xml:space="preserve">6.46350765228271</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">6.24215412139893</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25986289978027</t>
+    <t xml:space="preserve">6.25986242294312</t>
   </si>
   <si>
     <t xml:space="preserve">6.22444629669189</t>
@@ -539,37 +539,37 @@
     <t xml:space="preserve">6.79111003875732</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70256853103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70699548721313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65829801559448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58303785324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05673360824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11428451538086</t>
+    <t xml:space="preserve">6.70256900787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70699453353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65829753875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58303737640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05673265457153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11428546905518</t>
   </si>
   <si>
     <t xml:space="preserve">7.34891891479492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18511819839478</t>
+    <t xml:space="preserve">7.18511772155762</t>
   </si>
   <si>
     <t xml:space="preserve">7.12756633758545</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19397258758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24266958236694</t>
+    <t xml:space="preserve">7.19397306442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2426700592041</t>
   </si>
   <si>
     <t xml:space="preserve">7.41089725494385</t>
@@ -584,10 +584,10 @@
     <t xml:space="preserve">7.27365922927856</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17626285552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04787969589233</t>
+    <t xml:space="preserve">7.17626333236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04787921905518</t>
   </si>
   <si>
     <t xml:space="preserve">7.23381519317627</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">7.29136657714844</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42860698699951</t>
+    <t xml:space="preserve">7.42860651016235</t>
   </si>
   <si>
     <t xml:space="preserve">7.83589601516724</t>
@@ -608,85 +608,85 @@
     <t xml:space="preserve">8.13693523406982</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27860260009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3228702545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03120040893555</t>
+    <t xml:space="preserve">8.27860164642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32287216186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0312032699585</t>
   </si>
   <si>
     <t xml:space="preserve">8.53094387054443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49995708465576</t>
+    <t xml:space="preserve">8.49995517730713</t>
   </si>
   <si>
     <t xml:space="preserve">8.26089382171631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92495155334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5884952545166</t>
+    <t xml:space="preserve">8.92495441436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58849620819092</t>
   </si>
   <si>
     <t xml:space="preserve">8.97807788848877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76557731628418</t>
+    <t xml:space="preserve">8.76557922363281</t>
   </si>
   <si>
     <t xml:space="preserve">8.87182807922363</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56244945526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25255393981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02234649658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8541202545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82755661010742</t>
+    <t xml:space="preserve">9.56245136260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25255298614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02234840393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85411834716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82755851745605</t>
   </si>
   <si>
     <t xml:space="preserve">8.71245384216309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98693180084229</t>
+    <t xml:space="preserve">8.98693084716797</t>
   </si>
   <si>
     <t xml:space="preserve">8.89838981628418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80984687805176</t>
+    <t xml:space="preserve">8.80984878540039</t>
   </si>
   <si>
     <t xml:space="preserve">8.7213077545166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78328609466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67703723907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75672435760498</t>
+    <t xml:space="preserve">8.78328704833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67703628540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7567253112793</t>
   </si>
   <si>
     <t xml:space="preserve">9.10203456878662</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82312870025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94266223907471</t>
+    <t xml:space="preserve">8.82313060760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94266033172607</t>
   </si>
   <si>
     <t xml:space="preserve">9.20828437805176</t>
@@ -695,31 +695,31 @@
     <t xml:space="preserve">9.43287658691406</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4598274230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52271461486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32507228851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38795852661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35202312469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42389392852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29812240600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55864906311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67543601989746</t>
+    <t xml:space="preserve">9.45982837677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52271366119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32507038116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38795757293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35202407836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42389297485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29812145233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55864810943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67543697357178</t>
   </si>
   <si>
     <t xml:space="preserve">9.86409378051758</t>
@@ -728,28 +728,28 @@
     <t xml:space="preserve">10.5199031829834</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0617341995239</t>
+    <t xml:space="preserve">10.0617361068726</t>
   </si>
   <si>
     <t xml:space="preserve">9.88206100463867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74730587005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56763172149658</t>
+    <t xml:space="preserve">9.74730682373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56763076782227</t>
   </si>
   <si>
     <t xml:space="preserve">9.44185924530029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54068279266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34303855895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36100769042969</t>
+    <t xml:space="preserve">9.54068088531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34304046630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36100673675537</t>
   </si>
   <si>
     <t xml:space="preserve">9.50474548339844</t>
@@ -758,13 +758,13 @@
     <t xml:space="preserve">9.48677921295166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61255168914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77425765991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46881198883057</t>
+    <t xml:space="preserve">9.61255073547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77425670623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46881103515625</t>
   </si>
   <si>
     <t xml:space="preserve">9.5496654510498</t>
@@ -773,13 +773,13 @@
     <t xml:space="preserve">9.4777946472168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7023868560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30710411071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28015422821045</t>
+    <t xml:space="preserve">9.70238876342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30710506439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28015518188477</t>
   </si>
   <si>
     <t xml:space="preserve">9.21726894378662</t>
@@ -788,49 +788,49 @@
     <t xml:space="preserve">9.16336631774902</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25320339202881</t>
+    <t xml:space="preserve">9.25320243835449</t>
   </si>
   <si>
     <t xml:space="preserve">9.45084476470947</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58559799194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33405590057373</t>
+    <t xml:space="preserve">9.58559989929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33405780792236</t>
   </si>
   <si>
     <t xml:space="preserve">9.59458255767822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66645240783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71137142181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40592479705811</t>
+    <t xml:space="preserve">9.66645336151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71137046813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40592670440674</t>
   </si>
   <si>
     <t xml:space="preserve">9.26218605041504</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27116870880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28913879394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36999130249023</t>
+    <t xml:space="preserve">9.27116966247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28913688659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36999034881592</t>
   </si>
   <si>
     <t xml:space="preserve">9.65746879577637</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79222297668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76527309417725</t>
+    <t xml:space="preserve">9.7922248840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76527404785156</t>
   </si>
   <si>
     <t xml:space="preserve">9.7203540802002</t>
@@ -839,37 +839,37 @@
     <t xml:space="preserve">9.8101921081543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37897396087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.909010887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81917476654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73832225799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78324222564697</t>
+    <t xml:space="preserve">9.37897300720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90901279449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81917667388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73832130432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78323936462402</t>
   </si>
   <si>
     <t xml:space="preserve">9.69340419769287</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11844730377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08251190185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31608867645264</t>
+    <t xml:space="preserve">9.11844635009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08251094818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31608772277832</t>
   </si>
   <si>
     <t xml:space="preserve">9.19031715393066</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10048007965088</t>
+    <t xml:space="preserve">9.1004810333252</t>
   </si>
   <si>
     <t xml:space="preserve">9.22625160217285</t>
@@ -878,49 +878,49 @@
     <t xml:space="preserve">9.41490840911865</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39694118499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07353019714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57661437988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68442058563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09149551391602</t>
+    <t xml:space="preserve">9.39694309234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07352924346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57661533355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68441963195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09149646759033</t>
   </si>
   <si>
     <t xml:space="preserve">9.05556106567383</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14539813995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89385318756104</t>
+    <t xml:space="preserve">9.14539909362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89385509490967</t>
   </si>
   <si>
     <t xml:space="preserve">9.10946369171143</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23523426055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95393180847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5109205245972</t>
+    <t xml:space="preserve">9.2352352142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95393085479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5109195709229</t>
   </si>
   <si>
     <t xml:space="preserve">10.74449634552</t>
   </si>
   <si>
-    <t xml:space="preserve">10.546854019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6905937194824</t>
+    <t xml:space="preserve">10.5468530654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6905927658081</t>
   </si>
   <si>
     <t xml:space="preserve">10.9062032699585</t>
@@ -929,70 +929,70 @@
     <t xml:space="preserve">10.7804298400879</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7085609436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6546592712402</t>
+    <t xml:space="preserve">10.7085599899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6546583175659</t>
   </si>
   <si>
     <t xml:space="preserve">10.5288867950439</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4390506744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3312454223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1695384979248</t>
+    <t xml:space="preserve">10.4390487670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3312473297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1695394515991</t>
   </si>
   <si>
     <t xml:space="preserve">10.1875066757202</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1336040496826</t>
+    <t xml:space="preserve">10.1336030960083</t>
   </si>
   <si>
     <t xml:space="preserve">9.7562894821167</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63051891326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0078344345093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84612464904785</t>
+    <t xml:space="preserve">9.63051795959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0078325271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84612560272217</t>
   </si>
   <si>
     <t xml:space="preserve">10.0976705551147</t>
   </si>
   <si>
-    <t xml:space="preserve">10.205472946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2773427963257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2234420776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2414083480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7624616622925</t>
+    <t xml:space="preserve">10.2054738998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.27734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2234411239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2414073944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7624626159668</t>
   </si>
   <si>
     <t xml:space="preserve">10.2593765258789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91799449920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90002918243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67380714416504</t>
+    <t xml:space="preserve">9.91799545288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90002822875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67380619049072</t>
   </si>
   <si>
     <t xml:space="preserve">9.74667930603027</t>
@@ -1001,7 +1001,7 @@
     <t xml:space="preserve">9.87420558929443</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1656951904297</t>
+    <t xml:space="preserve">10.1656942367554</t>
   </si>
   <si>
     <t xml:space="preserve">9.85598754882812</t>
@@ -1010,46 +1010,46 @@
     <t xml:space="preserve">9.63736915588379</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47340679168701</t>
+    <t xml:space="preserve">9.47340774536133</t>
   </si>
   <si>
     <t xml:space="preserve">9.7648983001709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96529483795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0746040344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2385673522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3843097686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4207487106323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8033285140991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6940202713013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6211462020874</t>
+    <t xml:space="preserve">9.96529674530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0746059417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2385663986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3843116760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4207468032837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8033266067505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6940212249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6211471557617</t>
   </si>
   <si>
     <t xml:space="preserve">10.7851095199585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5482759475708</t>
+    <t xml:space="preserve">10.5482749938965</t>
   </si>
   <si>
     <t xml:space="preserve">10.4025297164917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2203493118286</t>
+    <t xml:space="preserve">10.2203502655029</t>
   </si>
   <si>
     <t xml:space="preserve">10.1474781036377</t>
@@ -1058,7 +1058,7 @@
     <t xml:space="preserve">10.3296585083008</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5847110748291</t>
+    <t xml:space="preserve">10.5847101211548</t>
   </si>
   <si>
     <t xml:space="preserve">10.3478755950928</t>
@@ -1067,16 +1067,16 @@
     <t xml:space="preserve">9.72846126556396</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56449890136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4187536239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40053462982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54627990722656</t>
+    <t xml:space="preserve">9.56449794769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41875267028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40053558349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54628086090088</t>
   </si>
   <si>
     <t xml:space="preserve">10.1110420227051</t>
@@ -1085,67 +1085,67 @@
     <t xml:space="preserve">10.2567853927612</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92885971069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0199499130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2021312713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0928239822388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8013334274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69202423095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8377685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94707870483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89242267608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65558910369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78311538696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91064167022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45518779754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2001371383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50984382629395</t>
+    <t xml:space="preserve">9.92886066436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0199489593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.202130317688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0928220748901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80133247375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69202613830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83776950836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94707775115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89242362976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65558815002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78311443328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91064262390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4551887512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20013618469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50984287261963</t>
   </si>
   <si>
     <t xml:space="preserve">9.43697071075439</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81955146789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49162673950195</t>
+    <t xml:space="preserve">9.81955051422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49162483215332</t>
   </si>
   <si>
     <t xml:space="preserve">9.61915302276611</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9835147857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6009349822998</t>
+    <t xml:space="preserve">9.98351383209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60093402862549</t>
   </si>
   <si>
     <t xml:space="preserve">9.10904598236084</t>
@@ -1154,37 +1154,37 @@
     <t xml:space="preserve">9.09993553161621</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3823184967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36409759521484</t>
+    <t xml:space="preserve">9.38231754302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36409854888916</t>
   </si>
   <si>
     <t xml:space="preserve">9.27300834655762</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71024322509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5827169418335</t>
+    <t xml:space="preserve">9.71024131774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58271598815918</t>
   </si>
   <si>
     <t xml:space="preserve">9.29122638702393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14548206329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3660955429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32766437530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0017318725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4754028320312</t>
+    <t xml:space="preserve">9.14548110961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3660945892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32766246795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0017328262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4754037857056</t>
   </si>
   <si>
     <t xml:space="preserve">10.8397636413574</t>
@@ -1193,25 +1193,25 @@
     <t xml:space="preserve">10.5664930343628</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3114385604858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2932214736938</t>
+    <t xml:space="preserve">10.3114395141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2932233810425</t>
   </si>
   <si>
     <t xml:space="preserve">10.0381689071655</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0563859939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1292581558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2750034332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1839141845703</t>
+    <t xml:space="preserve">10.0563850402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1292591094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2750024795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.183913230896</t>
   </si>
   <si>
     <t xml:space="preserve">10.675802230835</t>
@@ -1220,13 +1220,13 @@
     <t xml:space="preserve">10.7122373580933</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9308547973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0219459533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8762006759644</t>
+    <t xml:space="preserve">10.9308557510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0219440460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.87619972229</t>
   </si>
   <si>
     <t xml:space="preserve">10.894419670105</t>
@@ -1235,13 +1235,13 @@
     <t xml:space="preserve">10.7304553985596</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6575841903687</t>
+    <t xml:space="preserve">10.65758228302</t>
   </si>
   <si>
     <t xml:space="preserve">11.2644634246826</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1349878311157</t>
+    <t xml:space="preserve">11.1349868774414</t>
   </si>
   <si>
     <t xml:space="preserve">11.0979928970337</t>
@@ -1250,16 +1250,16 @@
     <t xml:space="preserve">11.2459669113159</t>
   </si>
   <si>
-    <t xml:space="preserve">11.319953918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0240068435669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8205442428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8390407562256</t>
+    <t xml:space="preserve">11.3199529647827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0240077972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8205423355103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8390417098999</t>
   </si>
   <si>
     <t xml:space="preserve">10.7280607223511</t>
@@ -1268,22 +1268,22 @@
     <t xml:space="preserve">10.8575372695923</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7095642089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6725702285767</t>
+    <t xml:space="preserve">10.7095632553101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.672571182251</t>
   </si>
   <si>
     <t xml:space="preserve">10.65407371521</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7835493087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7650547027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8020477294922</t>
+    <t xml:space="preserve">10.7835502624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7650537490845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8020467758179</t>
   </si>
   <si>
     <t xml:space="preserve">10.5615901947021</t>
@@ -1295,79 +1295,79 @@
     <t xml:space="preserve">10.3951206207275</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1176691055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2841396331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2656450271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.302638053894</t>
+    <t xml:space="preserve">10.1176710128784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2841415405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2656440734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3026371002197</t>
   </si>
   <si>
     <t xml:space="preserve">10.5060997009277</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3396320343018</t>
+    <t xml:space="preserve">10.3396310806274</t>
   </si>
   <si>
     <t xml:space="preserve">10.1361675262451</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0806770324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98819351196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0991744995117</t>
+    <t xml:space="preserve">10.080677986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98819446563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0991735458374</t>
   </si>
   <si>
     <t xml:space="preserve">9.93270397186279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89571094512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96969795227051</t>
+    <t xml:space="preserve">9.89571189880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96969699859619</t>
   </si>
   <si>
     <t xml:space="preserve">10.1731605529785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.062180519104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1546640396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71074485778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0251874923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91420841217041</t>
+    <t xml:space="preserve">10.0621814727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1546630859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71074390411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0251865386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91420745849609</t>
   </si>
   <si>
     <t xml:space="preserve">9.7662353515625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72924137115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65525436401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67374992370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47028923034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54427337646484</t>
+    <t xml:space="preserve">9.7292423248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65525341033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67375087738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47028636932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54427433013916</t>
   </si>
   <si>
     <t xml:space="preserve">9.56277084350586</t>
@@ -1379,28 +1379,28 @@
     <t xml:space="preserve">9.35930728912354</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52577877044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59976291656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61826038360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69224739074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8032283782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2286500930786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78472995758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.858717918396</t>
+    <t xml:space="preserve">9.52577781677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59976482391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61826133728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69224834442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80322742462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2286510467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78473091125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85871601104736</t>
   </si>
   <si>
     <t xml:space="preserve">10.0066909790039</t>
@@ -1424,16 +1424,16 @@
     <t xml:space="preserve">10.3766241073608</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2471485137939</t>
+    <t xml:space="preserve">10.247145652771</t>
   </si>
   <si>
     <t xml:space="preserve">10.2101535797119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84022045135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63675880432129</t>
+    <t xml:space="preserve">9.8402214050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63675689697266</t>
   </si>
   <si>
     <t xml:space="preserve">9.43329429626465</t>
@@ -1442,22 +1442,22 @@
     <t xml:space="preserve">9.41479778289795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39630222320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24832820892334</t>
+    <t xml:space="preserve">9.39630031585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24832725524902</t>
   </si>
   <si>
     <t xml:space="preserve">9.06336116790771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10960388183594</t>
+    <t xml:space="preserve">9.10960292816162</t>
   </si>
   <si>
     <t xml:space="preserve">9.32231426239014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28532123565674</t>
+    <t xml:space="preserve">9.28532028198242</t>
   </si>
   <si>
     <t xml:space="preserve">9.26682472229004</t>
@@ -1469,13 +1469,13 @@
     <t xml:space="preserve">9.22982978820801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48878479003906</t>
+    <t xml:space="preserve">9.48878574371338</t>
   </si>
   <si>
     <t xml:space="preserve">9.02636814117432</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97087860107422</t>
+    <t xml:space="preserve">8.9708776473999</t>
   </si>
   <si>
     <t xml:space="preserve">9.13734912872314</t>
@@ -1493,94 +1493,94 @@
     <t xml:space="preserve">8.55470371246338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36048698425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33274269104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0182991027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81483697891235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95356273651123</t>
+    <t xml:space="preserve">8.36048889160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33274364471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01830101013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8148365020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95356321334839</t>
   </si>
   <si>
     <t xml:space="preserve">7.49114608764648</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8610782623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50964164733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53738641738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58362913131714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76741504669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98937511444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16509246826172</t>
+    <t xml:space="preserve">7.86107921600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50964212417603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53738689422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58362865447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76741409301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98937606811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16509342193604</t>
   </si>
   <si>
     <t xml:space="preserve">9.12810039520264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09110641479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08185768127441</t>
+    <t xml:space="preserve">9.09110546112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0818567276001</t>
   </si>
   <si>
     <t xml:space="preserve">9.34081172943115</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0448637008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21133518218994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38705158233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17434024810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29456901550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1188497543335</t>
+    <t xml:space="preserve">9.04486465454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21133422851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38705253601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17434120178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29456996917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11885070800781</t>
   </si>
   <si>
     <t xml:space="preserve">8.78591156005859</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89689159393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74891757965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80440711975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87839412689209</t>
+    <t xml:space="preserve">8.89689064025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74891948699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80440902709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87839508056641</t>
   </si>
   <si>
     <t xml:space="preserve">8.9338846206665</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63793659210205</t>
+    <t xml:space="preserve">8.63793849945068</t>
   </si>
   <si>
     <t xml:space="preserve">8.71192455291748</t>
@@ -1592,49 +1592,49 @@
     <t xml:space="preserve">8.69342708587646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46113872528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6494197845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69649028778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74356174468994</t>
+    <t xml:space="preserve">9.46113967895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64942073822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69649124145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74356079101562</t>
   </si>
   <si>
     <t xml:space="preserve">9.97891330718994</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93184185028076</t>
+    <t xml:space="preserve">9.93184280395508</t>
   </si>
   <si>
     <t xml:space="preserve">9.79063129425049</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0730533599854</t>
+    <t xml:space="preserve">10.0730543136597</t>
   </si>
   <si>
     <t xml:space="preserve">10.3084058761597</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4496173858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1671943664551</t>
+    <t xml:space="preserve">10.4496154785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1671962738037</t>
   </si>
   <si>
     <t xml:space="preserve">10.1201238632202</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0259828567505</t>
+    <t xml:space="preserve">10.0259838104248</t>
   </si>
   <si>
     <t xml:space="preserve">10.2142648696899</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3554754257202</t>
+    <t xml:space="preserve">10.3554744720459</t>
   </si>
   <si>
     <t xml:space="preserve">10.2613344192505</t>
@@ -1643,28 +1643,28 @@
     <t xml:space="preserve">9.88477230072021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5908279418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4966859817505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5437574386597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2027406692505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1556720733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9673891067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0615301132202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7791090011597</t>
+    <t xml:space="preserve">10.5908269882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4966869354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5437564849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2027416229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1556711196899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9673900604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0615310668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7791080474854</t>
   </si>
   <si>
     <t xml:space="preserve">10.8261785507202</t>
@@ -1673,10 +1673,10 @@
     <t xml:space="preserve">11.0144605636597</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1086006164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9203195571899</t>
+    <t xml:space="preserve">11.1086025238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9203205108643</t>
   </si>
   <si>
     <t xml:space="preserve">10.8732490539551</t>
@@ -1685,10 +1685,10 @@
     <t xml:space="preserve">10.7320375442505</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6378974914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5322332382202</t>
+    <t xml:space="preserve">10.6378984451294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5322351455688</t>
   </si>
   <si>
     <t xml:space="preserve">11.6263742446899</t>
@@ -1706,34 +1706,34 @@
     <t xml:space="preserve">11.6734447479248</t>
   </si>
   <si>
-    <t xml:space="preserve">11.720516204834</t>
+    <t xml:space="preserve">11.7205152511597</t>
   </si>
   <si>
     <t xml:space="preserve">12.0029382705688</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2853593826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5677824020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5207109451294</t>
+    <t xml:space="preserve">12.2853603363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5677814483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5207118988037</t>
   </si>
   <si>
     <t xml:space="preserve">12.897274017334</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7560625076294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.661922454834</t>
+    <t xml:space="preserve">12.7560634613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6619215011597</t>
   </si>
   <si>
     <t xml:space="preserve">12.6148509979248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8031339645386</t>
+    <t xml:space="preserve">12.8031330108643</t>
   </si>
   <si>
     <t xml:space="preserve">12.8502035140991</t>
@@ -1742,37 +1742,37 @@
     <t xml:space="preserve">12.9914150238037</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1796960830688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4621181488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8386812210083</t>
+    <t xml:space="preserve">13.1796970367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.462119102478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.838680267334</t>
   </si>
   <si>
     <t xml:space="preserve">13.7445402145386</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6504001617432</t>
+    <t xml:space="preserve">13.6503992080688</t>
   </si>
   <si>
     <t xml:space="preserve">13.5091896057129</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7916097640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8857507705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9798927307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0269603729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0740327835083</t>
+    <t xml:space="preserve">13.7916107177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8857517242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9798917770386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0269613265991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.074031829834</t>
   </si>
   <si>
     <t xml:space="preserve">14.1681728363037</t>
@@ -1784,7 +1784,7 @@
     <t xml:space="preserve">14.2623138427734</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2152442932129</t>
+    <t xml:space="preserve">14.2152452468872</t>
   </si>
   <si>
     <t xml:space="preserve">14.4505958557129</t>
@@ -1793,10 +1793,10 @@
     <t xml:space="preserve">14.6859483718872</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3093843460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.403525352478</t>
+    <t xml:space="preserve">14.3093852996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4035263061523</t>
   </si>
   <si>
     <t xml:space="preserve">14.3564548492432</t>
@@ -1811,10 +1811,10 @@
     <t xml:space="preserve">14.638876914978</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7800884246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8271579742432</t>
+    <t xml:space="preserve">14.7800874710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8271589279175</t>
   </si>
   <si>
     <t xml:space="preserve">14.874228477478</t>
@@ -1823,19 +1823,19 @@
     <t xml:space="preserve">14.7330169677734</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3449306488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7685642242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0039157867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0415744781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.079231262207</t>
+    <t xml:space="preserve">15.344931602478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7685661315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0039176940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0415725708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0792293548584</t>
   </si>
   <si>
     <t xml:space="preserve">16.1921997070312</t>
@@ -1847,22 +1847,22 @@
     <t xml:space="preserve">16.2298545837402</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3804798126221</t>
+    <t xml:space="preserve">16.3804779052734</t>
   </si>
   <si>
     <t xml:space="preserve">16.3993072509766</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4181385040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5311031341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2675132751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9286060333252</t>
+    <t xml:space="preserve">16.4181346893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5311050415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2675113677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9286041259766</t>
   </si>
   <si>
     <t xml:space="preserve">15.8909473419189</t>
@@ -1871,28 +1871,28 @@
     <t xml:space="preserve">15.815634727478</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9662599563599</t>
+    <t xml:space="preserve">15.9662590026855</t>
   </si>
   <si>
     <t xml:space="preserve">15.7214956283569</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5332136154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.514386177063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7026672363281</t>
+    <t xml:space="preserve">15.5332145690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5143842697144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7026681900024</t>
   </si>
   <si>
     <t xml:space="preserve">15.2696199417114</t>
   </si>
   <si>
-    <t xml:space="preserve">15.476731300354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6838397979736</t>
+    <t xml:space="preserve">15.4767284393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.683837890625</t>
   </si>
   <si>
     <t xml:space="preserve">15.6650085449219</t>
@@ -1901,31 +1901,31 @@
     <t xml:space="preserve">15.4202442169189</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1566505432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2319641113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7779779434204</t>
+    <t xml:space="preserve">15.1566514968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2319631576538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7779788970947</t>
   </si>
   <si>
     <t xml:space="preserve">15.9833717346191</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9642992019653</t>
+    <t xml:space="preserve">15.964301109314</t>
   </si>
   <si>
     <t xml:space="preserve">15.6209812164307</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4874687194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7926378250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.811713218689</t>
+    <t xml:space="preserve">15.4874696731567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7926406860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8117151260376</t>
   </si>
   <si>
     <t xml:space="preserve">15.6019096374512</t>
@@ -1934,13 +1934,13 @@
     <t xml:space="preserve">15.5446872711182</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2585897445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6972732543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8307857513428</t>
+    <t xml:space="preserve">15.2585887908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6972742080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8307876586914</t>
   </si>
   <si>
     <t xml:space="preserve">16.2503986358643</t>
@@ -1949,22 +1949,22 @@
     <t xml:space="preserve">16.2313251495361</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0024452209473</t>
+    <t xml:space="preserve">16.0024471282959</t>
   </si>
   <si>
     <t xml:space="preserve">16.2694702148438</t>
   </si>
   <si>
-    <t xml:space="preserve">16.212251663208</t>
+    <t xml:space="preserve">16.2122535705566</t>
   </si>
   <si>
     <t xml:space="preserve">16.460205078125</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4411296844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5364952087402</t>
+    <t xml:space="preserve">16.4411315917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5364971160889</t>
   </si>
   <si>
     <t xml:space="preserve">16.555570602417</t>
@@ -1973,25 +1973,25 @@
     <t xml:space="preserve">17.1659145355225</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9561100006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2231330871582</t>
+    <t xml:space="preserve">16.9561080932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2231349945068</t>
   </si>
   <si>
     <t xml:space="preserve">17.3185005187988</t>
   </si>
   <si>
-    <t xml:space="preserve">17.08962059021</t>
+    <t xml:space="preserve">17.0896224975586</t>
   </si>
   <si>
     <t xml:space="preserve">16.8416690826416</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7462997436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9751796722412</t>
+    <t xml:space="preserve">16.746301651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9751815795898</t>
   </si>
   <si>
     <t xml:space="preserve">17.1277656555176</t>
@@ -2003,7 +2003,7 @@
     <t xml:space="preserve">17.5473785400391</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7571868896484</t>
+    <t xml:space="preserve">17.7571830749512</t>
   </si>
   <si>
     <t xml:space="preserve">17.6427440643311</t>
@@ -2012,13 +2012,13 @@
     <t xml:space="preserve">17.7381114959717</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4901580810547</t>
+    <t xml:space="preserve">17.4901599884033</t>
   </si>
   <si>
     <t xml:space="preserve">17.4710865020752</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3375720977783</t>
+    <t xml:space="preserve">17.337574005127</t>
   </si>
   <si>
     <t xml:space="preserve">17.2994251251221</t>
@@ -2027,19 +2027,19 @@
     <t xml:space="preserve">17.3566474914551</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2422046661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1468410491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0133285522461</t>
+    <t xml:space="preserve">17.2422065734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1468391418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0133266448975</t>
   </si>
   <si>
     <t xml:space="preserve">17.4520111083984</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8334789276123</t>
+    <t xml:space="preserve">17.8334770202637</t>
   </si>
   <si>
     <t xml:space="preserve">17.6999645233154</t>
@@ -2048,13 +2048,13 @@
     <t xml:space="preserve">17.8716239929199</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8525485992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0242099761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.424747467041</t>
+    <t xml:space="preserve">17.8525505065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0242080688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4247455596924</t>
   </si>
   <si>
     <t xml:space="preserve">18.5010414123535</t>
@@ -2069,7 +2069,7 @@
     <t xml:space="preserve">18.5582580566406</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7108459472656</t>
+    <t xml:space="preserve">18.7108478546143</t>
   </si>
   <si>
     <t xml:space="preserve">18.8062114715576</t>
@@ -2087,7 +2087,7 @@
     <t xml:space="preserve">19.8838500976562</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9792156219482</t>
+    <t xml:space="preserve">19.9792175292969</t>
   </si>
   <si>
     <t xml:space="preserve">19.4547023773193</t>
@@ -2102,19 +2102,19 @@
     <t xml:space="preserve">18.7871398925781</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6917724609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2162857055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1209201812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.76806640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9097709655762</t>
+    <t xml:space="preserve">18.6917743682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2162837982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1209182739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7680644989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9097690582275</t>
   </si>
   <si>
     <t xml:space="preserve">18.1195755004883</t>
@@ -2123,10 +2123,10 @@
     <t xml:space="preserve">17.6236705780029</t>
   </si>
   <si>
-    <t xml:space="preserve">17.890697479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1005039215088</t>
+    <t xml:space="preserve">17.8906955718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1005020141602</t>
   </si>
   <si>
     <t xml:space="preserve">18.2530879974365</t>
@@ -2135,28 +2135,28 @@
     <t xml:space="preserve">17.9669895172119</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1767921447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9969444274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0732383728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9778709411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8825035095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9397277832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9015789031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0268993377686</t>
+    <t xml:space="preserve">18.176794052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9969463348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0732364654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9778728485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8825054168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9397258758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9015769958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0268974304199</t>
   </si>
   <si>
     <t xml:space="preserve">20.2176322937012</t>
@@ -2168,7 +2168,7 @@
     <t xml:space="preserve">20.7421455383301</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9328765869141</t>
+    <t xml:space="preserve">20.9328804016113</t>
   </si>
   <si>
     <t xml:space="preserve">21.2189769744873</t>
@@ -2177,58 +2177,58 @@
     <t xml:space="preserve">21.4573917388916</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6944637298584</t>
+    <t xml:space="preserve">20.6944618225098</t>
   </si>
   <si>
     <t xml:space="preserve">20.3129978179932</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4560470581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.980562210083</t>
+    <t xml:space="preserve">20.4560508728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9805603027344</t>
   </si>
   <si>
     <t xml:space="preserve">19.8361663818359</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4083652496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1222629547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3116512298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2639713287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5977516174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6454334259033</t>
+    <t xml:space="preserve">20.4083633422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1222667694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.311653137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2639694213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.597749710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.645435333252</t>
   </si>
   <si>
     <t xml:space="preserve">20.1699485778809</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9315338134766</t>
+    <t xml:space="preserve">19.9315319061279</t>
   </si>
   <si>
     <t xml:space="preserve">19.7408027648926</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8443584442139</t>
+    <t xml:space="preserve">18.8443603515625</t>
   </si>
   <si>
     <t xml:space="preserve">19.016019821167</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0432815551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0051364898682</t>
+    <t xml:space="preserve">18.0432834625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0051345825195</t>
   </si>
   <si>
     <t xml:space="preserve">18.1386489868164</t>
@@ -2237,37 +2237,37 @@
     <t xml:space="preserve">18.0623569488525</t>
   </si>
   <si>
-    <t xml:space="preserve">18.081428527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6045970916748</t>
+    <t xml:space="preserve">18.0814266204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6045989990234</t>
   </si>
   <si>
     <t xml:space="preserve">17.2612800598145</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0514717102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2885456085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0324039459229</t>
+    <t xml:space="preserve">17.0514736175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2885437011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0324020385742</t>
   </si>
   <si>
     <t xml:space="preserve">16.7272300720215</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4792785644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8225955963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0705471038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.650936126709</t>
+    <t xml:space="preserve">16.4792766571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8225936889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0705490112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6509342193604</t>
   </si>
   <si>
     <t xml:space="preserve">16.8607425689697</t>
@@ -2279,16 +2279,16 @@
     <t xml:space="preserve">16.5937175750732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6318664550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2776641845703</t>
+    <t xml:space="preserve">16.6318626403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.277663230896</t>
   </si>
   <si>
     <t xml:space="preserve">14.8771257400513</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4956607818604</t>
+    <t xml:space="preserve">14.495659828186</t>
   </si>
   <si>
     <t xml:space="preserve">15.3730306625366</t>
@@ -2297,16 +2297,16 @@
     <t xml:space="preserve">14.9915647506714</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0869312286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6782026290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1441497802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9452266693115</t>
+    <t xml:space="preserve">15.0869302749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.678201675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1441507339478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9452276229858</t>
   </si>
   <si>
     <t xml:space="preserve">16.0787410736084</t>
@@ -2318,61 +2318,61 @@
     <t xml:space="preserve">16.5746421813965</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6890811920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5174236297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4983501434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7354211807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8880081176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5065422058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9724912643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3348836898804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2204437255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9152727127075</t>
+    <t xml:space="preserve">16.6890830993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5174217224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.498348236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7354202270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8880062103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5065412521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9724922180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3348827362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2204427719116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9152717590332</t>
   </si>
   <si>
     <t xml:space="preserve">14.781759262085</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8961982727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6400556564331</t>
+    <t xml:space="preserve">14.8961992263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6400547027588</t>
   </si>
   <si>
     <t xml:space="preserve">16.0978126525879</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2395153045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1060037612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0063896179199</t>
+    <t xml:space="preserve">15.2395162582397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1060047149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0063877105713</t>
   </si>
   <si>
     <t xml:space="preserve">16.1999359130859</t>
   </si>
   <si>
-    <t xml:space="preserve">16.354772567749</t>
+    <t xml:space="preserve">16.3547744750977</t>
   </si>
   <si>
     <t xml:space="preserve">16.0450973510742</t>
@@ -2381,10 +2381,10 @@
     <t xml:space="preserve">16.1418704986572</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2773551940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4709014892578</t>
+    <t xml:space="preserve">16.2773532867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4709033966064</t>
   </si>
   <si>
     <t xml:space="preserve">16.7805767059326</t>
@@ -2396,43 +2396,43 @@
     <t xml:space="preserve">17.767671585083</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4192848205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2321834564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7289619445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9418640136719</t>
+    <t xml:space="preserve">17.419282913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2321853637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7289600372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9418659210205</t>
   </si>
   <si>
     <t xml:space="preserve">17.4967041015625</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5934772491455</t>
+    <t xml:space="preserve">17.5934791564941</t>
   </si>
   <si>
     <t xml:space="preserve">17.4579963684082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8967056274414</t>
+    <t xml:space="preserve">16.8967037200928</t>
   </si>
   <si>
     <t xml:space="preserve">16.4515476226807</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9870328903198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8321943283081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9483213424683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3676795959473</t>
+    <t xml:space="preserve">15.9870338439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8321962356567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9483232498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3676805496216</t>
   </si>
   <si>
     <t xml:space="preserve">15.4450988769531</t>
@@ -2444,19 +2444,19 @@
     <t xml:space="preserve">15.1160688400269</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1354236602783</t>
+    <t xml:space="preserve">15.135422706604</t>
   </si>
   <si>
     <t xml:space="preserve">15.3289709091187</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6192922592163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8902587890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7547760009766</t>
+    <t xml:space="preserve">15.619291305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8902597427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7547750473022</t>
   </si>
   <si>
     <t xml:space="preserve">15.8128395080566</t>
@@ -2468,13 +2468,13 @@
     <t xml:space="preserve">15.6580018997192</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8709049224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4128379821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4321918487549</t>
+    <t xml:space="preserve">15.870903968811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4128360748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4321899414062</t>
   </si>
   <si>
     <t xml:space="preserve">15.7160663604736</t>
@@ -2483,13 +2483,13 @@
     <t xml:space="preserve">16.0644512176514</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5289649963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6838035583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5096092224121</t>
+    <t xml:space="preserve">16.5289669036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6838054656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5096111297607</t>
   </si>
   <si>
     <t xml:space="preserve">16.9160594940186</t>
@@ -2501,7 +2501,7 @@
     <t xml:space="preserve">17.3805732727051</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3418655395508</t>
+    <t xml:space="preserve">17.3418674468994</t>
   </si>
   <si>
     <t xml:space="preserve">17.2063827514648</t>
@@ -2510,31 +2510,31 @@
     <t xml:space="preserve">17.3225116729736</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2838039398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0515460968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.83864402771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2450923919678</t>
+    <t xml:space="preserve">17.2838020324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0515441894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8386421203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2450904846191</t>
   </si>
   <si>
     <t xml:space="preserve">17.6128330230713</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8192863464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1096076965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7225151062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1289653778076</t>
+    <t xml:space="preserve">16.8192882537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1096096038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7225131988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.128963470459</t>
   </si>
   <si>
     <t xml:space="preserve">16.8773517608643</t>
@@ -2576,13 +2576,13 @@
     <t xml:space="preserve">15.7741289138794</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6773557662964</t>
+    <t xml:space="preserve">15.677357673645</t>
   </si>
   <si>
     <t xml:space="preserve">15.5612277984619</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1805801391602</t>
+    <t xml:space="preserve">16.1805782318115</t>
   </si>
   <si>
     <t xml:space="preserve">16.8579978942871</t>
@@ -2591,22 +2591,22 @@
     <t xml:space="preserve">17.3031558990479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9031543731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8063793182373</t>
+    <t xml:space="preserve">17.9031524658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8063812255859</t>
   </si>
   <si>
     <t xml:space="preserve">17.1676731109619</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5160579681396</t>
+    <t xml:space="preserve">17.5160598754883</t>
   </si>
   <si>
     <t xml:space="preserve">17.3612194061279</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7354106903076</t>
+    <t xml:space="preserve">18.735408782959</t>
   </si>
   <si>
     <t xml:space="preserve">18.6579895019531</t>
@@ -2636,25 +2636,25 @@
     <t xml:space="preserve">18.2128295898438</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2902507781982</t>
+    <t xml:space="preserve">18.2902488708496</t>
   </si>
   <si>
     <t xml:space="preserve">18.1547660827637</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0192832946777</t>
+    <t xml:space="preserve">18.0192813873291</t>
   </si>
   <si>
     <t xml:space="preserve">17.9805736541748</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9612159729004</t>
+    <t xml:space="preserve">17.961217880249</t>
   </si>
   <si>
     <t xml:space="preserve">17.8450908660889</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6902542114258</t>
+    <t xml:space="preserve">17.6902523040771</t>
   </si>
   <si>
     <t xml:space="preserve">17.6321868896484</t>
@@ -2666,10 +2666,10 @@
     <t xml:space="preserve">17.4386405944824</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3999271392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2644481658936</t>
+    <t xml:space="preserve">17.3999290466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2644462585449</t>
   </si>
   <si>
     <t xml:space="preserve">17.7096061706543</t>
@@ -2678,46 +2678,46 @@
     <t xml:space="preserve">17.4773483276367</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8257331848145</t>
+    <t xml:space="preserve">17.8257369995117</t>
   </si>
   <si>
     <t xml:space="preserve">18.5805721282959</t>
   </si>
   <si>
-    <t xml:space="preserve">18.928955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8128261566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5483112335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9354038238525</t>
+    <t xml:space="preserve">18.9289569854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8128299713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5483093261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9354057312012</t>
   </si>
   <si>
     <t xml:space="preserve">19.7902450561523</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0321788787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7418575286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5966949462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9837913513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8386306762695</t>
+    <t xml:space="preserve">20.0321769714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7418556213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5966968536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9837894439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8386287689209</t>
   </si>
   <si>
     <t xml:space="preserve">20.0805644989014</t>
   </si>
   <si>
-    <t xml:space="preserve">20.370885848999</t>
+    <t xml:space="preserve">20.3708839416504</t>
   </si>
   <si>
     <t xml:space="preserve">19.8870162963867</t>
@@ -2726,46 +2726,46 @@
     <t xml:space="preserve">19.6450805664062</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1289501190186</t>
+    <t xml:space="preserve">20.1289520263672</t>
   </si>
   <si>
     <t xml:space="preserve">20.177339553833</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4192733764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4676609039307</t>
+    <t xml:space="preserve">20.4192752838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.467658996582</t>
   </si>
   <si>
     <t xml:space="preserve">21.2418518066406</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1934642791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4353981018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5805568695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6773338317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6289463043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0644264221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2579765319824</t>
+    <t xml:space="preserve">21.1934623718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.435396194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5805587768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6773319244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6289443969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0644283294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2579727172852</t>
   </si>
   <si>
     <t xml:space="preserve">22.6450710296631</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0321636199951</t>
+    <t xml:space="preserve">23.0321655273438</t>
   </si>
   <si>
     <t xml:space="preserve">23.4676475524902</t>
@@ -2777,10 +2777,10 @@
     <t xml:space="preserve">22.7902297973633</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7418441772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9676551818848</t>
+    <t xml:space="preserve">22.7418422698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9676532745361</t>
   </si>
   <si>
     <t xml:space="preserve">22.6934585571289</t>
@@ -2795,7 +2795,7 @@
     <t xml:space="preserve">21.8224925994873</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3547477722168</t>
+    <t xml:space="preserve">22.3547496795654</t>
   </si>
   <si>
     <t xml:space="preserve">22.112813949585</t>
@@ -2807,31 +2807,31 @@
     <t xml:space="preserve">22.9837779998779</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9031314849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1934509277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0966777801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0160293579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9676418304443</t>
+    <t xml:space="preserve">23.9031295776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.193452835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0966758728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0160312652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9676399230957</t>
   </si>
   <si>
     <t xml:space="preserve">25.4031238555908</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8386077880859</t>
+    <t xml:space="preserve">25.8386058807373</t>
   </si>
   <si>
     <t xml:space="preserve">25.9353790283203</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3547382354736</t>
+    <t xml:space="preserve">25.354736328125</t>
   </si>
   <si>
     <t xml:space="preserve">25.161190032959</t>
@@ -2846,7 +2846,7 @@
     <t xml:space="preserve">25.451509475708</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2095756530762</t>
+    <t xml:space="preserve">25.2095737457275</t>
   </si>
   <si>
     <t xml:space="preserve">25.5482845306396</t>
@@ -2861,22 +2861,22 @@
     <t xml:space="preserve">26.5160217285156</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9515037536621</t>
+    <t xml:space="preserve">26.9515056610107</t>
   </si>
   <si>
     <t xml:space="preserve">25.6934432983398</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5966739654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3063488006592</t>
+    <t xml:space="preserve">25.5966720581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3063507080078</t>
   </si>
   <si>
     <t xml:space="preserve">25.8869934082031</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3708610534668</t>
+    <t xml:space="preserve">26.3708629608154</t>
   </si>
   <si>
     <t xml:space="preserve">26.2043304443359</t>
@@ -2885,7 +2885,7 @@
     <t xml:space="preserve">25.616569519043</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1267681121826</t>
+    <t xml:space="preserve">25.1267700195312</t>
   </si>
   <si>
     <t xml:space="preserve">25.9594306945801</t>
@@ -2897,16 +2897,16 @@
     <t xml:space="preserve">25.2737083435059</t>
   </si>
   <si>
-    <t xml:space="preserve">25.02880859375</t>
+    <t xml:space="preserve">25.0288066864014</t>
   </si>
   <si>
     <t xml:space="preserve">25.2247295379639</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7349300384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.441047668457</t>
+    <t xml:space="preserve">24.7349281311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4410495758057</t>
   </si>
   <si>
     <t xml:space="preserve">24.8818683624268</t>
@@ -2921,10 +2921,10 @@
     <t xml:space="preserve">24.4900283813477</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7839069366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8328895568848</t>
+    <t xml:space="preserve">24.7839088439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8328876495361</t>
   </si>
   <si>
     <t xml:space="preserve">24.979829788208</t>
@@ -2933,19 +2933,19 @@
     <t xml:space="preserve">25.4696292877197</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9104518890381</t>
+    <t xml:space="preserve">25.9104499816895</t>
   </si>
   <si>
     <t xml:space="preserve">25.8614692687988</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7635078430176</t>
+    <t xml:space="preserve">25.7635097503662</t>
   </si>
   <si>
     <t xml:space="preserve">25.7145290374756</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2533111572266</t>
+    <t xml:space="preserve">26.2533092498779</t>
   </si>
   <si>
     <t xml:space="preserve">26.6941299438477</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">26.7920913696289</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5961685180664</t>
+    <t xml:space="preserve">26.596170425415</t>
   </si>
   <si>
     <t xml:space="preserve">26.4492301940918</t>
@@ -2987,7 +2987,7 @@
     <t xml:space="preserve">25.3716678619385</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1471672058105</t>
+    <t xml:space="preserve">24.1471691131592</t>
   </si>
   <si>
     <t xml:space="preserve">26.3512687683105</t>
@@ -3002,13 +3002,13 @@
     <t xml:space="preserve">26.9880104064941</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9390296936035</t>
+    <t xml:space="preserve">26.9390316009521</t>
   </si>
   <si>
     <t xml:space="preserve">26.0573902130127</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1063690185547</t>
+    <t xml:space="preserve">26.1063709259033</t>
   </si>
   <si>
     <t xml:space="preserve">26.6451511383057</t>
@@ -3023,40 +3023,40 @@
     <t xml:space="preserve">27.134952545166</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1553516387939</t>
+    <t xml:space="preserve">26.1553497314453</t>
   </si>
   <si>
     <t xml:space="preserve">27.3798522949219</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3308715820312</t>
+    <t xml:space="preserve">27.3308696746826</t>
   </si>
   <si>
     <t xml:space="preserve">27.7227115631104</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6737327575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0165939331055</t>
+    <t xml:space="preserve">27.6737308502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0165920257568</t>
   </si>
   <si>
     <t xml:space="preserve">27.5757713317871</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4778118133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5267906188965</t>
+    <t xml:space="preserve">27.4778099060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5267925262451</t>
   </si>
   <si>
     <t xml:space="preserve">25.8124904632568</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3022899627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2818908691406</t>
+    <t xml:space="preserve">26.3022918701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2818927764893</t>
   </si>
   <si>
     <t xml:space="preserve">27.4288330078125</t>
@@ -3065,13 +3065,13 @@
     <t xml:space="preserve">27.23291015625</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6247520446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8410720825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4982109069824</t>
+    <t xml:space="preserve">27.6247539520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8410701751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4982089996338</t>
   </si>
   <si>
     <t xml:space="preserve">25.567590713501</t>
@@ -3098,7 +3098,7 @@
     <t xml:space="preserve">28.5553722381592</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0451717376709</t>
+    <t xml:space="preserve">29.0451736450195</t>
   </si>
   <si>
     <t xml:space="preserve">29.1431331634521</t>
@@ -3116,10 +3116,10 @@
     <t xml:space="preserve">29.6819133758545</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7798728942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1921138763428</t>
+    <t xml:space="preserve">29.7798748016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1921119689941</t>
   </si>
   <si>
     <t xml:space="preserve">29.5349731445312</t>
@@ -3131,10 +3131,10 @@
     <t xml:space="preserve">30.2206954956055</t>
   </si>
   <si>
-    <t xml:space="preserve">30.514575958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8574371337891</t>
+    <t xml:space="preserve">30.5145740509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8574352264404</t>
   </si>
   <si>
     <t xml:space="preserve">32.1798973083496</t>
@@ -3149,10 +3149,10 @@
     <t xml:space="preserve">32.5227584838867</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0901222229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8248176574707</t>
+    <t xml:space="preserve">34.0901184082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.824821472168</t>
   </si>
   <si>
     <t xml:space="preserve">34.2860374450684</t>
@@ -3161,22 +3161,22 @@
     <t xml:space="preserve">34.6288986206055</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1390953063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7758369445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7472610473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8941993713379</t>
+    <t xml:space="preserve">34.1390991210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7758407592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.747257232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8941955566406</t>
   </si>
   <si>
     <t xml:space="preserve">34.335018157959</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9431800842285</t>
+    <t xml:space="preserve">33.9431838989258</t>
   </si>
   <si>
     <t xml:space="preserve">35.0207405090332</t>
@@ -3185,7 +3185,7 @@
     <t xml:space="preserve">35.4125823974609</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9635772705078</t>
+    <t xml:space="preserve">32.9635810852051</t>
   </si>
   <si>
     <t xml:space="preserve">32.9145965576172</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">33.0125579833984</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4451961517334</t>
+    <t xml:space="preserve">31.4451942443848</t>
   </si>
   <si>
     <t xml:space="preserve">31.5641193389893</t>
@@ -69866,7 +69866,7 @@
     </row>
     <row r="2527">
       <c r="A2527" s="1" t="n">
-        <v>45996.6913078704</v>
+        <v>45996.3333333333</v>
       </c>
       <c r="B2527" t="n">
         <v>69555</v>
@@ -69887,6 +69887,32 @@
         <v>1268</v>
       </c>
       <c r="H2527" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2528">
+      <c r="A2528" s="1" t="n">
+        <v>45999.6911226852</v>
+      </c>
+      <c r="B2528" t="n">
+        <v>15720</v>
+      </c>
+      <c r="C2528" t="n">
+        <v>49.3499984741211</v>
+      </c>
+      <c r="D2528" t="n">
+        <v>48.7999992370605</v>
+      </c>
+      <c r="E2528" t="n">
+        <v>49.2999992370605</v>
+      </c>
+      <c r="F2528" t="n">
+        <v>49</v>
+      </c>
+      <c r="G2528" t="s">
+        <v>1274</v>
+      </c>
+      <c r="H2528" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SOL.MI.xlsx
+++ b/data/SOL.MI.xlsx
@@ -47,10 +47,10 @@
     <t xml:space="preserve">7.14067268371582</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18862581253052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16247034072876</t>
+    <t xml:space="preserve">7.18862533569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16246891021729</t>
   </si>
   <si>
     <t xml:space="preserve">7.06220436096191</t>
@@ -59,13 +59,13 @@
     <t xml:space="preserve">6.90962553024292</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90526628494263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94885969161987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71781158447266</t>
+    <t xml:space="preserve">6.90526580810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94886016845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71781206130981</t>
   </si>
   <si>
     <t xml:space="preserve">6.62626504898071</t>
@@ -74,55 +74,55 @@
     <t xml:space="preserve">6.71345233917236</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29931163787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36470222473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43009233474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41265487670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44753074645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20776462554932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17288827896118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46060848236084</t>
+    <t xml:space="preserve">6.2993106842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3647027015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43009281158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41265535354614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4475302696228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20776414871216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1728892326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46060800552368</t>
   </si>
   <si>
     <t xml:space="preserve">6.54779672622681</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38214015960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51292085647583</t>
+    <t xml:space="preserve">6.38213920593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51292037963867</t>
   </si>
   <si>
     <t xml:space="preserve">6.50420188903809</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65242147445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80064105987549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72217178344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79192209243774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00989103317261</t>
+    <t xml:space="preserve">6.65242099761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80064153671265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72217130661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7919225692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00989055633545</t>
   </si>
   <si>
     <t xml:space="preserve">6.84423446655273</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">6.88346862792969</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96629667282104</t>
+    <t xml:space="preserve">6.9662971496582</t>
   </si>
   <si>
     <t xml:space="preserve">7.08835935592651</t>
@@ -146,211 +146,211 @@
     <t xml:space="preserve">6.8311562538147</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6785774230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57395315170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63062477111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68729686737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78320264816284</t>
+    <t xml:space="preserve">6.67857789993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57395219802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63062429428101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68729591369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.783203125</t>
   </si>
   <si>
     <t xml:space="preserve">6.77884340286255</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81371879577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80935955047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79628086090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69601535797119</t>
+    <t xml:space="preserve">6.81371784210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80936002731323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79628133773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69601488113403</t>
   </si>
   <si>
     <t xml:space="preserve">6.81807851791382</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8747501373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91398477554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67421817779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55215549468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46496772766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43881177902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73089075088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87910985946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85295295715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84859371185303</t>
+    <t xml:space="preserve">6.87475061416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91398525238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67421865463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5521559715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46496820449829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43881225585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73089027404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87910938262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85295391082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84859323501587</t>
   </si>
   <si>
     <t xml:space="preserve">6.85731220245361</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74832820892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51728010177612</t>
+    <t xml:space="preserve">6.74832773208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51728057861328</t>
   </si>
   <si>
     <t xml:space="preserve">6.37342071533203</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56523370742798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66985893249512</t>
+    <t xml:space="preserve">6.56523418426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66985940933228</t>
   </si>
   <si>
     <t xml:space="preserve">6.7701244354248</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86167144775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97501564025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94163036346436</t>
+    <t xml:space="preserve">6.86167192459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97501659393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9416298866272</t>
   </si>
   <si>
     <t xml:space="preserve">6.95048379898071</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88407754898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90178632736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34006595611572</t>
+    <t xml:space="preserve">6.88407802581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9017858505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34006500244141</t>
   </si>
   <si>
     <t xml:space="preserve">7.22496175765991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41975116729736</t>
+    <t xml:space="preserve">7.41975069046021</t>
   </si>
   <si>
     <t xml:space="preserve">7.43745946884155</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36662626266479</t>
+    <t xml:space="preserve">7.36662673950195</t>
   </si>
   <si>
     <t xml:space="preserve">7.26037836074829</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46845054626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40204381942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44631433486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38433599472046</t>
+    <t xml:space="preserve">7.46845006942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40204429626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44631481170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3843355178833</t>
   </si>
   <si>
     <t xml:space="preserve">7.0434513092041</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9726185798645</t>
+    <t xml:space="preserve">6.97261905670166</t>
   </si>
   <si>
     <t xml:space="preserve">7.10985708236694</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87079763412476</t>
+    <t xml:space="preserve">6.8707971572876</t>
   </si>
   <si>
     <t xml:space="preserve">7.20725345611572</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37105369567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57027196884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69422912597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70308446884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71193838119507</t>
+    <t xml:space="preserve">7.37105464935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57027149200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69423007965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70308494567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71193790435791</t>
   </si>
   <si>
     <t xml:space="preserve">7.65881204605103</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04396629333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61454391479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2957935333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99475431442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10100412368774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55256462097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31350231170654</t>
+    <t xml:space="preserve">8.04396820068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61454343795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29579448699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99475383758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1010046005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55256271362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3135027885437</t>
   </si>
   <si>
     <t xml:space="preserve">7.50829219818115</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42417907714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37548065185547</t>
+    <t xml:space="preserve">7.4241795539856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37548112869263</t>
   </si>
   <si>
     <t xml:space="preserve">7.52600145339966</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54370975494385</t>
+    <t xml:space="preserve">7.54371023178101</t>
   </si>
   <si>
     <t xml:space="preserve">7.41532516479492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21610689163208</t>
+    <t xml:space="preserve">7.21610736846924</t>
   </si>
   <si>
     <t xml:space="preserve">6.99032688140869</t>
@@ -362,73 +362,73 @@
     <t xml:space="preserve">6.75569343566895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00803565979004</t>
+    <t xml:space="preserve">7.0080361366272</t>
   </si>
   <si>
     <t xml:space="preserve">7.26923274993896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34449195861816</t>
+    <t xml:space="preserve">7.34449148178101</t>
   </si>
   <si>
     <t xml:space="preserve">7.46402311325073</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51714706420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39319086074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45516872406006</t>
+    <t xml:space="preserve">7.51714754104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39318990707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45516920089722</t>
   </si>
   <si>
     <t xml:space="preserve">7.1718373298645</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33563804626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33121061325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39761686325073</t>
+    <t xml:space="preserve">7.33563756942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33121109008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39761638641357</t>
   </si>
   <si>
     <t xml:space="preserve">7.30464839935303</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27808570861816</t>
+    <t xml:space="preserve">7.27808666229248</t>
   </si>
   <si>
     <t xml:space="preserve">7.25152397155762</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16298341751099</t>
+    <t xml:space="preserve">7.16298294067383</t>
   </si>
   <si>
     <t xml:space="preserve">7.03017091751099</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87965106964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91064023971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95491027832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88850498199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95933771133423</t>
+    <t xml:space="preserve">6.8796501159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91063976287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95491075515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88850545883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95933866500854</t>
   </si>
   <si>
     <t xml:space="preserve">6.85751485824585</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77340126037598</t>
+    <t xml:space="preserve">6.77340173721313</t>
   </si>
   <si>
     <t xml:space="preserve">6.74683904647827</t>
@@ -440,10 +440,10 @@
     <t xml:space="preserve">6.68486070632935</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81767129898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90621328353882</t>
+    <t xml:space="preserve">6.81767225265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90621376037598</t>
   </si>
   <si>
     <t xml:space="preserve">7.01689004898071</t>
@@ -452,10 +452,10 @@
     <t xml:space="preserve">6.8973593711853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83538055419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86194276809692</t>
+    <t xml:space="preserve">6.83538007736206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86194324493408</t>
   </si>
   <si>
     <t xml:space="preserve">6.92392158508301</t>
@@ -464,61 +464,61 @@
     <t xml:space="preserve">6.97704648971558</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00360774993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91506719589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91949462890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93720245361328</t>
+    <t xml:space="preserve">7.00360870361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91506814956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91949367523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93720293045044</t>
   </si>
   <si>
     <t xml:space="preserve">7.07001447677612</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98590087890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75126552581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77782821655273</t>
+    <t xml:space="preserve">6.98589992523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75126695632935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77782869338989</t>
   </si>
   <si>
     <t xml:space="preserve">6.64944410324097</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38382053375244</t>
+    <t xml:space="preserve">6.38382005691528</t>
   </si>
   <si>
     <t xml:space="preserve">6.37053918838501</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36168479919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37939357757568</t>
+    <t xml:space="preserve">6.36168432235718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37939310073853</t>
   </si>
   <si>
     <t xml:space="preserve">6.40595531463623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48121643066406</t>
+    <t xml:space="preserve">6.48121500015259</t>
   </si>
   <si>
     <t xml:space="preserve">6.47678852081299</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54319381713867</t>
+    <t xml:space="preserve">6.54319477081299</t>
   </si>
   <si>
     <t xml:space="preserve">6.46350765228271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24215459823608</t>
+    <t xml:space="preserve">6.24215412139893</t>
   </si>
   <si>
     <t xml:space="preserve">6.25986242294312</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">6.22444581985474</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64501619338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64058971405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03902435302734</t>
+    <t xml:space="preserve">6.64501667022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64058923721313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0390248298645</t>
   </si>
   <si>
     <t xml:space="preserve">6.79110956192017</t>
@@ -542,79 +542,79 @@
     <t xml:space="preserve">6.70256853103638</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70699453353882</t>
+    <t xml:space="preserve">6.70699596405029</t>
   </si>
   <si>
     <t xml:space="preserve">6.65829801559448</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58303737640381</t>
+    <t xml:space="preserve">6.58303785324097</t>
   </si>
   <si>
     <t xml:space="preserve">7.05673360824585</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11428499221802</t>
+    <t xml:space="preserve">7.11428451538086</t>
   </si>
   <si>
     <t xml:space="preserve">7.34891891479492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18511819839478</t>
+    <t xml:space="preserve">7.18511772155762</t>
   </si>
   <si>
     <t xml:space="preserve">7.12756633758545</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19397258758545</t>
+    <t xml:space="preserve">7.19397211074829</t>
   </si>
   <si>
     <t xml:space="preserve">7.24267053604126</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41089820861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48173141479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14527368545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27365970611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17626333236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04787969589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23381567001343</t>
+    <t xml:space="preserve">7.41089868545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48172998428345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14527416229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27365827560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1762638092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04788017272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23381614685059</t>
   </si>
   <si>
     <t xml:space="preserve">7.2913670539856</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42860651016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83589649200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82704162597656</t>
+    <t xml:space="preserve">7.4286060333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83589553833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82704210281372</t>
   </si>
   <si>
     <t xml:space="preserve">8.13693618774414</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27860069274902</t>
+    <t xml:space="preserve">8.27860260009766</t>
   </si>
   <si>
     <t xml:space="preserve">8.32287216186523</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03120136260986</t>
+    <t xml:space="preserve">9.03120231628418</t>
   </si>
   <si>
     <t xml:space="preserve">8.53094482421875</t>
@@ -629,37 +629,37 @@
     <t xml:space="preserve">8.92495155334473</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58849430084229</t>
+    <t xml:space="preserve">8.58849620819092</t>
   </si>
   <si>
     <t xml:space="preserve">8.97807693481445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76557636260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87182807922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56244850158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25255489349365</t>
+    <t xml:space="preserve">8.7655782699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87182903289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56244945526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25255393981934</t>
   </si>
   <si>
     <t xml:space="preserve">9.02234745025635</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85411834716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82755756378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7124547958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98693084716797</t>
+    <t xml:space="preserve">8.85411930084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82755851745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71245288848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98693180084229</t>
   </si>
   <si>
     <t xml:space="preserve">8.8983907699585</t>
@@ -668,67 +668,67 @@
     <t xml:space="preserve">8.80984973907471</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7213077545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78328514099121</t>
+    <t xml:space="preserve">8.72130870819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78328704833984</t>
   </si>
   <si>
     <t xml:space="preserve">8.67703819274902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75672435760498</t>
+    <t xml:space="preserve">8.7567253112793</t>
   </si>
   <si>
     <t xml:space="preserve">9.10203552246094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82312965393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94266033172607</t>
+    <t xml:space="preserve">8.82313060760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94266128540039</t>
   </si>
   <si>
     <t xml:space="preserve">9.20828342437744</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43287658691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45982837677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52271270751953</t>
+    <t xml:space="preserve">9.43287467956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4598274230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52271366119385</t>
   </si>
   <si>
     <t xml:space="preserve">9.32507228851318</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38795852661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35202407836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4238920211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29812240600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55864906311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67543697357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86409378051758</t>
+    <t xml:space="preserve">9.38795757293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35202312469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42389297485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29812145233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55865001678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67543601989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86409473419189</t>
   </si>
   <si>
     <t xml:space="preserve">10.5199031829834</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0617341995239</t>
+    <t xml:space="preserve">10.0617351531982</t>
   </si>
   <si>
     <t xml:space="preserve">9.88206195831299</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">9.74730587005615</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5676326751709</t>
+    <t xml:space="preserve">9.56763076782227</t>
   </si>
   <si>
     <t xml:space="preserve">9.44186019897461</t>
@@ -749,25 +749,25 @@
     <t xml:space="preserve">9.34303855895996</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36100578308105</t>
+    <t xml:space="preserve">9.36100673675537</t>
   </si>
   <si>
     <t xml:space="preserve">9.50474548339844</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48677921295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61254978179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77425670623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46881008148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54966449737549</t>
+    <t xml:space="preserve">9.48678016662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61255073547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77425765991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46881294250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54966354370117</t>
   </si>
   <si>
     <t xml:space="preserve">9.47779560089111</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">9.70238780975342</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30710411071777</t>
+    <t xml:space="preserve">9.30710506439209</t>
   </si>
   <si>
     <t xml:space="preserve">9.28015327453613</t>
@@ -785,40 +785,40 @@
     <t xml:space="preserve">9.2172679901123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16336536407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20828437805176</t>
+    <t xml:space="preserve">9.16336631774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20828247070312</t>
   </si>
   <si>
     <t xml:space="preserve">9.25320243835449</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45084476470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58559894561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33405590057373</t>
+    <t xml:space="preserve">9.45084381103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58559799194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33405685424805</t>
   </si>
   <si>
     <t xml:space="preserve">9.59458351135254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66645240783691</t>
+    <t xml:space="preserve">9.66645336151123</t>
   </si>
   <si>
     <t xml:space="preserve">9.71137237548828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40592575073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26218700408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27116870880127</t>
+    <t xml:space="preserve">9.40592670440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26218605041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27116966247559</t>
   </si>
   <si>
     <t xml:space="preserve">9.289137840271</t>
@@ -839,25 +839,25 @@
     <t xml:space="preserve">9.72035503387451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81019115447998</t>
+    <t xml:space="preserve">9.81019020080566</t>
   </si>
   <si>
     <t xml:space="preserve">9.37897396087646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90901184082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81917667388916</t>
+    <t xml:space="preserve">9.909010887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81917572021484</t>
   </si>
   <si>
     <t xml:space="preserve">9.73832130432129</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78324127197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69340324401855</t>
+    <t xml:space="preserve">9.78324222564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69340419769287</t>
   </si>
   <si>
     <t xml:space="preserve">9.11844730377197</t>
@@ -869,13 +869,13 @@
     <t xml:space="preserve">9.31608867645264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19031715393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10048007965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22625255584717</t>
+    <t xml:space="preserve">9.19031620025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1004810333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22625160217285</t>
   </si>
   <si>
     <t xml:space="preserve">9.41490840911865</t>
@@ -884,70 +884,70 @@
     <t xml:space="preserve">9.39694213867188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07353019714355</t>
+    <t xml:space="preserve">9.07352924346924</t>
   </si>
   <si>
     <t xml:space="preserve">9.57661533355713</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68441867828369</t>
+    <t xml:space="preserve">9.68441963195801</t>
   </si>
   <si>
     <t xml:space="preserve">9.09149646759033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05556106567383</t>
+    <t xml:space="preserve">9.05556011199951</t>
   </si>
   <si>
     <t xml:space="preserve">9.14539909362793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89385318756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10946369171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2352352142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95392894744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5109195709229</t>
+    <t xml:space="preserve">8.89385509490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10946464538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23523616790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95393180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5109186172485</t>
   </si>
   <si>
     <t xml:space="preserve">10.7444953918457</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5468549728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6905918121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9062023162842</t>
+    <t xml:space="preserve">10.5468530654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6905927658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9062032699585</t>
   </si>
   <si>
     <t xml:space="preserve">10.7804298400879</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7085590362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6546592712402</t>
+    <t xml:space="preserve">10.7085609436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6546583175659</t>
   </si>
   <si>
     <t xml:space="preserve">10.5288867950439</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4390506744385</t>
+    <t xml:space="preserve">10.4390497207642</t>
   </si>
   <si>
     <t xml:space="preserve">10.3312454223633</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1695404052734</t>
+    <t xml:space="preserve">10.1695394515991</t>
   </si>
   <si>
     <t xml:space="preserve">10.1875066757202</t>
@@ -956,16 +956,16 @@
     <t xml:space="preserve">10.1336040496826</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7562894821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63051700592041</t>
+    <t xml:space="preserve">9.75628852844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63051891326904</t>
   </si>
   <si>
     <t xml:space="preserve">10.0078344345093</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84612560272217</t>
+    <t xml:space="preserve">9.8461275100708</t>
   </si>
   <si>
     <t xml:space="preserve">10.0976696014404</t>
@@ -974,25 +974,25 @@
     <t xml:space="preserve">10.205472946167</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2773427963257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2234420776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2414093017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7624616622925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2593746185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91799545288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90002822875977</t>
+    <t xml:space="preserve">10.27734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2234411239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2414102554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7624626159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2593774795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91799640655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90002918243408</t>
   </si>
   <si>
     <t xml:space="preserve">9.67380714416504</t>
@@ -1001,7 +1001,7 @@
     <t xml:space="preserve">9.74667835235596</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87420463562012</t>
+    <t xml:space="preserve">9.87420558929443</t>
   </si>
   <si>
     <t xml:space="preserve">10.1656942367554</t>
@@ -1010,46 +1010,46 @@
     <t xml:space="preserve">9.85598754882812</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63737010955811</t>
+    <t xml:space="preserve">9.63736915588379</t>
   </si>
   <si>
     <t xml:space="preserve">9.47340679168701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76489639282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96529483795166</t>
+    <t xml:space="preserve">9.76489734649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96529674530029</t>
   </si>
   <si>
     <t xml:space="preserve">10.0746059417725</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2385673522949</t>
+    <t xml:space="preserve">10.2385663986206</t>
   </si>
   <si>
     <t xml:space="preserve">10.3843126296997</t>
   </si>
   <si>
-    <t xml:space="preserve">10.420747756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8033285140991</t>
+    <t xml:space="preserve">10.4207468032837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8033275604248</t>
   </si>
   <si>
     <t xml:space="preserve">10.6940202713013</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6211471557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7851085662842</t>
+    <t xml:space="preserve">10.621148109436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7851095199585</t>
   </si>
   <si>
     <t xml:space="preserve">10.5482740402222</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4025287628174</t>
+    <t xml:space="preserve">10.4025297164917</t>
   </si>
   <si>
     <t xml:space="preserve">10.2203493118286</t>
@@ -1058,7 +1058,7 @@
     <t xml:space="preserve">10.1474781036377</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3296575546265</t>
+    <t xml:space="preserve">10.3296585083008</t>
   </si>
   <si>
     <t xml:space="preserve">10.5847120285034</t>
@@ -1076,28 +1076,28 @@
     <t xml:space="preserve">9.4187536239624</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40053367614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54627895355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1110401153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2567853927612</t>
+    <t xml:space="preserve">9.40053462982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54627990722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1110410690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2567863464355</t>
   </si>
   <si>
     <t xml:space="preserve">9.92885971069336</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0199508666992</t>
+    <t xml:space="preserve">10.0199499130249</t>
   </si>
   <si>
     <t xml:space="preserve">10.202130317688</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0928211212158</t>
+    <t xml:space="preserve">10.0928220748901</t>
   </si>
   <si>
     <t xml:space="preserve">9.8013334274292</t>
@@ -1112,13 +1112,13 @@
     <t xml:space="preserve">9.94707775115967</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89242362976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65558815002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78311538696289</t>
+    <t xml:space="preserve">9.89242267608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65558910369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78311347961426</t>
   </si>
   <si>
     <t xml:space="preserve">9.91064167022705</t>
@@ -1127,13 +1127,13 @@
     <t xml:space="preserve">9.45518970489502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2001371383667</t>
+    <t xml:space="preserve">9.20013523101807</t>
   </si>
   <si>
     <t xml:space="preserve">9.50984287261963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43697071075439</t>
+    <t xml:space="preserve">9.43697261810303</t>
   </si>
   <si>
     <t xml:space="preserve">9.81955051422119</t>
@@ -1142,28 +1142,28 @@
     <t xml:space="preserve">9.49162483215332</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61915302276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98351287841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60093307495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10904502868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09993648529053</t>
+    <t xml:space="preserve">9.61915397644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9835147857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6009349822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10904598236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09993553161621</t>
   </si>
   <si>
     <t xml:space="preserve">9.38231658935547</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36409854888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27300930023193</t>
+    <t xml:space="preserve">9.36409950256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27300834655762</t>
   </si>
   <si>
     <t xml:space="preserve">9.71024227142334</t>
@@ -1172,10 +1172,10 @@
     <t xml:space="preserve">9.5827169418335</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29122638702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14548206329346</t>
+    <t xml:space="preserve">9.29122734069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14548301696777</t>
   </si>
   <si>
     <t xml:space="preserve">10.3660945892334</t>
@@ -1184,25 +1184,25 @@
     <t xml:space="preserve">9.32766246795654</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0017318725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4754018783569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8397626876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5664920806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3114404678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2932224273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0381679534912</t>
+    <t xml:space="preserve">10.0017328262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4754028320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8397636413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5664930343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3114395141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2932233810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0381698608398</t>
   </si>
   <si>
     <t xml:space="preserve">10.0563859939575</t>
@@ -1211,22 +1211,22 @@
     <t xml:space="preserve">10.1292581558228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2750034332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.183913230896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6758012771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7122373580933</t>
+    <t xml:space="preserve">10.2750043869019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1839141845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.675802230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7122364044189</t>
   </si>
   <si>
     <t xml:space="preserve">10.9308547973633</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0219459533691</t>
+    <t xml:space="preserve">11.0219449996948</t>
   </si>
   <si>
     <t xml:space="preserve">10.8762006759644</t>
@@ -1235,13 +1235,13 @@
     <t xml:space="preserve">10.8944187164307</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7304544448853</t>
+    <t xml:space="preserve">10.7304553985596</t>
   </si>
   <si>
     <t xml:space="preserve">10.6575832366943</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2644634246826</t>
+    <t xml:space="preserve">11.2644624710083</t>
   </si>
   <si>
     <t xml:space="preserve">11.1349868774414</t>
@@ -1250,19 +1250,19 @@
     <t xml:space="preserve">11.097993850708</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2459669113159</t>
+    <t xml:space="preserve">11.2459659576416</t>
   </si>
   <si>
     <t xml:space="preserve">11.319953918457</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0240058898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8205442428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8390398025513</t>
+    <t xml:space="preserve">11.0240068435669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8205432891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8390417098999</t>
   </si>
   <si>
     <t xml:space="preserve">10.7280607223511</t>
@@ -1271,19 +1271,19 @@
     <t xml:space="preserve">10.8575372695923</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7095623016357</t>
+    <t xml:space="preserve">10.7095632553101</t>
   </si>
   <si>
     <t xml:space="preserve">10.6725692749023</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6540727615356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7835502624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7650537490845</t>
+    <t xml:space="preserve">10.65407371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7835512161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7650547027588</t>
   </si>
   <si>
     <t xml:space="preserve">10.8020477294922</t>
@@ -1301,13 +1301,13 @@
     <t xml:space="preserve">10.1176710128784</t>
   </si>
   <si>
-    <t xml:space="preserve">10.284140586853</t>
+    <t xml:space="preserve">10.2841396331787</t>
   </si>
   <si>
     <t xml:space="preserve">10.2656440734863</t>
   </si>
   <si>
-    <t xml:space="preserve">10.302638053894</t>
+    <t xml:space="preserve">10.3026371002197</t>
   </si>
   <si>
     <t xml:space="preserve">10.5060997009277</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">10.3396301269531</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1361665725708</t>
+    <t xml:space="preserve">10.1361675262451</t>
   </si>
   <si>
     <t xml:space="preserve">10.0806770324707</t>
@@ -1328,34 +1328,34 @@
     <t xml:space="preserve">10.0991735458374</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93270492553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89571094512939</t>
+    <t xml:space="preserve">9.93270397186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89570999145508</t>
   </si>
   <si>
     <t xml:space="preserve">9.96969699859619</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1731595993042</t>
+    <t xml:space="preserve">10.1731605529785</t>
   </si>
   <si>
     <t xml:space="preserve">10.062180519104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1546630859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71074295043945</t>
+    <t xml:space="preserve">10.1546649932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71074390411377</t>
   </si>
   <si>
     <t xml:space="preserve">10.0251865386963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91420841217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76623630523682</t>
+    <t xml:space="preserve">9.91420745849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7662353515625</t>
   </si>
   <si>
     <t xml:space="preserve">9.72924137115479</t>
@@ -1367,40 +1367,40 @@
     <t xml:space="preserve">9.67375087738037</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47028636932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54427337646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56277084350586</t>
+    <t xml:space="preserve">9.47028732299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54427433013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56277179718018</t>
   </si>
   <si>
     <t xml:space="preserve">9.45179176330566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35930728912354</t>
+    <t xml:space="preserve">9.35930824279785</t>
   </si>
   <si>
     <t xml:space="preserve">9.52577781677246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59976482391357</t>
+    <t xml:space="preserve">9.59976387023926</t>
   </si>
   <si>
     <t xml:space="preserve">9.61826133728027</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69224834442139</t>
+    <t xml:space="preserve">9.69224643707275</t>
   </si>
   <si>
     <t xml:space="preserve">9.80322742462158</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2286510467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78473091125488</t>
+    <t xml:space="preserve">10.2286520004272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78472995758057</t>
   </si>
   <si>
     <t xml:space="preserve">9.858717918396</t>
@@ -1424,10 +1424,10 @@
     <t xml:space="preserve">10.4321146011353</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3766250610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2471466064453</t>
+    <t xml:space="preserve">10.3766231536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2471475601196</t>
   </si>
   <si>
     <t xml:space="preserve">10.2101535797119</t>
@@ -1436,10 +1436,10 @@
     <t xml:space="preserve">9.8402214050293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63675689697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43329524993896</t>
+    <t xml:space="preserve">9.63675785064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43329429626465</t>
   </si>
   <si>
     <t xml:space="preserve">9.41479778289795</t>
@@ -1448,19 +1448,19 @@
     <t xml:space="preserve">9.39630126953125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24832725524902</t>
+    <t xml:space="preserve">9.24832820892334</t>
   </si>
   <si>
     <t xml:space="preserve">9.06336212158203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10960292816162</t>
+    <t xml:space="preserve">9.10960388183594</t>
   </si>
   <si>
     <t xml:space="preserve">9.32231426239014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28532028198242</t>
+    <t xml:space="preserve">9.28532123565674</t>
   </si>
   <si>
     <t xml:space="preserve">9.26682567596436</t>
@@ -1469,13 +1469,13 @@
     <t xml:space="preserve">9.19283771514893</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22983074188232</t>
+    <t xml:space="preserve">9.22982978820801</t>
   </si>
   <si>
     <t xml:space="preserve">9.48878383636475</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02636814117432</t>
+    <t xml:space="preserve">9.02636909484863</t>
   </si>
   <si>
     <t xml:space="preserve">8.97087860107422</t>
@@ -1484,43 +1484,43 @@
     <t xml:space="preserve">9.13734817504883</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96162986755371</t>
+    <t xml:space="preserve">8.96162891387939</t>
   </si>
   <si>
     <t xml:space="preserve">8.82290458679199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61944007873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55470275878906</t>
+    <t xml:space="preserve">8.61943912506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55470371246338</t>
   </si>
   <si>
     <t xml:space="preserve">8.36048889160156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33274364471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0182991027832</t>
+    <t xml:space="preserve">8.33274459838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01830005645752</t>
   </si>
   <si>
     <t xml:space="preserve">7.8148365020752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95356178283691</t>
+    <t xml:space="preserve">7.95356225967407</t>
   </si>
   <si>
     <t xml:space="preserve">7.49114561080933</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86107969284058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50964260101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53738689422607</t>
+    <t xml:space="preserve">7.86107873916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50964307785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53738641738892</t>
   </si>
   <si>
     <t xml:space="preserve">7.58362865447998</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">8.98937511444092</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16509342193604</t>
+    <t xml:space="preserve">9.16509246826172</t>
   </si>
   <si>
     <t xml:space="preserve">9.12810039520264</t>
@@ -1541,7 +1541,7 @@
     <t xml:space="preserve">9.09110736846924</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08185863494873</t>
+    <t xml:space="preserve">9.08185768127441</t>
   </si>
   <si>
     <t xml:space="preserve">9.34081077575684</t>
@@ -1550,10 +1550,10 @@
     <t xml:space="preserve">9.04486465454102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21133518218994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38705158233643</t>
+    <t xml:space="preserve">9.21133422851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38705253601074</t>
   </si>
   <si>
     <t xml:space="preserve">9.17434120178223</t>
@@ -1565,16 +1565,16 @@
     <t xml:space="preserve">9.11885070800781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78591060638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89689254760742</t>
+    <t xml:space="preserve">8.78591251373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89689159393311</t>
   </si>
   <si>
     <t xml:space="preserve">8.7489185333252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80440807342529</t>
+    <t xml:space="preserve">8.80440902709961</t>
   </si>
   <si>
     <t xml:space="preserve">8.87839508056641</t>
@@ -1583,16 +1583,16 @@
     <t xml:space="preserve">8.9338846206665</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63793754577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71192455291748</t>
+    <t xml:space="preserve">8.63793849945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7119255065918</t>
   </si>
   <si>
     <t xml:space="preserve">8.58244800567627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69342708587646</t>
+    <t xml:space="preserve">8.69342803955078</t>
   </si>
   <si>
     <t xml:space="preserve">9.46113967895508</t>
@@ -1610,7 +1610,7 @@
     <t xml:space="preserve">9.97891330718994</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93184280395508</t>
+    <t xml:space="preserve">9.93184375762939</t>
   </si>
   <si>
     <t xml:space="preserve">9.79063129425049</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">10.1671943664551</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1201229095459</t>
+    <t xml:space="preserve">10.1201238632202</t>
   </si>
   <si>
     <t xml:space="preserve">10.0259828567505</t>
@@ -1637,10 +1637,10 @@
     <t xml:space="preserve">10.2142639160156</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3554754257202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2613344192505</t>
+    <t xml:space="preserve">10.3554744720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2613334655762</t>
   </si>
   <si>
     <t xml:space="preserve">9.8847713470459</t>
@@ -1655,10 +1655,10 @@
     <t xml:space="preserve">10.5437574386597</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2027406692505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1556711196899</t>
+    <t xml:space="preserve">11.2027416229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1556720733643</t>
   </si>
   <si>
     <t xml:space="preserve">10.9673900604248</t>
@@ -1676,16 +1676,16 @@
     <t xml:space="preserve">11.0144605636597</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1086015701294</t>
+    <t xml:space="preserve">11.1086025238037</t>
   </si>
   <si>
     <t xml:space="preserve">10.9203205108643</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8732500076294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7320394515991</t>
+    <t xml:space="preserve">10.8732509613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7320384979248</t>
   </si>
   <si>
     <t xml:space="preserve">10.6378984451294</t>
@@ -1703,7 +1703,7 @@
     <t xml:space="preserve">11.8146562576294</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5793037414551</t>
+    <t xml:space="preserve">11.5793046951294</t>
   </si>
   <si>
     <t xml:space="preserve">11.6734447479248</t>
@@ -1712,7 +1712,7 @@
     <t xml:space="preserve">11.7205152511597</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0029382705688</t>
+    <t xml:space="preserve">12.0029373168945</t>
   </si>
   <si>
     <t xml:space="preserve">12.2853603363037</t>
@@ -1721,13 +1721,13 @@
     <t xml:space="preserve">12.5677814483643</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5207109451294</t>
+    <t xml:space="preserve">12.5207118988037</t>
   </si>
   <si>
     <t xml:space="preserve">12.897274017334</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7560625076294</t>
+    <t xml:space="preserve">12.7560634613037</t>
   </si>
   <si>
     <t xml:space="preserve">12.661922454834</t>
@@ -1742,13 +1742,13 @@
     <t xml:space="preserve">12.8502035140991</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9914150238037</t>
+    <t xml:space="preserve">12.991415977478</t>
   </si>
   <si>
     <t xml:space="preserve">13.1796970367432</t>
   </si>
   <si>
-    <t xml:space="preserve">13.462119102478</t>
+    <t xml:space="preserve">13.4621181488037</t>
   </si>
   <si>
     <t xml:space="preserve">13.838680267334</t>
@@ -1757,10 +1757,10 @@
     <t xml:space="preserve">13.7445411682129</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6504001617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5091896057129</t>
+    <t xml:space="preserve">13.6503992080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5091886520386</t>
   </si>
   <si>
     <t xml:space="preserve">13.7916097640991</t>
@@ -1772,7 +1772,7 @@
     <t xml:space="preserve">13.9798927307129</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0269622802734</t>
+    <t xml:space="preserve">14.0269613265991</t>
   </si>
   <si>
     <t xml:space="preserve">14.074031829834</t>
@@ -1781,13 +1781,13 @@
     <t xml:space="preserve">14.168173789978</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1211032867432</t>
+    <t xml:space="preserve">14.1211023330688</t>
   </si>
   <si>
     <t xml:space="preserve">14.2623138427734</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2152452468872</t>
+    <t xml:space="preserve">14.2152442932129</t>
   </si>
   <si>
     <t xml:space="preserve">14.4505958557129</t>
@@ -1796,13 +1796,13 @@
     <t xml:space="preserve">14.6859474182129</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3093843460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4035243988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3564548492432</t>
+    <t xml:space="preserve">14.3093852996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4035263061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3564558029175</t>
   </si>
   <si>
     <t xml:space="preserve">14.5447368621826</t>
@@ -1817,19 +1817,19 @@
     <t xml:space="preserve">14.7800884246826</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8271589279175</t>
+    <t xml:space="preserve">14.8271579742432</t>
   </si>
   <si>
     <t xml:space="preserve">14.874228477478</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7330179214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3449306488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7685670852661</t>
+    <t xml:space="preserve">14.7330169677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.344931602478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7685651779175</t>
   </si>
   <si>
     <t xml:space="preserve">16.0039176940918</t>
@@ -1838,127 +1838,127 @@
     <t xml:space="preserve">16.0415725708008</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0792274475098</t>
+    <t xml:space="preserve">16.0792293548584</t>
   </si>
   <si>
     <t xml:space="preserve">16.1921977996826</t>
   </si>
   <si>
+    <t xml:space="preserve">16.116886138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2298545837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3804798126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3993072509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4181346893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5311050415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2675113677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9286050796509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8909482955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8156328201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9662580490112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7214956283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5332117080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5143842697144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7026672363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2696199417114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4767293930054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6838369369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6650085449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4202451705933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1566514968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2319641113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7779769897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9833707809448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9643001556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6209812164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4874687194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7926406860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8117160797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6019086837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5446872711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2585897445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6972742080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8307876586914</t>
+  </si>
+  <si>
     <t xml:space="preserve">16.1168842315674</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2298545837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3804798126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3993072509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4181346893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5311031341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2675094604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9286050796509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8909482955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.815634727478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9662599563599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7214965820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5332126617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5143852233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7026672363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2696189880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4767293930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.683837890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6650094985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4202442169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1566505432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2319641113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7779779434204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9833717346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.964301109314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6209812164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4874696731567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7926406860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8117151260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6019096374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5446872711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2585887908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6972742080688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8307876586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.116886138916</t>
-  </si>
-  <si>
     <t xml:space="preserve">16.2503986358643</t>
   </si>
   <si>
     <t xml:space="preserve">16.2313251495361</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0024471282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2694702148438</t>
+    <t xml:space="preserve">16.0024452209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2694721221924</t>
   </si>
   <si>
     <t xml:space="preserve">16.2122535705566</t>
@@ -1976,7 +1976,7 @@
     <t xml:space="preserve">16.555570602417</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1659145355225</t>
+    <t xml:space="preserve">17.1659126281738</t>
   </si>
   <si>
     <t xml:space="preserve">16.9561080932617</t>
@@ -1997,13 +1997,13 @@
     <t xml:space="preserve">16.746301651001</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9751815795898</t>
+    <t xml:space="preserve">16.9751796722412</t>
   </si>
   <si>
     <t xml:space="preserve">17.1277656555176</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5092334747314</t>
+    <t xml:space="preserve">17.5092315673828</t>
   </si>
   <si>
     <t xml:space="preserve">17.5473785400391</t>
@@ -2015,13 +2015,13 @@
     <t xml:space="preserve">17.6427440643311</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7381114959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4901599884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4710865020752</t>
+    <t xml:space="preserve">17.7381134033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4901580810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4710845947266</t>
   </si>
   <si>
     <t xml:space="preserve">17.337574005127</t>
@@ -2045,13 +2045,13 @@
     <t xml:space="preserve">17.4520111083984</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8334770202637</t>
+    <t xml:space="preserve">17.8334789276123</t>
   </si>
   <si>
     <t xml:space="preserve">17.6999645233154</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8716239929199</t>
+    <t xml:space="preserve">17.8716259002686</t>
   </si>
   <si>
     <t xml:space="preserve">17.8525505065918</t>
@@ -2060,10 +2060,10 @@
     <t xml:space="preserve">18.0242080688477</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4247455596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5010414123535</t>
+    <t xml:space="preserve">18.424747467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5010395050049</t>
   </si>
   <si>
     <t xml:space="preserve">18.6536254882812</t>
@@ -2084,10 +2084,10 @@
     <t xml:space="preserve">18.520112991333</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5500679016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5023860931396</t>
+    <t xml:space="preserve">19.5500659942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5023880004883</t>
   </si>
   <si>
     <t xml:space="preserve">19.8838500976562</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">18.6917743682861</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2162837982178</t>
+    <t xml:space="preserve">19.2162857055664</t>
   </si>
   <si>
     <t xml:space="preserve">19.1209182739258</t>
@@ -2120,16 +2120,16 @@
     <t xml:space="preserve">18.7680644989014</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9097690582275</t>
+    <t xml:space="preserve">17.9097709655762</t>
   </si>
   <si>
     <t xml:space="preserve">18.1195755004883</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6236705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8906955718994</t>
+    <t xml:space="preserve">17.6236686706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.890697479248</t>
   </si>
   <si>
     <t xml:space="preserve">18.1005020141602</t>
@@ -2144,7 +2144,7 @@
     <t xml:space="preserve">18.176794052124</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9969463348389</t>
+    <t xml:space="preserve">18.9969444274902</t>
   </si>
   <si>
     <t xml:space="preserve">19.0732364654541</t>
@@ -2162,13 +2162,13 @@
     <t xml:space="preserve">18.9015769958496</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0268974304199</t>
+    <t xml:space="preserve">20.0268993377686</t>
   </si>
   <si>
     <t xml:space="preserve">20.2176322937012</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2653160095215</t>
+    <t xml:space="preserve">20.2653141021729</t>
   </si>
   <si>
     <t xml:space="preserve">20.7421455383301</t>
@@ -2192,10 +2192,10 @@
     <t xml:space="preserve">20.4560508728027</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9805603027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8361663818359</t>
+    <t xml:space="preserve">20.980562210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8361682891846</t>
   </si>
   <si>
     <t xml:space="preserve">20.4083633422852</t>
@@ -2204,7 +2204,7 @@
     <t xml:space="preserve">20.1222667694092</t>
   </si>
   <si>
-    <t xml:space="preserve">19.311653137207</t>
+    <t xml:space="preserve">19.3116550445557</t>
   </si>
   <si>
     <t xml:space="preserve">19.2639694213867</t>
@@ -2213,25 +2213,25 @@
     <t xml:space="preserve">19.597749710083</t>
   </si>
   <si>
-    <t xml:space="preserve">19.645435333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1699485778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9315319061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7408027648926</t>
+    <t xml:space="preserve">19.6454334259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1699466705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9315338134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7408008575439</t>
   </si>
   <si>
     <t xml:space="preserve">18.8443603515625</t>
   </si>
   <si>
-    <t xml:space="preserve">19.016019821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0432834625244</t>
+    <t xml:space="preserve">19.0160179138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0432815551758</t>
   </si>
   <si>
     <t xml:space="preserve">18.0051345825195</t>
@@ -2246,7 +2246,7 @@
     <t xml:space="preserve">18.0814266204834</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6045989990234</t>
+    <t xml:space="preserve">17.6045970916748</t>
   </si>
   <si>
     <t xml:space="preserve">17.2612800598145</t>
@@ -2255,31 +2255,31 @@
     <t xml:space="preserve">17.0514736175537</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2885437011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0324020385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7272300720215</t>
+    <t xml:space="preserve">16.2885456085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0324001312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7272319793701</t>
   </si>
   <si>
     <t xml:space="preserve">16.4792766571045</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8225936889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0705490112305</t>
+    <t xml:space="preserve">16.8225955963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0705471038818</t>
   </si>
   <si>
     <t xml:space="preserve">16.6509342193604</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8607425689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3076171875</t>
+    <t xml:space="preserve">16.8607444763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3076190948486</t>
   </si>
   <si>
     <t xml:space="preserve">16.5937175750732</t>
@@ -2312,7 +2312,7 @@
     <t xml:space="preserve">15.1441507339478</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9452276229858</t>
+    <t xml:space="preserve">15.9452257156372</t>
   </si>
   <si>
     <t xml:space="preserve">16.0787410736084</t>
@@ -2336,22 +2336,22 @@
     <t xml:space="preserve">15.7354202270508</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8880062103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5065412521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9724922180176</t>
+    <t xml:space="preserve">15.8880052566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5065402984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9724912643433</t>
   </si>
   <si>
     <t xml:space="preserve">15.3348827362061</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2204427719116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9152717590332</t>
+    <t xml:space="preserve">15.2204437255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9152727127075</t>
   </si>
   <si>
     <t xml:space="preserve">14.781759262085</t>
@@ -2372,7 +2372,7 @@
     <t xml:space="preserve">15.1060047149658</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0063877105713</t>
+    <t xml:space="preserve">16.0063896179199</t>
   </si>
   <si>
     <t xml:space="preserve">16.1999359130859</t>
@@ -2390,10 +2390,10 @@
     <t xml:space="preserve">16.2773532867432</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4709033966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7805767059326</t>
+    <t xml:space="preserve">16.4709014892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7805786132812</t>
   </si>
   <si>
     <t xml:space="preserve">17.1483173370361</t>
@@ -2402,28 +2402,28 @@
     <t xml:space="preserve">17.767671585083</t>
   </si>
   <si>
-    <t xml:space="preserve">17.419282913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2321853637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7289600372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9418659210205</t>
+    <t xml:space="preserve">17.4192848205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2321834564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7289619445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9418640136719</t>
   </si>
   <si>
     <t xml:space="preserve">17.4967041015625</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5934791564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4579963684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8967037200928</t>
+    <t xml:space="preserve">17.5934772491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4579944610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8967056274414</t>
   </si>
   <si>
     <t xml:space="preserve">16.4515476226807</t>
@@ -2432,13 +2432,13 @@
     <t xml:space="preserve">15.9870338439941</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8321962356567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9483232498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3676805496216</t>
+    <t xml:space="preserve">15.8321952819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9483222961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3676795959473</t>
   </si>
   <si>
     <t xml:space="preserve">15.4450988769531</t>
@@ -2447,10 +2447,10 @@
     <t xml:space="preserve">15.1741333007812</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1160688400269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.135422706604</t>
+    <t xml:space="preserve">15.1160678863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1354236602783</t>
   </si>
   <si>
     <t xml:space="preserve">15.3289709091187</t>
@@ -2459,13 +2459,13 @@
     <t xml:space="preserve">15.619291305542</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8902597427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7547750473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8128395080566</t>
+    <t xml:space="preserve">15.8902606964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7547760009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.812840461731</t>
   </si>
   <si>
     <t xml:space="preserve">16.161226272583</t>
@@ -2480,7 +2480,7 @@
     <t xml:space="preserve">16.4128360748291</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4321899414062</t>
+    <t xml:space="preserve">16.4321918487549</t>
   </si>
   <si>
     <t xml:space="preserve">15.7160663604736</t>
@@ -2504,10 +2504,10 @@
     <t xml:space="preserve">17.5354137420654</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3805732727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3418674468994</t>
+    <t xml:space="preserve">17.3805751800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3418655395508</t>
   </si>
   <si>
     <t xml:space="preserve">17.2063827514648</t>
@@ -2531,16 +2531,16 @@
     <t xml:space="preserve">17.6128330230713</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8192882537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1096096038818</t>
+    <t xml:space="preserve">16.8192863464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1096076965332</t>
   </si>
   <si>
     <t xml:space="preserve">16.7225131988525</t>
   </si>
   <si>
-    <t xml:space="preserve">17.128963470459</t>
+    <t xml:space="preserve">17.1289653778076</t>
   </si>
   <si>
     <t xml:space="preserve">16.8773517608643</t>
@@ -2561,13 +2561,13 @@
     <t xml:space="preserve">15.5031642913818</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2128419876099</t>
+    <t xml:space="preserve">15.2128429412842</t>
   </si>
   <si>
     <t xml:space="preserve">15.3096160888672</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5805826187134</t>
+    <t xml:space="preserve">15.5805835723877</t>
   </si>
   <si>
     <t xml:space="preserve">15.1547775268555</t>
@@ -2588,7 +2588,7 @@
     <t xml:space="preserve">15.5612277984619</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1805782318115</t>
+    <t xml:space="preserve">16.1805801391602</t>
   </si>
   <si>
     <t xml:space="preserve">16.8579978942871</t>
@@ -2597,10 +2597,10 @@
     <t xml:space="preserve">17.3031558990479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9031524658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8063812255859</t>
+    <t xml:space="preserve">17.9031543731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8063793182373</t>
   </si>
   <si>
     <t xml:space="preserve">17.1676731109619</t>
@@ -2615,7 +2615,7 @@
     <t xml:space="preserve">18.735408782959</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6579895019531</t>
+    <t xml:space="preserve">18.6579914093018</t>
   </si>
   <si>
     <t xml:space="preserve">18.4837970733643</t>
@@ -2630,7 +2630,7 @@
     <t xml:space="preserve">18.2515392303467</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8837985992432</t>
+    <t xml:space="preserve">17.8837966918945</t>
   </si>
   <si>
     <t xml:space="preserve">18.0386352539062</t>
@@ -2648,7 +2648,7 @@
     <t xml:space="preserve">18.1547660827637</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0192813873291</t>
+    <t xml:space="preserve">18.0192832946777</t>
   </si>
   <si>
     <t xml:space="preserve">17.9805736541748</t>
@@ -2660,7 +2660,7 @@
     <t xml:space="preserve">17.8450908660889</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6902523040771</t>
+    <t xml:space="preserve">17.6902503967285</t>
   </si>
   <si>
     <t xml:space="preserve">17.6321868896484</t>
@@ -2678,19 +2678,19 @@
     <t xml:space="preserve">17.2644462585449</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7096061706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4773483276367</t>
+    <t xml:space="preserve">17.7096042633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4773502349854</t>
   </si>
   <si>
     <t xml:space="preserve">17.8257369995117</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5805721282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9289569854736</t>
+    <t xml:space="preserve">18.5805702209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.928955078125</t>
   </si>
   <si>
     <t xml:space="preserve">18.8128299713135</t>
@@ -2705,10 +2705,10 @@
     <t xml:space="preserve">19.7902450561523</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0321769714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7418556213379</t>
+    <t xml:space="preserve">20.0321788787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7418575286865</t>
   </si>
   <si>
     <t xml:space="preserve">19.5966968536377</t>
@@ -2717,13 +2717,13 @@
     <t xml:space="preserve">19.9837894439697</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8386287689209</t>
+    <t xml:space="preserve">19.8386306762695</t>
   </si>
   <si>
     <t xml:space="preserve">20.0805644989014</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3708839416504</t>
+    <t xml:space="preserve">20.370885848999</t>
   </si>
   <si>
     <t xml:space="preserve">19.8870162963867</t>
@@ -2738,7 +2738,7 @@
     <t xml:space="preserve">20.177339553833</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4192752838135</t>
+    <t xml:space="preserve">20.4192733764648</t>
   </si>
   <si>
     <t xml:space="preserve">20.467658996582</t>
@@ -2762,10 +2762,10 @@
     <t xml:space="preserve">21.6289443969727</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0644283294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2579727172852</t>
+    <t xml:space="preserve">22.0644264221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2579746246338</t>
   </si>
   <si>
     <t xml:space="preserve">22.6450710296631</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">22.7902297973633</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7418422698975</t>
+    <t xml:space="preserve">22.7418441772461</t>
   </si>
   <si>
     <t xml:space="preserve">21.9676532745361</t>
@@ -2798,31 +2798,31 @@
     <t xml:space="preserve">22.3063621520996</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8224925994873</t>
+    <t xml:space="preserve">21.8224906921387</t>
   </si>
   <si>
     <t xml:space="preserve">22.3547496795654</t>
   </si>
   <si>
-    <t xml:space="preserve">22.112813949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5482959747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9837779998779</t>
+    <t xml:space="preserve">22.1128158569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5482978820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9837799072266</t>
   </si>
   <si>
     <t xml:space="preserve">23.9031295776367</t>
   </si>
   <si>
-    <t xml:space="preserve">24.193452835083</t>
+    <t xml:space="preserve">24.1934509277344</t>
   </si>
   <si>
     <t xml:space="preserve">24.0966758728027</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0160312652588</t>
+    <t xml:space="preserve">25.0160293579102</t>
   </si>
   <si>
     <t xml:space="preserve">24.9676399230957</t>
@@ -2837,22 +2837,22 @@
     <t xml:space="preserve">25.9353790283203</t>
   </si>
   <si>
-    <t xml:space="preserve">25.354736328125</t>
+    <t xml:space="preserve">25.3547382354736</t>
   </si>
   <si>
     <t xml:space="preserve">25.161190032959</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8708686828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.257963180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.451509475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2095737457275</t>
+    <t xml:space="preserve">24.8708667755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2579650878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4515113830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2095756530762</t>
   </si>
   <si>
     <t xml:space="preserve">25.5482845306396</t>
@@ -2870,7 +2870,7 @@
     <t xml:space="preserve">26.9515056610107</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6934432983398</t>
+    <t xml:space="preserve">25.6934452056885</t>
   </si>
   <si>
     <t xml:space="preserve">25.5966720581055</t>
@@ -2882,7 +2882,7 @@
     <t xml:space="preserve">25.8869934082031</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3708629608154</t>
+    <t xml:space="preserve">26.3708610534668</t>
   </si>
   <si>
     <t xml:space="preserve">26.2043304443359</t>
@@ -70037,7 +70037,7 @@
     </row>
     <row r="2533">
       <c r="A2533" s="1" t="n">
-        <v>46006.6911342593</v>
+        <v>46006.3333333333</v>
       </c>
       <c r="B2533" t="n">
         <v>87173</v>
@@ -70058,6 +70058,32 @@
         <v>1284</v>
       </c>
       <c r="H2533" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2534">
+      <c r="A2534" s="1" t="n">
+        <v>46007.6911805556</v>
+      </c>
+      <c r="B2534" t="n">
+        <v>91865</v>
+      </c>
+      <c r="C2534" t="n">
+        <v>49.3499984741211</v>
+      </c>
+      <c r="D2534" t="n">
+        <v>47.7999992370605</v>
+      </c>
+      <c r="E2534" t="n">
+        <v>49.3499984741211</v>
+      </c>
+      <c r="F2534" t="n">
+        <v>48</v>
+      </c>
+      <c r="G2534" t="s">
+        <v>1233</v>
+      </c>
+      <c r="H2534" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SOL.MI.xlsx
+++ b/data/SOL.MI.xlsx
@@ -38,58 +38,58 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14939117431641</t>
+    <t xml:space="preserve">7.14939165115356</t>
   </si>
   <si>
     <t xml:space="preserve">SOL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14067268371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18862628936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16247034072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0622034072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90962600708008</t>
+    <t xml:space="preserve">7.14067220687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18862581253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1624698638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06220293045044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90962553024292</t>
   </si>
   <si>
     <t xml:space="preserve">6.90526628494263</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94885873794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7178111076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62626504898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71345281600952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29931116104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36470127105713</t>
+    <t xml:space="preserve">6.94885921478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71781206130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62626457214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71345233917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29931163787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3647027015686</t>
   </si>
   <si>
     <t xml:space="preserve">6.43009281158447</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41265535354614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4475302696228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20776462554932</t>
+    <t xml:space="preserve">6.41265487670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44753074645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20776414871216</t>
   </si>
   <si>
     <t xml:space="preserve">6.1728892326355</t>
@@ -98,10 +98,10 @@
     <t xml:space="preserve">6.46060848236084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54779624938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38213968276978</t>
+    <t xml:space="preserve">6.54779672622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38213920593262</t>
   </si>
   <si>
     <t xml:space="preserve">6.51292085647583</t>
@@ -110,103 +110,103 @@
     <t xml:space="preserve">6.50420236587524</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65242195129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80064058303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72217226028442</t>
+    <t xml:space="preserve">6.6524224281311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80064105987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72217178344727</t>
   </si>
   <si>
     <t xml:space="preserve">6.79192161560059</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00989103317261</t>
+    <t xml:space="preserve">7.00989151000977</t>
   </si>
   <si>
     <t xml:space="preserve">6.84423398971558</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07964086532593</t>
+    <t xml:space="preserve">7.07964134216309</t>
   </si>
   <si>
     <t xml:space="preserve">6.88346910476685</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96629667282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08835983276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73524904251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8311562538147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67857789993286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57395219802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63062429428101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68729686737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78320264816284</t>
+    <t xml:space="preserve">6.96629762649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08836030960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7352499961853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83115577697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67857837677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57395267486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63062524795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68729734420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.783203125</t>
   </si>
   <si>
     <t xml:space="preserve">6.77884387969971</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81371831893921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80935859680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79628133773804</t>
+    <t xml:space="preserve">6.81371927261353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80935907363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79628086090088</t>
   </si>
   <si>
     <t xml:space="preserve">6.69601488113403</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81807899475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87475061416626</t>
+    <t xml:space="preserve">6.81807804107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8747501373291</t>
   </si>
   <si>
     <t xml:space="preserve">6.91398429870605</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67421913146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55215549468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46496820449829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43881177902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73088979721069</t>
+    <t xml:space="preserve">6.67421817779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55215501785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46496772766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43881130218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73089027404785</t>
   </si>
   <si>
     <t xml:space="preserve">6.87910938262939</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85295295715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84859323501587</t>
+    <t xml:space="preserve">6.85295391082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84859466552734</t>
   </si>
   <si>
     <t xml:space="preserve">6.85731220245361</t>
@@ -215,25 +215,25 @@
     <t xml:space="preserve">6.74832773208618</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51728105545044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37342023849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56523370742798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66985988616943</t>
+    <t xml:space="preserve">6.51728057861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37342071533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56523418426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66985940933228</t>
   </si>
   <si>
     <t xml:space="preserve">6.77012491226196</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86167240142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97501659393311</t>
+    <t xml:space="preserve">6.86167144775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97501611709595</t>
   </si>
   <si>
     <t xml:space="preserve">6.9416298866272</t>
@@ -242,31 +242,31 @@
     <t xml:space="preserve">6.95048379898071</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88407850265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90178632736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34006547927856</t>
+    <t xml:space="preserve">6.88407802581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9017858505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34006595611572</t>
   </si>
   <si>
     <t xml:space="preserve">7.22496175765991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41975164413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43745994567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36662721633911</t>
+    <t xml:space="preserve">7.41975212097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43746042251587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36662769317627</t>
   </si>
   <si>
     <t xml:space="preserve">7.26037788391113</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46845054626465</t>
+    <t xml:space="preserve">7.46845006942749</t>
   </si>
   <si>
     <t xml:space="preserve">7.40204381942749</t>
@@ -275,10 +275,10 @@
     <t xml:space="preserve">7.44631385803223</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3843355178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04345178604126</t>
+    <t xml:space="preserve">7.38433504104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04345226287842</t>
   </si>
   <si>
     <t xml:space="preserve">6.97261905670166</t>
@@ -290,43 +290,43 @@
     <t xml:space="preserve">6.87079668045044</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20725393295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37105417251587</t>
+    <t xml:space="preserve">7.20725345611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37105464935303</t>
   </si>
   <si>
     <t xml:space="preserve">7.57027149200439</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69422817230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70308399200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71193885803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6588134765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04396915435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61454296112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29579448699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99475526809692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1010046005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55256509780884</t>
+    <t xml:space="preserve">7.69423007965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70308494567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71193790435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65881395339966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04396724700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61454248428345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29579496383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99475479125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10100412368774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55256414413452</t>
   </si>
   <si>
     <t xml:space="preserve">7.31350231170654</t>
@@ -335,70 +335,70 @@
     <t xml:space="preserve">7.50829315185547</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4241795539856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3754825592041</t>
+    <t xml:space="preserve">7.42417907714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37548208236694</t>
   </si>
   <si>
     <t xml:space="preserve">7.52600240707397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54370880126953</t>
+    <t xml:space="preserve">7.54370975494385</t>
   </si>
   <si>
     <t xml:space="preserve">7.41532421112061</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21610689163208</t>
+    <t xml:space="preserve">7.21610736846924</t>
   </si>
   <si>
     <t xml:space="preserve">6.99032735824585</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79996347427368</t>
+    <t xml:space="preserve">6.79996395111084</t>
   </si>
   <si>
     <t xml:space="preserve">6.75569343566895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00803565979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26923227310181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34449291229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46402263641357</t>
+    <t xml:space="preserve">7.00803518295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26923274993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34449195861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46402215957642</t>
   </si>
   <si>
     <t xml:space="preserve">7.51714706420898</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39318895339966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45516967773438</t>
+    <t xml:space="preserve">7.39318943023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45516872406006</t>
   </si>
   <si>
     <t xml:space="preserve">7.17183637619019</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33563709259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33121061325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39761686325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30464887619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27808618545532</t>
+    <t xml:space="preserve">7.33563804626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33121156692505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39761638641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3046498298645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27808666229248</t>
   </si>
   <si>
     <t xml:space="preserve">7.25152349472046</t>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">6.91063976287842</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95491075515747</t>
+    <t xml:space="preserve">6.95491170883179</t>
   </si>
   <si>
     <t xml:space="preserve">6.88850545883179</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">6.95933866500854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85751581192017</t>
+    <t xml:space="preserve">6.85751533508301</t>
   </si>
   <si>
     <t xml:space="preserve">6.77340173721313</t>
@@ -434,28 +434,28 @@
     <t xml:space="preserve">6.74683952331543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82652568817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68486070632935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81767177581787</t>
+    <t xml:space="preserve">6.82652616500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68486022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81767129898071</t>
   </si>
   <si>
     <t xml:space="preserve">6.90621328353882</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01688957214355</t>
+    <t xml:space="preserve">7.01689052581787</t>
   </si>
   <si>
     <t xml:space="preserve">6.89735841751099</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83538007736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86194276809692</t>
+    <t xml:space="preserve">6.8353796005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86194324493408</t>
   </si>
   <si>
     <t xml:space="preserve">6.92392158508301</t>
@@ -464,16 +464,16 @@
     <t xml:space="preserve">6.97704648971558</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00360822677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91506719589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91949367523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93720293045044</t>
+    <t xml:space="preserve">7.00360774993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91506767272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91949510574341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93720197677612</t>
   </si>
   <si>
     <t xml:space="preserve">7.07001447677612</t>
@@ -488,13 +488,13 @@
     <t xml:space="preserve">6.77782821655273</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64944362640381</t>
+    <t xml:space="preserve">6.64944410324097</t>
   </si>
   <si>
     <t xml:space="preserve">6.38382005691528</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37053918838501</t>
+    <t xml:space="preserve">6.37053966522217</t>
   </si>
   <si>
     <t xml:space="preserve">6.36168479919434</t>
@@ -503,22 +503,22 @@
     <t xml:space="preserve">6.37939357757568</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40595531463623</t>
+    <t xml:space="preserve">6.40595579147339</t>
   </si>
   <si>
     <t xml:space="preserve">6.48121500015259</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47678852081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54319381713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46350765228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24215459823608</t>
+    <t xml:space="preserve">6.47678899765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54319524765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46350717544556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24215412139893</t>
   </si>
   <si>
     <t xml:space="preserve">6.25986194610596</t>
@@ -527,10 +527,10 @@
     <t xml:space="preserve">6.22444629669189</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64501714706421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64058971405029</t>
+    <t xml:space="preserve">6.64501667022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64059019088745</t>
   </si>
   <si>
     <t xml:space="preserve">7.03902435302734</t>
@@ -539,70 +539,70 @@
     <t xml:space="preserve">6.79111003875732</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70256805419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70699501037598</t>
+    <t xml:space="preserve">6.70256853103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70699596405029</t>
   </si>
   <si>
     <t xml:space="preserve">6.65829801559448</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58303785324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05673265457153</t>
+    <t xml:space="preserve">6.58303737640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05673313140869</t>
   </si>
   <si>
     <t xml:space="preserve">7.11428499221802</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34891939163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18511819839478</t>
+    <t xml:space="preserve">7.34891891479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18511772155762</t>
   </si>
   <si>
     <t xml:space="preserve">7.12756681442261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19397115707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24267053604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41089868545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48173093795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14527368545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27365970611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1762638092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04787874221802</t>
+    <t xml:space="preserve">7.19397211074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24266958236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41089820861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48173141479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14527416229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27365922927856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17626333236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04787969589233</t>
   </si>
   <si>
     <t xml:space="preserve">7.23381567001343</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29136610031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42860698699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83589506149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82704305648804</t>
+    <t xml:space="preserve">7.2913670539856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42860555648804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83589696884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82704257965088</t>
   </si>
   <si>
     <t xml:space="preserve">8.13693523406982</t>
@@ -626,67 +626,67 @@
     <t xml:space="preserve">8.26089286804199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92495059967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58849620819092</t>
+    <t xml:space="preserve">8.92495250701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58849716186523</t>
   </si>
   <si>
     <t xml:space="preserve">8.97807788848877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76557731628418</t>
+    <t xml:space="preserve">8.76557636260986</t>
   </si>
   <si>
     <t xml:space="preserve">8.87182807922363</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56244850158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25255298614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02234840393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8541202545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82755947113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71245288848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98693084716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8983907699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80984878540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72130870819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78328704833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67703723907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75672340393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10203456878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82312965393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94266128540039</t>
+    <t xml:space="preserve">9.56244945526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25255393981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02234649658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85412120819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82755851745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71245384216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9869327545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89838981628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80984687805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72130966186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78328609466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67703628540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75672435760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1020336151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82313060760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94266033172607</t>
   </si>
   <si>
     <t xml:space="preserve">9.20828247070312</t>
@@ -698,7 +698,7 @@
     <t xml:space="preserve">9.4598274230957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52271366119385</t>
+    <t xml:space="preserve">9.52271461486816</t>
   </si>
   <si>
     <t xml:space="preserve">9.32507228851318</t>
@@ -707,10 +707,10 @@
     <t xml:space="preserve">9.38795757293701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35202407836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42389392852783</t>
+    <t xml:space="preserve">9.35202217102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4238920211792</t>
   </si>
   <si>
     <t xml:space="preserve">9.29812049865723</t>
@@ -719,22 +719,22 @@
     <t xml:space="preserve">9.55864810943604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67543792724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86409282684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5199031829834</t>
+    <t xml:space="preserve">9.67543506622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86409473419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5199022293091</t>
   </si>
   <si>
     <t xml:space="preserve">10.0617351531982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88206005096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74730777740479</t>
+    <t xml:space="preserve">9.88206100463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74730587005615</t>
   </si>
   <si>
     <t xml:space="preserve">9.56763172149658</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">9.44186019897461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54068088531494</t>
+    <t xml:space="preserve">9.54068183898926</t>
   </si>
   <si>
     <t xml:space="preserve">9.34304046630859</t>
@@ -755,73 +755,73 @@
     <t xml:space="preserve">9.50474548339844</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48677825927734</t>
+    <t xml:space="preserve">9.48677921295166</t>
   </si>
   <si>
     <t xml:space="preserve">9.61254978179932</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77425670623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46881103515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5496654510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47779560089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7023868560791</t>
+    <t xml:space="preserve">9.77425765991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46881008148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54966354370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4777946472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70238876342773</t>
   </si>
   <si>
     <t xml:space="preserve">9.30710411071777</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28015422821045</t>
+    <t xml:space="preserve">9.28015327453613</t>
   </si>
   <si>
     <t xml:space="preserve">9.2172679901123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16336441040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25320434570312</t>
+    <t xml:space="preserve">9.16336631774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25320243835449</t>
   </si>
   <si>
     <t xml:space="preserve">9.45084476470947</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58559989929199</t>
+    <t xml:space="preserve">9.58559894561768</t>
   </si>
   <si>
     <t xml:space="preserve">9.33405685424805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59458255767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66645240783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71137142181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40592479705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26218700408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2711706161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.289137840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36999130249023</t>
+    <t xml:space="preserve">9.59458351135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66645336151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71137046813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40592670440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26218509674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27116966247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28913879394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3699893951416</t>
   </si>
   <si>
     <t xml:space="preserve">9.65746879577637</t>
@@ -830,37 +830,37 @@
     <t xml:space="preserve">9.79222393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76527404785156</t>
+    <t xml:space="preserve">9.76527214050293</t>
   </si>
   <si>
     <t xml:space="preserve">9.7203540802002</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81019115447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37897396087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.909010887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81917572021484</t>
+    <t xml:space="preserve">9.8101921081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37897300720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90901184082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81917476654053</t>
   </si>
   <si>
     <t xml:space="preserve">9.73832225799561</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78324222564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69340419769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11844825744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08251190185547</t>
+    <t xml:space="preserve">9.78323936462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69340324401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11844635009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08251285552979</t>
   </si>
   <si>
     <t xml:space="preserve">9.31608772277832</t>
@@ -872,22 +872,22 @@
     <t xml:space="preserve">9.10048007965088</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22625160217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41490936279297</t>
+    <t xml:space="preserve">9.22625064849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41490840911865</t>
   </si>
   <si>
     <t xml:space="preserve">9.39694213867188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07353019714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57661628723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68441963195801</t>
+    <t xml:space="preserve">9.07352924346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57661533355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68442058563232</t>
   </si>
   <si>
     <t xml:space="preserve">9.09149646759033</t>
@@ -896,7 +896,7 @@
     <t xml:space="preserve">9.05556201934814</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14540004730225</t>
+    <t xml:space="preserve">9.14539909362793</t>
   </si>
   <si>
     <t xml:space="preserve">8.89385414123535</t>
@@ -905,31 +905,31 @@
     <t xml:space="preserve">9.10946464538574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23523426055908</t>
+    <t xml:space="preserve">9.2352352142334</t>
   </si>
   <si>
     <t xml:space="preserve">9.95393085479736</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5109186172485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.74449634552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5468549728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6905927658081</t>
+    <t xml:space="preserve">10.5109205245972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7444953918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5468530654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6905937194824</t>
   </si>
   <si>
     <t xml:space="preserve">10.9062013626099</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7804307937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7085618972778</t>
+    <t xml:space="preserve">10.7804298400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7085609436035</t>
   </si>
   <si>
     <t xml:space="preserve">10.6546583175659</t>
@@ -938,10 +938,10 @@
     <t xml:space="preserve">10.5288877487183</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4390506744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3312454223633</t>
+    <t xml:space="preserve">10.4390487670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3312463760376</t>
   </si>
   <si>
     <t xml:space="preserve">10.1695394515991</t>
@@ -953,7 +953,7 @@
     <t xml:space="preserve">10.1336030960083</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7562894821167</t>
+    <t xml:space="preserve">9.75629043579102</t>
   </si>
   <si>
     <t xml:space="preserve">9.63051700592041</t>
@@ -962,49 +962,49 @@
     <t xml:space="preserve">10.0078344345093</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84612560272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0976715087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2054738998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2773418426514</t>
+    <t xml:space="preserve">9.8461275100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0976705551147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.205472946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.27734375</t>
   </si>
   <si>
     <t xml:space="preserve">10.2234420776367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2414093017578</t>
+    <t xml:space="preserve">10.2414083480835</t>
   </si>
   <si>
     <t xml:space="preserve">10.7624626159668</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2593746185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91799545288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9000301361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67380523681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74667835235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87420654296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1656942367554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85598754882812</t>
+    <t xml:space="preserve">10.2593765258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91799640655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90002918243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67380714416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74667930603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87420558929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1656951904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85598659515381</t>
   </si>
   <si>
     <t xml:space="preserve">9.63737010955811</t>
@@ -1013,73 +1013,73 @@
     <t xml:space="preserve">9.47340774536133</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76489639282227</t>
+    <t xml:space="preserve">9.76489734649658</t>
   </si>
   <si>
     <t xml:space="preserve">9.96529579162598</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0746059417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2385683059692</t>
+    <t xml:space="preserve">10.0746049880981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2385663986206</t>
   </si>
   <si>
     <t xml:space="preserve">10.3843126296997</t>
   </si>
   <si>
-    <t xml:space="preserve">10.420747756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8033275604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6940202713013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6211462020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7851114273071</t>
+    <t xml:space="preserve">10.4207487106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8033266067505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.694019317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.621148109436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7851095199585</t>
   </si>
   <si>
     <t xml:space="preserve">10.5482749938965</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4025297164917</t>
+    <t xml:space="preserve">10.402530670166</t>
   </si>
   <si>
     <t xml:space="preserve">10.2203493118286</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1474771499634</t>
+    <t xml:space="preserve">10.1474781036377</t>
   </si>
   <si>
     <t xml:space="preserve">10.3296575546265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5847101211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3478755950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72846031188965</t>
+    <t xml:space="preserve">10.5847110748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3478746414185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72846221923828</t>
   </si>
   <si>
     <t xml:space="preserve">9.56449890136719</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41875457763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40053558349609</t>
+    <t xml:space="preserve">9.4187536239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40053462982178</t>
   </si>
   <si>
     <t xml:space="preserve">9.54627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1110410690308</t>
+    <t xml:space="preserve">10.1110401153564</t>
   </si>
   <si>
     <t xml:space="preserve">10.2567853927612</t>
@@ -1091,31 +1091,31 @@
     <t xml:space="preserve">10.0199499130249</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2021322250366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0928220748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80133438110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69202327728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83776950836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94707679748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89242362976074</t>
+    <t xml:space="preserve">10.2021293640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0928230285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8013334274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69202613830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83777046203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94707775115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89242458343506</t>
   </si>
   <si>
     <t xml:space="preserve">9.65558910369873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78311538696289</t>
+    <t xml:space="preserve">9.78311443328857</t>
   </si>
   <si>
     <t xml:space="preserve">9.91064167022705</t>
@@ -1124,49 +1124,49 @@
     <t xml:space="preserve">9.4551887512207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2001371383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50984287261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43697166442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81955146789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49162578582764</t>
+    <t xml:space="preserve">9.20013618469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50984382629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43697071075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81955051422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49162673950195</t>
   </si>
   <si>
     <t xml:space="preserve">9.6191520690918</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9835147857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6009349822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10904502868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09993743896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3823184967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36409854888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27300930023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71024227142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58271598815918</t>
+    <t xml:space="preserve">9.98351383209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60093402862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10904598236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09993648529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38231563568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36409759521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27300834655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71024322509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5827169418335</t>
   </si>
   <si>
     <t xml:space="preserve">9.29122638702393</t>
@@ -1178,52 +1178,52 @@
     <t xml:space="preserve">10.3660945892334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32766342163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0017318725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4754028320312</t>
+    <t xml:space="preserve">9.32766246795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0017328262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4754037857056</t>
   </si>
   <si>
     <t xml:space="preserve">10.8397645950317</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5664939880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3114404678345</t>
+    <t xml:space="preserve">10.5664930343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3114395141602</t>
   </si>
   <si>
     <t xml:space="preserve">10.2932224273682</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0381689071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0563869476318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1292581558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2750034332275</t>
+    <t xml:space="preserve">10.0381679534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0563850402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1292591094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2750024795532</t>
   </si>
   <si>
     <t xml:space="preserve">10.183913230896</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6758012771606</t>
+    <t xml:space="preserve">10.6758031845093</t>
   </si>
   <si>
     <t xml:space="preserve">10.7122383117676</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9308557510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0219459533691</t>
+    <t xml:space="preserve">10.9308547973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0219440460205</t>
   </si>
   <si>
     <t xml:space="preserve">10.8762006759644</t>
@@ -1238,10 +1238,10 @@
     <t xml:space="preserve">10.6575832366943</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2644634246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1349868774414</t>
+    <t xml:space="preserve">11.2644643783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1349859237671</t>
   </si>
   <si>
     <t xml:space="preserve">11.0979928970337</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">11.2459669113159</t>
   </si>
   <si>
-    <t xml:space="preserve">11.319953918457</t>
+    <t xml:space="preserve">11.3199520111084</t>
   </si>
   <si>
     <t xml:space="preserve">11.0240068435669</t>
@@ -1259,22 +1259,22 @@
     <t xml:space="preserve">10.8205432891846</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8390407562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7280616760254</t>
+    <t xml:space="preserve">10.8390417098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7280607223511</t>
   </si>
   <si>
     <t xml:space="preserve">10.857536315918</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7095632553101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6725702285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6540746688843</t>
+    <t xml:space="preserve">10.7095642089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.672571182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.65407371521</t>
   </si>
   <si>
     <t xml:space="preserve">10.7835502624512</t>
@@ -1286,10 +1286,10 @@
     <t xml:space="preserve">10.8020477294922</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5615901947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6170797348022</t>
+    <t xml:space="preserve">10.5615911483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6170806884766</t>
   </si>
   <si>
     <t xml:space="preserve">10.3951206207275</t>
@@ -1298,25 +1298,25 @@
     <t xml:space="preserve">10.1176710128784</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2841396331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2656440734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.302638053894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5061006546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3396310806274</t>
+    <t xml:space="preserve">10.2841415405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.265643119812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3026371002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5060997009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3396301269531</t>
   </si>
   <si>
     <t xml:space="preserve">10.1361675262451</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0806760787964</t>
+    <t xml:space="preserve">10.0806770324707</t>
   </si>
   <si>
     <t xml:space="preserve">9.98819446563721</t>
@@ -1325,7 +1325,7 @@
     <t xml:space="preserve">10.0991735458374</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93270301818848</t>
+    <t xml:space="preserve">9.93270397186279</t>
   </si>
   <si>
     <t xml:space="preserve">9.89571094512939</t>
@@ -1334,10 +1334,10 @@
     <t xml:space="preserve">9.96969699859619</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1731595993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0621795654297</t>
+    <t xml:space="preserve">10.1731605529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0621814727783</t>
   </si>
   <si>
     <t xml:space="preserve">10.1546640396118</t>
@@ -1346,55 +1346,55 @@
     <t xml:space="preserve">9.71074485778809</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0251874923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91420841217041</t>
+    <t xml:space="preserve">10.0251865386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91420745849609</t>
   </si>
   <si>
     <t xml:space="preserve">9.76623439788818</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72924041748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65525341033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67374992370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47028636932373</t>
+    <t xml:space="preserve">9.7292423248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65525436401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67375087738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47028732299805</t>
   </si>
   <si>
     <t xml:space="preserve">9.54427337646484</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56277179718018</t>
+    <t xml:space="preserve">9.56277084350586</t>
   </si>
   <si>
     <t xml:space="preserve">9.45179176330566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35930824279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52577781677246</t>
+    <t xml:space="preserve">9.35930728912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52577590942383</t>
   </si>
   <si>
     <t xml:space="preserve">9.59976387023926</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61826133728027</t>
+    <t xml:space="preserve">9.61826229095459</t>
   </si>
   <si>
     <t xml:space="preserve">9.69224739074707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80322647094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2286510467529</t>
+    <t xml:space="preserve">9.80322933197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2286500930786</t>
   </si>
   <si>
     <t xml:space="preserve">9.78473091125488</t>
@@ -1403,13 +1403,13 @@
     <t xml:space="preserve">9.85871696472168</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0066909790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87721347808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7477388381958</t>
+    <t xml:space="preserve">10.0066900253296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8772144317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74773693084717</t>
   </si>
   <si>
     <t xml:space="preserve">9.58126735687256</t>
@@ -1418,13 +1418,13 @@
     <t xml:space="preserve">10.3211336135864</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4321146011353</t>
+    <t xml:space="preserve">10.4321126937866</t>
   </si>
   <si>
     <t xml:space="preserve">10.3766241073608</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2471466064453</t>
+    <t xml:space="preserve">10.2471475601196</t>
   </si>
   <si>
     <t xml:space="preserve">10.2101535797119</t>
@@ -1436,22 +1436,22 @@
     <t xml:space="preserve">9.63675785064697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43329429626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41479873657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39629936218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24832820892334</t>
+    <t xml:space="preserve">9.43329334259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41479778289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39630031585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24832725524902</t>
   </si>
   <si>
     <t xml:space="preserve">9.06336116790771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10960388183594</t>
+    <t xml:space="preserve">9.1096019744873</t>
   </si>
   <si>
     <t xml:space="preserve">9.32231426239014</t>
@@ -1466,7 +1466,7 @@
     <t xml:space="preserve">9.19283676147461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22983169555664</t>
+    <t xml:space="preserve">9.22982978820801</t>
   </si>
   <si>
     <t xml:space="preserve">9.48878479003906</t>
@@ -1475,19 +1475,19 @@
     <t xml:space="preserve">9.02636814117432</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97087955474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13734817504883</t>
+    <t xml:space="preserve">8.9708776473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13734912872314</t>
   </si>
   <si>
     <t xml:space="preserve">8.96162891387939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82290458679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61944198608398</t>
+    <t xml:space="preserve">8.82290649414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61944103240967</t>
   </si>
   <si>
     <t xml:space="preserve">8.55470371246338</t>
@@ -1496,10 +1496,10 @@
     <t xml:space="preserve">8.36048889160156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33274364471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01830005645752</t>
+    <t xml:space="preserve">8.33274459838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01830101013184</t>
   </si>
   <si>
     <t xml:space="preserve">7.81483745574951</t>
@@ -1508,31 +1508,31 @@
     <t xml:space="preserve">7.95356225967407</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49114608764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86107873916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50964307785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53738641738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58362865447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76741504669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9893741607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16509246826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12809944152832</t>
+    <t xml:space="preserve">7.49114561080933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86107921600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50964164733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53738689422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58362913131714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76741409301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98937511444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16509342193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.128098487854</t>
   </si>
   <si>
     <t xml:space="preserve">9.09110641479492</t>
@@ -1544,16 +1544,16 @@
     <t xml:space="preserve">9.34081172943115</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04486560821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21133518218994</t>
+    <t xml:space="preserve">9.04486465454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21133422851562</t>
   </si>
   <si>
     <t xml:space="preserve">9.38705253601074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17434215545654</t>
+    <t xml:space="preserve">9.17434120178223</t>
   </si>
   <si>
     <t xml:space="preserve">9.29456901550293</t>
@@ -1562,37 +1562,37 @@
     <t xml:space="preserve">9.11885166168213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78591060638428</t>
+    <t xml:space="preserve">8.78591251373291</t>
   </si>
   <si>
     <t xml:space="preserve">8.89689064025879</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74891757965088</t>
+    <t xml:space="preserve">8.7489185333252</t>
   </si>
   <si>
     <t xml:space="preserve">8.80440807342529</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87839508056641</t>
+    <t xml:space="preserve">8.87839603424072</t>
   </si>
   <si>
     <t xml:space="preserve">8.9338846206665</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63793849945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71192455291748</t>
+    <t xml:space="preserve">8.63793754577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71192646026611</t>
   </si>
   <si>
     <t xml:space="preserve">8.58244800567627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69342708587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46113872528076</t>
+    <t xml:space="preserve">8.69342803955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46113967895508</t>
   </si>
   <si>
     <t xml:space="preserve">9.64942073822021</t>
@@ -1601,10 +1601,10 @@
     <t xml:space="preserve">9.69649124145508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74356174468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97891235351562</t>
+    <t xml:space="preserve">9.74356079101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97891330718994</t>
   </si>
   <si>
     <t xml:space="preserve">9.93184280395508</t>
@@ -1616,22 +1616,22 @@
     <t xml:space="preserve">10.0730533599854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3084058761597</t>
+    <t xml:space="preserve">10.3084049224854</t>
   </si>
   <si>
     <t xml:space="preserve">10.4496164321899</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1671943664551</t>
+    <t xml:space="preserve">10.1671953201294</t>
   </si>
   <si>
     <t xml:space="preserve">10.1201238632202</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0259838104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2142658233643</t>
+    <t xml:space="preserve">10.0259828567505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2142639160156</t>
   </si>
   <si>
     <t xml:space="preserve">10.3554744720459</t>
@@ -1640,13 +1640,13 @@
     <t xml:space="preserve">10.2613334655762</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88477230072021</t>
+    <t xml:space="preserve">9.8847713470459</t>
   </si>
   <si>
     <t xml:space="preserve">10.5908279418945</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4966869354248</t>
+    <t xml:space="preserve">10.4966878890991</t>
   </si>
   <si>
     <t xml:space="preserve">10.5437574386597</t>
@@ -1658,37 +1658,37 @@
     <t xml:space="preserve">11.1556711196899</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9673891067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0615301132202</t>
+    <t xml:space="preserve">10.9673900604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0615310668945</t>
   </si>
   <si>
     <t xml:space="preserve">10.7791080474854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8261795043945</t>
+    <t xml:space="preserve">10.8261785507202</t>
   </si>
   <si>
     <t xml:space="preserve">11.0144605636597</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1086015701294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9203214645386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8732481002808</t>
+    <t xml:space="preserve">11.1086025238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9203205108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8732500076294</t>
   </si>
   <si>
     <t xml:space="preserve">10.7320384979248</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6378974914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5322341918945</t>
+    <t xml:space="preserve">10.6378984451294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5322351455688</t>
   </si>
   <si>
     <t xml:space="preserve">11.6263751983643</t>
@@ -1697,13 +1697,13 @@
     <t xml:space="preserve">11.7675857543945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8146572113037</t>
+    <t xml:space="preserve">11.8146562576294</t>
   </si>
   <si>
     <t xml:space="preserve">11.5793046951294</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6734457015991</t>
+    <t xml:space="preserve">11.6734447479248</t>
   </si>
   <si>
     <t xml:space="preserve">11.7205152511597</t>
@@ -1715,46 +1715,46 @@
     <t xml:space="preserve">12.2853593826294</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5677824020386</t>
+    <t xml:space="preserve">12.5677814483643</t>
   </si>
   <si>
     <t xml:space="preserve">12.5207118988037</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8972730636597</t>
+    <t xml:space="preserve">12.897274017334</t>
   </si>
   <si>
     <t xml:space="preserve">12.7560634613037</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6619215011597</t>
+    <t xml:space="preserve">12.661922454834</t>
   </si>
   <si>
     <t xml:space="preserve">12.6148519515991</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8031330108643</t>
+    <t xml:space="preserve">12.8031339645386</t>
   </si>
   <si>
     <t xml:space="preserve">12.8502044677734</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9914140701294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1796951293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.462119102478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8386812210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7445421218872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6504001617432</t>
+    <t xml:space="preserve">12.991415977478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1796970367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4621181488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.838680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7445411682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6503992080688</t>
   </si>
   <si>
     <t xml:space="preserve">13.5091886520386</t>
@@ -1766,25 +1766,25 @@
     <t xml:space="preserve">13.8857517242432</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9798927307129</t>
+    <t xml:space="preserve">13.9798917770386</t>
   </si>
   <si>
     <t xml:space="preserve">14.0269613265991</t>
   </si>
   <si>
-    <t xml:space="preserve">14.074031829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.168173789978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1211032867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2623128890991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2152433395386</t>
+    <t xml:space="preserve">14.0740308761597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1681728363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1211023330688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2623138427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2152442932129</t>
   </si>
   <si>
     <t xml:space="preserve">14.4505958557129</t>
@@ -1793,16 +1793,16 @@
     <t xml:space="preserve">14.6859474182129</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3093843460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.403525352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3564548492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5447359085083</t>
+    <t xml:space="preserve">14.3093852996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4035263061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3564558029175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5447368621826</t>
   </si>
   <si>
     <t xml:space="preserve">14.5918064117432</t>
@@ -1811,22 +1811,22 @@
     <t xml:space="preserve">14.638876914978</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7800874710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8271579742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8742294311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7330169677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3449306488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7685642242432</t>
+    <t xml:space="preserve">14.7800884246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8271589279175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.874228477478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7330179214478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.344931602478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7685661315918</t>
   </si>
   <si>
     <t xml:space="preserve">16.0039176940918</t>
@@ -1838,111 +1838,114 @@
     <t xml:space="preserve">16.0792293548584</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1921997070312</t>
+    <t xml:space="preserve">16.1921977996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1168880462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2298545837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3804798126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3993072509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4181346893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5311050415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2675113677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9286060333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8909492492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8156328201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9662590026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7214956283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5332126617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5143852233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7026681900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2696199417114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4767293930054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.683837890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6650085449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4202442169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1566514968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2319641113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7779769897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9833717346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.964301109314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6209812164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4874696731567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7926406860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8117151260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6019096374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5446872711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2585887908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6972742080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8307876586914</t>
   </si>
   <si>
     <t xml:space="preserve">16.116886138916</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2298526763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3804798126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3993053436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4181365966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5311031341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2675132751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9286050796509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8909473419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.815634727478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9662609100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7214956283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5332145690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5143852233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7026662826538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2696180343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4767303466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6838369369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6650114059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4202432632446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1566524505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2319631576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7779788970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9833726882935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.964301109314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6209812164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4874696731567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7926397323608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8117141723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6019077301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5446872711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2585897445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6972732543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8307867050171</t>
-  </si>
-  <si>
     <t xml:space="preserve">16.2503986358643</t>
   </si>
   <si>
@@ -1955,19 +1958,19 @@
     <t xml:space="preserve">16.2694702148438</t>
   </si>
   <si>
-    <t xml:space="preserve">16.212251663208</t>
+    <t xml:space="preserve">16.2122535705566</t>
   </si>
   <si>
     <t xml:space="preserve">16.460205078125</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4411296844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5364952087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5555725097656</t>
+    <t xml:space="preserve">16.4411315917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5364971160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.555570602417</t>
   </si>
   <si>
     <t xml:space="preserve">17.1659145355225</t>
@@ -1976,13 +1979,13 @@
     <t xml:space="preserve">16.9561080932617</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2231330871582</t>
+    <t xml:space="preserve">17.2231349945068</t>
   </si>
   <si>
     <t xml:space="preserve">17.3185005187988</t>
   </si>
   <si>
-    <t xml:space="preserve">17.08962059021</t>
+    <t xml:space="preserve">17.0896224975586</t>
   </si>
   <si>
     <t xml:space="preserve">16.8416690826416</t>
@@ -2003,22 +2006,22 @@
     <t xml:space="preserve">17.5473785400391</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7571849822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6427459716797</t>
+    <t xml:space="preserve">17.7571830749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6427440643311</t>
   </si>
   <si>
     <t xml:space="preserve">17.7381114959717</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4901580810547</t>
+    <t xml:space="preserve">17.4901599884033</t>
   </si>
   <si>
     <t xml:space="preserve">17.4710865020752</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3375720977783</t>
+    <t xml:space="preserve">17.337574005127</t>
   </si>
   <si>
     <t xml:space="preserve">17.2994251251221</t>
@@ -2030,19 +2033,19 @@
     <t xml:space="preserve">17.2422065734863</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1468372344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0133285522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4520130157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8334789276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6999626159668</t>
+    <t xml:space="preserve">17.1468391418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0133266448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4520111083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8334770202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6999645233154</t>
   </si>
   <si>
     <t xml:space="preserve">17.8716239929199</t>
@@ -2051,10 +2054,10 @@
     <t xml:space="preserve">17.8525505065918</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0242118835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4247493743896</t>
+    <t xml:space="preserve">18.0242080688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4247455596924</t>
   </si>
   <si>
     <t xml:space="preserve">18.5010414123535</t>
@@ -2066,31 +2069,31 @@
     <t xml:space="preserve">18.5964069366455</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5582599639893</t>
+    <t xml:space="preserve">18.5582580566406</t>
   </si>
   <si>
     <t xml:space="preserve">18.7108478546143</t>
   </si>
   <si>
-    <t xml:space="preserve">18.806209564209</t>
+    <t xml:space="preserve">18.8062114715576</t>
   </si>
   <si>
     <t xml:space="preserve">18.520112991333</t>
   </si>
   <si>
-    <t xml:space="preserve">19.55006980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5023880004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8838520050049</t>
+    <t xml:space="preserve">19.5500679016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5023860931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8838500976562</t>
   </si>
   <si>
     <t xml:space="preserve">19.9792175292969</t>
   </si>
   <si>
-    <t xml:space="preserve">19.454704284668</t>
+    <t xml:space="preserve">19.4547023773193</t>
   </si>
   <si>
     <t xml:space="preserve">19.3593349456787</t>
@@ -2105,16 +2108,16 @@
     <t xml:space="preserve">18.6917743682861</t>
   </si>
   <si>
-    <t xml:space="preserve">19.216287612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1209201812744</t>
+    <t xml:space="preserve">19.2162837982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1209182739258</t>
   </si>
   <si>
     <t xml:space="preserve">18.7680644989014</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9097709655762</t>
+    <t xml:space="preserve">17.9097690582275</t>
   </si>
   <si>
     <t xml:space="preserve">18.1195755004883</t>
@@ -2123,25 +2126,25 @@
     <t xml:space="preserve">17.6236705780029</t>
   </si>
   <si>
-    <t xml:space="preserve">17.890697479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1005001068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2530860900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9669876098633</t>
+    <t xml:space="preserve">17.8906955718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1005020141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2530879974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9669895172119</t>
   </si>
   <si>
     <t xml:space="preserve">18.176794052124</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9969444274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0732383728027</t>
+    <t xml:space="preserve">18.9969463348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0732364654541</t>
   </si>
   <si>
     <t xml:space="preserve">18.9778728485107</t>
@@ -2153,10 +2156,10 @@
     <t xml:space="preserve">18.9397258758545</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9015789031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0268993377686</t>
+    <t xml:space="preserve">18.9015769958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0268974304199</t>
   </si>
   <si>
     <t xml:space="preserve">20.2176322937012</t>
@@ -2165,7 +2168,7 @@
     <t xml:space="preserve">20.2653160095215</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7421474456787</t>
+    <t xml:space="preserve">20.7421455383301</t>
   </si>
   <si>
     <t xml:space="preserve">20.9328804016113</t>
@@ -2177,22 +2180,22 @@
     <t xml:space="preserve">21.4573917388916</t>
   </si>
   <si>
-    <t xml:space="preserve">20.694465637207</t>
+    <t xml:space="preserve">20.6944618225098</t>
   </si>
   <si>
     <t xml:space="preserve">20.3129978179932</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4560489654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.980562210083</t>
+    <t xml:space="preserve">20.4560508728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9805603027344</t>
   </si>
   <si>
     <t xml:space="preserve">19.8361663818359</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4083652496338</t>
+    <t xml:space="preserve">20.4083633422852</t>
   </si>
   <si>
     <t xml:space="preserve">20.1222667694092</t>
@@ -2201,19 +2204,19 @@
     <t xml:space="preserve">19.311653137207</t>
   </si>
   <si>
-    <t xml:space="preserve">19.263973236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5977516174316</t>
+    <t xml:space="preserve">19.2639694213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.597749710083</t>
   </si>
   <si>
     <t xml:space="preserve">19.645435333252</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1699504852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9315338134766</t>
+    <t xml:space="preserve">20.1699485778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9315319061279</t>
   </si>
   <si>
     <t xml:space="preserve">19.7408027648926</t>
@@ -2222,22 +2225,22 @@
     <t xml:space="preserve">18.8443603515625</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0160160064697</t>
+    <t xml:space="preserve">19.016019821167</t>
   </si>
   <si>
     <t xml:space="preserve">18.0432834625244</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0051364898682</t>
+    <t xml:space="preserve">18.0051345825195</t>
   </si>
   <si>
     <t xml:space="preserve">18.1386489868164</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0623550415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.081428527832</t>
+    <t xml:space="preserve">18.0623569488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0814266204834</t>
   </si>
   <si>
     <t xml:space="preserve">17.6045989990234</t>
@@ -2252,13 +2255,13 @@
     <t xml:space="preserve">16.2885437011719</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0324039459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7272281646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4792785644531</t>
+    <t xml:space="preserve">17.0324020385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7272300720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4792766571045</t>
   </si>
   <si>
     <t xml:space="preserve">16.8225936889648</t>
@@ -2267,52 +2270,52 @@
     <t xml:space="preserve">17.0705490112305</t>
   </si>
   <si>
-    <t xml:space="preserve">16.650936126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8607406616211</t>
+    <t xml:space="preserve">16.6509342193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8607425689697</t>
   </si>
   <si>
     <t xml:space="preserve">16.3076171875</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5937194824219</t>
+    <t xml:space="preserve">16.5937175750732</t>
   </si>
   <si>
     <t xml:space="preserve">16.6318626403809</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2776641845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8771266937256</t>
+    <t xml:space="preserve">15.277663230896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8771257400513</t>
   </si>
   <si>
     <t xml:space="preserve">14.495659828186</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3730316162109</t>
+    <t xml:space="preserve">15.3730306625366</t>
   </si>
   <si>
     <t xml:space="preserve">14.9915647506714</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0869312286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6782007217407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1441497802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9452266693115</t>
+    <t xml:space="preserve">15.0869302749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.678201675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1441507339478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9452276229858</t>
   </si>
   <si>
     <t xml:space="preserve">16.0787410736084</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0405941009521</t>
+    <t xml:space="preserve">16.0405921936035</t>
   </si>
   <si>
     <t xml:space="preserve">16.5746421813965</t>
@@ -2321,22 +2324,22 @@
     <t xml:space="preserve">16.6890830993652</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5174236297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4983501434326</t>
+    <t xml:space="preserve">16.5174217224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.498348236084</t>
   </si>
   <si>
     <t xml:space="preserve">15.7354202270508</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8880052566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5065422058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9724912643433</t>
+    <t xml:space="preserve">15.8880062103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5065412521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9724922180176</t>
   </si>
   <si>
     <t xml:space="preserve">15.3348827362061</t>
@@ -2345,7 +2348,7 @@
     <t xml:space="preserve">15.2204427719116</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9152727127075</t>
+    <t xml:space="preserve">14.9152717590332</t>
   </si>
   <si>
     <t xml:space="preserve">14.781759262085</t>
@@ -2354,10 +2357,10 @@
     <t xml:space="preserve">14.8961992263794</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6400556564331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0978107452393</t>
+    <t xml:space="preserve">15.6400547027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0978126525879</t>
   </si>
   <si>
     <t xml:space="preserve">15.2395162582397</t>
@@ -2366,13 +2369,13 @@
     <t xml:space="preserve">15.1060047149658</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0063896179199</t>
+    <t xml:space="preserve">16.0063877105713</t>
   </si>
   <si>
     <t xml:space="preserve">16.1999359130859</t>
   </si>
   <si>
-    <t xml:space="preserve">16.354772567749</t>
+    <t xml:space="preserve">16.3547744750977</t>
   </si>
   <si>
     <t xml:space="preserve">16.0450973510742</t>
@@ -2381,10 +2384,10 @@
     <t xml:space="preserve">16.1418704986572</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2773551940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4709014892578</t>
+    <t xml:space="preserve">16.2773532867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4709033966064</t>
   </si>
   <si>
     <t xml:space="preserve">16.7805767059326</t>
@@ -2396,43 +2399,43 @@
     <t xml:space="preserve">17.767671585083</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4192848205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2321834564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7289619445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9418640136719</t>
+    <t xml:space="preserve">17.419282913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2321853637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7289600372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9418659210205</t>
   </si>
   <si>
     <t xml:space="preserve">17.4967041015625</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5934772491455</t>
+    <t xml:space="preserve">17.5934791564941</t>
   </si>
   <si>
     <t xml:space="preserve">17.4579963684082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8967056274414</t>
+    <t xml:space="preserve">16.8967037200928</t>
   </si>
   <si>
     <t xml:space="preserve">16.4515476226807</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9870328903198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8321943283081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9483213424683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3676795959473</t>
+    <t xml:space="preserve">15.9870338439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8321962356567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9483232498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3676805496216</t>
   </si>
   <si>
     <t xml:space="preserve">15.4450988769531</t>
@@ -2444,19 +2447,19 @@
     <t xml:space="preserve">15.1160688400269</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1354236602783</t>
+    <t xml:space="preserve">15.135422706604</t>
   </si>
   <si>
     <t xml:space="preserve">15.3289709091187</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6192922592163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8902587890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7547760009766</t>
+    <t xml:space="preserve">15.619291305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8902597427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7547750473022</t>
   </si>
   <si>
     <t xml:space="preserve">15.8128395080566</t>
@@ -2468,16 +2471,13 @@
     <t xml:space="preserve">15.6580018997192</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8709049224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4128379821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4321918487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7354211807251</t>
+    <t xml:space="preserve">15.870903968811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4128360748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4321899414062</t>
   </si>
   <si>
     <t xml:space="preserve">15.7160663604736</t>
@@ -2486,13 +2486,13 @@
     <t xml:space="preserve">16.0644512176514</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5289649963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6838035583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5096092224121</t>
+    <t xml:space="preserve">16.5289669036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6838054656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5096111297607</t>
   </si>
   <si>
     <t xml:space="preserve">16.9160594940186</t>
@@ -2504,7 +2504,7 @@
     <t xml:space="preserve">17.3805732727051</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3418655395508</t>
+    <t xml:space="preserve">17.3418674468994</t>
   </si>
   <si>
     <t xml:space="preserve">17.2063827514648</t>
@@ -2513,31 +2513,31 @@
     <t xml:space="preserve">17.3225116729736</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2838039398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0515460968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.83864402771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2450923919678</t>
+    <t xml:space="preserve">17.2838020324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0515441894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8386421203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2450904846191</t>
   </si>
   <si>
     <t xml:space="preserve">17.6128330230713</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8192863464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1096076965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7225151062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1289653778076</t>
+    <t xml:space="preserve">16.8192882537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1096096038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7225131988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.128963470459</t>
   </si>
   <si>
     <t xml:space="preserve">16.8773517608643</t>
@@ -2579,13 +2579,13 @@
     <t xml:space="preserve">15.7741289138794</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6773557662964</t>
+    <t xml:space="preserve">15.677357673645</t>
   </si>
   <si>
     <t xml:space="preserve">15.5612277984619</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1805801391602</t>
+    <t xml:space="preserve">16.1805782318115</t>
   </si>
   <si>
     <t xml:space="preserve">16.8579978942871</t>
@@ -2594,22 +2594,22 @@
     <t xml:space="preserve">17.3031558990479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9031543731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8063793182373</t>
+    <t xml:space="preserve">17.9031524658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8063812255859</t>
   </si>
   <si>
     <t xml:space="preserve">17.1676731109619</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5160579681396</t>
+    <t xml:space="preserve">17.5160598754883</t>
   </si>
   <si>
     <t xml:space="preserve">17.3612194061279</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7354106903076</t>
+    <t xml:space="preserve">18.735408782959</t>
   </si>
   <si>
     <t xml:space="preserve">18.6579895019531</t>
@@ -2639,25 +2639,25 @@
     <t xml:space="preserve">18.2128295898438</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2902507781982</t>
+    <t xml:space="preserve">18.2902488708496</t>
   </si>
   <si>
     <t xml:space="preserve">18.1547660827637</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0192832946777</t>
+    <t xml:space="preserve">18.0192813873291</t>
   </si>
   <si>
     <t xml:space="preserve">17.9805736541748</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9612159729004</t>
+    <t xml:space="preserve">17.961217880249</t>
   </si>
   <si>
     <t xml:space="preserve">17.8450908660889</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6902542114258</t>
+    <t xml:space="preserve">17.6902523040771</t>
   </si>
   <si>
     <t xml:space="preserve">17.6321868896484</t>
@@ -2669,10 +2669,10 @@
     <t xml:space="preserve">17.4386405944824</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3999271392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2644481658936</t>
+    <t xml:space="preserve">17.3999290466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2644462585449</t>
   </si>
   <si>
     <t xml:space="preserve">17.7096061706543</t>
@@ -2681,46 +2681,46 @@
     <t xml:space="preserve">17.4773483276367</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8257331848145</t>
+    <t xml:space="preserve">17.8257369995117</t>
   </si>
   <si>
     <t xml:space="preserve">18.5805721282959</t>
   </si>
   <si>
-    <t xml:space="preserve">18.928955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8128261566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5483112335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9354038238525</t>
+    <t xml:space="preserve">18.9289569854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8128299713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5483093261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9354057312012</t>
   </si>
   <si>
     <t xml:space="preserve">19.7902450561523</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0321788787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7418575286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5966949462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9837913513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8386306762695</t>
+    <t xml:space="preserve">20.0321769714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7418556213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5966968536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9837894439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8386287689209</t>
   </si>
   <si>
     <t xml:space="preserve">20.0805644989014</t>
   </si>
   <si>
-    <t xml:space="preserve">20.370885848999</t>
+    <t xml:space="preserve">20.3708839416504</t>
   </si>
   <si>
     <t xml:space="preserve">19.8870162963867</t>
@@ -2729,46 +2729,46 @@
     <t xml:space="preserve">19.6450805664062</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1289501190186</t>
+    <t xml:space="preserve">20.1289520263672</t>
   </si>
   <si>
     <t xml:space="preserve">20.177339553833</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4192733764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4676609039307</t>
+    <t xml:space="preserve">20.4192752838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.467658996582</t>
   </si>
   <si>
     <t xml:space="preserve">21.2418518066406</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1934642791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4353981018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5805568695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6773338317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6289463043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0644264221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2579765319824</t>
+    <t xml:space="preserve">21.1934623718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.435396194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5805587768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6773319244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6289443969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0644283294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2579727172852</t>
   </si>
   <si>
     <t xml:space="preserve">22.6450710296631</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0321636199951</t>
+    <t xml:space="preserve">23.0321655273438</t>
   </si>
   <si>
     <t xml:space="preserve">23.4676475524902</t>
@@ -2780,10 +2780,10 @@
     <t xml:space="preserve">22.7902297973633</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7418441772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9676551818848</t>
+    <t xml:space="preserve">22.7418422698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9676532745361</t>
   </si>
   <si>
     <t xml:space="preserve">22.6934585571289</t>
@@ -2798,7 +2798,7 @@
     <t xml:space="preserve">21.8224925994873</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3547477722168</t>
+    <t xml:space="preserve">22.3547496795654</t>
   </si>
   <si>
     <t xml:space="preserve">22.112813949585</t>
@@ -2810,31 +2810,31 @@
     <t xml:space="preserve">22.9837779998779</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9031314849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1934509277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0966777801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0160293579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9676418304443</t>
+    <t xml:space="preserve">23.9031295776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.193452835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0966758728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0160312652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9676399230957</t>
   </si>
   <si>
     <t xml:space="preserve">25.4031238555908</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8386077880859</t>
+    <t xml:space="preserve">25.8386058807373</t>
   </si>
   <si>
     <t xml:space="preserve">25.9353790283203</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3547382354736</t>
+    <t xml:space="preserve">25.354736328125</t>
   </si>
   <si>
     <t xml:space="preserve">25.161190032959</t>
@@ -2849,7 +2849,7 @@
     <t xml:space="preserve">25.451509475708</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2095756530762</t>
+    <t xml:space="preserve">25.2095737457275</t>
   </si>
   <si>
     <t xml:space="preserve">25.5482845306396</t>
@@ -2864,22 +2864,22 @@
     <t xml:space="preserve">26.5160217285156</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9515037536621</t>
+    <t xml:space="preserve">26.9515056610107</t>
   </si>
   <si>
     <t xml:space="preserve">25.6934432983398</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5966739654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3063488006592</t>
+    <t xml:space="preserve">25.5966720581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3063507080078</t>
   </si>
   <si>
     <t xml:space="preserve">25.8869934082031</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3708610534668</t>
+    <t xml:space="preserve">26.3708629608154</t>
   </si>
   <si>
     <t xml:space="preserve">26.2043304443359</t>
@@ -2888,7 +2888,7 @@
     <t xml:space="preserve">25.616569519043</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1267681121826</t>
+    <t xml:space="preserve">25.1267700195312</t>
   </si>
   <si>
     <t xml:space="preserve">25.9594306945801</t>
@@ -2900,16 +2900,16 @@
     <t xml:space="preserve">25.2737083435059</t>
   </si>
   <si>
-    <t xml:space="preserve">25.02880859375</t>
+    <t xml:space="preserve">25.0288066864014</t>
   </si>
   <si>
     <t xml:space="preserve">25.2247295379639</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7349300384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.441047668457</t>
+    <t xml:space="preserve">24.7349281311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4410495758057</t>
   </si>
   <si>
     <t xml:space="preserve">24.8818683624268</t>
@@ -2924,10 +2924,10 @@
     <t xml:space="preserve">24.4900283813477</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7839069366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8328895568848</t>
+    <t xml:space="preserve">24.7839088439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8328876495361</t>
   </si>
   <si>
     <t xml:space="preserve">24.979829788208</t>
@@ -2936,19 +2936,19 @@
     <t xml:space="preserve">25.4696292877197</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9104518890381</t>
+    <t xml:space="preserve">25.9104499816895</t>
   </si>
   <si>
     <t xml:space="preserve">25.8614692687988</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7635078430176</t>
+    <t xml:space="preserve">25.7635097503662</t>
   </si>
   <si>
     <t xml:space="preserve">25.7145290374756</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2533111572266</t>
+    <t xml:space="preserve">26.2533092498779</t>
   </si>
   <si>
     <t xml:space="preserve">26.6941299438477</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">26.7920913696289</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5961685180664</t>
+    <t xml:space="preserve">26.596170425415</t>
   </si>
   <si>
     <t xml:space="preserve">26.4492301940918</t>
@@ -2990,7 +2990,7 @@
     <t xml:space="preserve">25.3716678619385</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1471672058105</t>
+    <t xml:space="preserve">24.1471691131592</t>
   </si>
   <si>
     <t xml:space="preserve">26.3512687683105</t>
@@ -3005,13 +3005,13 @@
     <t xml:space="preserve">26.9880104064941</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9390296936035</t>
+    <t xml:space="preserve">26.9390316009521</t>
   </si>
   <si>
     <t xml:space="preserve">26.0573902130127</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1063690185547</t>
+    <t xml:space="preserve">26.1063709259033</t>
   </si>
   <si>
     <t xml:space="preserve">26.6451511383057</t>
@@ -3026,40 +3026,40 @@
     <t xml:space="preserve">27.134952545166</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1553516387939</t>
+    <t xml:space="preserve">26.1553497314453</t>
   </si>
   <si>
     <t xml:space="preserve">27.3798522949219</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3308715820312</t>
+    <t xml:space="preserve">27.3308696746826</t>
   </si>
   <si>
     <t xml:space="preserve">27.7227115631104</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6737327575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0165939331055</t>
+    <t xml:space="preserve">27.6737308502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0165920257568</t>
   </si>
   <si>
     <t xml:space="preserve">27.5757713317871</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4778118133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5267906188965</t>
+    <t xml:space="preserve">27.4778099060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5267925262451</t>
   </si>
   <si>
     <t xml:space="preserve">25.8124904632568</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3022899627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2818908691406</t>
+    <t xml:space="preserve">26.3022918701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2818927764893</t>
   </si>
   <si>
     <t xml:space="preserve">27.4288330078125</t>
@@ -3068,13 +3068,13 @@
     <t xml:space="preserve">27.23291015625</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6247520446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8410720825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4982109069824</t>
+    <t xml:space="preserve">27.6247539520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8410701751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4982089996338</t>
   </si>
   <si>
     <t xml:space="preserve">25.567590713501</t>
@@ -3101,7 +3101,7 @@
     <t xml:space="preserve">28.5553722381592</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0451717376709</t>
+    <t xml:space="preserve">29.0451736450195</t>
   </si>
   <si>
     <t xml:space="preserve">29.1431331634521</t>
@@ -3119,10 +3119,10 @@
     <t xml:space="preserve">29.6819133758545</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7798728942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1921138763428</t>
+    <t xml:space="preserve">29.7798748016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1921119689941</t>
   </si>
   <si>
     <t xml:space="preserve">29.5349731445312</t>
@@ -3134,10 +3134,10 @@
     <t xml:space="preserve">30.2206954956055</t>
   </si>
   <si>
-    <t xml:space="preserve">30.514575958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8574371337891</t>
+    <t xml:space="preserve">30.5145740509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8574352264404</t>
   </si>
   <si>
     <t xml:space="preserve">32.1798973083496</t>
@@ -3152,10 +3152,10 @@
     <t xml:space="preserve">32.5227584838867</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0901222229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8248176574707</t>
+    <t xml:space="preserve">34.0901184082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.824821472168</t>
   </si>
   <si>
     <t xml:space="preserve">34.2860374450684</t>
@@ -3164,22 +3164,22 @@
     <t xml:space="preserve">34.6288986206055</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1390953063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7758369445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7472610473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8941993713379</t>
+    <t xml:space="preserve">34.1390991210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7758407592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.747257232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8941955566406</t>
   </si>
   <si>
     <t xml:space="preserve">34.335018157959</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9431800842285</t>
+    <t xml:space="preserve">33.9431838989258</t>
   </si>
   <si>
     <t xml:space="preserve">35.0207405090332</t>
@@ -3188,7 +3188,7 @@
     <t xml:space="preserve">35.4125823974609</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9635772705078</t>
+    <t xml:space="preserve">32.9635810852051</t>
   </si>
   <si>
     <t xml:space="preserve">32.9145965576172</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">33.0125579833984</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4451961517334</t>
+    <t xml:space="preserve">31.4451942443848</t>
   </si>
   <si>
     <t xml:space="preserve">31.5641193389893</t>
@@ -40103,7 +40103,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1381" t="s">
-        <v>609</v>
+        <v>643</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -40129,7 +40129,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1382" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -40155,7 +40155,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1383" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -40181,7 +40181,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1384" t="s">
-        <v>609</v>
+        <v>643</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -40233,7 +40233,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1386" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -40259,7 +40259,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1387" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -40285,7 +40285,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G1388" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -40337,7 +40337,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1390" t="s">
-        <v>609</v>
+        <v>643</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -40363,7 +40363,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1391" t="s">
-        <v>609</v>
+        <v>643</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -40389,7 +40389,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1392" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -40415,7 +40415,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1393" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -40441,7 +40441,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1394" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -40467,7 +40467,7 @@
         <v>17</v>
       </c>
       <c r="G1395" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -40493,7 +40493,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1396" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -40519,7 +40519,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1397" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -40545,7 +40545,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1398" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -40571,7 +40571,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1399" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -40597,7 +40597,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1400" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -40623,7 +40623,7 @@
         <v>18</v>
       </c>
       <c r="G1401" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -40649,7 +40649,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1402" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -40675,7 +40675,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1403" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -40701,7 +40701,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1404" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -40727,7 +40727,7 @@
         <v>18</v>
       </c>
       <c r="G1405" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -40753,7 +40753,7 @@
         <v>18</v>
       </c>
       <c r="G1406" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -40779,7 +40779,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1407" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -40805,7 +40805,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G1408" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -40831,7 +40831,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1409" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -40857,7 +40857,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1410" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -40883,7 +40883,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1411" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -40909,7 +40909,7 @@
         <v>18</v>
       </c>
       <c r="G1412" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -40935,7 +40935,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G1413" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -40961,7 +40961,7 @@
         <v>18</v>
       </c>
       <c r="G1414" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -40987,7 +40987,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G1415" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -41013,7 +41013,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1416" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -41039,7 +41039,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1417" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -41065,7 +41065,7 @@
         <v>18.5</v>
       </c>
       <c r="G1418" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -41091,7 +41091,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1419" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -41117,7 +41117,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1420" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -41143,7 +41143,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1421" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -41169,7 +41169,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1422" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -41195,7 +41195,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1423" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -41221,7 +41221,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1424" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -41247,7 +41247,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1425" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -41273,7 +41273,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1426" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -41299,7 +41299,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1427" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -41325,7 +41325,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G1428" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -41351,7 +41351,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G1429" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -41377,7 +41377,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1430" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -41403,7 +41403,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1431" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -41429,7 +41429,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1432" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -41455,7 +41455,7 @@
         <v>18.5</v>
       </c>
       <c r="G1433" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -41481,7 +41481,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1434" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -41507,7 +41507,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1435" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -41533,7 +41533,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1436" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -41559,7 +41559,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G1437" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -41585,7 +41585,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1438" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -41611,7 +41611,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1439" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -41637,7 +41637,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1440" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -41663,7 +41663,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1441" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -41689,7 +41689,7 @@
         <v>19.5</v>
       </c>
       <c r="G1442" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -41715,7 +41715,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1443" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -41741,7 +41741,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G1444" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -41767,7 +41767,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1445" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -41793,7 +41793,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1446" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -41819,7 +41819,7 @@
         <v>20.5</v>
       </c>
       <c r="G1447" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -41845,7 +41845,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1448" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -41871,7 +41871,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1449" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -41897,7 +41897,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1450" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -41923,7 +41923,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1451" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -41949,7 +41949,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1452" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -41975,7 +41975,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1453" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -42001,7 +42001,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1454" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -42027,7 +42027,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1455" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -42053,7 +42053,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1456" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -42079,7 +42079,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1457" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -42105,7 +42105,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1458" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -42131,7 +42131,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1459" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -42157,7 +42157,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G1460" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -42183,7 +42183,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1461" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -42209,7 +42209,7 @@
         <v>19</v>
       </c>
       <c r="G1462" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -42235,7 +42235,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1463" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -42261,7 +42261,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G1464" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -42287,7 +42287,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1465" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -42313,7 +42313,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G1466" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -42339,7 +42339,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G1467" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -42365,7 +42365,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1468" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -42391,7 +42391,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1469" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -42417,7 +42417,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1470" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -42443,7 +42443,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1471" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -42469,7 +42469,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1472" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -42495,7 +42495,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G1473" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -42521,7 +42521,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1474" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -42547,7 +42547,7 @@
         <v>20</v>
       </c>
       <c r="G1475" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -42573,7 +42573,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1476" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -42599,7 +42599,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1477" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -42625,7 +42625,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1478" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -42651,7 +42651,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G1479" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -42677,7 +42677,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1480" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -42703,7 +42703,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1481" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -42729,7 +42729,7 @@
         <v>20</v>
       </c>
       <c r="G1482" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -42755,7 +42755,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1483" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -42781,7 +42781,7 @@
         <v>20</v>
       </c>
       <c r="G1484" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -42807,7 +42807,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1485" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -42833,7 +42833,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1486" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -42859,7 +42859,7 @@
         <v>20</v>
       </c>
       <c r="G1487" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -42885,7 +42885,7 @@
         <v>20</v>
       </c>
       <c r="G1488" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -42911,7 +42911,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G1489" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -42937,7 +42937,7 @@
         <v>20</v>
       </c>
       <c r="G1490" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -42963,7 +42963,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1491" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -42989,7 +42989,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1492" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -43015,7 +43015,7 @@
         <v>21</v>
       </c>
       <c r="G1493" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -43041,7 +43041,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1494" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -43067,7 +43067,7 @@
         <v>21.25</v>
       </c>
       <c r="G1495" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -43093,7 +43093,7 @@
         <v>21.75</v>
       </c>
       <c r="G1496" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -43119,7 +43119,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G1497" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -43145,7 +43145,7 @@
         <v>22.25</v>
       </c>
       <c r="G1498" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -43171,7 +43171,7 @@
         <v>22.5</v>
       </c>
       <c r="G1499" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -43197,7 +43197,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1500" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -43223,7 +43223,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1501" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -43249,7 +43249,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G1502" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -43275,7 +43275,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1503" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -43301,7 +43301,7 @@
         <v>22</v>
       </c>
       <c r="G1504" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -43327,7 +43327,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1505" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -43353,7 +43353,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1506" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -43379,7 +43379,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1507" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -43405,7 +43405,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1508" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -43431,7 +43431,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1509" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -43457,7 +43457,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1510" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -43483,7 +43483,7 @@
         <v>20.25</v>
       </c>
       <c r="G1511" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -43509,7 +43509,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1512" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -43535,7 +43535,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1513" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -43561,7 +43561,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1514" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -43587,7 +43587,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1515" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -43613,7 +43613,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G1516" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -43639,7 +43639,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1517" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -43665,7 +43665,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1518" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -43691,7 +43691,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1519" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -43717,7 +43717,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1520" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -43743,7 +43743,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1521" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -43769,7 +43769,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1522" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -43795,7 +43795,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1523" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -43821,7 +43821,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1524" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -43847,7 +43847,7 @@
         <v>21</v>
       </c>
       <c r="G1525" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -43873,7 +43873,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1526" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -43899,7 +43899,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1527" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -43925,7 +43925,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1528" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -43951,7 +43951,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1529" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -43977,7 +43977,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1530" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -44003,7 +44003,7 @@
         <v>20.5</v>
       </c>
       <c r="G1531" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -44029,7 +44029,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G1532" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -44055,7 +44055,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1533" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -44081,7 +44081,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1534" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -44107,7 +44107,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1535" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -44133,7 +44133,7 @@
         <v>20</v>
       </c>
       <c r="G1536" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -44159,7 +44159,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1537" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -44185,7 +44185,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1538" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -44211,7 +44211,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G1539" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -44237,7 +44237,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1540" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -44263,7 +44263,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1541" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -44289,7 +44289,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G1542" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -44315,7 +44315,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1543" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -44341,7 +44341,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1544" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -44367,7 +44367,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1545" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -44393,7 +44393,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G1546" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -44419,7 +44419,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G1547" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -44445,7 +44445,7 @@
         <v>19</v>
       </c>
       <c r="G1548" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -44471,7 +44471,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G1549" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -44497,7 +44497,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G1550" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -44523,7 +44523,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1551" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -44549,7 +44549,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G1552" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -44575,7 +44575,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G1553" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -44601,7 +44601,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1554" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -44627,7 +44627,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1555" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -44653,7 +44653,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1556" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -44679,7 +44679,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1557" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -44705,7 +44705,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G1558" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -44731,7 +44731,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1559" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -44757,7 +44757,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1560" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -44783,7 +44783,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G1561" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -44809,7 +44809,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1562" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -44835,7 +44835,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1563" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -44861,7 +44861,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G1564" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -44887,7 +44887,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1565" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -44913,7 +44913,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1566" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -44939,7 +44939,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1567" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -44965,7 +44965,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1568" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -44991,7 +44991,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1569" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -45017,7 +45017,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G1570" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -45043,7 +45043,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G1571" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -45069,7 +45069,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1572" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -45095,7 +45095,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1573" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -45121,7 +45121,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G1574" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -45147,7 +45147,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G1575" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -45173,7 +45173,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1576" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -45199,7 +45199,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1577" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -45225,7 +45225,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1578" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -45251,7 +45251,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1579" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -45277,7 +45277,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G1580" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -45303,7 +45303,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1581" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -45329,7 +45329,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1582" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -45355,7 +45355,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1583" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -45381,7 +45381,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1584" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -45407,7 +45407,7 @@
         <v>17</v>
       </c>
       <c r="G1585" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -45433,7 +45433,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G1586" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -45459,7 +45459,7 @@
         <v>17.5</v>
       </c>
       <c r="G1587" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -45485,7 +45485,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1588" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -45511,7 +45511,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1589" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -45537,7 +45537,7 @@
         <v>16.5</v>
       </c>
       <c r="G1590" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -45563,7 +45563,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1591" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -45641,7 +45641,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G1594" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -45667,7 +45667,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G1595" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -45719,7 +45719,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1597" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -45771,7 +45771,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G1599" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -45797,7 +45797,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G1600" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -45823,7 +45823,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1601" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -45849,7 +45849,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1602" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -45875,7 +45875,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G1603" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -45901,7 +45901,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1604" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -45927,7 +45927,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1605" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -45953,7 +45953,7 @@
         <v>15.5</v>
       </c>
       <c r="G1606" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -45979,7 +45979,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G1607" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -46005,7 +46005,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1608" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -46057,7 +46057,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G1610" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -46109,7 +46109,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1612" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -46187,7 +46187,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G1615" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -46239,7 +46239,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1617" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -46265,7 +46265,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G1618" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -46291,7 +46291,7 @@
         <v>16.5</v>
       </c>
       <c r="G1619" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -46317,7 +46317,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1620" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -46343,7 +46343,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1621" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -46369,7 +46369,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1622" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -46395,7 +46395,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G1623" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -46421,7 +46421,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1624" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -46447,7 +46447,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1625" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -46473,7 +46473,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1626" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -46499,7 +46499,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1627" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -46525,7 +46525,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1628" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -46551,7 +46551,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G1629" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -46577,7 +46577,7 @@
         <v>18</v>
       </c>
       <c r="G1630" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -46603,7 +46603,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1631" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -46629,7 +46629,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1632" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -46655,7 +46655,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1633" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -46681,7 +46681,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1634" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -46707,7 +46707,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1635" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -46733,7 +46733,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1636" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -46759,7 +46759,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1637" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -46785,7 +46785,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1638" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -46811,7 +46811,7 @@
         <v>17</v>
       </c>
       <c r="G1639" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -46837,7 +46837,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1640" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -46863,7 +46863,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1641" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -46889,7 +46889,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1642" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -46915,7 +46915,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1643" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -46941,7 +46941,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1644" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -46967,7 +46967,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1645" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -46993,7 +46993,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1646" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -47019,7 +47019,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G1647" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -47045,7 +47045,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1648" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -47071,7 +47071,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G1649" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -47097,7 +47097,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1650" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -47123,7 +47123,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G1651" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -47149,7 +47149,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G1652" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -47175,7 +47175,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1653" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -47201,7 +47201,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1654" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -47227,7 +47227,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1655" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -47253,7 +47253,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G1656" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -47279,7 +47279,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1657" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -47305,7 +47305,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1658" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -47331,7 +47331,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1659" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -47357,7 +47357,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G1660" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -47383,7 +47383,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1661" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -47409,7 +47409,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G1662" t="s">
-        <v>821</v>
+        <v>772</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -47487,7 +47487,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1665" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -47513,7 +47513,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1666" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -47539,7 +47539,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G1667" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -47565,7 +47565,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1668" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -47591,7 +47591,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1669" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -48007,7 +48007,7 @@
         <v>18</v>
       </c>
       <c r="G1685" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -48059,7 +48059,7 @@
         <v>18</v>
       </c>
       <c r="G1687" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -48111,7 +48111,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1689" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -48241,7 +48241,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1694" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -48267,7 +48267,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1695" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -48319,7 +48319,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1697" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -48423,7 +48423,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1701" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -48501,7 +48501,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1704" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -48527,7 +48527,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1705" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -48579,7 +48579,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1707" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -48631,7 +48631,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G1709" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -48683,7 +48683,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1711" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -49021,7 +49021,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1724" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -49073,7 +49073,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1726" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -49125,7 +49125,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1728" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -49307,7 +49307,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1735" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -49437,7 +49437,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1740" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -49489,7 +49489,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1742" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -49515,7 +49515,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1743" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -50009,7 +50009,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1762" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -50087,7 +50087,7 @@
         <v>18</v>
       </c>
       <c r="G1765" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -50139,7 +50139,7 @@
         <v>18</v>
       </c>
       <c r="G1767" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -50373,7 +50373,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1776" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -50451,7 +50451,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1779" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -50581,7 +50581,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1784" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -50659,7 +50659,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1787" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -70193,7 +70193,7 @@
     </row>
     <row r="2539">
       <c r="A2539" s="1" t="n">
-        <v>46014.691099537</v>
+        <v>46014.3333333333</v>
       </c>
       <c r="B2539" t="n">
         <v>12938</v>

--- a/data/SOL.MI.xlsx
+++ b/data/SOL.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14939117431641</t>
+    <t xml:space="preserve">7.14939165115356</t>
   </si>
   <si>
     <t xml:space="preserve">SOL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14067268371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18862533569336</t>
+    <t xml:space="preserve">7.14067220687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18862581253052</t>
   </si>
   <si>
     <t xml:space="preserve">7.16246891021729</t>
@@ -56,37 +56,37 @@
     <t xml:space="preserve">7.06220388412476</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90962553024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90526628494263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94885921478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71781158447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62626552581787</t>
+    <t xml:space="preserve">6.90962600708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90526580810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94885969161987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71781206130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62626504898071</t>
   </si>
   <si>
     <t xml:space="preserve">6.71345281600952</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29931116104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36470222473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43009233474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4126558303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4475302696228</t>
+    <t xml:space="preserve">6.29931163787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3647027015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43009281158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41265535354614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44753074645996</t>
   </si>
   <si>
     <t xml:space="preserve">6.20776414871216</t>
@@ -101,34 +101,34 @@
     <t xml:space="preserve">6.54779577255249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38213968276978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51292133331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50420141220093</t>
+    <t xml:space="preserve">6.38213920593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51292037963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50420236587524</t>
   </si>
   <si>
     <t xml:space="preserve">6.65242195129395</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80064058303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72217130661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79192113876343</t>
+    <t xml:space="preserve">6.80064010620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72217082977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79192161560059</t>
   </si>
   <si>
     <t xml:space="preserve">7.00989151000977</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84423398971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07964086532593</t>
+    <t xml:space="preserve">6.84423446655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07964134216309</t>
   </si>
   <si>
     <t xml:space="preserve">6.88346862792969</t>
@@ -137,64 +137,64 @@
     <t xml:space="preserve">6.9662971496582</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08836030960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73524951934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83115673065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67857789993286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57395219802856</t>
+    <t xml:space="preserve">7.08835983276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7352499961853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8311562538147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67857837677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57395267486572</t>
   </si>
   <si>
     <t xml:space="preserve">6.63062429428101</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68729686737061</t>
+    <t xml:space="preserve">6.68729639053345</t>
   </si>
   <si>
     <t xml:space="preserve">6.783203125</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77884292602539</t>
+    <t xml:space="preserve">6.77884387969971</t>
   </si>
   <si>
     <t xml:space="preserve">6.81371879577637</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80936002731323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79628133773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69601440429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81807851791382</t>
+    <t xml:space="preserve">6.80935955047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79628086090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69601488113403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81807804107666</t>
   </si>
   <si>
     <t xml:space="preserve">6.8747501373291</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91398477554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67421817779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55215549468994</t>
+    <t xml:space="preserve">6.91398429870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67421913146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5521559715271</t>
   </si>
   <si>
     <t xml:space="preserve">6.46496820449829</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43881177902222</t>
+    <t xml:space="preserve">6.43881130218506</t>
   </si>
   <si>
     <t xml:space="preserve">6.73089027404785</t>
@@ -203,22 +203,22 @@
     <t xml:space="preserve">6.87910938262939</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85295343399048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84859371185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85731267929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74832725524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51728057861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37342023849487</t>
+    <t xml:space="preserve">6.85295248031616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84859418869019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85731220245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74832773208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51728010177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37342071533203</t>
   </si>
   <si>
     <t xml:space="preserve">6.56523418426514</t>
@@ -230,19 +230,19 @@
     <t xml:space="preserve">6.7701244354248</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86167192459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97501611709595</t>
+    <t xml:space="preserve">6.86167240142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97501564025879</t>
   </si>
   <si>
     <t xml:space="preserve">6.9416298866272</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95048332214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88407754898071</t>
+    <t xml:space="preserve">6.95048427581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88407802581787</t>
   </si>
   <si>
     <t xml:space="preserve">6.90178680419922</t>
@@ -251,13 +251,13 @@
     <t xml:space="preserve">7.34006547927856</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22496128082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41975164413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43746042251587</t>
+    <t xml:space="preserve">7.22496175765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41975069046021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43745994567871</t>
   </si>
   <si>
     <t xml:space="preserve">7.36662721633911</t>
@@ -266,13 +266,13 @@
     <t xml:space="preserve">7.26037836074829</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46844959259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40204429626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44631385803223</t>
+    <t xml:space="preserve">7.46845006942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40204381942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44631481170654</t>
   </si>
   <si>
     <t xml:space="preserve">7.3843355178833</t>
@@ -281,103 +281,103 @@
     <t xml:space="preserve">7.04345178604126</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9726185798645</t>
+    <t xml:space="preserve">6.97261905670166</t>
   </si>
   <si>
     <t xml:space="preserve">7.1098575592041</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87079668045044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20725345611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37105417251587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57027292251587</t>
+    <t xml:space="preserve">6.8707971572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20725393295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37105464935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57027149200439</t>
   </si>
   <si>
     <t xml:space="preserve">7.69422960281372</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70308399200439</t>
+    <t xml:space="preserve">7.70308446884155</t>
   </si>
   <si>
     <t xml:space="preserve">7.71193885803223</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65881204605103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04396724700928</t>
+    <t xml:space="preserve">7.65881252288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04396629333496</t>
   </si>
   <si>
     <t xml:space="preserve">7.61454391479492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2957935333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99475479125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1010046005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55256462097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31350326538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50829362869263</t>
+    <t xml:space="preserve">7.29579401016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99475431442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10100412368774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55256366729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31350374221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50829315185547</t>
   </si>
   <si>
     <t xml:space="preserve">7.42417907714844</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3754825592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52600240707397</t>
+    <t xml:space="preserve">7.37548112869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52600145339966</t>
   </si>
   <si>
     <t xml:space="preserve">7.54371023178101</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41532421112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21610736846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99032783508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79996299743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75569343566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00803565979004</t>
+    <t xml:space="preserve">7.41532564163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21610689163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99032688140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79996395111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7556939125061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00803518295288</t>
   </si>
   <si>
     <t xml:space="preserve">7.26923274993896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34449291229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46402311325073</t>
+    <t xml:space="preserve">7.34449195861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46402406692505</t>
   </si>
   <si>
     <t xml:space="preserve">7.51714706420898</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39318943023682</t>
+    <t xml:space="preserve">7.39318990707397</t>
   </si>
   <si>
     <t xml:space="preserve">7.45516872406006</t>
@@ -386,31 +386,31 @@
     <t xml:space="preserve">7.17183685302734</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33563899993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33121061325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39761686325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30464935302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27808666229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25152444839478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16298294067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03017091751099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87965059280396</t>
+    <t xml:space="preserve">7.33563756942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33121109008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39761734008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30464887619019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27808713912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25152349472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16298246383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03017044067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87965106964111</t>
   </si>
   <si>
     <t xml:space="preserve">6.91063976287842</t>
@@ -419,16 +419,16 @@
     <t xml:space="preserve">6.95491075515747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88850498199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95933818817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85751533508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77340126037598</t>
+    <t xml:space="preserve">6.88850450515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95933771133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85751485824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77340173721313</t>
   </si>
   <si>
     <t xml:space="preserve">6.74683904647827</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">6.68486070632935</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81767225265503</t>
+    <t xml:space="preserve">6.81767177581787</t>
   </si>
   <si>
     <t xml:space="preserve">6.90621328353882</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01688957214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8973593711853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83538007736206</t>
+    <t xml:space="preserve">7.01689100265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89735889434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83538055419922</t>
   </si>
   <si>
     <t xml:space="preserve">6.86194324493408</t>
@@ -461,34 +461,34 @@
     <t xml:space="preserve">6.92392158508301</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97704648971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00360774993896</t>
+    <t xml:space="preserve">6.97704601287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00360822677612</t>
   </si>
   <si>
     <t xml:space="preserve">6.91506719589233</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91949367523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9372034072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07001495361328</t>
+    <t xml:space="preserve">6.91949415206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93720245361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07001399993896</t>
   </si>
   <si>
     <t xml:space="preserve">6.98590040206909</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75126552581787</t>
+    <t xml:space="preserve">6.75126647949219</t>
   </si>
   <si>
     <t xml:space="preserve">6.77782869338989</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64944410324097</t>
+    <t xml:space="preserve">6.64944362640381</t>
   </si>
   <si>
     <t xml:space="preserve">6.38382005691528</t>
@@ -506,76 +506,76 @@
     <t xml:space="preserve">6.40595531463623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48121547698975</t>
+    <t xml:space="preserve">6.4812159538269</t>
   </si>
   <si>
     <t xml:space="preserve">6.47678804397583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54319477081299</t>
+    <t xml:space="preserve">6.54319429397583</t>
   </si>
   <si>
     <t xml:space="preserve">6.46350765228271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24215507507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25986337661743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22444629669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64501714706421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64059066772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03902530670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79111051559448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70256900787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70699501037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65829706192017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58303785324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05673265457153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11428499221802</t>
+    <t xml:space="preserve">6.24215459823608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25986242294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22444581985474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64501667022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64058971405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0390248298645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79111003875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70256853103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70699548721313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65829753875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58303833007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05673360824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11428546905518</t>
   </si>
   <si>
     <t xml:space="preserve">7.34891891479492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18511772155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12756633758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19397258758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2426700592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41089725494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48173141479492</t>
+    <t xml:space="preserve">7.18511819839478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12756681442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19397211074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24267053604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41089773178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48173046112061</t>
   </si>
   <si>
     <t xml:space="preserve">7.14527463912964</t>
@@ -584,115 +584,115 @@
     <t xml:space="preserve">7.27365875244141</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17626333236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04787969589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23381519317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29136657714844</t>
+    <t xml:space="preserve">7.1762638092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04787921905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23381567001343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29136610031128</t>
   </si>
   <si>
     <t xml:space="preserve">7.42860698699951</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83589601516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82704067230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13693428039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27860260009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32287216186523</t>
+    <t xml:space="preserve">7.83589553833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8270411491394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13693523406982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27860164642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32287120819092</t>
   </si>
   <si>
     <t xml:space="preserve">9.03120136260986</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53094577789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49995613098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26089382171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92495250701904</t>
+    <t xml:space="preserve">8.53094387054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49995517730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26089286804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92495346069336</t>
   </si>
   <si>
     <t xml:space="preserve">8.58849620819092</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97807598114014</t>
+    <t xml:space="preserve">8.97807693481445</t>
   </si>
   <si>
     <t xml:space="preserve">8.7655782699585</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87182903289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56245040893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25255489349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02234745025635</t>
+    <t xml:space="preserve">8.87182807922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56244945526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25255584716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02234554290771</t>
   </si>
   <si>
     <t xml:space="preserve">8.85411930084229</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82755851745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71245288848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98693084716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89838981628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80984878540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7213077545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78328609466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67703819274902</t>
+    <t xml:space="preserve">8.82755756378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71245384216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98693180084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8983907699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80984973907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72130870819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78328704833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67703914642334</t>
   </si>
   <si>
     <t xml:space="preserve">8.75672435760498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1020336151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82313060760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94266223907471</t>
+    <t xml:space="preserve">9.10203456878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8231315612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94266128540039</t>
   </si>
   <si>
     <t xml:space="preserve">9.20828342437744</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43287658691406</t>
+    <t xml:space="preserve">9.43287563323975</t>
   </si>
   <si>
     <t xml:space="preserve">9.45982646942139</t>
@@ -704,130 +704,130 @@
     <t xml:space="preserve">9.32507228851318</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3879566192627</t>
+    <t xml:space="preserve">9.38795757293701</t>
   </si>
   <si>
     <t xml:space="preserve">9.35202312469482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42389297485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29812145233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55864810943604</t>
+    <t xml:space="preserve">9.4238920211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29812240600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55865001678467</t>
   </si>
   <si>
     <t xml:space="preserve">9.67543601989746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86409282684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5199041366577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0617341995239</t>
+    <t xml:space="preserve">9.86409473419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5199031829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0617332458496</t>
   </si>
   <si>
     <t xml:space="preserve">9.88206100463867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74730491638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56763076782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44186019897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54068088531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34304046630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36100673675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50474643707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48678016662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61255168914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77425479888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46881103515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54966449737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4777946472168</t>
+    <t xml:space="preserve">9.74730587005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56763172149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44186115264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54067993164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34303951263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36100482940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50474452972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48677921295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61254978179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77425670623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46881294250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54966354370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47779560089111</t>
   </si>
   <si>
     <t xml:space="preserve">9.70238780975342</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30710601806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28015422821045</t>
+    <t xml:space="preserve">9.30710506439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28015327453613</t>
   </si>
   <si>
     <t xml:space="preserve">9.2172679901123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16336536407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25320434570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45084381103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58559989929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33405494689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59458255767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66645336151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71137142181396</t>
+    <t xml:space="preserve">9.16336631774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25320243835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45084476470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58560085296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33405685424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59458351135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66645240783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71137046813965</t>
   </si>
   <si>
     <t xml:space="preserve">9.40592670440674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26218605041504</t>
+    <t xml:space="preserve">9.26218795776367</t>
   </si>
   <si>
     <t xml:space="preserve">9.27116966247559</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28913593292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36999225616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65746879577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79222393035889</t>
+    <t xml:space="preserve">9.289137840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36999034881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65746974945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7922248840332</t>
   </si>
   <si>
     <t xml:space="preserve">9.76527309417725</t>
@@ -836,46 +836,46 @@
     <t xml:space="preserve">9.72035503387451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8101921081543</t>
+    <t xml:space="preserve">9.81019115447998</t>
   </si>
   <si>
     <t xml:space="preserve">9.37897396087646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90901374816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81917667388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73832225799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78324031829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69340419769287</t>
+    <t xml:space="preserve">9.90901279449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81917572021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73832130432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78324127197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69340324401855</t>
   </si>
   <si>
     <t xml:space="preserve">9.11844730377197</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08251094818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31608867645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19031715393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10048007965088</t>
+    <t xml:space="preserve">9.08251190185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31608772277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19031524658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1004810333252</t>
   </si>
   <si>
     <t xml:space="preserve">9.22625255584717</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41490840911865</t>
+    <t xml:space="preserve">9.41491031646729</t>
   </si>
   <si>
     <t xml:space="preserve">9.39694213867188</t>
@@ -884,43 +884,43 @@
     <t xml:space="preserve">9.07352924346924</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57661533355713</t>
+    <t xml:space="preserve">9.57661437988281</t>
   </si>
   <si>
     <t xml:space="preserve">9.68441963195801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09149646759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05556106567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14539909362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89385509490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10946273803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23523330688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95393085479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5109205245972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7444953918457</t>
+    <t xml:space="preserve">9.09149551391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05556297302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14539813995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89385414123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10946369171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23523616790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95392990112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5109195709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7444972991943</t>
   </si>
   <si>
     <t xml:space="preserve">10.546854019165</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6905927658081</t>
+    <t xml:space="preserve">10.6905918121338</t>
   </si>
   <si>
     <t xml:space="preserve">10.9062032699585</t>
@@ -932,25 +932,25 @@
     <t xml:space="preserve">10.7085609436035</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6546573638916</t>
+    <t xml:space="preserve">10.6546583175659</t>
   </si>
   <si>
     <t xml:space="preserve">10.5288877487183</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4390487670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3312463760376</t>
+    <t xml:space="preserve">10.4390506744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3312454223633</t>
   </si>
   <si>
     <t xml:space="preserve">10.1695394515991</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1875066757202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1336050033569</t>
+    <t xml:space="preserve">10.1875076293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1336030960083</t>
   </si>
   <si>
     <t xml:space="preserve">9.7562894821167</t>
@@ -959,34 +959,34 @@
     <t xml:space="preserve">9.63051795959473</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0078325271606</t>
+    <t xml:space="preserve">10.007833480835</t>
   </si>
   <si>
     <t xml:space="preserve">9.84612655639648</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0976696014404</t>
+    <t xml:space="preserve">10.0976705551147</t>
   </si>
   <si>
     <t xml:space="preserve">10.205472946167</t>
   </si>
   <si>
-    <t xml:space="preserve">10.27734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2234411239624</t>
+    <t xml:space="preserve">10.2773427963257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2234420776367</t>
   </si>
   <si>
     <t xml:space="preserve">10.2414083480835</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7624607086182</t>
+    <t xml:space="preserve">10.7624626159668</t>
   </si>
   <si>
     <t xml:space="preserve">10.2593774795532</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91799640655518</t>
+    <t xml:space="preserve">9.91799545288086</t>
   </si>
   <si>
     <t xml:space="preserve">9.90002822875977</t>
@@ -995,7 +995,7 @@
     <t xml:space="preserve">9.67380619049072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74667930603027</t>
+    <t xml:space="preserve">9.74667835235596</t>
   </si>
   <si>
     <t xml:space="preserve">9.87420463562012</t>
@@ -1004,31 +1004,31 @@
     <t xml:space="preserve">10.1656942367554</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85598754882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63737010955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47340774536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76489639282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96529483795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0746049880981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2385673522949</t>
+    <t xml:space="preserve">9.85598850250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63736915588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47340679168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76489734649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96529674530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0746059417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2385683059692</t>
   </si>
   <si>
     <t xml:space="preserve">10.3843116760254</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4207468032837</t>
+    <t xml:space="preserve">10.420747756958</t>
   </si>
   <si>
     <t xml:space="preserve">10.8033285140991</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">10.6940202713013</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6211462020874</t>
+    <t xml:space="preserve">10.6211471557617</t>
   </si>
   <si>
     <t xml:space="preserve">10.7851095199585</t>
@@ -1046,31 +1046,31 @@
     <t xml:space="preserve">10.5482740402222</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4025297164917</t>
+    <t xml:space="preserve">10.402530670166</t>
   </si>
   <si>
     <t xml:space="preserve">10.2203493118286</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1474771499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3296566009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5847110748291</t>
+    <t xml:space="preserve">10.1474781036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3296585083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5847120285034</t>
   </si>
   <si>
     <t xml:space="preserve">10.3478746414185</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72846031188965</t>
+    <t xml:space="preserve">9.72846221923828</t>
   </si>
   <si>
     <t xml:space="preserve">9.56449794769287</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41875267028809</t>
+    <t xml:space="preserve">9.4187536239624</t>
   </si>
   <si>
     <t xml:space="preserve">9.40053462982178</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">9.54627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1110401153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2567853927612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92885875701904</t>
+    <t xml:space="preserve">10.1110410690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2567863464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92886066436768</t>
   </si>
   <si>
     <t xml:space="preserve">10.0199499130249</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2021312713623</t>
+    <t xml:space="preserve">10.202130317688</t>
   </si>
   <si>
     <t xml:space="preserve">10.0928220748901</t>
@@ -1100,16 +1100,16 @@
     <t xml:space="preserve">9.8013334274292</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69202518463135</t>
+    <t xml:space="preserve">9.69202613830566</t>
   </si>
   <si>
     <t xml:space="preserve">9.83776950836182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94707775115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89242362976074</t>
+    <t xml:space="preserve">9.94707679748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89242267608643</t>
   </si>
   <si>
     <t xml:space="preserve">9.65558815002441</t>
@@ -1118,7 +1118,7 @@
     <t xml:space="preserve">9.78311443328857</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91064167022705</t>
+    <t xml:space="preserve">9.91064262390137</t>
   </si>
   <si>
     <t xml:space="preserve">9.45518970489502</t>
@@ -1136,58 +1136,58 @@
     <t xml:space="preserve">9.81955051422119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49162483215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61915397644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98351383209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60093402862549</t>
+    <t xml:space="preserve">9.491623878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61915302276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9835147857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6009349822998</t>
   </si>
   <si>
     <t xml:space="preserve">9.10904598236084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09993648529053</t>
+    <t xml:space="preserve">9.09993553161621</t>
   </si>
   <si>
     <t xml:space="preserve">9.38231658935547</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36409854888916</t>
+    <t xml:space="preserve">9.36409950256348</t>
   </si>
   <si>
     <t xml:space="preserve">9.27300930023193</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71024227142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58271598815918</t>
+    <t xml:space="preserve">9.71024131774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5827169418335</t>
   </si>
   <si>
     <t xml:space="preserve">9.29122734069824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14548206329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3660936355591</t>
+    <t xml:space="preserve">9.14548110961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3660945892334</t>
   </si>
   <si>
     <t xml:space="preserve">9.32766246795654</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0017309188843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4754018783569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8397645950317</t>
+    <t xml:space="preserve">10.0017328262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4754028320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8397626876831</t>
   </si>
   <si>
     <t xml:space="preserve">10.5664920806885</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">10.2932224273682</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0381689071655</t>
+    <t xml:space="preserve">10.0381679534912</t>
   </si>
   <si>
     <t xml:space="preserve">10.0563859939575</t>
@@ -1208,28 +1208,28 @@
     <t xml:space="preserve">10.1292591094971</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2750015258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.183913230896</t>
+    <t xml:space="preserve">10.2750024795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1839141845703</t>
   </si>
   <si>
     <t xml:space="preserve">10.675802230835</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7122383117676</t>
+    <t xml:space="preserve">10.7122373580933</t>
   </si>
   <si>
     <t xml:space="preserve">10.9308557510376</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0219449996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.87619972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8944187164307</t>
+    <t xml:space="preserve">11.0219440460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8762006759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.894419670105</t>
   </si>
   <si>
     <t xml:space="preserve">10.7304553985596</t>
@@ -1253,7 +1253,7 @@
     <t xml:space="preserve">11.319953918457</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0240068435669</t>
+    <t xml:space="preserve">11.0240058898926</t>
   </si>
   <si>
     <t xml:space="preserve">10.8205432891846</t>
@@ -1268,28 +1268,28 @@
     <t xml:space="preserve">10.8575372695923</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7095623016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6725702285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6540746688843</t>
+    <t xml:space="preserve">10.7095632553101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.672571182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.65407371521</t>
   </si>
   <si>
     <t xml:space="preserve">10.7835493087769</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7650547027588</t>
+    <t xml:space="preserve">10.7650537490845</t>
   </si>
   <si>
     <t xml:space="preserve">10.8020467758179</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5615892410278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6170806884766</t>
+    <t xml:space="preserve">10.5615901947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6170797348022</t>
   </si>
   <si>
     <t xml:space="preserve">10.3951206207275</t>
@@ -1310,13 +1310,13 @@
     <t xml:space="preserve">10.5061006546021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3396301269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1361665725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.080677986145</t>
+    <t xml:space="preserve">10.3396310806274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1361675262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0806789398193</t>
   </si>
   <si>
     <t xml:space="preserve">9.98819351196289</t>
@@ -1328,19 +1328,19 @@
     <t xml:space="preserve">9.93270397186279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89571189880371</t>
+    <t xml:space="preserve">9.89571094512939</t>
   </si>
   <si>
     <t xml:space="preserve">9.96969795227051</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1731595993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.062180519104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1546640396118</t>
+    <t xml:space="preserve">10.1731605529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0621814727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1546630859375</t>
   </si>
   <si>
     <t xml:space="preserve">9.71074390411377</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">10.0251865386963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91420745849609</t>
+    <t xml:space="preserve">9.91420841217041</t>
   </si>
   <si>
     <t xml:space="preserve">9.76623439788818</t>
@@ -1358,7 +1358,7 @@
     <t xml:space="preserve">9.72924137115479</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65525341033936</t>
+    <t xml:space="preserve">9.65525245666504</t>
   </si>
   <si>
     <t xml:space="preserve">9.67375087738037</t>
@@ -1367,31 +1367,31 @@
     <t xml:space="preserve">9.47028732299805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54427433013916</t>
+    <t xml:space="preserve">9.54427337646484</t>
   </si>
   <si>
     <t xml:space="preserve">9.56277084350586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45179080963135</t>
+    <t xml:space="preserve">9.45179176330566</t>
   </si>
   <si>
     <t xml:space="preserve">9.35930824279785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52577877044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59976482391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61826038360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69224739074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80322742462158</t>
+    <t xml:space="preserve">9.52577781677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59976387023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61826133728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69224834442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8032283782959</t>
   </si>
   <si>
     <t xml:space="preserve">10.2286510467529</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">9.74773788452148</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58126735687256</t>
+    <t xml:space="preserve">9.58126831054688</t>
   </si>
   <si>
     <t xml:space="preserve">10.3211336135864</t>
@@ -1424,13 +1424,13 @@
     <t xml:space="preserve">10.3766241073608</t>
   </si>
   <si>
-    <t xml:space="preserve">10.247145652771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2101526260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84022045135498</t>
+    <t xml:space="preserve">10.2471466064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2101535797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8402214050293</t>
   </si>
   <si>
     <t xml:space="preserve">9.63675689697266</t>
@@ -1439,10 +1439,10 @@
     <t xml:space="preserve">9.43329429626465</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41479682922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39630126953125</t>
+    <t xml:space="preserve">9.41479778289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39630031585693</t>
   </si>
   <si>
     <t xml:space="preserve">9.24832725524902</t>
@@ -1451,7 +1451,7 @@
     <t xml:space="preserve">9.06336116790771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10960388183594</t>
+    <t xml:space="preserve">9.10960292816162</t>
   </si>
   <si>
     <t xml:space="preserve">9.32231426239014</t>
@@ -1460,28 +1460,28 @@
     <t xml:space="preserve">9.28532028198242</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26682376861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19283676147461</t>
+    <t xml:space="preserve">9.26682472229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19283771514893</t>
   </si>
   <si>
     <t xml:space="preserve">9.22982978820801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48878479003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02636814117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9708776473999</t>
+    <t xml:space="preserve">9.48878383636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0263671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97087860107422</t>
   </si>
   <si>
     <t xml:space="preserve">9.13734817504883</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96162891387939</t>
+    <t xml:space="preserve">8.96162986755371</t>
   </si>
   <si>
     <t xml:space="preserve">8.82290458679199</t>
@@ -1499,19 +1499,19 @@
     <t xml:space="preserve">8.33274269104004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0182991027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81483745574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95356273651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49114608764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86107921600342</t>
+    <t xml:space="preserve">8.01830005645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81483697891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95356369018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49114561080933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86107778549194</t>
   </si>
   <si>
     <t xml:space="preserve">7.50964212417603</t>
@@ -1520,7 +1520,7 @@
     <t xml:space="preserve">7.53738689422607</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58362865447998</t>
+    <t xml:space="preserve">7.58362913131714</t>
   </si>
   <si>
     <t xml:space="preserve">8.76741409301758</t>
@@ -1529,37 +1529,37 @@
     <t xml:space="preserve">8.98937511444092</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16509246826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12810039520264</t>
+    <t xml:space="preserve">9.16509342193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12810134887695</t>
   </si>
   <si>
     <t xml:space="preserve">9.09110546112061</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0818567276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34081077575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0448637008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21133422851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38705158233643</t>
+    <t xml:space="preserve">9.08185768127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34081172943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04486465454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21133518218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38705253601074</t>
   </si>
   <si>
     <t xml:space="preserve">9.17434120178223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29456996917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11885070800781</t>
+    <t xml:space="preserve">9.29457092285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11885166168213</t>
   </si>
   <si>
     <t xml:space="preserve">8.78591060638428</t>
@@ -1577,13 +1577,13 @@
     <t xml:space="preserve">8.87839508056641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9338846206665</t>
+    <t xml:space="preserve">8.93388557434082</t>
   </si>
   <si>
     <t xml:space="preserve">8.63793754577637</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71192359924316</t>
+    <t xml:space="preserve">8.71192455291748</t>
   </si>
   <si>
     <t xml:space="preserve">8.58244895935059</t>
@@ -1592,13 +1592,13 @@
     <t xml:space="preserve">8.69342708587646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46114063262939</t>
+    <t xml:space="preserve">9.46113967895508</t>
   </si>
   <si>
     <t xml:space="preserve">9.6494197845459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69649219512939</t>
+    <t xml:space="preserve">9.69649124145508</t>
   </si>
   <si>
     <t xml:space="preserve">9.74356079101562</t>
@@ -1607,7 +1607,7 @@
     <t xml:space="preserve">9.97891330718994</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93184375762939</t>
+    <t xml:space="preserve">9.93184280395508</t>
   </si>
   <si>
     <t xml:space="preserve">9.7906322479248</t>
@@ -1616,10 +1616,10 @@
     <t xml:space="preserve">10.0730543136597</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3084049224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4496173858643</t>
+    <t xml:space="preserve">10.308403968811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4496164321899</t>
   </si>
   <si>
     <t xml:space="preserve">10.1671953201294</t>
@@ -1631,19 +1631,19 @@
     <t xml:space="preserve">10.0259828567505</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2142648696899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3554763793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2613353729248</t>
+    <t xml:space="preserve">10.2142639160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3554754257202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2613344192505</t>
   </si>
   <si>
     <t xml:space="preserve">9.88477230072021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5908279418945</t>
+    <t xml:space="preserve">10.5908269882202</t>
   </si>
   <si>
     <t xml:space="preserve">10.4966869354248</t>
@@ -1658,13 +1658,13 @@
     <t xml:space="preserve">11.1556720733643</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9673900604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0615301132202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7791090011597</t>
+    <t xml:space="preserve">10.9673910140991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0615310668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7791080474854</t>
   </si>
   <si>
     <t xml:space="preserve">10.8261785507202</t>
@@ -1676,13 +1676,13 @@
     <t xml:space="preserve">11.1086015701294</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9203205108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8732500076294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7320394515991</t>
+    <t xml:space="preserve">10.9203195571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8732490539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7320384979248</t>
   </si>
   <si>
     <t xml:space="preserve">10.6378984451294</t>
@@ -1694,10 +1694,10 @@
     <t xml:space="preserve">11.6263751983643</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7675867080688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8146572113037</t>
+    <t xml:space="preserve">11.7675857543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8146562576294</t>
   </si>
   <si>
     <t xml:space="preserve">11.5793046951294</t>
@@ -1712,28 +1712,28 @@
     <t xml:space="preserve">12.0029382705688</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2853603363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5677824020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5207118988037</t>
+    <t xml:space="preserve">12.285361289978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5677814483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5207109451294</t>
   </si>
   <si>
     <t xml:space="preserve">12.897274017334</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7560625076294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.661922454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6148519515991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8031330108643</t>
+    <t xml:space="preserve">12.7560634613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6619215011597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6148509979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8031339645386</t>
   </si>
   <si>
     <t xml:space="preserve">12.8502035140991</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">12.9914150238037</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1796960830688</t>
+    <t xml:space="preserve">13.1796970367432</t>
   </si>
   <si>
     <t xml:space="preserve">13.4621181488037</t>
@@ -1751,16 +1751,16 @@
     <t xml:space="preserve">13.838680267334</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7445421218872</t>
+    <t xml:space="preserve">13.7445411682129</t>
   </si>
   <si>
     <t xml:space="preserve">13.6504001617432</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5091896057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7916107177734</t>
+    <t xml:space="preserve">13.5091886520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7916097640991</t>
   </si>
   <si>
     <t xml:space="preserve">13.8857517242432</t>
@@ -1769,16 +1769,16 @@
     <t xml:space="preserve">13.9798927307129</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0269632339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.074031829834</t>
+    <t xml:space="preserve">14.0269622802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0740327835083</t>
   </si>
   <si>
     <t xml:space="preserve">14.168173789978</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1211032867432</t>
+    <t xml:space="preserve">14.1211042404175</t>
   </si>
   <si>
     <t xml:space="preserve">14.2623138427734</t>
@@ -1787,7 +1787,7 @@
     <t xml:space="preserve">14.2152452468872</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4505968093872</t>
+    <t xml:space="preserve">14.4505958557129</t>
   </si>
   <si>
     <t xml:space="preserve">14.6859474182129</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">14.3093852996826</t>
   </si>
   <si>
-    <t xml:space="preserve">14.403525352478</t>
+    <t xml:space="preserve">14.4035243988037</t>
   </si>
   <si>
     <t xml:space="preserve">14.3564548492432</t>
@@ -1814,10 +1814,10 @@
     <t xml:space="preserve">14.7800874710083</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8271589279175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.874228477478</t>
+    <t xml:space="preserve">14.8271579742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8742275238037</t>
   </si>
   <si>
     <t xml:space="preserve">14.7330169677734</t>
@@ -1826,10 +1826,10 @@
     <t xml:space="preserve">15.3449306488037</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7685670852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0039157867432</t>
+    <t xml:space="preserve">15.7685661315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0039176940918</t>
   </si>
   <si>
     <t xml:space="preserve">16.0415725708008</t>
@@ -1841,112 +1841,115 @@
     <t xml:space="preserve">16.1921977996826</t>
   </si>
   <si>
+    <t xml:space="preserve">16.1168842315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2298564910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3804779052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3993091583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4181365966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5311031341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2675094604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9286050796509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8909482955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.815634727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9662599563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7214975357056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5332126617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.51438331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7026662826538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2696199417114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4767293930054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6838388442993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6650094985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4202432632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1566514968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2319641113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7779769897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9833707809448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9643001556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6209802627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4874687194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7926406860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8117141723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6019086837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5446872711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2585897445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6972732543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8307876586914</t>
+  </si>
+  <si>
     <t xml:space="preserve">16.116886138916</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2298545837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3804798126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3993091583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4181346893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5311050415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2675094604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9286050796509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8909482955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.815634727478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9662599563599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7214956283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5332136154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5143852233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7026662826538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2696189880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4767284393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6838369369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6650104522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4202442169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1566505432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2319631576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7779788970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9833726882935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.964301109314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6209812164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4874696731567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7926397323608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8117141723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6019096374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5446872711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2585906982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6972723007202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8307867050171</t>
-  </si>
-  <si>
     <t xml:space="preserve">16.2503986358643</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2313270568848</t>
+    <t xml:space="preserve">16.2313251495361</t>
   </si>
   <si>
     <t xml:space="preserve">16.0024471282959</t>
@@ -1955,16 +1958,16 @@
     <t xml:space="preserve">16.2694721221924</t>
   </si>
   <si>
-    <t xml:space="preserve">16.212251663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4602069854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4411315917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5364952087402</t>
+    <t xml:space="preserve">16.2122535705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.460205078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4411334991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5364990234375</t>
   </si>
   <si>
     <t xml:space="preserve">16.555570602417</t>
@@ -1973,10 +1976,10 @@
     <t xml:space="preserve">17.1659126281738</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9561080932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2231330871582</t>
+    <t xml:space="preserve">16.9561100006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2231349945068</t>
   </si>
   <si>
     <t xml:space="preserve">17.3185005187988</t>
@@ -1985,28 +1988,28 @@
     <t xml:space="preserve">17.0896224975586</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8416690826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7463035583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9751815795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1277656555176</t>
+    <t xml:space="preserve">16.841667175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.746301651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9751796722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1277675628662</t>
   </si>
   <si>
     <t xml:space="preserve">17.5092334747314</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5473804473877</t>
+    <t xml:space="preserve">17.5473785400391</t>
   </si>
   <si>
     <t xml:space="preserve">17.7571830749512</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6427440643311</t>
+    <t xml:space="preserve">17.6427459716797</t>
   </si>
   <si>
     <t xml:space="preserve">17.7381134033203</t>
@@ -2015,28 +2018,28 @@
     <t xml:space="preserve">17.4901580810547</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4710845947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.337574005127</t>
+    <t xml:space="preserve">17.4710865020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3375720977783</t>
   </si>
   <si>
     <t xml:space="preserve">17.2994251251221</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3566474914551</t>
+    <t xml:space="preserve">17.3566455841064</t>
   </si>
   <si>
     <t xml:space="preserve">17.2422065734863</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1468391418457</t>
+    <t xml:space="preserve">17.1468410491943</t>
   </si>
   <si>
     <t xml:space="preserve">17.0133266448975</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4520130157471</t>
+    <t xml:space="preserve">17.4520111083984</t>
   </si>
   <si>
     <t xml:space="preserve">17.8334789276123</t>
@@ -2045,10 +2048,10 @@
     <t xml:space="preserve">17.6999645233154</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8716220855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8525505065918</t>
+    <t xml:space="preserve">17.8716239929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8525485992432</t>
   </si>
   <si>
     <t xml:space="preserve">18.0242099761963</t>
@@ -2060,13 +2063,13 @@
     <t xml:space="preserve">18.5010395050049</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6536273956299</t>
+    <t xml:space="preserve">18.6536254882812</t>
   </si>
   <si>
     <t xml:space="preserve">18.5964069366455</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5582599639893</t>
+    <t xml:space="preserve">18.5582580566406</t>
   </si>
   <si>
     <t xml:space="preserve">18.7108478546143</t>
@@ -2084,7 +2087,7 @@
     <t xml:space="preserve">19.5023880004883</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8838520050049</t>
+    <t xml:space="preserve">19.8838500976562</t>
   </si>
   <si>
     <t xml:space="preserve">19.9792175292969</t>
@@ -2093,19 +2096,19 @@
     <t xml:space="preserve">19.4547023773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3593349456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1686058044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7871417999268</t>
+    <t xml:space="preserve">19.3593330383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1686038970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7871398925781</t>
   </si>
   <si>
     <t xml:space="preserve">18.6917743682861</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2162857055664</t>
+    <t xml:space="preserve">19.216287612915</t>
   </si>
   <si>
     <t xml:space="preserve">19.1209201812744</t>
@@ -2120,28 +2123,28 @@
     <t xml:space="preserve">18.1195755004883</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6236705780029</t>
+    <t xml:space="preserve">17.6236686706543</t>
   </si>
   <si>
     <t xml:space="preserve">17.890697479248</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1005001068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2530860900879</t>
+    <t xml:space="preserve">18.1005020141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2530879974365</t>
   </si>
   <si>
     <t xml:space="preserve">17.9669895172119</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1767959594727</t>
+    <t xml:space="preserve">18.176794052124</t>
   </si>
   <si>
     <t xml:space="preserve">18.9969444274902</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0732383728027</t>
+    <t xml:space="preserve">19.0732364654541</t>
   </si>
   <si>
     <t xml:space="preserve">18.9778709411621</t>
@@ -2153,7 +2156,7 @@
     <t xml:space="preserve">18.9397258758545</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9015789031982</t>
+    <t xml:space="preserve">18.9015769958496</t>
   </si>
   <si>
     <t xml:space="preserve">20.0268993377686</t>
@@ -2162,22 +2165,22 @@
     <t xml:space="preserve">20.2176322937012</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2653160095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7421474456787</t>
+    <t xml:space="preserve">20.2653141021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7421455383301</t>
   </si>
   <si>
     <t xml:space="preserve">20.9328804016113</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2189788818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4573936462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6944637298584</t>
+    <t xml:space="preserve">21.2189769744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4573917388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6944618225098</t>
   </si>
   <si>
     <t xml:space="preserve">20.3129978179932</t>
@@ -2186,7 +2189,7 @@
     <t xml:space="preserve">20.4560489654541</t>
   </si>
   <si>
-    <t xml:space="preserve">20.980562210083</t>
+    <t xml:space="preserve">20.9805603027344</t>
   </si>
   <si>
     <t xml:space="preserve">19.8361682891846</t>
@@ -2195,22 +2198,22 @@
     <t xml:space="preserve">20.4083652496338</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1222686767578</t>
+    <t xml:space="preserve">20.1222667694092</t>
   </si>
   <si>
     <t xml:space="preserve">19.3116550445557</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2639713287354</t>
+    <t xml:space="preserve">19.2639694213867</t>
   </si>
   <si>
     <t xml:space="preserve">19.5977516174316</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6454372406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1699485778809</t>
+    <t xml:space="preserve">19.645435333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1699466705322</t>
   </si>
   <si>
     <t xml:space="preserve">19.9315338134766</t>
@@ -2219,16 +2222,16 @@
     <t xml:space="preserve">19.7408008575439</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8443603515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.016019821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0432834625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0051345825195</t>
+    <t xml:space="preserve">18.8443584442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0160179138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0432815551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0051364898682</t>
   </si>
   <si>
     <t xml:space="preserve">18.1386489868164</t>
@@ -2237,25 +2240,25 @@
     <t xml:space="preserve">18.0623569488525</t>
   </si>
   <si>
-    <t xml:space="preserve">18.081428527832</t>
+    <t xml:space="preserve">18.0814266204834</t>
   </si>
   <si>
     <t xml:space="preserve">17.6045970916748</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2612819671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0514736175537</t>
+    <t xml:space="preserve">17.2612800598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0514755249023</t>
   </si>
   <si>
     <t xml:space="preserve">16.2885456085205</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0324020385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7272300720215</t>
+    <t xml:space="preserve">17.0324001312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7272319793701</t>
   </si>
   <si>
     <t xml:space="preserve">16.4792766571045</t>
@@ -2264,7 +2267,7 @@
     <t xml:space="preserve">16.8225936889648</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0705490112305</t>
+    <t xml:space="preserve">17.0705471038818</t>
   </si>
   <si>
     <t xml:space="preserve">16.6509342193604</t>
@@ -2273,16 +2276,16 @@
     <t xml:space="preserve">16.8607425689697</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3076171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5937175750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6318626403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2776641845703</t>
+    <t xml:space="preserve">16.3076190948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5937156677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6318645477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.277663230896</t>
   </si>
   <si>
     <t xml:space="preserve">14.8771257400513</t>
@@ -2291,46 +2294,46 @@
     <t xml:space="preserve">14.4956607818604</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3730316162109</t>
+    <t xml:space="preserve">15.3730297088623</t>
   </si>
   <si>
     <t xml:space="preserve">14.9915647506714</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0869312286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6782007217407</t>
+    <t xml:space="preserve">15.0869302749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.678201675415</t>
   </si>
   <si>
     <t xml:space="preserve">15.1441507339478</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9452247619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0787410736084</t>
+    <t xml:space="preserve">15.9452257156372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0787391662598</t>
   </si>
   <si>
     <t xml:space="preserve">16.0405921936035</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5746440887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6890850067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5174236297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4983501434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7354211807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8880052566528</t>
+    <t xml:space="preserve">16.5746421813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6890811920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5174217224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.498348236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7354202270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8880071640015</t>
   </si>
   <si>
     <t xml:space="preserve">15.5065412521362</t>
@@ -2339,13 +2342,13 @@
     <t xml:space="preserve">14.9724912643433</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3348827362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2204427719116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9152717590332</t>
+    <t xml:space="preserve">15.3348836898804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2204437255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9152727127075</t>
   </si>
   <si>
     <t xml:space="preserve">14.781759262085</t>
@@ -2360,13 +2363,13 @@
     <t xml:space="preserve">16.0978126525879</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2395153045654</t>
+    <t xml:space="preserve">15.2395162582397</t>
   </si>
   <si>
     <t xml:space="preserve">15.1060047149658</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0063877105713</t>
+    <t xml:space="preserve">16.0063896179199</t>
   </si>
   <si>
     <t xml:space="preserve">16.1999359130859</t>
@@ -2384,10 +2387,10 @@
     <t xml:space="preserve">16.2773532867432</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4709033966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7805767059326</t>
+    <t xml:space="preserve">16.4709014892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7805786132812</t>
   </si>
   <si>
     <t xml:space="preserve">17.1483173370361</t>
@@ -2396,28 +2399,28 @@
     <t xml:space="preserve">17.767671585083</t>
   </si>
   <si>
-    <t xml:space="preserve">17.419282913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2321853637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7289600372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9418659210205</t>
+    <t xml:space="preserve">17.4192848205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2321834564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7289619445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9418640136719</t>
   </si>
   <si>
     <t xml:space="preserve">17.4967041015625</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5934791564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4579963684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8967037200928</t>
+    <t xml:space="preserve">17.5934772491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4579944610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8967056274414</t>
   </si>
   <si>
     <t xml:space="preserve">16.4515476226807</t>
@@ -2426,13 +2429,13 @@
     <t xml:space="preserve">15.9870338439941</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8321962356567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9483232498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3676805496216</t>
+    <t xml:space="preserve">15.8321952819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9483222961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3676795959473</t>
   </si>
   <si>
     <t xml:space="preserve">15.4450988769531</t>
@@ -2441,10 +2444,10 @@
     <t xml:space="preserve">15.1741333007812</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1160688400269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.135422706604</t>
+    <t xml:space="preserve">15.1160678863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1354236602783</t>
   </si>
   <si>
     <t xml:space="preserve">15.3289709091187</t>
@@ -2453,13 +2456,13 @@
     <t xml:space="preserve">15.619291305542</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8902597427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7547750473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8128395080566</t>
+    <t xml:space="preserve">15.8902606964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7547760009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.812840461731</t>
   </si>
   <si>
     <t xml:space="preserve">16.161226272583</t>
@@ -2474,10 +2477,7 @@
     <t xml:space="preserve">16.4128360748291</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4321899414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7354202270508</t>
+    <t xml:space="preserve">16.4321918487549</t>
   </si>
   <si>
     <t xml:space="preserve">15.7160663604736</t>
@@ -2501,10 +2501,10 @@
     <t xml:space="preserve">17.5354137420654</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3805732727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3418674468994</t>
+    <t xml:space="preserve">17.3805751800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3418655395508</t>
   </si>
   <si>
     <t xml:space="preserve">17.2063827514648</t>
@@ -2528,16 +2528,16 @@
     <t xml:space="preserve">17.6128330230713</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8192882537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1096096038818</t>
+    <t xml:space="preserve">16.8192863464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1096076965332</t>
   </si>
   <si>
     <t xml:space="preserve">16.7225131988525</t>
   </si>
   <si>
-    <t xml:space="preserve">17.128963470459</t>
+    <t xml:space="preserve">17.1289653778076</t>
   </si>
   <si>
     <t xml:space="preserve">16.8773517608643</t>
@@ -2558,13 +2558,13 @@
     <t xml:space="preserve">15.5031642913818</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2128419876099</t>
+    <t xml:space="preserve">15.2128429412842</t>
   </si>
   <si>
     <t xml:space="preserve">15.3096160888672</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5805826187134</t>
+    <t xml:space="preserve">15.5805835723877</t>
   </si>
   <si>
     <t xml:space="preserve">15.1547775268555</t>
@@ -2585,7 +2585,7 @@
     <t xml:space="preserve">15.5612277984619</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1805782318115</t>
+    <t xml:space="preserve">16.1805801391602</t>
   </si>
   <si>
     <t xml:space="preserve">16.8579978942871</t>
@@ -2594,10 +2594,10 @@
     <t xml:space="preserve">17.3031558990479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9031524658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8063812255859</t>
+    <t xml:space="preserve">17.9031543731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8063793182373</t>
   </si>
   <si>
     <t xml:space="preserve">17.1676731109619</t>
@@ -2612,7 +2612,7 @@
     <t xml:space="preserve">18.735408782959</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6579895019531</t>
+    <t xml:space="preserve">18.6579914093018</t>
   </si>
   <si>
     <t xml:space="preserve">18.4837970733643</t>
@@ -2627,7 +2627,7 @@
     <t xml:space="preserve">18.2515392303467</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8837985992432</t>
+    <t xml:space="preserve">17.8837966918945</t>
   </si>
   <si>
     <t xml:space="preserve">18.0386352539062</t>
@@ -2645,7 +2645,7 @@
     <t xml:space="preserve">18.1547660827637</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0192813873291</t>
+    <t xml:space="preserve">18.0192832946777</t>
   </si>
   <si>
     <t xml:space="preserve">17.9805736541748</t>
@@ -2657,7 +2657,7 @@
     <t xml:space="preserve">17.8450908660889</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6902523040771</t>
+    <t xml:space="preserve">17.6902503967285</t>
   </si>
   <si>
     <t xml:space="preserve">17.6321868896484</t>
@@ -2675,19 +2675,19 @@
     <t xml:space="preserve">17.2644462585449</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7096061706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4773483276367</t>
+    <t xml:space="preserve">17.7096042633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4773502349854</t>
   </si>
   <si>
     <t xml:space="preserve">17.8257369995117</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5805721282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9289569854736</t>
+    <t xml:space="preserve">18.5805702209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.928955078125</t>
   </si>
   <si>
     <t xml:space="preserve">18.8128299713135</t>
@@ -2702,10 +2702,10 @@
     <t xml:space="preserve">19.7902450561523</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0321769714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7418556213379</t>
+    <t xml:space="preserve">20.0321788787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7418575286865</t>
   </si>
   <si>
     <t xml:space="preserve">19.5966968536377</t>
@@ -2714,13 +2714,13 @@
     <t xml:space="preserve">19.9837894439697</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8386287689209</t>
+    <t xml:space="preserve">19.8386306762695</t>
   </si>
   <si>
     <t xml:space="preserve">20.0805644989014</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3708839416504</t>
+    <t xml:space="preserve">20.370885848999</t>
   </si>
   <si>
     <t xml:space="preserve">19.8870162963867</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">20.177339553833</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4192752838135</t>
+    <t xml:space="preserve">20.4192733764648</t>
   </si>
   <si>
     <t xml:space="preserve">20.467658996582</t>
@@ -2759,10 +2759,10 @@
     <t xml:space="preserve">21.6289443969727</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0644283294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2579727172852</t>
+    <t xml:space="preserve">22.0644264221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2579746246338</t>
   </si>
   <si>
     <t xml:space="preserve">22.6450710296631</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">22.7902297973633</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7418422698975</t>
+    <t xml:space="preserve">22.7418441772461</t>
   </si>
   <si>
     <t xml:space="preserve">21.9676532745361</t>
@@ -2795,31 +2795,31 @@
     <t xml:space="preserve">22.3063621520996</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8224925994873</t>
+    <t xml:space="preserve">21.8224906921387</t>
   </si>
   <si>
     <t xml:space="preserve">22.3547496795654</t>
   </si>
   <si>
-    <t xml:space="preserve">22.112813949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5482959747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9837779998779</t>
+    <t xml:space="preserve">22.1128158569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5482978820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9837799072266</t>
   </si>
   <si>
     <t xml:space="preserve">23.9031295776367</t>
   </si>
   <si>
-    <t xml:space="preserve">24.193452835083</t>
+    <t xml:space="preserve">24.1934509277344</t>
   </si>
   <si>
     <t xml:space="preserve">24.0966758728027</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0160312652588</t>
+    <t xml:space="preserve">25.0160293579102</t>
   </si>
   <si>
     <t xml:space="preserve">24.9676399230957</t>
@@ -2834,22 +2834,22 @@
     <t xml:space="preserve">25.9353790283203</t>
   </si>
   <si>
-    <t xml:space="preserve">25.354736328125</t>
+    <t xml:space="preserve">25.3547382354736</t>
   </si>
   <si>
     <t xml:space="preserve">25.161190032959</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8708686828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.257963180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.451509475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2095737457275</t>
+    <t xml:space="preserve">24.8708667755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2579650878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4515113830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2095756530762</t>
   </si>
   <si>
     <t xml:space="preserve">25.5482845306396</t>
@@ -2867,7 +2867,7 @@
     <t xml:space="preserve">26.9515056610107</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6934432983398</t>
+    <t xml:space="preserve">25.6934452056885</t>
   </si>
   <si>
     <t xml:space="preserve">25.5966720581055</t>
@@ -2879,7 +2879,7 @@
     <t xml:space="preserve">25.8869934082031</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3708629608154</t>
+    <t xml:space="preserve">26.3708610534668</t>
   </si>
   <si>
     <t xml:space="preserve">26.2043304443359</t>
@@ -40103,7 +40103,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1381" t="s">
-        <v>609</v>
+        <v>643</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -40129,7 +40129,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1382" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -40155,7 +40155,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1383" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -40181,7 +40181,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1384" t="s">
-        <v>609</v>
+        <v>643</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -40233,7 +40233,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1386" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -40259,7 +40259,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1387" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -40285,7 +40285,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G1388" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -40337,7 +40337,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1390" t="s">
-        <v>609</v>
+        <v>643</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -40363,7 +40363,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1391" t="s">
-        <v>609</v>
+        <v>643</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -40389,7 +40389,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1392" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -40415,7 +40415,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1393" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -40441,7 +40441,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1394" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -40467,7 +40467,7 @@
         <v>17</v>
       </c>
       <c r="G1395" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -40493,7 +40493,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1396" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -40519,7 +40519,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1397" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -40545,7 +40545,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1398" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -40571,7 +40571,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1399" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -40597,7 +40597,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1400" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -40623,7 +40623,7 @@
         <v>18</v>
       </c>
       <c r="G1401" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -40649,7 +40649,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1402" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -40675,7 +40675,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1403" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -40701,7 +40701,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1404" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -40727,7 +40727,7 @@
         <v>18</v>
       </c>
       <c r="G1405" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -40753,7 +40753,7 @@
         <v>18</v>
       </c>
       <c r="G1406" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -40779,7 +40779,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1407" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -40805,7 +40805,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G1408" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -40831,7 +40831,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1409" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -40857,7 +40857,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1410" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -40883,7 +40883,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1411" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -40909,7 +40909,7 @@
         <v>18</v>
       </c>
       <c r="G1412" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -40935,7 +40935,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G1413" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -40961,7 +40961,7 @@
         <v>18</v>
       </c>
       <c r="G1414" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -40987,7 +40987,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G1415" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -41013,7 +41013,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1416" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -41039,7 +41039,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1417" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -41065,7 +41065,7 @@
         <v>18.5</v>
       </c>
       <c r="G1418" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -41091,7 +41091,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1419" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -41117,7 +41117,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1420" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -41143,7 +41143,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1421" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -41169,7 +41169,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1422" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -41195,7 +41195,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1423" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -41221,7 +41221,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1424" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -41247,7 +41247,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1425" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -41273,7 +41273,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1426" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -41299,7 +41299,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1427" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -41325,7 +41325,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G1428" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -41351,7 +41351,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G1429" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -41377,7 +41377,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1430" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -41403,7 +41403,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1431" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -41429,7 +41429,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1432" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -41455,7 +41455,7 @@
         <v>18.5</v>
       </c>
       <c r="G1433" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -41481,7 +41481,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1434" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -41507,7 +41507,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1435" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -41533,7 +41533,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1436" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -41559,7 +41559,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G1437" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -41585,7 +41585,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1438" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -41611,7 +41611,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1439" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -41637,7 +41637,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1440" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -41663,7 +41663,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1441" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -41689,7 +41689,7 @@
         <v>19.5</v>
       </c>
       <c r="G1442" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -41715,7 +41715,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1443" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -41741,7 +41741,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G1444" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -41767,7 +41767,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1445" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -41793,7 +41793,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1446" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -41819,7 +41819,7 @@
         <v>20.5</v>
       </c>
       <c r="G1447" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -41845,7 +41845,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1448" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -41871,7 +41871,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1449" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -41897,7 +41897,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1450" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -41923,7 +41923,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1451" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -41949,7 +41949,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1452" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -41975,7 +41975,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1453" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -42001,7 +42001,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1454" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -42027,7 +42027,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1455" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -42053,7 +42053,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1456" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -42079,7 +42079,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1457" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -42105,7 +42105,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1458" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -42131,7 +42131,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1459" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -42157,7 +42157,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G1460" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -42183,7 +42183,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1461" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -42209,7 +42209,7 @@
         <v>19</v>
       </c>
       <c r="G1462" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -42235,7 +42235,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1463" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -42261,7 +42261,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G1464" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -42287,7 +42287,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1465" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -42313,7 +42313,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G1466" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -42339,7 +42339,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G1467" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -42365,7 +42365,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1468" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -42391,7 +42391,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1469" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -42417,7 +42417,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1470" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -42443,7 +42443,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1471" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -42469,7 +42469,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1472" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -42495,7 +42495,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G1473" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -42521,7 +42521,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1474" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -42547,7 +42547,7 @@
         <v>20</v>
       </c>
       <c r="G1475" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -42573,7 +42573,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1476" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -42599,7 +42599,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1477" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -42625,7 +42625,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1478" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -42651,7 +42651,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G1479" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -42677,7 +42677,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1480" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -42703,7 +42703,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1481" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -42729,7 +42729,7 @@
         <v>20</v>
       </c>
       <c r="G1482" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -42755,7 +42755,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1483" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -42781,7 +42781,7 @@
         <v>20</v>
       </c>
       <c r="G1484" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -42807,7 +42807,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1485" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -42833,7 +42833,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1486" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -42859,7 +42859,7 @@
         <v>20</v>
       </c>
       <c r="G1487" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -42885,7 +42885,7 @@
         <v>20</v>
       </c>
       <c r="G1488" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -42911,7 +42911,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G1489" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -42937,7 +42937,7 @@
         <v>20</v>
       </c>
       <c r="G1490" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -42963,7 +42963,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1491" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -42989,7 +42989,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1492" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -43015,7 +43015,7 @@
         <v>21</v>
       </c>
       <c r="G1493" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -43041,7 +43041,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1494" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -43067,7 +43067,7 @@
         <v>21.25</v>
       </c>
       <c r="G1495" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -43093,7 +43093,7 @@
         <v>21.75</v>
       </c>
       <c r="G1496" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -43119,7 +43119,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G1497" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -43145,7 +43145,7 @@
         <v>22.25</v>
       </c>
       <c r="G1498" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -43171,7 +43171,7 @@
         <v>22.5</v>
       </c>
       <c r="G1499" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -43197,7 +43197,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1500" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -43223,7 +43223,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1501" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -43249,7 +43249,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G1502" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -43275,7 +43275,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1503" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -43301,7 +43301,7 @@
         <v>22</v>
       </c>
       <c r="G1504" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -43327,7 +43327,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1505" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -43353,7 +43353,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1506" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -43379,7 +43379,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1507" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -43405,7 +43405,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1508" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -43431,7 +43431,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1509" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -43457,7 +43457,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1510" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -43483,7 +43483,7 @@
         <v>20.25</v>
       </c>
       <c r="G1511" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -43509,7 +43509,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1512" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -43535,7 +43535,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1513" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -43561,7 +43561,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1514" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -43587,7 +43587,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1515" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -43613,7 +43613,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G1516" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -43639,7 +43639,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1517" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -43665,7 +43665,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1518" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -43691,7 +43691,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1519" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -43717,7 +43717,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1520" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -43743,7 +43743,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1521" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -43769,7 +43769,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1522" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -43795,7 +43795,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1523" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -43821,7 +43821,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1524" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -43847,7 +43847,7 @@
         <v>21</v>
       </c>
       <c r="G1525" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -43873,7 +43873,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1526" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -43899,7 +43899,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1527" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -43925,7 +43925,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1528" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -43951,7 +43951,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1529" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -43977,7 +43977,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1530" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -44003,7 +44003,7 @@
         <v>20.5</v>
       </c>
       <c r="G1531" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -44029,7 +44029,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G1532" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -44055,7 +44055,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1533" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -44081,7 +44081,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1534" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -44107,7 +44107,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1535" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -44133,7 +44133,7 @@
         <v>20</v>
       </c>
       <c r="G1536" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -44159,7 +44159,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1537" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -44185,7 +44185,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1538" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -44211,7 +44211,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G1539" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -44237,7 +44237,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1540" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -44263,7 +44263,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1541" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -44289,7 +44289,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G1542" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -44315,7 +44315,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1543" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -44341,7 +44341,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1544" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -44367,7 +44367,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1545" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -44393,7 +44393,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G1546" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -44419,7 +44419,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G1547" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -44445,7 +44445,7 @@
         <v>19</v>
       </c>
       <c r="G1548" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -44471,7 +44471,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G1549" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -44497,7 +44497,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G1550" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -44523,7 +44523,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1551" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -44549,7 +44549,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G1552" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -44575,7 +44575,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G1553" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -44601,7 +44601,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1554" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -44627,7 +44627,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1555" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -44653,7 +44653,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1556" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -44679,7 +44679,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1557" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -44705,7 +44705,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G1558" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -44731,7 +44731,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1559" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -44757,7 +44757,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1560" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -44783,7 +44783,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G1561" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -44809,7 +44809,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1562" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -44835,7 +44835,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1563" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -44861,7 +44861,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G1564" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -44887,7 +44887,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1565" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -44913,7 +44913,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1566" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -44939,7 +44939,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1567" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -44965,7 +44965,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1568" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -44991,7 +44991,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1569" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -45017,7 +45017,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G1570" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -45043,7 +45043,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G1571" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -45069,7 +45069,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1572" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -45095,7 +45095,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1573" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -45121,7 +45121,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G1574" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -45147,7 +45147,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G1575" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -45173,7 +45173,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1576" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -45199,7 +45199,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1577" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -45225,7 +45225,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1578" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -45251,7 +45251,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1579" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -45277,7 +45277,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G1580" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -45303,7 +45303,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1581" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -45329,7 +45329,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1582" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -45355,7 +45355,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1583" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -45381,7 +45381,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1584" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -45407,7 +45407,7 @@
         <v>17</v>
       </c>
       <c r="G1585" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -45433,7 +45433,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G1586" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -45459,7 +45459,7 @@
         <v>17.5</v>
       </c>
       <c r="G1587" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -45485,7 +45485,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1588" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -45511,7 +45511,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1589" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -45537,7 +45537,7 @@
         <v>16.5</v>
       </c>
       <c r="G1590" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -45563,7 +45563,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1591" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -45641,7 +45641,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G1594" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -45667,7 +45667,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G1595" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -45719,7 +45719,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1597" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -45771,7 +45771,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G1599" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -45797,7 +45797,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G1600" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -45823,7 +45823,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1601" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -45849,7 +45849,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1602" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -45875,7 +45875,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G1603" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -45901,7 +45901,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1604" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -45927,7 +45927,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1605" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -45953,7 +45953,7 @@
         <v>15.5</v>
       </c>
       <c r="G1606" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -45979,7 +45979,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G1607" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -46005,7 +46005,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1608" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -46057,7 +46057,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G1610" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -46109,7 +46109,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1612" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -46187,7 +46187,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G1615" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -46239,7 +46239,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1617" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -46265,7 +46265,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G1618" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -46291,7 +46291,7 @@
         <v>16.5</v>
       </c>
       <c r="G1619" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -46317,7 +46317,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1620" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -46343,7 +46343,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1621" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -46369,7 +46369,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1622" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -46395,7 +46395,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G1623" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -46421,7 +46421,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1624" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -46447,7 +46447,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1625" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -46473,7 +46473,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1626" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -46499,7 +46499,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1627" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -46525,7 +46525,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1628" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -46551,7 +46551,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G1629" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -46577,7 +46577,7 @@
         <v>18</v>
       </c>
       <c r="G1630" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -46603,7 +46603,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1631" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -46629,7 +46629,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1632" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -46655,7 +46655,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1633" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -46681,7 +46681,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1634" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -46707,7 +46707,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1635" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -46733,7 +46733,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1636" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -46759,7 +46759,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1637" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -46785,7 +46785,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1638" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -46811,7 +46811,7 @@
         <v>17</v>
       </c>
       <c r="G1639" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -46837,7 +46837,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1640" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -46863,7 +46863,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1641" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -46889,7 +46889,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1642" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -46915,7 +46915,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1643" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -46941,7 +46941,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1644" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -46967,7 +46967,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1645" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -46993,7 +46993,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1646" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -47019,7 +47019,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G1647" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -47045,7 +47045,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1648" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -47071,7 +47071,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G1649" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -47097,7 +47097,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1650" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -47123,7 +47123,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G1651" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -47149,7 +47149,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G1652" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -47175,7 +47175,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1653" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -47201,7 +47201,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1654" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -47227,7 +47227,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1655" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -47253,7 +47253,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G1656" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -47279,7 +47279,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1657" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -47305,7 +47305,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1658" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -47331,7 +47331,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1659" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -47357,7 +47357,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G1660" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -47383,7 +47383,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1661" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -47409,7 +47409,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G1662" t="s">
-        <v>821</v>
+        <v>772</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -47487,7 +47487,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1665" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -47513,7 +47513,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1666" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -47539,7 +47539,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G1667" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -47565,7 +47565,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1668" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -47591,7 +47591,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1669" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -48007,7 +48007,7 @@
         <v>18</v>
       </c>
       <c r="G1685" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -48059,7 +48059,7 @@
         <v>18</v>
       </c>
       <c r="G1687" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -48111,7 +48111,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1689" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -48241,7 +48241,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1694" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -48267,7 +48267,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1695" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -48319,7 +48319,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1697" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -48423,7 +48423,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1701" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -48501,7 +48501,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1704" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -48527,7 +48527,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1705" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -48579,7 +48579,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1707" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -48631,7 +48631,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G1709" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -48683,7 +48683,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1711" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -49021,7 +49021,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1724" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -49073,7 +49073,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1726" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -49125,7 +49125,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1728" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -49307,7 +49307,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1735" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -49437,7 +49437,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1740" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -49489,7 +49489,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1742" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -49515,7 +49515,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1743" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -50009,7 +50009,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1762" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -50087,7 +50087,7 @@
         <v>18</v>
       </c>
       <c r="G1765" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -50139,7 +50139,7 @@
         <v>18</v>
       </c>
       <c r="G1767" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -50373,7 +50373,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1776" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -50451,7 +50451,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1779" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -50581,7 +50581,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1784" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -50659,7 +50659,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1787" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -70266,6 +70266,32 @@
         <v>1276</v>
       </c>
       <c r="H2541" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2542">
+      <c r="A2542" s="1" t="n">
+        <v>46024.6910300926</v>
+      </c>
+      <c r="B2542" t="n">
+        <v>22648</v>
+      </c>
+      <c r="C2542" t="n">
+        <v>49.4500007629395</v>
+      </c>
+      <c r="D2542" t="n">
+        <v>47.8499984741211</v>
+      </c>
+      <c r="E2542" t="n">
+        <v>49.4500007629395</v>
+      </c>
+      <c r="F2542" t="n">
+        <v>48.0499992370605</v>
+      </c>
+      <c r="G2542" t="s">
+        <v>1284</v>
+      </c>
+      <c r="H2542" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SOL.MI.xlsx
+++ b/data/SOL.MI.xlsx
@@ -50,22 +50,22 @@
     <t xml:space="preserve">7.18862581253052</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16246891021729</t>
+    <t xml:space="preserve">7.16246938705444</t>
   </si>
   <si>
     <t xml:space="preserve">7.06220388412476</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90962600708008</t>
+    <t xml:space="preserve">6.90962553024292</t>
   </si>
   <si>
     <t xml:space="preserve">6.90526580810547</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94885969161987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71781206130981</t>
+    <t xml:space="preserve">6.94886016845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71781158447266</t>
   </si>
   <si>
     <t xml:space="preserve">6.62626504898071</t>
@@ -74,79 +74,79 @@
     <t xml:space="preserve">6.71345281600952</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29931163787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3647027015686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43009281158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41265535354614</t>
+    <t xml:space="preserve">6.29931116104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36470222473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43009233474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4126558303833</t>
   </si>
   <si>
     <t xml:space="preserve">6.44753074645996</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20776414871216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1728892326355</t>
+    <t xml:space="preserve">6.207763671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17288875579834</t>
   </si>
   <si>
     <t xml:space="preserve">6.46060800552368</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54779577255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38213920593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51292037963867</t>
+    <t xml:space="preserve">6.54779624938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38214015960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51292133331299</t>
   </si>
   <si>
     <t xml:space="preserve">6.50420236587524</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65242195129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80064010620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72217082977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79192161560059</t>
+    <t xml:space="preserve">6.65242052078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80064058303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72217178344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79192209243774</t>
   </si>
   <si>
     <t xml:space="preserve">7.00989151000977</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84423446655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07964134216309</t>
+    <t xml:space="preserve">6.84423351287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07964086532593</t>
   </si>
   <si>
     <t xml:space="preserve">6.88346862792969</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9662971496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08835983276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7352499961853</t>
+    <t xml:space="preserve">6.96629619598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08836030960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73524951934814</t>
   </si>
   <si>
     <t xml:space="preserve">6.8311562538147</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67857837677002</t>
+    <t xml:space="preserve">6.67857694625854</t>
   </si>
   <si>
     <t xml:space="preserve">6.57395267486572</t>
@@ -155,10 +155,10 @@
     <t xml:space="preserve">6.63062429428101</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68729639053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.783203125</t>
+    <t xml:space="preserve">6.68729686737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78320360183716</t>
   </si>
   <si>
     <t xml:space="preserve">6.77884387969971</t>
@@ -167,16 +167,16 @@
     <t xml:space="preserve">6.81371879577637</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80935955047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79628086090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69601488113403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81807804107666</t>
+    <t xml:space="preserve">6.80935907363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79628133773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69601535797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81807851791382</t>
   </si>
   <si>
     <t xml:space="preserve">6.8747501373291</t>
@@ -185,16 +185,16 @@
     <t xml:space="preserve">6.91398429870605</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67421913146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5521559715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46496820449829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43881130218506</t>
+    <t xml:space="preserve">6.67421865463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55215549468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46496725082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43881225585938</t>
   </si>
   <si>
     <t xml:space="preserve">6.73089027404785</t>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">6.87910938262939</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85295248031616</t>
+    <t xml:space="preserve">6.85295343399048</t>
   </si>
   <si>
     <t xml:space="preserve">6.84859418869019</t>
@@ -212,61 +212,61 @@
     <t xml:space="preserve">6.85731220245361</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74832773208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51728010177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37342071533203</t>
+    <t xml:space="preserve">6.74832725524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51728057861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37342119216919</t>
   </si>
   <si>
     <t xml:space="preserve">6.56523418426514</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66985940933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7701244354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86167240142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97501564025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9416298866272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95048427581787</t>
+    <t xml:space="preserve">6.66985988616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77012491226196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86167144775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97501611709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94163036346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9504828453064</t>
   </si>
   <si>
     <t xml:space="preserve">6.88407802581787</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90178680419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34006547927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22496175765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41975069046021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43745994567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36662721633911</t>
+    <t xml:space="preserve">6.90178632736206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34006452560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22495985031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41975116729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43746089935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36662769317627</t>
   </si>
   <si>
     <t xml:space="preserve">7.26037836074829</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46845006942749</t>
+    <t xml:space="preserve">7.46845054626465</t>
   </si>
   <si>
     <t xml:space="preserve">7.40204381942749</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">7.3843355178833</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04345178604126</t>
+    <t xml:space="preserve">7.0434513092041</t>
   </si>
   <si>
     <t xml:space="preserve">6.97261905670166</t>
@@ -287,91 +287,91 @@
     <t xml:space="preserve">7.1098575592041</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8707971572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20725393295288</t>
+    <t xml:space="preserve">6.87079668045044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20725345611572</t>
   </si>
   <si>
     <t xml:space="preserve">7.37105464935303</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57027149200439</t>
+    <t xml:space="preserve">7.57027196884155</t>
   </si>
   <si>
     <t xml:space="preserve">7.69422960281372</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70308446884155</t>
+    <t xml:space="preserve">7.70308351516724</t>
   </si>
   <si>
     <t xml:space="preserve">7.71193885803223</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65881252288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04396629333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61454391479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29579401016235</t>
+    <t xml:space="preserve">7.65881299972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04396915435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61454248428345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2957935333252</t>
   </si>
   <si>
     <t xml:space="preserve">6.99475431442261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10100412368774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55256366729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31350374221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50829315185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42417907714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37548112869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52600145339966</t>
+    <t xml:space="preserve">7.10100364685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55256414413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31350326538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50829267501831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42418003082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37548160552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52600193023682</t>
   </si>
   <si>
     <t xml:space="preserve">7.54371023178101</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41532564163208</t>
+    <t xml:space="preserve">7.41532468795776</t>
   </si>
   <si>
     <t xml:space="preserve">7.21610689163208</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99032688140869</t>
+    <t xml:space="preserve">6.99032735824585</t>
   </si>
   <si>
     <t xml:space="preserve">6.79996395111084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7556939125061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00803518295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26923274993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34449195861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46402406692505</t>
+    <t xml:space="preserve">6.75569248199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00803565979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26923227310181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34449243545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46402311325073</t>
   </si>
   <si>
     <t xml:space="preserve">7.51714706420898</t>
@@ -380,7 +380,7 @@
     <t xml:space="preserve">7.39318990707397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45516872406006</t>
+    <t xml:space="preserve">7.4551682472229</t>
   </si>
   <si>
     <t xml:space="preserve">7.17183685302734</t>
@@ -392,13 +392,13 @@
     <t xml:space="preserve">7.33121109008789</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39761734008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30464887619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27808713912964</t>
+    <t xml:space="preserve">7.39761590957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30464935302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27808618545532</t>
   </si>
   <si>
     <t xml:space="preserve">7.25152349472046</t>
@@ -407,28 +407,28 @@
     <t xml:space="preserve">7.16298246383667</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03017044067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87965106964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91063976287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95491075515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88850450515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95933771133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85751485824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77340173721313</t>
+    <t xml:space="preserve">7.03017139434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87965059280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91064023971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95491123199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88850545883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95933818817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85751581192017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77340221405029</t>
   </si>
   <si>
     <t xml:space="preserve">6.74683904647827</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">6.82652616500854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68486070632935</t>
+    <t xml:space="preserve">6.6848611831665</t>
   </si>
   <si>
     <t xml:space="preserve">6.81767177581787</t>
@@ -446,37 +446,37 @@
     <t xml:space="preserve">6.90621328353882</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01689100265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89735889434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83538055419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86194324493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92392158508301</t>
+    <t xml:space="preserve">7.01689004898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8973593711853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83538007736206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86194276809692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92392206192017</t>
   </si>
   <si>
     <t xml:space="preserve">6.97704601287842</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00360822677612</t>
+    <t xml:space="preserve">7.00360870361328</t>
   </si>
   <si>
     <t xml:space="preserve">6.91506719589233</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91949415206909</t>
+    <t xml:space="preserve">6.91949462890625</t>
   </si>
   <si>
     <t xml:space="preserve">6.93720245361328</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07001399993896</t>
+    <t xml:space="preserve">7.07001495361328</t>
   </si>
   <si>
     <t xml:space="preserve">6.98590040206909</t>
@@ -491,10 +491,10 @@
     <t xml:space="preserve">6.64944362640381</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38382005691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37053918838501</t>
+    <t xml:space="preserve">6.38381958007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37053966522217</t>
   </si>
   <si>
     <t xml:space="preserve">6.36168479919434</t>
@@ -503,16 +503,16 @@
     <t xml:space="preserve">6.37939310073853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40595531463623</t>
+    <t xml:space="preserve">6.40595579147339</t>
   </si>
   <si>
     <t xml:space="preserve">6.4812159538269</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47678804397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54319429397583</t>
+    <t xml:space="preserve">6.47678756713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54319477081299</t>
   </si>
   <si>
     <t xml:space="preserve">6.46350765228271</t>
@@ -521,19 +521,19 @@
     <t xml:space="preserve">6.24215459823608</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25986242294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22444581985474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64501667022705</t>
+    <t xml:space="preserve">6.25986289978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22444677352905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64501714706421</t>
   </si>
   <si>
     <t xml:space="preserve">6.64058971405029</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0390248298645</t>
+    <t xml:space="preserve">7.03902435302734</t>
   </si>
   <si>
     <t xml:space="preserve">6.79111003875732</t>
@@ -542,13 +542,13 @@
     <t xml:space="preserve">6.70256853103638</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70699548721313</t>
+    <t xml:space="preserve">6.70699501037598</t>
   </si>
   <si>
     <t xml:space="preserve">6.65829753875732</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58303833007812</t>
+    <t xml:space="preserve">6.58303737640381</t>
   </si>
   <si>
     <t xml:space="preserve">7.05673360824585</t>
@@ -557,10 +557,10 @@
     <t xml:space="preserve">7.11428546905518</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34891891479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18511819839478</t>
+    <t xml:space="preserve">7.34891939163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18511772155762</t>
   </si>
   <si>
     <t xml:space="preserve">7.12756681442261</t>
@@ -572,46 +572,46 @@
     <t xml:space="preserve">7.24267053604126</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41089773178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48173046112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14527463912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27365875244141</t>
+    <t xml:space="preserve">7.41089820861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48173141479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14527416229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27365922927856</t>
   </si>
   <si>
     <t xml:space="preserve">7.1762638092041</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04787921905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23381567001343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29136610031128</t>
+    <t xml:space="preserve">7.04787969589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23381614685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29136753082275</t>
   </si>
   <si>
     <t xml:space="preserve">7.42860698699951</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83589553833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8270411491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13693523406982</t>
+    <t xml:space="preserve">7.83589601516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82704162597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13693618774414</t>
   </si>
   <si>
     <t xml:space="preserve">8.27860164642334</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32287120819092</t>
+    <t xml:space="preserve">8.32287311553955</t>
   </si>
   <si>
     <t xml:space="preserve">9.03120136260986</t>
@@ -620,22 +620,22 @@
     <t xml:space="preserve">8.53094387054443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49995517730713</t>
+    <t xml:space="preserve">8.49995613098145</t>
   </si>
   <si>
     <t xml:space="preserve">8.26089286804199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92495346069336</t>
+    <t xml:space="preserve">8.92495250701904</t>
   </si>
   <si>
     <t xml:space="preserve">8.58849620819092</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97807693481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7655782699585</t>
+    <t xml:space="preserve">8.97807788848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76557731628418</t>
   </si>
   <si>
     <t xml:space="preserve">8.87182807922363</t>
@@ -647,7 +647,7 @@
     <t xml:space="preserve">9.25255584716797</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02234554290771</t>
+    <t xml:space="preserve">9.02234840393066</t>
   </si>
   <si>
     <t xml:space="preserve">8.85411930084229</t>
@@ -662,19 +662,19 @@
     <t xml:space="preserve">8.98693180084229</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8983907699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80984973907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72130870819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78328704833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67703914642334</t>
+    <t xml:space="preserve">8.89838981628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80984878540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72130680084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78328514099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67703723907471</t>
   </si>
   <si>
     <t xml:space="preserve">8.75672435760498</t>
@@ -683,46 +683,46 @@
     <t xml:space="preserve">9.10203456878662</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8231315612793</t>
+    <t xml:space="preserve">8.82312965393066</t>
   </si>
   <si>
     <t xml:space="preserve">8.94266128540039</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20828342437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43287563323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45982646942139</t>
+    <t xml:space="preserve">9.20828533172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43287658691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4598274230957</t>
   </si>
   <si>
     <t xml:space="preserve">9.52271366119385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32507228851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38795757293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35202312469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4238920211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29812240600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55865001678467</t>
+    <t xml:space="preserve">9.3250732421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3879566192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35202217102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42389297485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29812145233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55864906311035</t>
   </si>
   <si>
     <t xml:space="preserve">9.67543601989746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86409473419189</t>
+    <t xml:space="preserve">9.86409378051758</t>
   </si>
   <si>
     <t xml:space="preserve">10.5199031829834</t>
@@ -743,37 +743,37 @@
     <t xml:space="preserve">9.44186115264893</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54067993164062</t>
+    <t xml:space="preserve">9.54068183898926</t>
   </si>
   <si>
     <t xml:space="preserve">9.34303951263428</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36100482940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50474452972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48677921295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61254978179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77425670623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46881294250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54966354370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47779560089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70238780975342</t>
+    <t xml:space="preserve">9.36100769042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50474548339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48677825927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61255264282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77425575256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46881198883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54966449737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4777946472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7023868560791</t>
   </si>
   <si>
     <t xml:space="preserve">9.30710506439209</t>
@@ -782,22 +782,22 @@
     <t xml:space="preserve">9.28015327453613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2172679901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16336631774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25320243835449</t>
+    <t xml:space="preserve">9.21726703643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16336536407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25320339202881</t>
   </si>
   <si>
     <t xml:space="preserve">9.45084476470947</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58560085296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33405685424805</t>
+    <t xml:space="preserve">9.58559894561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33405590057373</t>
   </si>
   <si>
     <t xml:space="preserve">9.59458351135254</t>
@@ -806,76 +806,76 @@
     <t xml:space="preserve">9.66645240783691</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71137046813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40592670440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26218795776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27116966247559</t>
+    <t xml:space="preserve">9.71137142181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40592575073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26218605041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2711706161499</t>
   </si>
   <si>
     <t xml:space="preserve">9.289137840271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36999034881592</t>
+    <t xml:space="preserve">9.36999130249023</t>
   </si>
   <si>
     <t xml:space="preserve">9.65746974945068</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7922248840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76527309417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72035503387451</t>
+    <t xml:space="preserve">9.79222393035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76527214050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72035312652588</t>
   </si>
   <si>
     <t xml:space="preserve">9.81019115447998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37897396087646</t>
+    <t xml:space="preserve">9.37897300720215</t>
   </si>
   <si>
     <t xml:space="preserve">9.90901279449463</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81917572021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73832130432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78324127197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69340324401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11844730377197</t>
+    <t xml:space="preserve">9.81917476654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73832225799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78324031829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69340419769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11844635009766</t>
   </si>
   <si>
     <t xml:space="preserve">9.08251190185547</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31608772277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19031524658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1004810333252</t>
+    <t xml:space="preserve">9.31608867645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19031620025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10047912597656</t>
   </si>
   <si>
     <t xml:space="preserve">9.22625255584717</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41491031646729</t>
+    <t xml:space="preserve">9.41490840911865</t>
   </si>
   <si>
     <t xml:space="preserve">9.39694213867188</t>
@@ -884,19 +884,19 @@
     <t xml:space="preserve">9.07352924346924</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57661437988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68441963195801</t>
+    <t xml:space="preserve">9.57661533355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68442058563232</t>
   </si>
   <si>
     <t xml:space="preserve">9.09149551391602</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05556297302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14539813995361</t>
+    <t xml:space="preserve">9.05556201934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1453971862793</t>
   </si>
   <si>
     <t xml:space="preserve">8.89385414123535</t>
@@ -905,25 +905,25 @@
     <t xml:space="preserve">9.10946369171143</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23523616790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95392990112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5109195709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7444972991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.546854019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6905918121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9062032699585</t>
+    <t xml:space="preserve">9.23523330688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95393085479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5109205245972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7444953918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5468530654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6905927658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9062013626099</t>
   </si>
   <si>
     <t xml:space="preserve">10.7804307937622</t>
@@ -935,10 +935,10 @@
     <t xml:space="preserve">10.6546583175659</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5288877487183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4390506744385</t>
+    <t xml:space="preserve">10.5288896560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4390487670898</t>
   </si>
   <si>
     <t xml:space="preserve">10.3312454223633</t>
@@ -947,16 +947,16 @@
     <t xml:space="preserve">10.1695394515991</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1875076293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1336030960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7562894821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63051795959473</t>
+    <t xml:space="preserve">10.1875066757202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1336040496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75629043579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63051700592041</t>
   </si>
   <si>
     <t xml:space="preserve">10.007833480835</t>
@@ -968,85 +968,85 @@
     <t xml:space="preserve">10.0976705551147</t>
   </si>
   <si>
-    <t xml:space="preserve">10.205472946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2773427963257</t>
+    <t xml:space="preserve">10.2054719924927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2773447036743</t>
   </si>
   <si>
     <t xml:space="preserve">10.2234420776367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2414083480835</t>
+    <t xml:space="preserve">10.2414102554321</t>
   </si>
   <si>
     <t xml:space="preserve">10.7624626159668</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2593774795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91799545288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90002822875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67380619049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74667835235596</t>
+    <t xml:space="preserve">10.2593765258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91799449920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90002918243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67380809783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74668025970459</t>
   </si>
   <si>
     <t xml:space="preserve">9.87420463562012</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1656942367554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85598850250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63736915588379</t>
+    <t xml:space="preserve">10.1656951904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85598659515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63737010955811</t>
   </si>
   <si>
     <t xml:space="preserve">9.47340679168701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76489734649658</t>
+    <t xml:space="preserve">9.76489639282227</t>
   </si>
   <si>
     <t xml:space="preserve">9.96529674530029</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0746059417725</t>
+    <t xml:space="preserve">10.0746049880981</t>
   </si>
   <si>
     <t xml:space="preserve">10.2385683059692</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3843116760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.420747756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8033285140991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6940202713013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6211471557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7851095199585</t>
+    <t xml:space="preserve">10.384313583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4207487106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8033275604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.694019317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6211462020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7851104736328</t>
   </si>
   <si>
     <t xml:space="preserve">10.5482740402222</t>
   </si>
   <si>
-    <t xml:space="preserve">10.402530670166</t>
+    <t xml:space="preserve">10.4025297164917</t>
   </si>
   <si>
     <t xml:space="preserve">10.2203493118286</t>
@@ -1055,7 +1055,7 @@
     <t xml:space="preserve">10.1474781036377</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3296585083008</t>
+    <t xml:space="preserve">10.3296566009521</t>
   </si>
   <si>
     <t xml:space="preserve">10.5847120285034</t>
@@ -1064,28 +1064,28 @@
     <t xml:space="preserve">10.3478746414185</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72846221923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56449794769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4187536239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40053462982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54627990722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1110410690308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2567863464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92886066436768</t>
+    <t xml:space="preserve">9.72846126556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56449890136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41875457763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40053558349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54627895355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1110401153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2567853927612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92885875701904</t>
   </si>
   <si>
     <t xml:space="preserve">10.0199499130249</t>
@@ -1094,85 +1094,85 @@
     <t xml:space="preserve">10.202130317688</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0928220748901</t>
+    <t xml:space="preserve">10.0928230285645</t>
   </si>
   <si>
     <t xml:space="preserve">9.8013334274292</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69202613830566</t>
+    <t xml:space="preserve">9.69202518463135</t>
   </si>
   <si>
     <t xml:space="preserve">9.83776950836182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94707679748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89242267608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65558815002441</t>
+    <t xml:space="preserve">9.94707775115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89242458343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65558910369873</t>
   </si>
   <si>
     <t xml:space="preserve">9.78311443328857</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91064262390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45518970489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2001371383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50984382629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43697166442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81955051422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.491623878479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61915302276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9835147857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6009349822998</t>
+    <t xml:space="preserve">9.91064167022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45519065856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20013618469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50984287261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43697071075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81955146789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49162673950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6191520690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98351287841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60093402862549</t>
   </si>
   <si>
     <t xml:space="preserve">9.10904598236084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09993553161621</t>
+    <t xml:space="preserve">9.09993648529053</t>
   </si>
   <si>
     <t xml:space="preserve">9.38231658935547</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36409950256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27300930023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71024131774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5827169418335</t>
+    <t xml:space="preserve">9.36409759521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27300834655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71024227142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58271598815918</t>
   </si>
   <si>
     <t xml:space="preserve">9.29122734069824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14548110961914</t>
+    <t xml:space="preserve">9.14548206329346</t>
   </si>
   <si>
     <t xml:space="preserve">10.3660945892334</t>
@@ -1181,31 +1181,31 @@
     <t xml:space="preserve">9.32766246795654</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0017328262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4754028320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8397626876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5664920806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3114395141602</t>
+    <t xml:space="preserve">10.0017318725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4754018783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8397645950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5664930343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3114404678345</t>
   </si>
   <si>
     <t xml:space="preserve">10.2932224273682</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0381679534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0563859939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1292591094971</t>
+    <t xml:space="preserve">10.0381698608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0563850402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1292581558228</t>
   </si>
   <si>
     <t xml:space="preserve">10.2750024795532</t>
@@ -1217,7 +1217,7 @@
     <t xml:space="preserve">10.675802230835</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7122373580933</t>
+    <t xml:space="preserve">10.7122383117676</t>
   </si>
   <si>
     <t xml:space="preserve">10.9308557510376</t>
@@ -1226,19 +1226,19 @@
     <t xml:space="preserve">11.0219440460205</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8762006759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.894419670105</t>
+    <t xml:space="preserve">10.87619972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8944187164307</t>
   </si>
   <si>
     <t xml:space="preserve">10.7304553985596</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6575832366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2644634246826</t>
+    <t xml:space="preserve">10.6575841903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2644643783569</t>
   </si>
   <si>
     <t xml:space="preserve">11.1349859237671</t>
@@ -1253,10 +1253,10 @@
     <t xml:space="preserve">11.319953918457</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0240058898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8205432891846</t>
+    <t xml:space="preserve">11.0240068435669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8205442428589</t>
   </si>
   <si>
     <t xml:space="preserve">10.8390417098999</t>
@@ -1265,31 +1265,31 @@
     <t xml:space="preserve">10.7280607223511</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8575372695923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7095632553101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.672571182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.65407371521</t>
+    <t xml:space="preserve">10.857536315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7095623016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6725702285767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6540746688843</t>
   </si>
   <si>
     <t xml:space="preserve">10.7835493087769</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7650537490845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8020467758179</t>
+    <t xml:space="preserve">10.7650547027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8020477294922</t>
   </si>
   <si>
     <t xml:space="preserve">10.5615901947021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6170797348022</t>
+    <t xml:space="preserve">10.6170806884766</t>
   </si>
   <si>
     <t xml:space="preserve">10.3951206207275</t>
@@ -1301,22 +1301,22 @@
     <t xml:space="preserve">10.2841396331787</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2656440734863</t>
+    <t xml:space="preserve">10.265643119812</t>
   </si>
   <si>
     <t xml:space="preserve">10.302638053894</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5061006546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3396310806274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1361675262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0806789398193</t>
+    <t xml:space="preserve">10.5060997009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3396301269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1361665725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0806770324707</t>
   </si>
   <si>
     <t xml:space="preserve">9.98819351196289</t>
@@ -1328,19 +1328,19 @@
     <t xml:space="preserve">9.93270397186279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89571094512939</t>
+    <t xml:space="preserve">9.89571189880371</t>
   </si>
   <si>
     <t xml:space="preserve">9.96969795227051</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1731605529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0621814727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1546630859375</t>
+    <t xml:space="preserve">10.1731595993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.062180519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1546640396118</t>
   </si>
   <si>
     <t xml:space="preserve">9.71074390411377</t>
@@ -1349,31 +1349,31 @@
     <t xml:space="preserve">10.0251865386963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91420841217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76623439788818</t>
+    <t xml:space="preserve">9.91420650482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76623344421387</t>
   </si>
   <si>
     <t xml:space="preserve">9.72924137115479</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65525245666504</t>
+    <t xml:space="preserve">9.65525341033936</t>
   </si>
   <si>
     <t xml:space="preserve">9.67375087738037</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47028732299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54427337646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56277084350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45179176330566</t>
+    <t xml:space="preserve">9.47028827667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54427433013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56277179718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45179080963135</t>
   </si>
   <si>
     <t xml:space="preserve">9.35930824279785</t>
@@ -1382,13 +1382,13 @@
     <t xml:space="preserve">9.52577781677246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59976387023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61826133728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69224834442139</t>
+    <t xml:space="preserve">9.59976482391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61826038360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69224643707275</t>
   </si>
   <si>
     <t xml:space="preserve">9.8032283782959</t>
@@ -1400,22 +1400,22 @@
     <t xml:space="preserve">9.78472995758057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85871696472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0066909790039</t>
+    <t xml:space="preserve">9.858717918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0066900253296</t>
   </si>
   <si>
     <t xml:space="preserve">9.8772144317627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74773788452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58126831054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3211336135864</t>
+    <t xml:space="preserve">9.74773693084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58126735687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3211345672607</t>
   </si>
   <si>
     <t xml:space="preserve">10.4321136474609</t>
@@ -1427,22 +1427,22 @@
     <t xml:space="preserve">10.2471466064453</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2101535797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8402214050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63675689697266</t>
+    <t xml:space="preserve">10.2101526260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84022045135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63675785064697</t>
   </si>
   <si>
     <t xml:space="preserve">9.43329429626465</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41479778289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39630031585693</t>
+    <t xml:space="preserve">9.41479682922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39630222320557</t>
   </si>
   <si>
     <t xml:space="preserve">9.24832725524902</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">9.28532028198242</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26682472229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19283771514893</t>
+    <t xml:space="preserve">9.26682376861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19283676147461</t>
   </si>
   <si>
     <t xml:space="preserve">9.22982978820801</t>
@@ -1472,22 +1472,22 @@
     <t xml:space="preserve">9.48878383636475</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0263671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97087860107422</t>
+    <t xml:space="preserve">9.02636814117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9708776473999</t>
   </si>
   <si>
     <t xml:space="preserve">9.13734817504883</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96162986755371</t>
+    <t xml:space="preserve">8.96162891387939</t>
   </si>
   <si>
     <t xml:space="preserve">8.82290458679199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61944103240967</t>
+    <t xml:space="preserve">8.61944198608398</t>
   </si>
   <si>
     <t xml:space="preserve">8.55470275878906</t>
@@ -1496,70 +1496,70 @@
     <t xml:space="preserve">8.36048889160156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33274269104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01830005645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81483697891235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95356369018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49114561080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86107778549194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50964212417603</t>
+    <t xml:space="preserve">8.33274364471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0182991027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81483745574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95356178283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49114608764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86108016967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50964164733887</t>
   </si>
   <si>
     <t xml:space="preserve">7.53738689422607</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58362913131714</t>
+    <t xml:space="preserve">7.58362865447998</t>
   </si>
   <si>
     <t xml:space="preserve">8.76741409301758</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98937511444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16509342193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12810134887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09110546112061</t>
+    <t xml:space="preserve">8.9893741607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16509246826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12809944152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09110641479492</t>
   </si>
   <si>
     <t xml:space="preserve">9.08185768127441</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34081172943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04486465454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21133518218994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38705253601074</t>
+    <t xml:space="preserve">9.34081077575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0448637008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21133422851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38705158233643</t>
   </si>
   <si>
     <t xml:space="preserve">9.17434120178223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29457092285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11885166168213</t>
+    <t xml:space="preserve">9.29456901550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11885070800781</t>
   </si>
   <si>
     <t xml:space="preserve">8.78591060638428</t>
@@ -1568,16 +1568,16 @@
     <t xml:space="preserve">8.89689064025879</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7489185333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80440902709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87839508056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93388557434082</t>
+    <t xml:space="preserve">8.74891757965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80440807342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87839603424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9338846206665</t>
   </si>
   <si>
     <t xml:space="preserve">8.63793754577637</t>
@@ -1589,16 +1589,16 @@
     <t xml:space="preserve">8.58244895935059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69342708587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46113967895508</t>
+    <t xml:space="preserve">8.69342803955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46114063262939</t>
   </si>
   <si>
     <t xml:space="preserve">9.6494197845459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69649124145508</t>
+    <t xml:space="preserve">9.69649219512939</t>
   </si>
   <si>
     <t xml:space="preserve">9.74356079101562</t>
@@ -1607,7 +1607,7 @@
     <t xml:space="preserve">9.97891330718994</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93184280395508</t>
+    <t xml:space="preserve">9.93184375762939</t>
   </si>
   <si>
     <t xml:space="preserve">9.7906322479248</t>
@@ -1616,10 +1616,10 @@
     <t xml:space="preserve">10.0730543136597</t>
   </si>
   <si>
-    <t xml:space="preserve">10.308403968811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4496164321899</t>
+    <t xml:space="preserve">10.3084049224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4496173858643</t>
   </si>
   <si>
     <t xml:space="preserve">10.1671953201294</t>
@@ -1631,19 +1631,19 @@
     <t xml:space="preserve">10.0259828567505</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2142639160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3554754257202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2613344192505</t>
+    <t xml:space="preserve">10.2142648696899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3554763793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2613353729248</t>
   </si>
   <si>
     <t xml:space="preserve">9.88477230072021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5908269882202</t>
+    <t xml:space="preserve">10.5908279418945</t>
   </si>
   <si>
     <t xml:space="preserve">10.4966869354248</t>
@@ -1658,13 +1658,13 @@
     <t xml:space="preserve">11.1556720733643</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9673910140991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0615310668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7791080474854</t>
+    <t xml:space="preserve">10.9673900604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0615301132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7791090011597</t>
   </si>
   <si>
     <t xml:space="preserve">10.8261785507202</t>
@@ -1676,13 +1676,13 @@
     <t xml:space="preserve">11.1086015701294</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9203195571899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8732490539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7320384979248</t>
+    <t xml:space="preserve">10.9203205108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8732500076294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7320394515991</t>
   </si>
   <si>
     <t xml:space="preserve">10.6378984451294</t>
@@ -1694,10 +1694,10 @@
     <t xml:space="preserve">11.6263751983643</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7675857543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8146562576294</t>
+    <t xml:space="preserve">11.7675867080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8146572113037</t>
   </si>
   <si>
     <t xml:space="preserve">11.5793046951294</t>
@@ -1712,28 +1712,28 @@
     <t xml:space="preserve">12.0029382705688</t>
   </si>
   <si>
-    <t xml:space="preserve">12.285361289978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5677814483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5207109451294</t>
+    <t xml:space="preserve">12.2853603363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5677824020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5207118988037</t>
   </si>
   <si>
     <t xml:space="preserve">12.897274017334</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7560634613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6619215011597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6148509979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8031339645386</t>
+    <t xml:space="preserve">12.7560625076294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.661922454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6148519515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8031330108643</t>
   </si>
   <si>
     <t xml:space="preserve">12.8502035140991</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">12.9914150238037</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1796970367432</t>
+    <t xml:space="preserve">13.1796960830688</t>
   </si>
   <si>
     <t xml:space="preserve">13.4621181488037</t>
@@ -1751,16 +1751,16 @@
     <t xml:space="preserve">13.838680267334</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7445411682129</t>
+    <t xml:space="preserve">13.7445421218872</t>
   </si>
   <si>
     <t xml:space="preserve">13.6504001617432</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5091886520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7916097640991</t>
+    <t xml:space="preserve">13.5091896057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7916107177734</t>
   </si>
   <si>
     <t xml:space="preserve">13.8857517242432</t>
@@ -1769,16 +1769,16 @@
     <t xml:space="preserve">13.9798927307129</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0269622802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0740327835083</t>
+    <t xml:space="preserve">14.0269632339478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.074031829834</t>
   </si>
   <si>
     <t xml:space="preserve">14.168173789978</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1211042404175</t>
+    <t xml:space="preserve">14.1211032867432</t>
   </si>
   <si>
     <t xml:space="preserve">14.2623138427734</t>
@@ -1787,7 +1787,7 @@
     <t xml:space="preserve">14.2152452468872</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4505958557129</t>
+    <t xml:space="preserve">14.4505968093872</t>
   </si>
   <si>
     <t xml:space="preserve">14.6859474182129</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">14.3093852996826</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4035243988037</t>
+    <t xml:space="preserve">14.403525352478</t>
   </si>
   <si>
     <t xml:space="preserve">14.3564548492432</t>
@@ -1814,10 +1814,10 @@
     <t xml:space="preserve">14.7800874710083</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8271579742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8742275238037</t>
+    <t xml:space="preserve">14.8271589279175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.874228477478</t>
   </si>
   <si>
     <t xml:space="preserve">14.7330169677734</t>
@@ -1826,10 +1826,10 @@
     <t xml:space="preserve">15.3449306488037</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7685661315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0039176940918</t>
+    <t xml:space="preserve">15.7685670852661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0039157867432</t>
   </si>
   <si>
     <t xml:space="preserve">16.0415725708008</t>
@@ -1841,22 +1841,22 @@
     <t xml:space="preserve">16.1921977996826</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1168842315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2298564910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3804779052734</t>
+    <t xml:space="preserve">16.116886138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2298545837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3804798126221</t>
   </si>
   <si>
     <t xml:space="preserve">16.3993091583252</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4181365966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5311031341553</t>
+    <t xml:space="preserve">16.4181346893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5311050415039</t>
   </si>
   <si>
     <t xml:space="preserve">16.2675094604492</t>
@@ -1874,82 +1874,79 @@
     <t xml:space="preserve">15.9662599563599</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7214975357056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5332126617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.51438331604</t>
+    <t xml:space="preserve">15.7214956283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5332136154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5143852233887</t>
   </si>
   <si>
     <t xml:space="preserve">15.7026662826538</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2696199417114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4767293930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6838388442993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6650094985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4202432632446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1566514968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2319641113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7779769897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9833707809448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9643001556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6209802627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4874687194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7926406860352</t>
+    <t xml:space="preserve">15.2696189880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4767284393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6838369369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6650104522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4202442169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1566505432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2319631576538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7779788970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9833726882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.964301109314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6209812164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4874696731567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7926397323608</t>
   </si>
   <si>
     <t xml:space="preserve">15.8117141723633</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6019086837769</t>
+    <t xml:space="preserve">15.6019096374512</t>
   </si>
   <si>
     <t xml:space="preserve">15.5446872711182</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2585897445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6972732543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8307876586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.116886138916</t>
+    <t xml:space="preserve">15.2585906982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6972723007202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8307867050171</t>
   </si>
   <si>
     <t xml:space="preserve">16.2503986358643</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2313251495361</t>
+    <t xml:space="preserve">16.2313270568848</t>
   </si>
   <si>
     <t xml:space="preserve">16.0024471282959</t>
@@ -1958,16 +1955,16 @@
     <t xml:space="preserve">16.2694721221924</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2122535705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.460205078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4411334991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5364990234375</t>
+    <t xml:space="preserve">16.212251663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4602069854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4411315917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5364952087402</t>
   </si>
   <si>
     <t xml:space="preserve">16.555570602417</t>
@@ -1976,10 +1973,10 @@
     <t xml:space="preserve">17.1659126281738</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9561100006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2231349945068</t>
+    <t xml:space="preserve">16.9561080932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2231330871582</t>
   </si>
   <si>
     <t xml:space="preserve">17.3185005187988</t>
@@ -1988,28 +1985,28 @@
     <t xml:space="preserve">17.0896224975586</t>
   </si>
   <si>
-    <t xml:space="preserve">16.841667175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.746301651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9751796722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1277675628662</t>
+    <t xml:space="preserve">16.8416690826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7463035583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9751815795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1277656555176</t>
   </si>
   <si>
     <t xml:space="preserve">17.5092334747314</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5473785400391</t>
+    <t xml:space="preserve">17.5473804473877</t>
   </si>
   <si>
     <t xml:space="preserve">17.7571830749512</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6427459716797</t>
+    <t xml:space="preserve">17.6427440643311</t>
   </si>
   <si>
     <t xml:space="preserve">17.7381134033203</t>
@@ -2018,28 +2015,28 @@
     <t xml:space="preserve">17.4901580810547</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4710865020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3375720977783</t>
+    <t xml:space="preserve">17.4710845947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.337574005127</t>
   </si>
   <si>
     <t xml:space="preserve">17.2994251251221</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3566455841064</t>
+    <t xml:space="preserve">17.3566474914551</t>
   </si>
   <si>
     <t xml:space="preserve">17.2422065734863</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1468410491943</t>
+    <t xml:space="preserve">17.1468391418457</t>
   </si>
   <si>
     <t xml:space="preserve">17.0133266448975</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4520111083984</t>
+    <t xml:space="preserve">17.4520130157471</t>
   </si>
   <si>
     <t xml:space="preserve">17.8334789276123</t>
@@ -2048,10 +2045,10 @@
     <t xml:space="preserve">17.6999645233154</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8716239929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8525485992432</t>
+    <t xml:space="preserve">17.8716220855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8525505065918</t>
   </si>
   <si>
     <t xml:space="preserve">18.0242099761963</t>
@@ -2063,13 +2060,13 @@
     <t xml:space="preserve">18.5010395050049</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6536254882812</t>
+    <t xml:space="preserve">18.6536273956299</t>
   </si>
   <si>
     <t xml:space="preserve">18.5964069366455</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5582580566406</t>
+    <t xml:space="preserve">18.5582599639893</t>
   </si>
   <si>
     <t xml:space="preserve">18.7108478546143</t>
@@ -2087,7 +2084,7 @@
     <t xml:space="preserve">19.5023880004883</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8838500976562</t>
+    <t xml:space="preserve">19.8838520050049</t>
   </si>
   <si>
     <t xml:space="preserve">19.9792175292969</t>
@@ -2096,19 +2093,19 @@
     <t xml:space="preserve">19.4547023773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3593330383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1686038970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7871398925781</t>
+    <t xml:space="preserve">19.3593349456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1686058044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7871417999268</t>
   </si>
   <si>
     <t xml:space="preserve">18.6917743682861</t>
   </si>
   <si>
-    <t xml:space="preserve">19.216287612915</t>
+    <t xml:space="preserve">19.2162857055664</t>
   </si>
   <si>
     <t xml:space="preserve">19.1209201812744</t>
@@ -2123,28 +2120,28 @@
     <t xml:space="preserve">18.1195755004883</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6236686706543</t>
+    <t xml:space="preserve">17.6236705780029</t>
   </si>
   <si>
     <t xml:space="preserve">17.890697479248</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1005020141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2530879974365</t>
+    <t xml:space="preserve">18.1005001068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2530860900879</t>
   </si>
   <si>
     <t xml:space="preserve">17.9669895172119</t>
   </si>
   <si>
-    <t xml:space="preserve">18.176794052124</t>
+    <t xml:space="preserve">18.1767959594727</t>
   </si>
   <si>
     <t xml:space="preserve">18.9969444274902</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0732364654541</t>
+    <t xml:space="preserve">19.0732383728027</t>
   </si>
   <si>
     <t xml:space="preserve">18.9778709411621</t>
@@ -2156,7 +2153,7 @@
     <t xml:space="preserve">18.9397258758545</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9015769958496</t>
+    <t xml:space="preserve">18.9015789031982</t>
   </si>
   <si>
     <t xml:space="preserve">20.0268993377686</t>
@@ -2165,22 +2162,22 @@
     <t xml:space="preserve">20.2176322937012</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2653141021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7421455383301</t>
+    <t xml:space="preserve">20.2653160095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7421474456787</t>
   </si>
   <si>
     <t xml:space="preserve">20.9328804016113</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2189769744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4573917388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6944618225098</t>
+    <t xml:space="preserve">21.2189788818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4573936462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6944637298584</t>
   </si>
   <si>
     <t xml:space="preserve">20.3129978179932</t>
@@ -2189,7 +2186,7 @@
     <t xml:space="preserve">20.4560489654541</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9805603027344</t>
+    <t xml:space="preserve">20.980562210083</t>
   </si>
   <si>
     <t xml:space="preserve">19.8361682891846</t>
@@ -2198,22 +2195,22 @@
     <t xml:space="preserve">20.4083652496338</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1222667694092</t>
+    <t xml:space="preserve">20.1222686767578</t>
   </si>
   <si>
     <t xml:space="preserve">19.3116550445557</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2639694213867</t>
+    <t xml:space="preserve">19.2639713287354</t>
   </si>
   <si>
     <t xml:space="preserve">19.5977516174316</t>
   </si>
   <si>
-    <t xml:space="preserve">19.645435333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1699466705322</t>
+    <t xml:space="preserve">19.6454372406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1699485778809</t>
   </si>
   <si>
     <t xml:space="preserve">19.9315338134766</t>
@@ -2222,16 +2219,16 @@
     <t xml:space="preserve">19.7408008575439</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8443584442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0160179138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0432815551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0051364898682</t>
+    <t xml:space="preserve">18.8443603515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.016019821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0432834625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0051345825195</t>
   </si>
   <si>
     <t xml:space="preserve">18.1386489868164</t>
@@ -2240,25 +2237,25 @@
     <t xml:space="preserve">18.0623569488525</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0814266204834</t>
+    <t xml:space="preserve">18.081428527832</t>
   </si>
   <si>
     <t xml:space="preserve">17.6045970916748</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2612800598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0514755249023</t>
+    <t xml:space="preserve">17.2612819671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0514736175537</t>
   </si>
   <si>
     <t xml:space="preserve">16.2885456085205</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0324001312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7272319793701</t>
+    <t xml:space="preserve">17.0324020385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7272300720215</t>
   </si>
   <si>
     <t xml:space="preserve">16.4792766571045</t>
@@ -2267,7 +2264,7 @@
     <t xml:space="preserve">16.8225936889648</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0705471038818</t>
+    <t xml:space="preserve">17.0705490112305</t>
   </si>
   <si>
     <t xml:space="preserve">16.6509342193604</t>
@@ -2276,16 +2273,16 @@
     <t xml:space="preserve">16.8607425689697</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3076190948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5937156677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6318645477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.277663230896</t>
+    <t xml:space="preserve">16.3076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5937175750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6318626403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2776641845703</t>
   </si>
   <si>
     <t xml:space="preserve">14.8771257400513</t>
@@ -2294,192 +2291,195 @@
     <t xml:space="preserve">14.4956607818604</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3730297088623</t>
+    <t xml:space="preserve">15.3730316162109</t>
   </si>
   <si>
     <t xml:space="preserve">14.9915647506714</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0869302749634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.678201675415</t>
+    <t xml:space="preserve">15.0869312286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6782007217407</t>
   </si>
   <si>
     <t xml:space="preserve">15.1441507339478</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9452257156372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0787391662598</t>
+    <t xml:space="preserve">15.9452247619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0787410736084</t>
   </si>
   <si>
     <t xml:space="preserve">16.0405921936035</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5746421813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6890811920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5174217224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.498348236084</t>
+    <t xml:space="preserve">16.5746440887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6890850067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5174236297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4983501434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7354211807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8880052566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5065412521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9724912643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3348827362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2204427719116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9152717590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.781759262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8961992263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6400547027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0978126525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2395153045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1060047149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0063877105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1999359130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3547744750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0450973510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1418704986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2773532867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4709033966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7805767059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1483173370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.767671585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.419282913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2321853637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7289600372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9418659210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4967041015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5934791564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4579963684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8967037200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4515476226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9870338439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8321962356567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9483232498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3676805496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4450988769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1741333007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1160688400269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.135422706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3289709091187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.619291305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8902597427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7547750473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8128395080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.161226272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6580018997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.870903968811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4128360748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4321899414062</t>
   </si>
   <si>
     <t xml:space="preserve">15.7354202270508</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8880071640015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5065412521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9724912643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3348836898804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2204437255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9152727127075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.781759262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8961992263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6400547027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0978126525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2395162582397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1060047149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0063896179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1999359130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3547744750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0450973510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1418704986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2773532867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4709014892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7805786132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1483173370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.767671585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4192848205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2321834564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7289619445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9418640136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4967041015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5934772491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4579944610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8967056274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4515476226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9870338439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8321952819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9483222961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3676795959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4450988769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1741333007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1160678863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1354236602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3289709091187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.619291305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8902606964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7547760009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.812840461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.161226272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6580018997192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.870903968811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4128360748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4321918487549</t>
-  </si>
-  <si>
     <t xml:space="preserve">15.7160663604736</t>
   </si>
   <si>
@@ -2501,10 +2501,10 @@
     <t xml:space="preserve">17.5354137420654</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3805751800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3418655395508</t>
+    <t xml:space="preserve">17.3805732727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3418674468994</t>
   </si>
   <si>
     <t xml:space="preserve">17.2063827514648</t>
@@ -2528,16 +2528,16 @@
     <t xml:space="preserve">17.6128330230713</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8192863464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1096076965332</t>
+    <t xml:space="preserve">16.8192882537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1096096038818</t>
   </si>
   <si>
     <t xml:space="preserve">16.7225131988525</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1289653778076</t>
+    <t xml:space="preserve">17.128963470459</t>
   </si>
   <si>
     <t xml:space="preserve">16.8773517608643</t>
@@ -2558,13 +2558,13 @@
     <t xml:space="preserve">15.5031642913818</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2128429412842</t>
+    <t xml:space="preserve">15.2128419876099</t>
   </si>
   <si>
     <t xml:space="preserve">15.3096160888672</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5805835723877</t>
+    <t xml:space="preserve">15.5805826187134</t>
   </si>
   <si>
     <t xml:space="preserve">15.1547775268555</t>
@@ -2585,7 +2585,7 @@
     <t xml:space="preserve">15.5612277984619</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1805801391602</t>
+    <t xml:space="preserve">16.1805782318115</t>
   </si>
   <si>
     <t xml:space="preserve">16.8579978942871</t>
@@ -2594,10 +2594,10 @@
     <t xml:space="preserve">17.3031558990479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9031543731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8063793182373</t>
+    <t xml:space="preserve">17.9031524658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8063812255859</t>
   </si>
   <si>
     <t xml:space="preserve">17.1676731109619</t>
@@ -2612,7 +2612,7 @@
     <t xml:space="preserve">18.735408782959</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6579914093018</t>
+    <t xml:space="preserve">18.6579895019531</t>
   </si>
   <si>
     <t xml:space="preserve">18.4837970733643</t>
@@ -2627,7 +2627,7 @@
     <t xml:space="preserve">18.2515392303467</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8837966918945</t>
+    <t xml:space="preserve">17.8837985992432</t>
   </si>
   <si>
     <t xml:space="preserve">18.0386352539062</t>
@@ -2645,7 +2645,7 @@
     <t xml:space="preserve">18.1547660827637</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0192832946777</t>
+    <t xml:space="preserve">18.0192813873291</t>
   </si>
   <si>
     <t xml:space="preserve">17.9805736541748</t>
@@ -2657,7 +2657,7 @@
     <t xml:space="preserve">17.8450908660889</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6902503967285</t>
+    <t xml:space="preserve">17.6902523040771</t>
   </si>
   <si>
     <t xml:space="preserve">17.6321868896484</t>
@@ -2675,19 +2675,19 @@
     <t xml:space="preserve">17.2644462585449</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7096042633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4773502349854</t>
+    <t xml:space="preserve">17.7096061706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4773483276367</t>
   </si>
   <si>
     <t xml:space="preserve">17.8257369995117</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5805702209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.928955078125</t>
+    <t xml:space="preserve">18.5805721282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9289569854736</t>
   </si>
   <si>
     <t xml:space="preserve">18.8128299713135</t>
@@ -2702,10 +2702,10 @@
     <t xml:space="preserve">19.7902450561523</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0321788787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7418575286865</t>
+    <t xml:space="preserve">20.0321769714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7418556213379</t>
   </si>
   <si>
     <t xml:space="preserve">19.5966968536377</t>
@@ -2714,13 +2714,13 @@
     <t xml:space="preserve">19.9837894439697</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8386306762695</t>
+    <t xml:space="preserve">19.8386287689209</t>
   </si>
   <si>
     <t xml:space="preserve">20.0805644989014</t>
   </si>
   <si>
-    <t xml:space="preserve">20.370885848999</t>
+    <t xml:space="preserve">20.3708839416504</t>
   </si>
   <si>
     <t xml:space="preserve">19.8870162963867</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">20.177339553833</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4192733764648</t>
+    <t xml:space="preserve">20.4192752838135</t>
   </si>
   <si>
     <t xml:space="preserve">20.467658996582</t>
@@ -2759,10 +2759,10 @@
     <t xml:space="preserve">21.6289443969727</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0644264221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2579746246338</t>
+    <t xml:space="preserve">22.0644283294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2579727172852</t>
   </si>
   <si>
     <t xml:space="preserve">22.6450710296631</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">22.7902297973633</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7418441772461</t>
+    <t xml:space="preserve">22.7418422698975</t>
   </si>
   <si>
     <t xml:space="preserve">21.9676532745361</t>
@@ -2795,31 +2795,31 @@
     <t xml:space="preserve">22.3063621520996</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8224906921387</t>
+    <t xml:space="preserve">21.8224925994873</t>
   </si>
   <si>
     <t xml:space="preserve">22.3547496795654</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1128158569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5482978820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9837799072266</t>
+    <t xml:space="preserve">22.112813949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5482959747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9837779998779</t>
   </si>
   <si>
     <t xml:space="preserve">23.9031295776367</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1934509277344</t>
+    <t xml:space="preserve">24.193452835083</t>
   </si>
   <si>
     <t xml:space="preserve">24.0966758728027</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0160293579102</t>
+    <t xml:space="preserve">25.0160312652588</t>
   </si>
   <si>
     <t xml:space="preserve">24.9676399230957</t>
@@ -2834,22 +2834,22 @@
     <t xml:space="preserve">25.9353790283203</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3547382354736</t>
+    <t xml:space="preserve">25.354736328125</t>
   </si>
   <si>
     <t xml:space="preserve">25.161190032959</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8708667755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2579650878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4515113830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2095756530762</t>
+    <t xml:space="preserve">24.8708686828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.257963180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.451509475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2095737457275</t>
   </si>
   <si>
     <t xml:space="preserve">25.5482845306396</t>
@@ -2867,7 +2867,7 @@
     <t xml:space="preserve">26.9515056610107</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6934452056885</t>
+    <t xml:space="preserve">25.6934432983398</t>
   </si>
   <si>
     <t xml:space="preserve">25.5966720581055</t>
@@ -2879,7 +2879,7 @@
     <t xml:space="preserve">25.8869934082031</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3708610534668</t>
+    <t xml:space="preserve">26.3708629608154</t>
   </si>
   <si>
     <t xml:space="preserve">26.2043304443359</t>
@@ -40103,7 +40103,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1381" t="s">
-        <v>643</v>
+        <v>609</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -40129,7 +40129,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1382" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -40155,7 +40155,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1383" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -40181,7 +40181,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1384" t="s">
-        <v>643</v>
+        <v>609</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -40233,7 +40233,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1386" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -40259,7 +40259,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1387" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -40285,7 +40285,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G1388" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -40337,7 +40337,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1390" t="s">
-        <v>643</v>
+        <v>609</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -40363,7 +40363,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1391" t="s">
-        <v>643</v>
+        <v>609</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -40389,7 +40389,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1392" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -40415,7 +40415,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1393" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -40441,7 +40441,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1394" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -40467,7 +40467,7 @@
         <v>17</v>
       </c>
       <c r="G1395" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -40493,7 +40493,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1396" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -40519,7 +40519,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1397" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -40545,7 +40545,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1398" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -40571,7 +40571,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1399" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -40597,7 +40597,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1400" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -40623,7 +40623,7 @@
         <v>18</v>
       </c>
       <c r="G1401" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -40649,7 +40649,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1402" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -40675,7 +40675,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1403" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -40701,7 +40701,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1404" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -40727,7 +40727,7 @@
         <v>18</v>
       </c>
       <c r="G1405" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -40753,7 +40753,7 @@
         <v>18</v>
       </c>
       <c r="G1406" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -40779,7 +40779,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1407" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -40805,7 +40805,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G1408" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -40831,7 +40831,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1409" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -40857,7 +40857,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1410" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -40883,7 +40883,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1411" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -40909,7 +40909,7 @@
         <v>18</v>
       </c>
       <c r="G1412" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -40935,7 +40935,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G1413" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -40961,7 +40961,7 @@
         <v>18</v>
       </c>
       <c r="G1414" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -40987,7 +40987,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G1415" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -41013,7 +41013,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1416" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -41039,7 +41039,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1417" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -41065,7 +41065,7 @@
         <v>18.5</v>
       </c>
       <c r="G1418" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -41091,7 +41091,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1419" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -41117,7 +41117,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1420" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -41143,7 +41143,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1421" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -41169,7 +41169,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1422" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -41195,7 +41195,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1423" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -41221,7 +41221,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1424" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -41247,7 +41247,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1425" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -41273,7 +41273,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1426" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -41299,7 +41299,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1427" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -41325,7 +41325,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G1428" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -41351,7 +41351,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G1429" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -41377,7 +41377,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1430" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -41403,7 +41403,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1431" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -41429,7 +41429,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1432" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -41455,7 +41455,7 @@
         <v>18.5</v>
       </c>
       <c r="G1433" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -41481,7 +41481,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1434" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -41507,7 +41507,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1435" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -41533,7 +41533,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1436" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -41559,7 +41559,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G1437" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -41585,7 +41585,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1438" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -41611,7 +41611,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1439" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -41637,7 +41637,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1440" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -41663,7 +41663,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1441" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -41689,7 +41689,7 @@
         <v>19.5</v>
       </c>
       <c r="G1442" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -41715,7 +41715,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1443" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -41741,7 +41741,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G1444" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -41767,7 +41767,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1445" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -41793,7 +41793,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1446" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -41819,7 +41819,7 @@
         <v>20.5</v>
       </c>
       <c r="G1447" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -41845,7 +41845,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1448" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -41871,7 +41871,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1449" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -41897,7 +41897,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1450" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -41923,7 +41923,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1451" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -41949,7 +41949,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1452" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -41975,7 +41975,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1453" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -42001,7 +42001,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1454" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -42027,7 +42027,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1455" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -42053,7 +42053,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1456" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -42079,7 +42079,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1457" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -42105,7 +42105,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1458" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -42131,7 +42131,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1459" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -42157,7 +42157,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G1460" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -42183,7 +42183,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1461" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -42209,7 +42209,7 @@
         <v>19</v>
       </c>
       <c r="G1462" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -42235,7 +42235,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1463" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -42261,7 +42261,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G1464" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -42287,7 +42287,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1465" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -42313,7 +42313,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G1466" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -42339,7 +42339,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G1467" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -42365,7 +42365,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1468" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -42391,7 +42391,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1469" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -42417,7 +42417,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1470" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -42443,7 +42443,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1471" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -42469,7 +42469,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1472" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -42495,7 +42495,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G1473" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -42521,7 +42521,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1474" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -42547,7 +42547,7 @@
         <v>20</v>
       </c>
       <c r="G1475" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -42573,7 +42573,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1476" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -42599,7 +42599,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1477" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -42625,7 +42625,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1478" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -42651,7 +42651,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G1479" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -42677,7 +42677,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1480" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -42703,7 +42703,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1481" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -42729,7 +42729,7 @@
         <v>20</v>
       </c>
       <c r="G1482" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -42755,7 +42755,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1483" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -42781,7 +42781,7 @@
         <v>20</v>
       </c>
       <c r="G1484" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -42807,7 +42807,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1485" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -42833,7 +42833,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1486" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -42859,7 +42859,7 @@
         <v>20</v>
       </c>
       <c r="G1487" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -42885,7 +42885,7 @@
         <v>20</v>
       </c>
       <c r="G1488" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -42911,7 +42911,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G1489" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -42937,7 +42937,7 @@
         <v>20</v>
       </c>
       <c r="G1490" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -42963,7 +42963,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1491" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -42989,7 +42989,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1492" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -43015,7 +43015,7 @@
         <v>21</v>
       </c>
       <c r="G1493" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -43041,7 +43041,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1494" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -43067,7 +43067,7 @@
         <v>21.25</v>
       </c>
       <c r="G1495" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -43093,7 +43093,7 @@
         <v>21.75</v>
       </c>
       <c r="G1496" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -43119,7 +43119,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G1497" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -43145,7 +43145,7 @@
         <v>22.25</v>
       </c>
       <c r="G1498" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -43171,7 +43171,7 @@
         <v>22.5</v>
       </c>
       <c r="G1499" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -43197,7 +43197,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1500" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -43223,7 +43223,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1501" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -43249,7 +43249,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G1502" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -43275,7 +43275,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1503" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -43301,7 +43301,7 @@
         <v>22</v>
       </c>
       <c r="G1504" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -43327,7 +43327,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1505" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -43353,7 +43353,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1506" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -43379,7 +43379,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1507" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -43405,7 +43405,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1508" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -43431,7 +43431,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1509" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -43457,7 +43457,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1510" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -43483,7 +43483,7 @@
         <v>20.25</v>
       </c>
       <c r="G1511" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -43509,7 +43509,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1512" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -43535,7 +43535,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1513" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -43561,7 +43561,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1514" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -43587,7 +43587,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1515" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -43613,7 +43613,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G1516" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -43639,7 +43639,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1517" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -43665,7 +43665,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1518" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -43691,7 +43691,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1519" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -43717,7 +43717,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1520" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -43743,7 +43743,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1521" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -43769,7 +43769,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1522" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -43795,7 +43795,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1523" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -43821,7 +43821,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1524" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -43847,7 +43847,7 @@
         <v>21</v>
       </c>
       <c r="G1525" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -43873,7 +43873,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1526" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -43899,7 +43899,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1527" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -43925,7 +43925,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1528" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -43951,7 +43951,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1529" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -43977,7 +43977,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1530" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -44003,7 +44003,7 @@
         <v>20.5</v>
       </c>
       <c r="G1531" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -44029,7 +44029,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G1532" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -44055,7 +44055,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1533" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -44081,7 +44081,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1534" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -44107,7 +44107,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1535" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -44133,7 +44133,7 @@
         <v>20</v>
       </c>
       <c r="G1536" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -44159,7 +44159,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1537" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -44185,7 +44185,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1538" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -44211,7 +44211,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G1539" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -44237,7 +44237,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1540" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -44263,7 +44263,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1541" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -44289,7 +44289,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G1542" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -44315,7 +44315,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1543" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -44341,7 +44341,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1544" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -44367,7 +44367,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1545" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -44393,7 +44393,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G1546" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -44419,7 +44419,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G1547" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -44445,7 +44445,7 @@
         <v>19</v>
       </c>
       <c r="G1548" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -44471,7 +44471,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G1549" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -44497,7 +44497,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G1550" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -44523,7 +44523,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1551" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -44549,7 +44549,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G1552" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -44575,7 +44575,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G1553" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -44601,7 +44601,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1554" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -44627,7 +44627,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1555" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -44653,7 +44653,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1556" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -44679,7 +44679,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1557" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -44705,7 +44705,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G1558" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -44731,7 +44731,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1559" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -44757,7 +44757,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1560" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -44783,7 +44783,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G1561" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -44809,7 +44809,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1562" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -44835,7 +44835,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1563" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -44861,7 +44861,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G1564" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -44887,7 +44887,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1565" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -44913,7 +44913,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1566" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -44939,7 +44939,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1567" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -44965,7 +44965,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1568" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -44991,7 +44991,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1569" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -45017,7 +45017,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G1570" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -45043,7 +45043,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G1571" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -45069,7 +45069,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1572" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -45095,7 +45095,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1573" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -45121,7 +45121,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G1574" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -45147,7 +45147,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G1575" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -45173,7 +45173,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1576" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -45199,7 +45199,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1577" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -45225,7 +45225,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1578" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -45251,7 +45251,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1579" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -45277,7 +45277,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G1580" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -45303,7 +45303,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1581" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -45329,7 +45329,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1582" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -45355,7 +45355,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1583" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -45381,7 +45381,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1584" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -45407,7 +45407,7 @@
         <v>17</v>
       </c>
       <c r="G1585" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -45433,7 +45433,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G1586" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -45459,7 +45459,7 @@
         <v>17.5</v>
       </c>
       <c r="G1587" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -45485,7 +45485,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1588" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -45511,7 +45511,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1589" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -45537,7 +45537,7 @@
         <v>16.5</v>
       </c>
       <c r="G1590" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -45563,7 +45563,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1591" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -45641,7 +45641,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G1594" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -45667,7 +45667,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G1595" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -45719,7 +45719,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1597" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -45771,7 +45771,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G1599" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -45797,7 +45797,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G1600" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -45823,7 +45823,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1601" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -45849,7 +45849,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1602" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -45875,7 +45875,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G1603" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -45901,7 +45901,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1604" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -45927,7 +45927,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1605" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -45953,7 +45953,7 @@
         <v>15.5</v>
       </c>
       <c r="G1606" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -45979,7 +45979,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G1607" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -46005,7 +46005,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1608" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -46057,7 +46057,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G1610" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -46109,7 +46109,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1612" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -46187,7 +46187,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G1615" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -46239,7 +46239,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1617" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -46265,7 +46265,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G1618" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -46291,7 +46291,7 @@
         <v>16.5</v>
       </c>
       <c r="G1619" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -46317,7 +46317,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1620" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -46343,7 +46343,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1621" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -46369,7 +46369,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1622" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -46395,7 +46395,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G1623" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -46421,7 +46421,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1624" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -46447,7 +46447,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1625" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -46473,7 +46473,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1626" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -46499,7 +46499,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1627" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -46525,7 +46525,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1628" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -46551,7 +46551,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G1629" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -46577,7 +46577,7 @@
         <v>18</v>
       </c>
       <c r="G1630" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -46603,7 +46603,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1631" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -46629,7 +46629,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1632" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -46655,7 +46655,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1633" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -46681,7 +46681,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1634" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -46707,7 +46707,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1635" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -46733,7 +46733,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1636" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -46759,7 +46759,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1637" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -46785,7 +46785,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1638" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -46811,7 +46811,7 @@
         <v>17</v>
       </c>
       <c r="G1639" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -46837,7 +46837,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1640" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -46863,7 +46863,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1641" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -46889,7 +46889,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1642" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -46915,7 +46915,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1643" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -46941,7 +46941,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1644" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -46967,7 +46967,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1645" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -46993,7 +46993,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1646" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -47019,7 +47019,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G1647" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -47045,7 +47045,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1648" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -47071,7 +47071,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G1649" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -47097,7 +47097,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1650" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -47123,7 +47123,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G1651" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -47149,7 +47149,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G1652" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -47175,7 +47175,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1653" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -47201,7 +47201,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1654" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -47227,7 +47227,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1655" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -47253,7 +47253,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G1656" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -47279,7 +47279,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1657" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -47305,7 +47305,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1658" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -47331,7 +47331,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1659" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -47357,7 +47357,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G1660" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -47383,7 +47383,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1661" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -47409,7 +47409,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G1662" t="s">
-        <v>772</v>
+        <v>821</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -47487,7 +47487,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1665" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -47513,7 +47513,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1666" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -47539,7 +47539,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G1667" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -47565,7 +47565,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1668" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -47591,7 +47591,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1669" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -48007,7 +48007,7 @@
         <v>18</v>
       </c>
       <c r="G1685" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -48059,7 +48059,7 @@
         <v>18</v>
       </c>
       <c r="G1687" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -48111,7 +48111,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1689" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -48241,7 +48241,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1694" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -48267,7 +48267,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1695" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -48319,7 +48319,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1697" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -48423,7 +48423,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1701" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -48501,7 +48501,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1704" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -48527,7 +48527,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1705" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -48579,7 +48579,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1707" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -48631,7 +48631,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G1709" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -48683,7 +48683,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1711" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -49021,7 +49021,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1724" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -49073,7 +49073,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1726" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -49125,7 +49125,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1728" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -49307,7 +49307,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1735" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -49437,7 +49437,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1740" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -49489,7 +49489,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1742" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -49515,7 +49515,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1743" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -50009,7 +50009,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1762" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -50087,7 +50087,7 @@
         <v>18</v>
       </c>
       <c r="G1765" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -50139,7 +50139,7 @@
         <v>18</v>
       </c>
       <c r="G1767" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -50373,7 +50373,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1776" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -50451,7 +50451,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1779" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -50581,7 +50581,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1784" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -50659,7 +50659,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1787" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -70271,7 +70271,7 @@
     </row>
     <row r="2542">
       <c r="A2542" s="1" t="n">
-        <v>46024.6910300926</v>
+        <v>46024.3333333333</v>
       </c>
       <c r="B2542" t="n">
         <v>22648</v>
@@ -70292,6 +70292,32 @@
         <v>1284</v>
       </c>
       <c r="H2542" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2543">
+      <c r="A2543" s="1" t="n">
+        <v>46027.6911921296</v>
+      </c>
+      <c r="B2543" t="n">
+        <v>32077</v>
+      </c>
+      <c r="C2543" t="n">
+        <v>48.2999992370605</v>
+      </c>
+      <c r="D2543" t="n">
+        <v>47.3499984741211</v>
+      </c>
+      <c r="E2543" t="n">
+        <v>48.2999992370605</v>
+      </c>
+      <c r="F2543" t="n">
+        <v>48</v>
+      </c>
+      <c r="G2543" t="s">
+        <v>1232</v>
+      </c>
+      <c r="H2543" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SOL.MI.xlsx
+++ b/data/SOL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1285" uniqueCount="1285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="1286">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,16 +44,16 @@
     <t xml:space="preserve">SOL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14067220687866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18862581253052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16246938705444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06220388412476</t>
+    <t xml:space="preserve">7.14067268371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18862533569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1624698638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06220436096191</t>
   </si>
   <si>
     <t xml:space="preserve">6.90962553024292</t>
@@ -62,28 +62,28 @@
     <t xml:space="preserve">6.90526580810547</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94886016845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71781158447266</t>
+    <t xml:space="preserve">6.94885921478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71781206130981</t>
   </si>
   <si>
     <t xml:space="preserve">6.62626504898071</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71345281600952</t>
+    <t xml:space="preserve">6.71345186233521</t>
   </si>
   <si>
     <t xml:space="preserve">6.29931116104126</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36470222473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43009233474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4126558303833</t>
+    <t xml:space="preserve">6.36470174789429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43009376525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41265487670898</t>
   </si>
   <si>
     <t xml:space="preserve">6.44753074645996</t>
@@ -92,28 +92,28 @@
     <t xml:space="preserve">6.207763671875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17288875579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46060800552368</t>
+    <t xml:space="preserve">6.1728892326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.460608959198</t>
   </si>
   <si>
     <t xml:space="preserve">6.54779624938965</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38214015960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51292133331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50420236587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65242052078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80064058303833</t>
+    <t xml:space="preserve">6.38213968276978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51291990280151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50420331954956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65242147445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80064010620117</t>
   </si>
   <si>
     <t xml:space="preserve">6.72217178344727</t>
@@ -122,43 +122,43 @@
     <t xml:space="preserve">6.79192209243774</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00989151000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84423351287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07964086532593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88346862792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96629619598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08836030960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73524951934814</t>
+    <t xml:space="preserve">7.00989103317261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84423494338989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07964181900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88346910476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96629667282104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08835887908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73524904251099</t>
   </si>
   <si>
     <t xml:space="preserve">6.8311562538147</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67857694625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57395267486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63062429428101</t>
+    <t xml:space="preserve">6.67857789993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57395219802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63062477111816</t>
   </si>
   <si>
     <t xml:space="preserve">6.68729686737061</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78320360183716</t>
+    <t xml:space="preserve">6.783203125</t>
   </si>
   <si>
     <t xml:space="preserve">6.77884387969971</t>
@@ -170,19 +170,19 @@
     <t xml:space="preserve">6.80935907363892</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79628133773804</t>
+    <t xml:space="preserve">6.79628086090088</t>
   </si>
   <si>
     <t xml:space="preserve">6.69601535797119</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81807851791382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8747501373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91398429870605</t>
+    <t xml:space="preserve">6.81807947158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87475061416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9139838218689</t>
   </si>
   <si>
     <t xml:space="preserve">6.67421865463257</t>
@@ -191,13 +191,13 @@
     <t xml:space="preserve">6.55215549468994</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46496725082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43881225585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73089027404785</t>
+    <t xml:space="preserve">6.46496868133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43881177902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73088932037354</t>
   </si>
   <si>
     <t xml:space="preserve">6.87910938262939</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">6.85295343399048</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84859418869019</t>
+    <t xml:space="preserve">6.84859371185303</t>
   </si>
   <si>
     <t xml:space="preserve">6.85731220245361</t>
@@ -215,88 +215,88 @@
     <t xml:space="preserve">6.74832725524902</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51728057861328</t>
+    <t xml:space="preserve">6.51728105545044</t>
   </si>
   <si>
     <t xml:space="preserve">6.37342119216919</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56523418426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66985988616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77012491226196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86167144775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97501611709595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94163036346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9504828453064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88407802581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90178632736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34006452560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22495985031128</t>
+    <t xml:space="preserve">6.56523370742798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66985893249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7701244354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86167192459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97501659393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9416298866272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95048379898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88407850265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9017858505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34006500244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22496175765991</t>
   </si>
   <si>
     <t xml:space="preserve">7.41975116729736</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43746089935303</t>
+    <t xml:space="preserve">7.43745994567871</t>
   </si>
   <si>
     <t xml:space="preserve">7.36662769317627</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26037836074829</t>
+    <t xml:space="preserve">7.26037788391113</t>
   </si>
   <si>
     <t xml:space="preserve">7.46845054626465</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40204381942749</t>
+    <t xml:space="preserve">7.40204334259033</t>
   </si>
   <si>
     <t xml:space="preserve">7.44631481170654</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3843355178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0434513092041</t>
+    <t xml:space="preserve">7.38433504104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04345178604126</t>
   </si>
   <si>
     <t xml:space="preserve">6.97261905670166</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1098575592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87079668045044</t>
+    <t xml:space="preserve">7.10985803604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87079620361328</t>
   </si>
   <si>
     <t xml:space="preserve">7.20725345611572</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37105464935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57027196884155</t>
+    <t xml:space="preserve">7.37105369567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57027149200439</t>
   </si>
   <si>
     <t xml:space="preserve">7.69422960281372</t>
@@ -305,61 +305,61 @@
     <t xml:space="preserve">7.70308351516724</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71193885803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65881299972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04396915435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61454248428345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2957935333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99475431442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10100364685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55256414413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31350326538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50829267501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42418003082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37548160552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52600193023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54371023178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41532468795776</t>
+    <t xml:space="preserve">7.71193790435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65881252288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04396820068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61454296112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29579401016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99475479125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1010046005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55256509780884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3135027885437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50829219818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4241795539856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37548208236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52600240707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54371070861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41532516479492</t>
   </si>
   <si>
     <t xml:space="preserve">7.21610689163208</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99032735824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79996395111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75569248199463</t>
+    <t xml:space="preserve">6.99032783508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79996347427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7556939125061</t>
   </si>
   <si>
     <t xml:space="preserve">7.00803565979004</t>
@@ -368,13 +368,13 @@
     <t xml:space="preserve">7.26923227310181</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34449243545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46402311325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51714706420898</t>
+    <t xml:space="preserve">7.34449195861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46402263641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51714754104614</t>
   </si>
   <si>
     <t xml:space="preserve">7.39318990707397</t>
@@ -383,16 +383,16 @@
     <t xml:space="preserve">7.4551682472229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17183685302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33563756942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33121109008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39761590957642</t>
+    <t xml:space="preserve">7.1718373298645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33563709259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33121013641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39761734008789</t>
   </si>
   <si>
     <t xml:space="preserve">7.30464935302734</t>
@@ -401,22 +401,22 @@
     <t xml:space="preserve">7.27808618545532</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25152349472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16298246383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03017139434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87965059280396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91064023971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95491123199463</t>
+    <t xml:space="preserve">7.25152397155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16298294067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03017044067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87965154647827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91064071655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95491075515747</t>
   </si>
   <si>
     <t xml:space="preserve">6.88850545883179</t>
@@ -425,49 +425,49 @@
     <t xml:space="preserve">6.95933818817139</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85751581192017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77340221405029</t>
+    <t xml:space="preserve">6.85751533508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77340078353882</t>
   </si>
   <si>
     <t xml:space="preserve">6.74683904647827</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82652616500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6848611831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81767177581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90621328353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01689004898071</t>
+    <t xml:space="preserve">6.8265266418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68486022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81767129898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90621280670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01688957214355</t>
   </si>
   <si>
     <t xml:space="preserve">6.8973593711853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83538007736206</t>
+    <t xml:space="preserve">6.8353796005249</t>
   </si>
   <si>
     <t xml:space="preserve">6.86194276809692</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92392206192017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97704601287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00360870361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91506719589233</t>
+    <t xml:space="preserve">6.92392253875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97704648971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00360822677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91506767272949</t>
   </si>
   <si>
     <t xml:space="preserve">6.91949462890625</t>
@@ -476,7 +476,7 @@
     <t xml:space="preserve">6.93720245361328</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07001495361328</t>
+    <t xml:space="preserve">7.07001543045044</t>
   </si>
   <si>
     <t xml:space="preserve">6.98590040206909</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">6.75126647949219</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77782869338989</t>
+    <t xml:space="preserve">6.77782821655273</t>
   </si>
   <si>
     <t xml:space="preserve">6.64944362640381</t>
@@ -497,25 +497,25 @@
     <t xml:space="preserve">6.37053966522217</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36168479919434</t>
+    <t xml:space="preserve">6.36168575286865</t>
   </si>
   <si>
     <t xml:space="preserve">6.37939310073853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40595579147339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4812159538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47678756713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54319477081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46350765228271</t>
+    <t xml:space="preserve">6.40595531463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48121547698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47678852081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54319429397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46350717544556</t>
   </si>
   <si>
     <t xml:space="preserve">6.24215459823608</t>
@@ -524,10 +524,10 @@
     <t xml:space="preserve">6.25986289978027</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22444677352905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64501714706421</t>
+    <t xml:space="preserve">6.22444629669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64501619338989</t>
   </si>
   <si>
     <t xml:space="preserve">6.64058971405029</t>
@@ -536,43 +536,43 @@
     <t xml:space="preserve">7.03902435302734</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79111003875732</t>
+    <t xml:space="preserve">6.79110956192017</t>
   </si>
   <si>
     <t xml:space="preserve">6.70256853103638</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70699501037598</t>
+    <t xml:space="preserve">6.70699548721313</t>
   </si>
   <si>
     <t xml:space="preserve">6.65829753875732</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58303737640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05673360824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11428546905518</t>
+    <t xml:space="preserve">6.58303785324097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05673313140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11428499221802</t>
   </si>
   <si>
     <t xml:space="preserve">7.34891939163208</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18511772155762</t>
+    <t xml:space="preserve">7.18511819839478</t>
   </si>
   <si>
     <t xml:space="preserve">7.12756681442261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19397211074829</t>
+    <t xml:space="preserve">7.19397163391113</t>
   </si>
   <si>
     <t xml:space="preserve">7.24267053604126</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41089820861816</t>
+    <t xml:space="preserve">7.41089773178101</t>
   </si>
   <si>
     <t xml:space="preserve">7.48173141479492</t>
@@ -581,46 +581,46 @@
     <t xml:space="preserve">7.14527416229248</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27365922927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1762638092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04787969589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23381614685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29136753082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42860698699951</t>
+    <t xml:space="preserve">7.27365970611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17626285552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04787921905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23381567001343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29136657714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4286060333252</t>
   </si>
   <si>
     <t xml:space="preserve">7.83589601516724</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82704162597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13693618774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27860164642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32287311553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03120136260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53094387054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49995613098145</t>
+    <t xml:space="preserve">7.8270411491394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13693714141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27860355377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32287120819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0312032699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53094482421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49995422363281</t>
   </si>
   <si>
     <t xml:space="preserve">8.26089286804199</t>
@@ -629,13 +629,13 @@
     <t xml:space="preserve">8.92495250701904</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58849620819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97807788848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76557731628418</t>
+    <t xml:space="preserve">8.5884952545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97807693481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7655782699585</t>
   </si>
   <si>
     <t xml:space="preserve">8.87182807922363</t>
@@ -644,7 +644,7 @@
     <t xml:space="preserve">9.56244945526123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25255584716797</t>
+    <t xml:space="preserve">9.25255393981934</t>
   </si>
   <si>
     <t xml:space="preserve">9.02234840393066</t>
@@ -653,7 +653,7 @@
     <t xml:space="preserve">8.85411930084229</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82755756378174</t>
+    <t xml:space="preserve">8.82755851745605</t>
   </si>
   <si>
     <t xml:space="preserve">8.71245384216309</t>
@@ -662,52 +662,52 @@
     <t xml:space="preserve">8.98693180084229</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89838981628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80984878540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72130680084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78328514099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67703723907471</t>
+    <t xml:space="preserve">8.89839172363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80984783172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72130870819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78328800201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67703628540039</t>
   </si>
   <si>
     <t xml:space="preserve">8.75672435760498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10203456878662</t>
+    <t xml:space="preserve">9.10203552246094</t>
   </si>
   <si>
     <t xml:space="preserve">8.82312965393066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94266128540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20828533172607</t>
+    <t xml:space="preserve">8.94266033172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20828437805176</t>
   </si>
   <si>
     <t xml:space="preserve">9.43287658691406</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4598274230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52271366119385</t>
+    <t xml:space="preserve">9.45982646942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52271461486816</t>
   </si>
   <si>
     <t xml:space="preserve">9.3250732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3879566192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35202217102051</t>
+    <t xml:space="preserve">9.38795757293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35202312469482</t>
   </si>
   <si>
     <t xml:space="preserve">9.42389297485352</t>
@@ -716,34 +716,34 @@
     <t xml:space="preserve">9.29812145233154</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55864906311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67543601989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86409378051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5199031829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0617332458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88206100463867</t>
+    <t xml:space="preserve">9.55864810943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67543697357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86409282684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5199041366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0617341995239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88206195831299</t>
   </si>
   <si>
     <t xml:space="preserve">9.74730587005615</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56763172149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44186115264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54068183898926</t>
+    <t xml:space="preserve">9.56763076782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44185924530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54068088531494</t>
   </si>
   <si>
     <t xml:space="preserve">9.34303951263428</t>
@@ -755,16 +755,16 @@
     <t xml:space="preserve">9.50474548339844</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48677825927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61255264282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77425575256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46881198883057</t>
+    <t xml:space="preserve">9.48677921295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.612548828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77425670623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46881103515625</t>
   </si>
   <si>
     <t xml:space="preserve">9.54966449737549</t>
@@ -773,46 +773,46 @@
     <t xml:space="preserve">9.4777946472168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7023868560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30710506439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28015327453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21726703643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16336536407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25320339202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45084476470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58559894561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33405590057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59458351135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66645240783691</t>
+    <t xml:space="preserve">9.70238780975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30710411071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28015422821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2172679901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16336631774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25320434570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45084381103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58559989929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33405780792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59458255767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66645336151123</t>
   </si>
   <si>
     <t xml:space="preserve">9.71137142181396</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40592575073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26218605041504</t>
+    <t xml:space="preserve">9.40592479705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26218700408936</t>
   </si>
   <si>
     <t xml:space="preserve">9.2711706161499</t>
@@ -824,16 +824,16 @@
     <t xml:space="preserve">9.36999130249023</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65746974945068</t>
+    <t xml:space="preserve">9.65746879577637</t>
   </si>
   <si>
     <t xml:space="preserve">9.79222393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76527214050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72035312652588</t>
+    <t xml:space="preserve">9.76527404785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72035503387451</t>
   </si>
   <si>
     <t xml:space="preserve">9.81019115447998</t>
@@ -842,16 +842,16 @@
     <t xml:space="preserve">9.37897300720215</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90901279449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81917476654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73832225799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78324031829834</t>
+    <t xml:space="preserve">9.90901184082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81917572021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73832130432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78324127197266</t>
   </si>
   <si>
     <t xml:space="preserve">9.69340419769287</t>
@@ -860,55 +860,55 @@
     <t xml:space="preserve">9.11844635009766</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08251190185547</t>
+    <t xml:space="preserve">9.08251094818115</t>
   </si>
   <si>
     <t xml:space="preserve">9.31608867645264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19031620025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10047912597656</t>
+    <t xml:space="preserve">9.19031715393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10048007965088</t>
   </si>
   <si>
     <t xml:space="preserve">9.22625255584717</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41490840911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39694213867188</t>
+    <t xml:space="preserve">9.41490745544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39694023132324</t>
   </si>
   <si>
     <t xml:space="preserve">9.07352924346924</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57661533355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68442058563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09149551391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05556201934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1453971862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89385414123535</t>
+    <t xml:space="preserve">9.57661628723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68441963195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09149646759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05556106567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14539813995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89385604858398</t>
   </si>
   <si>
     <t xml:space="preserve">9.10946369171143</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23523330688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95393085479736</t>
+    <t xml:space="preserve">9.23523426055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95392990112305</t>
   </si>
   <si>
     <t xml:space="preserve">10.5109205245972</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">10.7444953918457</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5468530654907</t>
+    <t xml:space="preserve">10.5468549728394</t>
   </si>
   <si>
     <t xml:space="preserve">10.6905927658081</t>
@@ -929,13 +929,13 @@
     <t xml:space="preserve">10.7804307937622</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7085609436035</t>
+    <t xml:space="preserve">10.7085599899292</t>
   </si>
   <si>
     <t xml:space="preserve">10.6546583175659</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5288896560669</t>
+    <t xml:space="preserve">10.5288877487183</t>
   </si>
   <si>
     <t xml:space="preserve">10.4390487670898</t>
@@ -947,19 +947,19 @@
     <t xml:space="preserve">10.1695394515991</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1875066757202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1336040496826</t>
+    <t xml:space="preserve">10.1875085830688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1336050033569</t>
   </si>
   <si>
     <t xml:space="preserve">9.75629043579102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63051700592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.007833480835</t>
+    <t xml:space="preserve">9.63051795959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0078325271606</t>
   </si>
   <si>
     <t xml:space="preserve">9.84612655639648</t>
@@ -968,151 +968,151 @@
     <t xml:space="preserve">10.0976705551147</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2054719924927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2773447036743</t>
+    <t xml:space="preserve">10.2054748535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2773427963257</t>
   </si>
   <si>
     <t xml:space="preserve">10.2234420776367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2414102554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7624626159668</t>
+    <t xml:space="preserve">10.2414073944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7624616622925</t>
   </si>
   <si>
     <t xml:space="preserve">10.2593765258789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91799449920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90002918243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67380809783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74668025970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87420463562012</t>
+    <t xml:space="preserve">9.91799640655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90002822875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67380714416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74667835235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87420558929443</t>
   </si>
   <si>
     <t xml:space="preserve">10.1656951904297</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85598659515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63737010955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47340679168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76489639282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96529674530029</t>
+    <t xml:space="preserve">9.85598754882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63737106323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47340774536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76489734649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96529483795166</t>
   </si>
   <si>
     <t xml:space="preserve">10.0746049880981</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2385683059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.384313583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4207487106323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8033275604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.694019317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6211462020874</t>
+    <t xml:space="preserve">10.2385663986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3843126296997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4207496643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8033285140991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6940183639526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6211471557617</t>
   </si>
   <si>
     <t xml:space="preserve">10.7851104736328</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5482740402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4025297164917</t>
+    <t xml:space="preserve">10.5482749938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.402530670166</t>
   </si>
   <si>
     <t xml:space="preserve">10.2203493118286</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1474781036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3296566009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5847120285034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3478746414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72846126556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56449890136719</t>
+    <t xml:space="preserve">10.1474771499634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3296585083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5847101211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3478755950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72846031188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56449699401855</t>
   </si>
   <si>
     <t xml:space="preserve">9.41875457763672</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40053558349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54627895355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1110401153564</t>
+    <t xml:space="preserve">9.40053462982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54627990722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1110410690308</t>
   </si>
   <si>
     <t xml:space="preserve">10.2567853927612</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92885875701904</t>
+    <t xml:space="preserve">9.92885971069336</t>
   </si>
   <si>
     <t xml:space="preserve">10.0199499130249</t>
   </si>
   <si>
-    <t xml:space="preserve">10.202130317688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0928230285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8013334274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69202518463135</t>
+    <t xml:space="preserve">10.2021312713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0928220748901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80133438110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69202327728271</t>
   </si>
   <si>
     <t xml:space="preserve">9.83776950836182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94707775115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89242458343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65558910369873</t>
+    <t xml:space="preserve">9.94707870483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89242362976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6555871963501</t>
   </si>
   <si>
     <t xml:space="preserve">9.78311443328857</t>
@@ -1127,40 +1127,40 @@
     <t xml:space="preserve">9.20013618469238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50984287261963</t>
+    <t xml:space="preserve">9.50984382629395</t>
   </si>
   <si>
     <t xml:space="preserve">9.43697071075439</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81955146789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49162673950195</t>
+    <t xml:space="preserve">9.81955242156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49162578582764</t>
   </si>
   <si>
     <t xml:space="preserve">9.6191520690918</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98351287841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60093402862549</t>
+    <t xml:space="preserve">9.98351383209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6009349822998</t>
   </si>
   <si>
     <t xml:space="preserve">9.10904598236084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09993648529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38231658935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36409759521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27300834655762</t>
+    <t xml:space="preserve">9.09993743896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38231754302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36409854888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27301025390625</t>
   </si>
   <si>
     <t xml:space="preserve">9.71024227142334</t>
@@ -1169,7 +1169,7 @@
     <t xml:space="preserve">9.58271598815918</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29122734069824</t>
+    <t xml:space="preserve">9.29122638702393</t>
   </si>
   <si>
     <t xml:space="preserve">9.14548206329346</t>
@@ -1178,7 +1178,7 @@
     <t xml:space="preserve">10.3660945892334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32766246795654</t>
+    <t xml:space="preserve">9.32766342163086</t>
   </si>
   <si>
     <t xml:space="preserve">10.0017318725586</t>
@@ -1190,16 +1190,16 @@
     <t xml:space="preserve">10.8397645950317</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5664930343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3114404678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2932224273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0381698608398</t>
+    <t xml:space="preserve">10.5664939880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3114395141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2932233810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0381689071655</t>
   </si>
   <si>
     <t xml:space="preserve">10.0563850402832</t>
@@ -1208,43 +1208,43 @@
     <t xml:space="preserve">10.1292581558228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2750024795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1839141845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.675802230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7122383117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9308557510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0219440460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.87619972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8944187164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7304553985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6575841903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2644643783569</t>
+    <t xml:space="preserve">10.2750034332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1839122772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6758012771606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7122392654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9308547973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0219459533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8762006759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.894419670105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7304544448853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.65758228302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2644634246826</t>
   </si>
   <si>
     <t xml:space="preserve">11.1349859237671</t>
   </si>
   <si>
-    <t xml:space="preserve">11.097993850708</t>
+    <t xml:space="preserve">11.0979928970337</t>
   </si>
   <si>
     <t xml:space="preserve">11.2459669113159</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">11.0240068435669</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8205442428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8390417098999</t>
+    <t xml:space="preserve">10.8205423355103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8390407562256</t>
   </si>
   <si>
     <t xml:space="preserve">10.7280607223511</t>
@@ -1268,19 +1268,19 @@
     <t xml:space="preserve">10.857536315918</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7095623016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6725702285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6540746688843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7835493087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7650547027588</t>
+    <t xml:space="preserve">10.7095642089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6725692749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6540756225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7835502624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7650537490845</t>
   </si>
   <si>
     <t xml:space="preserve">10.8020477294922</t>
@@ -1292,16 +1292,16 @@
     <t xml:space="preserve">10.6170806884766</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3951206207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1176710128784</t>
+    <t xml:space="preserve">10.3951196670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1176700592041</t>
   </si>
   <si>
     <t xml:space="preserve">10.2841396331787</t>
   </si>
   <si>
-    <t xml:space="preserve">10.265643119812</t>
+    <t xml:space="preserve">10.2656440734863</t>
   </si>
   <si>
     <t xml:space="preserve">10.302638053894</t>
@@ -1319,43 +1319,43 @@
     <t xml:space="preserve">10.0806770324707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98819351196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0991735458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93270397186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89571189880371</t>
+    <t xml:space="preserve">9.98819446563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0991744995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93270301818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89571094512939</t>
   </si>
   <si>
     <t xml:space="preserve">9.96969795227051</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1731595993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.062180519104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1546640396118</t>
+    <t xml:space="preserve">10.1731605529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0621795654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1546630859375</t>
   </si>
   <si>
     <t xml:space="preserve">9.71074390411377</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0251865386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91420650482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76623344421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72924137115479</t>
+    <t xml:space="preserve">10.0251874923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91420841217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76623439788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72924041748047</t>
   </si>
   <si>
     <t xml:space="preserve">9.65525341033936</t>
@@ -1364,10 +1364,10 @@
     <t xml:space="preserve">9.67375087738037</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47028827667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54427433013916</t>
+    <t xml:space="preserve">9.47028732299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54427337646484</t>
   </si>
   <si>
     <t xml:space="preserve">9.56277179718018</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">9.45179080963135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35930824279785</t>
+    <t xml:space="preserve">9.35930728912354</t>
   </si>
   <si>
     <t xml:space="preserve">9.52577781677246</t>
@@ -1385,31 +1385,31 @@
     <t xml:space="preserve">9.59976482391357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61826038360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69224643707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8032283782959</t>
+    <t xml:space="preserve">9.61826133728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69224739074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80322647094727</t>
   </si>
   <si>
     <t xml:space="preserve">10.2286510467529</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78472995758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.858717918396</t>
+    <t xml:space="preserve">9.7847318649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85871696472168</t>
   </si>
   <si>
     <t xml:space="preserve">10.0066900253296</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8772144317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74773693084717</t>
+    <t xml:space="preserve">9.87721347808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7477388381958</t>
   </si>
   <si>
     <t xml:space="preserve">9.58126735687256</t>
@@ -1424,7 +1424,7 @@
     <t xml:space="preserve">10.3766241073608</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2471466064453</t>
+    <t xml:space="preserve">10.2471475601196</t>
   </si>
   <si>
     <t xml:space="preserve">10.2101526260376</t>
@@ -1439,13 +1439,13 @@
     <t xml:space="preserve">9.43329429626465</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41479682922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39630222320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24832725524902</t>
+    <t xml:space="preserve">9.41479873657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39630126953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24832820892334</t>
   </si>
   <si>
     <t xml:space="preserve">9.06336116790771</t>
@@ -1457,28 +1457,28 @@
     <t xml:space="preserve">9.32231426239014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28532028198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26682376861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19283676147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22982978820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48878383636475</t>
+    <t xml:space="preserve">9.28532123565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26682567596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19283771514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22983074188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48878479003906</t>
   </si>
   <si>
     <t xml:space="preserve">9.02636814117432</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9708776473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13734817504883</t>
+    <t xml:space="preserve">8.97087860107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13734722137451</t>
   </si>
   <si>
     <t xml:space="preserve">8.96162891387939</t>
@@ -1499,55 +1499,55 @@
     <t xml:space="preserve">8.33274364471436</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0182991027832</t>
+    <t xml:space="preserve">8.01830005645752</t>
   </si>
   <si>
     <t xml:space="preserve">7.81483745574951</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95356178283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49114608764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86108016967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50964164733887</t>
+    <t xml:space="preserve">7.95356321334839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49114561080933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8610782623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50964260101318</t>
   </si>
   <si>
     <t xml:space="preserve">7.53738689422607</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58362865447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76741409301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9893741607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16509246826172</t>
+    <t xml:space="preserve">7.58362913131714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76741504669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98937511444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16509342193604</t>
   </si>
   <si>
     <t xml:space="preserve">9.12809944152832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09110641479492</t>
+    <t xml:space="preserve">9.09110736846924</t>
   </si>
   <si>
     <t xml:space="preserve">9.08185768127441</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34081077575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0448637008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21133422851562</t>
+    <t xml:space="preserve">9.34081172943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04486560821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21133518218994</t>
   </si>
   <si>
     <t xml:space="preserve">9.38705158233643</t>
@@ -1559,70 +1559,70 @@
     <t xml:space="preserve">9.29456901550293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11885070800781</t>
+    <t xml:space="preserve">9.11885166168213</t>
   </si>
   <si>
     <t xml:space="preserve">8.78591060638428</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89689064025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74891757965088</t>
+    <t xml:space="preserve">8.89689254760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74891662597656</t>
   </si>
   <si>
     <t xml:space="preserve">8.80440807342529</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87839603424072</t>
+    <t xml:space="preserve">8.87839412689209</t>
   </si>
   <si>
     <t xml:space="preserve">8.9338846206665</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63793754577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71192455291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58244895935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69342803955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46114063262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6494197845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69649219512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74356079101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97891330718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93184375762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7906322479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0730543136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3084049224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4496173858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1671953201294</t>
+    <t xml:space="preserve">8.63793849945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71192359924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58244800567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6934289932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46113872528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64942073822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69649028778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74356174468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97891235351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93184280395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79063034057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0730533599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3084058761597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4496164321899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1671943664551</t>
   </si>
   <si>
     <t xml:space="preserve">10.1201238632202</t>
@@ -1631,13 +1631,13 @@
     <t xml:space="preserve">10.0259828567505</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2142648696899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3554763793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2613353729248</t>
+    <t xml:space="preserve">10.2142658233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3554754257202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2613344192505</t>
   </si>
   <si>
     <t xml:space="preserve">9.88477230072021</t>
@@ -1652,25 +1652,25 @@
     <t xml:space="preserve">10.5437574386597</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2027416229248</t>
+    <t xml:space="preserve">11.2027406692505</t>
   </si>
   <si>
     <t xml:space="preserve">11.1556720733643</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9673900604248</t>
+    <t xml:space="preserve">10.9673891067505</t>
   </si>
   <si>
     <t xml:space="preserve">11.0615301132202</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7791090011597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8261785507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.014461517334</t>
+    <t xml:space="preserve">10.7791080474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8261795043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0144605636597</t>
   </si>
   <si>
     <t xml:space="preserve">11.1086015701294</t>
@@ -1679,25 +1679,25 @@
     <t xml:space="preserve">10.9203205108643</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8732500076294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7320394515991</t>
+    <t xml:space="preserve">10.8732490539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7320384979248</t>
   </si>
   <si>
     <t xml:space="preserve">10.6378984451294</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5322351455688</t>
+    <t xml:space="preserve">11.5322341918945</t>
   </si>
   <si>
     <t xml:space="preserve">11.6263751983643</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7675867080688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8146572113037</t>
+    <t xml:space="preserve">11.7675857543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8146562576294</t>
   </si>
   <si>
     <t xml:space="preserve">11.5793046951294</t>
@@ -1706,10 +1706,10 @@
     <t xml:space="preserve">11.6734447479248</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7205152511597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0029382705688</t>
+    <t xml:space="preserve">11.7205142974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0029373168945</t>
   </si>
   <si>
     <t xml:space="preserve">12.2853603363037</t>
@@ -1721,28 +1721,28 @@
     <t xml:space="preserve">12.5207118988037</t>
   </si>
   <si>
-    <t xml:space="preserve">12.897274017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7560625076294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.661922454834</t>
+    <t xml:space="preserve">12.8972730636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7560634613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6619215011597</t>
   </si>
   <si>
     <t xml:space="preserve">12.6148519515991</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8031330108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8502035140991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9914150238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1796960830688</t>
+    <t xml:space="preserve">12.8031339645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8502044677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9914140701294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1796951293945</t>
   </si>
   <si>
     <t xml:space="preserve">13.4621181488037</t>
@@ -1751,13 +1751,13 @@
     <t xml:space="preserve">13.838680267334</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7445421218872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6504001617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5091896057129</t>
+    <t xml:space="preserve">13.7445411682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6503992080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5091886520386</t>
   </si>
   <si>
     <t xml:space="preserve">13.7916107177734</t>
@@ -1769,10 +1769,10 @@
     <t xml:space="preserve">13.9798927307129</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0269632339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.074031829834</t>
+    <t xml:space="preserve">14.0269622802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0740327835083</t>
   </si>
   <si>
     <t xml:space="preserve">14.168173789978</t>
@@ -1781,13 +1781,13 @@
     <t xml:space="preserve">14.1211032867432</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2623138427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2152452468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4505968093872</t>
+    <t xml:space="preserve">14.2623128890991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2152442932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4505958557129</t>
   </si>
   <si>
     <t xml:space="preserve">14.6859474182129</t>
@@ -1799,13 +1799,13 @@
     <t xml:space="preserve">14.403525352478</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3564548492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5447368621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5918064117432</t>
+    <t xml:space="preserve">14.3564538955688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5447359085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5918073654175</t>
   </si>
   <si>
     <t xml:space="preserve">14.638876914978</t>
@@ -1826,85 +1826,85 @@
     <t xml:space="preserve">15.3449306488037</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7685670852661</t>
+    <t xml:space="preserve">15.7685623168945</t>
   </si>
   <si>
     <t xml:space="preserve">16.0039157867432</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0415725708008</t>
+    <t xml:space="preserve">16.0415744781494</t>
   </si>
   <si>
     <t xml:space="preserve">16.0792293548584</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1921977996826</t>
+    <t xml:space="preserve">16.1921997070312</t>
   </si>
   <si>
     <t xml:space="preserve">16.116886138916</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2298545837402</t>
+    <t xml:space="preserve">16.2298526763916</t>
   </si>
   <si>
     <t xml:space="preserve">16.3804798126221</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3993091583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4181346893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5311050415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2675094604492</t>
+    <t xml:space="preserve">16.3993072509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4181365966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5311031341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2675132751465</t>
   </si>
   <si>
     <t xml:space="preserve">15.9286050796509</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8909482955933</t>
+    <t xml:space="preserve">15.8909473419189</t>
   </si>
   <si>
     <t xml:space="preserve">15.815634727478</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9662599563599</t>
+    <t xml:space="preserve">15.9662609100342</t>
   </si>
   <si>
     <t xml:space="preserve">15.7214956283569</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5332136154175</t>
+    <t xml:space="preserve">15.5332145690918</t>
   </si>
   <si>
     <t xml:space="preserve">15.5143852233887</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7026662826538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2696189880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4767284393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6838369369507</t>
+    <t xml:space="preserve">15.7026672363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2696180343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4767303466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6838388442993</t>
   </si>
   <si>
     <t xml:space="preserve">15.6650104522705</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4202442169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1566505432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2319631576538</t>
+    <t xml:space="preserve">15.4202432632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1566514968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2319641113281</t>
   </si>
   <si>
     <t xml:space="preserve">15.7779788970947</t>
@@ -1928,10 +1928,10 @@
     <t xml:space="preserve">15.8117141723633</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6019096374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5446872711182</t>
+    <t xml:space="preserve">15.6019067764282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5446882247925</t>
   </si>
   <si>
     <t xml:space="preserve">15.2585906982422</t>
@@ -1946,31 +1946,31 @@
     <t xml:space="preserve">16.2503986358643</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2313270568848</t>
+    <t xml:space="preserve">16.2313251495361</t>
   </si>
   <si>
     <t xml:space="preserve">16.0024471282959</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2694721221924</t>
+    <t xml:space="preserve">16.2694702148438</t>
   </si>
   <si>
     <t xml:space="preserve">16.212251663208</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4602069854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4411315917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5364952087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.555570602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1659126281738</t>
+    <t xml:space="preserve">16.460205078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4411296844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5364971160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5555725097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1659145355225</t>
   </si>
   <si>
     <t xml:space="preserve">16.9561080932617</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">17.3185005187988</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0896224975586</t>
+    <t xml:space="preserve">17.08962059021</t>
   </si>
   <si>
     <t xml:space="preserve">16.8416690826416</t>
@@ -1994,31 +1994,31 @@
     <t xml:space="preserve">16.9751815795898</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1277656555176</t>
+    <t xml:space="preserve">17.1277675628662</t>
   </si>
   <si>
     <t xml:space="preserve">17.5092334747314</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5473804473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7571830749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6427440643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7381134033203</t>
+    <t xml:space="preserve">17.5473785400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7571849822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6427459716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7381114959717</t>
   </si>
   <si>
     <t xml:space="preserve">17.4901580810547</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4710845947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.337574005127</t>
+    <t xml:space="preserve">17.4710865020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3375720977783</t>
   </si>
   <si>
     <t xml:space="preserve">17.2994251251221</t>
@@ -2027,19 +2027,19 @@
     <t xml:space="preserve">17.3566474914551</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2422065734863</t>
+    <t xml:space="preserve">17.2422046661377</t>
   </si>
   <si>
     <t xml:space="preserve">17.1468391418457</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0133266448975</t>
+    <t xml:space="preserve">17.0133285522461</t>
   </si>
   <si>
     <t xml:space="preserve">17.4520130157471</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8334789276123</t>
+    <t xml:space="preserve">17.8334770202637</t>
   </si>
   <si>
     <t xml:space="preserve">17.6999645233154</t>
@@ -2060,7 +2060,7 @@
     <t xml:space="preserve">18.5010395050049</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6536273956299</t>
+    <t xml:space="preserve">18.6536254882812</t>
   </si>
   <si>
     <t xml:space="preserve">18.5964069366455</t>
@@ -2075,10 +2075,10 @@
     <t xml:space="preserve">18.8062114715576</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5201148986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5500679016113</t>
+    <t xml:space="preserve">18.520112991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.55006980896</t>
   </si>
   <si>
     <t xml:space="preserve">19.5023880004883</t>
@@ -2093,22 +2093,22 @@
     <t xml:space="preserve">19.4547023773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3593349456787</t>
+    <t xml:space="preserve">19.3593368530273</t>
   </si>
   <si>
     <t xml:space="preserve">19.1686058044434</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7871417999268</t>
+    <t xml:space="preserve">18.7871398925781</t>
   </si>
   <si>
     <t xml:space="preserve">18.6917743682861</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2162857055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1209201812744</t>
+    <t xml:space="preserve">19.216287612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.120922088623</t>
   </si>
   <si>
     <t xml:space="preserve">18.76806640625</t>
@@ -2126,13 +2126,13 @@
     <t xml:space="preserve">17.890697479248</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1005001068115</t>
+    <t xml:space="preserve">18.1005020141602</t>
   </si>
   <si>
     <t xml:space="preserve">18.2530860900879</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9669895172119</t>
+    <t xml:space="preserve">17.9669876098633</t>
   </si>
   <si>
     <t xml:space="preserve">18.1767959594727</t>
@@ -2144,16 +2144,16 @@
     <t xml:space="preserve">19.0732383728027</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9778709411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8825035095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9397258758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9015789031982</t>
+    <t xml:space="preserve">18.9778728485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8825054168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9397239685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9015769958496</t>
   </si>
   <si>
     <t xml:space="preserve">20.0268993377686</t>
@@ -2162,19 +2162,19 @@
     <t xml:space="preserve">20.2176322937012</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2653160095215</t>
+    <t xml:space="preserve">20.2653141021729</t>
   </si>
   <si>
     <t xml:space="preserve">20.7421474456787</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9328804016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2189788818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4573936462402</t>
+    <t xml:space="preserve">20.9328784942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2189769744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4573917388916</t>
   </si>
   <si>
     <t xml:space="preserve">20.6944637298584</t>
@@ -2195,70 +2195,70 @@
     <t xml:space="preserve">20.4083652496338</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1222686767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3116550445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2639713287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5977516174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6454372406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1699485778809</t>
+    <t xml:space="preserve">20.1222667694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.311653137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.263973236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5977535247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.645435333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1699504852295</t>
   </si>
   <si>
     <t xml:space="preserve">19.9315338134766</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7408008575439</t>
+    <t xml:space="preserve">19.7408027648926</t>
   </si>
   <si>
     <t xml:space="preserve">18.8443603515625</t>
   </si>
   <si>
-    <t xml:space="preserve">19.016019821167</t>
+    <t xml:space="preserve">19.0160179138184</t>
   </si>
   <si>
     <t xml:space="preserve">18.0432834625244</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0051345825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1386489868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0623569488525</t>
+    <t xml:space="preserve">18.0051364898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.138650894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0623550415039</t>
   </si>
   <si>
     <t xml:space="preserve">18.081428527832</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6045970916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2612819671631</t>
+    <t xml:space="preserve">17.6045989990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2612800598145</t>
   </si>
   <si>
     <t xml:space="preserve">17.0514736175537</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2885456085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0324020385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7272300720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4792766571045</t>
+    <t xml:space="preserve">16.2885437011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0324039459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7272281646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4792785644531</t>
   </si>
   <si>
     <t xml:space="preserve">16.8225936889648</t>
@@ -2267,16 +2267,16 @@
     <t xml:space="preserve">17.0705490112305</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6509342193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8607425689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3076171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5937175750732</t>
+    <t xml:space="preserve">16.650936126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8607406616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3076190948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5937194824219</t>
   </si>
   <si>
     <t xml:space="preserve">16.6318626403809</t>
@@ -2288,211 +2288,211 @@
     <t xml:space="preserve">14.8771257400513</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4956607818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3730316162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9915647506714</t>
+    <t xml:space="preserve">14.495659828186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3730306625366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9915657043457</t>
   </si>
   <si>
     <t xml:space="preserve">15.0869312286377</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6782007217407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1441507339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9452247619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0787410736084</t>
+    <t xml:space="preserve">15.678201675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1441497802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9452266693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0787391662598</t>
   </si>
   <si>
     <t xml:space="preserve">16.0405921936035</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5746440887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6890850067139</t>
+    <t xml:space="preserve">16.5746421813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6890830993652</t>
   </si>
   <si>
     <t xml:space="preserve">16.5174236297607</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4983501434326</t>
+    <t xml:space="preserve">16.4983520507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7354202270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8880052566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5065422058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9724912643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3348827362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2204427719116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9152727127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7817583084106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8961982727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6400547027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0978107452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2395162582397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1060047149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0063896179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1999359130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.354772567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0450973510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1418724060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2773532867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4709014892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7805786132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1483173370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.767671585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4192848205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2321834564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7289619445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9418640136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4967021942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5934772491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4579944610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8967056274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4515476226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9870338439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8321933746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9483222961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3676795959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4450988769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1741333007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1160678863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1354236602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3289709091187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.619291305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8902587890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7547760009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8128385543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.161226272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6580009460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.870903968811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4128360748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4321918487549</t>
   </si>
   <si>
     <t xml:space="preserve">15.7354211807251</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8880052566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5065412521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9724912643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3348827362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2204427719116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9152717590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.781759262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8961992263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6400547027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0978126525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2395153045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1060047149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0063877105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1999359130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3547744750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0450973510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1418704986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2773532867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4709033966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7805767059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1483173370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.767671585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.419282913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2321853637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7289600372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9418659210205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4967041015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5934791564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4579963684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8967037200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4515476226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9870338439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8321962356567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9483232498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3676805496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4450988769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1741333007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1160688400269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.135422706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3289709091187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.619291305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8902597427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7547750473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8128395080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.161226272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6580018997192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.870903968811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4128360748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4321899414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7354202270508</t>
-  </si>
-  <si>
     <t xml:space="preserve">15.7160663604736</t>
   </si>
   <si>
     <t xml:space="preserve">16.0644512176514</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5289669036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6838054656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5096111297607</t>
+    <t xml:space="preserve">16.5289649963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6838035583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5096092224121</t>
   </si>
   <si>
     <t xml:space="preserve">16.9160594940186</t>
@@ -2501,10 +2501,10 @@
     <t xml:space="preserve">17.5354137420654</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3805732727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3418674468994</t>
+    <t xml:space="preserve">17.3805751800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3418655395508</t>
   </si>
   <si>
     <t xml:space="preserve">17.2063827514648</t>
@@ -2513,13 +2513,13 @@
     <t xml:space="preserve">17.3225116729736</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2838020324707</t>
+    <t xml:space="preserve">17.2838039398193</t>
   </si>
   <si>
     <t xml:space="preserve">17.0515441894531</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8386421203613</t>
+    <t xml:space="preserve">16.83864402771</t>
   </si>
   <si>
     <t xml:space="preserve">17.2450904846191</t>
@@ -2528,16 +2528,16 @@
     <t xml:space="preserve">17.6128330230713</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8192882537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1096096038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7225131988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.128963470459</t>
+    <t xml:space="preserve">16.8192863464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1096076965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7225151062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1289653778076</t>
   </si>
   <si>
     <t xml:space="preserve">16.8773517608643</t>
@@ -2558,7 +2558,7 @@
     <t xml:space="preserve">15.5031642913818</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2128419876099</t>
+    <t xml:space="preserve">15.2128429412842</t>
   </si>
   <si>
     <t xml:space="preserve">15.3096160888672</t>
@@ -2576,37 +2576,37 @@
     <t xml:space="preserve">16.0838069915771</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7741289138794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.677357673645</t>
+    <t xml:space="preserve">15.7741298675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6773567199707</t>
   </si>
   <si>
     <t xml:space="preserve">15.5612277984619</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1805782318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8579978942871</t>
+    <t xml:space="preserve">16.1805801391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8579959869385</t>
   </si>
   <si>
     <t xml:space="preserve">17.3031558990479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9031524658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8063812255859</t>
+    <t xml:space="preserve">17.9031543731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8063793182373</t>
   </si>
   <si>
     <t xml:space="preserve">17.1676731109619</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5160598754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3612194061279</t>
+    <t xml:space="preserve">17.5160579681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3612213134766</t>
   </si>
   <si>
     <t xml:space="preserve">18.735408782959</t>
@@ -2633,7 +2633,7 @@
     <t xml:space="preserve">18.0386352539062</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0967025756836</t>
+    <t xml:space="preserve">18.096700668335</t>
   </si>
   <si>
     <t xml:space="preserve">18.2128295898438</t>
@@ -2645,7 +2645,7 @@
     <t xml:space="preserve">18.1547660827637</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0192813873291</t>
+    <t xml:space="preserve">18.0192832946777</t>
   </si>
   <si>
     <t xml:space="preserve">17.9805736541748</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">17.6321868896484</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6515426635742</t>
+    <t xml:space="preserve">17.6515407562256</t>
   </si>
   <si>
     <t xml:space="preserve">17.4386405944824</t>
@@ -2672,7 +2672,7 @@
     <t xml:space="preserve">17.3999290466309</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2644462585449</t>
+    <t xml:space="preserve">17.2644481658936</t>
   </si>
   <si>
     <t xml:space="preserve">17.7096061706543</t>
@@ -2681,52 +2681,52 @@
     <t xml:space="preserve">17.4773483276367</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8257369995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5805721282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9289569854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8128299713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5483093261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9354057312012</t>
+    <t xml:space="preserve">17.8257350921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5805702209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.928955078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8128280639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5483112335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9354038238525</t>
   </si>
   <si>
     <t xml:space="preserve">19.7902450561523</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0321769714355</t>
+    <t xml:space="preserve">20.0321788787842</t>
   </si>
   <si>
     <t xml:space="preserve">19.7418556213379</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5966968536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9837894439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8386287689209</t>
+    <t xml:space="preserve">19.5966949462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9837913513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8386306762695</t>
   </si>
   <si>
     <t xml:space="preserve">20.0805644989014</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3708839416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8870162963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6450805664062</t>
+    <t xml:space="preserve">20.370885848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8870182037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6450824737549</t>
   </si>
   <si>
     <t xml:space="preserve">20.1289520263672</t>
@@ -2735,13 +2735,13 @@
     <t xml:space="preserve">20.177339553833</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4192752838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.467658996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2418518066406</t>
+    <t xml:space="preserve">20.4192733764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4676609039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.241849899292</t>
   </si>
   <si>
     <t xml:space="preserve">21.1934623718262</t>
@@ -2750,22 +2750,22 @@
     <t xml:space="preserve">21.435396194458</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5805587768555</t>
+    <t xml:space="preserve">21.5805568695068</t>
   </si>
   <si>
     <t xml:space="preserve">21.6773319244385</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6289443969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0644283294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2579727172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6450710296631</t>
+    <t xml:space="preserve">21.6289463043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0644264221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2579765319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6450691223145</t>
   </si>
   <si>
     <t xml:space="preserve">23.0321655273438</t>
@@ -2777,13 +2777,13 @@
     <t xml:space="preserve">23.3224868774414</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7902297973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7418422698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9676532745361</t>
+    <t xml:space="preserve">22.7902317047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7418441772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9676551818848</t>
   </si>
   <si>
     <t xml:space="preserve">22.6934585571289</t>
@@ -2795,16 +2795,16 @@
     <t xml:space="preserve">22.3063621520996</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8224925994873</t>
+    <t xml:space="preserve">21.8224906921387</t>
   </si>
   <si>
     <t xml:space="preserve">22.3547496795654</t>
   </si>
   <si>
-    <t xml:space="preserve">22.112813949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5482959747314</t>
+    <t xml:space="preserve">22.1128158569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5482978820801</t>
   </si>
   <si>
     <t xml:space="preserve">22.9837779998779</t>
@@ -2813,13 +2813,13 @@
     <t xml:space="preserve">23.9031295776367</t>
   </si>
   <si>
-    <t xml:space="preserve">24.193452835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0966758728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0160312652588</t>
+    <t xml:space="preserve">24.1934509277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0966777801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0160293579102</t>
   </si>
   <si>
     <t xml:space="preserve">24.9676399230957</t>
@@ -2828,28 +2828,28 @@
     <t xml:space="preserve">25.4031238555908</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8386058807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9353790283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.354736328125</t>
+    <t xml:space="preserve">25.8386077880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9353809356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3547382354736</t>
   </si>
   <si>
     <t xml:space="preserve">25.161190032959</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8708686828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.257963180542</t>
+    <t xml:space="preserve">24.8708667755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2579650878906</t>
   </si>
   <si>
     <t xml:space="preserve">25.451509475708</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2095737457275</t>
+    <t xml:space="preserve">25.2095756530762</t>
   </si>
   <si>
     <t xml:space="preserve">25.5482845306396</t>
@@ -2858,19 +2858,19 @@
     <t xml:space="preserve">25.6450595855713</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1773128509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5160217285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9515056610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6934432983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5966720581055</t>
+    <t xml:space="preserve">26.1773147583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5160236358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9515037536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6934452056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5966739654541</t>
   </si>
   <si>
     <t xml:space="preserve">25.3063507080078</t>
@@ -2879,7 +2879,7 @@
     <t xml:space="preserve">25.8869934082031</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3708629608154</t>
+    <t xml:space="preserve">26.3708610534668</t>
   </si>
   <si>
     <t xml:space="preserve">26.2043304443359</t>
@@ -2888,7 +2888,7 @@
     <t xml:space="preserve">25.616569519043</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1267700195312</t>
+    <t xml:space="preserve">25.1267681121826</t>
   </si>
   <si>
     <t xml:space="preserve">25.9594306945801</t>
@@ -2900,16 +2900,16 @@
     <t xml:space="preserve">25.2737083435059</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0288066864014</t>
+    <t xml:space="preserve">25.02880859375</t>
   </si>
   <si>
     <t xml:space="preserve">25.2247295379639</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7349281311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4410495758057</t>
+    <t xml:space="preserve">24.7349300384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.441047668457</t>
   </si>
   <si>
     <t xml:space="preserve">24.8818683624268</t>
@@ -2924,10 +2924,10 @@
     <t xml:space="preserve">24.4900283813477</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7839088439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8328876495361</t>
+    <t xml:space="preserve">24.7839069366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8328895568848</t>
   </si>
   <si>
     <t xml:space="preserve">24.979829788208</t>
@@ -2936,19 +2936,19 @@
     <t xml:space="preserve">25.4696292877197</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9104499816895</t>
+    <t xml:space="preserve">25.9104518890381</t>
   </si>
   <si>
     <t xml:space="preserve">25.8614692687988</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7635097503662</t>
+    <t xml:space="preserve">25.7635078430176</t>
   </si>
   <si>
     <t xml:space="preserve">25.7145290374756</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2533092498779</t>
+    <t xml:space="preserve">26.2533111572266</t>
   </si>
   <si>
     <t xml:space="preserve">26.6941299438477</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">26.7920913696289</t>
   </si>
   <si>
-    <t xml:space="preserve">26.596170425415</t>
+    <t xml:space="preserve">26.5961685180664</t>
   </si>
   <si>
     <t xml:space="preserve">26.4492301940918</t>
@@ -2990,7 +2990,7 @@
     <t xml:space="preserve">25.3716678619385</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1471691131592</t>
+    <t xml:space="preserve">24.1471672058105</t>
   </si>
   <si>
     <t xml:space="preserve">26.3512687683105</t>
@@ -3005,13 +3005,13 @@
     <t xml:space="preserve">26.9880104064941</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9390316009521</t>
+    <t xml:space="preserve">26.9390296936035</t>
   </si>
   <si>
     <t xml:space="preserve">26.0573902130127</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1063709259033</t>
+    <t xml:space="preserve">26.1063690185547</t>
   </si>
   <si>
     <t xml:space="preserve">26.6451511383057</t>
@@ -3026,40 +3026,40 @@
     <t xml:space="preserve">27.134952545166</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1553497314453</t>
+    <t xml:space="preserve">26.1553516387939</t>
   </si>
   <si>
     <t xml:space="preserve">27.3798522949219</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3308696746826</t>
+    <t xml:space="preserve">27.3308715820312</t>
   </si>
   <si>
     <t xml:space="preserve">27.7227115631104</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6737308502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0165920257568</t>
+    <t xml:space="preserve">27.6737327575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0165939331055</t>
   </si>
   <si>
     <t xml:space="preserve">27.5757713317871</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4778099060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5267925262451</t>
+    <t xml:space="preserve">27.4778118133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5267906188965</t>
   </si>
   <si>
     <t xml:space="preserve">25.8124904632568</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3022918701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2818927764893</t>
+    <t xml:space="preserve">26.3022899627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2818908691406</t>
   </si>
   <si>
     <t xml:space="preserve">27.4288330078125</t>
@@ -3068,13 +3068,13 @@
     <t xml:space="preserve">27.23291015625</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6247539520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8410701751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4982089996338</t>
+    <t xml:space="preserve">27.6247520446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8410720825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4982109069824</t>
   </si>
   <si>
     <t xml:space="preserve">25.567590713501</t>
@@ -3101,7 +3101,7 @@
     <t xml:space="preserve">28.5553722381592</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0451736450195</t>
+    <t xml:space="preserve">29.0451717376709</t>
   </si>
   <si>
     <t xml:space="preserve">29.1431331634521</t>
@@ -3119,10 +3119,10 @@
     <t xml:space="preserve">29.6819133758545</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7798748016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1921119689941</t>
+    <t xml:space="preserve">29.7798728942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1921138763428</t>
   </si>
   <si>
     <t xml:space="preserve">29.5349731445312</t>
@@ -3134,10 +3134,10 @@
     <t xml:space="preserve">30.2206954956055</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5145740509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8574352264404</t>
+    <t xml:space="preserve">30.514575958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8574371337891</t>
   </si>
   <si>
     <t xml:space="preserve">32.1798973083496</t>
@@ -3152,10 +3152,10 @@
     <t xml:space="preserve">32.5227584838867</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0901184082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.824821472168</t>
+    <t xml:space="preserve">34.0901222229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8248176574707</t>
   </si>
   <si>
     <t xml:space="preserve">34.2860374450684</t>
@@ -3164,22 +3164,22 @@
     <t xml:space="preserve">34.6288986206055</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1390991210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7758407592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.747257232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8941955566406</t>
+    <t xml:space="preserve">34.1390953063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7758369445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7472610473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8941993713379</t>
   </si>
   <si>
     <t xml:space="preserve">34.335018157959</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9431838989258</t>
+    <t xml:space="preserve">33.9431800842285</t>
   </si>
   <si>
     <t xml:space="preserve">35.0207405090332</t>
@@ -3188,7 +3188,7 @@
     <t xml:space="preserve">35.4125823974609</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9635810852051</t>
+    <t xml:space="preserve">32.9635772705078</t>
   </si>
   <si>
     <t xml:space="preserve">32.9145965576172</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">33.0125579833984</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4451942443848</t>
+    <t xml:space="preserve">31.4451961517334</t>
   </si>
   <si>
     <t xml:space="preserve">31.5641193389893</t>
@@ -3867,6 +3867,9 @@
   </si>
   <si>
     <t xml:space="preserve">48.0499992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8499984741211</t>
   </si>
 </sst>
 </file>
@@ -70297,7 +70300,7 @@
     </row>
     <row r="2543">
       <c r="A2543" s="1" t="n">
-        <v>46027.6911921296</v>
+        <v>46027.3333333333</v>
       </c>
       <c r="B2543" t="n">
         <v>32077</v>
@@ -70318,6 +70321,32 @@
         <v>1232</v>
       </c>
       <c r="H2543" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2544">
+      <c r="A2544" s="1" t="n">
+        <v>46028.6829861111</v>
+      </c>
+      <c r="B2544" t="n">
+        <v>24038</v>
+      </c>
+      <c r="C2544" t="n">
+        <v>48.6500015258789</v>
+      </c>
+      <c r="D2544" t="n">
+        <v>48</v>
+      </c>
+      <c r="E2544" t="n">
+        <v>48.0499992370605</v>
+      </c>
+      <c r="F2544" t="n">
+        <v>48.8499984741211</v>
+      </c>
+      <c r="G2544" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H2544" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SOL.MI.xlsx
+++ b/data/SOL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="1286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1285" uniqueCount="1285">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,91 +44,91 @@
     <t xml:space="preserve">SOL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14067268371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18862533569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1624698638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06220436096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90962553024292</t>
+    <t xml:space="preserve">7.1406717300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1886248588562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16247081756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0622034072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90962600708008</t>
   </si>
   <si>
     <t xml:space="preserve">6.90526580810547</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94885921478271</t>
+    <t xml:space="preserve">6.94885969161987</t>
   </si>
   <si>
     <t xml:space="preserve">6.71781206130981</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62626504898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71345186233521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29931116104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36470174789429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43009376525879</t>
+    <t xml:space="preserve">6.62626552581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71345233917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29931163787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36470222473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43009233474731</t>
   </si>
   <si>
     <t xml:space="preserve">6.41265487670898</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44753074645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.207763671875</t>
+    <t xml:space="preserve">6.4475302696228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20776414871216</t>
   </si>
   <si>
     <t xml:space="preserve">6.1728892326355</t>
   </si>
   <si>
-    <t xml:space="preserve">6.460608959198</t>
+    <t xml:space="preserve">6.46060800552368</t>
   </si>
   <si>
     <t xml:space="preserve">6.54779624938965</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38213968276978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51291990280151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50420331954956</t>
+    <t xml:space="preserve">6.38213920593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51292133331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50420188903809</t>
   </si>
   <si>
     <t xml:space="preserve">6.65242147445679</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80064010620117</t>
+    <t xml:space="preserve">6.80064058303833</t>
   </si>
   <si>
     <t xml:space="preserve">6.72217178344727</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79192209243774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00989103317261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84423494338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07964181900024</t>
+    <t xml:space="preserve">6.79192113876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00989055633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84423398971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07964134216309</t>
   </si>
   <si>
     <t xml:space="preserve">6.88346910476685</t>
@@ -137,31 +137,31 @@
     <t xml:space="preserve">6.96629667282104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08835887908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73524904251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8311562538147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67857789993286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57395219802856</t>
+    <t xml:space="preserve">7.08836030960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73524951934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83115673065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67857837677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57395267486572</t>
   </si>
   <si>
     <t xml:space="preserve">6.63062477111816</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68729686737061</t>
+    <t xml:space="preserve">6.68729639053345</t>
   </si>
   <si>
     <t xml:space="preserve">6.783203125</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77884387969971</t>
+    <t xml:space="preserve">6.77884292602539</t>
   </si>
   <si>
     <t xml:space="preserve">6.81371879577637</t>
@@ -176,28 +176,28 @@
     <t xml:space="preserve">6.69601535797119</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81807947158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87475061416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9139838218689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67421865463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55215549468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46496868133545</t>
+    <t xml:space="preserve">6.81807804107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8747501373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91398525238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67421817779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5521559715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46496820449829</t>
   </si>
   <si>
     <t xml:space="preserve">6.43881177902222</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73088932037354</t>
+    <t xml:space="preserve">6.73088979721069</t>
   </si>
   <si>
     <t xml:space="preserve">6.87910938262939</t>
@@ -212,109 +212,109 @@
     <t xml:space="preserve">6.85731220245361</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74832725524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51728105545044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37342119216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56523370742798</t>
+    <t xml:space="preserve">6.74832773208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51728057861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37342071533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56523466110229</t>
   </si>
   <si>
     <t xml:space="preserve">6.66985893249512</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7701244354248</t>
+    <t xml:space="preserve">6.77012491226196</t>
   </si>
   <si>
     <t xml:space="preserve">6.86167192459106</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97501659393311</t>
+    <t xml:space="preserve">6.97501611709595</t>
   </si>
   <si>
     <t xml:space="preserve">6.9416298866272</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95048379898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88407850265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9017858505249</t>
+    <t xml:space="preserve">6.95048332214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88407802581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90178632736206</t>
   </si>
   <si>
     <t xml:space="preserve">7.34006500244141</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22496175765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41975116729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43745994567871</t>
+    <t xml:space="preserve">7.22496128082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41975164413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43746089935303</t>
   </si>
   <si>
     <t xml:space="preserve">7.36662769317627</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26037788391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46845054626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40204334259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44631481170654</t>
+    <t xml:space="preserve">7.26037836074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46845006942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40204429626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44631433486938</t>
   </si>
   <si>
     <t xml:space="preserve">7.38433504104614</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04345178604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97261905670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10985803604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87079620361328</t>
+    <t xml:space="preserve">7.04345226287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9726185798645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1098575592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87079668045044</t>
   </si>
   <si>
     <t xml:space="preserve">7.20725345611572</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37105369567871</t>
+    <t xml:space="preserve">7.37105321884155</t>
   </si>
   <si>
     <t xml:space="preserve">7.57027149200439</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69422960281372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70308351516724</t>
+    <t xml:space="preserve">7.6942286491394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70308446884155</t>
   </si>
   <si>
     <t xml:space="preserve">7.71193790435791</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65881252288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04396820068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61454296112061</t>
+    <t xml:space="preserve">7.6588134765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04396724700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61454248428345</t>
   </si>
   <si>
     <t xml:space="preserve">7.29579401016235</t>
@@ -323,172 +323,172 @@
     <t xml:space="preserve">6.99475479125977</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1010046005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55256509780884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3135027885437</t>
+    <t xml:space="preserve">7.10100412368774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55256462097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31350183486938</t>
   </si>
   <si>
     <t xml:space="preserve">7.50829219818115</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4241795539856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37548208236694</t>
+    <t xml:space="preserve">7.42418003082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3754825592041</t>
   </si>
   <si>
     <t xml:space="preserve">7.52600240707397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54371070861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41532516479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21610689163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99032783508301</t>
+    <t xml:space="preserve">7.54370880126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41532468795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21610641479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99032735824585</t>
   </si>
   <si>
     <t xml:space="preserve">6.79996347427368</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7556939125061</t>
+    <t xml:space="preserve">6.75569295883179</t>
   </si>
   <si>
     <t xml:space="preserve">7.00803565979004</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26923227310181</t>
+    <t xml:space="preserve">7.26923322677612</t>
   </si>
   <si>
     <t xml:space="preserve">7.34449195861816</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46402263641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51714754104614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39318990707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4551682472229</t>
+    <t xml:space="preserve">7.46402311325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51714658737183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39318895339966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45516872406006</t>
   </si>
   <si>
     <t xml:space="preserve">7.1718373298645</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33563709259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33121013641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39761734008789</t>
+    <t xml:space="preserve">7.33563756942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33121109008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39761686325073</t>
   </si>
   <si>
     <t xml:space="preserve">7.30464935302734</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27808618545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25152397155762</t>
+    <t xml:space="preserve">7.27808666229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25152349472046</t>
   </si>
   <si>
     <t xml:space="preserve">7.16298294067383</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03017044067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87965154647827</t>
+    <t xml:space="preserve">7.03017139434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87965059280396</t>
   </si>
   <si>
     <t xml:space="preserve">6.91064071655273</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95491075515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88850545883179</t>
+    <t xml:space="preserve">6.95491123199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88850498199463</t>
   </si>
   <si>
     <t xml:space="preserve">6.95933818817139</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85751533508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77340078353882</t>
+    <t xml:space="preserve">6.85751581192017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77340126037598</t>
   </si>
   <si>
     <t xml:space="preserve">6.74683904647827</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8265266418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68486022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81767129898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90621280670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01688957214355</t>
+    <t xml:space="preserve">6.82652616500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68486070632935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81767177581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90621328353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01689052581787</t>
   </si>
   <si>
     <t xml:space="preserve">6.8973593711853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8353796005249</t>
+    <t xml:space="preserve">6.83538055419922</t>
   </si>
   <si>
     <t xml:space="preserve">6.86194276809692</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92392253875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97704648971558</t>
+    <t xml:space="preserve">6.92392206192017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97704601287842</t>
   </si>
   <si>
     <t xml:space="preserve">7.00360822677612</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91506767272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91949462890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93720245361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07001543045044</t>
+    <t xml:space="preserve">6.91506719589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91949415206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9372034072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07001447677612</t>
   </si>
   <si>
     <t xml:space="preserve">6.98590040206909</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75126647949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77782821655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64944362640381</t>
+    <t xml:space="preserve">6.75126600265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77782773971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64944410324097</t>
   </si>
   <si>
     <t xml:space="preserve">6.38381958007812</t>
@@ -497,37 +497,37 @@
     <t xml:space="preserve">6.37053966522217</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36168575286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37939310073853</t>
+    <t xml:space="preserve">6.36168527603149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37939262390137</t>
   </si>
   <si>
     <t xml:space="preserve">6.40595531463623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48121547698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47678852081299</t>
+    <t xml:space="preserve">6.48121643066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47678804397583</t>
   </si>
   <si>
     <t xml:space="preserve">6.54319429397583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46350717544556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24215459823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25986289978027</t>
+    <t xml:space="preserve">6.46350765228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24215507507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25986242294312</t>
   </si>
   <si>
     <t xml:space="preserve">6.22444629669189</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64501619338989</t>
+    <t xml:space="preserve">6.64501667022705</t>
   </si>
   <si>
     <t xml:space="preserve">6.64058971405029</t>
@@ -536,7 +536,7 @@
     <t xml:space="preserve">7.03902435302734</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79110956192017</t>
+    <t xml:space="preserve">6.79111003875732</t>
   </si>
   <si>
     <t xml:space="preserve">6.70256853103638</t>
@@ -545,34 +545,34 @@
     <t xml:space="preserve">6.70699548721313</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65829753875732</t>
+    <t xml:space="preserve">6.65829801559448</t>
   </si>
   <si>
     <t xml:space="preserve">6.58303785324097</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05673313140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11428499221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34891939163208</t>
+    <t xml:space="preserve">7.05673360824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11428546905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34891843795776</t>
   </si>
   <si>
     <t xml:space="preserve">7.18511819839478</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12756681442261</t>
+    <t xml:space="preserve">7.12756633758545</t>
   </si>
   <si>
     <t xml:space="preserve">7.19397163391113</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24267053604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41089773178101</t>
+    <t xml:space="preserve">7.2426700592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41089868545532</t>
   </si>
   <si>
     <t xml:space="preserve">7.48173141479492</t>
@@ -584,16 +584,16 @@
     <t xml:space="preserve">7.27365970611572</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17626285552979</t>
+    <t xml:space="preserve">7.1762638092041</t>
   </si>
   <si>
     <t xml:space="preserve">7.04787921905518</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23381567001343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29136657714844</t>
+    <t xml:space="preserve">7.23381519317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2913670539856</t>
   </si>
   <si>
     <t xml:space="preserve">7.4286060333252</t>
@@ -602,28 +602,28 @@
     <t xml:space="preserve">7.83589601516724</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8270411491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13693714141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27860355377197</t>
+    <t xml:space="preserve">7.82704257965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13693428039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27860260009766</t>
   </si>
   <si>
     <t xml:space="preserve">8.32287120819092</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0312032699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53094482421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49995422363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26089286804199</t>
+    <t xml:space="preserve">9.03120136260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53094577789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49995613098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26089382171631</t>
   </si>
   <si>
     <t xml:space="preserve">8.92495250701904</t>
@@ -635,25 +635,25 @@
     <t xml:space="preserve">8.97807693481445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7655782699585</t>
+    <t xml:space="preserve">8.76557731628418</t>
   </si>
   <si>
     <t xml:space="preserve">8.87182807922363</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56244945526123</t>
+    <t xml:space="preserve">9.56245040893555</t>
   </si>
   <si>
     <t xml:space="preserve">9.25255393981934</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02234840393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85411930084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82755851745605</t>
+    <t xml:space="preserve">9.02234649658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8541202545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82755756378174</t>
   </si>
   <si>
     <t xml:space="preserve">8.71245384216309</t>
@@ -662,67 +662,67 @@
     <t xml:space="preserve">8.98693180084229</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89839172363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80984783172607</t>
+    <t xml:space="preserve">8.8983907699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80984878540039</t>
   </si>
   <si>
     <t xml:space="preserve">8.72130870819092</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78328800201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67703628540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75672435760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10203552246094</t>
+    <t xml:space="preserve">8.78328609466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67703819274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7567253112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10203266143799</t>
   </si>
   <si>
     <t xml:space="preserve">8.82312965393066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94266033172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20828437805176</t>
+    <t xml:space="preserve">8.94266223907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20828533172607</t>
   </si>
   <si>
     <t xml:space="preserve">9.43287658691406</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45982646942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52271461486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3250732421875</t>
+    <t xml:space="preserve">9.4598274230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52271270751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32507419586182</t>
   </si>
   <si>
     <t xml:space="preserve">9.38795757293701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35202312469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42389297485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29812145233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55864810943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67543697357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86409282684326</t>
+    <t xml:space="preserve">9.35202217102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4238920211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29812049865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55865001678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67543601989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86409378051758</t>
   </si>
   <si>
     <t xml:space="preserve">10.5199041366577</t>
@@ -731,34 +731,34 @@
     <t xml:space="preserve">10.0617341995239</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88206195831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74730587005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56763076782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44185924530029</t>
+    <t xml:space="preserve">9.88206100463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74730491638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56763172149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44186115264893</t>
   </si>
   <si>
     <t xml:space="preserve">9.54068088531494</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34303951263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36100769042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50474548339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48677921295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.612548828125</t>
+    <t xml:space="preserve">9.34304046630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36100578308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50474643707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48678016662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61255073547363</t>
   </si>
   <si>
     <t xml:space="preserve">9.77425670623779</t>
@@ -773,31 +773,31 @@
     <t xml:space="preserve">9.4777946472168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70238780975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30710411071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28015422821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2172679901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16336631774902</t>
+    <t xml:space="preserve">9.7023868560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30710506439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28015327453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21726703643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16336536407471</t>
   </si>
   <si>
     <t xml:space="preserve">9.25320434570312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45084381103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58559989929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33405780792236</t>
+    <t xml:space="preserve">9.45084476470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58559894561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33405685424805</t>
   </si>
   <si>
     <t xml:space="preserve">9.59458255767822</t>
@@ -809,61 +809,61 @@
     <t xml:space="preserve">9.71137142181396</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40592479705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26218700408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2711706161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.289137840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36999130249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65746879577637</t>
+    <t xml:space="preserve">9.40592575073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26218605041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27116966247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28913688659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36999225616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65746974945068</t>
   </si>
   <si>
     <t xml:space="preserve">9.79222393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76527404785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72035503387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81019115447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37897300720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90901184082031</t>
+    <t xml:space="preserve">9.76527214050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7203540802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81019020080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37897396087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90901279449463</t>
   </si>
   <si>
     <t xml:space="preserve">9.81917572021484</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73832130432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78324127197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69340419769287</t>
+    <t xml:space="preserve">9.73832321166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78324222564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69340324401855</t>
   </si>
   <si>
     <t xml:space="preserve">9.11844635009766</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08251094818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31608867645264</t>
+    <t xml:space="preserve">9.08251285552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31608772277832</t>
   </si>
   <si>
     <t xml:space="preserve">9.19031715393066</t>
@@ -875,19 +875,19 @@
     <t xml:space="preserve">9.22625255584717</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41490745544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39694023132324</t>
+    <t xml:space="preserve">9.41490936279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39694118499756</t>
   </si>
   <si>
     <t xml:space="preserve">9.07352924346924</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57661628723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68441963195801</t>
+    <t xml:space="preserve">9.57661437988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68442058563232</t>
   </si>
   <si>
     <t xml:space="preserve">9.09149646759033</t>
@@ -896,16 +896,16 @@
     <t xml:space="preserve">9.05556106567383</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14539813995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89385604858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10946369171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23523426055908</t>
+    <t xml:space="preserve">9.1453971862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89385509490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10946464538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2352352142334</t>
   </si>
   <si>
     <t xml:space="preserve">9.95392990112305</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">10.7444953918457</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5468549728394</t>
+    <t xml:space="preserve">10.546854019165</t>
   </si>
   <si>
     <t xml:space="preserve">10.6905927658081</t>
@@ -938,19 +938,19 @@
     <t xml:space="preserve">10.5288877487183</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4390487670898</t>
+    <t xml:space="preserve">10.4390506744385</t>
   </si>
   <si>
     <t xml:space="preserve">10.3312454223633</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1695394515991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1875085830688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1336050033569</t>
+    <t xml:space="preserve">10.1695404052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1875076293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1336040496826</t>
   </si>
   <si>
     <t xml:space="preserve">9.75629043579102</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">9.63051795959473</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0078325271606</t>
+    <t xml:space="preserve">10.007833480835</t>
   </si>
   <si>
     <t xml:space="preserve">9.84612655639648</t>
@@ -968,7 +968,7 @@
     <t xml:space="preserve">10.0976705551147</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2054748535156</t>
+    <t xml:space="preserve">10.205472946167</t>
   </si>
   <si>
     <t xml:space="preserve">10.2773427963257</t>
@@ -977,10 +977,10 @@
     <t xml:space="preserve">10.2234420776367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2414073944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7624616622925</t>
+    <t xml:space="preserve">10.2414083480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7624626159668</t>
   </si>
   <si>
     <t xml:space="preserve">10.2593765258789</t>
@@ -995,13 +995,13 @@
     <t xml:space="preserve">9.67380714416504</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74667835235596</t>
+    <t xml:space="preserve">9.74667930603027</t>
   </si>
   <si>
     <t xml:space="preserve">9.87420558929443</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1656951904297</t>
+    <t xml:space="preserve">10.1656942367554</t>
   </si>
   <si>
     <t xml:space="preserve">9.85598754882812</t>
@@ -1013,28 +1013,28 @@
     <t xml:space="preserve">9.47340774536133</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76489734649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96529483795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0746049880981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2385663986206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3843126296997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4207496643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8033285140991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6940183639526</t>
+    <t xml:space="preserve">9.76489639282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96529579162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0746059417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2385692596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3843116760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.420747756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8033275604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6940202713013</t>
   </si>
   <si>
     <t xml:space="preserve">10.6211471557617</t>
@@ -1052,25 +1052,25 @@
     <t xml:space="preserve">10.2203493118286</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1474771499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3296585083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5847101211548</t>
+    <t xml:space="preserve">10.1474781036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3296575546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5847120285034</t>
   </si>
   <si>
     <t xml:space="preserve">10.3478755950928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72846031188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56449699401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41875457763672</t>
+    <t xml:space="preserve">9.72846126556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56449794769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4187536239624</t>
   </si>
   <si>
     <t xml:space="preserve">9.40053462982178</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">9.54627990722656</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1110410690308</t>
+    <t xml:space="preserve">10.1110401153564</t>
   </si>
   <si>
     <t xml:space="preserve">10.2567853927612</t>
@@ -1088,37 +1088,37 @@
     <t xml:space="preserve">9.92885971069336</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0199499130249</t>
+    <t xml:space="preserve">10.0199489593506</t>
   </si>
   <si>
     <t xml:space="preserve">10.2021312713623</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0928220748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80133438110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69202327728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83776950836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94707870483398</t>
+    <t xml:space="preserve">10.0928230285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8013334274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69202518463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83777046203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94707679748535</t>
   </si>
   <si>
     <t xml:space="preserve">9.89242362976074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6555871963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78311443328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91064167022705</t>
+    <t xml:space="preserve">9.65558815002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78311347961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91064262390137</t>
   </si>
   <si>
     <t xml:space="preserve">9.45519065856934</t>
@@ -1127,49 +1127,49 @@
     <t xml:space="preserve">9.20013618469238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50984382629395</t>
+    <t xml:space="preserve">9.50984287261963</t>
   </si>
   <si>
     <t xml:space="preserve">9.43697071075439</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81955242156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49162578582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6191520690918</t>
+    <t xml:space="preserve">9.81955051422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49162483215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61915397644043</t>
   </si>
   <si>
     <t xml:space="preserve">9.98351383209229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6009349822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10904598236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09993743896484</t>
+    <t xml:space="preserve">9.60093402862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10904693603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09993648529053</t>
   </si>
   <si>
     <t xml:space="preserve">9.38231754302979</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36409854888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27301025390625</t>
+    <t xml:space="preserve">9.36409950256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27300834655762</t>
   </si>
   <si>
     <t xml:space="preserve">9.71024227142334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58271598815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29122638702393</t>
+    <t xml:space="preserve">9.5827169418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29122734069824</t>
   </si>
   <si>
     <t xml:space="preserve">9.14548206329346</t>
@@ -1178,7 +1178,7 @@
     <t xml:space="preserve">10.3660945892334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32766342163086</t>
+    <t xml:space="preserve">9.32766246795654</t>
   </si>
   <si>
     <t xml:space="preserve">10.0017318725586</t>
@@ -1190,10 +1190,10 @@
     <t xml:space="preserve">10.8397645950317</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5664939880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3114395141602</t>
+    <t xml:space="preserve">10.5664930343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3114404678345</t>
   </si>
   <si>
     <t xml:space="preserve">10.2932233810425</t>
@@ -1202,40 +1202,40 @@
     <t xml:space="preserve">10.0381689071655</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0563850402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1292581558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2750034332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1839122772217</t>
+    <t xml:space="preserve">10.0563869476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1292591094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2750015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.183913230896</t>
   </si>
   <si>
     <t xml:space="preserve">10.6758012771606</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7122392654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9308547973633</t>
+    <t xml:space="preserve">10.7122373580933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9308557510376</t>
   </si>
   <si>
     <t xml:space="preserve">11.0219459533691</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8762006759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.894419670105</t>
+    <t xml:space="preserve">10.87619972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8944177627563</t>
   </si>
   <si>
     <t xml:space="preserve">10.7304544448853</t>
   </si>
   <si>
-    <t xml:space="preserve">10.65758228302</t>
+    <t xml:space="preserve">10.6575841903687</t>
   </si>
   <si>
     <t xml:space="preserve">11.2644634246826</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">11.1349859237671</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0979928970337</t>
+    <t xml:space="preserve">11.097993850708</t>
   </si>
   <si>
     <t xml:space="preserve">11.2459669113159</t>
@@ -1256,7 +1256,7 @@
     <t xml:space="preserve">11.0240068435669</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8205423355103</t>
+    <t xml:space="preserve">10.8205442428589</t>
   </si>
   <si>
     <t xml:space="preserve">10.8390407562256</t>
@@ -1265,16 +1265,16 @@
     <t xml:space="preserve">10.7280607223511</t>
   </si>
   <si>
-    <t xml:space="preserve">10.857536315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7095642089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6725692749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6540756225586</t>
+    <t xml:space="preserve">10.8575372695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7095623016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6725702285767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6540746688843</t>
   </si>
   <si>
     <t xml:space="preserve">10.7835502624512</t>
@@ -1283,25 +1283,25 @@
     <t xml:space="preserve">10.7650537490845</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8020477294922</t>
+    <t xml:space="preserve">10.8020458221436</t>
   </si>
   <si>
     <t xml:space="preserve">10.5615901947021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6170806884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3951196670532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1176700592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2841396331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2656440734863</t>
+    <t xml:space="preserve">10.6170797348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3951215744019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1176710128784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.284140586853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.265643119812</t>
   </si>
   <si>
     <t xml:space="preserve">10.302638053894</t>
@@ -1322,7 +1322,7 @@
     <t xml:space="preserve">9.98819446563721</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0991744995117</t>
+    <t xml:space="preserve">10.0991725921631</t>
   </si>
   <si>
     <t xml:space="preserve">9.93270301818848</t>
@@ -1331,52 +1331,52 @@
     <t xml:space="preserve">9.89571094512939</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96969795227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1731605529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0621795654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1546630859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71074390411377</t>
+    <t xml:space="preserve">9.96969699859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1731595993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0621814727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1546640396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71074295043945</t>
   </si>
   <si>
     <t xml:space="preserve">10.0251874923706</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91420841217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76623439788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72924041748047</t>
+    <t xml:space="preserve">9.91420745849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7662353515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72924137115479</t>
   </si>
   <si>
     <t xml:space="preserve">9.65525341033936</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67375087738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47028732299805</t>
+    <t xml:space="preserve">9.67374992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47028636932373</t>
   </si>
   <si>
     <t xml:space="preserve">9.54427337646484</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56277179718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45179080963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35930728912354</t>
+    <t xml:space="preserve">9.56277084350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45179176330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35930824279785</t>
   </si>
   <si>
     <t xml:space="preserve">9.52577781677246</t>
@@ -1388,34 +1388,34 @@
     <t xml:space="preserve">9.61826133728027</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69224739074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80322647094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2286510467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7847318649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85871696472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0066900253296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87721347808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7477388381958</t>
+    <t xml:space="preserve">9.69224834442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80322742462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2286520004272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78472995758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.858717918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0066909790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8772144317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74773693084717</t>
   </si>
   <si>
     <t xml:space="preserve">9.58126735687256</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3211345672607</t>
+    <t xml:space="preserve">10.3211336135864</t>
   </si>
   <si>
     <t xml:space="preserve">10.4321136474609</t>
@@ -1424,28 +1424,28 @@
     <t xml:space="preserve">10.3766241073608</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2471475601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2101526260376</t>
+    <t xml:space="preserve">10.2471466064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2101535797119</t>
   </si>
   <si>
     <t xml:space="preserve">9.84022045135498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63675785064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43329429626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41479873657227</t>
+    <t xml:space="preserve">9.63675689697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43329524993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41479682922363</t>
   </si>
   <si>
     <t xml:space="preserve">9.39630126953125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24832820892334</t>
+    <t xml:space="preserve">9.24832725524902</t>
   </si>
   <si>
     <t xml:space="preserve">9.06336116790771</t>
@@ -1457,7 +1457,7 @@
     <t xml:space="preserve">9.32231426239014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28532123565674</t>
+    <t xml:space="preserve">9.28532028198242</t>
   </si>
   <si>
     <t xml:space="preserve">9.26682567596436</t>
@@ -1466,16 +1466,16 @@
     <t xml:space="preserve">9.19283771514893</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22983074188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48878479003906</t>
+    <t xml:space="preserve">9.22982978820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48878383636475</t>
   </si>
   <si>
     <t xml:space="preserve">9.02636814117432</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97087860107422</t>
+    <t xml:space="preserve">8.9708776473999</t>
   </si>
   <si>
     <t xml:space="preserve">9.13734722137451</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">8.82290458679199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61944198608398</t>
+    <t xml:space="preserve">8.61944103240967</t>
   </si>
   <si>
     <t xml:space="preserve">8.55470275878906</t>
@@ -1505,13 +1505,13 @@
     <t xml:space="preserve">7.81483745574951</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95356321334839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49114561080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8610782623291</t>
+    <t xml:space="preserve">7.95356178283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49114608764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86107921600342</t>
   </si>
   <si>
     <t xml:space="preserve">7.50964260101318</t>
@@ -1520,22 +1520,22 @@
     <t xml:space="preserve">7.53738689422607</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58362913131714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76741504669189</t>
+    <t xml:space="preserve">7.58362865447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76741409301758</t>
   </si>
   <si>
     <t xml:space="preserve">8.98937511444092</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16509342193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12809944152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09110736846924</t>
+    <t xml:space="preserve">9.16509246826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12810039520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09110546112061</t>
   </si>
   <si>
     <t xml:space="preserve">9.08185768127441</t>
@@ -1544,22 +1544,22 @@
     <t xml:space="preserve">9.34081172943115</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04486560821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21133518218994</t>
+    <t xml:space="preserve">9.0448637008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21133422851562</t>
   </si>
   <si>
     <t xml:space="preserve">9.38705158233643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17434120178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29456901550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11885166168213</t>
+    <t xml:space="preserve">9.17434024810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29456996917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11885070800781</t>
   </si>
   <si>
     <t xml:space="preserve">8.78591060638428</t>
@@ -1568,10 +1568,10 @@
     <t xml:space="preserve">8.89689254760742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74891662597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80440807342529</t>
+    <t xml:space="preserve">8.74891757965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80440711975098</t>
   </si>
   <si>
     <t xml:space="preserve">8.87839412689209</t>
@@ -1589,40 +1589,40 @@
     <t xml:space="preserve">8.58244800567627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6934289932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46113872528076</t>
+    <t xml:space="preserve">8.69342708587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46114063262939</t>
   </si>
   <si>
     <t xml:space="preserve">9.64942073822021</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69649028778076</t>
+    <t xml:space="preserve">9.69649219512939</t>
   </si>
   <si>
     <t xml:space="preserve">9.74356174468994</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97891235351562</t>
+    <t xml:space="preserve">9.97891330718994</t>
   </si>
   <si>
     <t xml:space="preserve">9.93184280395508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79063034057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0730533599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3084058761597</t>
+    <t xml:space="preserve">9.7906322479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0730543136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3084049224854</t>
   </si>
   <si>
     <t xml:space="preserve">10.4496164321899</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1671943664551</t>
+    <t xml:space="preserve">10.1671953201294</t>
   </si>
   <si>
     <t xml:space="preserve">10.1201238632202</t>
@@ -1631,19 +1631,19 @@
     <t xml:space="preserve">10.0259828567505</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2142658233643</t>
+    <t xml:space="preserve">10.2142648696899</t>
   </si>
   <si>
     <t xml:space="preserve">10.3554754257202</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2613344192505</t>
+    <t xml:space="preserve">10.2613353729248</t>
   </si>
   <si>
     <t xml:space="preserve">9.88477230072021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5908279418945</t>
+    <t xml:space="preserve">10.5908269882202</t>
   </si>
   <si>
     <t xml:space="preserve">10.4966869354248</t>
@@ -1652,25 +1652,25 @@
     <t xml:space="preserve">10.5437574386597</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2027406692505</t>
+    <t xml:space="preserve">11.2027416229248</t>
   </si>
   <si>
     <t xml:space="preserve">11.1556720733643</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9673891067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0615301132202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7791080474854</t>
+    <t xml:space="preserve">10.9673910140991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0615310668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7791090011597</t>
   </si>
   <si>
     <t xml:space="preserve">10.8261795043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0144605636597</t>
+    <t xml:space="preserve">11.014461517334</t>
   </si>
   <si>
     <t xml:space="preserve">11.1086015701294</t>
@@ -1679,7 +1679,7 @@
     <t xml:space="preserve">10.9203205108643</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8732490539551</t>
+    <t xml:space="preserve">10.8732500076294</t>
   </si>
   <si>
     <t xml:space="preserve">10.7320384979248</t>
@@ -1688,7 +1688,7 @@
     <t xml:space="preserve">10.6378984451294</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5322341918945</t>
+    <t xml:space="preserve">11.5322351455688</t>
   </si>
   <si>
     <t xml:space="preserve">11.6263751983643</t>
@@ -1706,13 +1706,13 @@
     <t xml:space="preserve">11.6734447479248</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7205142974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0029373168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2853603363037</t>
+    <t xml:space="preserve">11.7205152511597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0029382705688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.285361289978</t>
   </si>
   <si>
     <t xml:space="preserve">12.5677824020386</t>
@@ -1721,13 +1721,13 @@
     <t xml:space="preserve">12.5207118988037</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8972730636597</t>
+    <t xml:space="preserve">12.897274017334</t>
   </si>
   <si>
     <t xml:space="preserve">12.7560634613037</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6619215011597</t>
+    <t xml:space="preserve">12.661922454834</t>
   </si>
   <si>
     <t xml:space="preserve">12.6148519515991</t>
@@ -1736,25 +1736,25 @@
     <t xml:space="preserve">12.8031339645386</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8502044677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9914140701294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1796951293945</t>
+    <t xml:space="preserve">12.8502035140991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9914150238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1796970367432</t>
   </si>
   <si>
     <t xml:space="preserve">13.4621181488037</t>
   </si>
   <si>
-    <t xml:space="preserve">13.838680267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7445411682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6503992080688</t>
+    <t xml:space="preserve">13.8386812210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7445421218872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6504011154175</t>
   </si>
   <si>
     <t xml:space="preserve">13.5091886520386</t>
@@ -1778,13 +1778,13 @@
     <t xml:space="preserve">14.168173789978</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1211032867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2623128890991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2152442932129</t>
+    <t xml:space="preserve">14.1211042404175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2623138427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2152452468872</t>
   </si>
   <si>
     <t xml:space="preserve">14.4505958557129</t>
@@ -1796,16 +1796,16 @@
     <t xml:space="preserve">14.3093852996826</t>
   </si>
   <si>
-    <t xml:space="preserve">14.403525352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3564538955688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5447359085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5918073654175</t>
+    <t xml:space="preserve">14.4035243988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3564548492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5447368621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5918064117432</t>
   </si>
   <si>
     <t xml:space="preserve">14.638876914978</t>
@@ -1814,10 +1814,10 @@
     <t xml:space="preserve">14.7800874710083</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8271589279175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.874228477478</t>
+    <t xml:space="preserve">14.8271579742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8742275238037</t>
   </si>
   <si>
     <t xml:space="preserve">14.7330169677734</t>
@@ -1826,123 +1826,126 @@
     <t xml:space="preserve">15.3449306488037</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7685623168945</t>
+    <t xml:space="preserve">15.7685670852661</t>
   </si>
   <si>
     <t xml:space="preserve">16.0039157867432</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0415744781494</t>
+    <t xml:space="preserve">16.0415725708008</t>
   </si>
   <si>
     <t xml:space="preserve">16.0792293548584</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1921997070312</t>
+    <t xml:space="preserve">16.1921977996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1168842315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2298545837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3804798126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3993091583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4181346893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5311050415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2675094604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9286050796509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8909482955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.815634727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9662599563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7214956283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5332126617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5143842697144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7026662826538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2696199417114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4767293930054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6838369369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6650104522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4202442169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1566514968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2319631576538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7779769897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9833707809448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.964301109314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6209812164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4874696731567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7926397323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8117141723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6019086837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5446872711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2585906982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6972723007202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8307867050171</t>
   </si>
   <si>
     <t xml:space="preserve">16.116886138916</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2298526763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3804798126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3993072509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4181365966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5311031341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2675132751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9286050796509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8909473419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.815634727478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9662609100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7214956283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5332145690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5143852233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7026672363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2696180343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4767303466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6838388442993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6650104522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4202432632446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1566514968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2319641113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7779788970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9833726882935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.964301109314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6209812164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4874696731567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7926397323608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8117141723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6019067764282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5446882247925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2585906982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6972723007202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8307867050171</t>
-  </si>
-  <si>
     <t xml:space="preserve">16.2503986358643</t>
   </si>
   <si>
@@ -1952,7 +1955,7 @@
     <t xml:space="preserve">16.0024471282959</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2694702148438</t>
+    <t xml:space="preserve">16.2694721221924</t>
   </si>
   <si>
     <t xml:space="preserve">16.212251663208</t>
@@ -1961,7 +1964,7 @@
     <t xml:space="preserve">16.460205078125</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4411296844482</t>
+    <t xml:space="preserve">16.4411315917969</t>
   </si>
   <si>
     <t xml:space="preserve">16.5364971160889</t>
@@ -1976,7 +1979,7 @@
     <t xml:space="preserve">16.9561080932617</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2231330871582</t>
+    <t xml:space="preserve">17.2231349945068</t>
   </si>
   <si>
     <t xml:space="preserve">17.3185005187988</t>
@@ -2009,7 +2012,7 @@
     <t xml:space="preserve">17.6427459716797</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7381114959717</t>
+    <t xml:space="preserve">17.7381134033203</t>
   </si>
   <si>
     <t xml:space="preserve">17.4901580810547</t>
@@ -2027,19 +2030,19 @@
     <t xml:space="preserve">17.3566474914551</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2422046661377</t>
+    <t xml:space="preserve">17.2422065734863</t>
   </si>
   <si>
     <t xml:space="preserve">17.1468391418457</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0133285522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4520130157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8334770202637</t>
+    <t xml:space="preserve">17.0133266448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4520111083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8334789276123</t>
   </si>
   <si>
     <t xml:space="preserve">17.6999645233154</t>
@@ -2066,7 +2069,7 @@
     <t xml:space="preserve">18.5964069366455</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5582599639893</t>
+    <t xml:space="preserve">18.5582580566406</t>
   </si>
   <si>
     <t xml:space="preserve">18.7108478546143</t>
@@ -2075,7 +2078,7 @@
     <t xml:space="preserve">18.8062114715576</t>
   </si>
   <si>
-    <t xml:space="preserve">18.520112991333</t>
+    <t xml:space="preserve">18.5201148986816</t>
   </si>
   <si>
     <t xml:space="preserve">19.55006980896</t>
@@ -2087,13 +2090,13 @@
     <t xml:space="preserve">19.8838520050049</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9792175292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4547023773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3593368530273</t>
+    <t xml:space="preserve">19.9792194366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.454704284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3593349456787</t>
   </si>
   <si>
     <t xml:space="preserve">19.1686058044434</t>
@@ -2120,7 +2123,7 @@
     <t xml:space="preserve">18.1195755004883</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6236705780029</t>
+    <t xml:space="preserve">17.6236686706543</t>
   </si>
   <si>
     <t xml:space="preserve">17.890697479248</t>
@@ -2150,7 +2153,7 @@
     <t xml:space="preserve">18.8825054168701</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9397239685059</t>
+    <t xml:space="preserve">18.9397258758545</t>
   </si>
   <si>
     <t xml:space="preserve">18.9015769958496</t>
@@ -2162,13 +2165,13 @@
     <t xml:space="preserve">20.2176322937012</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2653141021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7421474456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9328784942627</t>
+    <t xml:space="preserve">20.2653160095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7421455383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9328804016113</t>
   </si>
   <si>
     <t xml:space="preserve">21.2189769744873</t>
@@ -2186,7 +2189,7 @@
     <t xml:space="preserve">20.4560489654541</t>
   </si>
   <si>
-    <t xml:space="preserve">20.980562210083</t>
+    <t xml:space="preserve">20.9805603027344</t>
   </si>
   <si>
     <t xml:space="preserve">19.8361682891846</t>
@@ -2198,19 +2201,19 @@
     <t xml:space="preserve">20.1222667694092</t>
   </si>
   <si>
-    <t xml:space="preserve">19.311653137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.263973236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5977535247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.645435333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1699504852295</t>
+    <t xml:space="preserve">19.3116550445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2639713287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5977516174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6454372406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1699485778809</t>
   </si>
   <si>
     <t xml:space="preserve">19.9315338134766</t>
@@ -2219,7 +2222,7 @@
     <t xml:space="preserve">19.7408027648926</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8443603515625</t>
+    <t xml:space="preserve">18.8443584442139</t>
   </si>
   <si>
     <t xml:space="preserve">19.0160179138184</t>
@@ -2231,7 +2234,7 @@
     <t xml:space="preserve">18.0051364898682</t>
   </si>
   <si>
-    <t xml:space="preserve">18.138650894165</t>
+    <t xml:space="preserve">18.1386489868164</t>
   </si>
   <si>
     <t xml:space="preserve">18.0623550415039</t>
@@ -2240,25 +2243,25 @@
     <t xml:space="preserve">18.081428527832</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6045989990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2612800598145</t>
+    <t xml:space="preserve">17.6045970916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2612819671631</t>
   </si>
   <si>
     <t xml:space="preserve">17.0514736175537</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2885437011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0324039459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7272281646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4792785644531</t>
+    <t xml:space="preserve">16.2885456085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0324020385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7272300720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4792766571045</t>
   </si>
   <si>
     <t xml:space="preserve">16.8225936889648</t>
@@ -2276,7 +2279,7 @@
     <t xml:space="preserve">16.3076190948486</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5937194824219</t>
+    <t xml:space="preserve">16.5937175750732</t>
   </si>
   <si>
     <t xml:space="preserve">16.6318626403809</t>
@@ -2288,7 +2291,7 @@
     <t xml:space="preserve">14.8771257400513</t>
   </si>
   <si>
-    <t xml:space="preserve">14.495659828186</t>
+    <t xml:space="preserve">14.4956607818604</t>
   </si>
   <si>
     <t xml:space="preserve">15.3730306625366</t>
@@ -2321,10 +2324,10 @@
     <t xml:space="preserve">16.6890830993652</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5174236297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4983520507812</t>
+    <t xml:space="preserve">16.5174217224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4983501434326</t>
   </si>
   <si>
     <t xml:space="preserve">15.7354202270508</t>
@@ -2333,7 +2336,7 @@
     <t xml:space="preserve">15.8880052566528</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5065422058105</t>
+    <t xml:space="preserve">15.5065412521362</t>
   </si>
   <si>
     <t xml:space="preserve">14.9724912643433</t>
@@ -2348,7 +2351,7 @@
     <t xml:space="preserve">14.9152727127075</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7817583084106</t>
+    <t xml:space="preserve">14.781759262085</t>
   </si>
   <si>
     <t xml:space="preserve">14.8961982727051</t>
@@ -2357,10 +2360,10 @@
     <t xml:space="preserve">15.6400547027588</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0978107452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2395162582397</t>
+    <t xml:space="preserve">16.0978126525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2395153045654</t>
   </si>
   <si>
     <t xml:space="preserve">15.1060047149658</t>
@@ -2372,13 +2375,13 @@
     <t xml:space="preserve">16.1999359130859</t>
   </si>
   <si>
-    <t xml:space="preserve">16.354772567749</t>
+    <t xml:space="preserve">16.3547744750977</t>
   </si>
   <si>
     <t xml:space="preserve">16.0450973510742</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1418724060059</t>
+    <t xml:space="preserve">16.1418704986572</t>
   </si>
   <si>
     <t xml:space="preserve">16.2773532867432</t>
@@ -2408,7 +2411,7 @@
     <t xml:space="preserve">17.9418640136719</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4967021942139</t>
+    <t xml:space="preserve">17.4967041015625</t>
   </si>
   <si>
     <t xml:space="preserve">17.5934772491455</t>
@@ -2426,7 +2429,7 @@
     <t xml:space="preserve">15.9870338439941</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8321933746338</t>
+    <t xml:space="preserve">15.8321952819824</t>
   </si>
   <si>
     <t xml:space="preserve">15.9483222961426</t>
@@ -2453,19 +2456,19 @@
     <t xml:space="preserve">15.619291305542</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8902587890625</t>
+    <t xml:space="preserve">15.8902606964111</t>
   </si>
   <si>
     <t xml:space="preserve">15.7547760009766</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8128385543823</t>
+    <t xml:space="preserve">15.812840461731</t>
   </si>
   <si>
     <t xml:space="preserve">16.161226272583</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6580009460449</t>
+    <t xml:space="preserve">15.6580018997192</t>
   </si>
   <si>
     <t xml:space="preserve">15.870903968811</t>
@@ -2477,22 +2480,19 @@
     <t xml:space="preserve">16.4321918487549</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7354211807251</t>
-  </si>
-  <si>
     <t xml:space="preserve">15.7160663604736</t>
   </si>
   <si>
     <t xml:space="preserve">16.0644512176514</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5289649963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6838035583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5096092224121</t>
+    <t xml:space="preserve">16.5289669036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6838054656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5096111297607</t>
   </si>
   <si>
     <t xml:space="preserve">16.9160594940186</t>
@@ -2513,13 +2513,13 @@
     <t xml:space="preserve">17.3225116729736</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2838039398193</t>
+    <t xml:space="preserve">17.2838020324707</t>
   </si>
   <si>
     <t xml:space="preserve">17.0515441894531</t>
   </si>
   <si>
-    <t xml:space="preserve">16.83864402771</t>
+    <t xml:space="preserve">16.8386421203613</t>
   </si>
   <si>
     <t xml:space="preserve">17.2450904846191</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">17.1096076965332</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7225151062012</t>
+    <t xml:space="preserve">16.7225131988525</t>
   </si>
   <si>
     <t xml:space="preserve">17.1289653778076</t>
@@ -2564,7 +2564,7 @@
     <t xml:space="preserve">15.3096160888672</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5805826187134</t>
+    <t xml:space="preserve">15.5805835723877</t>
   </si>
   <si>
     <t xml:space="preserve">15.1547775268555</t>
@@ -2576,10 +2576,10 @@
     <t xml:space="preserve">16.0838069915771</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7741298675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6773567199707</t>
+    <t xml:space="preserve">15.7741289138794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.677357673645</t>
   </si>
   <si>
     <t xml:space="preserve">15.5612277984619</t>
@@ -2588,7 +2588,7 @@
     <t xml:space="preserve">16.1805801391602</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8579959869385</t>
+    <t xml:space="preserve">16.8579978942871</t>
   </si>
   <si>
     <t xml:space="preserve">17.3031558990479</t>
@@ -2603,16 +2603,16 @@
     <t xml:space="preserve">17.1676731109619</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5160579681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3612213134766</t>
+    <t xml:space="preserve">17.5160598754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3612194061279</t>
   </si>
   <si>
     <t xml:space="preserve">18.735408782959</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6579895019531</t>
+    <t xml:space="preserve">18.6579914093018</t>
   </si>
   <si>
     <t xml:space="preserve">18.4837970733643</t>
@@ -2627,13 +2627,13 @@
     <t xml:space="preserve">18.2515392303467</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8837985992432</t>
+    <t xml:space="preserve">17.8837966918945</t>
   </si>
   <si>
     <t xml:space="preserve">18.0386352539062</t>
   </si>
   <si>
-    <t xml:space="preserve">18.096700668335</t>
+    <t xml:space="preserve">18.0967025756836</t>
   </si>
   <si>
     <t xml:space="preserve">18.2128295898438</t>
@@ -2657,13 +2657,13 @@
     <t xml:space="preserve">17.8450908660889</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6902523040771</t>
+    <t xml:space="preserve">17.6902503967285</t>
   </si>
   <si>
     <t xml:space="preserve">17.6321868896484</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6515407562256</t>
+    <t xml:space="preserve">17.6515426635742</t>
   </si>
   <si>
     <t xml:space="preserve">17.4386405944824</t>
@@ -2672,16 +2672,16 @@
     <t xml:space="preserve">17.3999290466309</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2644481658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7096061706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4773483276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8257350921631</t>
+    <t xml:space="preserve">17.2644462585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7096042633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4773502349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8257369995117</t>
   </si>
   <si>
     <t xml:space="preserve">18.5805702209473</t>
@@ -2690,13 +2690,13 @@
     <t xml:space="preserve">18.928955078125</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8128280639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5483112335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9354038238525</t>
+    <t xml:space="preserve">18.8128299713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5483093261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9354057312012</t>
   </si>
   <si>
     <t xml:space="preserve">19.7902450561523</t>
@@ -2705,13 +2705,13 @@
     <t xml:space="preserve">20.0321788787842</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7418556213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5966949462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9837913513184</t>
+    <t xml:space="preserve">19.7418575286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5966968536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9837894439697</t>
   </si>
   <si>
     <t xml:space="preserve">19.8386306762695</t>
@@ -2723,10 +2723,10 @@
     <t xml:space="preserve">20.370885848999</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8870182037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6450824737549</t>
+    <t xml:space="preserve">19.8870162963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6450805664062</t>
   </si>
   <si>
     <t xml:space="preserve">20.1289520263672</t>
@@ -2738,10 +2738,10 @@
     <t xml:space="preserve">20.4192733764648</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4676609039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.241849899292</t>
+    <t xml:space="preserve">20.467658996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2418518066406</t>
   </si>
   <si>
     <t xml:space="preserve">21.1934623718262</t>
@@ -2750,22 +2750,22 @@
     <t xml:space="preserve">21.435396194458</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5805568695068</t>
+    <t xml:space="preserve">21.5805587768555</t>
   </si>
   <si>
     <t xml:space="preserve">21.6773319244385</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6289463043213</t>
+    <t xml:space="preserve">21.6289443969727</t>
   </si>
   <si>
     <t xml:space="preserve">22.0644264221191</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2579765319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6450691223145</t>
+    <t xml:space="preserve">22.2579746246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6450710296631</t>
   </si>
   <si>
     <t xml:space="preserve">23.0321655273438</t>
@@ -2777,13 +2777,13 @@
     <t xml:space="preserve">23.3224868774414</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7902317047119</t>
+    <t xml:space="preserve">22.7902297973633</t>
   </si>
   <si>
     <t xml:space="preserve">22.7418441772461</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9676551818848</t>
+    <t xml:space="preserve">21.9676532745361</t>
   </si>
   <si>
     <t xml:space="preserve">22.6934585571289</t>
@@ -2807,7 +2807,7 @@
     <t xml:space="preserve">22.5482978820801</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9837779998779</t>
+    <t xml:space="preserve">22.9837799072266</t>
   </si>
   <si>
     <t xml:space="preserve">23.9031295776367</t>
@@ -2816,7 +2816,7 @@
     <t xml:space="preserve">24.1934509277344</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0966777801514</t>
+    <t xml:space="preserve">24.0966758728027</t>
   </si>
   <si>
     <t xml:space="preserve">25.0160293579102</t>
@@ -2828,10 +2828,10 @@
     <t xml:space="preserve">25.4031238555908</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8386077880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9353809356689</t>
+    <t xml:space="preserve">25.8386058807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9353790283203</t>
   </si>
   <si>
     <t xml:space="preserve">25.3547382354736</t>
@@ -2846,7 +2846,7 @@
     <t xml:space="preserve">25.2579650878906</t>
   </si>
   <si>
-    <t xml:space="preserve">25.451509475708</t>
+    <t xml:space="preserve">25.4515113830566</t>
   </si>
   <si>
     <t xml:space="preserve">25.2095756530762</t>
@@ -2858,19 +2858,19 @@
     <t xml:space="preserve">25.6450595855713</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1773147583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5160236358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9515037536621</t>
+    <t xml:space="preserve">26.1773128509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5160217285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9515056610107</t>
   </si>
   <si>
     <t xml:space="preserve">25.6934452056885</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5966739654541</t>
+    <t xml:space="preserve">25.5966720581055</t>
   </si>
   <si>
     <t xml:space="preserve">25.3063507080078</t>
@@ -2888,7 +2888,7 @@
     <t xml:space="preserve">25.616569519043</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1267681121826</t>
+    <t xml:space="preserve">25.1267700195312</t>
   </si>
   <si>
     <t xml:space="preserve">25.9594306945801</t>
@@ -2900,16 +2900,16 @@
     <t xml:space="preserve">25.2737083435059</t>
   </si>
   <si>
-    <t xml:space="preserve">25.02880859375</t>
+    <t xml:space="preserve">25.0288066864014</t>
   </si>
   <si>
     <t xml:space="preserve">25.2247295379639</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7349300384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.441047668457</t>
+    <t xml:space="preserve">24.7349281311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4410495758057</t>
   </si>
   <si>
     <t xml:space="preserve">24.8818683624268</t>
@@ -2924,10 +2924,10 @@
     <t xml:space="preserve">24.4900283813477</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7839069366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8328895568848</t>
+    <t xml:space="preserve">24.7839088439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8328876495361</t>
   </si>
   <si>
     <t xml:space="preserve">24.979829788208</t>
@@ -2936,19 +2936,19 @@
     <t xml:space="preserve">25.4696292877197</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9104518890381</t>
+    <t xml:space="preserve">25.9104499816895</t>
   </si>
   <si>
     <t xml:space="preserve">25.8614692687988</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7635078430176</t>
+    <t xml:space="preserve">25.7635097503662</t>
   </si>
   <si>
     <t xml:space="preserve">25.7145290374756</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2533111572266</t>
+    <t xml:space="preserve">26.2533092498779</t>
   </si>
   <si>
     <t xml:space="preserve">26.6941299438477</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">26.7920913696289</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5961685180664</t>
+    <t xml:space="preserve">26.596170425415</t>
   </si>
   <si>
     <t xml:space="preserve">26.4492301940918</t>
@@ -2990,7 +2990,7 @@
     <t xml:space="preserve">25.3716678619385</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1471672058105</t>
+    <t xml:space="preserve">24.1471691131592</t>
   </si>
   <si>
     <t xml:space="preserve">26.3512687683105</t>
@@ -3005,13 +3005,13 @@
     <t xml:space="preserve">26.9880104064941</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9390296936035</t>
+    <t xml:space="preserve">26.9390316009521</t>
   </si>
   <si>
     <t xml:space="preserve">26.0573902130127</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1063690185547</t>
+    <t xml:space="preserve">26.1063709259033</t>
   </si>
   <si>
     <t xml:space="preserve">26.6451511383057</t>
@@ -3026,40 +3026,40 @@
     <t xml:space="preserve">27.134952545166</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1553516387939</t>
+    <t xml:space="preserve">26.1553497314453</t>
   </si>
   <si>
     <t xml:space="preserve">27.3798522949219</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3308715820312</t>
+    <t xml:space="preserve">27.3308696746826</t>
   </si>
   <si>
     <t xml:space="preserve">27.7227115631104</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6737327575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0165939331055</t>
+    <t xml:space="preserve">27.6737308502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0165920257568</t>
   </si>
   <si>
     <t xml:space="preserve">27.5757713317871</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4778118133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5267906188965</t>
+    <t xml:space="preserve">27.4778099060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5267925262451</t>
   </si>
   <si>
     <t xml:space="preserve">25.8124904632568</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3022899627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2818908691406</t>
+    <t xml:space="preserve">26.3022918701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2818927764893</t>
   </si>
   <si>
     <t xml:space="preserve">27.4288330078125</t>
@@ -3068,13 +3068,13 @@
     <t xml:space="preserve">27.23291015625</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6247520446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8410720825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4982109069824</t>
+    <t xml:space="preserve">27.6247539520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8410701751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4982089996338</t>
   </si>
   <si>
     <t xml:space="preserve">25.567590713501</t>
@@ -3101,7 +3101,7 @@
     <t xml:space="preserve">28.5553722381592</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0451717376709</t>
+    <t xml:space="preserve">29.0451736450195</t>
   </si>
   <si>
     <t xml:space="preserve">29.1431331634521</t>
@@ -3119,10 +3119,10 @@
     <t xml:space="preserve">29.6819133758545</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7798728942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1921138763428</t>
+    <t xml:space="preserve">29.7798748016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1921119689941</t>
   </si>
   <si>
     <t xml:space="preserve">29.5349731445312</t>
@@ -3134,10 +3134,10 @@
     <t xml:space="preserve">30.2206954956055</t>
   </si>
   <si>
-    <t xml:space="preserve">30.514575958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8574371337891</t>
+    <t xml:space="preserve">30.5145740509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8574352264404</t>
   </si>
   <si>
     <t xml:space="preserve">32.1798973083496</t>
@@ -3152,10 +3152,10 @@
     <t xml:space="preserve">32.5227584838867</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0901222229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8248176574707</t>
+    <t xml:space="preserve">34.0901184082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.824821472168</t>
   </si>
   <si>
     <t xml:space="preserve">34.2860374450684</t>
@@ -3164,22 +3164,22 @@
     <t xml:space="preserve">34.6288986206055</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1390953063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7758369445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7472610473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8941993713379</t>
+    <t xml:space="preserve">34.1390991210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7758407592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.747257232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8941955566406</t>
   </si>
   <si>
     <t xml:space="preserve">34.335018157959</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9431800842285</t>
+    <t xml:space="preserve">33.9431838989258</t>
   </si>
   <si>
     <t xml:space="preserve">35.0207405090332</t>
@@ -3188,7 +3188,7 @@
     <t xml:space="preserve">35.4125823974609</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9635772705078</t>
+    <t xml:space="preserve">32.9635810852051</t>
   </si>
   <si>
     <t xml:space="preserve">32.9145965576172</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">33.0125579833984</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4451961517334</t>
+    <t xml:space="preserve">31.4451942443848</t>
   </si>
   <si>
     <t xml:space="preserve">31.5641193389893</t>
@@ -3867,9 +3867,6 @@
   </si>
   <si>
     <t xml:space="preserve">48.0499992370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8499984741211</t>
   </si>
 </sst>
 </file>
@@ -40106,7 +40103,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1381" t="s">
-        <v>609</v>
+        <v>643</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -40132,7 +40129,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1382" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -40158,7 +40155,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1383" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -40184,7 +40181,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1384" t="s">
-        <v>609</v>
+        <v>643</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -40236,7 +40233,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1386" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -40262,7 +40259,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1387" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -40288,7 +40285,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G1388" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -40340,7 +40337,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1390" t="s">
-        <v>609</v>
+        <v>643</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -40366,7 +40363,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1391" t="s">
-        <v>609</v>
+        <v>643</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -40392,7 +40389,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1392" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -40418,7 +40415,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1393" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -40444,7 +40441,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1394" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -40470,7 +40467,7 @@
         <v>17</v>
       </c>
       <c r="G1395" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -40496,7 +40493,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1396" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -40522,7 +40519,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1397" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -40548,7 +40545,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1398" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -40574,7 +40571,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1399" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -40600,7 +40597,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1400" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -40626,7 +40623,7 @@
         <v>18</v>
       </c>
       <c r="G1401" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -40652,7 +40649,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1402" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -40678,7 +40675,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1403" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -40704,7 +40701,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1404" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -40730,7 +40727,7 @@
         <v>18</v>
       </c>
       <c r="G1405" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -40756,7 +40753,7 @@
         <v>18</v>
       </c>
       <c r="G1406" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -40782,7 +40779,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1407" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -40808,7 +40805,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G1408" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -40834,7 +40831,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1409" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -40860,7 +40857,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1410" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -40886,7 +40883,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1411" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -40912,7 +40909,7 @@
         <v>18</v>
       </c>
       <c r="G1412" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -40938,7 +40935,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G1413" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -40964,7 +40961,7 @@
         <v>18</v>
       </c>
       <c r="G1414" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -40990,7 +40987,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G1415" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -41016,7 +41013,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1416" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -41042,7 +41039,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1417" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -41068,7 +41065,7 @@
         <v>18.5</v>
       </c>
       <c r="G1418" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -41094,7 +41091,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1419" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -41120,7 +41117,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1420" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -41146,7 +41143,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1421" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -41172,7 +41169,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1422" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -41198,7 +41195,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1423" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -41224,7 +41221,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1424" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -41250,7 +41247,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1425" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -41276,7 +41273,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1426" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -41302,7 +41299,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1427" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -41328,7 +41325,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G1428" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -41354,7 +41351,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G1429" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -41380,7 +41377,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1430" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -41406,7 +41403,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1431" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -41432,7 +41429,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1432" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -41458,7 +41455,7 @@
         <v>18.5</v>
       </c>
       <c r="G1433" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -41484,7 +41481,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1434" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -41510,7 +41507,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1435" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -41536,7 +41533,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1436" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -41562,7 +41559,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G1437" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -41588,7 +41585,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1438" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -41614,7 +41611,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1439" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -41640,7 +41637,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1440" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -41666,7 +41663,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1441" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -41692,7 +41689,7 @@
         <v>19.5</v>
       </c>
       <c r="G1442" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -41718,7 +41715,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1443" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -41744,7 +41741,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G1444" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -41770,7 +41767,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1445" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -41796,7 +41793,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1446" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -41822,7 +41819,7 @@
         <v>20.5</v>
       </c>
       <c r="G1447" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -41848,7 +41845,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1448" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -41874,7 +41871,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1449" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -41900,7 +41897,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1450" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -41926,7 +41923,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1451" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -41952,7 +41949,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1452" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -41978,7 +41975,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1453" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -42004,7 +42001,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1454" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -42030,7 +42027,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1455" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -42056,7 +42053,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1456" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -42082,7 +42079,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1457" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -42108,7 +42105,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1458" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -42134,7 +42131,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1459" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -42160,7 +42157,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G1460" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -42186,7 +42183,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1461" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -42212,7 +42209,7 @@
         <v>19</v>
       </c>
       <c r="G1462" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -42238,7 +42235,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1463" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -42264,7 +42261,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G1464" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -42290,7 +42287,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1465" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -42316,7 +42313,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G1466" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -42342,7 +42339,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G1467" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -42368,7 +42365,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1468" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -42394,7 +42391,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1469" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -42420,7 +42417,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1470" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -42446,7 +42443,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1471" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -42472,7 +42469,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1472" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -42498,7 +42495,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G1473" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -42524,7 +42521,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1474" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -42550,7 +42547,7 @@
         <v>20</v>
       </c>
       <c r="G1475" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -42576,7 +42573,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1476" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -42602,7 +42599,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1477" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -42628,7 +42625,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1478" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -42654,7 +42651,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G1479" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -42680,7 +42677,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1480" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -42706,7 +42703,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1481" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -42732,7 +42729,7 @@
         <v>20</v>
       </c>
       <c r="G1482" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -42758,7 +42755,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1483" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -42784,7 +42781,7 @@
         <v>20</v>
       </c>
       <c r="G1484" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -42810,7 +42807,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1485" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -42836,7 +42833,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1486" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -42862,7 +42859,7 @@
         <v>20</v>
       </c>
       <c r="G1487" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -42888,7 +42885,7 @@
         <v>20</v>
       </c>
       <c r="G1488" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -42914,7 +42911,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G1489" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -42940,7 +42937,7 @@
         <v>20</v>
       </c>
       <c r="G1490" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -42966,7 +42963,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1491" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -42992,7 +42989,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1492" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -43018,7 +43015,7 @@
         <v>21</v>
       </c>
       <c r="G1493" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -43044,7 +43041,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1494" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -43070,7 +43067,7 @@
         <v>21.25</v>
       </c>
       <c r="G1495" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -43096,7 +43093,7 @@
         <v>21.75</v>
       </c>
       <c r="G1496" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -43122,7 +43119,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G1497" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -43148,7 +43145,7 @@
         <v>22.25</v>
       </c>
       <c r="G1498" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -43174,7 +43171,7 @@
         <v>22.5</v>
       </c>
       <c r="G1499" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -43200,7 +43197,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1500" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -43226,7 +43223,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1501" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -43252,7 +43249,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G1502" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -43278,7 +43275,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1503" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -43304,7 +43301,7 @@
         <v>22</v>
       </c>
       <c r="G1504" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -43330,7 +43327,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1505" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -43356,7 +43353,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1506" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -43382,7 +43379,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1507" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -43408,7 +43405,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1508" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -43434,7 +43431,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1509" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -43460,7 +43457,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1510" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -43486,7 +43483,7 @@
         <v>20.25</v>
       </c>
       <c r="G1511" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -43512,7 +43509,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1512" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -43538,7 +43535,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1513" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -43564,7 +43561,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1514" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -43590,7 +43587,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1515" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -43616,7 +43613,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G1516" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -43642,7 +43639,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1517" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -43668,7 +43665,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1518" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -43694,7 +43691,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1519" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -43720,7 +43717,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1520" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -43746,7 +43743,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1521" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -43772,7 +43769,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1522" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -43798,7 +43795,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1523" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -43824,7 +43821,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1524" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -43850,7 +43847,7 @@
         <v>21</v>
       </c>
       <c r="G1525" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -43876,7 +43873,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1526" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -43902,7 +43899,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1527" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -43928,7 +43925,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1528" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -43954,7 +43951,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1529" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -43980,7 +43977,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1530" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -44006,7 +44003,7 @@
         <v>20.5</v>
       </c>
       <c r="G1531" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -44032,7 +44029,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G1532" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -44058,7 +44055,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1533" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -44084,7 +44081,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1534" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -44110,7 +44107,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1535" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -44136,7 +44133,7 @@
         <v>20</v>
       </c>
       <c r="G1536" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -44162,7 +44159,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1537" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -44188,7 +44185,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1538" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -44214,7 +44211,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G1539" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -44240,7 +44237,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1540" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -44266,7 +44263,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1541" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -44292,7 +44289,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G1542" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -44318,7 +44315,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1543" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -44344,7 +44341,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1544" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -44370,7 +44367,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1545" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -44396,7 +44393,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G1546" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -44422,7 +44419,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G1547" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -44448,7 +44445,7 @@
         <v>19</v>
       </c>
       <c r="G1548" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -44474,7 +44471,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G1549" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -44500,7 +44497,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G1550" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -44526,7 +44523,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1551" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -44552,7 +44549,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G1552" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -44578,7 +44575,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G1553" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -44604,7 +44601,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1554" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -44630,7 +44627,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1555" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -44656,7 +44653,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1556" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -44682,7 +44679,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1557" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -44708,7 +44705,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G1558" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -44734,7 +44731,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1559" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -44760,7 +44757,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1560" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -44786,7 +44783,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G1561" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -44812,7 +44809,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1562" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -44838,7 +44835,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1563" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -44864,7 +44861,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G1564" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -44890,7 +44887,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1565" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -44916,7 +44913,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1566" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -44942,7 +44939,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1567" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -44968,7 +44965,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1568" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -44994,7 +44991,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1569" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -45020,7 +45017,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G1570" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -45046,7 +45043,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G1571" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -45072,7 +45069,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1572" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -45098,7 +45095,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1573" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -45124,7 +45121,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G1574" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -45150,7 +45147,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G1575" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -45176,7 +45173,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1576" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -45202,7 +45199,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1577" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -45228,7 +45225,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1578" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -45254,7 +45251,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1579" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -45280,7 +45277,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G1580" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -45306,7 +45303,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1581" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -45332,7 +45329,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1582" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -45358,7 +45355,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1583" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -45384,7 +45381,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1584" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -45410,7 +45407,7 @@
         <v>17</v>
       </c>
       <c r="G1585" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -45436,7 +45433,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G1586" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -45462,7 +45459,7 @@
         <v>17.5</v>
       </c>
       <c r="G1587" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -45488,7 +45485,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1588" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -45514,7 +45511,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1589" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -45540,7 +45537,7 @@
         <v>16.5</v>
       </c>
       <c r="G1590" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -45566,7 +45563,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1591" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -45644,7 +45641,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G1594" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -45670,7 +45667,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G1595" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -45722,7 +45719,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1597" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -45774,7 +45771,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G1599" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -45800,7 +45797,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G1600" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -45826,7 +45823,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1601" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -45852,7 +45849,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1602" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -45878,7 +45875,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G1603" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -45904,7 +45901,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1604" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -45930,7 +45927,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1605" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -45956,7 +45953,7 @@
         <v>15.5</v>
       </c>
       <c r="G1606" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -45982,7 +45979,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G1607" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -46008,7 +46005,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1608" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -46060,7 +46057,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G1610" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -46112,7 +46109,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1612" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -46190,7 +46187,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G1615" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -46242,7 +46239,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1617" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -46268,7 +46265,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G1618" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -46294,7 +46291,7 @@
         <v>16.5</v>
       </c>
       <c r="G1619" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -46320,7 +46317,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1620" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -46346,7 +46343,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1621" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -46372,7 +46369,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1622" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -46398,7 +46395,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G1623" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -46424,7 +46421,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1624" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -46450,7 +46447,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1625" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -46476,7 +46473,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1626" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -46502,7 +46499,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1627" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -46528,7 +46525,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1628" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -46554,7 +46551,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G1629" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -46580,7 +46577,7 @@
         <v>18</v>
       </c>
       <c r="G1630" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -46606,7 +46603,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1631" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -46632,7 +46629,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1632" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -46658,7 +46655,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1633" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -46684,7 +46681,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1634" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -46710,7 +46707,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1635" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -46736,7 +46733,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1636" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -46762,7 +46759,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1637" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -46788,7 +46785,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1638" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -46814,7 +46811,7 @@
         <v>17</v>
       </c>
       <c r="G1639" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -46840,7 +46837,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1640" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -46866,7 +46863,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1641" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -46892,7 +46889,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1642" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -46918,7 +46915,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1643" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -46944,7 +46941,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1644" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -46970,7 +46967,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1645" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -46996,7 +46993,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1646" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -47022,7 +47019,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G1647" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -47048,7 +47045,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1648" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -47074,7 +47071,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G1649" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -47100,7 +47097,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1650" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -47126,7 +47123,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G1651" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -47152,7 +47149,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G1652" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -47178,7 +47175,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1653" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -47204,7 +47201,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1654" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -47230,7 +47227,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1655" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -47256,7 +47253,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G1656" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -47282,7 +47279,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1657" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -47308,7 +47305,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1658" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -47334,7 +47331,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1659" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -47360,7 +47357,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G1660" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -47386,7 +47383,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1661" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -47412,7 +47409,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G1662" t="s">
-        <v>821</v>
+        <v>772</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -47490,7 +47487,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1665" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -47516,7 +47513,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1666" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -47542,7 +47539,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G1667" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -47568,7 +47565,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1668" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -47594,7 +47591,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1669" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -48010,7 +48007,7 @@
         <v>18</v>
       </c>
       <c r="G1685" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -48062,7 +48059,7 @@
         <v>18</v>
       </c>
       <c r="G1687" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -48114,7 +48111,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1689" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -48244,7 +48241,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1694" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -48270,7 +48267,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1695" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -48322,7 +48319,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1697" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -48426,7 +48423,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1701" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -48504,7 +48501,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1704" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -48530,7 +48527,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1705" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -48582,7 +48579,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1707" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -48634,7 +48631,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G1709" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -48686,7 +48683,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1711" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -49024,7 +49021,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1724" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -49076,7 +49073,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1726" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -49128,7 +49125,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1728" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -49310,7 +49307,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1735" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -49440,7 +49437,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1740" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -49492,7 +49489,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1742" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -49518,7 +49515,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1743" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -50012,7 +50009,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1762" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -50090,7 +50087,7 @@
         <v>18</v>
       </c>
       <c r="G1765" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -50142,7 +50139,7 @@
         <v>18</v>
       </c>
       <c r="G1767" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -50376,7 +50373,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1776" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -50454,7 +50451,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1779" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -50584,7 +50581,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1784" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -50662,7 +50659,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1787" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -70326,13 +70323,13 @@
     </row>
     <row r="2544">
       <c r="A2544" s="1" t="n">
-        <v>46028.6829861111</v>
+        <v>46028.3333333333</v>
       </c>
       <c r="B2544" t="n">
-        <v>24038</v>
+        <v>36757</v>
       </c>
       <c r="C2544" t="n">
-        <v>48.6500015258789</v>
+        <v>49.1500015258789</v>
       </c>
       <c r="D2544" t="n">
         <v>48</v>
@@ -70341,12 +70338,38 @@
         <v>48.0499992370605</v>
       </c>
       <c r="F2544" t="n">
-        <v>48.8499984741211</v>
+        <v>49</v>
       </c>
       <c r="G2544" t="s">
-        <v>1285</v>
+        <v>1275</v>
       </c>
       <c r="H2544" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2545">
+      <c r="A2545" s="1" t="n">
+        <v>46029.6909722222</v>
+      </c>
+      <c r="B2545" t="n">
+        <v>49005</v>
+      </c>
+      <c r="C2545" t="n">
+        <v>49.4000015258789</v>
+      </c>
+      <c r="D2545" t="n">
+        <v>48.2999992370605</v>
+      </c>
+      <c r="E2545" t="n">
+        <v>49.1500015258789</v>
+      </c>
+      <c r="F2545" t="n">
+        <v>49.0999984741211</v>
+      </c>
+      <c r="G2545" t="s">
+        <v>1274</v>
+      </c>
+      <c r="H2545" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SOL.MI.xlsx
+++ b/data/SOL.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14939165115356</t>
+    <t xml:space="preserve">7.14939117431641</t>
   </si>
   <si>
     <t xml:space="preserve">SOL.MI</t>
@@ -50,28 +50,28 @@
     <t xml:space="preserve">7.1886248588562</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16247081756592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0622034072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90962600708008</t>
+    <t xml:space="preserve">7.16246938705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06220436096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9096245765686</t>
   </si>
   <si>
     <t xml:space="preserve">6.90526580810547</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94885969161987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71781206130981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62626552581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71345233917236</t>
+    <t xml:space="preserve">6.94885921478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71781253814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62626457214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71345329284668</t>
   </si>
   <si>
     <t xml:space="preserve">6.29931163787842</t>
@@ -83,13 +83,13 @@
     <t xml:space="preserve">6.43009233474731</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41265487670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4475302696228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20776414871216</t>
+    <t xml:space="preserve">6.41265535354614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44752979278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20776462554932</t>
   </si>
   <si>
     <t xml:space="preserve">6.1728892326355</t>
@@ -98,79 +98,79 @@
     <t xml:space="preserve">6.46060800552368</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54779624938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38213920593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51292133331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50420188903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65242147445679</t>
+    <t xml:space="preserve">6.54779672622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38214015960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51292037963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50420236587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65242099761963</t>
   </si>
   <si>
     <t xml:space="preserve">6.80064058303833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72217178344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79192113876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00989055633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84423398971558</t>
+    <t xml:space="preserve">6.72217130661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79192209243774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00989103317261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84423446655273</t>
   </si>
   <si>
     <t xml:space="preserve">7.07964134216309</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88346910476685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96629667282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08836030960083</t>
+    <t xml:space="preserve">6.88346862792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9662971496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08835983276367</t>
   </si>
   <si>
     <t xml:space="preserve">6.73524951934814</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83115673065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67857837677002</t>
+    <t xml:space="preserve">6.83115577697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67857694625854</t>
   </si>
   <si>
     <t xml:space="preserve">6.57395267486572</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63062477111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68729639053345</t>
+    <t xml:space="preserve">6.63062524795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68729686737061</t>
   </si>
   <si>
     <t xml:space="preserve">6.783203125</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77884292602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81371879577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80935907363892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79628086090088</t>
+    <t xml:space="preserve">6.77884387969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81371831893921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80935955047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7962818145752</t>
   </si>
   <si>
     <t xml:space="preserve">6.69601535797119</t>
@@ -179,106 +179,106 @@
     <t xml:space="preserve">6.81807804107666</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8747501373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91398525238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67421817779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5521559715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46496820449829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43881177902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73088979721069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87910938262939</t>
+    <t xml:space="preserve">6.87475061416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91398429870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67421865463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55215549468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46496772766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43881225585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73089027404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87910890579224</t>
   </si>
   <si>
     <t xml:space="preserve">6.85295343399048</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84859371185303</t>
+    <t xml:space="preserve">6.84859418869019</t>
   </si>
   <si>
     <t xml:space="preserve">6.85731220245361</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74832773208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51728057861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37342071533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56523466110229</t>
+    <t xml:space="preserve">6.74832725524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51728105545044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37342023849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56523370742798</t>
   </si>
   <si>
     <t xml:space="preserve">6.66985893249512</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77012491226196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86167192459106</t>
+    <t xml:space="preserve">6.77012538909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86167240142822</t>
   </si>
   <si>
     <t xml:space="preserve">6.97501611709595</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9416298866272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95048332214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88407802581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90178632736206</t>
+    <t xml:space="preserve">6.94162940979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95048427581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88407754898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90178680419922</t>
   </si>
   <si>
     <t xml:space="preserve">7.34006500244141</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22496128082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41975164413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43746089935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36662769317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26037836074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46845006942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40204429626465</t>
+    <t xml:space="preserve">7.22496175765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41975116729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43745994567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36662673950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26037788391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46845054626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40204381942749</t>
   </si>
   <si>
     <t xml:space="preserve">7.44631433486938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38433504104614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04345226287842</t>
+    <t xml:space="preserve">7.38433647155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04345178604126</t>
   </si>
   <si>
     <t xml:space="preserve">6.9726185798645</t>
@@ -287,118 +287,118 @@
     <t xml:space="preserve">7.1098575592041</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87079668045044</t>
+    <t xml:space="preserve">6.8707971572876</t>
   </si>
   <si>
     <t xml:space="preserve">7.20725345611572</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37105321884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57027149200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6942286491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70308446884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71193790435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6588134765625</t>
+    <t xml:space="preserve">7.37105417251587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57027244567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69422960281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70308399200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71193742752075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65881252288818</t>
   </si>
   <si>
     <t xml:space="preserve">8.04396724700928</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61454248428345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29579401016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99475479125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10100412368774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55256462097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31350183486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50829219818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42418003082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3754825592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52600240707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54370880126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41532468795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21610641479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99032735824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79996347427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75569295883179</t>
+    <t xml:space="preserve">7.61454296112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29579496383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99475383758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1010046005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55256366729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3135027885437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50829267501831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42417860031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37548112869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52600193023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54370975494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41532611846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21610736846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99032688140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79996395111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75569438934326</t>
   </si>
   <si>
     <t xml:space="preserve">7.00803565979004</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26923322677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34449195861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46402311325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51714658737183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39318895339966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45516872406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1718373298645</t>
+    <t xml:space="preserve">7.26923274993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34449148178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46402359008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51714754104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39318990707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4551682472229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17183685302734</t>
   </si>
   <si>
     <t xml:space="preserve">7.33563756942749</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33121109008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39761686325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30464935302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27808666229248</t>
+    <t xml:space="preserve">7.33121156692505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39761590957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30464839935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27808570861816</t>
   </si>
   <si>
     <t xml:space="preserve">7.25152349472046</t>
@@ -407,13 +407,13 @@
     <t xml:space="preserve">7.16298294067383</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03017139434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87965059280396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91064071655273</t>
+    <t xml:space="preserve">7.03017044067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8796501159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91063976287842</t>
   </si>
   <si>
     <t xml:space="preserve">6.95491123199463</t>
@@ -422,7 +422,7 @@
     <t xml:space="preserve">6.88850498199463</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95933818817139</t>
+    <t xml:space="preserve">6.95933866500854</t>
   </si>
   <si>
     <t xml:space="preserve">6.85751581192017</t>
@@ -437,13 +437,13 @@
     <t xml:space="preserve">6.82652616500854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68486070632935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81767177581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90621328353882</t>
+    <t xml:space="preserve">6.68486022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81767129898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90621376037598</t>
   </si>
   <si>
     <t xml:space="preserve">7.01689052581787</t>
@@ -452,91 +452,91 @@
     <t xml:space="preserve">6.8973593711853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83538055419922</t>
+    <t xml:space="preserve">6.83538007736206</t>
   </si>
   <si>
     <t xml:space="preserve">6.86194276809692</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92392206192017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97704601287842</t>
+    <t xml:space="preserve">6.92392158508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97704648971558</t>
   </si>
   <si>
     <t xml:space="preserve">7.00360822677612</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91506719589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91949415206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9372034072876</t>
+    <t xml:space="preserve">6.91506767272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91949510574341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93720245361328</t>
   </si>
   <si>
     <t xml:space="preserve">7.07001447677612</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98590040206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75126600265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77782773971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64944410324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38381958007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37053966522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36168527603149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37939262390137</t>
+    <t xml:space="preserve">6.98590087890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75126647949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77782869338989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64944362640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38382005691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37053918838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36168432235718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37939310073853</t>
   </si>
   <si>
     <t xml:space="preserve">6.40595531463623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48121643066406</t>
+    <t xml:space="preserve">6.48121500015259</t>
   </si>
   <si>
     <t xml:space="preserve">6.47678804397583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54319429397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46350765228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24215507507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25986242294312</t>
+    <t xml:space="preserve">6.54319334030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46350812911987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24215412139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25986289978027</t>
   </si>
   <si>
     <t xml:space="preserve">6.22444629669189</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64501667022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64058971405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03902435302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79111003875732</t>
+    <t xml:space="preserve">6.64501619338989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64058923721313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0390248298645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79110908508301</t>
   </si>
   <si>
     <t xml:space="preserve">6.70256853103638</t>
@@ -548,79 +548,79 @@
     <t xml:space="preserve">6.65829801559448</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58303785324097</t>
+    <t xml:space="preserve">6.58303737640381</t>
   </si>
   <si>
     <t xml:space="preserve">7.05673360824585</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11428546905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34891843795776</t>
+    <t xml:space="preserve">7.11428451538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34891986846924</t>
   </si>
   <si>
     <t xml:space="preserve">7.18511819839478</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12756633758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19397163391113</t>
+    <t xml:space="preserve">7.12756681442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19397258758545</t>
   </si>
   <si>
     <t xml:space="preserve">7.2426700592041</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41089868545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48173141479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14527416229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27365970611572</t>
+    <t xml:space="preserve">7.41089820861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48172998428345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14527368545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27365875244141</t>
   </si>
   <si>
     <t xml:space="preserve">7.1762638092041</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04787921905518</t>
+    <t xml:space="preserve">7.04787874221802</t>
   </si>
   <si>
     <t xml:space="preserve">7.23381519317627</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2913670539856</t>
+    <t xml:space="preserve">7.29136657714844</t>
   </si>
   <si>
     <t xml:space="preserve">7.4286060333252</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83589601516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82704257965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13693428039551</t>
+    <t xml:space="preserve">7.83589649200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82704210281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13693618774414</t>
   </si>
   <si>
     <t xml:space="preserve">8.27860260009766</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32287120819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03120136260986</t>
+    <t xml:space="preserve">8.32287216186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03120231628418</t>
   </si>
   <si>
     <t xml:space="preserve">8.53094577789307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49995613098145</t>
+    <t xml:space="preserve">8.49995517730713</t>
   </si>
   <si>
     <t xml:space="preserve">8.26089382171631</t>
@@ -641,16 +641,16 @@
     <t xml:space="preserve">8.87182807922363</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56245040893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25255393981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02234649658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8541202545166</t>
+    <t xml:space="preserve">9.56244945526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25255298614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02234840393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85411834716797</t>
   </si>
   <si>
     <t xml:space="preserve">8.82755756378174</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">8.71245384216309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98693180084229</t>
+    <t xml:space="preserve">8.98692989349365</t>
   </si>
   <si>
     <t xml:space="preserve">8.8983907699585</t>
@@ -671,40 +671,40 @@
     <t xml:space="preserve">8.72130870819092</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78328609466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67703819274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7567253112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10203266143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82312965393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94266223907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20828533172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43287658691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4598274230957</t>
+    <t xml:space="preserve">8.78328704833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67703723907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75672626495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10203456878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8231315612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94266033172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20828437805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43287563323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45982646942139</t>
   </si>
   <si>
     <t xml:space="preserve">9.52271270751953</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32507419586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38795757293701</t>
+    <t xml:space="preserve">9.32507228851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3879566192627</t>
   </si>
   <si>
     <t xml:space="preserve">9.35202217102051</t>
@@ -713,22 +713,22 @@
     <t xml:space="preserve">9.4238920211792</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29812049865723</t>
+    <t xml:space="preserve">9.29812145233154</t>
   </si>
   <si>
     <t xml:space="preserve">9.55865001678467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67543601989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86409378051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5199041366577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0617341995239</t>
+    <t xml:space="preserve">9.67543697357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86409282684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5199031829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0617351531982</t>
   </si>
   <si>
     <t xml:space="preserve">9.88206100463867</t>
@@ -740,19 +740,19 @@
     <t xml:space="preserve">9.56763172149658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44186115264893</t>
+    <t xml:space="preserve">9.44186019897461</t>
   </si>
   <si>
     <t xml:space="preserve">9.54068088531494</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34304046630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36100578308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50474643707275</t>
+    <t xml:space="preserve">9.34303951263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36100673675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50474452972412</t>
   </si>
   <si>
     <t xml:space="preserve">9.48678016662598</t>
@@ -761,19 +761,19 @@
     <t xml:space="preserve">9.61255073547363</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77425670623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46881103515625</t>
+    <t xml:space="preserve">9.77425765991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46881198883057</t>
   </si>
   <si>
     <t xml:space="preserve">9.54966449737549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4777946472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7023868560791</t>
+    <t xml:space="preserve">9.47779560089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70238780975342</t>
   </si>
   <si>
     <t xml:space="preserve">9.30710506439209</t>
@@ -785,40 +785,40 @@
     <t xml:space="preserve">9.21726703643799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16336536407471</t>
+    <t xml:space="preserve">9.16336631774902</t>
   </si>
   <si>
     <t xml:space="preserve">9.25320434570312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45084476470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58559894561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33405685424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59458255767822</t>
+    <t xml:space="preserve">9.45084285736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58559989929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33405590057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59458446502686</t>
   </si>
   <si>
     <t xml:space="preserve">9.66645336151123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71137142181396</t>
+    <t xml:space="preserve">9.71137237548828</t>
   </si>
   <si>
     <t xml:space="preserve">9.40592575073242</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26218605041504</t>
+    <t xml:space="preserve">9.26218700408936</t>
   </si>
   <si>
     <t xml:space="preserve">9.27116966247559</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28913688659668</t>
+    <t xml:space="preserve">9.289137840271</t>
   </si>
   <si>
     <t xml:space="preserve">9.36999225616455</t>
@@ -833,25 +833,25 @@
     <t xml:space="preserve">9.76527214050293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7203540802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81019020080566</t>
+    <t xml:space="preserve">9.72035598754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81019115447998</t>
   </si>
   <si>
     <t xml:space="preserve">9.37897396087646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90901279449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81917572021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73832321166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78324222564697</t>
+    <t xml:space="preserve">9.909010887146</t